--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -25,6 +25,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETERNAL" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIXON" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COFORGE" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSISTENT" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M&amp;M" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONCOR" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,6 +1390,1254 @@
       </c>
       <c r="N18" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5598.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.64</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5695.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5586</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5543.73</v>
+      </c>
+      <c r="K19" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4934</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>184.53</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>200.53</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4685.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4635.08</v>
+      </c>
+      <c r="K20" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>128</v>
+      </c>
+      <c r="D21" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>130.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>127.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5486.56</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5572</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5486.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5465</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5334.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="D23" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>113.07</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3414</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3436.39</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-22.39</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3436.39</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3410</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3348.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F25" t="n">
+        <v>522</v>
+      </c>
+      <c r="G25" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I25" t="n">
+        <v>510</v>
+      </c>
+      <c r="J25" t="n">
+        <v>500.09</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F26" t="n">
+        <v>367</v>
+      </c>
+      <c r="G26" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I26" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12099</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12088.83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12204</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12195.97</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11999.72</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1474</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1446.53</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2731.16</v>
+      </c>
+      <c r="E29" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2763.74</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2718.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>733.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F30" t="n">
+        <v>743.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>732.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>732</v>
+      </c>
+      <c r="J30" t="n">
+        <v>722.0700000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1216.11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1216.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1199.92</v>
+      </c>
+      <c r="K31" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>800.16</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F32" t="n">
+        <v>814.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>812.45</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="H33" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1160.63</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5330</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5326.11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5424</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5414.12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5315</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5328.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-13.45</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2084.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2111.77</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2103</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2111.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2068.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2062.42</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>609</v>
+      </c>
+      <c r="D36" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F36" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I36" t="n">
+        <v>597</v>
+      </c>
+      <c r="J36" t="n">
+        <v>593.99</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7935</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7824.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8081.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7896.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7935</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2095</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="H38" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2025.82</v>
+      </c>
+      <c r="K38" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1606.52</v>
+      </c>
+      <c r="E39" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1670</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1662.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13967.07</v>
+      </c>
+      <c r="E40" t="n">
+        <v>232.93</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14320.44</v>
+      </c>
+      <c r="H40" t="n">
+        <v>124.56</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J40" t="n">
+        <v>14090.25</v>
+      </c>
+      <c r="K40" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F41" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I41" t="n">
+        <v>310</v>
+      </c>
+      <c r="J41" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1750.26</v>
+      </c>
+      <c r="E42" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1801.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1772.85</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +2651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +2776,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>733.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F3" t="n">
+        <v>743.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>732.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>732</v>
+      </c>
+      <c r="J3" t="n">
+        <v>722.0700000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -1538,7 +2841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,6 +2966,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1160.63</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1676,7 +3031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,6 +3156,58 @@
       </c>
       <c r="N2" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>609</v>
+      </c>
+      <c r="D3" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>597</v>
+      </c>
+      <c r="J3" t="n">
+        <v>593.99</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +3221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1939,6 +3346,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7935</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7824.85</v>
+      </c>
+      <c r="E3" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8081.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7896.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7935</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +3411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,6 +3536,58 @@
       </c>
       <c r="N2" t="n">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2095</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2025.82</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +3601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2215,6 +3726,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1606.52</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1670</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1662.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1635</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>
@@ -2228,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2353,6 +3916,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F3" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I3" t="n">
+        <v>310</v>
+      </c>
+      <c r="J3" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -2366,7 +3981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,6 +4106,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13967.07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>232.93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14320.44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>124.56</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14090.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -2504,6 +4171,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Stock Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Actual Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Predicted Close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variance (Close)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Actual High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Predicted High</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variance (High)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Actual Low</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Predicted Low</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variance (Low)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Live_Signal</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Accuracy_Status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Error_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1771.87</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1821.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-33.67</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1745.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1777</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1750.26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1801.51</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1772.85</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2582,40 +4439,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1777</v>
+        <v>5474</v>
       </c>
       <c r="D2" t="n">
-        <v>1771.87</v>
+        <v>5486.56</v>
       </c>
       <c r="E2" t="n">
-        <v>5.13</v>
+        <v>-12.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1788</v>
+        <v>5572</v>
       </c>
       <c r="G2" t="n">
-        <v>1821.67</v>
+        <v>5486.56</v>
       </c>
       <c r="H2" t="n">
-        <v>-33.67</v>
+        <v>85.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1745.1</v>
+        <v>5465</v>
       </c>
       <c r="J2" t="n">
-        <v>1777</v>
+        <v>5334.6</v>
       </c>
       <c r="K2" t="n">
-        <v>-31.9</v>
+        <v>130.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2628,7 +4485,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -2642,6 +4499,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Stock Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Actual Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Predicted Close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variance (Close)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Actual High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Predicted High</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variance (High)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Actual Low</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Predicted Low</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variance (Low)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Live_Signal</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Accuracy_Status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Error_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="D2" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>113.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="F3" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G3" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>113.07</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2720,44 +4767,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.55</v>
+        <v>3414</v>
       </c>
       <c r="D2" t="n">
-        <v>113.4</v>
+        <v>3436.39</v>
       </c>
       <c r="E2" t="n">
-        <v>0.15</v>
+        <v>-22.39</v>
       </c>
       <c r="F2" t="n">
-        <v>115.2</v>
+        <v>3449</v>
       </c>
       <c r="G2" t="n">
-        <v>113.67</v>
+        <v>3436.39</v>
       </c>
       <c r="H2" t="n">
-        <v>1.53</v>
+        <v>12.61</v>
       </c>
       <c r="I2" t="n">
-        <v>113.3</v>
+        <v>3410</v>
       </c>
       <c r="J2" t="n">
-        <v>112.1</v>
+        <v>3348.98</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2</v>
+        <v>61.02</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2766,7 +4813,145 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Stock Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Actual Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Predicted Close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variance (Close)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Actual High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Predicted High</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variance (High)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Actual Low</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Predicted Low</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variance (Low)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Live_Signal</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Accuracy_Status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Error_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>522</v>
+      </c>
+      <c r="G2" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>510</v>
+      </c>
+      <c r="J2" t="n">
+        <v>500.09</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +4965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2905,6 +5090,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D3" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F3" t="n">
+        <v>130.32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I3" t="n">
+        <v>127.74</v>
+      </c>
+      <c r="J3" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,6 +5280,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5598.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5695.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5586</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5543.73</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
@@ -3056,7 +5345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3181,6 +5470,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1474</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1446.53</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -3194,7 +5535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3319,6 +5660,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>367</v>
+      </c>
+      <c r="G3" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -3332,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +5850,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12099</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12088.83</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12204</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12195.97</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12011</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11999.72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,6 +6040,58 @@
       </c>
       <c r="N2" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4934</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="E3" t="n">
+        <v>184.53</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="H3" t="n">
+        <v>200.53</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4685.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4635.08</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>
@@ -3608,7 +6105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3735,6 +6232,58 @@
         <v>0.04</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2731.16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2763.74</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2718.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Stocks Accuracy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IEX" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALKEM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIPLA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECLTD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ULTRACEMCO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAL" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIANPAINT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDHOTEL" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="360ONE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGEL" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EICHERMOT" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GODREJPROP" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TECHM" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETERNAL" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIXON" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COFORGE" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSISTENT" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M&amp;M" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONCOR" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="All Stocks Accuracy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PNB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IEX" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ALKEM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CIPLA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RECLTD" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ULTRACEMCO" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="HAL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ASIANPAINT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="INDHOTEL" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="360ONE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PGEL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="EICHERMOT" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GODREJPROP" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TECHM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ETERNAL" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="DIXON" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="COFORGE" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="PERSISTENT" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="M&amp;M" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CONCOR" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,39 +1504,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>128</v>
+        <v>5459.5</v>
       </c>
       <c r="D21" t="n">
-        <v>126.34</v>
+        <v>5490.58</v>
       </c>
       <c r="E21" t="n">
-        <v>1.66</v>
+        <v>-31.08</v>
       </c>
       <c r="F21" t="n">
-        <v>130.32</v>
+        <v>5572</v>
       </c>
       <c r="G21" t="n">
-        <v>126.34</v>
+        <v>5490.58</v>
       </c>
       <c r="H21" t="n">
-        <v>3.98</v>
+        <v>81.42</v>
       </c>
       <c r="I21" t="n">
-        <v>127.74</v>
+        <v>5459.5</v>
       </c>
       <c r="J21" t="n">
-        <v>124.36</v>
+        <v>5302.29</v>
       </c>
       <c r="K21" t="n">
-        <v>3.38</v>
+        <v>157.21</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
@@ -1556,39 +1556,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5474</v>
+        <v>128.83</v>
       </c>
       <c r="D22" t="n">
-        <v>5486.56</v>
+        <v>131.57</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.56</v>
+        <v>-2.74</v>
       </c>
       <c r="F22" t="n">
-        <v>5572</v>
+        <v>130.32</v>
       </c>
       <c r="G22" t="n">
-        <v>5486.56</v>
+        <v>131.57</v>
       </c>
       <c r="H22" t="n">
-        <v>85.44</v>
+        <v>-1.25</v>
       </c>
       <c r="I22" t="n">
-        <v>5465</v>
+        <v>127.74</v>
       </c>
       <c r="J22" t="n">
-        <v>5334.6</v>
+        <v>124.83</v>
       </c>
       <c r="K22" t="n">
-        <v>130.4</v>
+        <v>2.91</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.23</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="23">
@@ -1612,31 +1612,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>114.44</v>
+        <v>114.3</v>
       </c>
       <c r="D23" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.37</v>
+        <v>-0.54</v>
       </c>
       <c r="F23" t="n">
         <v>114.85</v>
       </c>
       <c r="G23" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="H23" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I23" t="n">
         <v>113.2</v>
       </c>
       <c r="J23" t="n">
-        <v>113.07</v>
+        <v>112.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="24">
@@ -1664,31 +1664,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="D24" t="n">
-        <v>3436.39</v>
+        <v>3410.87</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.39</v>
+        <v>-4.87</v>
       </c>
       <c r="F24" t="n">
         <v>3449</v>
       </c>
       <c r="G24" t="n">
-        <v>3436.39</v>
+        <v>3416.49</v>
       </c>
       <c r="H24" t="n">
-        <v>12.61</v>
+        <v>32.51</v>
       </c>
       <c r="I24" t="n">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="J24" t="n">
-        <v>3348.98</v>
+        <v>3329.27</v>
       </c>
       <c r="K24" t="n">
-        <v>61.02</v>
+        <v>76.73</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="25">
@@ -1716,31 +1716,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>511.5</v>
+        <v>512</v>
       </c>
       <c r="D25" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.25</v>
+        <v>-3.85</v>
       </c>
       <c r="F25" t="n">
         <v>522</v>
       </c>
       <c r="G25" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="H25" t="n">
-        <v>10.25</v>
+        <v>6.15</v>
       </c>
       <c r="I25" t="n">
         <v>510</v>
       </c>
       <c r="J25" t="n">
-        <v>500.09</v>
+        <v>499.14</v>
       </c>
       <c r="K25" t="n">
-        <v>9.91</v>
+        <v>10.86</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26">
@@ -1768,31 +1768,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>363.3</v>
+        <v>361.5</v>
       </c>
       <c r="D26" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.16</v>
+        <v>-2.73</v>
       </c>
       <c r="F26" t="n">
         <v>367</v>
       </c>
       <c r="G26" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="H26" t="n">
-        <v>3.54</v>
+        <v>2.77</v>
       </c>
       <c r="I26" t="n">
-        <v>361.6</v>
+        <v>361.5</v>
       </c>
       <c r="J26" t="n">
-        <v>357.14</v>
+        <v>354.29</v>
       </c>
       <c r="K26" t="n">
-        <v>4.46</v>
+        <v>7.21</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.04</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -1820,31 +1820,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12099</v>
+        <v>12190</v>
       </c>
       <c r="D27" t="n">
-        <v>12088.83</v>
+        <v>12181.82</v>
       </c>
       <c r="E27" t="n">
-        <v>10.17</v>
+        <v>8.18</v>
       </c>
       <c r="F27" t="n">
-        <v>12204</v>
+        <v>12239</v>
       </c>
       <c r="G27" t="n">
-        <v>12195.97</v>
+        <v>12246.74</v>
       </c>
       <c r="H27" t="n">
-        <v>8.029999999999999</v>
+        <v>-7.74</v>
       </c>
       <c r="I27" t="n">
-        <v>12011</v>
+        <v>11970</v>
       </c>
       <c r="J27" t="n">
-        <v>11999.72</v>
+        <v>11938.81</v>
       </c>
       <c r="K27" t="n">
-        <v>11.28</v>
+        <v>31.19</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1872,31 +1872,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="D28" t="n">
-        <v>1486.61</v>
+        <v>1476.19</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F28" t="n">
         <v>1488.1</v>
       </c>
       <c r="G28" t="n">
-        <v>1486.61</v>
+        <v>1483.21</v>
       </c>
       <c r="H28" t="n">
-        <v>1.49</v>
+        <v>4.89</v>
       </c>
       <c r="I28" t="n">
         <v>1461</v>
       </c>
       <c r="J28" t="n">
-        <v>1446.53</v>
+        <v>1445.41</v>
       </c>
       <c r="K28" t="n">
-        <v>14.47</v>
+        <v>15.59</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29">
@@ -1927,28 +1927,28 @@
         <v>2755</v>
       </c>
       <c r="D29" t="n">
-        <v>2731.16</v>
+        <v>2801.28</v>
       </c>
       <c r="E29" t="n">
-        <v>23.84</v>
+        <v>-46.28</v>
       </c>
       <c r="F29" t="n">
         <v>2788</v>
       </c>
       <c r="G29" t="n">
-        <v>2763.74</v>
+        <v>2801.28</v>
       </c>
       <c r="H29" t="n">
-        <v>24.26</v>
+        <v>-13.28</v>
       </c>
       <c r="I29" t="n">
         <v>2741.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2718.8</v>
+        <v>2710.9</v>
       </c>
       <c r="K29" t="n">
-        <v>22.8</v>
+        <v>30.7</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.87</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="30">
@@ -1976,31 +1976,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>733.9</v>
+        <v>736</v>
       </c>
       <c r="D30" t="n">
-        <v>732.24</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.66</v>
+        <v>-7.57</v>
       </c>
       <c r="F30" t="n">
         <v>743.8</v>
       </c>
       <c r="G30" t="n">
-        <v>732.9</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>10.9</v>
+        <v>0.23</v>
       </c>
       <c r="I30" t="n">
         <v>732</v>
       </c>
       <c r="J30" t="n">
-        <v>722.0700000000001</v>
+        <v>722.08</v>
       </c>
       <c r="K30" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.23</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="31">
@@ -2024,35 +2024,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1232.1</v>
+        <v>799.45</v>
       </c>
       <c r="D31" t="n">
-        <v>1216.11</v>
+        <v>805.13</v>
       </c>
       <c r="E31" t="n">
-        <v>15.99</v>
+        <v>-5.68</v>
       </c>
       <c r="F31" t="n">
-        <v>1257</v>
+        <v>814.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1216.32</v>
+        <v>817.6</v>
       </c>
       <c r="H31" t="n">
-        <v>40.68</v>
+        <v>-3.05</v>
       </c>
       <c r="I31" t="n">
-        <v>1229.5</v>
+        <v>798.25</v>
       </c>
       <c r="J31" t="n">
-        <v>1199.92</v>
+        <v>797.28</v>
       </c>
       <c r="K31" t="n">
-        <v>29.58</v>
+        <v>0.97</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="32">
@@ -2076,35 +2076,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>799.45</v>
+        <v>1186</v>
       </c>
       <c r="D32" t="n">
-        <v>800.16</v>
+        <v>1194.33</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.71</v>
+        <v>-8.33</v>
       </c>
       <c r="F32" t="n">
-        <v>814.55</v>
+        <v>1197</v>
       </c>
       <c r="G32" t="n">
-        <v>812.45</v>
+        <v>1194.33</v>
       </c>
       <c r="H32" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="I32" t="n">
-        <v>798.25</v>
+        <v>1180.9</v>
       </c>
       <c r="J32" t="n">
-        <v>799.45</v>
+        <v>1157.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.2</v>
+        <v>23.63</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -2128,35 +2128,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1186</v>
+        <v>5318.5</v>
       </c>
       <c r="D33" t="n">
-        <v>1187.15</v>
+        <v>5364.96</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.15</v>
+        <v>-46.46</v>
       </c>
       <c r="F33" t="n">
-        <v>1197</v>
+        <v>5424</v>
       </c>
       <c r="G33" t="n">
-        <v>1187.15</v>
+        <v>5434.76</v>
       </c>
       <c r="H33" t="n">
-        <v>9.85</v>
+        <v>-10.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1180.9</v>
+        <v>5315</v>
       </c>
       <c r="J33" t="n">
-        <v>1160.63</v>
+        <v>5299.51</v>
       </c>
       <c r="K33" t="n">
-        <v>20.27</v>
+        <v>15.49</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.1</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="34">
@@ -2180,35 +2180,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5330</v>
+        <v>1240</v>
       </c>
       <c r="D34" t="n">
-        <v>5326.11</v>
+        <v>1266.36</v>
       </c>
       <c r="E34" t="n">
-        <v>3.89</v>
+        <v>-26.36</v>
       </c>
       <c r="F34" t="n">
-        <v>5424</v>
+        <v>1257</v>
       </c>
       <c r="G34" t="n">
-        <v>5414.12</v>
+        <v>1266.36</v>
       </c>
       <c r="H34" t="n">
-        <v>9.880000000000001</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>5315</v>
+        <v>1229.5</v>
       </c>
       <c r="J34" t="n">
-        <v>5328.45</v>
+        <v>1204.38</v>
       </c>
       <c r="K34" t="n">
-        <v>-13.45</v>
+        <v>25.12</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="35">
@@ -2236,31 +2236,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2084.5</v>
+        <v>2086</v>
       </c>
       <c r="D35" t="n">
-        <v>2111.77</v>
+        <v>2075.54</v>
       </c>
       <c r="E35" t="n">
-        <v>-27.27</v>
+        <v>10.46</v>
       </c>
       <c r="F35" t="n">
-        <v>2103</v>
+        <v>2118.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2111.77</v>
+        <v>2111.58</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.77</v>
+        <v>6.92</v>
       </c>
       <c r="I35" t="n">
-        <v>2068.6</v>
+        <v>2076.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2062.42</v>
+        <v>2058.35</v>
       </c>
       <c r="K35" t="n">
-        <v>6.18</v>
+        <v>17.75</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>609</v>
+        <v>609.75</v>
       </c>
       <c r="D36" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>3.65</v>
+        <v>-7.57</v>
       </c>
       <c r="F36" t="n">
         <v>616.2</v>
       </c>
       <c r="G36" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>10.85</v>
+        <v>-1.12</v>
       </c>
       <c r="I36" t="n">
         <v>597</v>
       </c>
       <c r="J36" t="n">
-        <v>593.99</v>
+        <v>591.96</v>
       </c>
       <c r="K36" t="n">
-        <v>3.01</v>
+        <v>5.04</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.6</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="37">
@@ -2340,31 +2340,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7935</v>
+        <v>7986.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7824.85</v>
+        <v>8149.04</v>
       </c>
       <c r="E37" t="n">
-        <v>110.15</v>
+        <v>-162.54</v>
       </c>
       <c r="F37" t="n">
-        <v>8044</v>
+        <v>8019</v>
       </c>
       <c r="G37" t="n">
-        <v>8081.8</v>
+        <v>8168.44</v>
       </c>
       <c r="H37" t="n">
-        <v>-37.8</v>
+        <v>-149.44</v>
       </c>
       <c r="I37" t="n">
-        <v>7896.5</v>
+        <v>7905.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7935</v>
+        <v>7966.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.5</v>
+        <v>-60.59</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="38">
@@ -2392,31 +2392,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2095</v>
+        <v>2081.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="E38" t="n">
-        <v>35.08</v>
+        <v>-52.4</v>
       </c>
       <c r="F38" t="n">
         <v>2109</v>
       </c>
       <c r="G38" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="H38" t="n">
-        <v>49.08</v>
+        <v>-25.3</v>
       </c>
       <c r="I38" t="n">
         <v>2072.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2025.82</v>
+        <v>2006.73</v>
       </c>
       <c r="K38" t="n">
-        <v>46.38</v>
+        <v>65.47</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="39">
@@ -2444,31 +2444,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D39" t="n">
-        <v>1606.52</v>
+        <v>1674.43</v>
       </c>
       <c r="E39" t="n">
-        <v>28.48</v>
+        <v>-24.43</v>
       </c>
       <c r="F39" t="n">
-        <v>1670</v>
+        <v>1664.8</v>
       </c>
       <c r="G39" t="n">
-        <v>1662.3</v>
+        <v>1674.43</v>
       </c>
       <c r="H39" t="n">
-        <v>7.7</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="J39" t="n">
-        <v>1635</v>
+        <v>1627.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-4</v>
+        <v>11.16</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="40">
@@ -2496,31 +2496,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14200</v>
+        <v>14310</v>
       </c>
       <c r="D40" t="n">
-        <v>13967.07</v>
+        <v>14552.35</v>
       </c>
       <c r="E40" t="n">
-        <v>232.93</v>
+        <v>-242.35</v>
       </c>
       <c r="F40" t="n">
-        <v>14445</v>
+        <v>14395</v>
       </c>
       <c r="G40" t="n">
-        <v>14320.44</v>
+        <v>14552.35</v>
       </c>
       <c r="H40" t="n">
-        <v>124.56</v>
+        <v>-157.35</v>
       </c>
       <c r="I40" t="n">
-        <v>14137</v>
+        <v>14023</v>
       </c>
       <c r="J40" t="n">
-        <v>14090.25</v>
+        <v>14049.2</v>
       </c>
       <c r="K40" t="n">
-        <v>46.75</v>
+        <v>-26.2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2548,31 +2548,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>316.5</v>
+        <v>316.25</v>
       </c>
       <c r="D41" t="n">
-        <v>317.34</v>
+        <v>317.64</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.84</v>
+        <v>-1.39</v>
       </c>
       <c r="F41" t="n">
         <v>319.7</v>
       </c>
       <c r="G41" t="n">
-        <v>321.23</v>
+        <v>322.58</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.53</v>
+        <v>-2.88</v>
       </c>
       <c r="I41" t="n">
         <v>310</v>
       </c>
       <c r="J41" t="n">
-        <v>316.14</v>
+        <v>314.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.14</v>
+        <v>-4.55</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="42">
@@ -2600,44 +2600,2384 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1778</v>
+        <v>1772.8</v>
       </c>
       <c r="D42" t="n">
-        <v>1750.26</v>
+        <v>1815.3</v>
       </c>
       <c r="E42" t="n">
-        <v>27.74</v>
+        <v>-42.5</v>
       </c>
       <c r="F42" t="n">
         <v>1813.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1801.51</v>
+        <v>1815.3</v>
       </c>
       <c r="H42" t="n">
-        <v>12.39</v>
+        <v>-1.4</v>
       </c>
       <c r="I42" t="n">
         <v>1757.9</v>
       </c>
       <c r="J42" t="n">
-        <v>1772.85</v>
+        <v>1760.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-14.95</v>
+        <v>-2.74</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5459.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-28.06</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5572</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="H43" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5459.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5382.37</v>
+      </c>
+      <c r="K43" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>1.58</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="D44" t="n">
+        <v>276.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F44" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>277.41</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I44" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>275.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5587.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5542.31</v>
+      </c>
+      <c r="E45" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5685.32</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5631.66</v>
+      </c>
+      <c r="H45" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5576.02</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5543.83</v>
+      </c>
+      <c r="K45" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F46" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G46" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I46" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>512</v>
+      </c>
+      <c r="D47" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F47" t="n">
+        <v>522</v>
+      </c>
+      <c r="G47" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="H47" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="I47" t="n">
+        <v>510</v>
+      </c>
+      <c r="J47" t="n">
+        <v>493.14</v>
+      </c>
+      <c r="K47" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12075</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12210.02</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-135.02</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12204</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12256.51</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-52.51</v>
+      </c>
+      <c r="I48" t="n">
+        <v>12011</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12069.81</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-58.81</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1477</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1435.23</v>
+      </c>
+      <c r="K49" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2086</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2035.18</v>
+      </c>
+      <c r="E50" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2103</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2035.18</v>
+      </c>
+      <c r="H50" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2068.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1971.08</v>
+      </c>
+      <c r="K50" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3406</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3524.97</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-118.97</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3526.89</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-77.89</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3406</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3472.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-66.5</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>367.17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="F52" t="n">
+        <v>367</v>
+      </c>
+      <c r="G52" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I52" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2711.34</v>
+      </c>
+      <c r="E53" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2748.63</v>
+      </c>
+      <c r="H53" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2706.05</v>
+      </c>
+      <c r="K53" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="D54" t="n">
+        <v>788.2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F54" t="n">
+        <v>814.55</v>
+      </c>
+      <c r="G54" t="n">
+        <v>788.2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I54" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="J54" t="n">
+        <v>774.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1169.23</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1170.66</v>
+      </c>
+      <c r="H55" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1152.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1209.39</v>
+      </c>
+      <c r="E56" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1222.15</v>
+      </c>
+      <c r="H56" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1202.88</v>
+      </c>
+      <c r="K56" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5318.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5329.11</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-10.61</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5424</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5348.56</v>
+      </c>
+      <c r="H57" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5315</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5265.31</v>
+      </c>
+      <c r="K57" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2081.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="E58" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="H58" t="n">
+        <v>73.67</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2001.43</v>
+      </c>
+      <c r="K58" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>7967.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7948.47</v>
+      </c>
+      <c r="E59" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8169.85</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-125.85</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7896.5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>8020</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-123.5</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1632.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1624.03</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1670</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1653.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1628.55</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>609.75</v>
+      </c>
+      <c r="D61" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-18.16</v>
+      </c>
+      <c r="F61" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="I61" t="n">
+        <v>597</v>
+      </c>
+      <c r="J61" t="n">
+        <v>616.61</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-19.61</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>316.13</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F62" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G62" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I62" t="n">
+        <v>310</v>
+      </c>
+      <c r="J62" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14075.28</v>
+      </c>
+      <c r="E63" t="n">
+        <v>124.72</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14183.21</v>
+      </c>
+      <c r="H63" t="n">
+        <v>261.79</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J63" t="n">
+        <v>13960.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>176.62</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1772.8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1748.3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1781.99</v>
+      </c>
+      <c r="H64" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1754.28</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4075.67</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4171.64</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-91.64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4025.8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4039.37</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-13.57</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3425.49</v>
+      </c>
+      <c r="E66" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3534.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3518.57</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3491.1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3423.59</v>
+      </c>
+      <c r="K66" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F67" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="G67" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I67" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>111.89</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5489.59</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-15.59</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5543.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5564.29</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-20.79</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5425</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5386.73</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1661.44</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1665.9</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1680.86</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1627.71</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5333.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5365.47</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-31.97</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5355</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5428.65</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-73.65000000000001</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5297</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5255.68</v>
+      </c>
+      <c r="K70" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1467.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1480.12</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-12.42</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1483.7</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1483.16</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1462</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1435.54</v>
+      </c>
+      <c r="K71" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-40.04</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1822.6</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-27.44</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1783.1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1779.32</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-66.63</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2761.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-55.13</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2713.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2713.72</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1337.1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1298.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1337.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-38.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1236.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1282</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-45.3</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>621.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>608.64</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>630.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>635.02</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I75" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>614.85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="D76" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F76" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="G76" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="I76" t="n">
+        <v>179.94</v>
+      </c>
+      <c r="J76" t="n">
+        <v>181.03</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7975</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8058.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-83.01000000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8024</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8202.75</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-178.75</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7938</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7944.32</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1940.93</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1959</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1991.14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-32.14</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1928.16</v>
+      </c>
+      <c r="K78" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>789.45</v>
+      </c>
+      <c r="D79" t="n">
+        <v>807.13</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-17.68</v>
+      </c>
+      <c r="F79" t="n">
+        <v>798.4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>807.13</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="I79" t="n">
+        <v>780.05</v>
+      </c>
+      <c r="J79" t="n">
+        <v>776.51</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>280</v>
+      </c>
+      <c r="D80" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="F80" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="I80" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>273.61</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12038</v>
+      </c>
+      <c r="D81" t="n">
+        <v>12000.09</v>
+      </c>
+      <c r="E81" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12124</v>
+      </c>
+      <c r="G81" t="n">
+        <v>12345.48</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-221.48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>11921</v>
+      </c>
+      <c r="J81" t="n">
+        <v>11955.31</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-34.31</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1175.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-26.39</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1161.7</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1148.12</v>
+      </c>
+      <c r="K82" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2108.4</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-65.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-53.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2057.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2031.51</v>
+      </c>
+      <c r="K83" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="D84" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="G84" t="n">
+        <v>317.62</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I84" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>307.57</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2021.3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2088.35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2037.1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2088.35</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-51.25</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1968.33</v>
+      </c>
+      <c r="K85" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>14115</v>
+      </c>
+      <c r="D86" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-238.98</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14271</v>
+      </c>
+      <c r="G86" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="I86" t="n">
+        <v>14001</v>
+      </c>
+      <c r="J86" t="n">
+        <v>13803.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="D87" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="F87" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I87" t="n">
+        <v>498.25</v>
+      </c>
+      <c r="J87" t="n">
+        <v>487.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>
@@ -2790,31 +5130,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>733.9</v>
+        <v>736</v>
       </c>
       <c r="D3" t="n">
-        <v>732.24</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>1.66</v>
+        <v>-7.57</v>
       </c>
       <c r="F3" t="n">
         <v>743.8</v>
       </c>
       <c r="G3" t="n">
-        <v>732.9</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>10.9</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="n">
         <v>732</v>
       </c>
       <c r="J3" t="n">
-        <v>722.0700000000001</v>
+        <v>722.08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2827,7 +5167,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.23</v>
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>
@@ -2841,7 +5181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2983,28 +5323,28 @@
         <v>1186</v>
       </c>
       <c r="D3" t="n">
-        <v>1187.15</v>
+        <v>1194.33</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.15</v>
+        <v>-8.33</v>
       </c>
       <c r="F3" t="n">
         <v>1197</v>
       </c>
       <c r="G3" t="n">
-        <v>1187.15</v>
+        <v>1194.33</v>
       </c>
       <c r="H3" t="n">
-        <v>9.85</v>
+        <v>2.67</v>
       </c>
       <c r="I3" t="n">
         <v>1180.9</v>
       </c>
       <c r="J3" t="n">
-        <v>1160.63</v>
+        <v>1157.27</v>
       </c>
       <c r="K3" t="n">
-        <v>20.27</v>
+        <v>23.63</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3017,7 +5357,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1169.23</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1170.66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1152.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1175.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-26.39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1161.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1148.12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -3031,7 +5475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,31 +5614,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>609</v>
+        <v>609.75</v>
       </c>
       <c r="D3" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.65</v>
+        <v>-7.57</v>
       </c>
       <c r="F3" t="n">
         <v>616.2</v>
       </c>
       <c r="G3" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>10.85</v>
+        <v>-1.12</v>
       </c>
       <c r="I3" t="n">
         <v>597</v>
       </c>
       <c r="J3" t="n">
-        <v>593.99</v>
+        <v>591.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.01</v>
+        <v>5.04</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3207,7 +5651,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>609.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-18.16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="I4" t="n">
+        <v>597</v>
+      </c>
+      <c r="J4" t="n">
+        <v>616.61</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-19.61</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>621.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>608.64</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>630.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>635.02</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>614.85</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
@@ -3221,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,44 +5908,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7935</v>
+        <v>7986.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7824.85</v>
+        <v>8149.04</v>
       </c>
       <c r="E3" t="n">
-        <v>110.15</v>
+        <v>-162.54</v>
       </c>
       <c r="F3" t="n">
+        <v>8019</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8168.44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-149.44</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7905.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7966.09</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-60.59</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7967.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7948.47</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="F4" t="n">
         <v>8044</v>
       </c>
-      <c r="G3" t="n">
-        <v>8081.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-37.8</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G4" t="n">
+        <v>8169.85</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-125.85</v>
+      </c>
+      <c r="I4" t="n">
         <v>7896.5</v>
       </c>
-      <c r="J3" t="n">
-        <v>7935</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="J4" t="n">
+        <v>8020</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-123.5</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.41</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7975</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8058.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.01000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8024</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8202.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-178.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7938</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7944.32</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -3411,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3550,31 +6202,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2095</v>
+        <v>2081.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="E3" t="n">
-        <v>35.08</v>
+        <v>-52.4</v>
       </c>
       <c r="F3" t="n">
         <v>2109</v>
       </c>
       <c r="G3" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="H3" t="n">
-        <v>49.08</v>
+        <v>-25.3</v>
       </c>
       <c r="I3" t="n">
         <v>2072.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2025.82</v>
+        <v>2006.73</v>
       </c>
       <c r="K3" t="n">
-        <v>46.38</v>
+        <v>65.47</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3587,7 +6239,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2081.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="H4" t="n">
+        <v>73.67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2001.43</v>
+      </c>
+      <c r="K4" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2108.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-65.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-53.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2057.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2031.51</v>
+      </c>
+      <c r="K5" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>3.01</v>
       </c>
     </row>
   </sheetData>
@@ -3601,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3740,44 +6496,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D3" t="n">
-        <v>1606.52</v>
+        <v>1674.43</v>
       </c>
       <c r="E3" t="n">
-        <v>28.48</v>
+        <v>-24.43</v>
       </c>
       <c r="F3" t="n">
+        <v>1664.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1674.43</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1639</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1627.84</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1632.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1624.03</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="F4" t="n">
         <v>1670</v>
       </c>
-      <c r="G3" t="n">
-        <v>1662.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G4" t="n">
+        <v>1653.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1631</v>
       </c>
-      <c r="J3" t="n">
-        <v>1635</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.77</v>
+      <c r="J4" t="n">
+        <v>1628.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1661.44</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1665.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1680.86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1627.71</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -3791,7 +6651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3930,31 +6790,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>316.5</v>
+        <v>316.25</v>
       </c>
       <c r="D3" t="n">
-        <v>317.34</v>
+        <v>317.64</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.84</v>
+        <v>-1.39</v>
       </c>
       <c r="F3" t="n">
         <v>319.7</v>
       </c>
       <c r="G3" t="n">
-        <v>321.23</v>
+        <v>322.58</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.53</v>
+        <v>-2.88</v>
       </c>
       <c r="I3" t="n">
         <v>310</v>
       </c>
       <c r="J3" t="n">
-        <v>316.14</v>
+        <v>314.55</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.14</v>
+        <v>-4.55</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3967,7 +6827,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>316.13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I4" t="n">
+        <v>310</v>
+      </c>
+      <c r="J4" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>317.62</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I5" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>307.57</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -3981,7 +6945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4120,31 +7084,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14200</v>
+        <v>14310</v>
       </c>
       <c r="D3" t="n">
-        <v>13967.07</v>
+        <v>14552.35</v>
       </c>
       <c r="E3" t="n">
-        <v>232.93</v>
+        <v>-242.35</v>
       </c>
       <c r="F3" t="n">
-        <v>14445</v>
+        <v>14395</v>
       </c>
       <c r="G3" t="n">
-        <v>14320.44</v>
+        <v>14552.35</v>
       </c>
       <c r="H3" t="n">
-        <v>124.56</v>
+        <v>-157.35</v>
       </c>
       <c r="I3" t="n">
-        <v>14137</v>
+        <v>14023</v>
       </c>
       <c r="J3" t="n">
-        <v>14090.25</v>
+        <v>14049.2</v>
       </c>
       <c r="K3" t="n">
-        <v>46.75</v>
+        <v>-26.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4158,6 +7122,110 @@
       </c>
       <c r="N3" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14075.28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>124.72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14183.21</v>
+      </c>
+      <c r="H4" t="n">
+        <v>261.79</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13960.38</v>
+      </c>
+      <c r="K4" t="n">
+        <v>176.62</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14115</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-238.98</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14271</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13803.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1.66</v>
       </c>
     </row>
   </sheetData>
@@ -4171,7 +7239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,44 +7378,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1778</v>
+        <v>1772.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1750.26</v>
+        <v>1815.3</v>
       </c>
       <c r="E3" t="n">
-        <v>27.74</v>
+        <v>-42.5</v>
       </c>
       <c r="F3" t="n">
         <v>1813.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1801.51</v>
+        <v>1815.3</v>
       </c>
       <c r="H3" t="n">
-        <v>12.39</v>
+        <v>-1.4</v>
       </c>
       <c r="I3" t="n">
         <v>1757.9</v>
       </c>
       <c r="J3" t="n">
-        <v>1772.85</v>
+        <v>1760.64</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.95</v>
+        <v>-2.74</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1772.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1748.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1781.99</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1754.28</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.58</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-40.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1822.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-27.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1783.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1779.32</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
@@ -4361,7 +7533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4448,31 +7620,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5474</v>
+        <v>5459.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5486.56</v>
+        <v>5490.58</v>
       </c>
       <c r="E2" t="n">
-        <v>-12.56</v>
+        <v>-31.08</v>
       </c>
       <c r="F2" t="n">
         <v>5572</v>
       </c>
       <c r="G2" t="n">
-        <v>5486.56</v>
+        <v>5490.58</v>
       </c>
       <c r="H2" t="n">
-        <v>85.44</v>
+        <v>81.42</v>
       </c>
       <c r="I2" t="n">
-        <v>5465</v>
+        <v>5459.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5334.6</v>
+        <v>5302.29</v>
       </c>
       <c r="K2" t="n">
-        <v>130.4</v>
+        <v>157.21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4485,7 +7657,111 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.23</v>
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5459.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-28.06</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5572</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="H3" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5459.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5382.37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5489.59</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-15.59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5543.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5564.29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-20.79</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5425</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5386.73</v>
+      </c>
+      <c r="K4" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -4499,7 +7775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4638,31 +7914,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>114.44</v>
+        <v>114.3</v>
       </c>
       <c r="D3" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.37</v>
+        <v>-0.54</v>
       </c>
       <c r="F3" t="n">
         <v>114.85</v>
       </c>
       <c r="G3" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>113.2</v>
       </c>
       <c r="J3" t="n">
-        <v>113.07</v>
+        <v>112.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4675,7 +7951,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F4" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>111.89</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -4689,7 +8069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4776,31 +8156,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="D2" t="n">
-        <v>3436.39</v>
+        <v>3410.87</v>
       </c>
       <c r="E2" t="n">
-        <v>-22.39</v>
+        <v>-4.87</v>
       </c>
       <c r="F2" t="n">
         <v>3449</v>
       </c>
       <c r="G2" t="n">
-        <v>3436.39</v>
+        <v>3416.49</v>
       </c>
       <c r="H2" t="n">
-        <v>12.61</v>
+        <v>32.51</v>
       </c>
       <c r="I2" t="n">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="J2" t="n">
-        <v>3348.98</v>
+        <v>3329.27</v>
       </c>
       <c r="K2" t="n">
-        <v>61.02</v>
+        <v>76.73</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4813,7 +8193,111 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3406</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3524.97</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-118.97</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3526.89</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-77.89</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3406</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3472.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-66.5</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3425.49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3534.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3518.57</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3491.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3423.59</v>
+      </c>
+      <c r="K4" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>
@@ -4827,7 +8311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4914,31 +8398,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>511.5</v>
+        <v>512</v>
       </c>
       <c r="D2" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.25</v>
+        <v>-3.85</v>
       </c>
       <c r="F2" t="n">
         <v>522</v>
       </c>
       <c r="G2" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="H2" t="n">
-        <v>10.25</v>
+        <v>6.15</v>
       </c>
       <c r="I2" t="n">
         <v>510</v>
       </c>
       <c r="J2" t="n">
-        <v>500.09</v>
+        <v>499.14</v>
       </c>
       <c r="K2" t="n">
-        <v>9.91</v>
+        <v>10.86</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4951,7 +8435,111 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>512</v>
+      </c>
+      <c r="D3" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F3" t="n">
+        <v>522</v>
+      </c>
+      <c r="G3" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="I3" t="n">
+        <v>510</v>
+      </c>
+      <c r="J3" t="n">
+        <v>493.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I4" t="n">
+        <v>498.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>487.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>
@@ -5104,31 +8692,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>128</v>
+        <v>128.83</v>
       </c>
       <c r="D3" t="n">
-        <v>126.34</v>
+        <v>131.57</v>
       </c>
       <c r="E3" t="n">
-        <v>1.66</v>
+        <v>-2.74</v>
       </c>
       <c r="F3" t="n">
         <v>130.32</v>
       </c>
       <c r="G3" t="n">
-        <v>126.34</v>
+        <v>131.57</v>
       </c>
       <c r="H3" t="n">
-        <v>3.98</v>
+        <v>-1.25</v>
       </c>
       <c r="I3" t="n">
         <v>127.74</v>
       </c>
       <c r="J3" t="n">
-        <v>124.36</v>
+        <v>124.83</v>
       </c>
       <c r="K3" t="n">
-        <v>3.38</v>
+        <v>2.91</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -5141,7 +8729,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>
@@ -5155,7 +8743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5332,6 +8920,58 @@
       </c>
       <c r="N3" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5587.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5542.31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5685.32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5631.66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5576.02</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5543.83</v>
+      </c>
+      <c r="K4" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -5345,7 +8985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5484,31 +9124,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="D3" t="n">
-        <v>1486.61</v>
+        <v>1476.19</v>
       </c>
       <c r="E3" t="n">
-        <v>-12.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>1488.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1486.61</v>
+        <v>1483.21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.49</v>
+        <v>4.89</v>
       </c>
       <c r="I3" t="n">
         <v>1461</v>
       </c>
       <c r="J3" t="n">
-        <v>1446.53</v>
+        <v>1445.41</v>
       </c>
       <c r="K3" t="n">
-        <v>14.47</v>
+        <v>15.59</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -5521,7 +9161,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1477</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1435.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1467.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1480.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-12.42</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1483.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1483.16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1462</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1435.54</v>
+      </c>
+      <c r="K5" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -5535,7 +9279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5674,31 +9418,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>363.3</v>
+        <v>361.5</v>
       </c>
       <c r="D3" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.16</v>
+        <v>-2.73</v>
       </c>
       <c r="F3" t="n">
         <v>367</v>
       </c>
       <c r="G3" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="H3" t="n">
-        <v>3.54</v>
+        <v>2.77</v>
       </c>
       <c r="I3" t="n">
-        <v>361.6</v>
+        <v>361.5</v>
       </c>
       <c r="J3" t="n">
-        <v>357.14</v>
+        <v>354.29</v>
       </c>
       <c r="K3" t="n">
-        <v>4.46</v>
+        <v>7.21</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -5711,7 +9455,59 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.04</v>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>367.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>367</v>
+      </c>
+      <c r="G4" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I4" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -5725,7 +9521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5864,44 +9660,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12099</v>
+        <v>12190</v>
       </c>
       <c r="D3" t="n">
-        <v>12088.83</v>
+        <v>12181.82</v>
       </c>
       <c r="E3" t="n">
-        <v>10.17</v>
+        <v>8.18</v>
       </c>
       <c r="F3" t="n">
+        <v>12239</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12246.74</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11970</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11938.81</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12075</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12210.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-135.02</v>
+      </c>
+      <c r="F4" t="n">
         <v>12204</v>
       </c>
-      <c r="G3" t="n">
-        <v>12195.97</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G4" t="n">
+        <v>12256.51</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-52.51</v>
+      </c>
+      <c r="I4" t="n">
         <v>12011</v>
       </c>
-      <c r="J3" t="n">
-        <v>11999.72</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="J4" t="n">
+        <v>12069.81</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-58.81</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12038</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12000.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12124</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12345.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-221.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11921</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11955.31</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-34.31</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.08</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -6105,7 +10005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6247,28 +10147,28 @@
         <v>2755</v>
       </c>
       <c r="D3" t="n">
-        <v>2731.16</v>
+        <v>2801.28</v>
       </c>
       <c r="E3" t="n">
-        <v>23.84</v>
+        <v>-46.28</v>
       </c>
       <c r="F3" t="n">
         <v>2788</v>
       </c>
       <c r="G3" t="n">
-        <v>2763.74</v>
+        <v>2801.28</v>
       </c>
       <c r="H3" t="n">
-        <v>24.26</v>
+        <v>-13.28</v>
       </c>
       <c r="I3" t="n">
         <v>2741.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2718.8</v>
+        <v>2710.9</v>
       </c>
       <c r="K3" t="n">
-        <v>22.8</v>
+        <v>30.7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -6281,7 +10181,111 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.87</v>
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2711.34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2748.63</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2706.05</v>
+      </c>
+      <c r="K4" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-66.63</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2761.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-55.13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2713.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2713.72</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -3796,31 +3796,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4080</v>
+        <v>4056</v>
       </c>
       <c r="D65" t="n">
         <v>4075.67</v>
       </c>
       <c r="E65" t="n">
-        <v>4.33</v>
+        <v>-19.67</v>
       </c>
       <c r="F65" t="n">
-        <v>4080</v>
+        <v>4062</v>
       </c>
       <c r="G65" t="n">
         <v>4171.64</v>
       </c>
       <c r="H65" t="n">
-        <v>-91.64</v>
+        <v>-109.64</v>
       </c>
       <c r="I65" t="n">
-        <v>4025.8</v>
+        <v>4030</v>
       </c>
       <c r="J65" t="n">
         <v>4039.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-13.57</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="66">
@@ -3848,31 +3848,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3517</v>
+        <v>3502</v>
       </c>
       <c r="D66" t="n">
         <v>3425.49</v>
       </c>
       <c r="E66" t="n">
-        <v>91.51000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>3534.6</v>
+        <v>3504.9</v>
       </c>
       <c r="G66" t="n">
         <v>3518.57</v>
       </c>
       <c r="H66" t="n">
-        <v>16.03</v>
+        <v>-13.67</v>
       </c>
       <c r="I66" t="n">
-        <v>3491.1</v>
+        <v>3402.1</v>
       </c>
       <c r="J66" t="n">
         <v>3423.59</v>
       </c>
       <c r="K66" t="n">
-        <v>67.51000000000001</v>
+        <v>-21.49</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="67">
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>113.5</v>
+        <v>114.81</v>
       </c>
       <c r="D67" t="n">
         <v>113.53</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.03</v>
+        <v>1.28</v>
       </c>
       <c r="F67" t="n">
-        <v>115.19</v>
+        <v>115.37</v>
       </c>
       <c r="G67" t="n">
         <v>114.68</v>
       </c>
       <c r="H67" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>113.2</v>
+        <v>113.6</v>
       </c>
       <c r="J67" t="n">
         <v>111.89</v>
       </c>
       <c r="K67" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.03</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="68">
@@ -3952,31 +3952,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="D68" t="n">
         <v>5489.59</v>
       </c>
       <c r="E68" t="n">
-        <v>-15.59</v>
+        <v>-14.59</v>
       </c>
       <c r="F68" t="n">
-        <v>5543.5</v>
+        <v>5594</v>
       </c>
       <c r="G68" t="n">
         <v>5564.29</v>
       </c>
       <c r="H68" t="n">
-        <v>-20.79</v>
+        <v>29.71</v>
       </c>
       <c r="I68" t="n">
-        <v>5425</v>
+        <v>5448.5</v>
       </c>
       <c r="J68" t="n">
         <v>5386.73</v>
       </c>
       <c r="K68" t="n">
-        <v>38.27</v>
+        <v>61.77</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="69">
@@ -4004,31 +4004,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D69" t="n">
         <v>1661.44</v>
       </c>
       <c r="E69" t="n">
-        <v>-21.44</v>
+        <v>-26.44</v>
       </c>
       <c r="F69" t="n">
-        <v>1665.9</v>
+        <v>1681.5</v>
       </c>
       <c r="G69" t="n">
         <v>1680.86</v>
       </c>
       <c r="H69" t="n">
-        <v>-14.96</v>
+        <v>0.64</v>
       </c>
       <c r="I69" t="n">
-        <v>1630.8</v>
+        <v>1634.3</v>
       </c>
       <c r="J69" t="n">
         <v>1627.71</v>
       </c>
       <c r="K69" t="n">
-        <v>3.09</v>
+        <v>6.59</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="70">
@@ -4056,31 +4056,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5333.5</v>
+        <v>5333</v>
       </c>
       <c r="D70" t="n">
         <v>5365.47</v>
       </c>
       <c r="E70" t="n">
-        <v>-31.97</v>
+        <v>-32.47</v>
       </c>
       <c r="F70" t="n">
-        <v>5355</v>
+        <v>5367.5</v>
       </c>
       <c r="G70" t="n">
         <v>5428.65</v>
       </c>
       <c r="H70" t="n">
-        <v>-73.65000000000001</v>
+        <v>-61.15</v>
       </c>
       <c r="I70" t="n">
-        <v>5297</v>
+        <v>5281</v>
       </c>
       <c r="J70" t="n">
         <v>5255.68</v>
       </c>
       <c r="K70" t="n">
-        <v>41.32</v>
+        <v>25.32</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="71">
@@ -4108,31 +4108,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1467.7</v>
+        <v>1463.8</v>
       </c>
       <c r="D71" t="n">
         <v>1480.12</v>
       </c>
       <c r="E71" t="n">
-        <v>-12.42</v>
+        <v>-16.32</v>
       </c>
       <c r="F71" t="n">
-        <v>1483.7</v>
+        <v>1477</v>
       </c>
       <c r="G71" t="n">
         <v>1483.16</v>
       </c>
       <c r="H71" t="n">
-        <v>0.54</v>
+        <v>-6.16</v>
       </c>
       <c r="I71" t="n">
-        <v>1462</v>
+        <v>1462.1</v>
       </c>
       <c r="J71" t="n">
         <v>1435.54</v>
       </c>
       <c r="K71" t="n">
-        <v>26.46</v>
+        <v>26.56</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="72">
@@ -4160,31 +4160,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1810</v>
+        <v>1776</v>
       </c>
       <c r="D72" t="n">
         <v>1850.04</v>
       </c>
       <c r="E72" t="n">
-        <v>-40.04</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>1822.6</v>
+        <v>1809</v>
       </c>
       <c r="G72" t="n">
         <v>1850.04</v>
       </c>
       <c r="H72" t="n">
-        <v>-27.44</v>
+        <v>-41.04</v>
       </c>
       <c r="I72" t="n">
-        <v>1783.1</v>
+        <v>1765.5</v>
       </c>
       <c r="J72" t="n">
         <v>1779.32</v>
       </c>
       <c r="K72" t="n">
-        <v>3.78</v>
+        <v>-13.82</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -4212,31 +4212,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2750</v>
+        <v>2735</v>
       </c>
       <c r="D73" t="n">
         <v>2816.63</v>
       </c>
       <c r="E73" t="n">
-        <v>-66.63</v>
+        <v>-81.63</v>
       </c>
       <c r="F73" t="n">
-        <v>2761.5</v>
+        <v>2755</v>
       </c>
       <c r="G73" t="n">
         <v>2816.63</v>
       </c>
       <c r="H73" t="n">
-        <v>-55.13</v>
+        <v>-61.63</v>
       </c>
       <c r="I73" t="n">
-        <v>2713.5</v>
+        <v>2695</v>
       </c>
       <c r="J73" t="n">
         <v>2713.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.22</v>
+        <v>-18.72</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="74">
@@ -4264,31 +4264,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1282</v>
+        <v>1225.3</v>
       </c>
       <c r="D74" t="n">
         <v>1337.1</v>
       </c>
       <c r="E74" t="n">
-        <v>-55.1</v>
+        <v>-111.8</v>
       </c>
       <c r="F74" t="n">
-        <v>1298.5</v>
+        <v>1244</v>
       </c>
       <c r="G74" t="n">
         <v>1337.1</v>
       </c>
       <c r="H74" t="n">
-        <v>-38.6</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>1236.7</v>
+        <v>1222.6</v>
       </c>
       <c r="J74" t="n">
         <v>1282</v>
       </c>
       <c r="K74" t="n">
-        <v>-45.3</v>
+        <v>-59.4</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>4.12</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -4316,31 +4316,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>621.8</v>
+        <v>630.65</v>
       </c>
       <c r="D75" t="n">
         <v>608.64</v>
       </c>
       <c r="E75" t="n">
-        <v>13.16</v>
+        <v>22.01</v>
       </c>
       <c r="F75" t="n">
-        <v>630.75</v>
+        <v>643.95</v>
       </c>
       <c r="G75" t="n">
         <v>635.02</v>
       </c>
       <c r="H75" t="n">
-        <v>-4.27</v>
+        <v>8.93</v>
       </c>
       <c r="I75" t="n">
-        <v>610.6</v>
+        <v>602.45</v>
       </c>
       <c r="J75" t="n">
         <v>614.85</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.25</v>
+        <v>-12.4</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4349,11 +4349,11 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.16</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="76">
@@ -4368,31 +4368,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>181.14</v>
+        <v>183.6</v>
       </c>
       <c r="D76" t="n">
         <v>181.4</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.26</v>
+        <v>2.2</v>
       </c>
       <c r="F76" t="n">
-        <v>185.74</v>
+        <v>184.9</v>
       </c>
       <c r="G76" t="n">
         <v>186.9</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.16</v>
+        <v>-2</v>
       </c>
       <c r="I76" t="n">
-        <v>179.94</v>
+        <v>180</v>
       </c>
       <c r="J76" t="n">
         <v>181.03</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.09</v>
+        <v>-1.03</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.14</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="77">
@@ -4420,31 +4420,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7975</v>
+        <v>8020</v>
       </c>
       <c r="D77" t="n">
         <v>8058.01</v>
       </c>
       <c r="E77" t="n">
-        <v>-83.01000000000001</v>
+        <v>-38.01</v>
       </c>
       <c r="F77" t="n">
-        <v>8024</v>
+        <v>8067.5</v>
       </c>
       <c r="G77" t="n">
         <v>8202.75</v>
       </c>
       <c r="H77" t="n">
-        <v>-178.75</v>
+        <v>-135.25</v>
       </c>
       <c r="I77" t="n">
-        <v>7938</v>
+        <v>7920</v>
       </c>
       <c r="J77" t="n">
         <v>7944.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.32</v>
+        <v>-24.32</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.03</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="78">
@@ -4472,31 +4472,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1943</v>
+        <v>1959.9</v>
       </c>
       <c r="D78" t="n">
         <v>1940.93</v>
       </c>
       <c r="E78" t="n">
-        <v>2.07</v>
+        <v>18.97</v>
       </c>
       <c r="F78" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="G78" t="n">
         <v>1991.14</v>
       </c>
       <c r="H78" t="n">
-        <v>-32.14</v>
+        <v>-30.14</v>
       </c>
       <c r="I78" t="n">
-        <v>1935</v>
+        <v>1938.3</v>
       </c>
       <c r="J78" t="n">
         <v>1928.16</v>
       </c>
       <c r="K78" t="n">
-        <v>6.84</v>
+        <v>10.14</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="79">
@@ -4524,31 +4524,31 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>789.45</v>
+        <v>787.5</v>
       </c>
       <c r="D79" t="n">
         <v>807.13</v>
       </c>
       <c r="E79" t="n">
-        <v>-17.68</v>
+        <v>-19.63</v>
       </c>
       <c r="F79" t="n">
-        <v>798.4</v>
+        <v>801.05</v>
       </c>
       <c r="G79" t="n">
         <v>807.13</v>
       </c>
       <c r="H79" t="n">
-        <v>-8.73</v>
+        <v>-6.08</v>
       </c>
       <c r="I79" t="n">
-        <v>780.05</v>
+        <v>778.05</v>
       </c>
       <c r="J79" t="n">
         <v>776.51</v>
       </c>
       <c r="K79" t="n">
-        <v>3.54</v>
+        <v>1.54</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="80">
@@ -4576,13 +4576,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>280</v>
+        <v>280.6</v>
       </c>
       <c r="D80" t="n">
         <v>282.47</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.47</v>
+        <v>-1.87</v>
       </c>
       <c r="F80" t="n">
         <v>280.6</v>
@@ -4594,13 +4594,13 @@
         <v>-1.87</v>
       </c>
       <c r="I80" t="n">
-        <v>275.5</v>
+        <v>275.4</v>
       </c>
       <c r="J80" t="n">
         <v>273.61</v>
       </c>
       <c r="K80" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="81">
@@ -4628,31 +4628,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12038</v>
+        <v>12105</v>
       </c>
       <c r="D81" t="n">
         <v>12000.09</v>
       </c>
       <c r="E81" t="n">
-        <v>37.91</v>
+        <v>104.91</v>
       </c>
       <c r="F81" t="n">
-        <v>12124</v>
+        <v>12105</v>
       </c>
       <c r="G81" t="n">
         <v>12345.48</v>
       </c>
       <c r="H81" t="n">
-        <v>-221.48</v>
+        <v>-240.48</v>
       </c>
       <c r="I81" t="n">
-        <v>11921</v>
+        <v>11970</v>
       </c>
       <c r="J81" t="n">
         <v>11955.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.31</v>
+        <v>14.69</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="82">
@@ -4680,31 +4680,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1175.6</v>
+        <v>1168.1</v>
       </c>
       <c r="D82" t="n">
         <v>1201.99</v>
       </c>
       <c r="E82" t="n">
-        <v>-26.39</v>
+        <v>-33.89</v>
       </c>
       <c r="F82" t="n">
-        <v>1189.9</v>
+        <v>1192.8</v>
       </c>
       <c r="G82" t="n">
         <v>1201.99</v>
       </c>
       <c r="H82" t="n">
-        <v>-12.09</v>
+        <v>-9.19</v>
       </c>
       <c r="I82" t="n">
-        <v>1161.7</v>
+        <v>1151</v>
       </c>
       <c r="J82" t="n">
         <v>1148.12</v>
       </c>
       <c r="K82" t="n">
-        <v>13.58</v>
+        <v>2.88</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="83">
@@ -4732,31 +4732,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2108.4</v>
+        <v>2070</v>
       </c>
       <c r="D83" t="n">
         <v>2173.9</v>
       </c>
       <c r="E83" t="n">
-        <v>-65.5</v>
+        <v>-103.9</v>
       </c>
       <c r="F83" t="n">
-        <v>2120</v>
+        <v>2108.6</v>
       </c>
       <c r="G83" t="n">
         <v>2173.9</v>
       </c>
       <c r="H83" t="n">
-        <v>-53.9</v>
+        <v>-65.3</v>
       </c>
       <c r="I83" t="n">
-        <v>2057.6</v>
+        <v>2062.3</v>
       </c>
       <c r="J83" t="n">
         <v>2031.51</v>
       </c>
       <c r="K83" t="n">
-        <v>26.09</v>
+        <v>30.79</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>3.01</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="84">
@@ -4784,31 +4784,31 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>310.25</v>
+        <v>315</v>
       </c>
       <c r="D84" t="n">
         <v>312.85</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.6</v>
+        <v>2.15</v>
       </c>
       <c r="F84" t="n">
-        <v>316.25</v>
+        <v>316.9</v>
       </c>
       <c r="G84" t="n">
         <v>317.62</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.37</v>
+        <v>-0.72</v>
       </c>
       <c r="I84" t="n">
-        <v>309.5</v>
+        <v>313.15</v>
       </c>
       <c r="J84" t="n">
         <v>307.57</v>
       </c>
       <c r="K84" t="n">
-        <v>1.93</v>
+        <v>5.58</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -4836,31 +4836,31 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2021.3</v>
+        <v>2008.9</v>
       </c>
       <c r="D85" t="n">
         <v>2088.35</v>
       </c>
       <c r="E85" t="n">
-        <v>-67.05</v>
+        <v>-79.45</v>
       </c>
       <c r="F85" t="n">
-        <v>2037.1</v>
+        <v>2050</v>
       </c>
       <c r="G85" t="n">
         <v>2088.35</v>
       </c>
       <c r="H85" t="n">
-        <v>-51.25</v>
+        <v>-38.35</v>
       </c>
       <c r="I85" t="n">
-        <v>1992.6</v>
+        <v>1988</v>
       </c>
       <c r="J85" t="n">
         <v>1968.33</v>
       </c>
       <c r="K85" t="n">
-        <v>24.27</v>
+        <v>19.67</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="86">
@@ -4888,31 +4888,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>14115</v>
+        <v>14200</v>
       </c>
       <c r="D86" t="n">
         <v>14353.98</v>
       </c>
       <c r="E86" t="n">
-        <v>-238.98</v>
+        <v>-153.98</v>
       </c>
       <c r="F86" t="n">
-        <v>14271</v>
+        <v>14294</v>
       </c>
       <c r="G86" t="n">
         <v>14353.98</v>
       </c>
       <c r="H86" t="n">
-        <v>-82.98</v>
+        <v>-59.98</v>
       </c>
       <c r="I86" t="n">
-        <v>14001</v>
+        <v>14050</v>
       </c>
       <c r="J86" t="n">
         <v>13803.1</v>
       </c>
       <c r="K86" t="n">
-        <v>197.9</v>
+        <v>246.9</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="87">
@@ -4940,31 +4940,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>501.9</v>
+        <v>505.2</v>
       </c>
       <c r="D87" t="n">
         <v>512.49</v>
       </c>
       <c r="E87" t="n">
-        <v>-10.59</v>
+        <v>-7.29</v>
       </c>
       <c r="F87" t="n">
-        <v>507.4</v>
+        <v>513.9</v>
       </c>
       <c r="G87" t="n">
         <v>512.49</v>
       </c>
       <c r="H87" t="n">
-        <v>-5.09</v>
+        <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>498.25</v>
+        <v>505.2</v>
       </c>
       <c r="J87" t="n">
         <v>487.96</v>
       </c>
       <c r="K87" t="n">
-        <v>10.29</v>
+        <v>17.24</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -5424,31 +5424,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1175.6</v>
+        <v>1168.1</v>
       </c>
       <c r="D5" t="n">
         <v>1201.99</v>
       </c>
       <c r="E5" t="n">
-        <v>-26.39</v>
+        <v>-33.89</v>
       </c>
       <c r="F5" t="n">
-        <v>1189.9</v>
+        <v>1192.8</v>
       </c>
       <c r="G5" t="n">
         <v>1201.99</v>
       </c>
       <c r="H5" t="n">
-        <v>-12.09</v>
+        <v>-9.19</v>
       </c>
       <c r="I5" t="n">
-        <v>1161.7</v>
+        <v>1151</v>
       </c>
       <c r="J5" t="n">
         <v>1148.12</v>
       </c>
       <c r="K5" t="n">
-        <v>13.58</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -5718,31 +5718,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>621.8</v>
+        <v>630.65</v>
       </c>
       <c r="D5" t="n">
         <v>608.64</v>
       </c>
       <c r="E5" t="n">
-        <v>13.16</v>
+        <v>22.01</v>
       </c>
       <c r="F5" t="n">
-        <v>630.75</v>
+        <v>643.95</v>
       </c>
       <c r="G5" t="n">
         <v>635.02</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.27</v>
+        <v>8.93</v>
       </c>
       <c r="I5" t="n">
-        <v>610.6</v>
+        <v>602.45</v>
       </c>
       <c r="J5" t="n">
         <v>614.85</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.25</v>
+        <v>-12.4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -5751,11 +5751,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>3.62</v>
       </c>
     </row>
   </sheetData>
@@ -6012,31 +6012,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7975</v>
+        <v>8020</v>
       </c>
       <c r="D5" t="n">
         <v>8058.01</v>
       </c>
       <c r="E5" t="n">
-        <v>-83.01000000000001</v>
+        <v>-38.01</v>
       </c>
       <c r="F5" t="n">
-        <v>8024</v>
+        <v>8067.5</v>
       </c>
       <c r="G5" t="n">
         <v>8202.75</v>
       </c>
       <c r="H5" t="n">
-        <v>-178.75</v>
+        <v>-135.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7938</v>
+        <v>7920</v>
       </c>
       <c r="J5" t="n">
         <v>7944.32</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.32</v>
+        <v>-24.32</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -6306,31 +6306,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2108.4</v>
+        <v>2070</v>
       </c>
       <c r="D5" t="n">
         <v>2173.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-65.5</v>
+        <v>-103.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2120</v>
+        <v>2108.6</v>
       </c>
       <c r="G5" t="n">
         <v>2173.9</v>
       </c>
       <c r="H5" t="n">
-        <v>-53.9</v>
+        <v>-65.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2057.6</v>
+        <v>2062.3</v>
       </c>
       <c r="J5" t="n">
         <v>2031.51</v>
       </c>
       <c r="K5" t="n">
-        <v>26.09</v>
+        <v>30.79</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.01</v>
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>
@@ -6600,31 +6600,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D5" t="n">
         <v>1661.44</v>
       </c>
       <c r="E5" t="n">
-        <v>-21.44</v>
+        <v>-26.44</v>
       </c>
       <c r="F5" t="n">
-        <v>1665.9</v>
+        <v>1681.5</v>
       </c>
       <c r="G5" t="n">
         <v>1680.86</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.96</v>
+        <v>0.64</v>
       </c>
       <c r="I5" t="n">
-        <v>1630.8</v>
+        <v>1634.3</v>
       </c>
       <c r="J5" t="n">
         <v>1627.71</v>
       </c>
       <c r="K5" t="n">
-        <v>3.09</v>
+        <v>6.59</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>
@@ -6894,31 +6894,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>310.25</v>
+        <v>315</v>
       </c>
       <c r="D5" t="n">
         <v>312.85</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6</v>
+        <v>2.15</v>
       </c>
       <c r="F5" t="n">
-        <v>316.25</v>
+        <v>316.9</v>
       </c>
       <c r="G5" t="n">
         <v>317.62</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.37</v>
+        <v>-0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>309.5</v>
+        <v>313.15</v>
       </c>
       <c r="J5" t="n">
         <v>307.57</v>
       </c>
       <c r="K5" t="n">
-        <v>1.93</v>
+        <v>5.58</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7188,31 +7188,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14115</v>
+        <v>14200</v>
       </c>
       <c r="D5" t="n">
         <v>14353.98</v>
       </c>
       <c r="E5" t="n">
-        <v>-238.98</v>
+        <v>-153.98</v>
       </c>
       <c r="F5" t="n">
-        <v>14271</v>
+        <v>14294</v>
       </c>
       <c r="G5" t="n">
         <v>14353.98</v>
       </c>
       <c r="H5" t="n">
-        <v>-82.98</v>
+        <v>-59.98</v>
       </c>
       <c r="I5" t="n">
-        <v>14001</v>
+        <v>14050</v>
       </c>
       <c r="J5" t="n">
         <v>13803.1</v>
       </c>
       <c r="K5" t="n">
-        <v>197.9</v>
+        <v>246.9</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>
@@ -7482,31 +7482,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1810</v>
+        <v>1776</v>
       </c>
       <c r="D5" t="n">
         <v>1850.04</v>
       </c>
       <c r="E5" t="n">
-        <v>-40.04</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1822.6</v>
+        <v>1809</v>
       </c>
       <c r="G5" t="n">
         <v>1850.04</v>
       </c>
       <c r="H5" t="n">
-        <v>-27.44</v>
+        <v>-41.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1783.1</v>
+        <v>1765.5</v>
       </c>
       <c r="J5" t="n">
         <v>1779.32</v>
       </c>
       <c r="K5" t="n">
-        <v>3.78</v>
+        <v>-13.82</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7724,31 +7724,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="D4" t="n">
         <v>5489.59</v>
       </c>
       <c r="E4" t="n">
-        <v>-15.59</v>
+        <v>-14.59</v>
       </c>
       <c r="F4" t="n">
-        <v>5543.5</v>
+        <v>5594</v>
       </c>
       <c r="G4" t="n">
         <v>5564.29</v>
       </c>
       <c r="H4" t="n">
-        <v>-20.79</v>
+        <v>29.71</v>
       </c>
       <c r="I4" t="n">
-        <v>5425</v>
+        <v>5448.5</v>
       </c>
       <c r="J4" t="n">
         <v>5386.73</v>
       </c>
       <c r="K4" t="n">
-        <v>38.27</v>
+        <v>61.77</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -8018,31 +8018,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>113.5</v>
+        <v>114.81</v>
       </c>
       <c r="D5" t="n">
         <v>113.53</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03</v>
+        <v>1.28</v>
       </c>
       <c r="F5" t="n">
-        <v>115.19</v>
+        <v>115.37</v>
       </c>
       <c r="G5" t="n">
         <v>114.68</v>
       </c>
       <c r="H5" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>113.2</v>
+        <v>113.6</v>
       </c>
       <c r="J5" t="n">
         <v>111.89</v>
       </c>
       <c r="K5" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.03</v>
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -8260,31 +8260,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3517</v>
+        <v>3502</v>
       </c>
       <c r="D4" t="n">
         <v>3425.49</v>
       </c>
       <c r="E4" t="n">
-        <v>91.51000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3534.6</v>
+        <v>3504.9</v>
       </c>
       <c r="G4" t="n">
         <v>3518.57</v>
       </c>
       <c r="H4" t="n">
-        <v>16.03</v>
+        <v>-13.67</v>
       </c>
       <c r="I4" t="n">
-        <v>3491.1</v>
+        <v>3402.1</v>
       </c>
       <c r="J4" t="n">
         <v>3423.59</v>
       </c>
       <c r="K4" t="n">
-        <v>67.51000000000001</v>
+        <v>-21.49</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>
@@ -8502,31 +8502,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>501.9</v>
+        <v>505.2</v>
       </c>
       <c r="D4" t="n">
         <v>512.49</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.59</v>
+        <v>-7.29</v>
       </c>
       <c r="F4" t="n">
-        <v>507.4</v>
+        <v>513.9</v>
       </c>
       <c r="G4" t="n">
         <v>512.49</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.09</v>
+        <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>498.25</v>
+        <v>505.2</v>
       </c>
       <c r="J4" t="n">
         <v>487.96</v>
       </c>
       <c r="K4" t="n">
-        <v>10.29</v>
+        <v>17.24</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -9228,31 +9228,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1467.7</v>
+        <v>1463.8</v>
       </c>
       <c r="D5" t="n">
         <v>1480.12</v>
       </c>
       <c r="E5" t="n">
-        <v>-12.42</v>
+        <v>-16.32</v>
       </c>
       <c r="F5" t="n">
-        <v>1483.7</v>
+        <v>1477</v>
       </c>
       <c r="G5" t="n">
         <v>1483.16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.54</v>
+        <v>-6.16</v>
       </c>
       <c r="I5" t="n">
-        <v>1462</v>
+        <v>1462.1</v>
       </c>
       <c r="J5" t="n">
         <v>1435.54</v>
       </c>
       <c r="K5" t="n">
-        <v>26.46</v>
+        <v>26.56</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -9764,31 +9764,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12038</v>
+        <v>12105</v>
       </c>
       <c r="D5" t="n">
         <v>12000.09</v>
       </c>
       <c r="E5" t="n">
-        <v>37.91</v>
+        <v>104.91</v>
       </c>
       <c r="F5" t="n">
-        <v>12124</v>
+        <v>12105</v>
       </c>
       <c r="G5" t="n">
         <v>12345.48</v>
       </c>
       <c r="H5" t="n">
-        <v>-221.48</v>
+        <v>-240.48</v>
       </c>
       <c r="I5" t="n">
-        <v>11921</v>
+        <v>11970</v>
       </c>
       <c r="J5" t="n">
         <v>11955.31</v>
       </c>
       <c r="K5" t="n">
-        <v>-34.31</v>
+        <v>14.69</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -10248,31 +10248,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2750</v>
+        <v>2735</v>
       </c>
       <c r="D5" t="n">
         <v>2816.63</v>
       </c>
       <c r="E5" t="n">
-        <v>-66.63</v>
+        <v>-81.63</v>
       </c>
       <c r="F5" t="n">
-        <v>2761.5</v>
+        <v>2755</v>
       </c>
       <c r="G5" t="n">
         <v>2816.63</v>
       </c>
       <c r="H5" t="n">
-        <v>-55.13</v>
+        <v>-61.63</v>
       </c>
       <c r="I5" t="n">
-        <v>2713.5</v>
+        <v>2695</v>
       </c>
       <c r="J5" t="n">
         <v>2713.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.22</v>
+        <v>-18.72</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4978,6 +4978,1150 @@
       </c>
       <c r="N87" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>114.03</v>
+      </c>
+      <c r="D88" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F88" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G88" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="I88" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5865.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>5786.78</v>
+      </c>
+      <c r="E89" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5937</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5786.78</v>
+      </c>
+      <c r="H89" t="n">
+        <v>150.22</v>
+      </c>
+      <c r="I89" t="n">
+        <v>5803.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>5685.21</v>
+      </c>
+      <c r="K89" t="n">
+        <v>118.29</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-29.45</v>
+      </c>
+      <c r="F90" t="n">
+        <v>5544</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-21.45</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5430.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5454.18</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-23.68</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>318</v>
+      </c>
+      <c r="D91" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="F91" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="I91" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-25.94</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8110</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="H92" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="I92" t="n">
+        <v>7955</v>
+      </c>
+      <c r="J92" t="n">
+        <v>7857.46</v>
+      </c>
+      <c r="K92" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1257.89</v>
+      </c>
+      <c r="E93" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1287.36</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1267</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1265.88</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1633.2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1660.3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1663.74</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1636.14</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="F95" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="G95" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="I95" t="n">
+        <v>179.88</v>
+      </c>
+      <c r="J95" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1760.17</v>
+      </c>
+      <c r="E96" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1836</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1792.28</v>
+      </c>
+      <c r="H96" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1809.8</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1760.84</v>
+      </c>
+      <c r="K96" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1256.26</v>
+      </c>
+      <c r="E97" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1356.17</v>
+      </c>
+      <c r="H97" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1332.95</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-41.85</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11780</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-198.02</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12061</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="H98" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I98" t="n">
+        <v>11720</v>
+      </c>
+      <c r="J98" t="n">
+        <v>11592.49</v>
+      </c>
+      <c r="K98" t="n">
+        <v>127.51</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5284</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5294.05</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-10.05</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5330</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5294.05</v>
+      </c>
+      <c r="H99" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5217.5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>5178.33</v>
+      </c>
+      <c r="K99" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4037.4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4050.04</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4075.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4060.6</v>
+      </c>
+      <c r="H100" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4028.5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4004.16</v>
+      </c>
+      <c r="K100" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2735.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2677.47</v>
+      </c>
+      <c r="E101" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2747.6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2749.07</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2702.76</v>
+      </c>
+      <c r="K101" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>3460.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-105.6</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3514.6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3455.1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3358.06</v>
+      </c>
+      <c r="K102" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>616</v>
+      </c>
+      <c r="D103" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-27.38</v>
+      </c>
+      <c r="F103" t="n">
+        <v>627</v>
+      </c>
+      <c r="G103" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-16.38</v>
+      </c>
+      <c r="I103" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>594.71</v>
+      </c>
+      <c r="K103" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1458.43</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1469.8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1458.71</v>
+      </c>
+      <c r="H104" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1457.2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1433.73</v>
+      </c>
+      <c r="K104" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>512</v>
+      </c>
+      <c r="D105" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F105" t="n">
+        <v>512</v>
+      </c>
+      <c r="G105" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I105" t="n">
+        <v>498.75</v>
+      </c>
+      <c r="J105" t="n">
+        <v>496.52</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>788</v>
+      </c>
+      <c r="D106" t="n">
+        <v>774.98</v>
+      </c>
+      <c r="E106" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F106" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>793.28</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I106" t="n">
+        <v>784.05</v>
+      </c>
+      <c r="J106" t="n">
+        <v>779.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1144.15</v>
+      </c>
+      <c r="E107" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1176.7</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1150.17</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1970.34</v>
+      </c>
+      <c r="E108" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2043.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2015.42</v>
+      </c>
+      <c r="H108" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1980.53</v>
+      </c>
+      <c r="K108" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>14023</v>
+      </c>
+      <c r="D109" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="E109" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="F109" t="n">
+        <v>14198</v>
+      </c>
+      <c r="G109" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="H109" t="n">
+        <v>214.49</v>
+      </c>
+      <c r="I109" t="n">
+        <v>14011</v>
+      </c>
+      <c r="J109" t="n">
+        <v>13569.36</v>
+      </c>
+      <c r="K109" t="n">
+        <v>441.64</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -5181,7 +6325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5462,6 +6606,58 @@
       </c>
       <c r="N5" t="n">
         <v>2.82</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1144.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1176.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1150.17</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>
@@ -5475,7 +6671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,6 +6952,58 @@
       </c>
       <c r="N5" t="n">
         <v>3.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>616</v>
+      </c>
+      <c r="D6" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-27.38</v>
+      </c>
+      <c r="F6" t="n">
+        <v>627</v>
+      </c>
+      <c r="G6" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-16.38</v>
+      </c>
+      <c r="I6" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>594.71</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4.26</v>
       </c>
     </row>
   </sheetData>
@@ -5769,7 +7017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6050,6 +7298,58 @@
       </c>
       <c r="N5" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-25.94</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8110</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="H6" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7955</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7857.46</v>
+      </c>
+      <c r="K6" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -6357,7 +7657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6638,6 +7938,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1633.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1660.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1663.74</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1636.14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +8003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6932,6 +8284,58 @@
       </c>
       <c r="N5" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>318</v>
+      </c>
+      <c r="D6" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="F6" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>
@@ -6945,7 +8349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7226,6 +8630,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14023</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14198</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="H6" t="n">
+        <v>214.49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14011</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13569.36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>441.64</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -7239,7 +8695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7520,6 +8976,58 @@
       </c>
       <c r="N5" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1760.17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1836</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1792.28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1809.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1760.84</v>
+      </c>
+      <c r="K6" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
@@ -7533,7 +9041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7762,6 +9270,58 @@
       </c>
       <c r="N4" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-29.45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5544</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-21.45</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5430.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5454.18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-23.68</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -7775,7 +9335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8056,6 +9616,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>114.03</v>
+      </c>
+      <c r="D6" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="I6" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -8069,7 +9681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8298,6 +9910,58 @@
       </c>
       <c r="N4" t="n">
         <v>2.23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3460.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-105.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3514.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3455.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3358.06</v>
+      </c>
+      <c r="K5" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.96</v>
       </c>
     </row>
   </sheetData>
@@ -8311,7 +9975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8540,6 +10204,58 @@
       </c>
       <c r="N4" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>512</v>
+      </c>
+      <c r="D5" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>512</v>
+      </c>
+      <c r="G5" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>498.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>496.52</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -8985,7 +10701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9266,6 +10982,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1458.43</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1469.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1458.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1457.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1433.73</v>
+      </c>
+      <c r="K6" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -9521,7 +11289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9802,6 +11570,58 @@
       </c>
       <c r="N5" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11780</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-198.02</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12061</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="H6" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11720</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11592.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>127.51</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -10005,7 +11825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10288,6 +12108,58 @@
         <v>2.9</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2735.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2677.47</v>
+      </c>
+      <c r="E6" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2747.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2749.07</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2702.76</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -4992,31 +4992,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>114.03</v>
+        <v>113.5</v>
       </c>
       <c r="D88" t="n">
         <v>116.24</v>
       </c>
       <c r="E88" t="n">
-        <v>-2.21</v>
+        <v>-2.74</v>
       </c>
       <c r="F88" t="n">
-        <v>114.3</v>
+        <v>115.19</v>
       </c>
       <c r="G88" t="n">
         <v>116.24</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.94</v>
+        <v>-1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>112.3</v>
+        <v>113.2</v>
       </c>
       <c r="J88" t="n">
         <v>112.08</v>
       </c>
       <c r="K88" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="89">
@@ -5044,31 +5044,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5865.5</v>
+        <v>5860</v>
       </c>
       <c r="D89" t="n">
         <v>5786.78</v>
       </c>
       <c r="E89" t="n">
-        <v>78.72</v>
+        <v>73.22</v>
       </c>
       <c r="F89" t="n">
-        <v>5937</v>
+        <v>5933</v>
       </c>
       <c r="G89" t="n">
         <v>5786.78</v>
       </c>
       <c r="H89" t="n">
-        <v>150.22</v>
+        <v>146.22</v>
       </c>
       <c r="I89" t="n">
-        <v>5803.5</v>
+        <v>5756.5</v>
       </c>
       <c r="J89" t="n">
         <v>5685.21</v>
       </c>
       <c r="K89" t="n">
-        <v>118.29</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="90">
@@ -5096,31 +5096,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5536</v>
+        <v>5474</v>
       </c>
       <c r="D90" t="n">
         <v>5565.45</v>
       </c>
       <c r="E90" t="n">
-        <v>-29.45</v>
+        <v>-91.45</v>
       </c>
       <c r="F90" t="n">
-        <v>5544</v>
+        <v>5543.5</v>
       </c>
       <c r="G90" t="n">
         <v>5565.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-21.45</v>
+        <v>-21.95</v>
       </c>
       <c r="I90" t="n">
-        <v>5430.5</v>
+        <v>5425</v>
       </c>
       <c r="J90" t="n">
         <v>5454.18</v>
       </c>
       <c r="K90" t="n">
-        <v>-23.68</v>
+        <v>-29.18</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0.53</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="91">
@@ -5148,31 +5148,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>318</v>
+        <v>310.25</v>
       </c>
       <c r="D91" t="n">
         <v>322.74</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.74</v>
+        <v>-12.49</v>
       </c>
       <c r="F91" t="n">
-        <v>318.5</v>
+        <v>316.25</v>
       </c>
       <c r="G91" t="n">
         <v>322.74</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.24</v>
+        <v>-6.49</v>
       </c>
       <c r="I91" t="n">
-        <v>306.2</v>
+        <v>309.5</v>
       </c>
       <c r="J91" t="n">
         <v>315.93</v>
       </c>
       <c r="K91" t="n">
-        <v>-9.73</v>
+        <v>-6.43</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5181,11 +5181,11 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.47</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="92">
@@ -5200,31 +5200,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8000</v>
+        <v>7975</v>
       </c>
       <c r="D92" t="n">
         <v>8025.94</v>
       </c>
       <c r="E92" t="n">
-        <v>-25.94</v>
+        <v>-50.94</v>
       </c>
       <c r="F92" t="n">
-        <v>8110</v>
+        <v>8024</v>
       </c>
       <c r="G92" t="n">
         <v>8025.94</v>
       </c>
       <c r="H92" t="n">
-        <v>84.06</v>
+        <v>-1.94</v>
       </c>
       <c r="I92" t="n">
-        <v>7955</v>
+        <v>7938</v>
       </c>
       <c r="J92" t="n">
         <v>7857.46</v>
       </c>
       <c r="K92" t="n">
-        <v>97.54000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="93">
@@ -5252,31 +5252,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="D93" t="n">
         <v>1257.89</v>
       </c>
       <c r="E93" t="n">
-        <v>17.11</v>
+        <v>30.11</v>
       </c>
       <c r="F93" t="n">
-        <v>1291.1</v>
+        <v>1298.3</v>
       </c>
       <c r="G93" t="n">
         <v>1287.36</v>
       </c>
       <c r="H93" t="n">
-        <v>3.74</v>
+        <v>10.94</v>
       </c>
       <c r="I93" t="n">
-        <v>1267</v>
+        <v>1280.7</v>
       </c>
       <c r="J93" t="n">
         <v>1265.88</v>
       </c>
       <c r="K93" t="n">
-        <v>1.12</v>
+        <v>14.82</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.36</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="94">
@@ -5304,31 +5304,31 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D94" t="n">
         <v>1633.2</v>
       </c>
       <c r="E94" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="F94" t="n">
-        <v>1660.3</v>
+        <v>1665.9</v>
       </c>
       <c r="G94" t="n">
         <v>1663.74</v>
       </c>
       <c r="H94" t="n">
-        <v>-3.44</v>
+        <v>2.16</v>
       </c>
       <c r="I94" t="n">
-        <v>1640</v>
+        <v>1630.8</v>
       </c>
       <c r="J94" t="n">
         <v>1636.14</v>
       </c>
       <c r="K94" t="n">
-        <v>3.86</v>
+        <v>-5.34</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="95">
@@ -5356,31 +5356,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>182.5</v>
+        <v>181.14</v>
       </c>
       <c r="D95" t="n">
         <v>186.19</v>
       </c>
       <c r="E95" t="n">
-        <v>-3.69</v>
+        <v>-5.05</v>
       </c>
       <c r="F95" t="n">
-        <v>184.85</v>
+        <v>185.74</v>
       </c>
       <c r="G95" t="n">
         <v>186.19</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.34</v>
+        <v>-0.45</v>
       </c>
       <c r="I95" t="n">
-        <v>179.88</v>
+        <v>179.94</v>
       </c>
       <c r="J95" t="n">
         <v>179.98</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.98</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="96">
@@ -5408,31 +5408,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="D96" t="n">
         <v>1760.17</v>
       </c>
       <c r="E96" t="n">
-        <v>58.83</v>
+        <v>49.83</v>
       </c>
       <c r="F96" t="n">
-        <v>1836</v>
+        <v>1822.6</v>
       </c>
       <c r="G96" t="n">
         <v>1792.28</v>
       </c>
       <c r="H96" t="n">
-        <v>43.72</v>
+        <v>30.32</v>
       </c>
       <c r="I96" t="n">
-        <v>1809.8</v>
+        <v>1783.1</v>
       </c>
       <c r="J96" t="n">
         <v>1760.84</v>
       </c>
       <c r="K96" t="n">
-        <v>48.96</v>
+        <v>22.26</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="97">
@@ -5460,31 +5460,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1360</v>
+        <v>1282</v>
       </c>
       <c r="D97" t="n">
         <v>1256.26</v>
       </c>
       <c r="E97" t="n">
-        <v>103.74</v>
+        <v>25.74</v>
       </c>
       <c r="F97" t="n">
-        <v>1391</v>
+        <v>1298.5</v>
       </c>
       <c r="G97" t="n">
         <v>1356.17</v>
       </c>
       <c r="H97" t="n">
-        <v>34.83</v>
+        <v>-57.67</v>
       </c>
       <c r="I97" t="n">
-        <v>1291.1</v>
+        <v>1236.7</v>
       </c>
       <c r="J97" t="n">
         <v>1332.95</v>
       </c>
       <c r="K97" t="n">
-        <v>-41.85</v>
+        <v>-96.25</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5493,11 +5493,11 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>8.26</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="98">
@@ -5512,31 +5512,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11780</v>
+        <v>12038</v>
       </c>
       <c r="D98" t="n">
         <v>11978.02</v>
       </c>
       <c r="E98" t="n">
-        <v>-198.02</v>
+        <v>59.98</v>
       </c>
       <c r="F98" t="n">
-        <v>12061</v>
+        <v>12124</v>
       </c>
       <c r="G98" t="n">
         <v>11978.02</v>
       </c>
       <c r="H98" t="n">
-        <v>82.98</v>
+        <v>145.98</v>
       </c>
       <c r="I98" t="n">
-        <v>11720</v>
+        <v>11921</v>
       </c>
       <c r="J98" t="n">
         <v>11592.49</v>
       </c>
       <c r="K98" t="n">
-        <v>127.51</v>
+        <v>328.51</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99">
@@ -5564,31 +5564,31 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5284</v>
+        <v>5333.5</v>
       </c>
       <c r="D99" t="n">
         <v>5294.05</v>
       </c>
       <c r="E99" t="n">
-        <v>-10.05</v>
+        <v>39.45</v>
       </c>
       <c r="F99" t="n">
-        <v>5330</v>
+        <v>5355</v>
       </c>
       <c r="G99" t="n">
         <v>5294.05</v>
       </c>
       <c r="H99" t="n">
-        <v>35.95</v>
+        <v>60.95</v>
       </c>
       <c r="I99" t="n">
-        <v>5217.5</v>
+        <v>5297</v>
       </c>
       <c r="J99" t="n">
         <v>5178.33</v>
       </c>
       <c r="K99" t="n">
-        <v>39.17</v>
+        <v>118.67</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="100">
@@ -5616,31 +5616,31 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4037.4</v>
+        <v>4080</v>
       </c>
       <c r="D100" t="n">
         <v>4050.04</v>
       </c>
       <c r="E100" t="n">
-        <v>-12.64</v>
+        <v>29.96</v>
       </c>
       <c r="F100" t="n">
-        <v>4075.5</v>
+        <v>4080</v>
       </c>
       <c r="G100" t="n">
         <v>4060.6</v>
       </c>
       <c r="H100" t="n">
-        <v>14.9</v>
+        <v>19.4</v>
       </c>
       <c r="I100" t="n">
-        <v>4028.5</v>
+        <v>4025.8</v>
       </c>
       <c r="J100" t="n">
         <v>4004.16</v>
       </c>
       <c r="K100" t="n">
-        <v>24.34</v>
+        <v>21.64</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="101">
@@ -5668,31 +5668,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2735.5</v>
+        <v>2750</v>
       </c>
       <c r="D101" t="n">
         <v>2677.47</v>
       </c>
       <c r="E101" t="n">
-        <v>58.03</v>
+        <v>72.53</v>
       </c>
       <c r="F101" t="n">
-        <v>2747.6</v>
+        <v>2761.5</v>
       </c>
       <c r="G101" t="n">
         <v>2749.07</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.47</v>
+        <v>12.43</v>
       </c>
       <c r="I101" t="n">
-        <v>2720</v>
+        <v>2713.5</v>
       </c>
       <c r="J101" t="n">
         <v>2702.76</v>
       </c>
       <c r="K101" t="n">
-        <v>17.24</v>
+        <v>10.74</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="102">
@@ -5720,31 +5720,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3460.1</v>
+        <v>3517</v>
       </c>
       <c r="D102" t="n">
         <v>3565.7</v>
       </c>
       <c r="E102" t="n">
-        <v>-105.6</v>
+        <v>-48.7</v>
       </c>
       <c r="F102" t="n">
-        <v>3514.6</v>
+        <v>3534.6</v>
       </c>
       <c r="G102" t="n">
         <v>3565.7</v>
       </c>
       <c r="H102" t="n">
-        <v>-51.1</v>
+        <v>-31.1</v>
       </c>
       <c r="I102" t="n">
-        <v>3455.1</v>
+        <v>3491.1</v>
       </c>
       <c r="J102" t="n">
         <v>3358.06</v>
       </c>
       <c r="K102" t="n">
-        <v>97.04000000000001</v>
+        <v>133.04</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.96</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="103">
@@ -5772,31 +5772,31 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>616</v>
+        <v>621.8</v>
       </c>
       <c r="D103" t="n">
         <v>643.38</v>
       </c>
       <c r="E103" t="n">
-        <v>-27.38</v>
+        <v>-21.58</v>
       </c>
       <c r="F103" t="n">
-        <v>627</v>
+        <v>630.75</v>
       </c>
       <c r="G103" t="n">
         <v>643.38</v>
       </c>
       <c r="H103" t="n">
-        <v>-16.38</v>
+        <v>-12.63</v>
       </c>
       <c r="I103" t="n">
-        <v>613.1</v>
+        <v>610.6</v>
       </c>
       <c r="J103" t="n">
         <v>594.71</v>
       </c>
       <c r="K103" t="n">
-        <v>18.39</v>
+        <v>15.89</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>4.26</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="104">
@@ -5824,31 +5824,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1463</v>
+        <v>1467.7</v>
       </c>
       <c r="D104" t="n">
         <v>1458.43</v>
       </c>
       <c r="E104" t="n">
-        <v>4.57</v>
+        <v>9.27</v>
       </c>
       <c r="F104" t="n">
-        <v>1469.8</v>
+        <v>1483.7</v>
       </c>
       <c r="G104" t="n">
         <v>1458.71</v>
       </c>
       <c r="H104" t="n">
-        <v>11.09</v>
+        <v>24.99</v>
       </c>
       <c r="I104" t="n">
-        <v>1457.2</v>
+        <v>1462</v>
       </c>
       <c r="J104" t="n">
         <v>1433.73</v>
       </c>
       <c r="K104" t="n">
-        <v>23.47</v>
+        <v>28.27</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="105">
@@ -5876,31 +5876,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>512</v>
+        <v>501.9</v>
       </c>
       <c r="D105" t="n">
         <v>508.76</v>
       </c>
       <c r="E105" t="n">
-        <v>3.24</v>
+        <v>-6.86</v>
       </c>
       <c r="F105" t="n">
-        <v>512</v>
+        <v>507.4</v>
       </c>
       <c r="G105" t="n">
         <v>508.76</v>
       </c>
       <c r="H105" t="n">
-        <v>3.24</v>
+        <v>-1.36</v>
       </c>
       <c r="I105" t="n">
-        <v>498.75</v>
+        <v>498.25</v>
       </c>
       <c r="J105" t="n">
         <v>496.52</v>
       </c>
       <c r="K105" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="106">
@@ -5928,31 +5928,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>788</v>
+        <v>789.45</v>
       </c>
       <c r="D106" t="n">
         <v>774.98</v>
       </c>
       <c r="E106" t="n">
-        <v>13.02</v>
+        <v>14.47</v>
       </c>
       <c r="F106" t="n">
-        <v>796.5</v>
+        <v>798.4</v>
       </c>
       <c r="G106" t="n">
         <v>793.28</v>
       </c>
       <c r="H106" t="n">
-        <v>3.22</v>
+        <v>5.12</v>
       </c>
       <c r="I106" t="n">
-        <v>784.05</v>
+        <v>780.05</v>
       </c>
       <c r="J106" t="n">
         <v>779.96</v>
       </c>
       <c r="K106" t="n">
-        <v>4.09</v>
+        <v>0.09</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="107">
@@ -5980,31 +5980,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1168</v>
+        <v>1175.6</v>
       </c>
       <c r="D107" t="n">
         <v>1144.15</v>
       </c>
       <c r="E107" t="n">
-        <v>23.85</v>
+        <v>31.45</v>
       </c>
       <c r="F107" t="n">
-        <v>1176.7</v>
+        <v>1189.9</v>
       </c>
       <c r="G107" t="n">
         <v>1170.01</v>
       </c>
       <c r="H107" t="n">
-        <v>6.69</v>
+        <v>19.89</v>
       </c>
       <c r="I107" t="n">
-        <v>1147.8</v>
+        <v>1161.7</v>
       </c>
       <c r="J107" t="n">
         <v>1150.17</v>
       </c>
       <c r="K107" t="n">
-        <v>-2.37</v>
+        <v>11.53</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="108">
@@ -6032,31 +6032,31 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2032</v>
+        <v>2021.3</v>
       </c>
       <c r="D108" t="n">
         <v>1970.34</v>
       </c>
       <c r="E108" t="n">
-        <v>61.66</v>
+        <v>50.96</v>
       </c>
       <c r="F108" t="n">
-        <v>2043.9</v>
+        <v>2037.1</v>
       </c>
       <c r="G108" t="n">
         <v>2015.42</v>
       </c>
       <c r="H108" t="n">
-        <v>28.48</v>
+        <v>21.68</v>
       </c>
       <c r="I108" t="n">
-        <v>2012</v>
+        <v>1992.6</v>
       </c>
       <c r="J108" t="n">
         <v>1980.53</v>
       </c>
       <c r="K108" t="n">
-        <v>31.47</v>
+        <v>12.07</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3.13</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="109">
@@ -6084,31 +6084,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14023</v>
+        <v>14115</v>
       </c>
       <c r="D109" t="n">
         <v>13983.51</v>
       </c>
       <c r="E109" t="n">
-        <v>39.49</v>
+        <v>131.49</v>
       </c>
       <c r="F109" t="n">
-        <v>14198</v>
+        <v>14271</v>
       </c>
       <c r="G109" t="n">
         <v>13983.51</v>
       </c>
       <c r="H109" t="n">
-        <v>214.49</v>
+        <v>287.49</v>
       </c>
       <c r="I109" t="n">
-        <v>14011</v>
+        <v>14001</v>
       </c>
       <c r="J109" t="n">
         <v>13569.36</v>
       </c>
       <c r="K109" t="n">
-        <v>441.64</v>
+        <v>431.64</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0.28</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6620,31 +6620,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1168</v>
+        <v>1175.6</v>
       </c>
       <c r="D6" t="n">
         <v>1144.15</v>
       </c>
       <c r="E6" t="n">
-        <v>23.85</v>
+        <v>31.45</v>
       </c>
       <c r="F6" t="n">
-        <v>1176.7</v>
+        <v>1189.9</v>
       </c>
       <c r="G6" t="n">
         <v>1170.01</v>
       </c>
       <c r="H6" t="n">
-        <v>6.69</v>
+        <v>19.89</v>
       </c>
       <c r="I6" t="n">
-        <v>1147.8</v>
+        <v>1161.7</v>
       </c>
       <c r="J6" t="n">
         <v>1150.17</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.37</v>
+        <v>11.53</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -6966,31 +6966,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>616</v>
+        <v>621.8</v>
       </c>
       <c r="D6" t="n">
         <v>643.38</v>
       </c>
       <c r="E6" t="n">
-        <v>-27.38</v>
+        <v>-21.58</v>
       </c>
       <c r="F6" t="n">
-        <v>627</v>
+        <v>630.75</v>
       </c>
       <c r="G6" t="n">
         <v>643.38</v>
       </c>
       <c r="H6" t="n">
-        <v>-16.38</v>
+        <v>-12.63</v>
       </c>
       <c r="I6" t="n">
-        <v>613.1</v>
+        <v>610.6</v>
       </c>
       <c r="J6" t="n">
         <v>594.71</v>
       </c>
       <c r="K6" t="n">
-        <v>18.39</v>
+        <v>15.89</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.26</v>
+        <v>3.35</v>
       </c>
     </row>
   </sheetData>
@@ -7312,31 +7312,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8000</v>
+        <v>7975</v>
       </c>
       <c r="D6" t="n">
         <v>8025.94</v>
       </c>
       <c r="E6" t="n">
-        <v>-25.94</v>
+        <v>-50.94</v>
       </c>
       <c r="F6" t="n">
-        <v>8110</v>
+        <v>8024</v>
       </c>
       <c r="G6" t="n">
         <v>8025.94</v>
       </c>
       <c r="H6" t="n">
-        <v>84.06</v>
+        <v>-1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>7955</v>
+        <v>7938</v>
       </c>
       <c r="J6" t="n">
         <v>7857.46</v>
       </c>
       <c r="K6" t="n">
-        <v>97.54000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -7952,31 +7952,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D6" t="n">
         <v>1633.2</v>
       </c>
       <c r="E6" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1660.3</v>
+        <v>1665.9</v>
       </c>
       <c r="G6" t="n">
         <v>1663.74</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.44</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>1640</v>
+        <v>1630.8</v>
       </c>
       <c r="J6" t="n">
         <v>1636.14</v>
       </c>
       <c r="K6" t="n">
-        <v>3.86</v>
+        <v>-5.34</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -8298,31 +8298,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>318</v>
+        <v>310.25</v>
       </c>
       <c r="D6" t="n">
         <v>322.74</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.74</v>
+        <v>-12.49</v>
       </c>
       <c r="F6" t="n">
-        <v>318.5</v>
+        <v>316.25</v>
       </c>
       <c r="G6" t="n">
         <v>322.74</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.24</v>
+        <v>-6.49</v>
       </c>
       <c r="I6" t="n">
-        <v>306.2</v>
+        <v>309.5</v>
       </c>
       <c r="J6" t="n">
         <v>315.93</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.73</v>
+        <v>-6.43</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -8331,11 +8331,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.47</v>
+        <v>3.87</v>
       </c>
     </row>
   </sheetData>
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14023</v>
+        <v>14115</v>
       </c>
       <c r="D6" t="n">
         <v>13983.51</v>
       </c>
       <c r="E6" t="n">
-        <v>39.49</v>
+        <v>131.49</v>
       </c>
       <c r="F6" t="n">
-        <v>14198</v>
+        <v>14271</v>
       </c>
       <c r="G6" t="n">
         <v>13983.51</v>
       </c>
       <c r="H6" t="n">
-        <v>214.49</v>
+        <v>287.49</v>
       </c>
       <c r="I6" t="n">
-        <v>14011</v>
+        <v>14001</v>
       </c>
       <c r="J6" t="n">
         <v>13569.36</v>
       </c>
       <c r="K6" t="n">
-        <v>441.64</v>
+        <v>431.64</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.28</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8990,31 +8990,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="D6" t="n">
         <v>1760.17</v>
       </c>
       <c r="E6" t="n">
-        <v>58.83</v>
+        <v>49.83</v>
       </c>
       <c r="F6" t="n">
-        <v>1836</v>
+        <v>1822.6</v>
       </c>
       <c r="G6" t="n">
         <v>1792.28</v>
       </c>
       <c r="H6" t="n">
-        <v>43.72</v>
+        <v>30.32</v>
       </c>
       <c r="I6" t="n">
-        <v>1809.8</v>
+        <v>1783.1</v>
       </c>
       <c r="J6" t="n">
         <v>1760.84</v>
       </c>
       <c r="K6" t="n">
-        <v>48.96</v>
+        <v>22.26</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>
@@ -9284,31 +9284,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5536</v>
+        <v>5474</v>
       </c>
       <c r="D5" t="n">
         <v>5565.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-29.45</v>
+        <v>-91.45</v>
       </c>
       <c r="F5" t="n">
-        <v>5544</v>
+        <v>5543.5</v>
       </c>
       <c r="G5" t="n">
         <v>5565.45</v>
       </c>
       <c r="H5" t="n">
-        <v>-21.45</v>
+        <v>-21.95</v>
       </c>
       <c r="I5" t="n">
-        <v>5430.5</v>
+        <v>5425</v>
       </c>
       <c r="J5" t="n">
         <v>5454.18</v>
       </c>
       <c r="K5" t="n">
-        <v>-23.68</v>
+        <v>-29.18</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.53</v>
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -9630,31 +9630,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>114.03</v>
+        <v>113.5</v>
       </c>
       <c r="D6" t="n">
         <v>116.24</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.21</v>
+        <v>-2.74</v>
       </c>
       <c r="F6" t="n">
-        <v>114.3</v>
+        <v>115.19</v>
       </c>
       <c r="G6" t="n">
         <v>116.24</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.94</v>
+        <v>-1.05</v>
       </c>
       <c r="I6" t="n">
-        <v>112.3</v>
+        <v>113.2</v>
       </c>
       <c r="J6" t="n">
         <v>112.08</v>
       </c>
       <c r="K6" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>
@@ -9924,31 +9924,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3460.1</v>
+        <v>3517</v>
       </c>
       <c r="D5" t="n">
         <v>3565.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-105.6</v>
+        <v>-48.7</v>
       </c>
       <c r="F5" t="n">
-        <v>3514.6</v>
+        <v>3534.6</v>
       </c>
       <c r="G5" t="n">
         <v>3565.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-51.1</v>
+        <v>-31.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3455.1</v>
+        <v>3491.1</v>
       </c>
       <c r="J5" t="n">
         <v>3358.06</v>
       </c>
       <c r="K5" t="n">
-        <v>97.04000000000001</v>
+        <v>133.04</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>
@@ -10218,31 +10218,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>512</v>
+        <v>501.9</v>
       </c>
       <c r="D5" t="n">
         <v>508.76</v>
       </c>
       <c r="E5" t="n">
-        <v>3.24</v>
+        <v>-6.86</v>
       </c>
       <c r="F5" t="n">
-        <v>512</v>
+        <v>507.4</v>
       </c>
       <c r="G5" t="n">
         <v>508.76</v>
       </c>
       <c r="H5" t="n">
-        <v>3.24</v>
+        <v>-1.36</v>
       </c>
       <c r="I5" t="n">
-        <v>498.75</v>
+        <v>498.25</v>
       </c>
       <c r="J5" t="n">
         <v>496.52</v>
       </c>
       <c r="K5" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
@@ -10996,31 +10996,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1463</v>
+        <v>1467.7</v>
       </c>
       <c r="D6" t="n">
         <v>1458.43</v>
       </c>
       <c r="E6" t="n">
-        <v>4.57</v>
+        <v>9.27</v>
       </c>
       <c r="F6" t="n">
-        <v>1469.8</v>
+        <v>1483.7</v>
       </c>
       <c r="G6" t="n">
         <v>1458.71</v>
       </c>
       <c r="H6" t="n">
-        <v>11.09</v>
+        <v>24.99</v>
       </c>
       <c r="I6" t="n">
-        <v>1457.2</v>
+        <v>1462</v>
       </c>
       <c r="J6" t="n">
         <v>1433.73</v>
       </c>
       <c r="K6" t="n">
-        <v>23.47</v>
+        <v>28.27</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -11584,31 +11584,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11780</v>
+        <v>12038</v>
       </c>
       <c r="D6" t="n">
         <v>11978.02</v>
       </c>
       <c r="E6" t="n">
-        <v>-198.02</v>
+        <v>59.98</v>
       </c>
       <c r="F6" t="n">
-        <v>12061</v>
+        <v>12124</v>
       </c>
       <c r="G6" t="n">
         <v>11978.02</v>
       </c>
       <c r="H6" t="n">
-        <v>82.98</v>
+        <v>145.98</v>
       </c>
       <c r="I6" t="n">
-        <v>11720</v>
+        <v>11921</v>
       </c>
       <c r="J6" t="n">
         <v>11592.49</v>
       </c>
       <c r="K6" t="n">
-        <v>127.51</v>
+        <v>328.51</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -12120,31 +12120,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2735.5</v>
+        <v>2750</v>
       </c>
       <c r="D6" t="n">
         <v>2677.47</v>
       </c>
       <c r="E6" t="n">
-        <v>58.03</v>
+        <v>72.53</v>
       </c>
       <c r="F6" t="n">
-        <v>2747.6</v>
+        <v>2761.5</v>
       </c>
       <c r="G6" t="n">
         <v>2749.07</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.47</v>
+        <v>12.43</v>
       </c>
       <c r="I6" t="n">
-        <v>2720</v>
+        <v>2713.5</v>
       </c>
       <c r="J6" t="n">
         <v>2702.76</v>
       </c>
       <c r="K6" t="n">
-        <v>17.24</v>
+        <v>10.74</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6122,6 +6122,1410 @@
       </c>
       <c r="N109" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>11579</v>
+      </c>
+      <c r="D110" t="n">
+        <v>11558.42</v>
+      </c>
+      <c r="E110" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11587</v>
+      </c>
+      <c r="G110" t="n">
+        <v>11558.42</v>
+      </c>
+      <c r="H110" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="I110" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J110" t="n">
+        <v>11371.84</v>
+      </c>
+      <c r="K110" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>8049</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8061.87</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8049</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8245.42</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-196.42</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7940</v>
+      </c>
+      <c r="J111" t="n">
+        <v>8021.49</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-104.75</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2748.4</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-96.34999999999999</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2698.2</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2740</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D113" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F113" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>120.99</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I113" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="J113" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5895</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6017.33</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-122.33</v>
+      </c>
+      <c r="F114" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G114" t="n">
+        <v>6030.82</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-114.82</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5844</v>
+      </c>
+      <c r="J114" t="n">
+        <v>5866.76</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-22.76</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F115" t="n">
+        <v>177.38</v>
+      </c>
+      <c r="G115" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="I115" t="n">
+        <v>174.43</v>
+      </c>
+      <c r="J115" t="n">
+        <v>176.25</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="D116" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="F116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="I116" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11728.34</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-78.34</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>11679</v>
+      </c>
+      <c r="D117" t="n">
+        <v>11658.24</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F117" t="n">
+        <v>11899</v>
+      </c>
+      <c r="G117" t="n">
+        <v>11951.71</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-52.71</v>
+      </c>
+      <c r="I117" t="n">
+        <v>11532</v>
+      </c>
+      <c r="J117" t="n">
+        <v>11626.71</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-94.70999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5415.71</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-82.70999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>5333</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5476.36</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-143.36</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5228</v>
+      </c>
+      <c r="J118" t="n">
+        <v>5328.09</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-100.09</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2240</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2236.02</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2246.63</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2192.7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2188.23</v>
+      </c>
+      <c r="K119" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1644.81</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1660.49</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1622.1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1615.26</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>187</v>
+      </c>
+      <c r="D121" t="n">
+        <v>183.57</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="F121" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G121" t="n">
+        <v>192.31</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I121" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="J121" t="n">
+        <v>187</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1272</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1278.7</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1272</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1225.65</v>
+      </c>
+      <c r="K122" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5427.13</v>
+      </c>
+      <c r="E123" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5530</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5544.99</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5392.25</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1941.54</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1945</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1978.44</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-33.44</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1901.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1924.24</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-22.94</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>279.85</v>
+      </c>
+      <c r="D125" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>281.9</v>
+      </c>
+      <c r="G125" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I125" t="n">
+        <v>277</v>
+      </c>
+      <c r="J125" t="n">
+        <v>274.16</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4020</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4082.15</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-62.15</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4044.1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4087.49</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-43.39</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3975.44</v>
+      </c>
+      <c r="K126" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F127" t="n">
+        <v>523.8</v>
+      </c>
+      <c r="G127" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="H127" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I127" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>499.53</v>
+      </c>
+      <c r="K127" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1484.08</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1492.03</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-23.23</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1456.1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1451.28</v>
+      </c>
+      <c r="K128" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>614.65</v>
+      </c>
+      <c r="D129" t="n">
+        <v>598.79</v>
+      </c>
+      <c r="E129" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="F129" t="n">
+        <v>620.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>615.76</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I129" t="n">
+        <v>604.25</v>
+      </c>
+      <c r="J129" t="n">
+        <v>598.5599999999999</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-65.81999999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1819.1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-48.22</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1780.4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1742.03</v>
+      </c>
+      <c r="K130" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3383.96</v>
+      </c>
+      <c r="E131" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3471.8</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3406.31</v>
+      </c>
+      <c r="H131" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>3320.14</v>
+      </c>
+      <c r="K131" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2020.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2089.33</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-68.83</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2028.4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2089.33</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-60.93</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2006.1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1973.8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1377.37</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-38.37</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1364</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1377.37</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1329.6</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1298.83</v>
+      </c>
+      <c r="K133" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D134" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-241.16</v>
+      </c>
+      <c r="F134" t="n">
+        <v>14090</v>
+      </c>
+      <c r="G134" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="H134" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="I134" t="n">
+        <v>13670</v>
+      </c>
+      <c r="J134" t="n">
+        <v>13456.8</v>
+      </c>
+      <c r="K134" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-41.46</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-34.96</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1140</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1145.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D136" t="n">
+        <v>304.31</v>
+      </c>
+      <c r="E136" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="F136" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="G136" t="n">
+        <v>318.08</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I136" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="J136" t="n">
+        <v>309.31</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -6325,7 +7729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6658,6 +8062,58 @@
       </c>
       <c r="N6" t="n">
         <v>2.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-41.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-34.96</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1140</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1145.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
@@ -6671,7 +8127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7004,6 +8460,58 @@
       </c>
       <c r="N6" t="n">
         <v>3.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>614.65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>598.79</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>620.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>615.76</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>604.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>598.5599999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.65</v>
       </c>
     </row>
   </sheetData>
@@ -7017,7 +8525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7350,6 +8858,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8049</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8061.87</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8049</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8245.42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-196.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7940</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8021.49</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -7657,7 +9217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7990,6 +9550,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1644.81</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1660.49</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1622.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1615.26</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -8003,7 +9615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8336,6 +9948,58 @@
       </c>
       <c r="N6" t="n">
         <v>3.87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>304.31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="F7" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="G7" t="n">
+        <v>318.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I7" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>309.31</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -8349,7 +10013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8682,6 +10346,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-241.16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14090</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>13670</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13456.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
@@ -8695,7 +10411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9028,6 +10744,58 @@
       </c>
       <c r="N6" t="n">
         <v>2.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-65.81999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1819.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-48.22</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1780.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1742.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3.52</v>
       </c>
     </row>
   </sheetData>
@@ -9041,7 +10809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9322,6 +11090,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5427.13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5530</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5544.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5392.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -9335,7 +11155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9668,6 +11488,58 @@
       </c>
       <c r="N6" t="n">
         <v>2.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D7" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>120.99</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>
@@ -9681,7 +11553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9962,6 +11834,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3383.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3471.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3406.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3320.14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -9975,7 +11899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10256,6 +12180,58 @@
       </c>
       <c r="N5" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F6" t="n">
+        <v>523.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I6" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>499.53</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10701,7 +12677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11034,6 +13010,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1484.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1492.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-23.23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1456.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1451.28</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -11289,7 +13317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11622,6 +13650,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11891</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11891</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11728.34</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-78.34</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -11825,7 +13905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12160,6 +14240,58 @@
         <v>2.71</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-104.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2748.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-96.34999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2698.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2740</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -6136,31 +6136,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11579</v>
+        <v>11550</v>
       </c>
       <c r="D110" t="n">
         <v>11558.42</v>
       </c>
       <c r="E110" t="n">
-        <v>20.58</v>
+        <v>-8.42</v>
       </c>
       <c r="F110" t="n">
-        <v>11587</v>
+        <v>11599</v>
       </c>
       <c r="G110" t="n">
         <v>11558.42</v>
       </c>
       <c r="H110" t="n">
-        <v>28.58</v>
+        <v>40.58</v>
       </c>
       <c r="I110" t="n">
-        <v>11410</v>
+        <v>11412</v>
       </c>
       <c r="J110" t="n">
         <v>11371.84</v>
       </c>
       <c r="K110" t="n">
-        <v>38.16</v>
+        <v>40.16</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6188,31 +6188,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8049</v>
+        <v>8000</v>
       </c>
       <c r="D111" t="n">
         <v>8061.87</v>
       </c>
       <c r="E111" t="n">
-        <v>-12.87</v>
+        <v>-61.87</v>
       </c>
       <c r="F111" t="n">
-        <v>8049</v>
+        <v>8110</v>
       </c>
       <c r="G111" t="n">
         <v>8245.42</v>
       </c>
       <c r="H111" t="n">
-        <v>-196.42</v>
+        <v>-135.42</v>
       </c>
       <c r="I111" t="n">
-        <v>7940</v>
+        <v>7955</v>
       </c>
       <c r="J111" t="n">
         <v>8021.49</v>
       </c>
       <c r="K111" t="n">
-        <v>-81.48999999999999</v>
+        <v>-66.48999999999999</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="112">
@@ -6240,31 +6240,31 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2740</v>
+        <v>2735.5</v>
       </c>
       <c r="D112" t="n">
         <v>2844.75</v>
       </c>
       <c r="E112" t="n">
-        <v>-104.75</v>
+        <v>-109.25</v>
       </c>
       <c r="F112" t="n">
-        <v>2748.4</v>
+        <v>2747.6</v>
       </c>
       <c r="G112" t="n">
         <v>2844.75</v>
       </c>
       <c r="H112" t="n">
-        <v>-96.34999999999999</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>2698.2</v>
+        <v>2720</v>
       </c>
       <c r="J112" t="n">
         <v>2740</v>
       </c>
       <c r="K112" t="n">
-        <v>-41.8</v>
+        <v>-20</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6273,11 +6273,11 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="113">
@@ -6292,31 +6292,31 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>118.98</v>
+        <v>114.03</v>
       </c>
       <c r="D113" t="n">
         <v>117.1</v>
       </c>
       <c r="E113" t="n">
-        <v>1.88</v>
+        <v>-3.07</v>
       </c>
       <c r="F113" t="n">
-        <v>119.5</v>
+        <v>114.3</v>
       </c>
       <c r="G113" t="n">
         <v>120.99</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.49</v>
+        <v>-6.69</v>
       </c>
       <c r="I113" t="n">
-        <v>113.72</v>
+        <v>112.3</v>
       </c>
       <c r="J113" t="n">
         <v>117.76</v>
       </c>
       <c r="K113" t="n">
-        <v>-4.04</v>
+        <v>-5.46</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6325,11 +6325,11 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="114">
@@ -6344,31 +6344,31 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5895</v>
+        <v>5865.5</v>
       </c>
       <c r="D114" t="n">
         <v>6017.33</v>
       </c>
       <c r="E114" t="n">
-        <v>-122.33</v>
+        <v>-151.83</v>
       </c>
       <c r="F114" t="n">
-        <v>5916</v>
+        <v>5937</v>
       </c>
       <c r="G114" t="n">
         <v>6030.82</v>
       </c>
       <c r="H114" t="n">
-        <v>-114.82</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>5844</v>
+        <v>5803.5</v>
       </c>
       <c r="J114" t="n">
         <v>5866.76</v>
       </c>
       <c r="K114" t="n">
-        <v>-22.76</v>
+        <v>-63.26</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="115">
@@ -6396,31 +6396,31 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>176.7</v>
+        <v>174.83</v>
       </c>
       <c r="D115" t="n">
         <v>176.38</v>
       </c>
       <c r="E115" t="n">
-        <v>0.32</v>
+        <v>-1.55</v>
       </c>
       <c r="F115" t="n">
-        <v>177.38</v>
+        <v>176.33</v>
       </c>
       <c r="G115" t="n">
         <v>181.16</v>
       </c>
       <c r="H115" t="n">
-        <v>-3.78</v>
+        <v>-4.83</v>
       </c>
       <c r="I115" t="n">
-        <v>174.43</v>
+        <v>172</v>
       </c>
       <c r="J115" t="n">
         <v>176.25</v>
       </c>
       <c r="K115" t="n">
-        <v>-1.82</v>
+        <v>-4.25</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="116">
@@ -6448,31 +6448,31 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>11891</v>
+        <v>11780</v>
       </c>
       <c r="D116" t="n">
         <v>12046.18</v>
       </c>
       <c r="E116" t="n">
-        <v>-155.18</v>
+        <v>-266.18</v>
       </c>
       <c r="F116" t="n">
-        <v>11891</v>
+        <v>12061</v>
       </c>
       <c r="G116" t="n">
         <v>12046.18</v>
       </c>
       <c r="H116" t="n">
-        <v>-155.18</v>
+        <v>14.82</v>
       </c>
       <c r="I116" t="n">
-        <v>11650</v>
+        <v>11720</v>
       </c>
       <c r="J116" t="n">
         <v>11728.34</v>
       </c>
       <c r="K116" t="n">
-        <v>-78.34</v>
+        <v>-8.34</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1.29</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="117">
@@ -6500,31 +6500,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11679</v>
+        <v>11896</v>
       </c>
       <c r="D117" t="n">
         <v>11658.24</v>
       </c>
       <c r="E117" t="n">
-        <v>20.76</v>
+        <v>237.76</v>
       </c>
       <c r="F117" t="n">
-        <v>11899</v>
+        <v>11968</v>
       </c>
       <c r="G117" t="n">
         <v>11951.71</v>
       </c>
       <c r="H117" t="n">
-        <v>-52.71</v>
+        <v>16.29</v>
       </c>
       <c r="I117" t="n">
-        <v>11532</v>
+        <v>11675</v>
       </c>
       <c r="J117" t="n">
         <v>11626.71</v>
       </c>
       <c r="K117" t="n">
-        <v>-94.70999999999999</v>
+        <v>48.29</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="118">
@@ -6552,31 +6552,31 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5333</v>
+        <v>5284</v>
       </c>
       <c r="D118" t="n">
         <v>5415.71</v>
       </c>
       <c r="E118" t="n">
-        <v>-82.70999999999999</v>
+        <v>-131.71</v>
       </c>
       <c r="F118" t="n">
-        <v>5333</v>
+        <v>5330</v>
       </c>
       <c r="G118" t="n">
         <v>5476.36</v>
       </c>
       <c r="H118" t="n">
-        <v>-143.36</v>
+        <v>-146.36</v>
       </c>
       <c r="I118" t="n">
-        <v>5228</v>
+        <v>5217.5</v>
       </c>
       <c r="J118" t="n">
         <v>5328.09</v>
       </c>
       <c r="K118" t="n">
-        <v>-100.09</v>
+        <v>-110.59</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.53</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="119">
@@ -6604,31 +6604,31 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2240</v>
+        <v>2200</v>
       </c>
       <c r="D119" t="n">
         <v>2236.02</v>
       </c>
       <c r="E119" t="n">
-        <v>3.98</v>
+        <v>-36.02</v>
       </c>
       <c r="F119" t="n">
-        <v>2245</v>
+        <v>2237</v>
       </c>
       <c r="G119" t="n">
         <v>2246.63</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.63</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>2192.7</v>
+        <v>2200</v>
       </c>
       <c r="J119" t="n">
         <v>2188.23</v>
       </c>
       <c r="K119" t="n">
-        <v>4.47</v>
+        <v>11.77</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0.18</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="120">
@@ -6656,31 +6656,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1625</v>
+        <v>1643</v>
       </c>
       <c r="D120" t="n">
         <v>1644.81</v>
       </c>
       <c r="E120" t="n">
-        <v>-19.81</v>
+        <v>-1.81</v>
       </c>
       <c r="F120" t="n">
-        <v>1657</v>
+        <v>1660.3</v>
       </c>
       <c r="G120" t="n">
         <v>1660.49</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.49</v>
+        <v>-0.19</v>
       </c>
       <c r="I120" t="n">
-        <v>1622.1</v>
+        <v>1640</v>
       </c>
       <c r="J120" t="n">
         <v>1615.26</v>
       </c>
       <c r="K120" t="n">
-        <v>6.84</v>
+        <v>24.74</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1.2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="121">
@@ -6708,31 +6708,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>187</v>
+        <v>182.5</v>
       </c>
       <c r="D121" t="n">
         <v>183.57</v>
       </c>
       <c r="E121" t="n">
-        <v>3.43</v>
+        <v>-1.07</v>
       </c>
       <c r="F121" t="n">
-        <v>187.6</v>
+        <v>184.85</v>
       </c>
       <c r="G121" t="n">
         <v>192.31</v>
       </c>
       <c r="H121" t="n">
-        <v>-4.71</v>
+        <v>-7.46</v>
       </c>
       <c r="I121" t="n">
-        <v>181.82</v>
+        <v>179.88</v>
       </c>
       <c r="J121" t="n">
         <v>187</v>
       </c>
       <c r="K121" t="n">
-        <v>-5.18</v>
+        <v>-7.12</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1.87</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="122">
@@ -6760,31 +6760,31 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1232.4</v>
+        <v>1275</v>
       </c>
       <c r="D122" t="n">
         <v>1272</v>
       </c>
       <c r="E122" t="n">
-        <v>-39.6</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>1278.7</v>
+        <v>1291.1</v>
       </c>
       <c r="G122" t="n">
         <v>1272</v>
       </c>
       <c r="H122" t="n">
-        <v>6.7</v>
+        <v>19.1</v>
       </c>
       <c r="I122" t="n">
-        <v>1232.4</v>
+        <v>1267</v>
       </c>
       <c r="J122" t="n">
         <v>1225.65</v>
       </c>
       <c r="K122" t="n">
-        <v>6.75</v>
+        <v>41.35</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>3.11</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="123">
@@ -6812,31 +6812,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="D123" t="n">
         <v>5427.13</v>
       </c>
       <c r="E123" t="n">
-        <v>46.87</v>
+        <v>108.87</v>
       </c>
       <c r="F123" t="n">
-        <v>5530</v>
+        <v>5544</v>
       </c>
       <c r="G123" t="n">
         <v>5544.99</v>
       </c>
       <c r="H123" t="n">
-        <v>-14.99</v>
+        <v>-0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>5390</v>
+        <v>5430.5</v>
       </c>
       <c r="J123" t="n">
         <v>5392.25</v>
       </c>
       <c r="K123" t="n">
-        <v>-2.25</v>
+        <v>38.25</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.86</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="124">
@@ -6864,31 +6864,31 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1945</v>
+        <v>1915.2</v>
       </c>
       <c r="D124" t="n">
         <v>1941.54</v>
       </c>
       <c r="E124" t="n">
-        <v>3.46</v>
+        <v>-26.34</v>
       </c>
       <c r="F124" t="n">
-        <v>1945</v>
+        <v>1938.3</v>
       </c>
       <c r="G124" t="n">
         <v>1978.44</v>
       </c>
       <c r="H124" t="n">
-        <v>-33.44</v>
+        <v>-40.14</v>
       </c>
       <c r="I124" t="n">
-        <v>1901.3</v>
+        <v>1914.4</v>
       </c>
       <c r="J124" t="n">
         <v>1924.24</v>
       </c>
       <c r="K124" t="n">
-        <v>-22.94</v>
+        <v>-9.84</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="125">
@@ -6916,31 +6916,31 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>279.85</v>
+        <v>277</v>
       </c>
       <c r="D125" t="n">
         <v>279.35</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5</v>
+        <v>-2.35</v>
       </c>
       <c r="F125" t="n">
-        <v>281.9</v>
+        <v>279.15</v>
       </c>
       <c r="G125" t="n">
         <v>281.63</v>
       </c>
       <c r="H125" t="n">
-        <v>0.27</v>
+        <v>-2.48</v>
       </c>
       <c r="I125" t="n">
-        <v>277</v>
+        <v>273.4</v>
       </c>
       <c r="J125" t="n">
         <v>274.16</v>
       </c>
       <c r="K125" t="n">
-        <v>2.84</v>
+        <v>-0.76</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0.18</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="126">
@@ -6968,31 +6968,31 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4020</v>
+        <v>4037.4</v>
       </c>
       <c r="D126" t="n">
         <v>4082.15</v>
       </c>
       <c r="E126" t="n">
-        <v>-62.15</v>
+        <v>-44.75</v>
       </c>
       <c r="F126" t="n">
-        <v>4044.1</v>
+        <v>4075.5</v>
       </c>
       <c r="G126" t="n">
         <v>4087.49</v>
       </c>
       <c r="H126" t="n">
-        <v>-43.39</v>
+        <v>-11.99</v>
       </c>
       <c r="I126" t="n">
-        <v>3990</v>
+        <v>4028.5</v>
       </c>
       <c r="J126" t="n">
         <v>3975.44</v>
       </c>
       <c r="K126" t="n">
-        <v>14.56</v>
+        <v>53.06</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="127">
@@ -7020,31 +7020,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>512.05</v>
+        <v>512</v>
       </c>
       <c r="D127" t="n">
         <v>509.19</v>
       </c>
       <c r="E127" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="F127" t="n">
-        <v>523.8</v>
+        <v>512</v>
       </c>
       <c r="G127" t="n">
         <v>509.19</v>
       </c>
       <c r="H127" t="n">
-        <v>14.61</v>
+        <v>2.81</v>
       </c>
       <c r="I127" t="n">
-        <v>510.4</v>
+        <v>498.75</v>
       </c>
       <c r="J127" t="n">
         <v>499.53</v>
       </c>
       <c r="K127" t="n">
-        <v>10.87</v>
+        <v>-0.78</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="128">
@@ -7081,22 +7081,22 @@
         <v>-21.08</v>
       </c>
       <c r="F128" t="n">
-        <v>1468.8</v>
+        <v>1469.8</v>
       </c>
       <c r="G128" t="n">
         <v>1492.03</v>
       </c>
       <c r="H128" t="n">
-        <v>-23.23</v>
+        <v>-22.23</v>
       </c>
       <c r="I128" t="n">
-        <v>1456.1</v>
+        <v>1457.2</v>
       </c>
       <c r="J128" t="n">
         <v>1451.28</v>
       </c>
       <c r="K128" t="n">
-        <v>4.82</v>
+        <v>5.92</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7124,31 +7124,31 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>614.65</v>
+        <v>616</v>
       </c>
       <c r="D129" t="n">
         <v>598.79</v>
       </c>
       <c r="E129" t="n">
-        <v>15.86</v>
+        <v>17.21</v>
       </c>
       <c r="F129" t="n">
-        <v>620.8</v>
+        <v>627</v>
       </c>
       <c r="G129" t="n">
         <v>615.76</v>
       </c>
       <c r="H129" t="n">
-        <v>5.04</v>
+        <v>11.24</v>
       </c>
       <c r="I129" t="n">
-        <v>604.25</v>
+        <v>613.1</v>
       </c>
       <c r="J129" t="n">
         <v>598.5599999999999</v>
       </c>
       <c r="K129" t="n">
-        <v>5.69</v>
+        <v>14.54</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="130">
@@ -7176,31 +7176,31 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1801.5</v>
+        <v>1819</v>
       </c>
       <c r="D130" t="n">
         <v>1867.32</v>
       </c>
       <c r="E130" t="n">
-        <v>-65.81999999999999</v>
+        <v>-48.32</v>
       </c>
       <c r="F130" t="n">
-        <v>1819.1</v>
+        <v>1836</v>
       </c>
       <c r="G130" t="n">
         <v>1867.32</v>
       </c>
       <c r="H130" t="n">
-        <v>-48.22</v>
+        <v>-31.32</v>
       </c>
       <c r="I130" t="n">
-        <v>1780.4</v>
+        <v>1809.8</v>
       </c>
       <c r="J130" t="n">
         <v>1742.03</v>
       </c>
       <c r="K130" t="n">
-        <v>38.37</v>
+        <v>67.77</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3.52</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="131">
@@ -7228,31 +7228,31 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3403.6</v>
+        <v>3460.1</v>
       </c>
       <c r="D131" t="n">
         <v>3383.96</v>
       </c>
       <c r="E131" t="n">
-        <v>19.64</v>
+        <v>76.14</v>
       </c>
       <c r="F131" t="n">
-        <v>3471.8</v>
+        <v>3514.6</v>
       </c>
       <c r="G131" t="n">
         <v>3406.31</v>
       </c>
       <c r="H131" t="n">
-        <v>65.48999999999999</v>
+        <v>108.29</v>
       </c>
       <c r="I131" t="n">
-        <v>3403.6</v>
+        <v>3455.1</v>
       </c>
       <c r="J131" t="n">
         <v>3320.14</v>
       </c>
       <c r="K131" t="n">
-        <v>83.45999999999999</v>
+        <v>134.96</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0.58</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="132">
@@ -7280,31 +7280,31 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2020.5</v>
+        <v>2032</v>
       </c>
       <c r="D132" t="n">
         <v>2089.33</v>
       </c>
       <c r="E132" t="n">
-        <v>-68.83</v>
+        <v>-57.33</v>
       </c>
       <c r="F132" t="n">
-        <v>2028.4</v>
+        <v>2043.9</v>
       </c>
       <c r="G132" t="n">
         <v>2089.33</v>
       </c>
       <c r="H132" t="n">
-        <v>-60.93</v>
+        <v>-45.43</v>
       </c>
       <c r="I132" t="n">
-        <v>2006.1</v>
+        <v>2012</v>
       </c>
       <c r="J132" t="n">
         <v>1973.8</v>
       </c>
       <c r="K132" t="n">
-        <v>32.3</v>
+        <v>38.2</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="133">
@@ -7332,31 +7332,31 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="D133" t="n">
         <v>1377.37</v>
       </c>
       <c r="E133" t="n">
-        <v>-38.37</v>
+        <v>-17.37</v>
       </c>
       <c r="F133" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="G133" t="n">
         <v>1377.37</v>
       </c>
       <c r="H133" t="n">
-        <v>-13.37</v>
+        <v>13.63</v>
       </c>
       <c r="I133" t="n">
-        <v>1329.6</v>
+        <v>1291.1</v>
       </c>
       <c r="J133" t="n">
         <v>1298.83</v>
       </c>
       <c r="K133" t="n">
-        <v>30.77</v>
+        <v>-7.73</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2.79</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="134">
@@ -7384,31 +7384,31 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>13800</v>
+        <v>14023</v>
       </c>
       <c r="D134" t="n">
         <v>14041.16</v>
       </c>
       <c r="E134" t="n">
-        <v>-241.16</v>
+        <v>-18.16</v>
       </c>
       <c r="F134" t="n">
-        <v>14090</v>
+        <v>14198</v>
       </c>
       <c r="G134" t="n">
         <v>14041.16</v>
       </c>
       <c r="H134" t="n">
-        <v>48.84</v>
+        <v>156.84</v>
       </c>
       <c r="I134" t="n">
-        <v>13670</v>
+        <v>14011</v>
       </c>
       <c r="J134" t="n">
         <v>13456.8</v>
       </c>
       <c r="K134" t="n">
-        <v>213.2</v>
+        <v>554.2</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1.72</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="135">
@@ -7436,31 +7436,31 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="D135" t="n">
         <v>1202.46</v>
       </c>
       <c r="E135" t="n">
-        <v>-41.46</v>
+        <v>-34.46</v>
       </c>
       <c r="F135" t="n">
-        <v>1167.5</v>
+        <v>1176.7</v>
       </c>
       <c r="G135" t="n">
         <v>1202.46</v>
       </c>
       <c r="H135" t="n">
-        <v>-34.96</v>
+        <v>-25.76</v>
       </c>
       <c r="I135" t="n">
-        <v>1140</v>
+        <v>1147.8</v>
       </c>
       <c r="J135" t="n">
         <v>1145.8</v>
       </c>
       <c r="K135" t="n">
-        <v>-5.8</v>
+        <v>2</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="136">
@@ -7488,31 +7488,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>314.05</v>
+        <v>318</v>
       </c>
       <c r="D136" t="n">
         <v>304.31</v>
       </c>
       <c r="E136" t="n">
-        <v>9.74</v>
+        <v>13.69</v>
       </c>
       <c r="F136" t="n">
-        <v>318.95</v>
+        <v>318.5</v>
       </c>
       <c r="G136" t="n">
         <v>318.08</v>
       </c>
       <c r="H136" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>312.6</v>
+        <v>306.2</v>
       </c>
       <c r="J136" t="n">
         <v>309.31</v>
       </c>
       <c r="K136" t="n">
-        <v>3.29</v>
+        <v>-3.11</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -8076,31 +8076,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="D7" t="n">
         <v>1202.46</v>
       </c>
       <c r="E7" t="n">
-        <v>-41.46</v>
+        <v>-34.46</v>
       </c>
       <c r="F7" t="n">
-        <v>1167.5</v>
+        <v>1176.7</v>
       </c>
       <c r="G7" t="n">
         <v>1202.46</v>
       </c>
       <c r="H7" t="n">
-        <v>-34.96</v>
+        <v>-25.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1140</v>
+        <v>1147.8</v>
       </c>
       <c r="J7" t="n">
         <v>1145.8</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.8</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -8474,31 +8474,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>614.65</v>
+        <v>616</v>
       </c>
       <c r="D7" t="n">
         <v>598.79</v>
       </c>
       <c r="E7" t="n">
-        <v>15.86</v>
+        <v>17.21</v>
       </c>
       <c r="F7" t="n">
-        <v>620.8</v>
+        <v>627</v>
       </c>
       <c r="G7" t="n">
         <v>615.76</v>
       </c>
       <c r="H7" t="n">
-        <v>5.04</v>
+        <v>11.24</v>
       </c>
       <c r="I7" t="n">
-        <v>604.25</v>
+        <v>613.1</v>
       </c>
       <c r="J7" t="n">
         <v>598.5599999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>5.69</v>
+        <v>14.54</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -8872,31 +8872,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8049</v>
+        <v>8000</v>
       </c>
       <c r="D7" t="n">
         <v>8061.87</v>
       </c>
       <c r="E7" t="n">
-        <v>-12.87</v>
+        <v>-61.87</v>
       </c>
       <c r="F7" t="n">
-        <v>8049</v>
+        <v>8110</v>
       </c>
       <c r="G7" t="n">
         <v>8245.42</v>
       </c>
       <c r="H7" t="n">
-        <v>-196.42</v>
+        <v>-135.42</v>
       </c>
       <c r="I7" t="n">
-        <v>7940</v>
+        <v>7955</v>
       </c>
       <c r="J7" t="n">
         <v>8021.49</v>
       </c>
       <c r="K7" t="n">
-        <v>-81.48999999999999</v>
+        <v>-66.48999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -9564,31 +9564,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1625</v>
+        <v>1643</v>
       </c>
       <c r="D7" t="n">
         <v>1644.81</v>
       </c>
       <c r="E7" t="n">
-        <v>-19.81</v>
+        <v>-1.81</v>
       </c>
       <c r="F7" t="n">
-        <v>1657</v>
+        <v>1660.3</v>
       </c>
       <c r="G7" t="n">
         <v>1660.49</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.49</v>
+        <v>-0.19</v>
       </c>
       <c r="I7" t="n">
-        <v>1622.1</v>
+        <v>1640</v>
       </c>
       <c r="J7" t="n">
         <v>1615.26</v>
       </c>
       <c r="K7" t="n">
-        <v>6.84</v>
+        <v>24.74</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -9962,31 +9962,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>314.05</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
         <v>304.31</v>
       </c>
       <c r="E7" t="n">
-        <v>9.74</v>
+        <v>13.69</v>
       </c>
       <c r="F7" t="n">
-        <v>318.95</v>
+        <v>318.5</v>
       </c>
       <c r="G7" t="n">
         <v>318.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="I7" t="n">
-        <v>312.6</v>
+        <v>306.2</v>
       </c>
       <c r="J7" t="n">
         <v>309.31</v>
       </c>
       <c r="K7" t="n">
-        <v>3.29</v>
+        <v>-3.11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -10360,31 +10360,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13800</v>
+        <v>14023</v>
       </c>
       <c r="D7" t="n">
         <v>14041.16</v>
       </c>
       <c r="E7" t="n">
-        <v>-241.16</v>
+        <v>-18.16</v>
       </c>
       <c r="F7" t="n">
-        <v>14090</v>
+        <v>14198</v>
       </c>
       <c r="G7" t="n">
         <v>14041.16</v>
       </c>
       <c r="H7" t="n">
-        <v>48.84</v>
+        <v>156.84</v>
       </c>
       <c r="I7" t="n">
-        <v>13670</v>
+        <v>14011</v>
       </c>
       <c r="J7" t="n">
         <v>13456.8</v>
       </c>
       <c r="K7" t="n">
-        <v>213.2</v>
+        <v>554.2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -10758,31 +10758,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1801.5</v>
+        <v>1819</v>
       </c>
       <c r="D7" t="n">
         <v>1867.32</v>
       </c>
       <c r="E7" t="n">
-        <v>-65.81999999999999</v>
+        <v>-48.32</v>
       </c>
       <c r="F7" t="n">
-        <v>1819.1</v>
+        <v>1836</v>
       </c>
       <c r="G7" t="n">
         <v>1867.32</v>
       </c>
       <c r="H7" t="n">
-        <v>-48.22</v>
+        <v>-31.32</v>
       </c>
       <c r="I7" t="n">
-        <v>1780.4</v>
+        <v>1809.8</v>
       </c>
       <c r="J7" t="n">
         <v>1742.03</v>
       </c>
       <c r="K7" t="n">
-        <v>38.37</v>
+        <v>67.77</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.52</v>
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>
@@ -11104,31 +11104,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="D6" t="n">
         <v>5427.13</v>
       </c>
       <c r="E6" t="n">
-        <v>46.87</v>
+        <v>108.87</v>
       </c>
       <c r="F6" t="n">
-        <v>5530</v>
+        <v>5544</v>
       </c>
       <c r="G6" t="n">
         <v>5544.99</v>
       </c>
       <c r="H6" t="n">
-        <v>-14.99</v>
+        <v>-0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>5390</v>
+        <v>5430.5</v>
       </c>
       <c r="J6" t="n">
         <v>5392.25</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.25</v>
+        <v>38.25</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.86</v>
+        <v>2.01</v>
       </c>
     </row>
   </sheetData>
@@ -11502,31 +11502,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>118.98</v>
+        <v>114.03</v>
       </c>
       <c r="D7" t="n">
         <v>117.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.88</v>
+        <v>-3.07</v>
       </c>
       <c r="F7" t="n">
-        <v>119.5</v>
+        <v>114.3</v>
       </c>
       <c r="G7" t="n">
         <v>120.99</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.49</v>
+        <v>-6.69</v>
       </c>
       <c r="I7" t="n">
-        <v>113.72</v>
+        <v>112.3</v>
       </c>
       <c r="J7" t="n">
         <v>117.76</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.04</v>
+        <v>-5.46</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -11535,11 +11535,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>
@@ -11848,31 +11848,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3403.6</v>
+        <v>3460.1</v>
       </c>
       <c r="D6" t="n">
         <v>3383.96</v>
       </c>
       <c r="E6" t="n">
-        <v>19.64</v>
+        <v>76.14</v>
       </c>
       <c r="F6" t="n">
-        <v>3471.8</v>
+        <v>3514.6</v>
       </c>
       <c r="G6" t="n">
         <v>3406.31</v>
       </c>
       <c r="H6" t="n">
-        <v>65.48999999999999</v>
+        <v>108.29</v>
       </c>
       <c r="I6" t="n">
-        <v>3403.6</v>
+        <v>3455.1</v>
       </c>
       <c r="J6" t="n">
         <v>3320.14</v>
       </c>
       <c r="K6" t="n">
-        <v>83.45999999999999</v>
+        <v>134.96</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
@@ -12194,31 +12194,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>512.05</v>
+        <v>512</v>
       </c>
       <c r="D6" t="n">
         <v>509.19</v>
       </c>
       <c r="E6" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="F6" t="n">
-        <v>523.8</v>
+        <v>512</v>
       </c>
       <c r="G6" t="n">
         <v>509.19</v>
       </c>
       <c r="H6" t="n">
-        <v>14.61</v>
+        <v>2.81</v>
       </c>
       <c r="I6" t="n">
-        <v>510.4</v>
+        <v>498.75</v>
       </c>
       <c r="J6" t="n">
         <v>499.53</v>
       </c>
       <c r="K6" t="n">
-        <v>10.87</v>
+        <v>-0.78</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -13033,22 +13033,22 @@
         <v>-21.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1468.8</v>
+        <v>1469.8</v>
       </c>
       <c r="G7" t="n">
         <v>1492.03</v>
       </c>
       <c r="H7" t="n">
-        <v>-23.23</v>
+        <v>-22.23</v>
       </c>
       <c r="I7" t="n">
-        <v>1456.1</v>
+        <v>1457.2</v>
       </c>
       <c r="J7" t="n">
         <v>1451.28</v>
       </c>
       <c r="K7" t="n">
-        <v>4.82</v>
+        <v>5.92</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -13664,31 +13664,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11891</v>
+        <v>11780</v>
       </c>
       <c r="D7" t="n">
         <v>12046.18</v>
       </c>
       <c r="E7" t="n">
-        <v>-155.18</v>
+        <v>-266.18</v>
       </c>
       <c r="F7" t="n">
-        <v>11891</v>
+        <v>12061</v>
       </c>
       <c r="G7" t="n">
         <v>12046.18</v>
       </c>
       <c r="H7" t="n">
-        <v>-155.18</v>
+        <v>14.82</v>
       </c>
       <c r="I7" t="n">
-        <v>11650</v>
+        <v>11720</v>
       </c>
       <c r="J7" t="n">
         <v>11728.34</v>
       </c>
       <c r="K7" t="n">
-        <v>-78.34</v>
+        <v>-8.34</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>
@@ -14252,31 +14252,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2740</v>
+        <v>2735.5</v>
       </c>
       <c r="D7" t="n">
         <v>2844.75</v>
       </c>
       <c r="E7" t="n">
-        <v>-104.75</v>
+        <v>-109.25</v>
       </c>
       <c r="F7" t="n">
-        <v>2748.4</v>
+        <v>2747.6</v>
       </c>
       <c r="G7" t="n">
         <v>2844.75</v>
       </c>
       <c r="H7" t="n">
-        <v>-96.34999999999999</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2698.2</v>
+        <v>2720</v>
       </c>
       <c r="J7" t="n">
         <v>2740</v>
       </c>
       <c r="K7" t="n">
-        <v>-41.8</v>
+        <v>-20</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -14285,11 +14285,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7526,6 +7526,1618 @@
       </c>
       <c r="N136" t="n">
         <v>4.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8011</v>
+      </c>
+      <c r="J137" t="n">
+        <v>7927.17</v>
+      </c>
+      <c r="K137" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1071.36</v>
+      </c>
+      <c r="E138" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1086.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1094.8</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1074.26</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1651.35</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1652.8</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1661.69</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1626.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1630.69</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1252.87</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1264.7</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1254.77</v>
+      </c>
+      <c r="H140" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1237</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1231.28</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5523</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-155.86</v>
+      </c>
+      <c r="F141" t="n">
+        <v>5529</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-149.86</v>
+      </c>
+      <c r="I141" t="n">
+        <v>5406</v>
+      </c>
+      <c r="J141" t="n">
+        <v>5482.76</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="E142" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1829.9</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="H142" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1788</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1760.38</v>
+      </c>
+      <c r="K142" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5281.32</v>
+      </c>
+      <c r="E143" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5323.7</v>
+      </c>
+      <c r="H143" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5281.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>5225.19</v>
+      </c>
+      <c r="K143" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D144" t="n">
+        <v>11583.54</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-83.54000000000001</v>
+      </c>
+      <c r="F144" t="n">
+        <v>11570</v>
+      </c>
+      <c r="G144" t="n">
+        <v>11583.54</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-13.54</v>
+      </c>
+      <c r="I144" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J144" t="n">
+        <v>11237.11</v>
+      </c>
+      <c r="K144" t="n">
+        <v>172.89</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D145" t="n">
+        <v>5748.02</v>
+      </c>
+      <c r="E145" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5934</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5783.85</v>
+      </c>
+      <c r="H145" t="n">
+        <v>150.15</v>
+      </c>
+      <c r="I145" t="n">
+        <v>5802</v>
+      </c>
+      <c r="J145" t="n">
+        <v>5685.73</v>
+      </c>
+      <c r="K145" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2670.88</v>
+      </c>
+      <c r="E146" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2779.43</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-23.93</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2727.08</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>615</v>
+      </c>
+      <c r="D147" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-22.74</v>
+      </c>
+      <c r="F147" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="G147" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-22.44</v>
+      </c>
+      <c r="I147" t="n">
+        <v>603</v>
+      </c>
+      <c r="J147" t="n">
+        <v>599.63</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4058.3</v>
+      </c>
+      <c r="E148" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="G148" t="n">
+        <v>4090.61</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-19.91</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4013.03</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-23.03</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3428.2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-105.18</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3440</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-93.38</v>
+      </c>
+      <c r="I149" t="n">
+        <v>3396.5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3329.44</v>
+      </c>
+      <c r="K149" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>318</v>
+      </c>
+      <c r="D150" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="F150" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="G150" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-15.61</v>
+      </c>
+      <c r="I150" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>313.13</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>533.65</v>
+      </c>
+      <c r="D151" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="F151" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="I151" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>517.74</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>14035</v>
+      </c>
+      <c r="D152" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-94.03</v>
+      </c>
+      <c r="F152" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G152" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-64.03</v>
+      </c>
+      <c r="I152" t="n">
+        <v>13645</v>
+      </c>
+      <c r="J152" t="n">
+        <v>13608.7</v>
+      </c>
+      <c r="K152" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="D153" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F153" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="G153" t="n">
+        <v>188.82</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I153" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="J153" t="n">
+        <v>185.29</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="D154" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F154" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="G154" t="n">
+        <v>176.89</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I154" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="J154" t="n">
+        <v>173.52</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1357.3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1350.91</v>
+      </c>
+      <c r="E155" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1369.4</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1350.91</v>
+      </c>
+      <c r="H155" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1305.64</v>
+      </c>
+      <c r="K155" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1985.19</v>
+      </c>
+      <c r="E156" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1985.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="I156" t="n">
+        <v>2006.7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1968.88</v>
+      </c>
+      <c r="K156" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>7710</v>
+      </c>
+      <c r="D157" t="n">
+        <v>7639.04</v>
+      </c>
+      <c r="E157" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>7772</v>
+      </c>
+      <c r="G157" t="n">
+        <v>7823.79</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-51.79</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7659</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7678.06</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-19.06</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>11706</v>
+      </c>
+      <c r="D158" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="E158" t="n">
+        <v>167.12</v>
+      </c>
+      <c r="F158" t="n">
+        <v>11905</v>
+      </c>
+      <c r="G158" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="H158" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="I158" t="n">
+        <v>11570</v>
+      </c>
+      <c r="J158" t="n">
+        <v>11473.64</v>
+      </c>
+      <c r="K158" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2237.1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2218.67</v>
+      </c>
+      <c r="E159" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2273.9</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2218.67</v>
+      </c>
+      <c r="H159" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2219.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2173.44</v>
+      </c>
+      <c r="K159" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1939.1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1928.09</v>
+      </c>
+      <c r="E160" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1957.36</v>
+      </c>
+      <c r="H160" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1920.55</v>
+      </c>
+      <c r="K160" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1046.25</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E161" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1052.94</v>
+      </c>
+      <c r="H161" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1040</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1033.02</v>
+      </c>
+      <c r="K161" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="D162" t="n">
+        <v>115.42</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F162" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="G162" t="n">
+        <v>116.28</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I162" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="J162" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="D163" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F163" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="G163" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="H163" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="I163" t="n">
+        <v>273</v>
+      </c>
+      <c r="J163" t="n">
+        <v>272.79</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1158.28</v>
+      </c>
+      <c r="E164" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1184.9</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1176.27</v>
+      </c>
+      <c r="H164" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1149.2</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1153.53</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="D165" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F165" t="n">
+        <v>413.65</v>
+      </c>
+      <c r="G165" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="H165" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="I165" t="n">
+        <v>400</v>
+      </c>
+      <c r="J165" t="n">
+        <v>387.32</v>
+      </c>
+      <c r="K165" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1458.8</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1451.27</v>
+      </c>
+      <c r="E166" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1476.44</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1456.2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1452.16</v>
+      </c>
+      <c r="K166" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>897</v>
+      </c>
+      <c r="D167" t="n">
+        <v>887.36</v>
+      </c>
+      <c r="E167" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="F167" t="n">
+        <v>903.8</v>
+      </c>
+      <c r="G167" t="n">
+        <v>906.5599999999999</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="I167" t="n">
+        <v>883.15</v>
+      </c>
+      <c r="J167" t="n">
+        <v>889.5599999999999</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>
@@ -7729,7 +9341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8114,6 +9726,58 @@
       </c>
       <c r="N7" t="n">
         <v>2.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1158.28</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1184.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1176.27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1149.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1153.53</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>
@@ -8127,7 +9791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8512,6 +10176,58 @@
       </c>
       <c r="N7" t="n">
         <v>2.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>615</v>
+      </c>
+      <c r="D8" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-22.74</v>
+      </c>
+      <c r="F8" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-22.44</v>
+      </c>
+      <c r="I8" t="n">
+        <v>603</v>
+      </c>
+      <c r="J8" t="n">
+        <v>599.63</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>3.57</v>
       </c>
     </row>
   </sheetData>
@@ -8525,7 +10241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8910,6 +10626,58 @@
       </c>
       <c r="N7" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8011</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7927.17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -9217,7 +10985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9602,6 +11370,58 @@
       </c>
       <c r="N7" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1651.35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1652.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1661.69</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1626.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1630.69</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -9615,7 +11435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10000,6 +11820,58 @@
       </c>
       <c r="N7" t="n">
         <v>4.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>318</v>
+      </c>
+      <c r="D8" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="F8" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-15.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>313.13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5.06</v>
       </c>
     </row>
   </sheetData>
@@ -10013,7 +11885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10398,6 +12270,58 @@
       </c>
       <c r="N7" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14035</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-94.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-64.03</v>
+      </c>
+      <c r="I8" t="n">
+        <v>13645</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13608.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -10411,7 +12335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10796,6 +12720,58 @@
       </c>
       <c r="N7" t="n">
         <v>2.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1829.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1788</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1760.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>
@@ -10809,7 +12785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,6 +13118,58 @@
       </c>
       <c r="N6" t="n">
         <v>2.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5523</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-155.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5529</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-149.86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5406</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5482.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.74</v>
       </c>
     </row>
   </sheetData>
@@ -11155,7 +13183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +13568,58 @@
       </c>
       <c r="N7" t="n">
         <v>2.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>115.42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>116.28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I8" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="J8" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>
@@ -11553,7 +13633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11886,6 +13966,58 @@
       </c>
       <c r="N6" t="n">
         <v>2.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3428.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-105.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3440</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-93.38</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3396.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3329.44</v>
+      </c>
+      <c r="K7" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.98</v>
       </c>
     </row>
   </sheetData>
@@ -11899,7 +14031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12232,6 +14364,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>533.65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="I7" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>517.74</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
@@ -12677,7 +14861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13062,6 +15246,58 @@
       </c>
       <c r="N7" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1458.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1451.27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1476.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1456.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1452.16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -13317,7 +15553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13702,6 +15938,58 @@
       </c>
       <c r="N7" t="n">
         <v>2.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>11706</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>167.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11905</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="H8" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11570</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11473.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -13905,7 +16193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14292,6 +16580,58 @@
         <v>3.84</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2670.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2779.43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-23.93</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2727.08</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Stocks Accuracy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PNB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="IEX" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ALKEM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CIPLA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RECLTD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ULTRACEMCO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="HAL" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ASIANPAINT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="INDHOTEL" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="360ONE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="PGEL" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="EICHERMOT" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="GODREJPROP" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TECHM" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ETERNAL" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="DIXON" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="COFORGE" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="PERSISTENT" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="M&amp;M" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="CONCOR" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Stocks Accuracy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IEX" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALKEM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIPLA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECLTD" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ULTRACEMCO" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIANPAINT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDHOTEL" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="360ONE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGEL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EICHERMOT" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GODREJPROP" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TECHM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETERNAL" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIXON" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COFORGE" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSISTENT" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M&amp;M" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONCOR" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7540,31 +7540,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="D137" t="n">
         <v>8102.18</v>
       </c>
       <c r="E137" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="F137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="G137" t="n">
         <v>8102.18</v>
       </c>
       <c r="H137" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="I137" t="n">
-        <v>8011</v>
+        <v>7940</v>
       </c>
       <c r="J137" t="n">
         <v>7927.17</v>
       </c>
       <c r="K137" t="n">
-        <v>83.83</v>
+        <v>12.83</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>0.03</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="138">
@@ -7592,31 +7592,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D138" t="n">
         <v>1071.36</v>
       </c>
       <c r="E138" t="n">
-        <v>11.64</v>
+        <v>10.64</v>
       </c>
       <c r="F138" t="n">
-        <v>1086.8</v>
+        <v>1085.5</v>
       </c>
       <c r="G138" t="n">
         <v>1094.8</v>
       </c>
       <c r="H138" t="n">
-        <v>-8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="J138" t="n">
         <v>1074.26</v>
       </c>
       <c r="K138" t="n">
-        <v>-1.26</v>
+        <v>-8.26</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="139">
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="D139" t="n">
         <v>1651.35</v>
       </c>
       <c r="E139" t="n">
-        <v>-12.35</v>
+        <v>-26.35</v>
       </c>
       <c r="F139" t="n">
-        <v>1652.8</v>
+        <v>1657</v>
       </c>
       <c r="G139" t="n">
         <v>1661.69</v>
       </c>
       <c r="H139" t="n">
-        <v>-8.890000000000001</v>
+        <v>-4.69</v>
       </c>
       <c r="I139" t="n">
-        <v>1626.3</v>
+        <v>1622.1</v>
       </c>
       <c r="J139" t="n">
         <v>1630.69</v>
       </c>
       <c r="K139" t="n">
-        <v>-4.39</v>
+        <v>-8.59</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="140">
@@ -7696,31 +7696,31 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1240</v>
+        <v>1232.4</v>
       </c>
       <c r="D140" t="n">
         <v>1252.87</v>
       </c>
       <c r="E140" t="n">
-        <v>-12.87</v>
+        <v>-20.47</v>
       </c>
       <c r="F140" t="n">
-        <v>1264.7</v>
+        <v>1278.7</v>
       </c>
       <c r="G140" t="n">
         <v>1254.77</v>
       </c>
       <c r="H140" t="n">
-        <v>9.93</v>
+        <v>23.93</v>
       </c>
       <c r="I140" t="n">
-        <v>1237</v>
+        <v>1232.4</v>
       </c>
       <c r="J140" t="n">
         <v>1231.28</v>
       </c>
       <c r="K140" t="n">
-        <v>5.72</v>
+        <v>1.12</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="141">
@@ -7748,31 +7748,31 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5523</v>
+        <v>5474</v>
       </c>
       <c r="D141" t="n">
         <v>5678.86</v>
       </c>
       <c r="E141" t="n">
-        <v>-155.86</v>
+        <v>-204.86</v>
       </c>
       <c r="F141" t="n">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G141" t="n">
         <v>5678.86</v>
       </c>
       <c r="H141" t="n">
-        <v>-149.86</v>
+        <v>-148.86</v>
       </c>
       <c r="I141" t="n">
-        <v>5406</v>
+        <v>5390</v>
       </c>
       <c r="J141" t="n">
         <v>5482.76</v>
       </c>
       <c r="K141" t="n">
-        <v>-76.76000000000001</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7781,11 +7781,11 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2.74</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="142">
@@ -7800,31 +7800,31 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1829</v>
+        <v>1801.5</v>
       </c>
       <c r="D142" t="n">
         <v>1795.92</v>
       </c>
       <c r="E142" t="n">
-        <v>33.08</v>
+        <v>5.58</v>
       </c>
       <c r="F142" t="n">
-        <v>1829.9</v>
+        <v>1819.1</v>
       </c>
       <c r="G142" t="n">
         <v>1795.92</v>
       </c>
       <c r="H142" t="n">
-        <v>33.98</v>
+        <v>23.18</v>
       </c>
       <c r="I142" t="n">
-        <v>1788</v>
+        <v>1780.4</v>
       </c>
       <c r="J142" t="n">
         <v>1760.38</v>
       </c>
       <c r="K142" t="n">
-        <v>27.62</v>
+        <v>20.02</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1.84</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="143">
@@ -7852,31 +7852,31 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="D143" t="n">
         <v>5281.32</v>
       </c>
       <c r="E143" t="n">
-        <v>88.68000000000001</v>
+        <v>51.68</v>
       </c>
       <c r="F143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="G143" t="n">
         <v>5323.7</v>
       </c>
       <c r="H143" t="n">
-        <v>46.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I143" t="n">
-        <v>5281.5</v>
+        <v>5228</v>
       </c>
       <c r="J143" t="n">
         <v>5225.19</v>
       </c>
       <c r="K143" t="n">
-        <v>56.31</v>
+        <v>2.81</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1.68</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="144">
@@ -7904,22 +7904,22 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>11500</v>
+        <v>11579</v>
       </c>
       <c r="D144" t="n">
         <v>11583.54</v>
       </c>
       <c r="E144" t="n">
-        <v>-83.54000000000001</v>
+        <v>-4.54</v>
       </c>
       <c r="F144" t="n">
-        <v>11570</v>
+        <v>11587</v>
       </c>
       <c r="G144" t="n">
         <v>11583.54</v>
       </c>
       <c r="H144" t="n">
-        <v>-13.54</v>
+        <v>3.46</v>
       </c>
       <c r="I144" t="n">
         <v>11410</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0.72</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="145">
@@ -7956,31 +7956,31 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5850</v>
+        <v>5895</v>
       </c>
       <c r="D145" t="n">
         <v>5748.02</v>
       </c>
       <c r="E145" t="n">
-        <v>101.98</v>
+        <v>146.98</v>
       </c>
       <c r="F145" t="n">
-        <v>5934</v>
+        <v>5916</v>
       </c>
       <c r="G145" t="n">
         <v>5783.85</v>
       </c>
       <c r="H145" t="n">
-        <v>150.15</v>
+        <v>132.15</v>
       </c>
       <c r="I145" t="n">
-        <v>5802</v>
+        <v>5844</v>
       </c>
       <c r="J145" t="n">
         <v>5685.73</v>
       </c>
       <c r="K145" t="n">
-        <v>116.27</v>
+        <v>158.27</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="146">
@@ -8008,31 +8008,31 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2755.5</v>
+        <v>2740</v>
       </c>
       <c r="D146" t="n">
         <v>2670.88</v>
       </c>
       <c r="E146" t="n">
-        <v>84.62</v>
+        <v>69.12</v>
       </c>
       <c r="F146" t="n">
-        <v>2755.5</v>
+        <v>2748.4</v>
       </c>
       <c r="G146" t="n">
         <v>2779.43</v>
       </c>
       <c r="H146" t="n">
-        <v>-23.93</v>
+        <v>-31.03</v>
       </c>
       <c r="I146" t="n">
-        <v>2720</v>
+        <v>2698.2</v>
       </c>
       <c r="J146" t="n">
         <v>2727.08</v>
       </c>
       <c r="K146" t="n">
-        <v>-7.08</v>
+        <v>-28.88</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>3.17</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="147">
@@ -8060,31 +8060,31 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>615</v>
+        <v>614.65</v>
       </c>
       <c r="D147" t="n">
         <v>637.74</v>
       </c>
       <c r="E147" t="n">
-        <v>-22.74</v>
+        <v>-23.09</v>
       </c>
       <c r="F147" t="n">
-        <v>615.3</v>
+        <v>620.8</v>
       </c>
       <c r="G147" t="n">
         <v>637.74</v>
       </c>
       <c r="H147" t="n">
-        <v>-22.44</v>
+        <v>-16.94</v>
       </c>
       <c r="I147" t="n">
-        <v>603</v>
+        <v>604.25</v>
       </c>
       <c r="J147" t="n">
         <v>599.63</v>
       </c>
       <c r="K147" t="n">
-        <v>3.37</v>
+        <v>4.62</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="148">
@@ -8112,22 +8112,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4070.7</v>
+        <v>4020</v>
       </c>
       <c r="D148" t="n">
         <v>4058.3</v>
       </c>
       <c r="E148" t="n">
-        <v>12.4</v>
+        <v>-38.3</v>
       </c>
       <c r="F148" t="n">
-        <v>4070.7</v>
+        <v>4044.1</v>
       </c>
       <c r="G148" t="n">
         <v>4090.61</v>
       </c>
       <c r="H148" t="n">
-        <v>-19.91</v>
+        <v>-46.51</v>
       </c>
       <c r="I148" t="n">
         <v>3990</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>0.31</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8164,31 +8164,31 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3428.2</v>
+        <v>3403.6</v>
       </c>
       <c r="D149" t="n">
         <v>3533.38</v>
       </c>
       <c r="E149" t="n">
-        <v>-105.18</v>
+        <v>-129.78</v>
       </c>
       <c r="F149" t="n">
-        <v>3440</v>
+        <v>3471.8</v>
       </c>
       <c r="G149" t="n">
         <v>3533.38</v>
       </c>
       <c r="H149" t="n">
-        <v>-93.38</v>
+        <v>-61.58</v>
       </c>
       <c r="I149" t="n">
-        <v>3396.5</v>
+        <v>3403.6</v>
       </c>
       <c r="J149" t="n">
         <v>3329.44</v>
       </c>
       <c r="K149" t="n">
-        <v>67.06</v>
+        <v>74.16</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="150">
@@ -8216,31 +8216,31 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>318</v>
+        <v>314.05</v>
       </c>
       <c r="D150" t="n">
         <v>334.96</v>
       </c>
       <c r="E150" t="n">
-        <v>-16.96</v>
+        <v>-20.91</v>
       </c>
       <c r="F150" t="n">
-        <v>319.35</v>
+        <v>318.95</v>
       </c>
       <c r="G150" t="n">
         <v>334.96</v>
       </c>
       <c r="H150" t="n">
-        <v>-15.61</v>
+        <v>-16.01</v>
       </c>
       <c r="I150" t="n">
-        <v>313.3</v>
+        <v>312.6</v>
       </c>
       <c r="J150" t="n">
         <v>313.13</v>
       </c>
       <c r="K150" t="n">
-        <v>0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>5.06</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="151">
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>533.65</v>
+        <v>512.05</v>
       </c>
       <c r="D151" t="n">
         <v>540.89</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.24</v>
+        <v>-28.84</v>
       </c>
       <c r="F151" t="n">
-        <v>535.5</v>
+        <v>523.8</v>
       </c>
       <c r="G151" t="n">
         <v>540.89</v>
       </c>
       <c r="H151" t="n">
-        <v>-5.39</v>
+        <v>-17.09</v>
       </c>
       <c r="I151" t="n">
-        <v>513.7</v>
+        <v>510.4</v>
       </c>
       <c r="J151" t="n">
         <v>517.74</v>
       </c>
       <c r="K151" t="n">
-        <v>-4.04</v>
+        <v>-7.34</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1.34</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="152">
@@ -8320,31 +8320,31 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>14035</v>
+        <v>13800</v>
       </c>
       <c r="D152" t="n">
         <v>14129.03</v>
       </c>
       <c r="E152" t="n">
-        <v>-94.03</v>
+        <v>-329.03</v>
       </c>
       <c r="F152" t="n">
-        <v>14065</v>
+        <v>14090</v>
       </c>
       <c r="G152" t="n">
         <v>14129.03</v>
       </c>
       <c r="H152" t="n">
-        <v>-64.03</v>
+        <v>-39.03</v>
       </c>
       <c r="I152" t="n">
-        <v>13645</v>
+        <v>13670</v>
       </c>
       <c r="J152" t="n">
         <v>13608.7</v>
       </c>
       <c r="K152" t="n">
-        <v>36.3</v>
+        <v>61.3</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="153">
@@ -8372,31 +8372,31 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="D153" t="n">
         <v>186.89</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.39</v>
+        <v>0.11</v>
       </c>
       <c r="F153" t="n">
-        <v>188.7</v>
+        <v>187.6</v>
       </c>
       <c r="G153" t="n">
         <v>188.82</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.12</v>
+        <v>-1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>185.32</v>
+        <v>181.82</v>
       </c>
       <c r="J153" t="n">
         <v>185.29</v>
       </c>
       <c r="K153" t="n">
-        <v>0.03</v>
+        <v>-3.47</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="154">
@@ -8424,31 +8424,31 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>176.23</v>
+        <v>176.7</v>
       </c>
       <c r="D154" t="n">
         <v>176.08</v>
       </c>
       <c r="E154" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="F154" t="n">
-        <v>182.7</v>
+        <v>177.38</v>
       </c>
       <c r="G154" t="n">
         <v>176.89</v>
       </c>
       <c r="H154" t="n">
-        <v>5.81</v>
+        <v>0.49</v>
       </c>
       <c r="I154" t="n">
-        <v>176.23</v>
+        <v>174.43</v>
       </c>
       <c r="J154" t="n">
         <v>173.52</v>
       </c>
       <c r="K154" t="n">
-        <v>2.71</v>
+        <v>0.91</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="155">
@@ -8476,31 +8476,31 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1357.3</v>
+        <v>1339</v>
       </c>
       <c r="D155" t="n">
         <v>1350.91</v>
       </c>
       <c r="E155" t="n">
-        <v>6.39</v>
+        <v>-11.91</v>
       </c>
       <c r="F155" t="n">
-        <v>1369.4</v>
+        <v>1364</v>
       </c>
       <c r="G155" t="n">
         <v>1350.91</v>
       </c>
       <c r="H155" t="n">
-        <v>18.49</v>
+        <v>13.09</v>
       </c>
       <c r="I155" t="n">
-        <v>1336.5</v>
+        <v>1329.6</v>
       </c>
       <c r="J155" t="n">
         <v>1305.64</v>
       </c>
       <c r="K155" t="n">
-        <v>30.86</v>
+        <v>23.96</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="156">
@@ -8528,31 +8528,31 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2025</v>
+        <v>2020.5</v>
       </c>
       <c r="D156" t="n">
         <v>1985.19</v>
       </c>
       <c r="E156" t="n">
-        <v>39.81</v>
+        <v>35.31</v>
       </c>
       <c r="F156" t="n">
-        <v>2038</v>
+        <v>2028.4</v>
       </c>
       <c r="G156" t="n">
         <v>1985.19</v>
       </c>
       <c r="H156" t="n">
-        <v>52.81</v>
+        <v>43.21</v>
       </c>
       <c r="I156" t="n">
-        <v>2006.7</v>
+        <v>2006.1</v>
       </c>
       <c r="J156" t="n">
         <v>1968.88</v>
       </c>
       <c r="K156" t="n">
-        <v>37.82</v>
+        <v>37.22</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="157">
@@ -8589,22 +8589,22 @@
         <v>70.95999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>7772</v>
+        <v>7741</v>
       </c>
       <c r="G157" t="n">
         <v>7823.79</v>
       </c>
       <c r="H157" t="n">
-        <v>-51.79</v>
+        <v>-82.79000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>7659</v>
+        <v>7585.5</v>
       </c>
       <c r="J157" t="n">
         <v>7678.06</v>
       </c>
       <c r="K157" t="n">
-        <v>-19.06</v>
+        <v>-92.56</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8632,31 +8632,31 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>11706</v>
+        <v>11891</v>
       </c>
       <c r="D158" t="n">
         <v>11538.88</v>
       </c>
       <c r="E158" t="n">
-        <v>167.12</v>
+        <v>352.12</v>
       </c>
       <c r="F158" t="n">
-        <v>11905</v>
+        <v>11891</v>
       </c>
       <c r="G158" t="n">
         <v>11538.88</v>
       </c>
       <c r="H158" t="n">
-        <v>366.12</v>
+        <v>352.12</v>
       </c>
       <c r="I158" t="n">
-        <v>11570</v>
+        <v>11650</v>
       </c>
       <c r="J158" t="n">
         <v>11473.64</v>
       </c>
       <c r="K158" t="n">
-        <v>96.36</v>
+        <v>176.36</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8665,11 +8665,11 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="159">
@@ -8684,31 +8684,31 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2237.1</v>
+        <v>2240</v>
       </c>
       <c r="D159" t="n">
         <v>2218.67</v>
       </c>
       <c r="E159" t="n">
-        <v>18.43</v>
+        <v>21.33</v>
       </c>
       <c r="F159" t="n">
-        <v>2273.9</v>
+        <v>2245</v>
       </c>
       <c r="G159" t="n">
         <v>2218.67</v>
       </c>
       <c r="H159" t="n">
-        <v>55.23</v>
+        <v>26.33</v>
       </c>
       <c r="I159" t="n">
-        <v>2219.5</v>
+        <v>2192.7</v>
       </c>
       <c r="J159" t="n">
         <v>2173.44</v>
       </c>
       <c r="K159" t="n">
-        <v>46.06</v>
+        <v>19.26</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="160">
@@ -8736,31 +8736,31 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1939.1</v>
+        <v>1945</v>
       </c>
       <c r="D160" t="n">
         <v>1928.09</v>
       </c>
       <c r="E160" t="n">
-        <v>11.01</v>
+        <v>16.91</v>
       </c>
       <c r="F160" t="n">
-        <v>1970</v>
+        <v>1945</v>
       </c>
       <c r="G160" t="n">
         <v>1957.36</v>
       </c>
       <c r="H160" t="n">
-        <v>12.64</v>
+        <v>-12.36</v>
       </c>
       <c r="I160" t="n">
-        <v>1930.5</v>
+        <v>1901.3</v>
       </c>
       <c r="J160" t="n">
         <v>1920.55</v>
       </c>
       <c r="K160" t="n">
-        <v>9.949999999999999</v>
+        <v>-19.25</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="161">
@@ -8788,31 +8788,31 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1046.25</v>
+        <v>1078.5</v>
       </c>
       <c r="D161" t="n">
         <v>1035</v>
       </c>
       <c r="E161" t="n">
-        <v>11.25</v>
+        <v>43.5</v>
       </c>
       <c r="F161" t="n">
-        <v>1073</v>
+        <v>1087.95</v>
       </c>
       <c r="G161" t="n">
         <v>1052.94</v>
       </c>
       <c r="H161" t="n">
-        <v>20.06</v>
+        <v>35.01</v>
       </c>
       <c r="I161" t="n">
-        <v>1040</v>
+        <v>1056.9</v>
       </c>
       <c r="J161" t="n">
         <v>1033.02</v>
       </c>
       <c r="K161" t="n">
-        <v>6.98</v>
+        <v>23.88</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8821,11 +8821,11 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="162">
@@ -8840,31 +8840,31 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>117.59</v>
+        <v>118.98</v>
       </c>
       <c r="D162" t="n">
         <v>115.42</v>
       </c>
       <c r="E162" t="n">
-        <v>2.17</v>
+        <v>3.56</v>
       </c>
       <c r="F162" t="n">
-        <v>119.35</v>
+        <v>119.5</v>
       </c>
       <c r="G162" t="n">
         <v>116.28</v>
       </c>
       <c r="H162" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="I162" t="n">
-        <v>117.31</v>
+        <v>113.72</v>
       </c>
       <c r="J162" t="n">
         <v>115.38</v>
       </c>
       <c r="K162" t="n">
-        <v>1.93</v>
+        <v>-1.66</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8873,11 +8873,11 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1.88</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="163">
@@ -8892,31 +8892,31 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>279.3</v>
+        <v>279.85</v>
       </c>
       <c r="D163" t="n">
         <v>279.16</v>
       </c>
       <c r="E163" t="n">
-        <v>0.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F163" t="n">
-        <v>287.4</v>
+        <v>281.9</v>
       </c>
       <c r="G163" t="n">
         <v>279.16</v>
       </c>
       <c r="H163" t="n">
-        <v>8.24</v>
+        <v>2.74</v>
       </c>
       <c r="I163" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J163" t="n">
         <v>272.79</v>
       </c>
       <c r="K163" t="n">
-        <v>0.21</v>
+        <v>4.21</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="164">
@@ -8944,31 +8944,31 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1183</v>
+        <v>1161</v>
       </c>
       <c r="D164" t="n">
         <v>1158.28</v>
       </c>
       <c r="E164" t="n">
-        <v>24.72</v>
+        <v>2.72</v>
       </c>
       <c r="F164" t="n">
-        <v>1184.9</v>
+        <v>1167.5</v>
       </c>
       <c r="G164" t="n">
         <v>1176.27</v>
       </c>
       <c r="H164" t="n">
-        <v>8.630000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="I164" t="n">
-        <v>1149.2</v>
+        <v>1140</v>
       </c>
       <c r="J164" t="n">
         <v>1153.53</v>
       </c>
       <c r="K164" t="n">
-        <v>-4.33</v>
+        <v>-13.53</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2.13</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="165">
@@ -8996,31 +8996,31 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>400.5</v>
+        <v>420</v>
       </c>
       <c r="D165" t="n">
         <v>396.19</v>
       </c>
       <c r="E165" t="n">
-        <v>4.31</v>
+        <v>23.81</v>
       </c>
       <c r="F165" t="n">
-        <v>413.65</v>
+        <v>422.2</v>
       </c>
       <c r="G165" t="n">
         <v>396.19</v>
       </c>
       <c r="H165" t="n">
-        <v>17.46</v>
+        <v>26.01</v>
       </c>
       <c r="I165" t="n">
-        <v>400</v>
+        <v>398.5</v>
       </c>
       <c r="J165" t="n">
         <v>387.32</v>
       </c>
       <c r="K165" t="n">
-        <v>12.68</v>
+        <v>11.18</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9029,11 +9029,11 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1.09</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="166">
@@ -9048,31 +9048,31 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1458.8</v>
+        <v>1463</v>
       </c>
       <c r="D166" t="n">
         <v>1451.27</v>
       </c>
       <c r="E166" t="n">
-        <v>7.53</v>
+        <v>11.73</v>
       </c>
       <c r="F166" t="n">
-        <v>1464.4</v>
+        <v>1468.8</v>
       </c>
       <c r="G166" t="n">
         <v>1476.44</v>
       </c>
       <c r="H166" t="n">
-        <v>-12.04</v>
+        <v>-7.64</v>
       </c>
       <c r="I166" t="n">
-        <v>1456.2</v>
+        <v>1456.1</v>
       </c>
       <c r="J166" t="n">
         <v>1452.16</v>
       </c>
       <c r="K166" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9109,22 +9109,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="F167" t="n">
-        <v>903.8</v>
+        <v>897.65</v>
       </c>
       <c r="G167" t="n">
         <v>906.5599999999999</v>
       </c>
       <c r="H167" t="n">
-        <v>-2.76</v>
+        <v>-8.91</v>
       </c>
       <c r="I167" t="n">
-        <v>883.15</v>
+        <v>873.1</v>
       </c>
       <c r="J167" t="n">
         <v>889.5599999999999</v>
       </c>
       <c r="K167" t="n">
-        <v>-6.41</v>
+        <v>-16.46</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9740,31 +9740,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1183</v>
+        <v>1161</v>
       </c>
       <c r="D8" t="n">
         <v>1158.28</v>
       </c>
       <c r="E8" t="n">
-        <v>24.72</v>
+        <v>2.72</v>
       </c>
       <c r="F8" t="n">
-        <v>1184.9</v>
+        <v>1167.5</v>
       </c>
       <c r="G8" t="n">
         <v>1176.27</v>
       </c>
       <c r="H8" t="n">
-        <v>8.630000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="I8" t="n">
-        <v>1149.2</v>
+        <v>1140</v>
       </c>
       <c r="J8" t="n">
         <v>1153.53</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.33</v>
+        <v>-13.53</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -10190,31 +10190,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>615</v>
+        <v>614.65</v>
       </c>
       <c r="D8" t="n">
         <v>637.74</v>
       </c>
       <c r="E8" t="n">
-        <v>-22.74</v>
+        <v>-23.09</v>
       </c>
       <c r="F8" t="n">
-        <v>615.3</v>
+        <v>620.8</v>
       </c>
       <c r="G8" t="n">
         <v>637.74</v>
       </c>
       <c r="H8" t="n">
-        <v>-22.44</v>
+        <v>-16.94</v>
       </c>
       <c r="I8" t="n">
-        <v>603</v>
+        <v>604.25</v>
       </c>
       <c r="J8" t="n">
         <v>599.63</v>
       </c>
       <c r="K8" t="n">
-        <v>3.37</v>
+        <v>4.62</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
     </row>
   </sheetData>
@@ -10640,31 +10640,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="D8" t="n">
         <v>8102.18</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="F8" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="G8" t="n">
         <v>8102.18</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="I8" t="n">
-        <v>8011</v>
+        <v>7940</v>
       </c>
       <c r="J8" t="n">
         <v>7927.17</v>
       </c>
       <c r="K8" t="n">
-        <v>83.83</v>
+        <v>12.83</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -11384,31 +11384,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="D8" t="n">
         <v>1651.35</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.35</v>
+        <v>-26.35</v>
       </c>
       <c r="F8" t="n">
-        <v>1652.8</v>
+        <v>1657</v>
       </c>
       <c r="G8" t="n">
         <v>1661.69</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.890000000000001</v>
+        <v>-4.69</v>
       </c>
       <c r="I8" t="n">
-        <v>1626.3</v>
+        <v>1622.1</v>
       </c>
       <c r="J8" t="n">
         <v>1630.69</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.39</v>
+        <v>-8.59</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -11834,31 +11834,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>318</v>
+        <v>314.05</v>
       </c>
       <c r="D8" t="n">
         <v>334.96</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.96</v>
+        <v>-20.91</v>
       </c>
       <c r="F8" t="n">
-        <v>319.35</v>
+        <v>318.95</v>
       </c>
       <c r="G8" t="n">
         <v>334.96</v>
       </c>
       <c r="H8" t="n">
-        <v>-15.61</v>
+        <v>-16.01</v>
       </c>
       <c r="I8" t="n">
-        <v>313.3</v>
+        <v>312.6</v>
       </c>
       <c r="J8" t="n">
         <v>313.13</v>
       </c>
       <c r="K8" t="n">
-        <v>0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.06</v>
+        <v>6.24</v>
       </c>
     </row>
   </sheetData>
@@ -12284,31 +12284,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14035</v>
+        <v>13800</v>
       </c>
       <c r="D8" t="n">
         <v>14129.03</v>
       </c>
       <c r="E8" t="n">
-        <v>-94.03</v>
+        <v>-329.03</v>
       </c>
       <c r="F8" t="n">
-        <v>14065</v>
+        <v>14090</v>
       </c>
       <c r="G8" t="n">
         <v>14129.03</v>
       </c>
       <c r="H8" t="n">
-        <v>-64.03</v>
+        <v>-39.03</v>
       </c>
       <c r="I8" t="n">
-        <v>13645</v>
+        <v>13670</v>
       </c>
       <c r="J8" t="n">
         <v>13608.7</v>
       </c>
       <c r="K8" t="n">
-        <v>36.3</v>
+        <v>61.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -12734,31 +12734,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1829</v>
+        <v>1801.5</v>
       </c>
       <c r="D8" t="n">
         <v>1795.92</v>
       </c>
       <c r="E8" t="n">
-        <v>33.08</v>
+        <v>5.58</v>
       </c>
       <c r="F8" t="n">
-        <v>1829.9</v>
+        <v>1819.1</v>
       </c>
       <c r="G8" t="n">
         <v>1795.92</v>
       </c>
       <c r="H8" t="n">
-        <v>33.98</v>
+        <v>23.18</v>
       </c>
       <c r="I8" t="n">
-        <v>1788</v>
+        <v>1780.4</v>
       </c>
       <c r="J8" t="n">
         <v>1760.38</v>
       </c>
       <c r="K8" t="n">
-        <v>27.62</v>
+        <v>20.02</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -13132,31 +13132,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5523</v>
+        <v>5474</v>
       </c>
       <c r="D7" t="n">
         <v>5678.86</v>
       </c>
       <c r="E7" t="n">
-        <v>-155.86</v>
+        <v>-204.86</v>
       </c>
       <c r="F7" t="n">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G7" t="n">
         <v>5678.86</v>
       </c>
       <c r="H7" t="n">
-        <v>-149.86</v>
+        <v>-148.86</v>
       </c>
       <c r="I7" t="n">
-        <v>5406</v>
+        <v>5390</v>
       </c>
       <c r="J7" t="n">
         <v>5482.76</v>
       </c>
       <c r="K7" t="n">
-        <v>-76.76000000000001</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -13165,11 +13165,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>3.61</v>
       </c>
     </row>
   </sheetData>
@@ -13582,31 +13582,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>117.59</v>
+        <v>118.98</v>
       </c>
       <c r="D8" t="n">
         <v>115.42</v>
       </c>
       <c r="E8" t="n">
-        <v>2.17</v>
+        <v>3.56</v>
       </c>
       <c r="F8" t="n">
-        <v>119.35</v>
+        <v>119.5</v>
       </c>
       <c r="G8" t="n">
         <v>116.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="I8" t="n">
-        <v>117.31</v>
+        <v>113.72</v>
       </c>
       <c r="J8" t="n">
         <v>115.38</v>
       </c>
       <c r="K8" t="n">
-        <v>1.93</v>
+        <v>-1.66</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -13615,11 +13615,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>
@@ -13980,31 +13980,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3428.2</v>
+        <v>3403.6</v>
       </c>
       <c r="D7" t="n">
         <v>3533.38</v>
       </c>
       <c r="E7" t="n">
-        <v>-105.18</v>
+        <v>-129.78</v>
       </c>
       <c r="F7" t="n">
-        <v>3440</v>
+        <v>3471.8</v>
       </c>
       <c r="G7" t="n">
         <v>3533.38</v>
       </c>
       <c r="H7" t="n">
-        <v>-93.38</v>
+        <v>-61.58</v>
       </c>
       <c r="I7" t="n">
-        <v>3396.5</v>
+        <v>3403.6</v>
       </c>
       <c r="J7" t="n">
         <v>3329.44</v>
       </c>
       <c r="K7" t="n">
-        <v>67.06</v>
+        <v>74.16</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
     </row>
   </sheetData>
@@ -14378,31 +14378,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>533.65</v>
+        <v>512.05</v>
       </c>
       <c r="D7" t="n">
         <v>540.89</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.24</v>
+        <v>-28.84</v>
       </c>
       <c r="F7" t="n">
-        <v>535.5</v>
+        <v>523.8</v>
       </c>
       <c r="G7" t="n">
         <v>540.89</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.39</v>
+        <v>-17.09</v>
       </c>
       <c r="I7" t="n">
-        <v>513.7</v>
+        <v>510.4</v>
       </c>
       <c r="J7" t="n">
         <v>517.74</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.04</v>
+        <v>-7.34</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>5.33</v>
       </c>
     </row>
   </sheetData>
@@ -15260,31 +15260,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1458.8</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
         <v>1451.27</v>
       </c>
       <c r="E8" t="n">
-        <v>7.53</v>
+        <v>11.73</v>
       </c>
       <c r="F8" t="n">
-        <v>1464.4</v>
+        <v>1468.8</v>
       </c>
       <c r="G8" t="n">
         <v>1476.44</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.04</v>
+        <v>-7.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1456.2</v>
+        <v>1456.1</v>
       </c>
       <c r="J8" t="n">
         <v>1452.16</v>
       </c>
       <c r="K8" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15952,31 +15952,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11706</v>
+        <v>11891</v>
       </c>
       <c r="D8" t="n">
         <v>11538.88</v>
       </c>
       <c r="E8" t="n">
-        <v>167.12</v>
+        <v>352.12</v>
       </c>
       <c r="F8" t="n">
-        <v>11905</v>
+        <v>11891</v>
       </c>
       <c r="G8" t="n">
         <v>11538.88</v>
       </c>
       <c r="H8" t="n">
-        <v>366.12</v>
+        <v>352.12</v>
       </c>
       <c r="I8" t="n">
-        <v>11570</v>
+        <v>11650</v>
       </c>
       <c r="J8" t="n">
         <v>11473.64</v>
       </c>
       <c r="K8" t="n">
-        <v>96.36</v>
+        <v>176.36</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -15985,11 +15985,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>
@@ -16592,31 +16592,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2755.5</v>
+        <v>2740</v>
       </c>
       <c r="D8" t="n">
         <v>2670.88</v>
       </c>
       <c r="E8" t="n">
-        <v>84.62</v>
+        <v>69.12</v>
       </c>
       <c r="F8" t="n">
-        <v>2755.5</v>
+        <v>2748.4</v>
       </c>
       <c r="G8" t="n">
         <v>2779.43</v>
       </c>
       <c r="H8" t="n">
-        <v>-23.93</v>
+        <v>-31.03</v>
       </c>
       <c r="I8" t="n">
-        <v>2720</v>
+        <v>2698.2</v>
       </c>
       <c r="J8" t="n">
         <v>2727.08</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.08</v>
+        <v>-28.88</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9138,6 +9138,1566 @@
       </c>
       <c r="N167" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>118</v>
+      </c>
+      <c r="D168" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F168" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G168" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="H168" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="I168" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J168" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1086.93</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-19.23</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1089.74</v>
+      </c>
+      <c r="H169" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1065.1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1057.42</v>
+      </c>
+      <c r="K169" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D170" t="n">
+        <v>11780.86</v>
+      </c>
+      <c r="E170" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="F170" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G170" t="n">
+        <v>12109.86</v>
+      </c>
+      <c r="H170" t="n">
+        <v>-259.86</v>
+      </c>
+      <c r="I170" t="n">
+        <v>11318</v>
+      </c>
+      <c r="J170" t="n">
+        <v>11751.99</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-433.99</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>11475</v>
+      </c>
+      <c r="D171" t="n">
+        <v>11562.29</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-87.29000000000001</v>
+      </c>
+      <c r="F171" t="n">
+        <v>11541</v>
+      </c>
+      <c r="G171" t="n">
+        <v>11562.29</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-21.29</v>
+      </c>
+      <c r="I171" t="n">
+        <v>11387</v>
+      </c>
+      <c r="J171" t="n">
+        <v>11214.54</v>
+      </c>
+      <c r="K171" t="n">
+        <v>172.46</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1246.9</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1268.15</v>
+      </c>
+      <c r="H172" t="n">
+        <v>-21.25</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1230.1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1230.63</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>187.38</v>
+      </c>
+      <c r="D173" t="n">
+        <v>189.94</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F173" t="n">
+        <v>189.34</v>
+      </c>
+      <c r="G173" t="n">
+        <v>192.97</v>
+      </c>
+      <c r="H173" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="I173" t="n">
+        <v>186.39</v>
+      </c>
+      <c r="J173" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1992.1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2038.57</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-46.47</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2039.97</v>
+      </c>
+      <c r="H174" t="n">
+        <v>-34.17</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1932</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1992.1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-60.1</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>8077.69</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="F175" t="n">
+        <v>8143</v>
+      </c>
+      <c r="G175" t="n">
+        <v>8093.76</v>
+      </c>
+      <c r="H175" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J175" t="n">
+        <v>7900.17</v>
+      </c>
+      <c r="K175" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>5580</v>
+      </c>
+      <c r="D176" t="n">
+        <v>5421.76</v>
+      </c>
+      <c r="E176" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5618.5</v>
+      </c>
+      <c r="G176" t="n">
+        <v>5718.11</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-99.61</v>
+      </c>
+      <c r="I176" t="n">
+        <v>5447</v>
+      </c>
+      <c r="J176" t="n">
+        <v>5549.31</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-102.31</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1632.8</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1619.59</v>
+      </c>
+      <c r="E177" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1667.09</v>
+      </c>
+      <c r="H177" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1614.4</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5985.55</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-195.55</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5849</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5985.55</v>
+      </c>
+      <c r="H178" t="n">
+        <v>-136.55</v>
+      </c>
+      <c r="I178" t="n">
+        <v>5765</v>
+      </c>
+      <c r="J178" t="n">
+        <v>5694.13</v>
+      </c>
+      <c r="K178" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>3428.3</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3328.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3417.82</v>
+      </c>
+      <c r="H179" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I179" t="n">
+        <v>3378.3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3334.66</v>
+      </c>
+      <c r="K179" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D180" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E180" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="F180" t="n">
+        <v>325</v>
+      </c>
+      <c r="G180" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I180" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D181" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="E181" t="n">
+        <v>218.68</v>
+      </c>
+      <c r="F181" t="n">
+        <v>14209</v>
+      </c>
+      <c r="G181" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="H181" t="n">
+        <v>297.68</v>
+      </c>
+      <c r="I181" t="n">
+        <v>13999</v>
+      </c>
+      <c r="J181" t="n">
+        <v>13697.56</v>
+      </c>
+      <c r="K181" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>601</v>
+      </c>
+      <c r="D182" t="n">
+        <v>583.87</v>
+      </c>
+      <c r="E182" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="F182" t="n">
+        <v>615.9</v>
+      </c>
+      <c r="G182" t="n">
+        <v>606.37</v>
+      </c>
+      <c r="H182" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I182" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="J182" t="n">
+        <v>588.14</v>
+      </c>
+      <c r="K182" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D183" t="n">
+        <v>5404.88</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-94.88</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G183" t="n">
+        <v>5404.88</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-34.88</v>
+      </c>
+      <c r="I183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="J183" t="n">
+        <v>5220.06</v>
+      </c>
+      <c r="K183" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>171.64</v>
+      </c>
+      <c r="D184" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="F184" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G184" t="n">
+        <v>174.94</v>
+      </c>
+      <c r="H184" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I184" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="J184" t="n">
+        <v>169.74</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D185" t="n">
+        <v>7781.82</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-132.82</v>
+      </c>
+      <c r="F185" t="n">
+        <v>7825</v>
+      </c>
+      <c r="G185" t="n">
+        <v>7793.45</v>
+      </c>
+      <c r="H185" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="I185" t="n">
+        <v>7639</v>
+      </c>
+      <c r="J185" t="n">
+        <v>7561.84</v>
+      </c>
+      <c r="K185" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2237.89</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2255</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2237.89</v>
+      </c>
+      <c r="H186" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2191.6</v>
+      </c>
+      <c r="J186" t="n">
+        <v>2135.13</v>
+      </c>
+      <c r="K186" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="H187" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1804.2</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1760.46</v>
+      </c>
+      <c r="K187" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1341.8</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1367.1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1365.14</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1337</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1324.46</v>
+      </c>
+      <c r="K188" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D189" t="n">
+        <v>4054.81</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4072.5</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4138.36</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-65.86</v>
+      </c>
+      <c r="I189" t="n">
+        <v>4033.1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>4038.69</v>
+      </c>
+      <c r="K189" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="D190" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="F190" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="G190" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="H190" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="I190" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="J190" t="n">
+        <v>277.17</v>
+      </c>
+      <c r="K190" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1473.41</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-23.41</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1474.3</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1481.82</v>
+      </c>
+      <c r="H191" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1449.2</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1437.94</v>
+      </c>
+      <c r="K191" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>376</v>
+      </c>
+      <c r="D192" t="n">
+        <v>401.79</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-25.79</v>
+      </c>
+      <c r="F192" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="G192" t="n">
+        <v>401.79</v>
+      </c>
+      <c r="H192" t="n">
+        <v>-16.84</v>
+      </c>
+      <c r="I192" t="n">
+        <v>375</v>
+      </c>
+      <c r="J192" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="K192" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2008.3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2060.38</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-52.08</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2033.6</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2060.38</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-26.78</v>
+      </c>
+      <c r="I193" t="n">
+        <v>2006.6</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1952.58</v>
+      </c>
+      <c r="K193" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1029.5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1081.36</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-51.86</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1036.8</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1081.36</v>
+      </c>
+      <c r="H194" t="n">
+        <v>-44.56</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1021.35</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1000.9</v>
+      </c>
+      <c r="K194" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1191.5</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="H195" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1167</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1142.98</v>
+      </c>
+      <c r="K195" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>527</v>
+      </c>
+      <c r="D196" t="n">
+        <v>502.9</v>
+      </c>
+      <c r="E196" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>543.7</v>
+      </c>
+      <c r="G196" t="n">
+        <v>521.27</v>
+      </c>
+      <c r="H196" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="I196" t="n">
+        <v>527</v>
+      </c>
+      <c r="J196" t="n">
+        <v>510.37</v>
+      </c>
+      <c r="K196" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>894.95</v>
+      </c>
+      <c r="D197" t="n">
+        <v>911.91</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="F197" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="G197" t="n">
+        <v>911.91</v>
+      </c>
+      <c r="H197" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="I197" t="n">
+        <v>885.3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>884.1799999999999</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>
@@ -9341,7 +10901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9778,6 +11338,58 @@
       </c>
       <c r="N8" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1191.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1167</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1142.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -9791,7 +11403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10228,6 +11840,58 @@
       </c>
       <c r="N8" t="n">
         <v>3.62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>601</v>
+      </c>
+      <c r="D9" t="n">
+        <v>583.87</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>615.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>606.37</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>588.14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2.93</v>
       </c>
     </row>
   </sheetData>
@@ -10241,7 +11905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10678,6 +12342,58 @@
       </c>
       <c r="N8" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8077.69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8093.76</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7900.17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -10985,7 +12701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11422,6 +13138,58 @@
       </c>
       <c r="N8" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1632.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1619.59</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1667.09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1614.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -11435,7 +13203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11872,6 +13640,58 @@
       </c>
       <c r="N8" t="n">
         <v>6.24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="F9" t="n">
+        <v>325</v>
+      </c>
+      <c r="G9" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5.81</v>
       </c>
     </row>
   </sheetData>
@@ -11885,7 +13705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12322,6 +14142,58 @@
       </c>
       <c r="N8" t="n">
         <v>2.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>218.68</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14209</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>297.68</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13697.56</v>
+      </c>
+      <c r="K9" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>
@@ -12335,7 +14207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12772,6 +14644,58 @@
       </c>
       <c r="N8" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1804.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1760.46</v>
+      </c>
+      <c r="K9" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -12785,7 +14709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13170,6 +15094,58 @@
       </c>
       <c r="N7" t="n">
         <v>3.61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5421.76</v>
+      </c>
+      <c r="E8" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5618.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5718.11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-99.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5549.31</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-102.31</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.92</v>
       </c>
     </row>
   </sheetData>
@@ -13183,7 +15159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13620,6 +15596,58 @@
       </c>
       <c r="N8" t="n">
         <v>3.08</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>118</v>
+      </c>
+      <c r="D9" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F9" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3.76</v>
       </c>
     </row>
   </sheetData>
@@ -13633,7 +15661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14018,6 +16046,58 @@
       </c>
       <c r="N7" t="n">
         <v>3.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3428.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3328.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3417.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3378.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3334.66</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.99</v>
       </c>
     </row>
   </sheetData>
@@ -14031,7 +16111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14416,6 +16496,58 @@
       </c>
       <c r="N7" t="n">
         <v>5.33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>527</v>
+      </c>
+      <c r="D8" t="n">
+        <v>502.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>543.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>521.27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="I8" t="n">
+        <v>527</v>
+      </c>
+      <c r="J8" t="n">
+        <v>510.37</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>4.79</v>
       </c>
     </row>
   </sheetData>
@@ -14861,7 +16993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15298,6 +17430,58 @@
       </c>
       <c r="N8" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1473.41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-23.41</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1474.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1481.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1449.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1437.94</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -9152,31 +9152,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>118</v>
+        <v>117.59</v>
       </c>
       <c r="D168" t="n">
         <v>122.61</v>
       </c>
       <c r="E168" t="n">
-        <v>-4.61</v>
+        <v>-5.02</v>
       </c>
       <c r="F168" t="n">
-        <v>118.9</v>
+        <v>119.35</v>
       </c>
       <c r="G168" t="n">
         <v>122.61</v>
       </c>
       <c r="H168" t="n">
-        <v>-3.71</v>
+        <v>-3.26</v>
       </c>
       <c r="I168" t="n">
-        <v>117.4</v>
+        <v>117.31</v>
       </c>
       <c r="J168" t="n">
         <v>115.8</v>
       </c>
       <c r="K168" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="169">
@@ -9204,31 +9204,31 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1067.7</v>
+        <v>1083</v>
       </c>
       <c r="D169" t="n">
         <v>1086.93</v>
       </c>
       <c r="E169" t="n">
-        <v>-19.23</v>
+        <v>-3.93</v>
       </c>
       <c r="F169" t="n">
-        <v>1082</v>
+        <v>1086.8</v>
       </c>
       <c r="G169" t="n">
         <v>1089.74</v>
       </c>
       <c r="H169" t="n">
-        <v>-7.74</v>
+        <v>-2.94</v>
       </c>
       <c r="I169" t="n">
-        <v>1065.1</v>
+        <v>1073</v>
       </c>
       <c r="J169" t="n">
         <v>1057.42</v>
       </c>
       <c r="K169" t="n">
-        <v>7.68</v>
+        <v>15.58</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>1.77</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="170">
@@ -9256,31 +9256,31 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11828</v>
+        <v>11420</v>
       </c>
       <c r="D170" t="n">
         <v>11780.86</v>
       </c>
       <c r="E170" t="n">
-        <v>47.14</v>
+        <v>-360.86</v>
       </c>
       <c r="F170" t="n">
-        <v>11850</v>
+        <v>11686</v>
       </c>
       <c r="G170" t="n">
         <v>12109.86</v>
       </c>
       <c r="H170" t="n">
-        <v>-259.86</v>
+        <v>-423.86</v>
       </c>
       <c r="I170" t="n">
-        <v>11318</v>
+        <v>11350</v>
       </c>
       <c r="J170" t="n">
         <v>11751.99</v>
       </c>
       <c r="K170" t="n">
-        <v>-433.99</v>
+        <v>-401.99</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9289,11 +9289,11 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0.4</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="171">
@@ -9308,31 +9308,31 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11475</v>
+        <v>11500</v>
       </c>
       <c r="D171" t="n">
         <v>11562.29</v>
       </c>
       <c r="E171" t="n">
-        <v>-87.29000000000001</v>
+        <v>-62.29</v>
       </c>
       <c r="F171" t="n">
-        <v>11541</v>
+        <v>11570</v>
       </c>
       <c r="G171" t="n">
         <v>11562.29</v>
       </c>
       <c r="H171" t="n">
-        <v>-21.29</v>
+        <v>7.71</v>
       </c>
       <c r="I171" t="n">
-        <v>11387</v>
+        <v>11410</v>
       </c>
       <c r="J171" t="n">
         <v>11214.54</v>
       </c>
       <c r="K171" t="n">
-        <v>172.46</v>
+        <v>195.46</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0.75</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="172">
@@ -9369,22 +9369,22 @@
         <v>10.5</v>
       </c>
       <c r="F172" t="n">
-        <v>1246.9</v>
+        <v>1264.7</v>
       </c>
       <c r="G172" t="n">
         <v>1268.15</v>
       </c>
       <c r="H172" t="n">
-        <v>-21.25</v>
+        <v>-3.45</v>
       </c>
       <c r="I172" t="n">
-        <v>1230.1</v>
+        <v>1237</v>
       </c>
       <c r="J172" t="n">
         <v>1230.63</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.53</v>
+        <v>6.37</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9412,31 +9412,31 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D173" t="n">
         <v>189.94</v>
       </c>
       <c r="E173" t="n">
-        <v>-2.56</v>
+        <v>-3.44</v>
       </c>
       <c r="F173" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G173" t="n">
         <v>192.97</v>
       </c>
       <c r="H173" t="n">
-        <v>-3.63</v>
+        <v>-4.27</v>
       </c>
       <c r="I173" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J173" t="n">
         <v>187.3</v>
       </c>
       <c r="K173" t="n">
-        <v>-0.91</v>
+        <v>-1.98</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="174">
@@ -9464,31 +9464,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1992.1</v>
+        <v>1939.1</v>
       </c>
       <c r="D174" t="n">
         <v>2038.57</v>
       </c>
       <c r="E174" t="n">
-        <v>-46.47</v>
+        <v>-99.47</v>
       </c>
       <c r="F174" t="n">
-        <v>2005.8</v>
+        <v>1970</v>
       </c>
       <c r="G174" t="n">
         <v>2039.97</v>
       </c>
       <c r="H174" t="n">
-        <v>-34.17</v>
+        <v>-69.97</v>
       </c>
       <c r="I174" t="n">
-        <v>1932</v>
+        <v>1930.5</v>
       </c>
       <c r="J174" t="n">
         <v>1992.1</v>
       </c>
       <c r="K174" t="n">
-        <v>-60.1</v>
+        <v>-61.6</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2.28</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="175">
@@ -9516,31 +9516,31 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8066.5</v>
+        <v>8100</v>
       </c>
       <c r="D175" t="n">
         <v>8077.69</v>
       </c>
       <c r="E175" t="n">
-        <v>-11.19</v>
+        <v>22.31</v>
       </c>
       <c r="F175" t="n">
-        <v>8143</v>
+        <v>8100</v>
       </c>
       <c r="G175" t="n">
         <v>8093.76</v>
       </c>
       <c r="H175" t="n">
-        <v>49.24</v>
+        <v>6.24</v>
       </c>
       <c r="I175" t="n">
-        <v>8030</v>
+        <v>8011</v>
       </c>
       <c r="J175" t="n">
         <v>7900.17</v>
       </c>
       <c r="K175" t="n">
-        <v>129.83</v>
+        <v>110.83</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="176">
@@ -9568,31 +9568,31 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5580</v>
+        <v>5523</v>
       </c>
       <c r="D176" t="n">
         <v>5421.76</v>
       </c>
       <c r="E176" t="n">
-        <v>158.24</v>
+        <v>101.24</v>
       </c>
       <c r="F176" t="n">
-        <v>5618.5</v>
+        <v>5529</v>
       </c>
       <c r="G176" t="n">
         <v>5718.11</v>
       </c>
       <c r="H176" t="n">
-        <v>-99.61</v>
+        <v>-189.11</v>
       </c>
       <c r="I176" t="n">
-        <v>5447</v>
+        <v>5406</v>
       </c>
       <c r="J176" t="n">
         <v>5549.31</v>
       </c>
       <c r="K176" t="n">
-        <v>-102.31</v>
+        <v>-143.31</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9601,11 +9601,11 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="177">
@@ -9620,31 +9620,31 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1632.8</v>
+        <v>1639</v>
       </c>
       <c r="D177" t="n">
         <v>1619.59</v>
       </c>
       <c r="E177" t="n">
-        <v>13.21</v>
+        <v>19.41</v>
       </c>
       <c r="F177" t="n">
-        <v>1652</v>
+        <v>1652.8</v>
       </c>
       <c r="G177" t="n">
         <v>1667.09</v>
       </c>
       <c r="H177" t="n">
-        <v>-15.09</v>
+        <v>-14.29</v>
       </c>
       <c r="I177" t="n">
-        <v>1614.4</v>
+        <v>1626.3</v>
       </c>
       <c r="J177" t="n">
         <v>1617.66</v>
       </c>
       <c r="K177" t="n">
-        <v>-3.26</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="178">
@@ -9672,31 +9672,31 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D178" t="n">
         <v>5985.55</v>
       </c>
       <c r="E178" t="n">
-        <v>-195.55</v>
+        <v>-135.55</v>
       </c>
       <c r="F178" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G178" t="n">
         <v>5985.55</v>
       </c>
       <c r="H178" t="n">
-        <v>-136.55</v>
+        <v>-51.55</v>
       </c>
       <c r="I178" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J178" t="n">
         <v>5694.13</v>
       </c>
       <c r="K178" t="n">
-        <v>70.87</v>
+        <v>107.87</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="179">
@@ -9724,31 +9724,31 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3428.3</v>
+        <v>3428.2</v>
       </c>
       <c r="D179" t="n">
         <v>3328.8</v>
       </c>
       <c r="E179" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F179" t="n">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="G179" t="n">
         <v>3417.82</v>
       </c>
       <c r="H179" t="n">
-        <v>12.18</v>
+        <v>22.18</v>
       </c>
       <c r="I179" t="n">
-        <v>3378.3</v>
+        <v>3396.5</v>
       </c>
       <c r="J179" t="n">
         <v>3334.66</v>
       </c>
       <c r="K179" t="n">
-        <v>43.64</v>
+        <v>61.84</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9776,31 +9776,31 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>318.5</v>
+        <v>318</v>
       </c>
       <c r="D180" t="n">
         <v>301.01</v>
       </c>
       <c r="E180" t="n">
-        <v>17.49</v>
+        <v>16.99</v>
       </c>
       <c r="F180" t="n">
-        <v>325</v>
+        <v>319.35</v>
       </c>
       <c r="G180" t="n">
         <v>324.15</v>
       </c>
       <c r="H180" t="n">
-        <v>0.85</v>
+        <v>-4.8</v>
       </c>
       <c r="I180" t="n">
-        <v>316.8</v>
+        <v>313.3</v>
       </c>
       <c r="J180" t="n">
         <v>314.5</v>
       </c>
       <c r="K180" t="n">
-        <v>2.3</v>
+        <v>-1.2</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="181">
@@ -9828,31 +9828,31 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14130</v>
+        <v>14035</v>
       </c>
       <c r="D181" t="n">
         <v>13911.32</v>
       </c>
       <c r="E181" t="n">
-        <v>218.68</v>
+        <v>123.68</v>
       </c>
       <c r="F181" t="n">
-        <v>14209</v>
+        <v>14065</v>
       </c>
       <c r="G181" t="n">
         <v>13911.32</v>
       </c>
       <c r="H181" t="n">
-        <v>297.68</v>
+        <v>153.68</v>
       </c>
       <c r="I181" t="n">
-        <v>13999</v>
+        <v>13645</v>
       </c>
       <c r="J181" t="n">
         <v>13697.56</v>
       </c>
       <c r="K181" t="n">
-        <v>301.44</v>
+        <v>-52.56</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="182">
@@ -9880,31 +9880,31 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D182" t="n">
         <v>583.87</v>
       </c>
       <c r="E182" t="n">
-        <v>17.13</v>
+        <v>31.13</v>
       </c>
       <c r="F182" t="n">
-        <v>615.9</v>
+        <v>615.3</v>
       </c>
       <c r="G182" t="n">
         <v>606.37</v>
       </c>
       <c r="H182" t="n">
-        <v>9.529999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="I182" t="n">
-        <v>599.5</v>
+        <v>603</v>
       </c>
       <c r="J182" t="n">
         <v>588.14</v>
       </c>
       <c r="K182" t="n">
-        <v>11.36</v>
+        <v>14.86</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>2.93</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="183">
@@ -9932,13 +9932,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5310</v>
+        <v>5370</v>
       </c>
       <c r="D183" t="n">
         <v>5404.88</v>
       </c>
       <c r="E183" t="n">
-        <v>-94.88</v>
+        <v>-34.88</v>
       </c>
       <c r="F183" t="n">
         <v>5370</v>
@@ -9950,13 +9950,13 @@
         <v>-34.88</v>
       </c>
       <c r="I183" t="n">
-        <v>5310</v>
+        <v>5281.5</v>
       </c>
       <c r="J183" t="n">
         <v>5220.06</v>
       </c>
       <c r="K183" t="n">
-        <v>89.94</v>
+        <v>61.44</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1.76</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="184">
@@ -9984,31 +9984,31 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>171.64</v>
+        <v>176.23</v>
       </c>
       <c r="D184" t="n">
         <v>173.62</v>
       </c>
       <c r="E184" t="n">
-        <v>-1.98</v>
+        <v>2.61</v>
       </c>
       <c r="F184" t="n">
-        <v>179.5</v>
+        <v>182.7</v>
       </c>
       <c r="G184" t="n">
         <v>174.94</v>
       </c>
       <c r="H184" t="n">
-        <v>4.56</v>
+        <v>7.76</v>
       </c>
       <c r="I184" t="n">
-        <v>169.75</v>
+        <v>176.23</v>
       </c>
       <c r="J184" t="n">
         <v>169.74</v>
       </c>
       <c r="K184" t="n">
-        <v>0.01</v>
+        <v>6.49</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="185">
@@ -10036,31 +10036,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D185" t="n">
         <v>7781.82</v>
       </c>
       <c r="E185" t="n">
-        <v>-132.82</v>
+        <v>-71.81999999999999</v>
       </c>
       <c r="F185" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G185" t="n">
         <v>7793.45</v>
       </c>
       <c r="H185" t="n">
-        <v>31.55</v>
+        <v>-21.45</v>
       </c>
       <c r="I185" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J185" t="n">
         <v>7561.84</v>
       </c>
       <c r="K185" t="n">
-        <v>77.16</v>
+        <v>97.16</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="186">
@@ -10088,31 +10088,31 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2199</v>
+        <v>2237.1</v>
       </c>
       <c r="D186" t="n">
         <v>2237.89</v>
       </c>
       <c r="E186" t="n">
-        <v>-38.89</v>
+        <v>-0.79</v>
       </c>
       <c r="F186" t="n">
-        <v>2255</v>
+        <v>2273.9</v>
       </c>
       <c r="G186" t="n">
         <v>2237.89</v>
       </c>
       <c r="H186" t="n">
-        <v>17.11</v>
+        <v>36.01</v>
       </c>
       <c r="I186" t="n">
-        <v>2191.6</v>
+        <v>2219.5</v>
       </c>
       <c r="J186" t="n">
         <v>2135.13</v>
       </c>
       <c r="K186" t="n">
-        <v>56.47</v>
+        <v>84.37</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1.74</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="187">
@@ -10140,31 +10140,31 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D187" t="n">
         <v>1832.18</v>
       </c>
       <c r="E187" t="n">
-        <v>-20.18</v>
+        <v>-3.18</v>
       </c>
       <c r="F187" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G187" t="n">
         <v>1832.18</v>
       </c>
       <c r="H187" t="n">
-        <v>4.22</v>
+        <v>-2.28</v>
       </c>
       <c r="I187" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J187" t="n">
         <v>1760.46</v>
       </c>
       <c r="K187" t="n">
-        <v>43.74</v>
+        <v>27.54</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1.1</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="188">
@@ -10192,31 +10192,31 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1343</v>
+        <v>1357.3</v>
       </c>
       <c r="D188" t="n">
         <v>1341.8</v>
       </c>
       <c r="E188" t="n">
-        <v>1.2</v>
+        <v>15.5</v>
       </c>
       <c r="F188" t="n">
-        <v>1367.1</v>
+        <v>1369.4</v>
       </c>
       <c r="G188" t="n">
         <v>1365.14</v>
       </c>
       <c r="H188" t="n">
-        <v>1.96</v>
+        <v>4.26</v>
       </c>
       <c r="I188" t="n">
-        <v>1337</v>
+        <v>1336.5</v>
       </c>
       <c r="J188" t="n">
         <v>1324.46</v>
       </c>
       <c r="K188" t="n">
-        <v>12.54</v>
+        <v>12.04</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>0.09</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="189">
@@ -10244,31 +10244,31 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4057</v>
+        <v>4070.7</v>
       </c>
       <c r="D189" t="n">
         <v>4054.81</v>
       </c>
       <c r="E189" t="n">
-        <v>2.19</v>
+        <v>15.89</v>
       </c>
       <c r="F189" t="n">
-        <v>4072.5</v>
+        <v>4070.7</v>
       </c>
       <c r="G189" t="n">
         <v>4138.36</v>
       </c>
       <c r="H189" t="n">
-        <v>-65.86</v>
+        <v>-67.66</v>
       </c>
       <c r="I189" t="n">
-        <v>4033.1</v>
+        <v>3990</v>
       </c>
       <c r="J189" t="n">
         <v>4038.69</v>
       </c>
       <c r="K189" t="n">
-        <v>-5.59</v>
+        <v>-48.69</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="190">
@@ -10296,31 +10296,31 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>282.6</v>
+        <v>279.3</v>
       </c>
       <c r="D190" t="n">
         <v>285.56</v>
       </c>
       <c r="E190" t="n">
-        <v>-2.96</v>
+        <v>-6.26</v>
       </c>
       <c r="F190" t="n">
-        <v>283.5</v>
+        <v>287.4</v>
       </c>
       <c r="G190" t="n">
         <v>285.73</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.23</v>
+        <v>1.67</v>
       </c>
       <c r="I190" t="n">
-        <v>277.15</v>
+        <v>273</v>
       </c>
       <c r="J190" t="n">
         <v>277.17</v>
       </c>
       <c r="K190" t="n">
-        <v>-0.02</v>
+        <v>-4.17</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1.04</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="191">
@@ -10348,31 +10348,31 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1450</v>
+        <v>1458.8</v>
       </c>
       <c r="D191" t="n">
         <v>1473.41</v>
       </c>
       <c r="E191" t="n">
-        <v>-23.41</v>
+        <v>-14.61</v>
       </c>
       <c r="F191" t="n">
-        <v>1474.3</v>
+        <v>1464.4</v>
       </c>
       <c r="G191" t="n">
         <v>1481.82</v>
       </c>
       <c r="H191" t="n">
-        <v>-7.52</v>
+        <v>-17.42</v>
       </c>
       <c r="I191" t="n">
-        <v>1449.2</v>
+        <v>1456.2</v>
       </c>
       <c r="J191" t="n">
         <v>1437.94</v>
       </c>
       <c r="K191" t="n">
-        <v>11.26</v>
+        <v>18.26</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1.59</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="192">
@@ -10400,31 +10400,31 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D192" t="n">
         <v>401.79</v>
       </c>
       <c r="E192" t="n">
-        <v>-25.79</v>
+        <v>-1.29</v>
       </c>
       <c r="F192" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G192" t="n">
         <v>401.79</v>
       </c>
       <c r="H192" t="n">
-        <v>-16.84</v>
+        <v>11.86</v>
       </c>
       <c r="I192" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J192" t="n">
         <v>361.7</v>
       </c>
       <c r="K192" t="n">
-        <v>13.3</v>
+        <v>38.3</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>6.42</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="193">
@@ -10452,31 +10452,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2008.3</v>
+        <v>2025</v>
       </c>
       <c r="D193" t="n">
         <v>2060.38</v>
       </c>
       <c r="E193" t="n">
-        <v>-52.08</v>
+        <v>-35.38</v>
       </c>
       <c r="F193" t="n">
-        <v>2033.6</v>
+        <v>2038</v>
       </c>
       <c r="G193" t="n">
         <v>2060.38</v>
       </c>
       <c r="H193" t="n">
-        <v>-26.78</v>
+        <v>-22.38</v>
       </c>
       <c r="I193" t="n">
-        <v>2006.6</v>
+        <v>2006.7</v>
       </c>
       <c r="J193" t="n">
         <v>1952.58</v>
       </c>
       <c r="K193" t="n">
-        <v>54.02</v>
+        <v>54.12</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="194">
@@ -10504,31 +10504,31 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1029.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D194" t="n">
         <v>1081.36</v>
       </c>
       <c r="E194" t="n">
-        <v>-51.86</v>
+        <v>-35.11</v>
       </c>
       <c r="F194" t="n">
-        <v>1036.8</v>
+        <v>1073</v>
       </c>
       <c r="G194" t="n">
         <v>1081.36</v>
       </c>
       <c r="H194" t="n">
-        <v>-44.56</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>1021.35</v>
+        <v>1040</v>
       </c>
       <c r="J194" t="n">
         <v>1000.9</v>
       </c>
       <c r="K194" t="n">
-        <v>20.45</v>
+        <v>39.1</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="195">
@@ -10556,31 +10556,31 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D195" t="n">
         <v>1192.24</v>
       </c>
       <c r="E195" t="n">
-        <v>-12.24</v>
+        <v>-9.24</v>
       </c>
       <c r="F195" t="n">
-        <v>1191.5</v>
+        <v>1184.9</v>
       </c>
       <c r="G195" t="n">
         <v>1192.24</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.74</v>
+        <v>-7.34</v>
       </c>
       <c r="I195" t="n">
-        <v>1167</v>
+        <v>1149.2</v>
       </c>
       <c r="J195" t="n">
         <v>1142.98</v>
       </c>
       <c r="K195" t="n">
-        <v>24.02</v>
+        <v>6.22</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="196">
@@ -10608,31 +10608,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>527</v>
+        <v>533.65</v>
       </c>
       <c r="D196" t="n">
         <v>502.9</v>
       </c>
       <c r="E196" t="n">
-        <v>24.1</v>
+        <v>30.75</v>
       </c>
       <c r="F196" t="n">
-        <v>543.7</v>
+        <v>535.5</v>
       </c>
       <c r="G196" t="n">
         <v>521.27</v>
       </c>
       <c r="H196" t="n">
-        <v>22.43</v>
+        <v>14.23</v>
       </c>
       <c r="I196" t="n">
-        <v>527</v>
+        <v>513.7</v>
       </c>
       <c r="J196" t="n">
         <v>510.37</v>
       </c>
       <c r="K196" t="n">
-        <v>16.63</v>
+        <v>3.33</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>4.79</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="197">
@@ -10660,31 +10660,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>894.95</v>
+        <v>897</v>
       </c>
       <c r="D197" t="n">
         <v>911.91</v>
       </c>
       <c r="E197" t="n">
-        <v>-16.96</v>
+        <v>-14.91</v>
       </c>
       <c r="F197" t="n">
-        <v>902.8</v>
+        <v>903.8</v>
       </c>
       <c r="G197" t="n">
         <v>911.91</v>
       </c>
       <c r="H197" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>885.3</v>
+        <v>883.15</v>
       </c>
       <c r="J197" t="n">
         <v>884.1799999999999</v>
       </c>
       <c r="K197" t="n">
-        <v>1.12</v>
+        <v>-1.03</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -11352,31 +11352,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D9" t="n">
         <v>1192.24</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.24</v>
+        <v>-9.24</v>
       </c>
       <c r="F9" t="n">
-        <v>1191.5</v>
+        <v>1184.9</v>
       </c>
       <c r="G9" t="n">
         <v>1192.24</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.74</v>
+        <v>-7.34</v>
       </c>
       <c r="I9" t="n">
-        <v>1167</v>
+        <v>1149.2</v>
       </c>
       <c r="J9" t="n">
         <v>1142.98</v>
       </c>
       <c r="K9" t="n">
-        <v>24.02</v>
+        <v>6.22</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -11854,31 +11854,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
         <v>583.87</v>
       </c>
       <c r="E9" t="n">
-        <v>17.13</v>
+        <v>31.13</v>
       </c>
       <c r="F9" t="n">
-        <v>615.9</v>
+        <v>615.3</v>
       </c>
       <c r="G9" t="n">
         <v>606.37</v>
       </c>
       <c r="H9" t="n">
-        <v>9.529999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="I9" t="n">
-        <v>599.5</v>
+        <v>603</v>
       </c>
       <c r="J9" t="n">
         <v>588.14</v>
       </c>
       <c r="K9" t="n">
-        <v>11.36</v>
+        <v>14.86</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>5.33</v>
       </c>
     </row>
   </sheetData>
@@ -12356,31 +12356,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8066.5</v>
+        <v>8100</v>
       </c>
       <c r="D9" t="n">
         <v>8077.69</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.19</v>
+        <v>22.31</v>
       </c>
       <c r="F9" t="n">
-        <v>8143</v>
+        <v>8100</v>
       </c>
       <c r="G9" t="n">
         <v>8093.76</v>
       </c>
       <c r="H9" t="n">
-        <v>49.24</v>
+        <v>6.24</v>
       </c>
       <c r="I9" t="n">
-        <v>8030</v>
+        <v>8011</v>
       </c>
       <c r="J9" t="n">
         <v>7900.17</v>
       </c>
       <c r="K9" t="n">
-        <v>129.83</v>
+        <v>110.83</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -13152,31 +13152,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1632.8</v>
+        <v>1639</v>
       </c>
       <c r="D9" t="n">
         <v>1619.59</v>
       </c>
       <c r="E9" t="n">
-        <v>13.21</v>
+        <v>19.41</v>
       </c>
       <c r="F9" t="n">
-        <v>1652</v>
+        <v>1652.8</v>
       </c>
       <c r="G9" t="n">
         <v>1667.09</v>
       </c>
       <c r="H9" t="n">
-        <v>-15.09</v>
+        <v>-14.29</v>
       </c>
       <c r="I9" t="n">
-        <v>1614.4</v>
+        <v>1626.3</v>
       </c>
       <c r="J9" t="n">
         <v>1617.66</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.26</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -13654,31 +13654,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>318.5</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
         <v>301.01</v>
       </c>
       <c r="E9" t="n">
-        <v>17.49</v>
+        <v>16.99</v>
       </c>
       <c r="F9" t="n">
-        <v>325</v>
+        <v>319.35</v>
       </c>
       <c r="G9" t="n">
         <v>324.15</v>
       </c>
       <c r="H9" t="n">
-        <v>0.85</v>
+        <v>-4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>316.8</v>
+        <v>313.3</v>
       </c>
       <c r="J9" t="n">
         <v>314.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>-1.2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
     </row>
   </sheetData>
@@ -14156,31 +14156,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14130</v>
+        <v>14035</v>
       </c>
       <c r="D9" t="n">
         <v>13911.32</v>
       </c>
       <c r="E9" t="n">
-        <v>218.68</v>
+        <v>123.68</v>
       </c>
       <c r="F9" t="n">
-        <v>14209</v>
+        <v>14065</v>
       </c>
       <c r="G9" t="n">
         <v>13911.32</v>
       </c>
       <c r="H9" t="n">
-        <v>297.68</v>
+        <v>153.68</v>
       </c>
       <c r="I9" t="n">
-        <v>13999</v>
+        <v>13645</v>
       </c>
       <c r="J9" t="n">
         <v>13697.56</v>
       </c>
       <c r="K9" t="n">
-        <v>301.44</v>
+        <v>-52.56</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -14658,31 +14658,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D9" t="n">
         <v>1832.18</v>
       </c>
       <c r="E9" t="n">
-        <v>-20.18</v>
+        <v>-3.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G9" t="n">
         <v>1832.18</v>
       </c>
       <c r="H9" t="n">
-        <v>4.22</v>
+        <v>-2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J9" t="n">
         <v>1760.46</v>
       </c>
       <c r="K9" t="n">
-        <v>43.74</v>
+        <v>27.54</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -15108,31 +15108,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5580</v>
+        <v>5523</v>
       </c>
       <c r="D8" t="n">
         <v>5421.76</v>
       </c>
       <c r="E8" t="n">
-        <v>158.24</v>
+        <v>101.24</v>
       </c>
       <c r="F8" t="n">
-        <v>5618.5</v>
+        <v>5529</v>
       </c>
       <c r="G8" t="n">
         <v>5718.11</v>
       </c>
       <c r="H8" t="n">
-        <v>-99.61</v>
+        <v>-189.11</v>
       </c>
       <c r="I8" t="n">
-        <v>5447</v>
+        <v>5406</v>
       </c>
       <c r="J8" t="n">
         <v>5549.31</v>
       </c>
       <c r="K8" t="n">
-        <v>-102.31</v>
+        <v>-143.31</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -15141,11 +15141,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>
@@ -15610,31 +15610,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>117.59</v>
       </c>
       <c r="D9" t="n">
         <v>122.61</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.61</v>
+        <v>-5.02</v>
       </c>
       <c r="F9" t="n">
-        <v>118.9</v>
+        <v>119.35</v>
       </c>
       <c r="G9" t="n">
         <v>122.61</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.71</v>
+        <v>-3.26</v>
       </c>
       <c r="I9" t="n">
-        <v>117.4</v>
+        <v>117.31</v>
       </c>
       <c r="J9" t="n">
         <v>115.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
     </row>
   </sheetData>
@@ -16060,31 +16060,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3428.3</v>
+        <v>3428.2</v>
       </c>
       <c r="D8" t="n">
         <v>3328.8</v>
       </c>
       <c r="E8" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="G8" t="n">
         <v>3417.82</v>
       </c>
       <c r="H8" t="n">
-        <v>12.18</v>
+        <v>22.18</v>
       </c>
       <c r="I8" t="n">
-        <v>3378.3</v>
+        <v>3396.5</v>
       </c>
       <c r="J8" t="n">
         <v>3334.66</v>
       </c>
       <c r="K8" t="n">
-        <v>43.64</v>
+        <v>61.84</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -16510,31 +16510,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>527</v>
+        <v>533.65</v>
       </c>
       <c r="D8" t="n">
         <v>502.9</v>
       </c>
       <c r="E8" t="n">
-        <v>24.1</v>
+        <v>30.75</v>
       </c>
       <c r="F8" t="n">
-        <v>543.7</v>
+        <v>535.5</v>
       </c>
       <c r="G8" t="n">
         <v>521.27</v>
       </c>
       <c r="H8" t="n">
-        <v>22.43</v>
+        <v>14.23</v>
       </c>
       <c r="I8" t="n">
-        <v>527</v>
+        <v>513.7</v>
       </c>
       <c r="J8" t="n">
         <v>510.37</v>
       </c>
       <c r="K8" t="n">
-        <v>16.63</v>
+        <v>3.33</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.79</v>
+        <v>6.11</v>
       </c>
     </row>
   </sheetData>
@@ -17444,31 +17444,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1450</v>
+        <v>1458.8</v>
       </c>
       <c r="D9" t="n">
         <v>1473.41</v>
       </c>
       <c r="E9" t="n">
-        <v>-23.41</v>
+        <v>-14.61</v>
       </c>
       <c r="F9" t="n">
-        <v>1474.3</v>
+        <v>1464.4</v>
       </c>
       <c r="G9" t="n">
         <v>1481.82</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.52</v>
+        <v>-17.42</v>
       </c>
       <c r="I9" t="n">
-        <v>1449.2</v>
+        <v>1456.2</v>
       </c>
       <c r="J9" t="n">
         <v>1437.94</v>
       </c>
       <c r="K9" t="n">
-        <v>11.26</v>
+        <v>18.26</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.59</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -9152,31 +9152,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>117.59</v>
+        <v>118</v>
       </c>
       <c r="D168" t="n">
-        <v>122.61</v>
+        <v>114.07</v>
       </c>
       <c r="E168" t="n">
-        <v>-5.02</v>
+        <v>3.93</v>
       </c>
       <c r="F168" t="n">
-        <v>119.35</v>
+        <v>118.9</v>
       </c>
       <c r="G168" t="n">
-        <v>122.61</v>
+        <v>118.72</v>
       </c>
       <c r="H168" t="n">
-        <v>-3.26</v>
+        <v>0.18</v>
       </c>
       <c r="I168" t="n">
-        <v>117.31</v>
+        <v>117.4</v>
       </c>
       <c r="J168" t="n">
-        <v>115.8</v>
+        <v>116.76</v>
       </c>
       <c r="K168" t="n">
-        <v>1.51</v>
+        <v>0.64</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>4.09</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="169">
@@ -9204,31 +9204,31 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1083</v>
+        <v>1067.7</v>
       </c>
       <c r="D169" t="n">
-        <v>1086.93</v>
+        <v>1072.34</v>
       </c>
       <c r="E169" t="n">
-        <v>-3.93</v>
+        <v>-4.64</v>
       </c>
       <c r="F169" t="n">
-        <v>1086.8</v>
+        <v>1082</v>
       </c>
       <c r="G169" t="n">
-        <v>1089.74</v>
+        <v>1081.22</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.94</v>
+        <v>0.78</v>
       </c>
       <c r="I169" t="n">
-        <v>1073</v>
+        <v>1065.1</v>
       </c>
       <c r="J169" t="n">
-        <v>1057.42</v>
+        <v>1062.44</v>
       </c>
       <c r="K169" t="n">
-        <v>15.58</v>
+        <v>2.66</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="170">
@@ -9252,35 +9252,35 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11420</v>
+        <v>5580</v>
       </c>
       <c r="D170" t="n">
-        <v>11780.86</v>
+        <v>5729.65</v>
       </c>
       <c r="E170" t="n">
-        <v>-360.86</v>
+        <v>-149.65</v>
       </c>
       <c r="F170" t="n">
-        <v>11686</v>
+        <v>5618.5</v>
       </c>
       <c r="G170" t="n">
-        <v>12109.86</v>
+        <v>5729.65</v>
       </c>
       <c r="H170" t="n">
-        <v>-423.86</v>
+        <v>-111.15</v>
       </c>
       <c r="I170" t="n">
-        <v>11350</v>
+        <v>5447</v>
       </c>
       <c r="J170" t="n">
-        <v>11751.99</v>
+        <v>5507.17</v>
       </c>
       <c r="K170" t="n">
-        <v>-401.99</v>
+        <v>-60.17</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9289,11 +9289,11 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>3.06</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="171">
@@ -9304,35 +9304,35 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11500</v>
+        <v>11828</v>
       </c>
       <c r="D171" t="n">
-        <v>11562.29</v>
+        <v>11594.94</v>
       </c>
       <c r="E171" t="n">
-        <v>-62.29</v>
+        <v>233.06</v>
       </c>
       <c r="F171" t="n">
-        <v>11570</v>
+        <v>11850</v>
       </c>
       <c r="G171" t="n">
-        <v>11562.29</v>
+        <v>12105.29</v>
       </c>
       <c r="H171" t="n">
-        <v>7.71</v>
+        <v>-255.29</v>
       </c>
       <c r="I171" t="n">
-        <v>11410</v>
+        <v>11318</v>
       </c>
       <c r="J171" t="n">
-        <v>11214.54</v>
+        <v>11828</v>
       </c>
       <c r="K171" t="n">
-        <v>195.46</v>
+        <v>-510</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0.54</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="172">
@@ -9356,35 +9356,35 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1240</v>
+        <v>3428.3</v>
       </c>
       <c r="D172" t="n">
-        <v>1229.5</v>
+        <v>3558.92</v>
       </c>
       <c r="E172" t="n">
-        <v>10.5</v>
+        <v>-130.62</v>
       </c>
       <c r="F172" t="n">
-        <v>1264.7</v>
+        <v>3430</v>
       </c>
       <c r="G172" t="n">
-        <v>1268.15</v>
+        <v>3558.92</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.45</v>
+        <v>-128.92</v>
       </c>
       <c r="I172" t="n">
-        <v>1237</v>
+        <v>3378.3</v>
       </c>
       <c r="J172" t="n">
-        <v>1230.63</v>
+        <v>3362.29</v>
       </c>
       <c r="K172" t="n">
-        <v>6.37</v>
+        <v>16.01</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0.85</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="173">
@@ -9408,35 +9408,35 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>186.5</v>
+        <v>8066.5</v>
       </c>
       <c r="D173" t="n">
-        <v>189.94</v>
+        <v>8153.47</v>
       </c>
       <c r="E173" t="n">
-        <v>-3.44</v>
+        <v>-86.97</v>
       </c>
       <c r="F173" t="n">
-        <v>188.7</v>
+        <v>8143</v>
       </c>
       <c r="G173" t="n">
-        <v>192.97</v>
+        <v>8153.47</v>
       </c>
       <c r="H173" t="n">
-        <v>-4.27</v>
+        <v>-10.47</v>
       </c>
       <c r="I173" t="n">
-        <v>185.32</v>
+        <v>8030</v>
       </c>
       <c r="J173" t="n">
-        <v>187.3</v>
+        <v>7965.64</v>
       </c>
       <c r="K173" t="n">
-        <v>-1.98</v>
+        <v>64.36</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1.81</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="174">
@@ -9460,35 +9460,35 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1939.1</v>
+        <v>187.38</v>
       </c>
       <c r="D174" t="n">
-        <v>2038.57</v>
+        <v>186.39</v>
       </c>
       <c r="E174" t="n">
-        <v>-99.47</v>
+        <v>0.99</v>
       </c>
       <c r="F174" t="n">
-        <v>1970</v>
+        <v>189.34</v>
       </c>
       <c r="G174" t="n">
-        <v>2039.97</v>
+        <v>192.11</v>
       </c>
       <c r="H174" t="n">
-        <v>-69.97</v>
+        <v>-2.77</v>
       </c>
       <c r="I174" t="n">
-        <v>1930.5</v>
+        <v>186.39</v>
       </c>
       <c r="J174" t="n">
-        <v>1992.1</v>
+        <v>187.38</v>
       </c>
       <c r="K174" t="n">
-        <v>-61.6</v>
+        <v>-0.99</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>4.88</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="175">
@@ -9512,35 +9512,35 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8100</v>
+        <v>5790</v>
       </c>
       <c r="D175" t="n">
-        <v>8077.69</v>
+        <v>5704.13</v>
       </c>
       <c r="E175" t="n">
-        <v>22.31</v>
+        <v>85.87</v>
       </c>
       <c r="F175" t="n">
-        <v>8100</v>
+        <v>5849</v>
       </c>
       <c r="G175" t="n">
-        <v>8093.76</v>
+        <v>5841.09</v>
       </c>
       <c r="H175" t="n">
-        <v>6.24</v>
+        <v>7.91</v>
       </c>
       <c r="I175" t="n">
-        <v>8011</v>
+        <v>5765</v>
       </c>
       <c r="J175" t="n">
-        <v>7900.17</v>
+        <v>5738.86</v>
       </c>
       <c r="K175" t="n">
-        <v>110.83</v>
+        <v>26.14</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0.28</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="176">
@@ -9564,35 +9564,35 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5523</v>
+        <v>1632.8</v>
       </c>
       <c r="D176" t="n">
-        <v>5421.76</v>
+        <v>1665.58</v>
       </c>
       <c r="E176" t="n">
-        <v>101.24</v>
+        <v>-32.78</v>
       </c>
       <c r="F176" t="n">
-        <v>5529</v>
+        <v>1652</v>
       </c>
       <c r="G176" t="n">
-        <v>5718.11</v>
+        <v>1665.58</v>
       </c>
       <c r="H176" t="n">
-        <v>-189.11</v>
+        <v>-13.58</v>
       </c>
       <c r="I176" t="n">
-        <v>5406</v>
+        <v>1614.4</v>
       </c>
       <c r="J176" t="n">
-        <v>5549.31</v>
+        <v>1631.3</v>
       </c>
       <c r="K176" t="n">
-        <v>-143.31</v>
+        <v>-16.9</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="177">
@@ -9616,35 +9616,35 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1639</v>
+        <v>318.5</v>
       </c>
       <c r="D177" t="n">
-        <v>1619.59</v>
+        <v>339.17</v>
       </c>
       <c r="E177" t="n">
-        <v>19.41</v>
+        <v>-20.67</v>
       </c>
       <c r="F177" t="n">
-        <v>1652.8</v>
+        <v>325</v>
       </c>
       <c r="G177" t="n">
-        <v>1667.09</v>
+        <v>339.17</v>
       </c>
       <c r="H177" t="n">
-        <v>-14.29</v>
+        <v>-14.17</v>
       </c>
       <c r="I177" t="n">
-        <v>1626.3</v>
+        <v>316.8</v>
       </c>
       <c r="J177" t="n">
-        <v>1617.66</v>
+        <v>317.11</v>
       </c>
       <c r="K177" t="n">
-        <v>8.640000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1.2</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="178">
@@ -9668,35 +9668,35 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5850</v>
+        <v>1992.1</v>
       </c>
       <c r="D178" t="n">
-        <v>5985.55</v>
+        <v>1920.95</v>
       </c>
       <c r="E178" t="n">
-        <v>-135.55</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F178" t="n">
-        <v>5934</v>
+        <v>2005.8</v>
       </c>
       <c r="G178" t="n">
-        <v>5985.55</v>
+        <v>2030.91</v>
       </c>
       <c r="H178" t="n">
-        <v>-51.55</v>
+        <v>-25.11</v>
       </c>
       <c r="I178" t="n">
-        <v>5802</v>
+        <v>1932</v>
       </c>
       <c r="J178" t="n">
-        <v>5694.13</v>
+        <v>1992.1</v>
       </c>
       <c r="K178" t="n">
-        <v>107.87</v>
+        <v>-60.1</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9705,11 +9705,11 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="179">
@@ -9720,39 +9720,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3428.2</v>
+        <v>5310</v>
       </c>
       <c r="D179" t="n">
-        <v>3328.8</v>
+        <v>5317.96</v>
       </c>
       <c r="E179" t="n">
-        <v>99.40000000000001</v>
+        <v>-7.96</v>
       </c>
       <c r="F179" t="n">
-        <v>3440</v>
+        <v>5370</v>
       </c>
       <c r="G179" t="n">
-        <v>3417.82</v>
+        <v>5357.07</v>
       </c>
       <c r="H179" t="n">
-        <v>22.18</v>
+        <v>12.93</v>
       </c>
       <c r="I179" t="n">
-        <v>3396.5</v>
+        <v>5310</v>
       </c>
       <c r="J179" t="n">
-        <v>3334.66</v>
+        <v>5263.32</v>
       </c>
       <c r="K179" t="n">
-        <v>61.84</v>
+        <v>46.68</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>2.99</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="180">
@@ -9772,39 +9772,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>318</v>
+        <v>14130</v>
       </c>
       <c r="D180" t="n">
-        <v>301.01</v>
+        <v>14369.66</v>
       </c>
       <c r="E180" t="n">
-        <v>16.99</v>
+        <v>-239.66</v>
       </c>
       <c r="F180" t="n">
-        <v>319.35</v>
+        <v>14209</v>
       </c>
       <c r="G180" t="n">
-        <v>324.15</v>
+        <v>14369.66</v>
       </c>
       <c r="H180" t="n">
-        <v>-4.8</v>
+        <v>-160.66</v>
       </c>
       <c r="I180" t="n">
-        <v>313.3</v>
+        <v>13999</v>
       </c>
       <c r="J180" t="n">
-        <v>314.5</v>
+        <v>13811.08</v>
       </c>
       <c r="K180" t="n">
-        <v>-1.2</v>
+        <v>187.92</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="181">
@@ -9824,39 +9824,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14035</v>
+        <v>1240</v>
       </c>
       <c r="D181" t="n">
-        <v>13911.32</v>
+        <v>1260.59</v>
       </c>
       <c r="E181" t="n">
-        <v>123.68</v>
+        <v>-20.59</v>
       </c>
       <c r="F181" t="n">
-        <v>14065</v>
+        <v>1246.9</v>
       </c>
       <c r="G181" t="n">
-        <v>13911.32</v>
+        <v>1261.6</v>
       </c>
       <c r="H181" t="n">
-        <v>153.68</v>
+        <v>-14.7</v>
       </c>
       <c r="I181" t="n">
-        <v>13645</v>
+        <v>1230.1</v>
       </c>
       <c r="J181" t="n">
-        <v>13697.56</v>
+        <v>1239.9</v>
       </c>
       <c r="K181" t="n">
-        <v>-52.56</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0.89</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="182">
@@ -9876,39 +9876,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>615</v>
+        <v>376</v>
       </c>
       <c r="D182" t="n">
-        <v>583.87</v>
+        <v>377.79</v>
       </c>
       <c r="E182" t="n">
-        <v>31.13</v>
+        <v>-1.79</v>
       </c>
       <c r="F182" t="n">
-        <v>615.3</v>
+        <v>384.95</v>
       </c>
       <c r="G182" t="n">
-        <v>606.37</v>
+        <v>377.79</v>
       </c>
       <c r="H182" t="n">
-        <v>8.93</v>
+        <v>7.16</v>
       </c>
       <c r="I182" t="n">
-        <v>603</v>
+        <v>375</v>
       </c>
       <c r="J182" t="n">
-        <v>588.14</v>
+        <v>364.69</v>
       </c>
       <c r="K182" t="n">
-        <v>14.86</v>
+        <v>10.31</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>5.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="183">
@@ -9928,35 +9928,35 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5370</v>
+        <v>7649</v>
       </c>
       <c r="D183" t="n">
-        <v>5404.88</v>
+        <v>7639.02</v>
       </c>
       <c r="E183" t="n">
-        <v>-34.88</v>
+        <v>9.98</v>
       </c>
       <c r="F183" t="n">
-        <v>5370</v>
+        <v>7825</v>
       </c>
       <c r="G183" t="n">
-        <v>5404.88</v>
+        <v>7758.82</v>
       </c>
       <c r="H183" t="n">
-        <v>-34.88</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="I183" t="n">
-        <v>5281.5</v>
+        <v>7639</v>
       </c>
       <c r="J183" t="n">
-        <v>5220.06</v>
+        <v>7624.51</v>
       </c>
       <c r="K183" t="n">
-        <v>61.44</v>
+        <v>14.49</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="184">
@@ -9980,35 +9980,35 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>176.23</v>
+        <v>11475</v>
       </c>
       <c r="D184" t="n">
-        <v>173.62</v>
+        <v>11504.45</v>
       </c>
       <c r="E184" t="n">
-        <v>2.61</v>
+        <v>-29.45</v>
       </c>
       <c r="F184" t="n">
-        <v>182.7</v>
+        <v>11541</v>
       </c>
       <c r="G184" t="n">
-        <v>174.94</v>
+        <v>11504.45</v>
       </c>
       <c r="H184" t="n">
-        <v>7.76</v>
+        <v>36.55</v>
       </c>
       <c r="I184" t="n">
-        <v>176.23</v>
+        <v>11387</v>
       </c>
       <c r="J184" t="n">
-        <v>169.74</v>
+        <v>11317.78</v>
       </c>
       <c r="K184" t="n">
-        <v>6.49</v>
+        <v>69.22</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="185">
@@ -10032,35 +10032,35 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7710</v>
+        <v>1812</v>
       </c>
       <c r="D185" t="n">
-        <v>7781.82</v>
+        <v>1823.32</v>
       </c>
       <c r="E185" t="n">
-        <v>-71.81999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="F185" t="n">
-        <v>7772</v>
+        <v>1836.4</v>
       </c>
       <c r="G185" t="n">
-        <v>7793.45</v>
+        <v>1823.32</v>
       </c>
       <c r="H185" t="n">
-        <v>-21.45</v>
+        <v>13.08</v>
       </c>
       <c r="I185" t="n">
-        <v>7659</v>
+        <v>1804.2</v>
       </c>
       <c r="J185" t="n">
-        <v>7561.84</v>
+        <v>1772.18</v>
       </c>
       <c r="K185" t="n">
-        <v>97.16</v>
+        <v>32.02</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="186">
@@ -10088,31 +10088,31 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2237.1</v>
+        <v>2199</v>
       </c>
       <c r="D186" t="n">
-        <v>2237.89</v>
+        <v>2215.81</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.79</v>
+        <v>-16.81</v>
       </c>
       <c r="F186" t="n">
-        <v>2273.9</v>
+        <v>2255</v>
       </c>
       <c r="G186" t="n">
-        <v>2237.89</v>
+        <v>2215.81</v>
       </c>
       <c r="H186" t="n">
-        <v>36.01</v>
+        <v>39.19</v>
       </c>
       <c r="I186" t="n">
-        <v>2219.5</v>
+        <v>2191.6</v>
       </c>
       <c r="J186" t="n">
-        <v>2135.13</v>
+        <v>2152.82</v>
       </c>
       <c r="K186" t="n">
-        <v>84.37</v>
+        <v>38.78</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="187">
@@ -10136,35 +10136,35 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1829</v>
+        <v>4057</v>
       </c>
       <c r="D187" t="n">
-        <v>1832.18</v>
+        <v>4109.5</v>
       </c>
       <c r="E187" t="n">
-        <v>-3.18</v>
+        <v>-52.5</v>
       </c>
       <c r="F187" t="n">
-        <v>1829.9</v>
+        <v>4072.5</v>
       </c>
       <c r="G187" t="n">
-        <v>1832.18</v>
+        <v>4119.97</v>
       </c>
       <c r="H187" t="n">
-        <v>-2.28</v>
+        <v>-47.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1788</v>
+        <v>4033.1</v>
       </c>
       <c r="J187" t="n">
-        <v>1760.46</v>
+        <v>4057</v>
       </c>
       <c r="K187" t="n">
-        <v>27.54</v>
+        <v>-23.9</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>0.17</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="188">
@@ -10188,35 +10188,35 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1357.3</v>
+        <v>171.64</v>
       </c>
       <c r="D188" t="n">
-        <v>1341.8</v>
+        <v>175.61</v>
       </c>
       <c r="E188" t="n">
-        <v>15.5</v>
+        <v>-3.97</v>
       </c>
       <c r="F188" t="n">
-        <v>1369.4</v>
+        <v>179.5</v>
       </c>
       <c r="G188" t="n">
-        <v>1365.14</v>
+        <v>175.61</v>
       </c>
       <c r="H188" t="n">
-        <v>4.26</v>
+        <v>3.89</v>
       </c>
       <c r="I188" t="n">
-        <v>1336.5</v>
+        <v>169.75</v>
       </c>
       <c r="J188" t="n">
-        <v>1324.46</v>
+        <v>171.41</v>
       </c>
       <c r="K188" t="n">
-        <v>12.04</v>
+        <v>-1.66</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="189">
@@ -10240,35 +10240,35 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4070.7</v>
+        <v>1029.5</v>
       </c>
       <c r="D189" t="n">
-        <v>4054.81</v>
+        <v>1004.04</v>
       </c>
       <c r="E189" t="n">
-        <v>15.89</v>
+        <v>25.46</v>
       </c>
       <c r="F189" t="n">
-        <v>4070.7</v>
+        <v>1036.8</v>
       </c>
       <c r="G189" t="n">
-        <v>4138.36</v>
+        <v>1022.66</v>
       </c>
       <c r="H189" t="n">
-        <v>-67.66</v>
+        <v>14.14</v>
       </c>
       <c r="I189" t="n">
-        <v>3990</v>
+        <v>1021.35</v>
       </c>
       <c r="J189" t="n">
-        <v>4038.69</v>
+        <v>1009.19</v>
       </c>
       <c r="K189" t="n">
-        <v>-48.69</v>
+        <v>12.16</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0.39</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="190">
@@ -10296,31 +10296,31 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>279.3</v>
+        <v>282.6</v>
       </c>
       <c r="D190" t="n">
-        <v>285.56</v>
+        <v>278.62</v>
       </c>
       <c r="E190" t="n">
-        <v>-6.26</v>
+        <v>3.98</v>
       </c>
       <c r="F190" t="n">
-        <v>287.4</v>
+        <v>283.5</v>
       </c>
       <c r="G190" t="n">
-        <v>285.73</v>
+        <v>283.43</v>
       </c>
       <c r="H190" t="n">
-        <v>1.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>273</v>
+        <v>277.15</v>
       </c>
       <c r="J190" t="n">
-        <v>277.17</v>
+        <v>278.41</v>
       </c>
       <c r="K190" t="n">
-        <v>-4.17</v>
+        <v>-1.26</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>2.19</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="191">
@@ -10348,31 +10348,31 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1458.8</v>
+        <v>1450</v>
       </c>
       <c r="D191" t="n">
-        <v>1473.41</v>
+        <v>1447.1</v>
       </c>
       <c r="E191" t="n">
-        <v>-14.61</v>
+        <v>2.9</v>
       </c>
       <c r="F191" t="n">
-        <v>1464.4</v>
+        <v>1474.3</v>
       </c>
       <c r="G191" t="n">
-        <v>1481.82</v>
+        <v>1460.9</v>
       </c>
       <c r="H191" t="n">
-        <v>-17.42</v>
+        <v>13.4</v>
       </c>
       <c r="I191" t="n">
-        <v>1456.2</v>
+        <v>1449.2</v>
       </c>
       <c r="J191" t="n">
-        <v>1437.94</v>
+        <v>1436.58</v>
       </c>
       <c r="K191" t="n">
-        <v>18.26</v>
+        <v>12.62</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="192">
@@ -10396,35 +10396,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>400.5</v>
+        <v>601</v>
       </c>
       <c r="D192" t="n">
-        <v>401.79</v>
+        <v>638.11</v>
       </c>
       <c r="E192" t="n">
-        <v>-1.29</v>
+        <v>-37.11</v>
       </c>
       <c r="F192" t="n">
-        <v>413.65</v>
+        <v>615.9</v>
       </c>
       <c r="G192" t="n">
-        <v>401.79</v>
+        <v>638.11</v>
       </c>
       <c r="H192" t="n">
-        <v>11.86</v>
+        <v>-22.21</v>
       </c>
       <c r="I192" t="n">
-        <v>400</v>
+        <v>599.5</v>
       </c>
       <c r="J192" t="n">
-        <v>361.7</v>
+        <v>589.05</v>
       </c>
       <c r="K192" t="n">
-        <v>38.3</v>
+        <v>10.45</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0.32</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="193">
@@ -10452,31 +10452,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2025</v>
+        <v>2008.3</v>
       </c>
       <c r="D193" t="n">
-        <v>2060.38</v>
+        <v>1989.61</v>
       </c>
       <c r="E193" t="n">
-        <v>-35.38</v>
+        <v>18.69</v>
       </c>
       <c r="F193" t="n">
-        <v>2038</v>
+        <v>2033.6</v>
       </c>
       <c r="G193" t="n">
-        <v>2060.38</v>
+        <v>1989.61</v>
       </c>
       <c r="H193" t="n">
-        <v>-22.38</v>
+        <v>43.99</v>
       </c>
       <c r="I193" t="n">
-        <v>2006.7</v>
+        <v>2006.6</v>
       </c>
       <c r="J193" t="n">
-        <v>1952.58</v>
+        <v>1968.34</v>
       </c>
       <c r="K193" t="n">
-        <v>54.12</v>
+        <v>38.26</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1.72</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10500,35 +10500,35 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1046.25</v>
+        <v>1180</v>
       </c>
       <c r="D194" t="n">
-        <v>1081.36</v>
+        <v>1180.22</v>
       </c>
       <c r="E194" t="n">
-        <v>-35.11</v>
+        <v>-0.22</v>
       </c>
       <c r="F194" t="n">
-        <v>1073</v>
+        <v>1191.5</v>
       </c>
       <c r="G194" t="n">
-        <v>1081.36</v>
+        <v>1180.22</v>
       </c>
       <c r="H194" t="n">
-        <v>-8.359999999999999</v>
+        <v>11.28</v>
       </c>
       <c r="I194" t="n">
-        <v>1040</v>
+        <v>1167</v>
       </c>
       <c r="J194" t="n">
-        <v>1000.9</v>
+        <v>1152.46</v>
       </c>
       <c r="K194" t="n">
-        <v>39.1</v>
+        <v>14.54</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>3.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="195">
@@ -10552,35 +10552,35 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1183</v>
+        <v>1343</v>
       </c>
       <c r="D195" t="n">
-        <v>1192.24</v>
+        <v>1369.38</v>
       </c>
       <c r="E195" t="n">
-        <v>-9.24</v>
+        <v>-26.38</v>
       </c>
       <c r="F195" t="n">
-        <v>1184.9</v>
+        <v>1367.1</v>
       </c>
       <c r="G195" t="n">
-        <v>1192.24</v>
+        <v>1369.38</v>
       </c>
       <c r="H195" t="n">
-        <v>-7.34</v>
+        <v>-2.28</v>
       </c>
       <c r="I195" t="n">
-        <v>1149.2</v>
+        <v>1337</v>
       </c>
       <c r="J195" t="n">
-        <v>1142.98</v>
+        <v>1319.59</v>
       </c>
       <c r="K195" t="n">
-        <v>6.22</v>
+        <v>17.41</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0.78</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="196">
@@ -10608,31 +10608,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>533.65</v>
+        <v>527</v>
       </c>
       <c r="D196" t="n">
-        <v>502.9</v>
+        <v>563.7</v>
       </c>
       <c r="E196" t="n">
-        <v>30.75</v>
+        <v>-36.7</v>
       </c>
       <c r="F196" t="n">
-        <v>535.5</v>
+        <v>543.7</v>
       </c>
       <c r="G196" t="n">
-        <v>521.27</v>
+        <v>563.7</v>
       </c>
       <c r="H196" t="n">
-        <v>14.23</v>
+        <v>-20</v>
       </c>
       <c r="I196" t="n">
-        <v>513.7</v>
+        <v>527</v>
       </c>
       <c r="J196" t="n">
-        <v>510.37</v>
+        <v>514.75</v>
       </c>
       <c r="K196" t="n">
-        <v>3.33</v>
+        <v>12.25</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10641,11 +10641,11 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>6.11</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="197">
@@ -10660,31 +10660,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>897</v>
+        <v>894.95</v>
       </c>
       <c r="D197" t="n">
-        <v>911.91</v>
+        <v>887.36</v>
       </c>
       <c r="E197" t="n">
-        <v>-14.91</v>
+        <v>7.59</v>
       </c>
       <c r="F197" t="n">
-        <v>903.8</v>
+        <v>902.8</v>
       </c>
       <c r="G197" t="n">
-        <v>911.91</v>
+        <v>907.2</v>
       </c>
       <c r="H197" t="n">
-        <v>-8.109999999999999</v>
+        <v>-4.4</v>
       </c>
       <c r="I197" t="n">
-        <v>883.15</v>
+        <v>885.3</v>
       </c>
       <c r="J197" t="n">
-        <v>884.1799999999999</v>
+        <v>891.47</v>
       </c>
       <c r="K197" t="n">
-        <v>-1.03</v>
+        <v>-6.17</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1.64</v>
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -11352,31 +11352,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="D9" t="n">
-        <v>1192.24</v>
+        <v>1180.22</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.24</v>
+        <v>-0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1184.9</v>
+        <v>1191.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1192.24</v>
+        <v>1180.22</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.34</v>
+        <v>11.28</v>
       </c>
       <c r="I9" t="n">
-        <v>1149.2</v>
+        <v>1167</v>
       </c>
       <c r="J9" t="n">
-        <v>1142.98</v>
+        <v>1152.46</v>
       </c>
       <c r="K9" t="n">
-        <v>6.22</v>
+        <v>14.54</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.78</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -11854,35 +11854,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="D9" t="n">
-        <v>583.87</v>
+        <v>638.11</v>
       </c>
       <c r="E9" t="n">
-        <v>31.13</v>
+        <v>-37.11</v>
       </c>
       <c r="F9" t="n">
-        <v>615.3</v>
+        <v>615.9</v>
       </c>
       <c r="G9" t="n">
-        <v>606.37</v>
+        <v>638.11</v>
       </c>
       <c r="H9" t="n">
-        <v>8.93</v>
+        <v>-22.21</v>
       </c>
       <c r="I9" t="n">
-        <v>603</v>
+        <v>599.5</v>
       </c>
       <c r="J9" t="n">
-        <v>588.14</v>
+        <v>589.05</v>
       </c>
       <c r="K9" t="n">
-        <v>14.86</v>
+        <v>10.45</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -11891,7 +11891,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.33</v>
+        <v>5.82</v>
       </c>
     </row>
   </sheetData>
@@ -12356,31 +12356,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8100</v>
+        <v>8066.5</v>
       </c>
       <c r="D9" t="n">
-        <v>8077.69</v>
+        <v>8153.47</v>
       </c>
       <c r="E9" t="n">
-        <v>22.31</v>
+        <v>-86.97</v>
       </c>
       <c r="F9" t="n">
-        <v>8100</v>
+        <v>8143</v>
       </c>
       <c r="G9" t="n">
-        <v>8093.76</v>
+        <v>8153.47</v>
       </c>
       <c r="H9" t="n">
-        <v>6.24</v>
+        <v>-10.47</v>
       </c>
       <c r="I9" t="n">
-        <v>8011</v>
+        <v>8030</v>
       </c>
       <c r="J9" t="n">
-        <v>7900.17</v>
+        <v>7965.64</v>
       </c>
       <c r="K9" t="n">
-        <v>110.83</v>
+        <v>64.36</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.28</v>
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>
@@ -13152,31 +13152,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1639</v>
+        <v>1632.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1619.59</v>
+        <v>1665.58</v>
       </c>
       <c r="E9" t="n">
-        <v>19.41</v>
+        <v>-32.78</v>
       </c>
       <c r="F9" t="n">
-        <v>1652.8</v>
+        <v>1652</v>
       </c>
       <c r="G9" t="n">
-        <v>1667.09</v>
+        <v>1665.58</v>
       </c>
       <c r="H9" t="n">
-        <v>-14.29</v>
+        <v>-13.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1626.3</v>
+        <v>1614.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1617.66</v>
+        <v>1631.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8.640000000000001</v>
+        <v>-16.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
     </row>
   </sheetData>
@@ -13654,31 +13654,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>318.5</v>
       </c>
       <c r="D9" t="n">
-        <v>301.01</v>
+        <v>339.17</v>
       </c>
       <c r="E9" t="n">
-        <v>16.99</v>
+        <v>-20.67</v>
       </c>
       <c r="F9" t="n">
-        <v>319.35</v>
+        <v>325</v>
       </c>
       <c r="G9" t="n">
-        <v>324.15</v>
+        <v>339.17</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.8</v>
+        <v>-14.17</v>
       </c>
       <c r="I9" t="n">
-        <v>313.3</v>
+        <v>316.8</v>
       </c>
       <c r="J9" t="n">
-        <v>314.5</v>
+        <v>317.11</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2</v>
+        <v>-0.31</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.64</v>
+        <v>6.09</v>
       </c>
     </row>
   </sheetData>
@@ -14156,35 +14156,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14035</v>
+        <v>14130</v>
       </c>
       <c r="D9" t="n">
-        <v>13911.32</v>
+        <v>14369.66</v>
       </c>
       <c r="E9" t="n">
-        <v>123.68</v>
+        <v>-239.66</v>
       </c>
       <c r="F9" t="n">
-        <v>14065</v>
+        <v>14209</v>
       </c>
       <c r="G9" t="n">
-        <v>13911.32</v>
+        <v>14369.66</v>
       </c>
       <c r="H9" t="n">
-        <v>153.68</v>
+        <v>-160.66</v>
       </c>
       <c r="I9" t="n">
-        <v>13645</v>
+        <v>13999</v>
       </c>
       <c r="J9" t="n">
-        <v>13697.56</v>
+        <v>13811.08</v>
       </c>
       <c r="K9" t="n">
-        <v>-52.56</v>
+        <v>187.92</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -14658,31 +14658,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1829</v>
+        <v>1812</v>
       </c>
       <c r="D9" t="n">
-        <v>1832.18</v>
+        <v>1823.32</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.18</v>
+        <v>-11.32</v>
       </c>
       <c r="F9" t="n">
-        <v>1829.9</v>
+        <v>1836.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1832.18</v>
+        <v>1823.32</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.28</v>
+        <v>13.08</v>
       </c>
       <c r="I9" t="n">
-        <v>1788</v>
+        <v>1804.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1760.46</v>
+        <v>1772.18</v>
       </c>
       <c r="K9" t="n">
-        <v>27.54</v>
+        <v>32.02</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -15108,31 +15108,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5523</v>
+        <v>5580</v>
       </c>
       <c r="D8" t="n">
-        <v>5421.76</v>
+        <v>5729.65</v>
       </c>
       <c r="E8" t="n">
-        <v>101.24</v>
+        <v>-149.65</v>
       </c>
       <c r="F8" t="n">
-        <v>5529</v>
+        <v>5618.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5718.11</v>
+        <v>5729.65</v>
       </c>
       <c r="H8" t="n">
-        <v>-189.11</v>
+        <v>-111.15</v>
       </c>
       <c r="I8" t="n">
-        <v>5406</v>
+        <v>5447</v>
       </c>
       <c r="J8" t="n">
-        <v>5549.31</v>
+        <v>5507.17</v>
       </c>
       <c r="K8" t="n">
-        <v>-143.31</v>
+        <v>-60.17</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>2.61</v>
       </c>
     </row>
   </sheetData>
@@ -15610,31 +15610,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>117.59</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>122.61</v>
+        <v>114.07</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.02</v>
+        <v>3.93</v>
       </c>
       <c r="F9" t="n">
-        <v>119.35</v>
+        <v>118.9</v>
       </c>
       <c r="G9" t="n">
-        <v>122.61</v>
+        <v>118.72</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.26</v>
+        <v>0.18</v>
       </c>
       <c r="I9" t="n">
-        <v>117.31</v>
+        <v>117.4</v>
       </c>
       <c r="J9" t="n">
-        <v>115.8</v>
+        <v>116.76</v>
       </c>
       <c r="K9" t="n">
-        <v>1.51</v>
+        <v>0.64</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.09</v>
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
@@ -16060,31 +16060,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3428.2</v>
+        <v>3428.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3328.8</v>
+        <v>3558.92</v>
       </c>
       <c r="E8" t="n">
-        <v>99.40000000000001</v>
+        <v>-130.62</v>
       </c>
       <c r="F8" t="n">
-        <v>3440</v>
+        <v>3430</v>
       </c>
       <c r="G8" t="n">
-        <v>3417.82</v>
+        <v>3558.92</v>
       </c>
       <c r="H8" t="n">
-        <v>22.18</v>
+        <v>-128.92</v>
       </c>
       <c r="I8" t="n">
-        <v>3396.5</v>
+        <v>3378.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3334.66</v>
+        <v>3362.29</v>
       </c>
       <c r="K8" t="n">
-        <v>61.84</v>
+        <v>16.01</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>3.67</v>
       </c>
     </row>
   </sheetData>
@@ -16510,31 +16510,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>533.65</v>
+        <v>527</v>
       </c>
       <c r="D8" t="n">
-        <v>502.9</v>
+        <v>563.7</v>
       </c>
       <c r="E8" t="n">
-        <v>30.75</v>
+        <v>-36.7</v>
       </c>
       <c r="F8" t="n">
-        <v>535.5</v>
+        <v>543.7</v>
       </c>
       <c r="G8" t="n">
-        <v>521.27</v>
+        <v>563.7</v>
       </c>
       <c r="H8" t="n">
-        <v>14.23</v>
+        <v>-20</v>
       </c>
       <c r="I8" t="n">
-        <v>513.7</v>
+        <v>527</v>
       </c>
       <c r="J8" t="n">
-        <v>510.37</v>
+        <v>514.75</v>
       </c>
       <c r="K8" t="n">
-        <v>3.33</v>
+        <v>12.25</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -16543,11 +16543,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.11</v>
+        <v>6.51</v>
       </c>
     </row>
   </sheetData>
@@ -17444,31 +17444,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1458.8</v>
+        <v>1450</v>
       </c>
       <c r="D9" t="n">
-        <v>1473.41</v>
+        <v>1447.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.61</v>
+        <v>2.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1464.4</v>
+        <v>1474.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1481.82</v>
+        <v>1460.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.42</v>
+        <v>13.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1456.2</v>
+        <v>1449.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1437.94</v>
+        <v>1436.58</v>
       </c>
       <c r="K9" t="n">
-        <v>18.26</v>
+        <v>12.62</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -9464,31 +9464,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D174" t="n">
         <v>186.39</v>
       </c>
       <c r="E174" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="F174" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G174" t="n">
         <v>192.11</v>
       </c>
       <c r="H174" t="n">
-        <v>-2.77</v>
+        <v>-3.41</v>
       </c>
       <c r="I174" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J174" t="n">
         <v>187.38</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.99</v>
+        <v>-2.06</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="175">
@@ -9516,31 +9516,31 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D175" t="n">
         <v>5704.13</v>
       </c>
       <c r="E175" t="n">
-        <v>85.87</v>
+        <v>145.87</v>
       </c>
       <c r="F175" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G175" t="n">
         <v>5841.09</v>
       </c>
       <c r="H175" t="n">
-        <v>7.91</v>
+        <v>92.91</v>
       </c>
       <c r="I175" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J175" t="n">
         <v>5738.86</v>
       </c>
       <c r="K175" t="n">
-        <v>26.14</v>
+        <v>63.14</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="176">
@@ -9880,31 +9880,31 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D182" t="n">
         <v>377.79</v>
       </c>
       <c r="E182" t="n">
-        <v>-1.79</v>
+        <v>22.71</v>
       </c>
       <c r="F182" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G182" t="n">
         <v>377.79</v>
       </c>
       <c r="H182" t="n">
-        <v>7.16</v>
+        <v>35.86</v>
       </c>
       <c r="I182" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J182" t="n">
         <v>364.69</v>
       </c>
       <c r="K182" t="n">
-        <v>10.31</v>
+        <v>35.31</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9913,11 +9913,11 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="183">
@@ -9932,31 +9932,31 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D183" t="n">
         <v>7639.02</v>
       </c>
       <c r="E183" t="n">
-        <v>9.98</v>
+        <v>70.98</v>
       </c>
       <c r="F183" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G183" t="n">
         <v>7758.82</v>
       </c>
       <c r="H183" t="n">
-        <v>66.18000000000001</v>
+        <v>13.18</v>
       </c>
       <c r="I183" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J183" t="n">
         <v>7624.51</v>
       </c>
       <c r="K183" t="n">
-        <v>14.49</v>
+        <v>34.49</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.13</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="184">
@@ -10036,31 +10036,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D185" t="n">
         <v>1823.32</v>
       </c>
       <c r="E185" t="n">
-        <v>-11.32</v>
+        <v>5.68</v>
       </c>
       <c r="F185" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G185" t="n">
         <v>1823.32</v>
       </c>
       <c r="H185" t="n">
-        <v>13.08</v>
+        <v>6.58</v>
       </c>
       <c r="I185" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J185" t="n">
         <v>1772.18</v>
       </c>
       <c r="K185" t="n">
-        <v>32.02</v>
+        <v>15.82</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="186">
@@ -14658,31 +14658,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D9" t="n">
         <v>1823.32</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.32</v>
+        <v>5.68</v>
       </c>
       <c r="F9" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G9" t="n">
         <v>1823.32</v>
       </c>
       <c r="H9" t="n">
-        <v>13.08</v>
+        <v>6.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J9" t="n">
         <v>1772.18</v>
       </c>
       <c r="K9" t="n">
-        <v>32.02</v>
+        <v>15.82</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N197"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10698,6 +10698,1566 @@
       </c>
       <c r="N197" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="D198" t="n">
+        <v>190.94</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F198" t="n">
+        <v>190.15</v>
+      </c>
+      <c r="G198" t="n">
+        <v>193.61</v>
+      </c>
+      <c r="H198" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="I198" t="n">
+        <v>184.27</v>
+      </c>
+      <c r="J198" t="n">
+        <v>188.62</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>174.54</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F199" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>181.19</v>
+      </c>
+      <c r="H199" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I199" t="n">
+        <v>171.98</v>
+      </c>
+      <c r="J199" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D200" t="n">
+        <v>7793.01</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-133.01</v>
+      </c>
+      <c r="F200" t="n">
+        <v>7760</v>
+      </c>
+      <c r="G200" t="n">
+        <v>7793.01</v>
+      </c>
+      <c r="H200" t="n">
+        <v>-33.01</v>
+      </c>
+      <c r="I200" t="n">
+        <v>7627</v>
+      </c>
+      <c r="J200" t="n">
+        <v>7557.5</v>
+      </c>
+      <c r="K200" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5745</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5939.03</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-194.03</v>
+      </c>
+      <c r="F201" t="n">
+        <v>5811.5</v>
+      </c>
+      <c r="G201" t="n">
+        <v>5939.03</v>
+      </c>
+      <c r="H201" t="n">
+        <v>-127.53</v>
+      </c>
+      <c r="I201" t="n">
+        <v>5740</v>
+      </c>
+      <c r="J201" t="n">
+        <v>5644.95</v>
+      </c>
+      <c r="K201" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1061.2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1065.06</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1068.8</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1079.14</v>
+      </c>
+      <c r="H202" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1052.4</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1051.01</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1049.9</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1085.14</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-35.24</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1085.14</v>
+      </c>
+      <c r="H203" t="n">
+        <v>-25.14</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1032.7</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1045.02</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-12.32</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>5570</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5474.57</v>
+      </c>
+      <c r="E204" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="F204" t="n">
+        <v>5613</v>
+      </c>
+      <c r="G204" t="n">
+        <v>5703.39</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-90.39</v>
+      </c>
+      <c r="I204" t="n">
+        <v>5520</v>
+      </c>
+      <c r="J204" t="n">
+        <v>5556.07</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-36.07</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1269.9</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1259.16</v>
+      </c>
+      <c r="E205" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1263.84</v>
+      </c>
+      <c r="H205" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1237.57</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>117.32</v>
+      </c>
+      <c r="D206" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="F206" t="n">
+        <v>118.06</v>
+      </c>
+      <c r="G206" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I206" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="J206" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="D207" t="n">
+        <v>414.13</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-26.58</v>
+      </c>
+      <c r="F207" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="G207" t="n">
+        <v>414.13</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-22.63</v>
+      </c>
+      <c r="I207" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J207" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="K207" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1355.8</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1340.33</v>
+      </c>
+      <c r="E208" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1374</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1351.8</v>
+      </c>
+      <c r="H208" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1340.7</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1315.63</v>
+      </c>
+      <c r="K208" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>11789</v>
+      </c>
+      <c r="D209" t="n">
+        <v>12122.16</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-333.16</v>
+      </c>
+      <c r="F209" t="n">
+        <v>11920</v>
+      </c>
+      <c r="G209" t="n">
+        <v>12122.16</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-202.16</v>
+      </c>
+      <c r="I209" t="n">
+        <v>11742</v>
+      </c>
+      <c r="J209" t="n">
+        <v>11614.72</v>
+      </c>
+      <c r="K209" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4066.74</v>
+      </c>
+      <c r="E210" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="F210" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="G210" t="n">
+        <v>4131.85</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-45.15</v>
+      </c>
+      <c r="I210" t="n">
+        <v>4026</v>
+      </c>
+      <c r="J210" t="n">
+        <v>4025.37</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>614</v>
+      </c>
+      <c r="D211" t="n">
+        <v>582.91</v>
+      </c>
+      <c r="E211" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="F211" t="n">
+        <v>614</v>
+      </c>
+      <c r="G211" t="n">
+        <v>619.24</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I211" t="n">
+        <v>594.25</v>
+      </c>
+      <c r="J211" t="n">
+        <v>602.92</v>
+      </c>
+      <c r="K211" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>318</v>
+      </c>
+      <c r="D212" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E212" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F212" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="G212" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="H212" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I212" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="J212" t="n">
+        <v>316.79</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>5275.5</v>
+      </c>
+      <c r="D213" t="n">
+        <v>5309.72</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-34.22</v>
+      </c>
+      <c r="F213" t="n">
+        <v>5332.5</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5386.06</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-53.56</v>
+      </c>
+      <c r="I213" t="n">
+        <v>5262.5</v>
+      </c>
+      <c r="J213" t="n">
+        <v>5246.39</v>
+      </c>
+      <c r="K213" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-20.13</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1821</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1799.6</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1760.55</v>
+      </c>
+      <c r="K214" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>11379</v>
+      </c>
+      <c r="D215" t="n">
+        <v>11440.67</v>
+      </c>
+      <c r="E215" t="n">
+        <v>-61.67</v>
+      </c>
+      <c r="F215" t="n">
+        <v>11574</v>
+      </c>
+      <c r="G215" t="n">
+        <v>11488.9</v>
+      </c>
+      <c r="H215" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="I215" t="n">
+        <v>11306</v>
+      </c>
+      <c r="J215" t="n">
+        <v>11186.56</v>
+      </c>
+      <c r="K215" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1590.94</v>
+      </c>
+      <c r="E216" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1638.9</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1638.15</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1604.2</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1595.48</v>
+      </c>
+      <c r="K216" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2065.98</v>
+      </c>
+      <c r="E217" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2110.9</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2081.91</v>
+      </c>
+      <c r="H217" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2072.4</v>
+      </c>
+      <c r="J217" t="n">
+        <v>2026.46</v>
+      </c>
+      <c r="K217" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2190.76</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2209.6</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2190.76</v>
+      </c>
+      <c r="H218" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="I218" t="n">
+        <v>2172.4</v>
+      </c>
+      <c r="J218" t="n">
+        <v>2128.63</v>
+      </c>
+      <c r="K218" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>955</v>
+      </c>
+      <c r="D219" t="n">
+        <v>947.97</v>
+      </c>
+      <c r="E219" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="F219" t="n">
+        <v>964</v>
+      </c>
+      <c r="G219" t="n">
+        <v>947.97</v>
+      </c>
+      <c r="H219" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I219" t="n">
+        <v>897.1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>933.12</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-36.02</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2040.02</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-35.02</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2028.2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2040.02</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1997.2</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1953.72</v>
+      </c>
+      <c r="K220" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>3390.4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F221" t="n">
+        <v>3451.9</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="I221" t="n">
+        <v>3388.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3305.46</v>
+      </c>
+      <c r="K221" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1182.16</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1174.7</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1153.24</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2058.58</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-89.28</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1993.2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>2058.58</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-65.38</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1956.69</v>
+      </c>
+      <c r="K223" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>14025</v>
+      </c>
+      <c r="D224" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="E224" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="F224" t="n">
+        <v>14287</v>
+      </c>
+      <c r="G224" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="H224" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="I224" t="n">
+        <v>14025</v>
+      </c>
+      <c r="J224" t="n">
+        <v>13622.58</v>
+      </c>
+      <c r="K224" t="n">
+        <v>402.42</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="D225" t="n">
+        <v>288.11</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="F225" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="G225" t="n">
+        <v>288.11</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I225" t="n">
+        <v>281.65</v>
+      </c>
+      <c r="J225" t="n">
+        <v>275.07</v>
+      </c>
+      <c r="K225" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="D226" t="n">
+        <v>494.28</v>
+      </c>
+      <c r="E226" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="F226" t="n">
+        <v>530</v>
+      </c>
+      <c r="G226" t="n">
+        <v>512.17</v>
+      </c>
+      <c r="H226" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="I226" t="n">
+        <v>518.3</v>
+      </c>
+      <c r="J226" t="n">
+        <v>508.18</v>
+      </c>
+      <c r="K226" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>881.2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>895.84</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-14.64</v>
+      </c>
+      <c r="F227" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>895.84</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="I227" t="n">
+        <v>870.3</v>
+      </c>
+      <c r="J227" t="n">
+        <v>870.1799999999999</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -10901,7 +12461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11390,6 +12950,58 @@
       </c>
       <c r="N9" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1182.16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1174.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1153.24</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -11403,7 +13015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11892,6 +13504,58 @@
       </c>
       <c r="N9" t="n">
         <v>5.82</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>614</v>
+      </c>
+      <c r="D10" t="n">
+        <v>582.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>614</v>
+      </c>
+      <c r="G10" t="n">
+        <v>619.24</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>594.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>602.92</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>5.33</v>
       </c>
     </row>
   </sheetData>
@@ -12701,7 +14365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13190,6 +14854,58 @@
       </c>
       <c r="N9" t="n">
         <v>1.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1590.94</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1638.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1638.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1604.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1595.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -13203,7 +14919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13692,6 +15408,58 @@
       </c>
       <c r="N9" t="n">
         <v>6.09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>318</v>
+      </c>
+      <c r="D10" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>316.79</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>5.64</v>
       </c>
     </row>
   </sheetData>
@@ -13705,7 +15473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14194,6 +15962,58 @@
       </c>
       <c r="N9" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14287</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="H10" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14025</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13622.58</v>
+      </c>
+      <c r="K10" t="n">
+        <v>402.42</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -14207,7 +16027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14696,6 +16516,58 @@
       </c>
       <c r="N9" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-20.13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1821</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1799.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1760.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -14709,7 +16581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15146,6 +17018,58 @@
       </c>
       <c r="N8" t="n">
         <v>2.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5570</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5474.57</v>
+      </c>
+      <c r="E9" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5613</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5703.39</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-90.39</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5520</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5556.07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-36.07</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>
@@ -15159,7 +17083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15648,6 +17572,58 @@
       </c>
       <c r="N9" t="n">
         <v>3.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>117.32</v>
+      </c>
+      <c r="D10" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>118.06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I10" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="J10" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
@@ -15661,7 +17637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16098,6 +18074,58 @@
       </c>
       <c r="N8" t="n">
         <v>3.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3390.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3451.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3388.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3305.46</v>
+      </c>
+      <c r="K9" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2.99</v>
       </c>
     </row>
   </sheetData>
@@ -16111,7 +18139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16548,6 +18576,58 @@
       </c>
       <c r="N8" t="n">
         <v>6.51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>494.28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>530</v>
+      </c>
+      <c r="G9" t="n">
+        <v>512.17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="I9" t="n">
+        <v>518.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>508.18</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>6.11</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -10712,31 +10712,31 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>188.9</v>
+        <v>187.38</v>
       </c>
       <c r="D198" t="n">
         <v>190.94</v>
       </c>
       <c r="E198" t="n">
-        <v>-2.04</v>
+        <v>-3.56</v>
       </c>
       <c r="F198" t="n">
-        <v>190.15</v>
+        <v>189.34</v>
       </c>
       <c r="G198" t="n">
         <v>193.61</v>
       </c>
       <c r="H198" t="n">
-        <v>-3.46</v>
+        <v>-4.27</v>
       </c>
       <c r="I198" t="n">
-        <v>184.27</v>
+        <v>186.39</v>
       </c>
       <c r="J198" t="n">
         <v>188.62</v>
       </c>
       <c r="K198" t="n">
-        <v>-4.35</v>
+        <v>-2.23</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="199">
@@ -10764,31 +10764,31 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>177.1</v>
+        <v>171.64</v>
       </c>
       <c r="D199" t="n">
         <v>174.54</v>
       </c>
       <c r="E199" t="n">
-        <v>2.56</v>
+        <v>-2.9</v>
       </c>
       <c r="F199" t="n">
-        <v>179.1</v>
+        <v>179.5</v>
       </c>
       <c r="G199" t="n">
         <v>181.19</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.09</v>
+        <v>-1.69</v>
       </c>
       <c r="I199" t="n">
-        <v>171.98</v>
+        <v>169.75</v>
       </c>
       <c r="J199" t="n">
         <v>176.5</v>
       </c>
       <c r="K199" t="n">
-        <v>-4.52</v>
+        <v>-6.75</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="200">
@@ -10816,31 +10816,31 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>7660</v>
+        <v>7649</v>
       </c>
       <c r="D200" t="n">
         <v>7793.01</v>
       </c>
       <c r="E200" t="n">
-        <v>-133.01</v>
+        <v>-144.01</v>
       </c>
       <c r="F200" t="n">
-        <v>7760</v>
+        <v>7825</v>
       </c>
       <c r="G200" t="n">
         <v>7793.01</v>
       </c>
       <c r="H200" t="n">
-        <v>-33.01</v>
+        <v>31.99</v>
       </c>
       <c r="I200" t="n">
-        <v>7627</v>
+        <v>7639</v>
       </c>
       <c r="J200" t="n">
         <v>7557.5</v>
       </c>
       <c r="K200" t="n">
-        <v>69.5</v>
+        <v>81.5</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="201">
@@ -10868,31 +10868,31 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5745</v>
+        <v>5790</v>
       </c>
       <c r="D201" t="n">
         <v>5939.03</v>
       </c>
       <c r="E201" t="n">
-        <v>-194.03</v>
+        <v>-149.03</v>
       </c>
       <c r="F201" t="n">
-        <v>5811.5</v>
+        <v>5849</v>
       </c>
       <c r="G201" t="n">
         <v>5939.03</v>
       </c>
       <c r="H201" t="n">
-        <v>-127.53</v>
+        <v>-90.03</v>
       </c>
       <c r="I201" t="n">
-        <v>5740</v>
+        <v>5765</v>
       </c>
       <c r="J201" t="n">
         <v>5644.95</v>
       </c>
       <c r="K201" t="n">
-        <v>95.05</v>
+        <v>120.05</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>3.27</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="202">
@@ -10920,31 +10920,31 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1061.2</v>
+        <v>1067.7</v>
       </c>
       <c r="D202" t="n">
         <v>1065.06</v>
       </c>
       <c r="E202" t="n">
-        <v>-3.86</v>
+        <v>2.64</v>
       </c>
       <c r="F202" t="n">
-        <v>1068.8</v>
+        <v>1082</v>
       </c>
       <c r="G202" t="n">
         <v>1079.14</v>
       </c>
       <c r="H202" t="n">
-        <v>-10.34</v>
+        <v>2.86</v>
       </c>
       <c r="I202" t="n">
-        <v>1052.4</v>
+        <v>1065.1</v>
       </c>
       <c r="J202" t="n">
         <v>1051.01</v>
       </c>
       <c r="K202" t="n">
-        <v>1.39</v>
+        <v>14.09</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="203">
@@ -10972,31 +10972,31 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1049.9</v>
+        <v>1029.5</v>
       </c>
       <c r="D203" t="n">
         <v>1085.14</v>
       </c>
       <c r="E203" t="n">
-        <v>-35.24</v>
+        <v>-55.64</v>
       </c>
       <c r="F203" t="n">
-        <v>1060</v>
+        <v>1036.8</v>
       </c>
       <c r="G203" t="n">
         <v>1085.14</v>
       </c>
       <c r="H203" t="n">
-        <v>-25.14</v>
+        <v>-48.34</v>
       </c>
       <c r="I203" t="n">
-        <v>1032.7</v>
+        <v>1021.35</v>
       </c>
       <c r="J203" t="n">
         <v>1045.02</v>
       </c>
       <c r="K203" t="n">
-        <v>-12.32</v>
+        <v>-23.67</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -11005,11 +11005,11 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>3.25</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="204">
@@ -11024,31 +11024,31 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="D204" t="n">
         <v>5474.57</v>
       </c>
       <c r="E204" t="n">
-        <v>95.43000000000001</v>
+        <v>105.43</v>
       </c>
       <c r="F204" t="n">
-        <v>5613</v>
+        <v>5618.5</v>
       </c>
       <c r="G204" t="n">
         <v>5703.39</v>
       </c>
       <c r="H204" t="n">
-        <v>-90.39</v>
+        <v>-84.89</v>
       </c>
       <c r="I204" t="n">
-        <v>5520</v>
+        <v>5447</v>
       </c>
       <c r="J204" t="n">
         <v>5556.07</v>
       </c>
       <c r="K204" t="n">
-        <v>-36.07</v>
+        <v>-109.07</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="205">
@@ -11076,31 +11076,31 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1269.9</v>
+        <v>1240</v>
       </c>
       <c r="D205" t="n">
         <v>1259.16</v>
       </c>
       <c r="E205" t="n">
-        <v>10.74</v>
+        <v>-19.16</v>
       </c>
       <c r="F205" t="n">
-        <v>1272</v>
+        <v>1246.9</v>
       </c>
       <c r="G205" t="n">
         <v>1263.84</v>
       </c>
       <c r="H205" t="n">
-        <v>8.16</v>
+        <v>-16.94</v>
       </c>
       <c r="I205" t="n">
-        <v>1235.9</v>
+        <v>1230.1</v>
       </c>
       <c r="J205" t="n">
         <v>1237.57</v>
       </c>
       <c r="K205" t="n">
-        <v>-1.67</v>
+        <v>-7.47</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="206">
@@ -11128,31 +11128,31 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>117.32</v>
+        <v>118</v>
       </c>
       <c r="D206" t="n">
         <v>122.33</v>
       </c>
       <c r="E206" t="n">
-        <v>-5.01</v>
+        <v>-4.33</v>
       </c>
       <c r="F206" t="n">
-        <v>118.06</v>
+        <v>118.9</v>
       </c>
       <c r="G206" t="n">
         <v>122.33</v>
       </c>
       <c r="H206" t="n">
-        <v>-4.27</v>
+        <v>-3.43</v>
       </c>
       <c r="I206" t="n">
-        <v>115.32</v>
+        <v>117.4</v>
       </c>
       <c r="J206" t="n">
         <v>115.36</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.04</v>
+        <v>2.04</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="207">
@@ -11180,31 +11180,31 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>387.55</v>
+        <v>376</v>
       </c>
       <c r="D207" t="n">
         <v>414.13</v>
       </c>
       <c r="E207" t="n">
-        <v>-26.58</v>
+        <v>-38.13</v>
       </c>
       <c r="F207" t="n">
-        <v>391.5</v>
+        <v>384.95</v>
       </c>
       <c r="G207" t="n">
         <v>414.13</v>
       </c>
       <c r="H207" t="n">
-        <v>-22.63</v>
+        <v>-29.18</v>
       </c>
       <c r="I207" t="n">
-        <v>376.5</v>
+        <v>375</v>
       </c>
       <c r="J207" t="n">
         <v>373.35</v>
       </c>
       <c r="K207" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>6.42</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -11232,31 +11232,31 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1355.8</v>
+        <v>1343</v>
       </c>
       <c r="D208" t="n">
         <v>1340.33</v>
       </c>
       <c r="E208" t="n">
-        <v>15.47</v>
+        <v>2.67</v>
       </c>
       <c r="F208" t="n">
-        <v>1374</v>
+        <v>1367.1</v>
       </c>
       <c r="G208" t="n">
         <v>1351.8</v>
       </c>
       <c r="H208" t="n">
-        <v>22.2</v>
+        <v>15.3</v>
       </c>
       <c r="I208" t="n">
-        <v>1340.7</v>
+        <v>1337</v>
       </c>
       <c r="J208" t="n">
         <v>1315.63</v>
       </c>
       <c r="K208" t="n">
-        <v>25.07</v>
+        <v>21.37</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="209">
@@ -11284,31 +11284,31 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>11789</v>
+        <v>11828</v>
       </c>
       <c r="D209" t="n">
         <v>12122.16</v>
       </c>
       <c r="E209" t="n">
-        <v>-333.16</v>
+        <v>-294.16</v>
       </c>
       <c r="F209" t="n">
-        <v>11920</v>
+        <v>11850</v>
       </c>
       <c r="G209" t="n">
         <v>12122.16</v>
       </c>
       <c r="H209" t="n">
-        <v>-202.16</v>
+        <v>-272.16</v>
       </c>
       <c r="I209" t="n">
-        <v>11742</v>
+        <v>11318</v>
       </c>
       <c r="J209" t="n">
         <v>11614.72</v>
       </c>
       <c r="K209" t="n">
-        <v>127.28</v>
+        <v>-296.72</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="210">
@@ -11336,31 +11336,31 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4086.7</v>
+        <v>4057</v>
       </c>
       <c r="D210" t="n">
         <v>4066.74</v>
       </c>
       <c r="E210" t="n">
-        <v>19.96</v>
+        <v>-9.74</v>
       </c>
       <c r="F210" t="n">
-        <v>4086.7</v>
+        <v>4072.5</v>
       </c>
       <c r="G210" t="n">
         <v>4131.85</v>
       </c>
       <c r="H210" t="n">
-        <v>-45.15</v>
+        <v>-59.35</v>
       </c>
       <c r="I210" t="n">
-        <v>4026</v>
+        <v>4033.1</v>
       </c>
       <c r="J210" t="n">
         <v>4025.37</v>
       </c>
       <c r="K210" t="n">
-        <v>0.63</v>
+        <v>7.73</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="211">
@@ -11388,31 +11388,31 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D211" t="n">
         <v>582.91</v>
       </c>
       <c r="E211" t="n">
-        <v>31.09</v>
+        <v>18.09</v>
       </c>
       <c r="F211" t="n">
-        <v>614</v>
+        <v>615.9</v>
       </c>
       <c r="G211" t="n">
         <v>619.24</v>
       </c>
       <c r="H211" t="n">
-        <v>-5.24</v>
+        <v>-3.34</v>
       </c>
       <c r="I211" t="n">
-        <v>594.25</v>
+        <v>599.5</v>
       </c>
       <c r="J211" t="n">
         <v>602.92</v>
       </c>
       <c r="K211" t="n">
-        <v>-8.67</v>
+        <v>-3.42</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>5.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="212">
@@ -11440,31 +11440,31 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>318</v>
+        <v>318.5</v>
       </c>
       <c r="D212" t="n">
         <v>301.01</v>
       </c>
       <c r="E212" t="n">
-        <v>16.99</v>
+        <v>17.49</v>
       </c>
       <c r="F212" t="n">
-        <v>321.9</v>
+        <v>325</v>
       </c>
       <c r="G212" t="n">
         <v>325.2</v>
       </c>
       <c r="H212" t="n">
-        <v>-3.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I212" t="n">
-        <v>316.2</v>
+        <v>316.8</v>
       </c>
       <c r="J212" t="n">
         <v>316.79</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.59</v>
+        <v>0.01</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>5.64</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="213">
@@ -11492,31 +11492,31 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>5275.5</v>
+        <v>5310</v>
       </c>
       <c r="D213" t="n">
         <v>5309.72</v>
       </c>
       <c r="E213" t="n">
-        <v>-34.22</v>
+        <v>0.28</v>
       </c>
       <c r="F213" t="n">
-        <v>5332.5</v>
+        <v>5370</v>
       </c>
       <c r="G213" t="n">
         <v>5386.06</v>
       </c>
       <c r="H213" t="n">
-        <v>-53.56</v>
+        <v>-16.06</v>
       </c>
       <c r="I213" t="n">
-        <v>5262.5</v>
+        <v>5310</v>
       </c>
       <c r="J213" t="n">
         <v>5246.39</v>
       </c>
       <c r="K213" t="n">
-        <v>16.11</v>
+        <v>63.61</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="214">
@@ -11544,31 +11544,31 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="D214" t="n">
         <v>1826.13</v>
       </c>
       <c r="E214" t="n">
-        <v>-20.13</v>
+        <v>-14.13</v>
       </c>
       <c r="F214" t="n">
-        <v>1821</v>
+        <v>1836.4</v>
       </c>
       <c r="G214" t="n">
         <v>1826.13</v>
       </c>
       <c r="H214" t="n">
-        <v>-5.13</v>
+        <v>10.27</v>
       </c>
       <c r="I214" t="n">
-        <v>1799.6</v>
+        <v>1804.2</v>
       </c>
       <c r="J214" t="n">
         <v>1760.55</v>
       </c>
       <c r="K214" t="n">
-        <v>39.05</v>
+        <v>43.65</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="215">
@@ -11596,31 +11596,31 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>11379</v>
+        <v>11475</v>
       </c>
       <c r="D215" t="n">
         <v>11440.67</v>
       </c>
       <c r="E215" t="n">
-        <v>-61.67</v>
+        <v>34.33</v>
       </c>
       <c r="F215" t="n">
-        <v>11574</v>
+        <v>11541</v>
       </c>
       <c r="G215" t="n">
         <v>11488.9</v>
       </c>
       <c r="H215" t="n">
-        <v>85.09999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="I215" t="n">
-        <v>11306</v>
+        <v>11387</v>
       </c>
       <c r="J215" t="n">
         <v>11186.56</v>
       </c>
       <c r="K215" t="n">
-        <v>119.44</v>
+        <v>200.44</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="216">
@@ -11648,31 +11648,31 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1610</v>
+        <v>1632.8</v>
       </c>
       <c r="D216" t="n">
         <v>1590.94</v>
       </c>
       <c r="E216" t="n">
-        <v>19.06</v>
+        <v>41.86</v>
       </c>
       <c r="F216" t="n">
-        <v>1638.9</v>
+        <v>1652</v>
       </c>
       <c r="G216" t="n">
         <v>1638.15</v>
       </c>
       <c r="H216" t="n">
-        <v>0.75</v>
+        <v>13.85</v>
       </c>
       <c r="I216" t="n">
-        <v>1604.2</v>
+        <v>1614.4</v>
       </c>
       <c r="J216" t="n">
         <v>1595.48</v>
       </c>
       <c r="K216" t="n">
-        <v>8.720000000000001</v>
+        <v>18.92</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1.2</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="217">
@@ -11700,31 +11700,31 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2081.3</v>
+        <v>2083.3</v>
       </c>
       <c r="D217" t="n">
         <v>2065.98</v>
       </c>
       <c r="E217" t="n">
-        <v>15.32</v>
+        <v>17.32</v>
       </c>
       <c r="F217" t="n">
-        <v>2110.9</v>
+        <v>2099</v>
       </c>
       <c r="G217" t="n">
         <v>2081.91</v>
       </c>
       <c r="H217" t="n">
-        <v>28.99</v>
+        <v>17.09</v>
       </c>
       <c r="I217" t="n">
-        <v>2072.4</v>
+        <v>2037</v>
       </c>
       <c r="J217" t="n">
         <v>2026.46</v>
       </c>
       <c r="K217" t="n">
-        <v>45.94</v>
+        <v>10.54</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="218">
@@ -11752,31 +11752,31 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2190</v>
+        <v>2199</v>
       </c>
       <c r="D218" t="n">
         <v>2190.76</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.76</v>
+        <v>8.24</v>
       </c>
       <c r="F218" t="n">
-        <v>2209.6</v>
+        <v>2255</v>
       </c>
       <c r="G218" t="n">
         <v>2190.76</v>
       </c>
       <c r="H218" t="n">
-        <v>18.84</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>2172.4</v>
+        <v>2191.6</v>
       </c>
       <c r="J218" t="n">
         <v>2128.63</v>
       </c>
       <c r="K218" t="n">
-        <v>43.77</v>
+        <v>62.97</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="219">
@@ -11804,31 +11804,31 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>955</v>
+        <v>903.7</v>
       </c>
       <c r="D219" t="n">
         <v>947.97</v>
       </c>
       <c r="E219" t="n">
-        <v>7.03</v>
+        <v>-44.27</v>
       </c>
       <c r="F219" t="n">
-        <v>964</v>
+        <v>905.95</v>
       </c>
       <c r="G219" t="n">
         <v>947.97</v>
       </c>
       <c r="H219" t="n">
-        <v>16.03</v>
+        <v>-42.02</v>
       </c>
       <c r="I219" t="n">
-        <v>897.1</v>
+        <v>890</v>
       </c>
       <c r="J219" t="n">
         <v>933.12</v>
       </c>
       <c r="K219" t="n">
-        <v>-36.02</v>
+        <v>-43.12</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -11837,11 +11837,11 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0.74</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="220">
@@ -11856,31 +11856,31 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2005</v>
+        <v>2008.3</v>
       </c>
       <c r="D220" t="n">
         <v>2040.02</v>
       </c>
       <c r="E220" t="n">
-        <v>-35.02</v>
+        <v>-31.72</v>
       </c>
       <c r="F220" t="n">
-        <v>2028.2</v>
+        <v>2033.6</v>
       </c>
       <c r="G220" t="n">
         <v>2040.02</v>
       </c>
       <c r="H220" t="n">
-        <v>-11.82</v>
+        <v>-6.42</v>
       </c>
       <c r="I220" t="n">
-        <v>1997.2</v>
+        <v>2006.6</v>
       </c>
       <c r="J220" t="n">
         <v>1953.72</v>
       </c>
       <c r="K220" t="n">
-        <v>43.48</v>
+        <v>52.88</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="221">
@@ -11908,31 +11908,31 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3390.4</v>
+        <v>3428.3</v>
       </c>
       <c r="D221" t="n">
         <v>3292.1</v>
       </c>
       <c r="E221" t="n">
-        <v>98.3</v>
+        <v>136.2</v>
       </c>
       <c r="F221" t="n">
-        <v>3451.9</v>
+        <v>3430</v>
       </c>
       <c r="G221" t="n">
         <v>3292.1</v>
       </c>
       <c r="H221" t="n">
-        <v>159.8</v>
+        <v>137.9</v>
       </c>
       <c r="I221" t="n">
-        <v>3388.3</v>
+        <v>3378.3</v>
       </c>
       <c r="J221" t="n">
         <v>3305.46</v>
       </c>
       <c r="K221" t="n">
-        <v>82.84</v>
+        <v>72.84</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="222">
@@ -11960,31 +11960,31 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="D222" t="n">
         <v>1182.16</v>
       </c>
       <c r="E222" t="n">
-        <v>-9.16</v>
+        <v>-2.16</v>
       </c>
       <c r="F222" t="n">
-        <v>1174.7</v>
+        <v>1191.5</v>
       </c>
       <c r="G222" t="n">
         <v>1184.4</v>
       </c>
       <c r="H222" t="n">
-        <v>-9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I222" t="n">
-        <v>1150.5</v>
+        <v>1167</v>
       </c>
       <c r="J222" t="n">
         <v>1153.24</v>
       </c>
       <c r="K222" t="n">
-        <v>-2.74</v>
+        <v>13.76</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0.77</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="223">
@@ -12012,31 +12012,31 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1969.3</v>
+        <v>1992.1</v>
       </c>
       <c r="D223" t="n">
         <v>2058.58</v>
       </c>
       <c r="E223" t="n">
-        <v>-89.28</v>
+        <v>-66.48</v>
       </c>
       <c r="F223" t="n">
-        <v>1993.2</v>
+        <v>2005.8</v>
       </c>
       <c r="G223" t="n">
         <v>2058.58</v>
       </c>
       <c r="H223" t="n">
-        <v>-65.38</v>
+        <v>-52.78</v>
       </c>
       <c r="I223" t="n">
-        <v>1969.3</v>
+        <v>1932</v>
       </c>
       <c r="J223" t="n">
         <v>1956.69</v>
       </c>
       <c r="K223" t="n">
-        <v>12.61</v>
+        <v>-24.69</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>4.34</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="224">
@@ -12064,31 +12064,31 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>14025</v>
+        <v>14130</v>
       </c>
       <c r="D224" t="n">
         <v>13901.39</v>
       </c>
       <c r="E224" t="n">
-        <v>123.61</v>
+        <v>228.61</v>
       </c>
       <c r="F224" t="n">
-        <v>14287</v>
+        <v>14209</v>
       </c>
       <c r="G224" t="n">
         <v>13901.39</v>
       </c>
       <c r="H224" t="n">
-        <v>385.61</v>
+        <v>307.61</v>
       </c>
       <c r="I224" t="n">
-        <v>14025</v>
+        <v>13999</v>
       </c>
       <c r="J224" t="n">
         <v>13622.58</v>
       </c>
       <c r="K224" t="n">
-        <v>402.42</v>
+        <v>376.42</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>0.89</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="225">
@@ -12116,31 +12116,31 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>281.8</v>
+        <v>282.6</v>
       </c>
       <c r="D225" t="n">
         <v>288.11</v>
       </c>
       <c r="E225" t="n">
-        <v>-6.31</v>
+        <v>-5.51</v>
       </c>
       <c r="F225" t="n">
-        <v>286.4</v>
+        <v>283.5</v>
       </c>
       <c r="G225" t="n">
         <v>288.11</v>
       </c>
       <c r="H225" t="n">
-        <v>-1.71</v>
+        <v>-4.61</v>
       </c>
       <c r="I225" t="n">
-        <v>281.65</v>
+        <v>277.15</v>
       </c>
       <c r="J225" t="n">
         <v>275.07</v>
       </c>
       <c r="K225" t="n">
-        <v>6.58</v>
+        <v>2.08</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="226">
@@ -12168,31 +12168,31 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>524.5</v>
+        <v>527</v>
       </c>
       <c r="D226" t="n">
         <v>494.28</v>
       </c>
       <c r="E226" t="n">
-        <v>30.22</v>
+        <v>32.72</v>
       </c>
       <c r="F226" t="n">
-        <v>530</v>
+        <v>543.7</v>
       </c>
       <c r="G226" t="n">
         <v>512.17</v>
       </c>
       <c r="H226" t="n">
-        <v>17.83</v>
+        <v>31.53</v>
       </c>
       <c r="I226" t="n">
-        <v>518.3</v>
+        <v>527</v>
       </c>
       <c r="J226" t="n">
         <v>508.18</v>
       </c>
       <c r="K226" t="n">
-        <v>10.12</v>
+        <v>18.82</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>6.11</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="227">
@@ -12220,31 +12220,31 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>881.2</v>
+        <v>894.95</v>
       </c>
       <c r="D227" t="n">
         <v>895.84</v>
       </c>
       <c r="E227" t="n">
-        <v>-14.64</v>
+        <v>-0.89</v>
       </c>
       <c r="F227" t="n">
-        <v>891.8</v>
+        <v>902.8</v>
       </c>
       <c r="G227" t="n">
         <v>895.84</v>
       </c>
       <c r="H227" t="n">
-        <v>-4.04</v>
+        <v>6.96</v>
       </c>
       <c r="I227" t="n">
-        <v>870.3</v>
+        <v>885.3</v>
       </c>
       <c r="J227" t="n">
         <v>870.1799999999999</v>
       </c>
       <c r="K227" t="n">
-        <v>0.12</v>
+        <v>15.12</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1.63</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -12964,31 +12964,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="D10" t="n">
         <v>1182.16</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.16</v>
+        <v>-2.16</v>
       </c>
       <c r="F10" t="n">
-        <v>1174.7</v>
+        <v>1191.5</v>
       </c>
       <c r="G10" t="n">
         <v>1184.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1150.5</v>
+        <v>1167</v>
       </c>
       <c r="J10" t="n">
         <v>1153.24</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.74</v>
+        <v>13.76</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.77</v>
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -13518,31 +13518,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D10" t="n">
         <v>582.91</v>
       </c>
       <c r="E10" t="n">
-        <v>31.09</v>
+        <v>18.09</v>
       </c>
       <c r="F10" t="n">
-        <v>614</v>
+        <v>615.9</v>
       </c>
       <c r="G10" t="n">
         <v>619.24</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.24</v>
+        <v>-3.34</v>
       </c>
       <c r="I10" t="n">
-        <v>594.25</v>
+        <v>599.5</v>
       </c>
       <c r="J10" t="n">
         <v>602.92</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.67</v>
+        <v>-3.42</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.33</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -14868,31 +14868,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1610</v>
+        <v>1632.8</v>
       </c>
       <c r="D10" t="n">
         <v>1590.94</v>
       </c>
       <c r="E10" t="n">
-        <v>19.06</v>
+        <v>41.86</v>
       </c>
       <c r="F10" t="n">
-        <v>1638.9</v>
+        <v>1652</v>
       </c>
       <c r="G10" t="n">
         <v>1638.15</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>13.85</v>
       </c>
       <c r="I10" t="n">
-        <v>1604.2</v>
+        <v>1614.4</v>
       </c>
       <c r="J10" t="n">
         <v>1595.48</v>
       </c>
       <c r="K10" t="n">
-        <v>8.720000000000001</v>
+        <v>18.92</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>2.63</v>
       </c>
     </row>
   </sheetData>
@@ -15422,31 +15422,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>318.5</v>
       </c>
       <c r="D10" t="n">
         <v>301.01</v>
       </c>
       <c r="E10" t="n">
-        <v>16.99</v>
+        <v>17.49</v>
       </c>
       <c r="F10" t="n">
-        <v>321.9</v>
+        <v>325</v>
       </c>
       <c r="G10" t="n">
         <v>325.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>316.2</v>
+        <v>316.8</v>
       </c>
       <c r="J10" t="n">
         <v>316.79</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.59</v>
+        <v>0.01</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.64</v>
+        <v>5.81</v>
       </c>
     </row>
   </sheetData>
@@ -15976,31 +15976,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14025</v>
+        <v>14130</v>
       </c>
       <c r="D10" t="n">
         <v>13901.39</v>
       </c>
       <c r="E10" t="n">
-        <v>123.61</v>
+        <v>228.61</v>
       </c>
       <c r="F10" t="n">
-        <v>14287</v>
+        <v>14209</v>
       </c>
       <c r="G10" t="n">
         <v>13901.39</v>
       </c>
       <c r="H10" t="n">
-        <v>385.61</v>
+        <v>307.61</v>
       </c>
       <c r="I10" t="n">
-        <v>14025</v>
+        <v>13999</v>
       </c>
       <c r="J10" t="n">
         <v>13622.58</v>
       </c>
       <c r="K10" t="n">
-        <v>402.42</v>
+        <v>376.42</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.89</v>
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -16530,31 +16530,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="D10" t="n">
         <v>1826.13</v>
       </c>
       <c r="E10" t="n">
-        <v>-20.13</v>
+        <v>-14.13</v>
       </c>
       <c r="F10" t="n">
-        <v>1821</v>
+        <v>1836.4</v>
       </c>
       <c r="G10" t="n">
         <v>1826.13</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.13</v>
+        <v>10.27</v>
       </c>
       <c r="I10" t="n">
-        <v>1799.6</v>
+        <v>1804.2</v>
       </c>
       <c r="J10" t="n">
         <v>1760.55</v>
       </c>
       <c r="K10" t="n">
-        <v>39.05</v>
+        <v>43.65</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -17032,31 +17032,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="D9" t="n">
         <v>5474.57</v>
       </c>
       <c r="E9" t="n">
-        <v>95.43000000000001</v>
+        <v>105.43</v>
       </c>
       <c r="F9" t="n">
-        <v>5613</v>
+        <v>5618.5</v>
       </c>
       <c r="G9" t="n">
         <v>5703.39</v>
       </c>
       <c r="H9" t="n">
-        <v>-90.39</v>
+        <v>-84.89</v>
       </c>
       <c r="I9" t="n">
-        <v>5520</v>
+        <v>5447</v>
       </c>
       <c r="J9" t="n">
         <v>5556.07</v>
       </c>
       <c r="K9" t="n">
-        <v>-36.07</v>
+        <v>-109.07</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
@@ -17586,31 +17586,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>117.32</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
         <v>122.33</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.01</v>
+        <v>-4.33</v>
       </c>
       <c r="F10" t="n">
-        <v>118.06</v>
+        <v>118.9</v>
       </c>
       <c r="G10" t="n">
         <v>122.33</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.27</v>
+        <v>-3.43</v>
       </c>
       <c r="I10" t="n">
-        <v>115.32</v>
+        <v>117.4</v>
       </c>
       <c r="J10" t="n">
         <v>115.36</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04</v>
+        <v>2.04</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
     </row>
   </sheetData>
@@ -18088,31 +18088,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3390.4</v>
+        <v>3428.3</v>
       </c>
       <c r="D9" t="n">
         <v>3292.1</v>
       </c>
       <c r="E9" t="n">
-        <v>98.3</v>
+        <v>136.2</v>
       </c>
       <c r="F9" t="n">
-        <v>3451.9</v>
+        <v>3430</v>
       </c>
       <c r="G9" t="n">
         <v>3292.1</v>
       </c>
       <c r="H9" t="n">
-        <v>159.8</v>
+        <v>137.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3388.3</v>
+        <v>3378.3</v>
       </c>
       <c r="J9" t="n">
         <v>3305.46</v>
       </c>
       <c r="K9" t="n">
-        <v>82.84</v>
+        <v>72.84</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
   </sheetData>
@@ -18590,31 +18590,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>524.5</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
         <v>494.28</v>
       </c>
       <c r="E9" t="n">
-        <v>30.22</v>
+        <v>32.72</v>
       </c>
       <c r="F9" t="n">
-        <v>530</v>
+        <v>543.7</v>
       </c>
       <c r="G9" t="n">
         <v>512.17</v>
       </c>
       <c r="H9" t="n">
-        <v>17.83</v>
+        <v>31.53</v>
       </c>
       <c r="I9" t="n">
-        <v>518.3</v>
+        <v>527</v>
       </c>
       <c r="J9" t="n">
         <v>508.18</v>
       </c>
       <c r="K9" t="n">
-        <v>10.12</v>
+        <v>18.82</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.11</v>
+        <v>6.62</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12258,6 +12258,1358 @@
       </c>
       <c r="N227" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>5745.5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>5646.15</v>
+      </c>
+      <c r="E228" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="F228" t="n">
+        <v>5778</v>
+      </c>
+      <c r="G228" t="n">
+        <v>5719.7</v>
+      </c>
+      <c r="H228" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="I228" t="n">
+        <v>5694.5</v>
+      </c>
+      <c r="J228" t="n">
+        <v>5601.44</v>
+      </c>
+      <c r="K228" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2115</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2149.79</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-34.79</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2149.79</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-27.79</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2075.1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2098.65</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-23.55</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1064.05</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1064.71</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1042.38</v>
+      </c>
+      <c r="K230" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1263.65</v>
+      </c>
+      <c r="E231" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1281.2</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1281.43</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1263</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1254.36</v>
+      </c>
+      <c r="K231" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1934.2</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1886.72</v>
+      </c>
+      <c r="E232" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1959.7</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1967.12</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1923.2</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1926.27</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>3421.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-170.05</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3435</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-156.55</v>
+      </c>
+      <c r="I233" t="n">
+        <v>3390.2</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3340.95</v>
+      </c>
+      <c r="K233" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>388</v>
+      </c>
+      <c r="D234" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="E234" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="F234" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G234" t="n">
+        <v>383.58</v>
+      </c>
+      <c r="H234" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I234" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="J234" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="K234" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-21.54</v>
+      </c>
+      <c r="F235" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G235" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I235" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="J235" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D236" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F236" t="n">
+        <v>117.99</v>
+      </c>
+      <c r="G236" t="n">
+        <v>118.51</v>
+      </c>
+      <c r="H236" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I236" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J236" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1795</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="H237" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1762.2</v>
+      </c>
+      <c r="J237" t="n">
+        <v>1727.77</v>
+      </c>
+      <c r="K237" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>14150</v>
+      </c>
+      <c r="D238" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-347.83</v>
+      </c>
+      <c r="F238" t="n">
+        <v>14420</v>
+      </c>
+      <c r="G238" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="H238" t="n">
+        <v>-77.83</v>
+      </c>
+      <c r="I238" t="n">
+        <v>14066</v>
+      </c>
+      <c r="J238" t="n">
+        <v>13762.25</v>
+      </c>
+      <c r="K238" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1368.46</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-13.56</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1368.8</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1368.46</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1331.1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1320.97</v>
+      </c>
+      <c r="K239" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1592</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-55.33</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1608</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="H240" t="n">
+        <v>-39.33</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1579.9</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1588.49</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="D241" t="n">
+        <v>174.81</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F241" t="n">
+        <v>177.59</v>
+      </c>
+      <c r="G241" t="n">
+        <v>178.96</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I241" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="J241" t="n">
+        <v>175.22</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2186</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2211.78</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-25.78</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2221.9</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2211.78</v>
+      </c>
+      <c r="H242" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="I242" t="n">
+        <v>2179</v>
+      </c>
+      <c r="J242" t="n">
+        <v>2126.27</v>
+      </c>
+      <c r="K242" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2011.2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1995.77</v>
+      </c>
+      <c r="E243" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="F243" t="n">
+        <v>2018.8</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1995.77</v>
+      </c>
+      <c r="H243" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I243" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1962.36</v>
+      </c>
+      <c r="K243" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>11254</v>
+      </c>
+      <c r="D244" t="n">
+        <v>11378.06</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-124.06</v>
+      </c>
+      <c r="F244" t="n">
+        <v>11435</v>
+      </c>
+      <c r="G244" t="n">
+        <v>11442.61</v>
+      </c>
+      <c r="H244" t="n">
+        <v>-7.61</v>
+      </c>
+      <c r="I244" t="n">
+        <v>11211</v>
+      </c>
+      <c r="J244" t="n">
+        <v>11204.88</v>
+      </c>
+      <c r="K244" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>4064.3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>4086.98</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-22.68</v>
+      </c>
+      <c r="F245" t="n">
+        <v>4085</v>
+      </c>
+      <c r="G245" t="n">
+        <v>4086.98</v>
+      </c>
+      <c r="H245" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="I245" t="n">
+        <v>4050</v>
+      </c>
+      <c r="J245" t="n">
+        <v>4006.69</v>
+      </c>
+      <c r="K245" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>283.02</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F246" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="G246" t="n">
+        <v>286.47</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I246" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="J246" t="n">
+        <v>280.36</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>7546</v>
+      </c>
+      <c r="D247" t="n">
+        <v>7465.8</v>
+      </c>
+      <c r="E247" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F247" t="n">
+        <v>7734</v>
+      </c>
+      <c r="G247" t="n">
+        <v>7656.55</v>
+      </c>
+      <c r="H247" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="I247" t="n">
+        <v>7528.5</v>
+      </c>
+      <c r="J247" t="n">
+        <v>7496.93</v>
+      </c>
+      <c r="K247" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>183.49</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F248" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="G248" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="I248" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="J248" t="n">
+        <v>183.15</v>
+      </c>
+      <c r="K248" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1041.6</v>
+      </c>
+      <c r="D249" t="n">
+        <v>996.48</v>
+      </c>
+      <c r="E249" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1050.6</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1061.43</v>
+      </c>
+      <c r="H249" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="I249" t="n">
+        <v>1038</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1039.46</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1163.6</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="H250" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1154</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1141.13</v>
+      </c>
+      <c r="K250" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>875</v>
+      </c>
+      <c r="D251" t="n">
+        <v>881.13</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="F251" t="n">
+        <v>887</v>
+      </c>
+      <c r="G251" t="n">
+        <v>881.67</v>
+      </c>
+      <c r="H251" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I251" t="n">
+        <v>874</v>
+      </c>
+      <c r="J251" t="n">
+        <v>863.08</v>
+      </c>
+      <c r="K251" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="D252" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="E252" t="n">
+        <v>-38.73</v>
+      </c>
+      <c r="F252" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="G252" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="H252" t="n">
+        <v>-32.13</v>
+      </c>
+      <c r="I252" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="J252" t="n">
+        <v>506.25</v>
+      </c>
+      <c r="K252" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>938</v>
+      </c>
+      <c r="D253" t="n">
+        <v>901.35</v>
+      </c>
+      <c r="E253" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="F253" t="n">
+        <v>961.35</v>
+      </c>
+      <c r="G253" t="n">
+        <v>901.35</v>
+      </c>
+      <c r="H253" t="n">
+        <v>60</v>
+      </c>
+      <c r="I253" t="n">
+        <v>933.1</v>
+      </c>
+      <c r="J253" t="n">
+        <v>913.21</v>
+      </c>
+      <c r="K253" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>
@@ -12461,7 +13813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13002,6 +14354,58 @@
       </c>
       <c r="N10" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1163.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1154</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1141.13</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -14365,7 +15769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14906,6 +16310,58 @@
       </c>
       <c r="N10" t="n">
         <v>2.63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1592</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-55.33</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1608</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-39.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1579.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1588.49</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
@@ -14919,7 +16375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15460,6 +16916,58 @@
       </c>
       <c r="N10" t="n">
         <v>5.81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-21.54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>6.38</v>
       </c>
     </row>
   </sheetData>
@@ -15473,7 +16981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16014,6 +17522,58 @@
       </c>
       <c r="N10" t="n">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14150</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-347.83</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14420</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-77.83</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14066</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13762.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -16027,7 +17587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16568,6 +18128,58 @@
       </c>
       <c r="N10" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1795</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1762.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1727.77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -17083,7 +18695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17624,6 +19236,58 @@
       </c>
       <c r="N10" t="n">
         <v>3.54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>117.99</v>
+      </c>
+      <c r="G11" t="n">
+        <v>118.51</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I11" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -17637,7 +19301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18126,6 +19790,58 @@
       </c>
       <c r="N9" t="n">
         <v>4.14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3421.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-170.05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3435</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-156.55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3390.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3340.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4.73</v>
       </c>
     </row>
   </sheetData>
@@ -18139,7 +19855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18628,6 +20344,58 @@
       </c>
       <c r="N9" t="n">
         <v>6.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-38.73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-32.13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>506.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>6.95</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -12272,31 +12272,31 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5745.5</v>
+        <v>5745</v>
       </c>
       <c r="D228" t="n">
         <v>5646.15</v>
       </c>
       <c r="E228" t="n">
-        <v>99.34999999999999</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F228" t="n">
-        <v>5778</v>
+        <v>5811.5</v>
       </c>
       <c r="G228" t="n">
         <v>5719.7</v>
       </c>
       <c r="H228" t="n">
-        <v>58.3</v>
+        <v>91.8</v>
       </c>
       <c r="I228" t="n">
-        <v>5694.5</v>
+        <v>5740</v>
       </c>
       <c r="J228" t="n">
         <v>5601.44</v>
       </c>
       <c r="K228" t="n">
-        <v>93.06</v>
+        <v>138.56</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="229">
@@ -12324,31 +12324,31 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2115</v>
+        <v>2081.3</v>
       </c>
       <c r="D229" t="n">
         <v>2149.79</v>
       </c>
       <c r="E229" t="n">
-        <v>-34.79</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="F229" t="n">
-        <v>2122</v>
+        <v>2110.9</v>
       </c>
       <c r="G229" t="n">
         <v>2149.79</v>
       </c>
       <c r="H229" t="n">
-        <v>-27.79</v>
+        <v>-38.89</v>
       </c>
       <c r="I229" t="n">
-        <v>2075.1</v>
+        <v>2072.4</v>
       </c>
       <c r="J229" t="n">
         <v>2098.65</v>
       </c>
       <c r="K229" t="n">
-        <v>-23.55</v>
+        <v>-26.25</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1.62</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="230">
@@ -12376,31 +12376,31 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1053</v>
+        <v>1061.2</v>
       </c>
       <c r="D230" t="n">
         <v>1064.05</v>
       </c>
       <c r="E230" t="n">
-        <v>-11.05</v>
+        <v>-2.85</v>
       </c>
       <c r="F230" t="n">
-        <v>1067.7</v>
+        <v>1068.8</v>
       </c>
       <c r="G230" t="n">
         <v>1064.71</v>
       </c>
       <c r="H230" t="n">
-        <v>2.99</v>
+        <v>4.09</v>
       </c>
       <c r="I230" t="n">
-        <v>1053</v>
+        <v>1052.4</v>
       </c>
       <c r="J230" t="n">
         <v>1042.38</v>
       </c>
       <c r="K230" t="n">
-        <v>10.62</v>
+        <v>10.02</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="231">
@@ -12428,31 +12428,31 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1273</v>
+        <v>1269.9</v>
       </c>
       <c r="D231" t="n">
         <v>1263.65</v>
       </c>
       <c r="E231" t="n">
-        <v>9.35</v>
+        <v>6.25</v>
       </c>
       <c r="F231" t="n">
-        <v>1281.2</v>
+        <v>1272</v>
       </c>
       <c r="G231" t="n">
         <v>1281.43</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.23</v>
+        <v>-9.43</v>
       </c>
       <c r="I231" t="n">
-        <v>1263</v>
+        <v>1235.9</v>
       </c>
       <c r="J231" t="n">
         <v>1254.36</v>
       </c>
       <c r="K231" t="n">
-        <v>8.640000000000001</v>
+        <v>-18.46</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="232">
@@ -12480,31 +12480,31 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1934.2</v>
+        <v>1969.3</v>
       </c>
       <c r="D232" t="n">
         <v>1886.72</v>
       </c>
       <c r="E232" t="n">
-        <v>47.48</v>
+        <v>82.58</v>
       </c>
       <c r="F232" t="n">
-        <v>1959.7</v>
+        <v>1993.2</v>
       </c>
       <c r="G232" t="n">
         <v>1967.12</v>
       </c>
       <c r="H232" t="n">
-        <v>-7.42</v>
+        <v>26.08</v>
       </c>
       <c r="I232" t="n">
-        <v>1923.2</v>
+        <v>1969.3</v>
       </c>
       <c r="J232" t="n">
         <v>1926.27</v>
       </c>
       <c r="K232" t="n">
-        <v>-3.07</v>
+        <v>43.03</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2.52</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="233">
@@ -12532,31 +12532,31 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3421.5</v>
+        <v>3390.4</v>
       </c>
       <c r="D233" t="n">
         <v>3591.55</v>
       </c>
       <c r="E233" t="n">
-        <v>-170.05</v>
+        <v>-201.15</v>
       </c>
       <c r="F233" t="n">
-        <v>3435</v>
+        <v>3451.9</v>
       </c>
       <c r="G233" t="n">
         <v>3591.55</v>
       </c>
       <c r="H233" t="n">
-        <v>-156.55</v>
+        <v>-139.65</v>
       </c>
       <c r="I233" t="n">
-        <v>3390.2</v>
+        <v>3388.3</v>
       </c>
       <c r="J233" t="n">
         <v>3340.95</v>
       </c>
       <c r="K233" t="n">
-        <v>49.25</v>
+        <v>47.35</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>4.73</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="234">
@@ -12584,31 +12584,31 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>388</v>
+        <v>387.55</v>
       </c>
       <c r="D234" t="n">
         <v>355.09</v>
       </c>
       <c r="E234" t="n">
-        <v>32.91</v>
+        <v>32.46</v>
       </c>
       <c r="F234" t="n">
-        <v>390.85</v>
+        <v>391.5</v>
       </c>
       <c r="G234" t="n">
         <v>383.58</v>
       </c>
       <c r="H234" t="n">
-        <v>7.27</v>
+        <v>7.92</v>
       </c>
       <c r="I234" t="n">
-        <v>385.8</v>
+        <v>376.5</v>
       </c>
       <c r="J234" t="n">
         <v>375.23</v>
       </c>
       <c r="K234" t="n">
-        <v>10.57</v>
+        <v>1.27</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -12636,31 +12636,31 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>315.9</v>
+        <v>318</v>
       </c>
       <c r="D235" t="n">
         <v>337.44</v>
       </c>
       <c r="E235" t="n">
-        <v>-21.54</v>
+        <v>-19.44</v>
       </c>
       <c r="F235" t="n">
-        <v>321.2</v>
+        <v>321.9</v>
       </c>
       <c r="G235" t="n">
         <v>337.44</v>
       </c>
       <c r="H235" t="n">
-        <v>-16.24</v>
+        <v>-15.54</v>
       </c>
       <c r="I235" t="n">
-        <v>315.55</v>
+        <v>316.2</v>
       </c>
       <c r="J235" t="n">
         <v>315.62</v>
       </c>
       <c r="K235" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>6.38</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="236">
@@ -12688,31 +12688,31 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>116.5</v>
+        <v>117.32</v>
       </c>
       <c r="D236" t="n">
         <v>113.3</v>
       </c>
       <c r="E236" t="n">
-        <v>3.2</v>
+        <v>4.02</v>
       </c>
       <c r="F236" t="n">
-        <v>117.99</v>
+        <v>118.06</v>
       </c>
       <c r="G236" t="n">
         <v>118.51</v>
       </c>
       <c r="H236" t="n">
-        <v>-0.52</v>
+        <v>-0.45</v>
       </c>
       <c r="I236" t="n">
-        <v>116.5</v>
+        <v>115.32</v>
       </c>
       <c r="J236" t="n">
         <v>116.24</v>
       </c>
       <c r="K236" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="237">
@@ -12740,31 +12740,31 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1773</v>
+        <v>1806</v>
       </c>
       <c r="D237" t="n">
         <v>1773.35</v>
       </c>
       <c r="E237" t="n">
-        <v>-0.35</v>
+        <v>32.65</v>
       </c>
       <c r="F237" t="n">
-        <v>1795</v>
+        <v>1821</v>
       </c>
       <c r="G237" t="n">
         <v>1773.35</v>
       </c>
       <c r="H237" t="n">
-        <v>21.65</v>
+        <v>47.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1762.2</v>
+        <v>1799.6</v>
       </c>
       <c r="J237" t="n">
         <v>1727.77</v>
       </c>
       <c r="K237" t="n">
-        <v>34.43</v>
+        <v>71.83</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0.02</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="238">
@@ -12792,31 +12792,31 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>14150</v>
+        <v>14025</v>
       </c>
       <c r="D238" t="n">
         <v>14497.83</v>
       </c>
       <c r="E238" t="n">
-        <v>-347.83</v>
+        <v>-472.83</v>
       </c>
       <c r="F238" t="n">
-        <v>14420</v>
+        <v>14287</v>
       </c>
       <c r="G238" t="n">
         <v>14497.83</v>
       </c>
       <c r="H238" t="n">
-        <v>-77.83</v>
+        <v>-210.83</v>
       </c>
       <c r="I238" t="n">
-        <v>14066</v>
+        <v>14025</v>
       </c>
       <c r="J238" t="n">
         <v>13762.25</v>
       </c>
       <c r="K238" t="n">
-        <v>303.75</v>
+        <v>262.75</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>2.4</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="239">
@@ -12844,31 +12844,31 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1354.9</v>
+        <v>1355.8</v>
       </c>
       <c r="D239" t="n">
         <v>1368.46</v>
       </c>
       <c r="E239" t="n">
-        <v>-13.56</v>
+        <v>-12.66</v>
       </c>
       <c r="F239" t="n">
-        <v>1368.8</v>
+        <v>1374</v>
       </c>
       <c r="G239" t="n">
         <v>1368.46</v>
       </c>
       <c r="H239" t="n">
-        <v>0.34</v>
+        <v>5.54</v>
       </c>
       <c r="I239" t="n">
-        <v>1331.1</v>
+        <v>1340.7</v>
       </c>
       <c r="J239" t="n">
         <v>1320.97</v>
       </c>
       <c r="K239" t="n">
-        <v>10.13</v>
+        <v>19.73</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="240">
@@ -12896,31 +12896,31 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1592</v>
+        <v>1610</v>
       </c>
       <c r="D240" t="n">
         <v>1647.33</v>
       </c>
       <c r="E240" t="n">
-        <v>-55.33</v>
+        <v>-37.33</v>
       </c>
       <c r="F240" t="n">
-        <v>1608</v>
+        <v>1638.9</v>
       </c>
       <c r="G240" t="n">
         <v>1647.33</v>
       </c>
       <c r="H240" t="n">
-        <v>-39.33</v>
+        <v>-8.43</v>
       </c>
       <c r="I240" t="n">
-        <v>1579.9</v>
+        <v>1604.2</v>
       </c>
       <c r="J240" t="n">
         <v>1588.49</v>
       </c>
       <c r="K240" t="n">
-        <v>-8.59</v>
+        <v>15.71</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>3.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="241">
@@ -12948,31 +12948,31 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>176.35</v>
+        <v>177.1</v>
       </c>
       <c r="D241" t="n">
         <v>174.81</v>
       </c>
       <c r="E241" t="n">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="F241" t="n">
-        <v>177.59</v>
+        <v>179.1</v>
       </c>
       <c r="G241" t="n">
         <v>178.96</v>
       </c>
       <c r="H241" t="n">
-        <v>-1.37</v>
+        <v>0.14</v>
       </c>
       <c r="I241" t="n">
-        <v>174.5</v>
+        <v>171.98</v>
       </c>
       <c r="J241" t="n">
         <v>175.22</v>
       </c>
       <c r="K241" t="n">
-        <v>-0.72</v>
+        <v>-3.24</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0.88</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="242">
@@ -13000,31 +13000,31 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="D242" t="n">
         <v>2211.78</v>
       </c>
       <c r="E242" t="n">
-        <v>-25.78</v>
+        <v>-21.78</v>
       </c>
       <c r="F242" t="n">
-        <v>2221.9</v>
+        <v>2209.6</v>
       </c>
       <c r="G242" t="n">
         <v>2211.78</v>
       </c>
       <c r="H242" t="n">
-        <v>10.12</v>
+        <v>-2.18</v>
       </c>
       <c r="I242" t="n">
-        <v>2179</v>
+        <v>2172.4</v>
       </c>
       <c r="J242" t="n">
         <v>2126.27</v>
       </c>
       <c r="K242" t="n">
-        <v>52.73</v>
+        <v>46.13</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="243">
@@ -13052,31 +13052,31 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2011.2</v>
+        <v>2005</v>
       </c>
       <c r="D243" t="n">
         <v>1995.77</v>
       </c>
       <c r="E243" t="n">
-        <v>15.43</v>
+        <v>9.23</v>
       </c>
       <c r="F243" t="n">
-        <v>2018.8</v>
+        <v>2028.2</v>
       </c>
       <c r="G243" t="n">
         <v>1995.77</v>
       </c>
       <c r="H243" t="n">
-        <v>23.03</v>
+        <v>32.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1998</v>
+        <v>1997.2</v>
       </c>
       <c r="J243" t="n">
         <v>1962.36</v>
       </c>
       <c r="K243" t="n">
-        <v>35.64</v>
+        <v>34.84</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="244">
@@ -13104,31 +13104,31 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>11254</v>
+        <v>11379</v>
       </c>
       <c r="D244" t="n">
         <v>11378.06</v>
       </c>
       <c r="E244" t="n">
-        <v>-124.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F244" t="n">
-        <v>11435</v>
+        <v>11574</v>
       </c>
       <c r="G244" t="n">
         <v>11442.61</v>
       </c>
       <c r="H244" t="n">
-        <v>-7.61</v>
+        <v>131.39</v>
       </c>
       <c r="I244" t="n">
-        <v>11211</v>
+        <v>11306</v>
       </c>
       <c r="J244" t="n">
         <v>11204.88</v>
       </c>
       <c r="K244" t="n">
-        <v>6.12</v>
+        <v>101.12</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1.09</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="245">
@@ -13156,31 +13156,31 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4064.3</v>
+        <v>4086.7</v>
       </c>
       <c r="D245" t="n">
         <v>4086.98</v>
       </c>
       <c r="E245" t="n">
-        <v>-22.68</v>
+        <v>-0.28</v>
       </c>
       <c r="F245" t="n">
-        <v>4085</v>
+        <v>4086.7</v>
       </c>
       <c r="G245" t="n">
         <v>4086.98</v>
       </c>
       <c r="H245" t="n">
-        <v>-1.98</v>
+        <v>-0.28</v>
       </c>
       <c r="I245" t="n">
-        <v>4050</v>
+        <v>4026</v>
       </c>
       <c r="J245" t="n">
         <v>4006.69</v>
       </c>
       <c r="K245" t="n">
-        <v>43.31</v>
+        <v>19.31</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.55</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="246">
@@ -13208,31 +13208,31 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>286.25</v>
+        <v>281.8</v>
       </c>
       <c r="D246" t="n">
         <v>283.02</v>
       </c>
       <c r="E246" t="n">
-        <v>3.23</v>
+        <v>-1.22</v>
       </c>
       <c r="F246" t="n">
-        <v>286.95</v>
+        <v>286.4</v>
       </c>
       <c r="G246" t="n">
         <v>286.47</v>
       </c>
       <c r="H246" t="n">
-        <v>0.48</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I246" t="n">
-        <v>281.8</v>
+        <v>281.65</v>
       </c>
       <c r="J246" t="n">
         <v>280.36</v>
       </c>
       <c r="K246" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="247">
@@ -13260,31 +13260,31 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>7546</v>
+        <v>7660</v>
       </c>
       <c r="D247" t="n">
         <v>7465.8</v>
       </c>
       <c r="E247" t="n">
-        <v>80.2</v>
+        <v>194.2</v>
       </c>
       <c r="F247" t="n">
-        <v>7734</v>
+        <v>7760</v>
       </c>
       <c r="G247" t="n">
         <v>7656.55</v>
       </c>
       <c r="H247" t="n">
-        <v>77.45</v>
+        <v>103.45</v>
       </c>
       <c r="I247" t="n">
-        <v>7528.5</v>
+        <v>7627</v>
       </c>
       <c r="J247" t="n">
         <v>7496.93</v>
       </c>
       <c r="K247" t="n">
-        <v>31.57</v>
+        <v>130.07</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>1.07</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="248">
@@ -13312,31 +13312,31 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>185.5</v>
+        <v>188.9</v>
       </c>
       <c r="D248" t="n">
         <v>183.49</v>
       </c>
       <c r="E248" t="n">
-        <v>2.01</v>
+        <v>5.41</v>
       </c>
       <c r="F248" t="n">
-        <v>190.58</v>
+        <v>190.15</v>
       </c>
       <c r="G248" t="n">
         <v>187.1</v>
       </c>
       <c r="H248" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="I248" t="n">
-        <v>185.5</v>
+        <v>184.27</v>
       </c>
       <c r="J248" t="n">
         <v>183.15</v>
       </c>
       <c r="K248" t="n">
-        <v>2.35</v>
+        <v>1.12</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1.1</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="249">
@@ -13364,31 +13364,31 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1041.6</v>
+        <v>1049.9</v>
       </c>
       <c r="D249" t="n">
         <v>996.48</v>
       </c>
       <c r="E249" t="n">
-        <v>45.12</v>
+        <v>53.42</v>
       </c>
       <c r="F249" t="n">
-        <v>1050.6</v>
+        <v>1060</v>
       </c>
       <c r="G249" t="n">
         <v>1061.43</v>
       </c>
       <c r="H249" t="n">
-        <v>-10.83</v>
+        <v>-1.43</v>
       </c>
       <c r="I249" t="n">
-        <v>1038</v>
+        <v>1032.7</v>
       </c>
       <c r="J249" t="n">
         <v>1039.46</v>
       </c>
       <c r="K249" t="n">
-        <v>-1.46</v>
+        <v>-6.76</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>4.53</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="250">
@@ -13416,31 +13416,31 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1163.6</v>
+        <v>1173</v>
       </c>
       <c r="D250" t="n">
         <v>1170.76</v>
       </c>
       <c r="E250" t="n">
-        <v>-7.16</v>
+        <v>2.24</v>
       </c>
       <c r="F250" t="n">
-        <v>1185</v>
+        <v>1174.7</v>
       </c>
       <c r="G250" t="n">
         <v>1170.76</v>
       </c>
       <c r="H250" t="n">
-        <v>14.24</v>
+        <v>3.94</v>
       </c>
       <c r="I250" t="n">
-        <v>1154</v>
+        <v>1150.5</v>
       </c>
       <c r="J250" t="n">
         <v>1141.13</v>
       </c>
       <c r="K250" t="n">
-        <v>12.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="251">
@@ -13468,31 +13468,31 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>875</v>
+        <v>881.2</v>
       </c>
       <c r="D251" t="n">
         <v>881.13</v>
       </c>
       <c r="E251" t="n">
-        <v>-6.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F251" t="n">
-        <v>887</v>
+        <v>891.8</v>
       </c>
       <c r="G251" t="n">
         <v>881.67</v>
       </c>
       <c r="H251" t="n">
-        <v>5.33</v>
+        <v>10.13</v>
       </c>
       <c r="I251" t="n">
-        <v>874</v>
+        <v>870.3</v>
       </c>
       <c r="J251" t="n">
         <v>863.08</v>
       </c>
       <c r="K251" t="n">
-        <v>10.92</v>
+        <v>7.22</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="252">
@@ -13520,31 +13520,31 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>518.25</v>
+        <v>524.5</v>
       </c>
       <c r="D252" t="n">
         <v>556.98</v>
       </c>
       <c r="E252" t="n">
-        <v>-38.73</v>
+        <v>-32.48</v>
       </c>
       <c r="F252" t="n">
-        <v>524.85</v>
+        <v>530</v>
       </c>
       <c r="G252" t="n">
         <v>556.98</v>
       </c>
       <c r="H252" t="n">
-        <v>-32.13</v>
+        <v>-26.98</v>
       </c>
       <c r="I252" t="n">
-        <v>517.55</v>
+        <v>518.3</v>
       </c>
       <c r="J252" t="n">
         <v>506.25</v>
       </c>
       <c r="K252" t="n">
-        <v>11.3</v>
+        <v>12.05</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>6.95</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="253">
@@ -13572,31 +13572,31 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="D253" t="n">
         <v>901.35</v>
       </c>
       <c r="E253" t="n">
-        <v>36.65</v>
+        <v>53.65</v>
       </c>
       <c r="F253" t="n">
-        <v>961.35</v>
+        <v>964</v>
       </c>
       <c r="G253" t="n">
         <v>901.35</v>
       </c>
       <c r="H253" t="n">
-        <v>60</v>
+        <v>62.65</v>
       </c>
       <c r="I253" t="n">
-        <v>933.1</v>
+        <v>897.1</v>
       </c>
       <c r="J253" t="n">
         <v>913.21</v>
       </c>
       <c r="K253" t="n">
-        <v>19.89</v>
+        <v>-16.11</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>4.07</v>
+        <v>5.95</v>
       </c>
     </row>
   </sheetData>
@@ -14368,31 +14368,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1163.6</v>
+        <v>1173</v>
       </c>
       <c r="D11" t="n">
         <v>1170.76</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.16</v>
+        <v>2.24</v>
       </c>
       <c r="F11" t="n">
-        <v>1185</v>
+        <v>1174.7</v>
       </c>
       <c r="G11" t="n">
         <v>1170.76</v>
       </c>
       <c r="H11" t="n">
-        <v>14.24</v>
+        <v>3.94</v>
       </c>
       <c r="I11" t="n">
-        <v>1154</v>
+        <v>1150.5</v>
       </c>
       <c r="J11" t="n">
         <v>1141.13</v>
       </c>
       <c r="K11" t="n">
-        <v>12.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -16324,31 +16324,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1592</v>
+        <v>1610</v>
       </c>
       <c r="D11" t="n">
         <v>1647.33</v>
       </c>
       <c r="E11" t="n">
-        <v>-55.33</v>
+        <v>-37.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1608</v>
+        <v>1638.9</v>
       </c>
       <c r="G11" t="n">
         <v>1647.33</v>
       </c>
       <c r="H11" t="n">
-        <v>-39.33</v>
+        <v>-8.43</v>
       </c>
       <c r="I11" t="n">
-        <v>1579.9</v>
+        <v>1604.2</v>
       </c>
       <c r="J11" t="n">
         <v>1588.49</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.59</v>
+        <v>15.71</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.36</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>
@@ -16930,31 +16930,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>315.9</v>
+        <v>318</v>
       </c>
       <c r="D11" t="n">
         <v>337.44</v>
       </c>
       <c r="E11" t="n">
-        <v>-21.54</v>
+        <v>-19.44</v>
       </c>
       <c r="F11" t="n">
-        <v>321.2</v>
+        <v>321.9</v>
       </c>
       <c r="G11" t="n">
         <v>337.44</v>
       </c>
       <c r="H11" t="n">
-        <v>-16.24</v>
+        <v>-15.54</v>
       </c>
       <c r="I11" t="n">
-        <v>315.55</v>
+        <v>316.2</v>
       </c>
       <c r="J11" t="n">
         <v>315.62</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6.38</v>
+        <v>5.76</v>
       </c>
     </row>
   </sheetData>
@@ -17536,31 +17536,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14150</v>
+        <v>14025</v>
       </c>
       <c r="D11" t="n">
         <v>14497.83</v>
       </c>
       <c r="E11" t="n">
-        <v>-347.83</v>
+        <v>-472.83</v>
       </c>
       <c r="F11" t="n">
-        <v>14420</v>
+        <v>14287</v>
       </c>
       <c r="G11" t="n">
         <v>14497.83</v>
       </c>
       <c r="H11" t="n">
-        <v>-77.83</v>
+        <v>-210.83</v>
       </c>
       <c r="I11" t="n">
-        <v>14066</v>
+        <v>14025</v>
       </c>
       <c r="J11" t="n">
         <v>13762.25</v>
       </c>
       <c r="K11" t="n">
-        <v>303.75</v>
+        <v>262.75</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>3.26</v>
       </c>
     </row>
   </sheetData>
@@ -18142,31 +18142,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1773</v>
+        <v>1806</v>
       </c>
       <c r="D11" t="n">
         <v>1773.35</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.35</v>
+        <v>32.65</v>
       </c>
       <c r="F11" t="n">
-        <v>1795</v>
+        <v>1821</v>
       </c>
       <c r="G11" t="n">
         <v>1773.35</v>
       </c>
       <c r="H11" t="n">
-        <v>21.65</v>
+        <v>47.65</v>
       </c>
       <c r="I11" t="n">
-        <v>1762.2</v>
+        <v>1799.6</v>
       </c>
       <c r="J11" t="n">
         <v>1727.77</v>
       </c>
       <c r="K11" t="n">
-        <v>34.43</v>
+        <v>71.83</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.02</v>
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>
@@ -19250,31 +19250,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>116.5</v>
+        <v>117.32</v>
       </c>
       <c r="D11" t="n">
         <v>113.3</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2</v>
+        <v>4.02</v>
       </c>
       <c r="F11" t="n">
-        <v>117.99</v>
+        <v>118.06</v>
       </c>
       <c r="G11" t="n">
         <v>118.51</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.52</v>
+        <v>-0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>116.5</v>
+        <v>115.32</v>
       </c>
       <c r="J11" t="n">
         <v>116.24</v>
       </c>
       <c r="K11" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
     </row>
   </sheetData>
@@ -19804,31 +19804,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3421.5</v>
+        <v>3390.4</v>
       </c>
       <c r="D10" t="n">
         <v>3591.55</v>
       </c>
       <c r="E10" t="n">
-        <v>-170.05</v>
+        <v>-201.15</v>
       </c>
       <c r="F10" t="n">
-        <v>3435</v>
+        <v>3451.9</v>
       </c>
       <c r="G10" t="n">
         <v>3591.55</v>
       </c>
       <c r="H10" t="n">
-        <v>-156.55</v>
+        <v>-139.65</v>
       </c>
       <c r="I10" t="n">
-        <v>3390.2</v>
+        <v>3388.3</v>
       </c>
       <c r="J10" t="n">
         <v>3340.95</v>
       </c>
       <c r="K10" t="n">
-        <v>49.25</v>
+        <v>47.35</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.73</v>
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -20358,31 +20358,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>518.25</v>
+        <v>524.5</v>
       </c>
       <c r="D10" t="n">
         <v>556.98</v>
       </c>
       <c r="E10" t="n">
-        <v>-38.73</v>
+        <v>-32.48</v>
       </c>
       <c r="F10" t="n">
-        <v>524.85</v>
+        <v>530</v>
       </c>
       <c r="G10" t="n">
         <v>556.98</v>
       </c>
       <c r="H10" t="n">
-        <v>-32.13</v>
+        <v>-26.98</v>
       </c>
       <c r="I10" t="n">
-        <v>517.55</v>
+        <v>518.3</v>
       </c>
       <c r="J10" t="n">
         <v>506.25</v>
       </c>
       <c r="K10" t="n">
-        <v>11.3</v>
+        <v>12.05</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.95</v>
+        <v>5.83</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N253"/>
+  <dimension ref="A1:N279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13610,6 +13610,1358 @@
       </c>
       <c r="N253" t="n">
         <v>5.95</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="D254" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="F254" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="G254" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="H254" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="I254" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="J254" t="n">
+        <v>117.34</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>11774</v>
+      </c>
+      <c r="D255" t="n">
+        <v>11809.19</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-35.19</v>
+      </c>
+      <c r="F255" t="n">
+        <v>11854</v>
+      </c>
+      <c r="G255" t="n">
+        <v>12117.36</v>
+      </c>
+      <c r="H255" t="n">
+        <v>-263.36</v>
+      </c>
+      <c r="I255" t="n">
+        <v>11640</v>
+      </c>
+      <c r="J255" t="n">
+        <v>11774</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-134</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="D256" t="n">
+        <v>194.91</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="F256" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G256" t="n">
+        <v>194.91</v>
+      </c>
+      <c r="H256" t="n">
+        <v>-7.31</v>
+      </c>
+      <c r="I256" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="J256" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1376.58</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1376.58</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I257" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="J257" t="n">
+        <v>1338.45</v>
+      </c>
+      <c r="K257" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1272</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1288.53</v>
+      </c>
+      <c r="E258" t="n">
+        <v>-16.53</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1288</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1288.53</v>
+      </c>
+      <c r="H258" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1243.88</v>
+      </c>
+      <c r="K258" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2070.63</v>
+      </c>
+      <c r="E259" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="F259" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="G259" t="n">
+        <v>2130.79</v>
+      </c>
+      <c r="H259" t="n">
+        <v>-8.99</v>
+      </c>
+      <c r="I259" t="n">
+        <v>2097.2</v>
+      </c>
+      <c r="J259" t="n">
+        <v>2072.54</v>
+      </c>
+      <c r="K259" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D260" t="n">
+        <v>2037.47</v>
+      </c>
+      <c r="E260" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G260" t="n">
+        <v>2037.47</v>
+      </c>
+      <c r="H260" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1968.74</v>
+      </c>
+      <c r="K260" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1813.1</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-48.15</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="H261" t="n">
+        <v>-43.25</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1785.4</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1767.88</v>
+      </c>
+      <c r="K261" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>320</v>
+      </c>
+      <c r="D262" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="E262" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="F262" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="G262" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="H262" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I262" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="J262" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D263" t="n">
+        <v>14102.32</v>
+      </c>
+      <c r="E263" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="F263" t="n">
+        <v>14550</v>
+      </c>
+      <c r="G263" t="n">
+        <v>14407.41</v>
+      </c>
+      <c r="H263" t="n">
+        <v>142.59</v>
+      </c>
+      <c r="I263" t="n">
+        <v>14026</v>
+      </c>
+      <c r="J263" t="n">
+        <v>14110.8</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-84.8</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>5709.5</v>
+      </c>
+      <c r="D264" t="n">
+        <v>5855.95</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-146.45</v>
+      </c>
+      <c r="F264" t="n">
+        <v>5767.5</v>
+      </c>
+      <c r="G264" t="n">
+        <v>5855.95</v>
+      </c>
+      <c r="H264" t="n">
+        <v>-88.45</v>
+      </c>
+      <c r="I264" t="n">
+        <v>5664.5</v>
+      </c>
+      <c r="J264" t="n">
+        <v>5574.16</v>
+      </c>
+      <c r="K264" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="D265" t="n">
+        <v>425.26</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-38.71</v>
+      </c>
+      <c r="F265" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="G265" t="n">
+        <v>425.26</v>
+      </c>
+      <c r="H265" t="n">
+        <v>-38.71</v>
+      </c>
+      <c r="I265" t="n">
+        <v>379</v>
+      </c>
+      <c r="J265" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>3415</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3249.52</v>
+      </c>
+      <c r="E266" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3425.6</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3358.81</v>
+      </c>
+      <c r="H266" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I266" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>3347.22</v>
+      </c>
+      <c r="K266" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D267" t="n">
+        <v>5514.7</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="F267" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5625.41</v>
+      </c>
+      <c r="H267" t="n">
+        <v>-48.41</v>
+      </c>
+      <c r="I267" t="n">
+        <v>5475.5</v>
+      </c>
+      <c r="J267" t="n">
+        <v>5474.84</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>11380</v>
+      </c>
+      <c r="D268" t="n">
+        <v>11471.96</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-91.95999999999999</v>
+      </c>
+      <c r="F268" t="n">
+        <v>11383</v>
+      </c>
+      <c r="G268" t="n">
+        <v>11482.91</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-99.91</v>
+      </c>
+      <c r="I268" t="n">
+        <v>11234</v>
+      </c>
+      <c r="J268" t="n">
+        <v>11181.79</v>
+      </c>
+      <c r="K268" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1048.6</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1054.16</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1054.8</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1064.76</v>
+      </c>
+      <c r="H269" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1041.4</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1036.06</v>
+      </c>
+      <c r="K269" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="D270" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F270" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="G270" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I270" t="n">
+        <v>285.65</v>
+      </c>
+      <c r="J270" t="n">
+        <v>282.61</v>
+      </c>
+      <c r="K270" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1185.5</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="H271" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1157.5</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1155.29</v>
+      </c>
+      <c r="K271" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>4041.3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>4073.34</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-32.04</v>
+      </c>
+      <c r="F272" t="n">
+        <v>4069</v>
+      </c>
+      <c r="G272" t="n">
+        <v>4108.7</v>
+      </c>
+      <c r="H272" t="n">
+        <v>-39.7</v>
+      </c>
+      <c r="I272" t="n">
+        <v>4024.8</v>
+      </c>
+      <c r="J272" t="n">
+        <v>4001.68</v>
+      </c>
+      <c r="K272" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2174.5</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2170.31</v>
+      </c>
+      <c r="E273" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F273" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="G273" t="n">
+        <v>2170.31</v>
+      </c>
+      <c r="H273" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="I273" t="n">
+        <v>2160.1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2119.1</v>
+      </c>
+      <c r="K273" t="n">
+        <v>41</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="D274" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="F274" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I274" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="J274" t="n">
+        <v>170.49</v>
+      </c>
+      <c r="K274" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1038.95</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1103.4</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-64.45</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1039.2</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1103.4</v>
+      </c>
+      <c r="H275" t="n">
+        <v>-64.2</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1025.55</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-7.65</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>942.1</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1006.16</v>
+      </c>
+      <c r="E276" t="n">
+        <v>-64.06</v>
+      </c>
+      <c r="F276" t="n">
+        <v>948.45</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1006.16</v>
+      </c>
+      <c r="H276" t="n">
+        <v>-57.71</v>
+      </c>
+      <c r="I276" t="n">
+        <v>930.05</v>
+      </c>
+      <c r="J276" t="n">
+        <v>930.6799999999999</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1589.8</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1566.21</v>
+      </c>
+      <c r="E277" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1610.7</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1632.03</v>
+      </c>
+      <c r="H277" t="n">
+        <v>-21.33</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1575.8</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1588.66</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-12.86</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>873.15</v>
+      </c>
+      <c r="D278" t="n">
+        <v>880.21</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="F278" t="n">
+        <v>881</v>
+      </c>
+      <c r="G278" t="n">
+        <v>892.14</v>
+      </c>
+      <c r="H278" t="n">
+        <v>-11.14</v>
+      </c>
+      <c r="I278" t="n">
+        <v>865</v>
+      </c>
+      <c r="J278" t="n">
+        <v>868.29</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="D279" t="n">
+        <v>488.23</v>
+      </c>
+      <c r="E279" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="F279" t="n">
+        <v>519.65</v>
+      </c>
+      <c r="G279" t="n">
+        <v>495.68</v>
+      </c>
+      <c r="H279" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="I279" t="n">
+        <v>511.55</v>
+      </c>
+      <c r="J279" t="n">
+        <v>503.49</v>
+      </c>
+      <c r="K279" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>5.35</v>
       </c>
     </row>
   </sheetData>
@@ -13813,7 +15165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14406,6 +15758,58 @@
       </c>
       <c r="N11" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1185.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1157.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1155.29</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -15769,7 +17173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16362,6 +17766,58 @@
       </c>
       <c r="N11" t="n">
         <v>2.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1589.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1566.21</v>
+      </c>
+      <c r="E12" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1610.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1632.03</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-21.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1575.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1588.66</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-12.86</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>
@@ -16375,7 +17831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16968,6 +18424,58 @@
       </c>
       <c r="N11" t="n">
         <v>5.76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>320</v>
+      </c>
+      <c r="D12" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="F12" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5.27</v>
       </c>
     </row>
   </sheetData>
@@ -16981,7 +18489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17574,6 +19082,58 @@
       </c>
       <c r="N11" t="n">
         <v>3.26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14102.32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14550</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14407.41</v>
+      </c>
+      <c r="H12" t="n">
+        <v>142.59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14026</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14110.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-84.8</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2.55</v>
       </c>
     </row>
   </sheetData>
@@ -17587,7 +19147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18180,6 +19740,58 @@
       </c>
       <c r="N11" t="n">
         <v>1.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1813.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-48.15</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-43.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1785.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1767.88</v>
+      </c>
+      <c r="K12" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>
@@ -18193,7 +19805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18682,6 +20294,58 @@
       </c>
       <c r="N9" t="n">
         <v>1.93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5514.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5625.41</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-48.41</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5475.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5474.84</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -18695,7 +20359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19288,6 +20952,58 @@
       </c>
       <c r="N11" t="n">
         <v>3.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="D12" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="I12" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="J12" t="n">
+        <v>117.34</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4.19</v>
       </c>
     </row>
   </sheetData>
@@ -19301,7 +21017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19842,6 +21558,58 @@
       </c>
       <c r="N10" t="n">
         <v>5.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3415</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3249.52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3425.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3358.81</v>
+      </c>
+      <c r="H11" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3347.22</v>
+      </c>
+      <c r="K11" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5.09</v>
       </c>
     </row>
   </sheetData>
@@ -19855,7 +21623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20396,6 +22164,58 @@
       </c>
       <c r="N10" t="n">
         <v>5.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="D11" t="n">
+        <v>488.23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>519.65</v>
+      </c>
+      <c r="G11" t="n">
+        <v>495.68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="I11" t="n">
+        <v>511.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>503.49</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5.35</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -13624,31 +13624,31 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>117.48</v>
+        <v>116.5</v>
       </c>
       <c r="D254" t="n">
         <v>122.62</v>
       </c>
       <c r="E254" t="n">
-        <v>-5.14</v>
+        <v>-6.12</v>
       </c>
       <c r="F254" t="n">
-        <v>117.59</v>
+        <v>117.99</v>
       </c>
       <c r="G254" t="n">
         <v>122.62</v>
       </c>
       <c r="H254" t="n">
-        <v>-5.03</v>
+        <v>-4.63</v>
       </c>
       <c r="I254" t="n">
-        <v>116.03</v>
+        <v>116.5</v>
       </c>
       <c r="J254" t="n">
         <v>117.34</v>
       </c>
       <c r="K254" t="n">
-        <v>-1.31</v>
+        <v>-0.84</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>4.19</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="255">
@@ -13676,31 +13676,31 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>11774</v>
+        <v>11623</v>
       </c>
       <c r="D255" t="n">
         <v>11809.19</v>
       </c>
       <c r="E255" t="n">
-        <v>-35.19</v>
+        <v>-186.19</v>
       </c>
       <c r="F255" t="n">
-        <v>11854</v>
+        <v>11840</v>
       </c>
       <c r="G255" t="n">
         <v>12117.36</v>
       </c>
       <c r="H255" t="n">
-        <v>-263.36</v>
+        <v>-277.36</v>
       </c>
       <c r="I255" t="n">
-        <v>11640</v>
+        <v>11614</v>
       </c>
       <c r="J255" t="n">
         <v>11774</v>
       </c>
       <c r="K255" t="n">
-        <v>-134</v>
+        <v>-160</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0.3</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="256">
@@ -13728,31 +13728,31 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>186.9</v>
+        <v>185.5</v>
       </c>
       <c r="D256" t="n">
         <v>194.91</v>
       </c>
       <c r="E256" t="n">
-        <v>-8.01</v>
+        <v>-9.41</v>
       </c>
       <c r="F256" t="n">
-        <v>187.6</v>
+        <v>190.58</v>
       </c>
       <c r="G256" t="n">
         <v>194.91</v>
       </c>
       <c r="H256" t="n">
-        <v>-7.31</v>
+        <v>-4.33</v>
       </c>
       <c r="I256" t="n">
-        <v>184.9</v>
+        <v>185.5</v>
       </c>
       <c r="J256" t="n">
         <v>186.9</v>
       </c>
       <c r="K256" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>4.11</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="257">
@@ -13780,31 +13780,31 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1378.4</v>
+        <v>1354.9</v>
       </c>
       <c r="D257" t="n">
         <v>1376.58</v>
       </c>
       <c r="E257" t="n">
-        <v>1.82</v>
+        <v>-21.68</v>
       </c>
       <c r="F257" t="n">
-        <v>1378.4</v>
+        <v>1368.8</v>
       </c>
       <c r="G257" t="n">
         <v>1376.58</v>
       </c>
       <c r="H257" t="n">
-        <v>1.82</v>
+        <v>-7.78</v>
       </c>
       <c r="I257" t="n">
-        <v>1351.5</v>
+        <v>1331.1</v>
       </c>
       <c r="J257" t="n">
         <v>1338.45</v>
       </c>
       <c r="K257" t="n">
-        <v>13.05</v>
+        <v>-7.35</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0.13</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="258">
@@ -13832,31 +13832,31 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D258" t="n">
         <v>1288.53</v>
       </c>
       <c r="E258" t="n">
-        <v>-16.53</v>
+        <v>-15.53</v>
       </c>
       <c r="F258" t="n">
-        <v>1288</v>
+        <v>1281.2</v>
       </c>
       <c r="G258" t="n">
         <v>1288.53</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.53</v>
+        <v>-7.33</v>
       </c>
       <c r="I258" t="n">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="J258" t="n">
         <v>1243.88</v>
       </c>
       <c r="K258" t="n">
-        <v>15.12</v>
+        <v>19.12</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="259">
@@ -13884,31 +13884,31 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2121.8</v>
+        <v>2115</v>
       </c>
       <c r="D259" t="n">
         <v>2070.63</v>
       </c>
       <c r="E259" t="n">
-        <v>51.17</v>
+        <v>44.37</v>
       </c>
       <c r="F259" t="n">
-        <v>2121.8</v>
+        <v>2122</v>
       </c>
       <c r="G259" t="n">
         <v>2130.79</v>
       </c>
       <c r="H259" t="n">
-        <v>-8.99</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>2097.2</v>
+        <v>2075.1</v>
       </c>
       <c r="J259" t="n">
         <v>2072.54</v>
       </c>
       <c r="K259" t="n">
-        <v>24.66</v>
+        <v>2.56</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="260">
@@ -13936,31 +13936,31 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2012</v>
+        <v>2011.2</v>
       </c>
       <c r="D260" t="n">
         <v>2037.47</v>
       </c>
       <c r="E260" t="n">
-        <v>-25.47</v>
+        <v>-26.27</v>
       </c>
       <c r="F260" t="n">
-        <v>2013</v>
+        <v>2018.8</v>
       </c>
       <c r="G260" t="n">
         <v>2037.47</v>
       </c>
       <c r="H260" t="n">
-        <v>-24.47</v>
+        <v>-18.67</v>
       </c>
       <c r="I260" t="n">
-        <v>1985</v>
+        <v>1998</v>
       </c>
       <c r="J260" t="n">
         <v>1968.74</v>
       </c>
       <c r="K260" t="n">
-        <v>16.26</v>
+        <v>29.26</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="261">
@@ -13988,31 +13988,31 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1813.1</v>
+        <v>1773</v>
       </c>
       <c r="D261" t="n">
         <v>1861.25</v>
       </c>
       <c r="E261" t="n">
-        <v>-48.15</v>
+        <v>-88.25</v>
       </c>
       <c r="F261" t="n">
-        <v>1818</v>
+        <v>1795</v>
       </c>
       <c r="G261" t="n">
         <v>1861.25</v>
       </c>
       <c r="H261" t="n">
-        <v>-43.25</v>
+        <v>-66.25</v>
       </c>
       <c r="I261" t="n">
-        <v>1785.4</v>
+        <v>1762.2</v>
       </c>
       <c r="J261" t="n">
         <v>1767.88</v>
       </c>
       <c r="K261" t="n">
-        <v>17.52</v>
+        <v>-5.68</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2.59</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="262">
@@ -14040,31 +14040,31 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>320</v>
+        <v>315.9</v>
       </c>
       <c r="D262" t="n">
         <v>303.98</v>
       </c>
       <c r="E262" t="n">
-        <v>16.02</v>
+        <v>11.92</v>
       </c>
       <c r="F262" t="n">
-        <v>322.85</v>
+        <v>321.2</v>
       </c>
       <c r="G262" t="n">
         <v>327.01</v>
       </c>
       <c r="H262" t="n">
-        <v>-4.16</v>
+        <v>-5.81</v>
       </c>
       <c r="I262" t="n">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="J262" t="n">
         <v>318.26</v>
       </c>
       <c r="K262" t="n">
-        <v>-2.41</v>
+        <v>-2.71</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>5.27</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="263">
@@ -14092,31 +14092,31 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>14462</v>
+        <v>14150</v>
       </c>
       <c r="D263" t="n">
         <v>14102.32</v>
       </c>
       <c r="E263" t="n">
-        <v>359.68</v>
+        <v>47.68</v>
       </c>
       <c r="F263" t="n">
-        <v>14550</v>
+        <v>14420</v>
       </c>
       <c r="G263" t="n">
         <v>14407.41</v>
       </c>
       <c r="H263" t="n">
-        <v>142.59</v>
+        <v>12.59</v>
       </c>
       <c r="I263" t="n">
-        <v>14026</v>
+        <v>14066</v>
       </c>
       <c r="J263" t="n">
         <v>14110.8</v>
       </c>
       <c r="K263" t="n">
-        <v>-84.8</v>
+        <v>-44.8</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2.55</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="264">
@@ -14144,31 +14144,31 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>5709.5</v>
+        <v>5745.5</v>
       </c>
       <c r="D264" t="n">
         <v>5855.95</v>
       </c>
       <c r="E264" t="n">
-        <v>-146.45</v>
+        <v>-110.45</v>
       </c>
       <c r="F264" t="n">
-        <v>5767.5</v>
+        <v>5778</v>
       </c>
       <c r="G264" t="n">
         <v>5855.95</v>
       </c>
       <c r="H264" t="n">
-        <v>-88.45</v>
+        <v>-77.95</v>
       </c>
       <c r="I264" t="n">
-        <v>5664.5</v>
+        <v>5694.5</v>
       </c>
       <c r="J264" t="n">
         <v>5574.16</v>
       </c>
       <c r="K264" t="n">
-        <v>90.34</v>
+        <v>120.34</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="265">
@@ -14196,31 +14196,31 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>386.55</v>
+        <v>388</v>
       </c>
       <c r="D265" t="n">
         <v>425.26</v>
       </c>
       <c r="E265" t="n">
-        <v>-38.71</v>
+        <v>-37.26</v>
       </c>
       <c r="F265" t="n">
-        <v>386.55</v>
+        <v>390.85</v>
       </c>
       <c r="G265" t="n">
         <v>425.26</v>
       </c>
       <c r="H265" t="n">
-        <v>-38.71</v>
+        <v>-34.41</v>
       </c>
       <c r="I265" t="n">
-        <v>379</v>
+        <v>385.8</v>
       </c>
       <c r="J265" t="n">
         <v>381.42</v>
       </c>
       <c r="K265" t="n">
-        <v>-2.42</v>
+        <v>4.38</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>9.1</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="266">
@@ -14248,31 +14248,31 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3415</v>
+        <v>3421.5</v>
       </c>
       <c r="D266" t="n">
         <v>3249.52</v>
       </c>
       <c r="E266" t="n">
-        <v>165.48</v>
+        <v>171.98</v>
       </c>
       <c r="F266" t="n">
-        <v>3425.6</v>
+        <v>3435</v>
       </c>
       <c r="G266" t="n">
         <v>3358.81</v>
       </c>
       <c r="H266" t="n">
-        <v>66.79000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="I266" t="n">
-        <v>3371.1</v>
+        <v>3390.2</v>
       </c>
       <c r="J266" t="n">
         <v>3347.22</v>
       </c>
       <c r="K266" t="n">
-        <v>23.88</v>
+        <v>42.98</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>5.09</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="267">
@@ -14300,31 +14300,31 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>5510</v>
+        <v>5442.5</v>
       </c>
       <c r="D267" t="n">
         <v>5514.7</v>
       </c>
       <c r="E267" t="n">
-        <v>-4.7</v>
+        <v>-72.2</v>
       </c>
       <c r="F267" t="n">
-        <v>5577</v>
+        <v>5571.5</v>
       </c>
       <c r="G267" t="n">
         <v>5625.41</v>
       </c>
       <c r="H267" t="n">
-        <v>-48.41</v>
+        <v>-53.91</v>
       </c>
       <c r="I267" t="n">
-        <v>5475.5</v>
+        <v>5442.5</v>
       </c>
       <c r="J267" t="n">
         <v>5474.84</v>
       </c>
       <c r="K267" t="n">
-        <v>0.66</v>
+        <v>-32.34</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0.09</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="268">
@@ -14352,31 +14352,31 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>11380</v>
+        <v>11254</v>
       </c>
       <c r="D268" t="n">
         <v>11471.96</v>
       </c>
       <c r="E268" t="n">
-        <v>-91.95999999999999</v>
+        <v>-217.96</v>
       </c>
       <c r="F268" t="n">
-        <v>11383</v>
+        <v>11435</v>
       </c>
       <c r="G268" t="n">
         <v>11482.91</v>
       </c>
       <c r="H268" t="n">
-        <v>-99.91</v>
+        <v>-47.91</v>
       </c>
       <c r="I268" t="n">
-        <v>11234</v>
+        <v>11211</v>
       </c>
       <c r="J268" t="n">
         <v>11181.79</v>
       </c>
       <c r="K268" t="n">
-        <v>52.21</v>
+        <v>29.21</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="269">
@@ -14404,31 +14404,31 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1048.6</v>
+        <v>1053</v>
       </c>
       <c r="D269" t="n">
         <v>1054.16</v>
       </c>
       <c r="E269" t="n">
-        <v>-5.56</v>
+        <v>-1.16</v>
       </c>
       <c r="F269" t="n">
-        <v>1054.8</v>
+        <v>1067.7</v>
       </c>
       <c r="G269" t="n">
         <v>1064.76</v>
       </c>
       <c r="H269" t="n">
-        <v>-9.960000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="I269" t="n">
-        <v>1041.4</v>
+        <v>1053</v>
       </c>
       <c r="J269" t="n">
         <v>1036.06</v>
       </c>
       <c r="K269" t="n">
-        <v>5.34</v>
+        <v>16.94</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0.53</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="270">
@@ -14456,31 +14456,31 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>288.15</v>
+        <v>286.25</v>
       </c>
       <c r="D270" t="n">
         <v>289.21</v>
       </c>
       <c r="E270" t="n">
-        <v>-1.06</v>
+        <v>-2.96</v>
       </c>
       <c r="F270" t="n">
-        <v>291.5</v>
+        <v>286.95</v>
       </c>
       <c r="G270" t="n">
         <v>289.21</v>
       </c>
       <c r="H270" t="n">
-        <v>2.29</v>
+        <v>-2.26</v>
       </c>
       <c r="I270" t="n">
-        <v>285.65</v>
+        <v>281.8</v>
       </c>
       <c r="J270" t="n">
         <v>282.61</v>
       </c>
       <c r="K270" t="n">
-        <v>3.04</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0.37</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="271">
@@ -14508,31 +14508,31 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1180.5</v>
+        <v>1163.6</v>
       </c>
       <c r="D271" t="n">
         <v>1192.21</v>
       </c>
       <c r="E271" t="n">
-        <v>-11.71</v>
+        <v>-28.61</v>
       </c>
       <c r="F271" t="n">
-        <v>1185.5</v>
+        <v>1185</v>
       </c>
       <c r="G271" t="n">
         <v>1192.21</v>
       </c>
       <c r="H271" t="n">
-        <v>-6.71</v>
+        <v>-7.21</v>
       </c>
       <c r="I271" t="n">
-        <v>1157.5</v>
+        <v>1154</v>
       </c>
       <c r="J271" t="n">
         <v>1155.29</v>
       </c>
       <c r="K271" t="n">
-        <v>2.21</v>
+        <v>-1.29</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0.98</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="272">
@@ -14560,31 +14560,31 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>4041.3</v>
+        <v>4064.3</v>
       </c>
       <c r="D272" t="n">
         <v>4073.34</v>
       </c>
       <c r="E272" t="n">
-        <v>-32.04</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>4069</v>
+        <v>4085</v>
       </c>
       <c r="G272" t="n">
         <v>4108.7</v>
       </c>
       <c r="H272" t="n">
-        <v>-39.7</v>
+        <v>-23.7</v>
       </c>
       <c r="I272" t="n">
-        <v>4024.8</v>
+        <v>4050</v>
       </c>
       <c r="J272" t="n">
         <v>4001.68</v>
       </c>
       <c r="K272" t="n">
-        <v>23.12</v>
+        <v>48.32</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0.79</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="273">
@@ -14612,31 +14612,31 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2174.5</v>
+        <v>2186</v>
       </c>
       <c r="D273" t="n">
         <v>2170.31</v>
       </c>
       <c r="E273" t="n">
-        <v>4.19</v>
+        <v>15.69</v>
       </c>
       <c r="F273" t="n">
-        <v>2218.8</v>
+        <v>2221.9</v>
       </c>
       <c r="G273" t="n">
         <v>2170.31</v>
       </c>
       <c r="H273" t="n">
-        <v>48.49</v>
+        <v>51.59</v>
       </c>
       <c r="I273" t="n">
-        <v>2160.1</v>
+        <v>2179</v>
       </c>
       <c r="J273" t="n">
         <v>2119.1</v>
       </c>
       <c r="K273" t="n">
-        <v>41</v>
+        <v>59.9</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0.19</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="274">
@@ -14664,31 +14664,31 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>173.1</v>
+        <v>176.35</v>
       </c>
       <c r="D274" t="n">
         <v>176.77</v>
       </c>
       <c r="E274" t="n">
-        <v>-3.67</v>
+        <v>-0.42</v>
       </c>
       <c r="F274" t="n">
-        <v>176.1</v>
+        <v>177.59</v>
       </c>
       <c r="G274" t="n">
         <v>176.77</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.67</v>
+        <v>0.82</v>
       </c>
       <c r="I274" t="n">
-        <v>173.1</v>
+        <v>174.5</v>
       </c>
       <c r="J274" t="n">
         <v>170.49</v>
       </c>
       <c r="K274" t="n">
-        <v>2.61</v>
+        <v>4.01</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2.08</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="275">
@@ -14716,31 +14716,31 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1038.95</v>
+        <v>1041.6</v>
       </c>
       <c r="D275" t="n">
         <v>1103.4</v>
       </c>
       <c r="E275" t="n">
-        <v>-64.45</v>
+        <v>-61.8</v>
       </c>
       <c r="F275" t="n">
-        <v>1039.2</v>
+        <v>1050.6</v>
       </c>
       <c r="G275" t="n">
         <v>1103.4</v>
       </c>
       <c r="H275" t="n">
-        <v>-64.2</v>
+        <v>-52.8</v>
       </c>
       <c r="I275" t="n">
-        <v>1025.55</v>
+        <v>1038</v>
       </c>
       <c r="J275" t="n">
         <v>1033.2</v>
       </c>
       <c r="K275" t="n">
-        <v>-7.65</v>
+        <v>4.8</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>5.84</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="276">
@@ -14768,31 +14768,31 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>942.1</v>
+        <v>938</v>
       </c>
       <c r="D276" t="n">
         <v>1006.16</v>
       </c>
       <c r="E276" t="n">
-        <v>-64.06</v>
+        <v>-68.16</v>
       </c>
       <c r="F276" t="n">
-        <v>948.45</v>
+        <v>961.35</v>
       </c>
       <c r="G276" t="n">
         <v>1006.16</v>
       </c>
       <c r="H276" t="n">
-        <v>-57.71</v>
+        <v>-44.81</v>
       </c>
       <c r="I276" t="n">
-        <v>930.05</v>
+        <v>933.1</v>
       </c>
       <c r="J276" t="n">
         <v>930.6799999999999</v>
       </c>
       <c r="K276" t="n">
-        <v>-0.63</v>
+        <v>2.42</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>6.37</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="277">
@@ -14820,31 +14820,31 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1589.8</v>
+        <v>1592</v>
       </c>
       <c r="D277" t="n">
         <v>1566.21</v>
       </c>
       <c r="E277" t="n">
-        <v>23.59</v>
+        <v>25.79</v>
       </c>
       <c r="F277" t="n">
-        <v>1610.7</v>
+        <v>1608</v>
       </c>
       <c r="G277" t="n">
         <v>1632.03</v>
       </c>
       <c r="H277" t="n">
-        <v>-21.33</v>
+        <v>-24.03</v>
       </c>
       <c r="I277" t="n">
-        <v>1575.8</v>
+        <v>1579.9</v>
       </c>
       <c r="J277" t="n">
         <v>1588.66</v>
       </c>
       <c r="K277" t="n">
-        <v>-12.86</v>
+        <v>-8.76</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="278">
@@ -14872,31 +14872,31 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>873.15</v>
+        <v>875</v>
       </c>
       <c r="D278" t="n">
         <v>880.21</v>
       </c>
       <c r="E278" t="n">
-        <v>-7.06</v>
+        <v>-5.21</v>
       </c>
       <c r="F278" t="n">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="G278" t="n">
         <v>892.14</v>
       </c>
       <c r="H278" t="n">
-        <v>-11.14</v>
+        <v>-5.14</v>
       </c>
       <c r="I278" t="n">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="J278" t="n">
         <v>868.29</v>
       </c>
       <c r="K278" t="n">
-        <v>-3.29</v>
+        <v>5.71</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="279">
@@ -14924,31 +14924,31 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>514.35</v>
+        <v>518.25</v>
       </c>
       <c r="D279" t="n">
         <v>488.23</v>
       </c>
       <c r="E279" t="n">
-        <v>26.12</v>
+        <v>30.02</v>
       </c>
       <c r="F279" t="n">
-        <v>519.65</v>
+        <v>524.85</v>
       </c>
       <c r="G279" t="n">
         <v>495.68</v>
       </c>
       <c r="H279" t="n">
-        <v>23.97</v>
+        <v>29.17</v>
       </c>
       <c r="I279" t="n">
-        <v>511.55</v>
+        <v>517.55</v>
       </c>
       <c r="J279" t="n">
         <v>503.49</v>
       </c>
       <c r="K279" t="n">
-        <v>8.06</v>
+        <v>14.06</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>5.35</v>
+        <v>6.15</v>
       </c>
     </row>
   </sheetData>
@@ -15772,31 +15772,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1180.5</v>
+        <v>1163.6</v>
       </c>
       <c r="D12" t="n">
         <v>1192.21</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.71</v>
+        <v>-28.61</v>
       </c>
       <c r="F12" t="n">
-        <v>1185.5</v>
+        <v>1185</v>
       </c>
       <c r="G12" t="n">
         <v>1192.21</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.71</v>
+        <v>-7.21</v>
       </c>
       <c r="I12" t="n">
-        <v>1157.5</v>
+        <v>1154</v>
       </c>
       <c r="J12" t="n">
         <v>1155.29</v>
       </c>
       <c r="K12" t="n">
-        <v>2.21</v>
+        <v>-1.29</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.98</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -17780,31 +17780,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1589.8</v>
+        <v>1592</v>
       </c>
       <c r="D12" t="n">
         <v>1566.21</v>
       </c>
       <c r="E12" t="n">
-        <v>23.59</v>
+        <v>25.79</v>
       </c>
       <c r="F12" t="n">
-        <v>1610.7</v>
+        <v>1608</v>
       </c>
       <c r="G12" t="n">
         <v>1632.03</v>
       </c>
       <c r="H12" t="n">
-        <v>-21.33</v>
+        <v>-24.03</v>
       </c>
       <c r="I12" t="n">
-        <v>1575.8</v>
+        <v>1579.9</v>
       </c>
       <c r="J12" t="n">
         <v>1588.66</v>
       </c>
       <c r="K12" t="n">
-        <v>-12.86</v>
+        <v>-8.76</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -18438,31 +18438,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>320</v>
+        <v>315.9</v>
       </c>
       <c r="D12" t="n">
         <v>303.98</v>
       </c>
       <c r="E12" t="n">
-        <v>16.02</v>
+        <v>11.92</v>
       </c>
       <c r="F12" t="n">
-        <v>322.85</v>
+        <v>321.2</v>
       </c>
       <c r="G12" t="n">
         <v>327.01</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.16</v>
+        <v>-5.81</v>
       </c>
       <c r="I12" t="n">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="J12" t="n">
         <v>318.26</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.41</v>
+        <v>-2.71</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.27</v>
+        <v>3.92</v>
       </c>
     </row>
   </sheetData>
@@ -19096,31 +19096,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14462</v>
+        <v>14150</v>
       </c>
       <c r="D12" t="n">
         <v>14102.32</v>
       </c>
       <c r="E12" t="n">
-        <v>359.68</v>
+        <v>47.68</v>
       </c>
       <c r="F12" t="n">
-        <v>14550</v>
+        <v>14420</v>
       </c>
       <c r="G12" t="n">
         <v>14407.41</v>
       </c>
       <c r="H12" t="n">
-        <v>142.59</v>
+        <v>12.59</v>
       </c>
       <c r="I12" t="n">
-        <v>14026</v>
+        <v>14066</v>
       </c>
       <c r="J12" t="n">
         <v>14110.8</v>
       </c>
       <c r="K12" t="n">
-        <v>-84.8</v>
+        <v>-44.8</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -19754,31 +19754,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1813.1</v>
+        <v>1773</v>
       </c>
       <c r="D12" t="n">
         <v>1861.25</v>
       </c>
       <c r="E12" t="n">
-        <v>-48.15</v>
+        <v>-88.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1818</v>
+        <v>1795</v>
       </c>
       <c r="G12" t="n">
         <v>1861.25</v>
       </c>
       <c r="H12" t="n">
-        <v>-43.25</v>
+        <v>-66.25</v>
       </c>
       <c r="I12" t="n">
-        <v>1785.4</v>
+        <v>1762.2</v>
       </c>
       <c r="J12" t="n">
         <v>1767.88</v>
       </c>
       <c r="K12" t="n">
-        <v>17.52</v>
+        <v>-5.68</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.59</v>
+        <v>4.74</v>
       </c>
     </row>
   </sheetData>
@@ -20308,31 +20308,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5510</v>
+        <v>5442.5</v>
       </c>
       <c r="D10" t="n">
         <v>5514.7</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7</v>
+        <v>-72.2</v>
       </c>
       <c r="F10" t="n">
-        <v>5577</v>
+        <v>5571.5</v>
       </c>
       <c r="G10" t="n">
         <v>5625.41</v>
       </c>
       <c r="H10" t="n">
-        <v>-48.41</v>
+        <v>-53.91</v>
       </c>
       <c r="I10" t="n">
-        <v>5475.5</v>
+        <v>5442.5</v>
       </c>
       <c r="J10" t="n">
         <v>5474.84</v>
       </c>
       <c r="K10" t="n">
-        <v>0.66</v>
+        <v>-32.34</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.09</v>
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>
@@ -20966,31 +20966,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>117.48</v>
+        <v>116.5</v>
       </c>
       <c r="D12" t="n">
         <v>122.62</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.14</v>
+        <v>-6.12</v>
       </c>
       <c r="F12" t="n">
-        <v>117.59</v>
+        <v>117.99</v>
       </c>
       <c r="G12" t="n">
         <v>122.62</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.03</v>
+        <v>-4.63</v>
       </c>
       <c r="I12" t="n">
-        <v>116.03</v>
+        <v>116.5</v>
       </c>
       <c r="J12" t="n">
         <v>117.34</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.31</v>
+        <v>-0.84</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.19</v>
+        <v>4.99</v>
       </c>
     </row>
   </sheetData>
@@ -21572,31 +21572,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3415</v>
+        <v>3421.5</v>
       </c>
       <c r="D11" t="n">
         <v>3249.52</v>
       </c>
       <c r="E11" t="n">
-        <v>165.48</v>
+        <v>171.98</v>
       </c>
       <c r="F11" t="n">
-        <v>3425.6</v>
+        <v>3435</v>
       </c>
       <c r="G11" t="n">
         <v>3358.81</v>
       </c>
       <c r="H11" t="n">
-        <v>66.79000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="I11" t="n">
-        <v>3371.1</v>
+        <v>3390.2</v>
       </c>
       <c r="J11" t="n">
         <v>3347.22</v>
       </c>
       <c r="K11" t="n">
-        <v>23.88</v>
+        <v>42.98</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.09</v>
+        <v>5.29</v>
       </c>
     </row>
   </sheetData>
@@ -22178,31 +22178,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>514.35</v>
+        <v>518.25</v>
       </c>
       <c r="D11" t="n">
         <v>488.23</v>
       </c>
       <c r="E11" t="n">
-        <v>26.12</v>
+        <v>30.02</v>
       </c>
       <c r="F11" t="n">
-        <v>519.65</v>
+        <v>524.85</v>
       </c>
       <c r="G11" t="n">
         <v>495.68</v>
       </c>
       <c r="H11" t="n">
-        <v>23.97</v>
+        <v>29.17</v>
       </c>
       <c r="I11" t="n">
-        <v>511.55</v>
+        <v>517.55</v>
       </c>
       <c r="J11" t="n">
         <v>503.49</v>
       </c>
       <c r="K11" t="n">
-        <v>8.06</v>
+        <v>14.06</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.35</v>
+        <v>6.15</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N279"/>
+  <dimension ref="A1:N308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14962,6 +14962,1514 @@
       </c>
       <c r="N279" t="n">
         <v>6.15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>118</v>
+      </c>
+      <c r="D280" t="n">
+        <v>113</v>
+      </c>
+      <c r="E280" t="n">
+        <v>5</v>
+      </c>
+      <c r="F280" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G280" t="n">
+        <v>118.24</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I280" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="J280" t="n">
+        <v>115.96</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="D281" t="n">
+        <v>174.77</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F281" t="n">
+        <v>175.57</v>
+      </c>
+      <c r="G281" t="n">
+        <v>174.77</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I281" t="n">
+        <v>172.61</v>
+      </c>
+      <c r="J281" t="n">
+        <v>171.11</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D282" t="n">
+        <v>2203.35</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-63.35</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2153.7</v>
+      </c>
+      <c r="G282" t="n">
+        <v>2203.35</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-49.65</v>
+      </c>
+      <c r="I282" t="n">
+        <v>2125</v>
+      </c>
+      <c r="J282" t="n">
+        <v>2101.37</v>
+      </c>
+      <c r="K282" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>5674</v>
+      </c>
+      <c r="D283" t="n">
+        <v>5679.22</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="F283" t="n">
+        <v>5706</v>
+      </c>
+      <c r="G283" t="n">
+        <v>5799.2</v>
+      </c>
+      <c r="H283" t="n">
+        <v>-93.2</v>
+      </c>
+      <c r="I283" t="n">
+        <v>5534</v>
+      </c>
+      <c r="J283" t="n">
+        <v>5674</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-140</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>5677.29</v>
+      </c>
+      <c r="E284" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="F284" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="G284" t="n">
+        <v>5677.29</v>
+      </c>
+      <c r="H284" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="I284" t="n">
+        <v>5670</v>
+      </c>
+      <c r="J284" t="n">
+        <v>5588.81</v>
+      </c>
+      <c r="K284" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D285" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-169.39</v>
+      </c>
+      <c r="F285" t="n">
+        <v>14953</v>
+      </c>
+      <c r="G285" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="H285" t="n">
+        <v>-66.39</v>
+      </c>
+      <c r="I285" t="n">
+        <v>14470</v>
+      </c>
+      <c r="J285" t="n">
+        <v>14441.25</v>
+      </c>
+      <c r="K285" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="D286" t="n">
+        <v>475.42</v>
+      </c>
+      <c r="E286" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F286" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="G286" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="I286" t="n">
+        <v>465</v>
+      </c>
+      <c r="J286" t="n">
+        <v>477.09</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>4081</v>
+      </c>
+      <c r="D287" t="n">
+        <v>4104.52</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-23.52</v>
+      </c>
+      <c r="F287" t="n">
+        <v>4084.9</v>
+      </c>
+      <c r="G287" t="n">
+        <v>4104.52</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-19.62</v>
+      </c>
+      <c r="I287" t="n">
+        <v>4048.3</v>
+      </c>
+      <c r="J287" t="n">
+        <v>4031.94</v>
+      </c>
+      <c r="K287" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>676.15</v>
+      </c>
+      <c r="D288" t="n">
+        <v>668.4400000000001</v>
+      </c>
+      <c r="E288" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="F288" t="n">
+        <v>682.45</v>
+      </c>
+      <c r="G288" t="n">
+        <v>668.4400000000001</v>
+      </c>
+      <c r="H288" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="I288" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="J288" t="n">
+        <v>658.89</v>
+      </c>
+      <c r="K288" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>3424.8</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-210.09</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3456.4</v>
+      </c>
+      <c r="G289" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="H289" t="n">
+        <v>-178.49</v>
+      </c>
+      <c r="I289" t="n">
+        <v>3401</v>
+      </c>
+      <c r="J289" t="n">
+        <v>3353.77</v>
+      </c>
+      <c r="K289" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D290" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="F290" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="G290" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="I290" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J290" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2005.94</v>
+      </c>
+      <c r="E291" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2030.1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>2005.94</v>
+      </c>
+      <c r="H291" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="I291" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1968.15</v>
+      </c>
+      <c r="K291" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1941.7</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1919.55</v>
+      </c>
+      <c r="E292" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1952.2</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1944.35</v>
+      </c>
+      <c r="H292" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1933</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1906.78</v>
+      </c>
+      <c r="K292" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2227</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2261.05</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-34.05</v>
+      </c>
+      <c r="F293" t="n">
+        <v>2233.7</v>
+      </c>
+      <c r="G293" t="n">
+        <v>2261.05</v>
+      </c>
+      <c r="H293" t="n">
+        <v>-27.35</v>
+      </c>
+      <c r="I293" t="n">
+        <v>2180.4</v>
+      </c>
+      <c r="J293" t="n">
+        <v>2183.32</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1055.22</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1052.9</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1055.22</v>
+      </c>
+      <c r="H294" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1045.7</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1026.08</v>
+      </c>
+      <c r="K294" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>735.85</v>
+      </c>
+      <c r="D295" t="n">
+        <v>727.46</v>
+      </c>
+      <c r="E295" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="F295" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="G295" t="n">
+        <v>745.61</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="I295" t="n">
+        <v>725.75</v>
+      </c>
+      <c r="J295" t="n">
+        <v>731.51</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1255.27</v>
+      </c>
+      <c r="E296" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1282.6</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1267.47</v>
+      </c>
+      <c r="H296" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="J296" t="n">
+        <v>1243.16</v>
+      </c>
+      <c r="K296" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1183.52</v>
+      </c>
+      <c r="E297" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1210.68</v>
+      </c>
+      <c r="H297" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1187.5</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>11368</v>
+      </c>
+      <c r="D298" t="n">
+        <v>11241.22</v>
+      </c>
+      <c r="E298" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="F298" t="n">
+        <v>11423</v>
+      </c>
+      <c r="G298" t="n">
+        <v>11359.28</v>
+      </c>
+      <c r="H298" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="I298" t="n">
+        <v>11303</v>
+      </c>
+      <c r="J298" t="n">
+        <v>11138.95</v>
+      </c>
+      <c r="K298" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="D299" t="n">
+        <v>914.72</v>
+      </c>
+      <c r="E299" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F299" t="n">
+        <v>989.55</v>
+      </c>
+      <c r="G299" t="n">
+        <v>978.86</v>
+      </c>
+      <c r="H299" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="I299" t="n">
+        <v>942.15</v>
+      </c>
+      <c r="J299" t="n">
+        <v>960.09</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-17.94</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="D300" t="n">
+        <v>290.73</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F300" t="n">
+        <v>293.75</v>
+      </c>
+      <c r="G300" t="n">
+        <v>291.04</v>
+      </c>
+      <c r="H300" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I300" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="J300" t="n">
+        <v>285.39</v>
+      </c>
+      <c r="K300" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2570</v>
+      </c>
+      <c r="D301" t="n">
+        <v>2540.69</v>
+      </c>
+      <c r="E301" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2583.2</v>
+      </c>
+      <c r="G301" t="n">
+        <v>2540.69</v>
+      </c>
+      <c r="H301" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="I301" t="n">
+        <v>2552</v>
+      </c>
+      <c r="J301" t="n">
+        <v>2495.69</v>
+      </c>
+      <c r="K301" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1807.12</v>
+      </c>
+      <c r="E302" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1888.5</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1868.99</v>
+      </c>
+      <c r="H302" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="I302" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1838.06</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D303" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="E303" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="F303" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="G303" t="n">
+        <v>389.84</v>
+      </c>
+      <c r="H303" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I303" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="J303" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="K303" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1360.9</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1350.18</v>
+      </c>
+      <c r="E304" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1390.1</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1350.18</v>
+      </c>
+      <c r="H304" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="I304" t="n">
+        <v>1355.3</v>
+      </c>
+      <c r="J304" t="n">
+        <v>1317.49</v>
+      </c>
+      <c r="K304" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>519</v>
+      </c>
+      <c r="D305" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-36.32</v>
+      </c>
+      <c r="F305" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="G305" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="H305" t="n">
+        <v>-30.92</v>
+      </c>
+      <c r="I305" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="J305" t="n">
+        <v>506.69</v>
+      </c>
+      <c r="K305" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="D306" t="n">
+        <v>177.17</v>
+      </c>
+      <c r="E306" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="F306" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="G306" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I306" t="n">
+        <v>184.39</v>
+      </c>
+      <c r="J306" t="n">
+        <v>182.74</v>
+      </c>
+      <c r="K306" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1029.85</v>
+      </c>
+      <c r="D307" t="n">
+        <v>979.95</v>
+      </c>
+      <c r="E307" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1021.07</v>
+      </c>
+      <c r="H307" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="I307" t="n">
+        <v>1013</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1001.8</v>
+      </c>
+      <c r="K307" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>871</v>
+      </c>
+      <c r="D308" t="n">
+        <v>872.77</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F308" t="n">
+        <v>883.8</v>
+      </c>
+      <c r="G308" t="n">
+        <v>876.28</v>
+      </c>
+      <c r="H308" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I308" t="n">
+        <v>871</v>
+      </c>
+      <c r="J308" t="n">
+        <v>859.49</v>
+      </c>
+      <c r="K308" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -14975,7 +16483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15152,6 +16660,58 @@
       </c>
       <c r="N3" t="n">
         <v>1.02</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>735.85</v>
+      </c>
+      <c r="D4" t="n">
+        <v>727.46</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>745.61</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="I4" t="n">
+        <v>725.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>731.51</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -15165,7 +16725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15810,6 +17370,58 @@
       </c>
       <c r="N12" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1183.52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1210.68</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1187.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -17831,7 +19443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18476,6 +20088,58 @@
       </c>
       <c r="N12" t="n">
         <v>3.92</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="F13" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="I13" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J13" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4.98</v>
       </c>
     </row>
   </sheetData>
@@ -18489,7 +20153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19134,6 +20798,58 @@
       </c>
       <c r="N12" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-169.39</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14953</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-66.39</v>
+      </c>
+      <c r="I13" t="n">
+        <v>14470</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14441.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -19147,7 +20863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19792,6 +21508,58 @@
       </c>
       <c r="N12" t="n">
         <v>4.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1807.12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1888.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1868.99</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1838.06</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4.14</v>
       </c>
     </row>
   </sheetData>
@@ -19805,7 +21573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20346,6 +22114,58 @@
       </c>
       <c r="N10" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5674</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5679.22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5706</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5799.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-93.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5534</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5674</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-140</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -20359,7 +22179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21004,6 +22824,58 @@
       </c>
       <c r="N12" t="n">
         <v>4.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>118</v>
+      </c>
+      <c r="D13" t="n">
+        <v>113</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>118.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I13" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="J13" t="n">
+        <v>115.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4.42</v>
       </c>
     </row>
   </sheetData>
@@ -21017,7 +22889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21610,6 +23482,58 @@
       </c>
       <c r="N11" t="n">
         <v>5.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3424.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-210.09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3456.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-178.49</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3401</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3353.77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5.78</v>
       </c>
     </row>
   </sheetData>
@@ -21623,7 +23547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22216,6 +24140,58 @@
       </c>
       <c r="N11" t="n">
         <v>6.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>519</v>
+      </c>
+      <c r="D12" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-36.32</v>
+      </c>
+      <c r="F12" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-30.92</v>
+      </c>
+      <c r="I12" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>506.69</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>6.54</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -14976,31 +14976,31 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>118</v>
+        <v>117.48</v>
       </c>
       <c r="D280" t="n">
         <v>113</v>
       </c>
       <c r="E280" t="n">
-        <v>5</v>
+        <v>4.48</v>
       </c>
       <c r="F280" t="n">
-        <v>119.1</v>
+        <v>117.59</v>
       </c>
       <c r="G280" t="n">
         <v>118.24</v>
       </c>
       <c r="H280" t="n">
-        <v>0.86</v>
+        <v>-0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>117.44</v>
+        <v>116.03</v>
       </c>
       <c r="J280" t="n">
         <v>115.96</v>
       </c>
       <c r="K280" t="n">
-        <v>1.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>4.42</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="281">
@@ -15028,31 +15028,31 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>173.8</v>
+        <v>173.1</v>
       </c>
       <c r="D281" t="n">
         <v>174.77</v>
       </c>
       <c r="E281" t="n">
-        <v>-0.97</v>
+        <v>-1.67</v>
       </c>
       <c r="F281" t="n">
-        <v>175.57</v>
+        <v>176.1</v>
       </c>
       <c r="G281" t="n">
         <v>174.77</v>
       </c>
       <c r="H281" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="I281" t="n">
-        <v>172.61</v>
+        <v>173.1</v>
       </c>
       <c r="J281" t="n">
         <v>171.11</v>
       </c>
       <c r="K281" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="282">
@@ -15080,31 +15080,31 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2140</v>
+        <v>2121.8</v>
       </c>
       <c r="D282" t="n">
         <v>2203.35</v>
       </c>
       <c r="E282" t="n">
-        <v>-63.35</v>
+        <v>-81.55</v>
       </c>
       <c r="F282" t="n">
-        <v>2153.7</v>
+        <v>2121.8</v>
       </c>
       <c r="G282" t="n">
         <v>2203.35</v>
       </c>
       <c r="H282" t="n">
-        <v>-49.65</v>
+        <v>-81.55</v>
       </c>
       <c r="I282" t="n">
-        <v>2125</v>
+        <v>2097.2</v>
       </c>
       <c r="J282" t="n">
         <v>2101.37</v>
       </c>
       <c r="K282" t="n">
-        <v>23.63</v>
+        <v>-4.17</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="283">
@@ -15132,31 +15132,31 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5674</v>
+        <v>5510</v>
       </c>
       <c r="D283" t="n">
         <v>5679.22</v>
       </c>
       <c r="E283" t="n">
-        <v>-5.22</v>
+        <v>-169.22</v>
       </c>
       <c r="F283" t="n">
-        <v>5706</v>
+        <v>5577</v>
       </c>
       <c r="G283" t="n">
         <v>5799.2</v>
       </c>
       <c r="H283" t="n">
-        <v>-93.2</v>
+        <v>-222.2</v>
       </c>
       <c r="I283" t="n">
-        <v>5534</v>
+        <v>5475.5</v>
       </c>
       <c r="J283" t="n">
         <v>5674</v>
       </c>
       <c r="K283" t="n">
-        <v>-140</v>
+        <v>-198.5</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -15165,11 +15165,11 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N283" t="n">
-        <v>0.09</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="284">
@@ -15184,31 +15184,31 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>5740.5</v>
+        <v>5709.5</v>
       </c>
       <c r="D284" t="n">
         <v>5677.29</v>
       </c>
       <c r="E284" t="n">
-        <v>63.21</v>
+        <v>32.21</v>
       </c>
       <c r="F284" t="n">
-        <v>5740.5</v>
+        <v>5767.5</v>
       </c>
       <c r="G284" t="n">
         <v>5677.29</v>
       </c>
       <c r="H284" t="n">
-        <v>63.21</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>5670</v>
+        <v>5664.5</v>
       </c>
       <c r="J284" t="n">
         <v>5588.81</v>
       </c>
       <c r="K284" t="n">
-        <v>81.19</v>
+        <v>75.69</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>1.11</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="285">
@@ -15236,31 +15236,31 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>14850</v>
+        <v>14462</v>
       </c>
       <c r="D285" t="n">
         <v>15019.39</v>
       </c>
       <c r="E285" t="n">
-        <v>-169.39</v>
+        <v>-557.39</v>
       </c>
       <c r="F285" t="n">
-        <v>14953</v>
+        <v>14550</v>
       </c>
       <c r="G285" t="n">
         <v>15019.39</v>
       </c>
       <c r="H285" t="n">
-        <v>-66.39</v>
+        <v>-469.39</v>
       </c>
       <c r="I285" t="n">
-        <v>14470</v>
+        <v>14026</v>
       </c>
       <c r="J285" t="n">
         <v>14441.25</v>
       </c>
       <c r="K285" t="n">
-        <v>28.75</v>
+        <v>-415.25</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -15269,11 +15269,11 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>1.13</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="286">
@@ -15288,31 +15288,31 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>480.9</v>
+        <v>474.85</v>
       </c>
       <c r="D286" t="n">
         <v>475.42</v>
       </c>
       <c r="E286" t="n">
-        <v>5.48</v>
+        <v>-0.57</v>
       </c>
       <c r="F286" t="n">
-        <v>481.5</v>
+        <v>485.8</v>
       </c>
       <c r="G286" t="n">
         <v>486.32</v>
       </c>
       <c r="H286" t="n">
-        <v>-4.82</v>
+        <v>-0.52</v>
       </c>
       <c r="I286" t="n">
-        <v>465</v>
+        <v>472.9</v>
       </c>
       <c r="J286" t="n">
         <v>477.09</v>
       </c>
       <c r="K286" t="n">
-        <v>-12.09</v>
+        <v>-4.19</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>1.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="287">
@@ -15340,31 +15340,31 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4081</v>
+        <v>4041.3</v>
       </c>
       <c r="D287" t="n">
         <v>4104.52</v>
       </c>
       <c r="E287" t="n">
-        <v>-23.52</v>
+        <v>-63.22</v>
       </c>
       <c r="F287" t="n">
-        <v>4084.9</v>
+        <v>4069</v>
       </c>
       <c r="G287" t="n">
         <v>4104.52</v>
       </c>
       <c r="H287" t="n">
-        <v>-19.62</v>
+        <v>-35.52</v>
       </c>
       <c r="I287" t="n">
-        <v>4048.3</v>
+        <v>4024.8</v>
       </c>
       <c r="J287" t="n">
         <v>4031.94</v>
       </c>
       <c r="K287" t="n">
-        <v>16.36</v>
+        <v>-7.14</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>0.57</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="288">
@@ -15392,31 +15392,31 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>676.15</v>
+        <v>669.9</v>
       </c>
       <c r="D288" t="n">
         <v>668.4400000000001</v>
       </c>
       <c r="E288" t="n">
-        <v>7.71</v>
+        <v>1.46</v>
       </c>
       <c r="F288" t="n">
-        <v>682.45</v>
+        <v>674.65</v>
       </c>
       <c r="G288" t="n">
         <v>668.4400000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>14.01</v>
+        <v>6.21</v>
       </c>
       <c r="I288" t="n">
-        <v>671.95</v>
+        <v>658.3</v>
       </c>
       <c r="J288" t="n">
         <v>658.89</v>
       </c>
       <c r="K288" t="n">
-        <v>13.06</v>
+        <v>-0.59</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>1.15</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="289">
@@ -15444,31 +15444,31 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3424.8</v>
+        <v>3415</v>
       </c>
       <c r="D289" t="n">
         <v>3634.89</v>
       </c>
       <c r="E289" t="n">
-        <v>-210.09</v>
+        <v>-219.89</v>
       </c>
       <c r="F289" t="n">
-        <v>3456.4</v>
+        <v>3425.6</v>
       </c>
       <c r="G289" t="n">
         <v>3634.89</v>
       </c>
       <c r="H289" t="n">
-        <v>-178.49</v>
+        <v>-209.29</v>
       </c>
       <c r="I289" t="n">
-        <v>3401</v>
+        <v>3371.1</v>
       </c>
       <c r="J289" t="n">
         <v>3353.77</v>
       </c>
       <c r="K289" t="n">
-        <v>47.23</v>
+        <v>17.33</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>5.78</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="290">
@@ -15496,31 +15496,31 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>327.95</v>
+        <v>320</v>
       </c>
       <c r="D290" t="n">
         <v>345.13</v>
       </c>
       <c r="E290" t="n">
-        <v>-17.18</v>
+        <v>-25.13</v>
       </c>
       <c r="F290" t="n">
-        <v>328.5</v>
+        <v>322.85</v>
       </c>
       <c r="G290" t="n">
         <v>345.13</v>
       </c>
       <c r="H290" t="n">
-        <v>-16.63</v>
+        <v>-22.28</v>
       </c>
       <c r="I290" t="n">
-        <v>321.35</v>
+        <v>315.85</v>
       </c>
       <c r="J290" t="n">
         <v>327.95</v>
       </c>
       <c r="K290" t="n">
-        <v>-6.6</v>
+        <v>-12.1</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>4.98</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="291">
@@ -15548,31 +15548,31 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D291" t="n">
         <v>2005.94</v>
       </c>
       <c r="E291" t="n">
-        <v>10.06</v>
+        <v>6.06</v>
       </c>
       <c r="F291" t="n">
-        <v>2030.1</v>
+        <v>2013</v>
       </c>
       <c r="G291" t="n">
         <v>2005.94</v>
       </c>
       <c r="H291" t="n">
-        <v>24.16</v>
+        <v>7.06</v>
       </c>
       <c r="I291" t="n">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="J291" t="n">
         <v>1968.15</v>
       </c>
       <c r="K291" t="n">
-        <v>44.85</v>
+        <v>16.85</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="292">
@@ -15600,31 +15600,31 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1941.7</v>
+        <v>1922</v>
       </c>
       <c r="D292" t="n">
         <v>1919.55</v>
       </c>
       <c r="E292" t="n">
-        <v>22.15</v>
+        <v>2.45</v>
       </c>
       <c r="F292" t="n">
-        <v>1952.2</v>
+        <v>1941.8</v>
       </c>
       <c r="G292" t="n">
         <v>1944.35</v>
       </c>
       <c r="H292" t="n">
-        <v>7.85</v>
+        <v>-2.55</v>
       </c>
       <c r="I292" t="n">
-        <v>1933</v>
+        <v>1922</v>
       </c>
       <c r="J292" t="n">
         <v>1906.78</v>
       </c>
       <c r="K292" t="n">
-        <v>26.22</v>
+        <v>15.22</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>1.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="293">
@@ -15652,31 +15652,31 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2227</v>
+        <v>2174.5</v>
       </c>
       <c r="D293" t="n">
         <v>2261.05</v>
       </c>
       <c r="E293" t="n">
-        <v>-34.05</v>
+        <v>-86.55</v>
       </c>
       <c r="F293" t="n">
-        <v>2233.7</v>
+        <v>2218.8</v>
       </c>
       <c r="G293" t="n">
         <v>2261.05</v>
       </c>
       <c r="H293" t="n">
-        <v>-27.35</v>
+        <v>-42.25</v>
       </c>
       <c r="I293" t="n">
-        <v>2180.4</v>
+        <v>2160.1</v>
       </c>
       <c r="J293" t="n">
         <v>2183.32</v>
       </c>
       <c r="K293" t="n">
-        <v>-2.92</v>
+        <v>-23.22</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>1.51</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="294">
@@ -15704,31 +15704,31 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1048</v>
+        <v>1048.6</v>
       </c>
       <c r="D294" t="n">
         <v>1055.22</v>
       </c>
       <c r="E294" t="n">
-        <v>-7.22</v>
+        <v>-6.62</v>
       </c>
       <c r="F294" t="n">
-        <v>1052.9</v>
+        <v>1054.8</v>
       </c>
       <c r="G294" t="n">
         <v>1055.22</v>
       </c>
       <c r="H294" t="n">
-        <v>-2.32</v>
+        <v>-0.42</v>
       </c>
       <c r="I294" t="n">
-        <v>1045.7</v>
+        <v>1041.4</v>
       </c>
       <c r="J294" t="n">
         <v>1026.08</v>
       </c>
       <c r="K294" t="n">
-        <v>19.62</v>
+        <v>15.32</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="295">
@@ -15756,31 +15756,31 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>735.85</v>
+        <v>723.35</v>
       </c>
       <c r="D295" t="n">
         <v>727.46</v>
       </c>
       <c r="E295" t="n">
-        <v>8.390000000000001</v>
+        <v>-4.11</v>
       </c>
       <c r="F295" t="n">
-        <v>737.1</v>
+        <v>724.95</v>
       </c>
       <c r="G295" t="n">
         <v>745.61</v>
       </c>
       <c r="H295" t="n">
-        <v>-8.51</v>
+        <v>-20.66</v>
       </c>
       <c r="I295" t="n">
-        <v>725.75</v>
+        <v>714.15</v>
       </c>
       <c r="J295" t="n">
         <v>731.51</v>
       </c>
       <c r="K295" t="n">
-        <v>-5.76</v>
+        <v>-17.36</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>1.15</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="296">
@@ -15808,31 +15808,31 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1260.5</v>
+        <v>1272</v>
       </c>
       <c r="D296" t="n">
         <v>1255.27</v>
       </c>
       <c r="E296" t="n">
-        <v>5.23</v>
+        <v>16.73</v>
       </c>
       <c r="F296" t="n">
-        <v>1282.6</v>
+        <v>1288</v>
       </c>
       <c r="G296" t="n">
         <v>1267.47</v>
       </c>
       <c r="H296" t="n">
-        <v>15.13</v>
+        <v>20.53</v>
       </c>
       <c r="I296" t="n">
-        <v>1260.5</v>
+        <v>1259</v>
       </c>
       <c r="J296" t="n">
         <v>1243.16</v>
       </c>
       <c r="K296" t="n">
-        <v>17.34</v>
+        <v>15.84</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>0.42</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="297">
@@ -15860,31 +15860,31 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1203</v>
+        <v>1180.5</v>
       </c>
       <c r="D297" t="n">
         <v>1183.52</v>
       </c>
       <c r="E297" t="n">
-        <v>19.48</v>
+        <v>-3.02</v>
       </c>
       <c r="F297" t="n">
-        <v>1222.9</v>
+        <v>1185.5</v>
       </c>
       <c r="G297" t="n">
         <v>1210.68</v>
       </c>
       <c r="H297" t="n">
-        <v>12.22</v>
+        <v>-25.18</v>
       </c>
       <c r="I297" t="n">
-        <v>1186</v>
+        <v>1157.5</v>
       </c>
       <c r="J297" t="n">
         <v>1187.5</v>
       </c>
       <c r="K297" t="n">
-        <v>-1.5</v>
+        <v>-30</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>1.65</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="298">
@@ -15912,31 +15912,31 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>11368</v>
+        <v>11380</v>
       </c>
       <c r="D298" t="n">
         <v>11241.22</v>
       </c>
       <c r="E298" t="n">
-        <v>126.78</v>
+        <v>138.78</v>
       </c>
       <c r="F298" t="n">
-        <v>11423</v>
+        <v>11383</v>
       </c>
       <c r="G298" t="n">
         <v>11359.28</v>
       </c>
       <c r="H298" t="n">
-        <v>63.72</v>
+        <v>23.72</v>
       </c>
       <c r="I298" t="n">
-        <v>11303</v>
+        <v>11234</v>
       </c>
       <c r="J298" t="n">
         <v>11138.95</v>
       </c>
       <c r="K298" t="n">
-        <v>164.05</v>
+        <v>95.05</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="299">
@@ -15964,31 +15964,31 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>973.4</v>
+        <v>942.1</v>
       </c>
       <c r="D299" t="n">
         <v>914.72</v>
       </c>
       <c r="E299" t="n">
-        <v>58.68</v>
+        <v>27.38</v>
       </c>
       <c r="F299" t="n">
-        <v>989.55</v>
+        <v>948.45</v>
       </c>
       <c r="G299" t="n">
         <v>978.86</v>
       </c>
       <c r="H299" t="n">
-        <v>10.69</v>
+        <v>-30.41</v>
       </c>
       <c r="I299" t="n">
-        <v>942.15</v>
+        <v>930.05</v>
       </c>
       <c r="J299" t="n">
         <v>960.09</v>
       </c>
       <c r="K299" t="n">
-        <v>-17.94</v>
+        <v>-30.04</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>6.42</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="300">
@@ -16016,31 +16016,31 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>291.4</v>
+        <v>288.15</v>
       </c>
       <c r="D300" t="n">
         <v>290.73</v>
       </c>
       <c r="E300" t="n">
-        <v>0.67</v>
+        <v>-2.58</v>
       </c>
       <c r="F300" t="n">
-        <v>293.75</v>
+        <v>291.5</v>
       </c>
       <c r="G300" t="n">
         <v>291.04</v>
       </c>
       <c r="H300" t="n">
-        <v>2.71</v>
+        <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>286.6</v>
+        <v>285.65</v>
       </c>
       <c r="J300" t="n">
         <v>285.39</v>
       </c>
       <c r="K300" t="n">
-        <v>1.21</v>
+        <v>0.26</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0.23</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="301">
@@ -16068,31 +16068,31 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2570</v>
+        <v>2559.18</v>
       </c>
       <c r="D301" t="n">
         <v>2540.69</v>
       </c>
       <c r="E301" t="n">
-        <v>29.31</v>
+        <v>18.49</v>
       </c>
       <c r="F301" t="n">
-        <v>2583.2</v>
+        <v>2599.81</v>
       </c>
       <c r="G301" t="n">
         <v>2540.69</v>
       </c>
       <c r="H301" t="n">
-        <v>42.51</v>
+        <v>59.12</v>
       </c>
       <c r="I301" t="n">
-        <v>2552</v>
+        <v>2533.43</v>
       </c>
       <c r="J301" t="n">
         <v>2495.69</v>
       </c>
       <c r="K301" t="n">
-        <v>56.31</v>
+        <v>37.74</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>1.15</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="302">
@@ -16120,31 +16120,31 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1882</v>
+        <v>1813.1</v>
       </c>
       <c r="D302" t="n">
         <v>1807.12</v>
       </c>
       <c r="E302" t="n">
-        <v>74.88</v>
+        <v>5.98</v>
       </c>
       <c r="F302" t="n">
-        <v>1888.5</v>
+        <v>1818</v>
       </c>
       <c r="G302" t="n">
         <v>1868.99</v>
       </c>
       <c r="H302" t="n">
-        <v>19.51</v>
+        <v>-50.99</v>
       </c>
       <c r="I302" t="n">
-        <v>1826.5</v>
+        <v>1785.4</v>
       </c>
       <c r="J302" t="n">
         <v>1838.06</v>
       </c>
       <c r="K302" t="n">
-        <v>-11.56</v>
+        <v>-52.66</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>4.14</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="303">
@@ -16172,31 +16172,31 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>385.6</v>
+        <v>386.55</v>
       </c>
       <c r="D303" t="n">
         <v>354.62</v>
       </c>
       <c r="E303" t="n">
-        <v>30.98</v>
+        <v>31.93</v>
       </c>
       <c r="F303" t="n">
-        <v>395.75</v>
+        <v>386.55</v>
       </c>
       <c r="G303" t="n">
         <v>389.84</v>
       </c>
       <c r="H303" t="n">
-        <v>5.91</v>
+        <v>-3.29</v>
       </c>
       <c r="I303" t="n">
-        <v>385.1</v>
+        <v>379</v>
       </c>
       <c r="J303" t="n">
         <v>382.45</v>
       </c>
       <c r="K303" t="n">
-        <v>2.65</v>
+        <v>-3.45</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>8.74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304">
@@ -16224,31 +16224,31 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1360.9</v>
+        <v>1378.4</v>
       </c>
       <c r="D304" t="n">
         <v>1350.18</v>
       </c>
       <c r="E304" t="n">
-        <v>10.72</v>
+        <v>28.22</v>
       </c>
       <c r="F304" t="n">
-        <v>1390.1</v>
+        <v>1378.4</v>
       </c>
       <c r="G304" t="n">
         <v>1350.18</v>
       </c>
       <c r="H304" t="n">
-        <v>39.92</v>
+        <v>28.22</v>
       </c>
       <c r="I304" t="n">
-        <v>1355.3</v>
+        <v>1351.5</v>
       </c>
       <c r="J304" t="n">
         <v>1317.49</v>
       </c>
       <c r="K304" t="n">
-        <v>37.81</v>
+        <v>34.01</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>0.79</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="305">
@@ -16276,31 +16276,31 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>519</v>
+        <v>514.35</v>
       </c>
       <c r="D305" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="E305" t="n">
-        <v>-36.32</v>
+        <v>-40.97</v>
       </c>
       <c r="F305" t="n">
-        <v>524.4</v>
+        <v>519.65</v>
       </c>
       <c r="G305" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="H305" t="n">
-        <v>-30.92</v>
+        <v>-35.67</v>
       </c>
       <c r="I305" t="n">
-        <v>513.8</v>
+        <v>511.55</v>
       </c>
       <c r="J305" t="n">
         <v>506.69</v>
       </c>
       <c r="K305" t="n">
-        <v>7.11</v>
+        <v>4.86</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>6.54</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="306">
@@ -16328,31 +16328,31 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>184.68</v>
+        <v>186.9</v>
       </c>
       <c r="D306" t="n">
         <v>177.17</v>
       </c>
       <c r="E306" t="n">
-        <v>7.51</v>
+        <v>9.73</v>
       </c>
       <c r="F306" t="n">
-        <v>189.46</v>
+        <v>187.6</v>
       </c>
       <c r="G306" t="n">
         <v>186.29</v>
       </c>
       <c r="H306" t="n">
-        <v>3.17</v>
+        <v>1.31</v>
       </c>
       <c r="I306" t="n">
-        <v>184.39</v>
+        <v>184.9</v>
       </c>
       <c r="J306" t="n">
         <v>182.74</v>
       </c>
       <c r="K306" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.24</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="307">
@@ -16380,31 +16380,31 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1029.85</v>
+        <v>1038.95</v>
       </c>
       <c r="D307" t="n">
         <v>979.95</v>
       </c>
       <c r="E307" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="F307" t="n">
-        <v>1048</v>
+        <v>1039.2</v>
       </c>
       <c r="G307" t="n">
         <v>1021.07</v>
       </c>
       <c r="H307" t="n">
-        <v>26.93</v>
+        <v>18.13</v>
       </c>
       <c r="I307" t="n">
-        <v>1013</v>
+        <v>1025.55</v>
       </c>
       <c r="J307" t="n">
         <v>1001.8</v>
       </c>
       <c r="K307" t="n">
-        <v>11.2</v>
+        <v>23.75</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -16413,11 +16413,11 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N307" t="n">
-        <v>5.09</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="308">
@@ -16432,31 +16432,31 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>871</v>
+        <v>873.15</v>
       </c>
       <c r="D308" t="n">
         <v>872.77</v>
       </c>
       <c r="E308" t="n">
-        <v>-1.77</v>
+        <v>0.38</v>
       </c>
       <c r="F308" t="n">
-        <v>883.8</v>
+        <v>881</v>
       </c>
       <c r="G308" t="n">
         <v>876.28</v>
       </c>
       <c r="H308" t="n">
-        <v>7.52</v>
+        <v>4.72</v>
       </c>
       <c r="I308" t="n">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="J308" t="n">
         <v>859.49</v>
       </c>
       <c r="K308" t="n">
-        <v>11.51</v>
+        <v>5.51</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -16674,31 +16674,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>735.85</v>
+        <v>723.35</v>
       </c>
       <c r="D4" t="n">
         <v>727.46</v>
       </c>
       <c r="E4" t="n">
-        <v>8.390000000000001</v>
+        <v>-4.11</v>
       </c>
       <c r="F4" t="n">
-        <v>737.1</v>
+        <v>724.95</v>
       </c>
       <c r="G4" t="n">
         <v>745.61</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.51</v>
+        <v>-20.66</v>
       </c>
       <c r="I4" t="n">
-        <v>725.75</v>
+        <v>714.15</v>
       </c>
       <c r="J4" t="n">
         <v>731.51</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.76</v>
+        <v>-17.36</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.15</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17384,31 +17384,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1203</v>
+        <v>1180.5</v>
       </c>
       <c r="D13" t="n">
         <v>1183.52</v>
       </c>
       <c r="E13" t="n">
-        <v>19.48</v>
+        <v>-3.02</v>
       </c>
       <c r="F13" t="n">
-        <v>1222.9</v>
+        <v>1185.5</v>
       </c>
       <c r="G13" t="n">
         <v>1210.68</v>
       </c>
       <c r="H13" t="n">
-        <v>12.22</v>
+        <v>-25.18</v>
       </c>
       <c r="I13" t="n">
-        <v>1186</v>
+        <v>1157.5</v>
       </c>
       <c r="J13" t="n">
         <v>1187.5</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5</v>
+        <v>-30</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -20102,31 +20102,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>327.95</v>
+        <v>320</v>
       </c>
       <c r="D13" t="n">
         <v>345.13</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.18</v>
+        <v>-25.13</v>
       </c>
       <c r="F13" t="n">
-        <v>328.5</v>
+        <v>322.85</v>
       </c>
       <c r="G13" t="n">
         <v>345.13</v>
       </c>
       <c r="H13" t="n">
-        <v>-16.63</v>
+        <v>-22.28</v>
       </c>
       <c r="I13" t="n">
-        <v>321.35</v>
+        <v>315.85</v>
       </c>
       <c r="J13" t="n">
         <v>327.95</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.6</v>
+        <v>-12.1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.98</v>
+        <v>7.28</v>
       </c>
     </row>
   </sheetData>
@@ -20812,31 +20812,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14850</v>
+        <v>14462</v>
       </c>
       <c r="D13" t="n">
         <v>15019.39</v>
       </c>
       <c r="E13" t="n">
-        <v>-169.39</v>
+        <v>-557.39</v>
       </c>
       <c r="F13" t="n">
-        <v>14953</v>
+        <v>14550</v>
       </c>
       <c r="G13" t="n">
         <v>15019.39</v>
       </c>
       <c r="H13" t="n">
-        <v>-66.39</v>
+        <v>-469.39</v>
       </c>
       <c r="I13" t="n">
-        <v>14470</v>
+        <v>14026</v>
       </c>
       <c r="J13" t="n">
         <v>14441.25</v>
       </c>
       <c r="K13" t="n">
-        <v>28.75</v>
+        <v>-415.25</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -20845,11 +20845,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.13</v>
+        <v>3.71</v>
       </c>
     </row>
   </sheetData>
@@ -21522,31 +21522,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1882</v>
+        <v>1813.1</v>
       </c>
       <c r="D13" t="n">
         <v>1807.12</v>
       </c>
       <c r="E13" t="n">
-        <v>74.88</v>
+        <v>5.98</v>
       </c>
       <c r="F13" t="n">
-        <v>1888.5</v>
+        <v>1818</v>
       </c>
       <c r="G13" t="n">
         <v>1868.99</v>
       </c>
       <c r="H13" t="n">
-        <v>19.51</v>
+        <v>-50.99</v>
       </c>
       <c r="I13" t="n">
-        <v>1826.5</v>
+        <v>1785.4</v>
       </c>
       <c r="J13" t="n">
         <v>1838.06</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.56</v>
+        <v>-52.66</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.14</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -22128,31 +22128,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5674</v>
+        <v>5510</v>
       </c>
       <c r="D11" t="n">
         <v>5679.22</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.22</v>
+        <v>-169.22</v>
       </c>
       <c r="F11" t="n">
-        <v>5706</v>
+        <v>5577</v>
       </c>
       <c r="G11" t="n">
         <v>5799.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-93.2</v>
+        <v>-222.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5534</v>
+        <v>5475.5</v>
       </c>
       <c r="J11" t="n">
         <v>5674</v>
       </c>
       <c r="K11" t="n">
-        <v>-140</v>
+        <v>-198.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -22161,11 +22161,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.09</v>
+        <v>2.98</v>
       </c>
     </row>
   </sheetData>
@@ -22838,31 +22838,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>117.48</v>
       </c>
       <c r="D13" t="n">
         <v>113</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4.48</v>
       </c>
       <c r="F13" t="n">
-        <v>119.1</v>
+        <v>117.59</v>
       </c>
       <c r="G13" t="n">
         <v>118.24</v>
       </c>
       <c r="H13" t="n">
-        <v>0.86</v>
+        <v>-0.65</v>
       </c>
       <c r="I13" t="n">
-        <v>117.44</v>
+        <v>116.03</v>
       </c>
       <c r="J13" t="n">
         <v>115.96</v>
       </c>
       <c r="K13" t="n">
-        <v>1.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.42</v>
+        <v>3.96</v>
       </c>
     </row>
   </sheetData>
@@ -23496,31 +23496,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3424.8</v>
+        <v>3415</v>
       </c>
       <c r="D12" t="n">
         <v>3634.89</v>
       </c>
       <c r="E12" t="n">
-        <v>-210.09</v>
+        <v>-219.89</v>
       </c>
       <c r="F12" t="n">
-        <v>3456.4</v>
+        <v>3425.6</v>
       </c>
       <c r="G12" t="n">
         <v>3634.89</v>
       </c>
       <c r="H12" t="n">
-        <v>-178.49</v>
+        <v>-209.29</v>
       </c>
       <c r="I12" t="n">
-        <v>3401</v>
+        <v>3371.1</v>
       </c>
       <c r="J12" t="n">
         <v>3353.77</v>
       </c>
       <c r="K12" t="n">
-        <v>47.23</v>
+        <v>17.33</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.78</v>
+        <v>6.05</v>
       </c>
     </row>
   </sheetData>
@@ -24154,31 +24154,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>519</v>
+        <v>514.35</v>
       </c>
       <c r="D12" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-36.32</v>
+        <v>-40.97</v>
       </c>
       <c r="F12" t="n">
-        <v>524.4</v>
+        <v>519.65</v>
       </c>
       <c r="G12" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-30.92</v>
+        <v>-35.67</v>
       </c>
       <c r="I12" t="n">
-        <v>513.8</v>
+        <v>511.55</v>
       </c>
       <c r="J12" t="n">
         <v>506.69</v>
       </c>
       <c r="K12" t="n">
-        <v>7.11</v>
+        <v>4.86</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.54</v>
+        <v>7.38</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:N340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16470,6 +16470,1670 @@
       </c>
       <c r="N308" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2054.95</v>
+      </c>
+      <c r="E309" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="F309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="G309" t="n">
+        <v>2054.95</v>
+      </c>
+      <c r="H309" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="I309" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1991.09</v>
+      </c>
+      <c r="K309" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="D310" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="F310" t="n">
+        <v>684.45</v>
+      </c>
+      <c r="G310" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="H310" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="I310" t="n">
+        <v>675.25</v>
+      </c>
+      <c r="J310" t="n">
+        <v>655.47</v>
+      </c>
+      <c r="K310" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1048.7</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1050.46</v>
+      </c>
+      <c r="E311" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1054.7</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1050.46</v>
+      </c>
+      <c r="H311" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I311" t="n">
+        <v>1040.1</v>
+      </c>
+      <c r="J311" t="n">
+        <v>1019.46</v>
+      </c>
+      <c r="K311" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>293</v>
+      </c>
+      <c r="D312" t="n">
+        <v>292.72</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F312" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="G312" t="n">
+        <v>292.72</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I312" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="J312" t="n">
+        <v>284.32</v>
+      </c>
+      <c r="K312" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1946</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1964.08</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-18.08</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1954.9</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1972.01</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-17.11</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1940.5</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1921.32</v>
+      </c>
+      <c r="K313" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>475</v>
+      </c>
+      <c r="D314" t="n">
+        <v>478.23</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="F314" t="n">
+        <v>482</v>
+      </c>
+      <c r="G314" t="n">
+        <v>478.23</v>
+      </c>
+      <c r="H314" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I314" t="n">
+        <v>475</v>
+      </c>
+      <c r="J314" t="n">
+        <v>462.93</v>
+      </c>
+      <c r="K314" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="H315" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="I315" t="n">
+        <v>1851</v>
+      </c>
+      <c r="J315" t="n">
+        <v>1832.84</v>
+      </c>
+      <c r="K315" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>5735</v>
+      </c>
+      <c r="D316" t="n">
+        <v>5813.66</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-78.66</v>
+      </c>
+      <c r="F316" t="n">
+        <v>5735</v>
+      </c>
+      <c r="G316" t="n">
+        <v>5813.66</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-78.66</v>
+      </c>
+      <c r="I316" t="n">
+        <v>5642</v>
+      </c>
+      <c r="J316" t="n">
+        <v>5557.57</v>
+      </c>
+      <c r="K316" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D317" t="n">
+        <v>3190.49</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="F317" t="n">
+        <v>3211.4</v>
+      </c>
+      <c r="G317" t="n">
+        <v>3249.54</v>
+      </c>
+      <c r="H317" t="n">
+        <v>-38.14</v>
+      </c>
+      <c r="I317" t="n">
+        <v>3132</v>
+      </c>
+      <c r="J317" t="n">
+        <v>3166.76</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-34.76</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1789.64</v>
+      </c>
+      <c r="E318" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1789.64</v>
+      </c>
+      <c r="H318" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I318" t="n">
+        <v>1757</v>
+      </c>
+      <c r="J318" t="n">
+        <v>1725.02</v>
+      </c>
+      <c r="K318" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>5667.5</v>
+      </c>
+      <c r="D319" t="n">
+        <v>5542.6</v>
+      </c>
+      <c r="E319" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="F319" t="n">
+        <v>5722</v>
+      </c>
+      <c r="G319" t="n">
+        <v>5725.33</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I319" t="n">
+        <v>5602</v>
+      </c>
+      <c r="J319" t="n">
+        <v>5577.53</v>
+      </c>
+      <c r="K319" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>990</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1027.79</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-37.79</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1004</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1027.79</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-23.79</v>
+      </c>
+      <c r="I320" t="n">
+        <v>968.55</v>
+      </c>
+      <c r="J320" t="n">
+        <v>956.1900000000001</v>
+      </c>
+      <c r="K320" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>11724</v>
+      </c>
+      <c r="D321" t="n">
+        <v>11687.68</v>
+      </c>
+      <c r="E321" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="F321" t="n">
+        <v>11870</v>
+      </c>
+      <c r="G321" t="n">
+        <v>11830.43</v>
+      </c>
+      <c r="H321" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="I321" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J321" t="n">
+        <v>11524.58</v>
+      </c>
+      <c r="K321" t="n">
+        <v>125.42</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>328</v>
+      </c>
+      <c r="D322" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="E322" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="F322" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="G322" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I322" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="J322" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1292.12</v>
+      </c>
+      <c r="E323" t="n">
+        <v>-27.12</v>
+      </c>
+      <c r="F323" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1292.12</v>
+      </c>
+      <c r="H323" t="n">
+        <v>-25.12</v>
+      </c>
+      <c r="I323" t="n">
+        <v>1252</v>
+      </c>
+      <c r="J323" t="n">
+        <v>1223.39</v>
+      </c>
+      <c r="K323" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D324" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="F324" t="n">
+        <v>117.52</v>
+      </c>
+      <c r="G324" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="H324" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="I324" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="J324" t="n">
+        <v>113.63</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1105.03</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-71.03</v>
+      </c>
+      <c r="F325" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1105.03</v>
+      </c>
+      <c r="H325" t="n">
+        <v>-64.58</v>
+      </c>
+      <c r="I325" t="n">
+        <v>1024.6</v>
+      </c>
+      <c r="J325" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="K325" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="D326" t="n">
+        <v>433.84</v>
+      </c>
+      <c r="E326" t="n">
+        <v>-39.39</v>
+      </c>
+      <c r="F326" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="G326" t="n">
+        <v>433.84</v>
+      </c>
+      <c r="H326" t="n">
+        <v>-36.34</v>
+      </c>
+      <c r="I326" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>390.67</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>2139</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2076.31</v>
+      </c>
+      <c r="E327" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="F327" t="n">
+        <v>2162.2</v>
+      </c>
+      <c r="G327" t="n">
+        <v>2118.48</v>
+      </c>
+      <c r="H327" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I327" t="n">
+        <v>2126.3</v>
+      </c>
+      <c r="J327" t="n">
+        <v>2066.74</v>
+      </c>
+      <c r="K327" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3231.44</v>
+      </c>
+      <c r="E328" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="F328" t="n">
+        <v>3453.9</v>
+      </c>
+      <c r="G328" t="n">
+        <v>3365.55</v>
+      </c>
+      <c r="H328" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="I328" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="J328" t="n">
+        <v>3329.82</v>
+      </c>
+      <c r="K328" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>173</v>
+      </c>
+      <c r="D329" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F329" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="G329" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I329" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="J329" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="K329" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>4093</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="E330" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F330" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G330" t="n">
+        <v>4101.72</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="I330" t="n">
+        <v>4061.4</v>
+      </c>
+      <c r="J330" t="n">
+        <v>4014.48</v>
+      </c>
+      <c r="K330" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1625.95</v>
+      </c>
+      <c r="E331" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1651.3</v>
+      </c>
+      <c r="G331" t="n">
+        <v>1625.95</v>
+      </c>
+      <c r="H331" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I331" t="n">
+        <v>1590</v>
+      </c>
+      <c r="J331" t="n">
+        <v>1568.44</v>
+      </c>
+      <c r="K331" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>11320</v>
+      </c>
+      <c r="D332" t="n">
+        <v>11551.48</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-231.48</v>
+      </c>
+      <c r="F332" t="n">
+        <v>11410</v>
+      </c>
+      <c r="G332" t="n">
+        <v>11551.48</v>
+      </c>
+      <c r="H332" t="n">
+        <v>-141.48</v>
+      </c>
+      <c r="I332" t="n">
+        <v>11280</v>
+      </c>
+      <c r="J332" t="n">
+        <v>11031.46</v>
+      </c>
+      <c r="K332" t="n">
+        <v>248.54</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2552</v>
+      </c>
+      <c r="D333" t="n">
+        <v>2591.15</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-39.15</v>
+      </c>
+      <c r="F333" t="n">
+        <v>2596</v>
+      </c>
+      <c r="G333" t="n">
+        <v>2591.15</v>
+      </c>
+      <c r="H333" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I333" t="n">
+        <v>2542</v>
+      </c>
+      <c r="J333" t="n">
+        <v>2463.59</v>
+      </c>
+      <c r="K333" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="E334" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G334" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="H334" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="I334" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="K334" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>876.9</v>
+      </c>
+      <c r="D335" t="n">
+        <v>884.3099999999999</v>
+      </c>
+      <c r="E335" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="F335" t="n">
+        <v>880.9</v>
+      </c>
+      <c r="G335" t="n">
+        <v>884.3099999999999</v>
+      </c>
+      <c r="H335" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="I335" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="J335" t="n">
+        <v>850.8099999999999</v>
+      </c>
+      <c r="K335" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1350.1</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1389.34</v>
+      </c>
+      <c r="E336" t="n">
+        <v>-39.24</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1367.8</v>
+      </c>
+      <c r="G336" t="n">
+        <v>1389.34</v>
+      </c>
+      <c r="H336" t="n">
+        <v>-21.54</v>
+      </c>
+      <c r="I336" t="n">
+        <v>1345.2</v>
+      </c>
+      <c r="J336" t="n">
+        <v>1296.01</v>
+      </c>
+      <c r="K336" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="D337" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="E337" t="n">
+        <v>-11.63</v>
+      </c>
+      <c r="F337" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="G337" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="H337" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="I337" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J337" t="n">
+        <v>178.56</v>
+      </c>
+      <c r="K337" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2150.93</v>
+      </c>
+      <c r="E338" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="F338" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="G338" t="n">
+        <v>2217.3</v>
+      </c>
+      <c r="H338" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I338" t="n">
+        <v>2211.1</v>
+      </c>
+      <c r="J338" t="n">
+        <v>2159.24</v>
+      </c>
+      <c r="K338" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="D339" t="n">
+        <v>480.87</v>
+      </c>
+      <c r="E339" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="F339" t="n">
+        <v>523</v>
+      </c>
+      <c r="G339" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="H339" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I339" t="n">
+        <v>512.15</v>
+      </c>
+      <c r="J339" t="n">
+        <v>498.74</v>
+      </c>
+      <c r="K339" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D340" t="n">
+        <v>14413.31</v>
+      </c>
+      <c r="E340" t="n">
+        <v>436.69</v>
+      </c>
+      <c r="F340" t="n">
+        <v>14924</v>
+      </c>
+      <c r="G340" t="n">
+        <v>14511.32</v>
+      </c>
+      <c r="H340" t="n">
+        <v>412.68</v>
+      </c>
+      <c r="I340" t="n">
+        <v>14620</v>
+      </c>
+      <c r="J340" t="n">
+        <v>14376.37</v>
+      </c>
+      <c r="K340" t="n">
+        <v>243.63</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -16725,7 +18389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17422,6 +19086,58 @@
       </c>
       <c r="N13" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -19443,7 +21159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20140,6 +21856,58 @@
       </c>
       <c r="N13" t="n">
         <v>7.28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>328</v>
+      </c>
+      <c r="D14" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I14" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20153,7 +21921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20850,6 +22618,58 @@
       </c>
       <c r="N13" t="n">
         <v>3.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14413.31</v>
+      </c>
+      <c r="E14" t="n">
+        <v>436.69</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14924</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14511.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>412.68</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14620</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14376.37</v>
+      </c>
+      <c r="K14" t="n">
+        <v>243.63</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -20863,7 +22683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21560,6 +23380,58 @@
       </c>
       <c r="N13" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1851</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1832.84</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -21573,7 +23445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22166,6 +24038,58 @@
       </c>
       <c r="N11" t="n">
         <v>2.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5667.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5542.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5722</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5725.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5602</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5577.53</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
@@ -22179,7 +24103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22876,6 +24800,58 @@
       </c>
       <c r="N13" t="n">
         <v>3.96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>117.52</v>
+      </c>
+      <c r="G14" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="I14" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="J14" t="n">
+        <v>113.63</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>4.58</v>
       </c>
     </row>
   </sheetData>
@@ -22889,7 +24865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23534,6 +25510,58 @@
       </c>
       <c r="N12" t="n">
         <v>6.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3231.44</v>
+      </c>
+      <c r="E13" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3453.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3365.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3329.82</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5.59</v>
       </c>
     </row>
   </sheetData>
@@ -23547,7 +25575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24192,6 +26220,58 @@
       </c>
       <c r="N12" t="n">
         <v>7.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="D13" t="n">
+        <v>480.87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="F13" t="n">
+        <v>523</v>
+      </c>
+      <c r="G13" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>512.15</v>
+      </c>
+      <c r="J13" t="n">
+        <v>498.74</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>7.11</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -16484,31 +16484,31 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2032.5</v>
+        <v>2016</v>
       </c>
       <c r="D309" t="n">
         <v>2054.95</v>
       </c>
       <c r="E309" t="n">
-        <v>-22.45</v>
+        <v>-38.95</v>
       </c>
       <c r="F309" t="n">
-        <v>2032.5</v>
+        <v>2030.1</v>
       </c>
       <c r="G309" t="n">
         <v>2054.95</v>
       </c>
       <c r="H309" t="n">
-        <v>-22.45</v>
+        <v>-24.85</v>
       </c>
       <c r="I309" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="J309" t="n">
         <v>1991.09</v>
       </c>
       <c r="K309" t="n">
-        <v>13.91</v>
+        <v>21.91</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="310">
@@ -16536,31 +16536,31 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>678.1</v>
+        <v>676.15</v>
       </c>
       <c r="D310" t="n">
         <v>685.01</v>
       </c>
       <c r="E310" t="n">
-        <v>-6.91</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F310" t="n">
-        <v>684.45</v>
+        <v>682.45</v>
       </c>
       <c r="G310" t="n">
         <v>685.01</v>
       </c>
       <c r="H310" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.56</v>
       </c>
       <c r="I310" t="n">
-        <v>675.25</v>
+        <v>671.95</v>
       </c>
       <c r="J310" t="n">
         <v>655.47</v>
       </c>
       <c r="K310" t="n">
-        <v>19.78</v>
+        <v>16.48</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="311">
@@ -16588,31 +16588,31 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1048.7</v>
+        <v>1048</v>
       </c>
       <c r="D311" t="n">
         <v>1050.46</v>
       </c>
       <c r="E311" t="n">
-        <v>-1.76</v>
+        <v>-2.46</v>
       </c>
       <c r="F311" t="n">
-        <v>1054.7</v>
+        <v>1052.9</v>
       </c>
       <c r="G311" t="n">
         <v>1050.46</v>
       </c>
       <c r="H311" t="n">
-        <v>4.24</v>
+        <v>2.44</v>
       </c>
       <c r="I311" t="n">
-        <v>1040.1</v>
+        <v>1045.7</v>
       </c>
       <c r="J311" t="n">
         <v>1019.46</v>
       </c>
       <c r="K311" t="n">
-        <v>20.64</v>
+        <v>26.24</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="312">
@@ -16640,31 +16640,31 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>293</v>
+        <v>291.4</v>
       </c>
       <c r="D312" t="n">
         <v>292.72</v>
       </c>
       <c r="E312" t="n">
-        <v>0.28</v>
+        <v>-1.32</v>
       </c>
       <c r="F312" t="n">
-        <v>293.5</v>
+        <v>293.75</v>
       </c>
       <c r="G312" t="n">
         <v>292.72</v>
       </c>
       <c r="H312" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="I312" t="n">
-        <v>289.75</v>
+        <v>286.6</v>
       </c>
       <c r="J312" t="n">
         <v>284.32</v>
       </c>
       <c r="K312" t="n">
-        <v>5.43</v>
+        <v>2.28</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="313">
@@ -16692,31 +16692,31 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1946</v>
+        <v>1941.7</v>
       </c>
       <c r="D313" t="n">
         <v>1964.08</v>
       </c>
       <c r="E313" t="n">
-        <v>-18.08</v>
+        <v>-22.38</v>
       </c>
       <c r="F313" t="n">
-        <v>1954.9</v>
+        <v>1952.2</v>
       </c>
       <c r="G313" t="n">
         <v>1972.01</v>
       </c>
       <c r="H313" t="n">
-        <v>-17.11</v>
+        <v>-19.81</v>
       </c>
       <c r="I313" t="n">
-        <v>1940.5</v>
+        <v>1933</v>
       </c>
       <c r="J313" t="n">
         <v>1921.32</v>
       </c>
       <c r="K313" t="n">
-        <v>19.18</v>
+        <v>11.68</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="314">
@@ -16744,31 +16744,31 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>475</v>
+        <v>480.9</v>
       </c>
       <c r="D314" t="n">
         <v>478.23</v>
       </c>
       <c r="E314" t="n">
-        <v>-3.23</v>
+        <v>2.67</v>
       </c>
       <c r="F314" t="n">
-        <v>482</v>
+        <v>481.5</v>
       </c>
       <c r="G314" t="n">
         <v>478.23</v>
       </c>
       <c r="H314" t="n">
-        <v>3.77</v>
+        <v>3.27</v>
       </c>
       <c r="I314" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J314" t="n">
         <v>462.93</v>
       </c>
       <c r="K314" t="n">
-        <v>12.07</v>
+        <v>2.07</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="315">
@@ -16796,31 +16796,31 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1891.7</v>
+        <v>1882</v>
       </c>
       <c r="D315" t="n">
         <v>1913.14</v>
       </c>
       <c r="E315" t="n">
-        <v>-21.44</v>
+        <v>-31.14</v>
       </c>
       <c r="F315" t="n">
-        <v>1891.7</v>
+        <v>1888.5</v>
       </c>
       <c r="G315" t="n">
         <v>1913.14</v>
       </c>
       <c r="H315" t="n">
-        <v>-21.44</v>
+        <v>-24.64</v>
       </c>
       <c r="I315" t="n">
-        <v>1851</v>
+        <v>1826.5</v>
       </c>
       <c r="J315" t="n">
         <v>1832.84</v>
       </c>
       <c r="K315" t="n">
-        <v>18.16</v>
+        <v>-6.34</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="316">
@@ -16848,31 +16848,31 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="D316" t="n">
         <v>5813.66</v>
       </c>
       <c r="E316" t="n">
-        <v>-78.66</v>
+        <v>-73.16</v>
       </c>
       <c r="F316" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="G316" t="n">
         <v>5813.66</v>
       </c>
       <c r="H316" t="n">
-        <v>-78.66</v>
+        <v>-73.16</v>
       </c>
       <c r="I316" t="n">
-        <v>5642</v>
+        <v>5670</v>
       </c>
       <c r="J316" t="n">
         <v>5557.57</v>
       </c>
       <c r="K316" t="n">
-        <v>84.43000000000001</v>
+        <v>112.43</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="317">
@@ -16900,31 +16900,31 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3185</v>
+        <v>3126</v>
       </c>
       <c r="D317" t="n">
         <v>3190.49</v>
       </c>
       <c r="E317" t="n">
-        <v>-5.49</v>
+        <v>-64.48999999999999</v>
       </c>
       <c r="F317" t="n">
-        <v>3211.4</v>
+        <v>3133.2</v>
       </c>
       <c r="G317" t="n">
         <v>3249.54</v>
       </c>
       <c r="H317" t="n">
-        <v>-38.14</v>
+        <v>-116.34</v>
       </c>
       <c r="I317" t="n">
-        <v>3132</v>
+        <v>3006</v>
       </c>
       <c r="J317" t="n">
         <v>3166.76</v>
       </c>
       <c r="K317" t="n">
-        <v>-34.76</v>
+        <v>-160.76</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>0.17</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="318">
@@ -16952,31 +16952,31 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1795.2</v>
+        <v>1779.6</v>
       </c>
       <c r="D318" t="n">
         <v>1789.64</v>
       </c>
       <c r="E318" t="n">
-        <v>5.56</v>
+        <v>-10.04</v>
       </c>
       <c r="F318" t="n">
-        <v>1799</v>
+        <v>1803.4</v>
       </c>
       <c r="G318" t="n">
         <v>1789.64</v>
       </c>
       <c r="H318" t="n">
-        <v>9.359999999999999</v>
+        <v>13.76</v>
       </c>
       <c r="I318" t="n">
-        <v>1757</v>
+        <v>1764</v>
       </c>
       <c r="J318" t="n">
         <v>1725.02</v>
       </c>
       <c r="K318" t="n">
-        <v>31.98</v>
+        <v>38.98</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -17004,31 +17004,31 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>5667.5</v>
+        <v>5674</v>
       </c>
       <c r="D319" t="n">
         <v>5542.6</v>
       </c>
       <c r="E319" t="n">
-        <v>124.9</v>
+        <v>131.4</v>
       </c>
       <c r="F319" t="n">
-        <v>5722</v>
+        <v>5706</v>
       </c>
       <c r="G319" t="n">
         <v>5725.33</v>
       </c>
       <c r="H319" t="n">
-        <v>-3.33</v>
+        <v>-19.33</v>
       </c>
       <c r="I319" t="n">
-        <v>5602</v>
+        <v>5534</v>
       </c>
       <c r="J319" t="n">
         <v>5577.53</v>
       </c>
       <c r="K319" t="n">
-        <v>24.47</v>
+        <v>-43.53</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="320">
@@ -17056,31 +17056,31 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>990</v>
+        <v>973.4</v>
       </c>
       <c r="D320" t="n">
         <v>1027.79</v>
       </c>
       <c r="E320" t="n">
-        <v>-37.79</v>
+        <v>-54.39</v>
       </c>
       <c r="F320" t="n">
-        <v>1004</v>
+        <v>989.55</v>
       </c>
       <c r="G320" t="n">
         <v>1027.79</v>
       </c>
       <c r="H320" t="n">
-        <v>-23.79</v>
+        <v>-38.24</v>
       </c>
       <c r="I320" t="n">
-        <v>968.55</v>
+        <v>942.15</v>
       </c>
       <c r="J320" t="n">
         <v>956.1900000000001</v>
       </c>
       <c r="K320" t="n">
-        <v>12.36</v>
+        <v>-14.04</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>3.68</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="321">
@@ -17108,31 +17108,31 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11724</v>
+        <v>11826</v>
       </c>
       <c r="D321" t="n">
         <v>11687.68</v>
       </c>
       <c r="E321" t="n">
-        <v>36.32</v>
+        <v>138.32</v>
       </c>
       <c r="F321" t="n">
-        <v>11870</v>
+        <v>11917</v>
       </c>
       <c r="G321" t="n">
         <v>11830.43</v>
       </c>
       <c r="H321" t="n">
-        <v>39.57</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>11650</v>
+        <v>11680</v>
       </c>
       <c r="J321" t="n">
         <v>11524.58</v>
       </c>
       <c r="K321" t="n">
-        <v>125.42</v>
+        <v>155.42</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>0.31</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="322">
@@ -17160,31 +17160,31 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>328</v>
+        <v>327.95</v>
       </c>
       <c r="D322" t="n">
         <v>306.55</v>
       </c>
       <c r="E322" t="n">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="F322" t="n">
-        <v>331.7</v>
+        <v>328.5</v>
       </c>
       <c r="G322" t="n">
         <v>331.99</v>
       </c>
       <c r="H322" t="n">
-        <v>-0.29</v>
+        <v>-3.49</v>
       </c>
       <c r="I322" t="n">
-        <v>324.1</v>
+        <v>321.35</v>
       </c>
       <c r="J322" t="n">
         <v>323.44</v>
       </c>
       <c r="K322" t="n">
-        <v>0.66</v>
+        <v>-2.09</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="323">
@@ -17212,31 +17212,31 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1265</v>
+        <v>1260.5</v>
       </c>
       <c r="D323" t="n">
         <v>1292.12</v>
       </c>
       <c r="E323" t="n">
-        <v>-27.12</v>
+        <v>-31.62</v>
       </c>
       <c r="F323" t="n">
-        <v>1267</v>
+        <v>1282.6</v>
       </c>
       <c r="G323" t="n">
         <v>1292.12</v>
       </c>
       <c r="H323" t="n">
-        <v>-25.12</v>
+        <v>-9.52</v>
       </c>
       <c r="I323" t="n">
-        <v>1252</v>
+        <v>1260.5</v>
       </c>
       <c r="J323" t="n">
         <v>1223.39</v>
       </c>
       <c r="K323" t="n">
-        <v>28.61</v>
+        <v>37.11</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="324">
@@ -17264,31 +17264,31 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>116.55</v>
+        <v>118</v>
       </c>
       <c r="D324" t="n">
         <v>122.14</v>
       </c>
       <c r="E324" t="n">
-        <v>-5.59</v>
+        <v>-4.14</v>
       </c>
       <c r="F324" t="n">
-        <v>117.52</v>
+        <v>119.1</v>
       </c>
       <c r="G324" t="n">
         <v>122.14</v>
       </c>
       <c r="H324" t="n">
-        <v>-4.62</v>
+        <v>-3.04</v>
       </c>
       <c r="I324" t="n">
-        <v>115.41</v>
+        <v>117.44</v>
       </c>
       <c r="J324" t="n">
         <v>113.63</v>
       </c>
       <c r="K324" t="n">
-        <v>1.78</v>
+        <v>3.81</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>4.58</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="325">
@@ -17316,31 +17316,31 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1034</v>
+        <v>1029.85</v>
       </c>
       <c r="D325" t="n">
         <v>1105.03</v>
       </c>
       <c r="E325" t="n">
-        <v>-71.03</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="F325" t="n">
-        <v>1040.45</v>
+        <v>1048</v>
       </c>
       <c r="G325" t="n">
         <v>1105.03</v>
       </c>
       <c r="H325" t="n">
-        <v>-64.58</v>
+        <v>-57.03</v>
       </c>
       <c r="I325" t="n">
-        <v>1024.6</v>
+        <v>1013</v>
       </c>
       <c r="J325" t="n">
         <v>1022.2</v>
       </c>
       <c r="K325" t="n">
-        <v>2.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6.43</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="326">
@@ -17368,31 +17368,31 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>394.45</v>
+        <v>385.6</v>
       </c>
       <c r="D326" t="n">
         <v>433.84</v>
       </c>
       <c r="E326" t="n">
-        <v>-39.39</v>
+        <v>-48.24</v>
       </c>
       <c r="F326" t="n">
-        <v>397.5</v>
+        <v>395.75</v>
       </c>
       <c r="G326" t="n">
         <v>433.84</v>
       </c>
       <c r="H326" t="n">
-        <v>-36.34</v>
+        <v>-38.09</v>
       </c>
       <c r="I326" t="n">
-        <v>384.6</v>
+        <v>385.1</v>
       </c>
       <c r="J326" t="n">
         <v>390.67</v>
       </c>
       <c r="K326" t="n">
-        <v>-6.07</v>
+        <v>-5.57</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -17401,11 +17401,11 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N326" t="n">
-        <v>9.08</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="327">
@@ -17420,31 +17420,31 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="D327" t="n">
         <v>2076.31</v>
       </c>
       <c r="E327" t="n">
-        <v>62.69</v>
+        <v>63.69</v>
       </c>
       <c r="F327" t="n">
-        <v>2162.2</v>
+        <v>2153.7</v>
       </c>
       <c r="G327" t="n">
         <v>2118.48</v>
       </c>
       <c r="H327" t="n">
-        <v>43.72</v>
+        <v>35.22</v>
       </c>
       <c r="I327" t="n">
-        <v>2126.3</v>
+        <v>2125</v>
       </c>
       <c r="J327" t="n">
         <v>2066.74</v>
       </c>
       <c r="K327" t="n">
-        <v>59.56</v>
+        <v>58.26</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="328">
@@ -17472,31 +17472,31 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3412.2</v>
+        <v>3424.8</v>
       </c>
       <c r="D328" t="n">
         <v>3231.44</v>
       </c>
       <c r="E328" t="n">
-        <v>180.76</v>
+        <v>193.36</v>
       </c>
       <c r="F328" t="n">
-        <v>3453.9</v>
+        <v>3456.4</v>
       </c>
       <c r="G328" t="n">
         <v>3365.55</v>
       </c>
       <c r="H328" t="n">
-        <v>88.34999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="I328" t="n">
-        <v>3412.2</v>
+        <v>3401</v>
       </c>
       <c r="J328" t="n">
         <v>3329.82</v>
       </c>
       <c r="K328" t="n">
-        <v>82.38</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="329">
@@ -17524,31 +17524,31 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>173</v>
+        <v>173.8</v>
       </c>
       <c r="D329" t="n">
         <v>172.71</v>
       </c>
       <c r="E329" t="n">
-        <v>0.29</v>
+        <v>1.09</v>
       </c>
       <c r="F329" t="n">
-        <v>173.69</v>
+        <v>175.57</v>
       </c>
       <c r="G329" t="n">
         <v>172.71</v>
       </c>
       <c r="H329" t="n">
-        <v>0.98</v>
+        <v>2.86</v>
       </c>
       <c r="I329" t="n">
-        <v>172.3</v>
+        <v>172.61</v>
       </c>
       <c r="J329" t="n">
         <v>167.6</v>
       </c>
       <c r="K329" t="n">
-        <v>4.7</v>
+        <v>5.01</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="330">
@@ -17576,31 +17576,31 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4093</v>
+        <v>4081</v>
       </c>
       <c r="D330" t="n">
         <v>4062.2</v>
       </c>
       <c r="E330" t="n">
-        <v>30.8</v>
+        <v>18.8</v>
       </c>
       <c r="F330" t="n">
-        <v>4100</v>
+        <v>4084.9</v>
       </c>
       <c r="G330" t="n">
         <v>4101.72</v>
       </c>
       <c r="H330" t="n">
-        <v>-1.72</v>
+        <v>-16.82</v>
       </c>
       <c r="I330" t="n">
-        <v>4061.4</v>
+        <v>4048.3</v>
       </c>
       <c r="J330" t="n">
         <v>4014.48</v>
       </c>
       <c r="K330" t="n">
-        <v>46.92</v>
+        <v>33.82</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="331">
@@ -17628,31 +17628,31 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1631</v>
+        <v>1585.5</v>
       </c>
       <c r="D331" t="n">
         <v>1625.95</v>
       </c>
       <c r="E331" t="n">
-        <v>5.05</v>
+        <v>-40.45</v>
       </c>
       <c r="F331" t="n">
-        <v>1651.3</v>
+        <v>1610</v>
       </c>
       <c r="G331" t="n">
         <v>1625.95</v>
       </c>
       <c r="H331" t="n">
-        <v>25.35</v>
+        <v>-15.95</v>
       </c>
       <c r="I331" t="n">
-        <v>1590</v>
+        <v>1581</v>
       </c>
       <c r="J331" t="n">
         <v>1568.44</v>
       </c>
       <c r="K331" t="n">
-        <v>21.56</v>
+        <v>12.56</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>0.31</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="332">
@@ -17680,31 +17680,31 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>11320</v>
+        <v>11368</v>
       </c>
       <c r="D332" t="n">
         <v>11551.48</v>
       </c>
       <c r="E332" t="n">
-        <v>-231.48</v>
+        <v>-183.48</v>
       </c>
       <c r="F332" t="n">
-        <v>11410</v>
+        <v>11423</v>
       </c>
       <c r="G332" t="n">
         <v>11551.48</v>
       </c>
       <c r="H332" t="n">
-        <v>-141.48</v>
+        <v>-128.48</v>
       </c>
       <c r="I332" t="n">
-        <v>11280</v>
+        <v>11303</v>
       </c>
       <c r="J332" t="n">
         <v>11031.46</v>
       </c>
       <c r="K332" t="n">
-        <v>248.54</v>
+        <v>271.54</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="333">
@@ -17732,31 +17732,31 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2552</v>
+        <v>2570</v>
       </c>
       <c r="D333" t="n">
         <v>2591.15</v>
       </c>
       <c r="E333" t="n">
-        <v>-39.15</v>
+        <v>-21.15</v>
       </c>
       <c r="F333" t="n">
-        <v>2596</v>
+        <v>2583.2</v>
       </c>
       <c r="G333" t="n">
         <v>2591.15</v>
       </c>
       <c r="H333" t="n">
-        <v>4.85</v>
+        <v>-7.95</v>
       </c>
       <c r="I333" t="n">
-        <v>2542</v>
+        <v>2552</v>
       </c>
       <c r="J333" t="n">
         <v>2463.59</v>
       </c>
       <c r="K333" t="n">
-        <v>78.41</v>
+        <v>88.41</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>1.51</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="334">
@@ -17784,31 +17784,31 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D334" t="n">
         <v>1205.51</v>
       </c>
       <c r="E334" t="n">
-        <v>-6.51</v>
+        <v>-2.51</v>
       </c>
       <c r="F334" t="n">
-        <v>1214</v>
+        <v>1222.9</v>
       </c>
       <c r="G334" t="n">
         <v>1205.51</v>
       </c>
       <c r="H334" t="n">
-        <v>8.49</v>
+        <v>17.39</v>
       </c>
       <c r="I334" t="n">
-        <v>1190.1</v>
+        <v>1186</v>
       </c>
       <c r="J334" t="n">
         <v>1171.8</v>
       </c>
       <c r="K334" t="n">
-        <v>18.3</v>
+        <v>14.2</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="335">
@@ -17836,31 +17836,31 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>876.9</v>
+        <v>871</v>
       </c>
       <c r="D335" t="n">
         <v>884.3099999999999</v>
       </c>
       <c r="E335" t="n">
-        <v>-7.41</v>
+        <v>-13.31</v>
       </c>
       <c r="F335" t="n">
-        <v>880.9</v>
+        <v>883.8</v>
       </c>
       <c r="G335" t="n">
         <v>884.3099999999999</v>
       </c>
       <c r="H335" t="n">
-        <v>-3.41</v>
+        <v>-0.51</v>
       </c>
       <c r="I335" t="n">
-        <v>870.5</v>
+        <v>871</v>
       </c>
       <c r="J335" t="n">
         <v>850.8099999999999</v>
       </c>
       <c r="K335" t="n">
-        <v>19.69</v>
+        <v>20.19</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>0.84</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="336">
@@ -17888,31 +17888,31 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1350.1</v>
+        <v>1360.9</v>
       </c>
       <c r="D336" t="n">
         <v>1389.34</v>
       </c>
       <c r="E336" t="n">
-        <v>-39.24</v>
+        <v>-28.44</v>
       </c>
       <c r="F336" t="n">
-        <v>1367.8</v>
+        <v>1390.1</v>
       </c>
       <c r="G336" t="n">
         <v>1389.34</v>
       </c>
       <c r="H336" t="n">
-        <v>-21.54</v>
+        <v>0.76</v>
       </c>
       <c r="I336" t="n">
-        <v>1345.2</v>
+        <v>1355.3</v>
       </c>
       <c r="J336" t="n">
         <v>1296.01</v>
       </c>
       <c r="K336" t="n">
-        <v>49.19</v>
+        <v>59.29</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2.82</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="337">
@@ -17940,31 +17940,31 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>183.45</v>
+        <v>184.68</v>
       </c>
       <c r="D337" t="n">
         <v>195.08</v>
       </c>
       <c r="E337" t="n">
-        <v>-11.63</v>
+        <v>-10.4</v>
       </c>
       <c r="F337" t="n">
-        <v>185.3</v>
+        <v>189.46</v>
       </c>
       <c r="G337" t="n">
         <v>195.08</v>
       </c>
       <c r="H337" t="n">
-        <v>-9.779999999999999</v>
+        <v>-5.62</v>
       </c>
       <c r="I337" t="n">
-        <v>182.5</v>
+        <v>184.39</v>
       </c>
       <c r="J337" t="n">
         <v>178.56</v>
       </c>
       <c r="K337" t="n">
-        <v>3.94</v>
+        <v>5.83</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>5.96</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="338">
@@ -17992,31 +17992,31 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2218.8</v>
+        <v>2227</v>
       </c>
       <c r="D338" t="n">
         <v>2150.93</v>
       </c>
       <c r="E338" t="n">
-        <v>67.87</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F338" t="n">
-        <v>2251.7</v>
+        <v>2233.7</v>
       </c>
       <c r="G338" t="n">
         <v>2217.3</v>
       </c>
       <c r="H338" t="n">
-        <v>34.4</v>
+        <v>16.4</v>
       </c>
       <c r="I338" t="n">
-        <v>2211.1</v>
+        <v>2180.4</v>
       </c>
       <c r="J338" t="n">
         <v>2159.24</v>
       </c>
       <c r="K338" t="n">
-        <v>51.86</v>
+        <v>21.16</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="339">
@@ -18044,31 +18044,31 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>515.05</v>
+        <v>519</v>
       </c>
       <c r="D339" t="n">
         <v>480.87</v>
       </c>
       <c r="E339" t="n">
-        <v>34.18</v>
+        <v>38.13</v>
       </c>
       <c r="F339" t="n">
-        <v>523</v>
+        <v>524.4</v>
       </c>
       <c r="G339" t="n">
         <v>505.57</v>
       </c>
       <c r="H339" t="n">
-        <v>17.43</v>
+        <v>18.83</v>
       </c>
       <c r="I339" t="n">
-        <v>512.15</v>
+        <v>513.8</v>
       </c>
       <c r="J339" t="n">
         <v>498.74</v>
       </c>
       <c r="K339" t="n">
-        <v>13.41</v>
+        <v>15.06</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>7.11</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="340">
@@ -18105,22 +18105,22 @@
         <v>436.69</v>
       </c>
       <c r="F340" t="n">
-        <v>14924</v>
+        <v>14953</v>
       </c>
       <c r="G340" t="n">
         <v>14511.32</v>
       </c>
       <c r="H340" t="n">
-        <v>412.68</v>
+        <v>441.68</v>
       </c>
       <c r="I340" t="n">
-        <v>14620</v>
+        <v>14470</v>
       </c>
       <c r="J340" t="n">
         <v>14376.37</v>
       </c>
       <c r="K340" t="n">
-        <v>243.63</v>
+        <v>93.63</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -19100,31 +19100,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D14" t="n">
         <v>1205.51</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.51</v>
+        <v>-2.51</v>
       </c>
       <c r="F14" t="n">
-        <v>1214</v>
+        <v>1222.9</v>
       </c>
       <c r="G14" t="n">
         <v>1205.51</v>
       </c>
       <c r="H14" t="n">
-        <v>8.49</v>
+        <v>17.39</v>
       </c>
       <c r="I14" t="n">
-        <v>1190.1</v>
+        <v>1186</v>
       </c>
       <c r="J14" t="n">
         <v>1171.8</v>
       </c>
       <c r="K14" t="n">
-        <v>18.3</v>
+        <v>14.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -21870,31 +21870,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>328</v>
+        <v>327.95</v>
       </c>
       <c r="D14" t="n">
         <v>306.55</v>
       </c>
       <c r="E14" t="n">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="F14" t="n">
-        <v>331.7</v>
+        <v>328.5</v>
       </c>
       <c r="G14" t="n">
         <v>331.99</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.29</v>
+        <v>-3.49</v>
       </c>
       <c r="I14" t="n">
-        <v>324.1</v>
+        <v>321.35</v>
       </c>
       <c r="J14" t="n">
         <v>323.44</v>
       </c>
       <c r="K14" t="n">
-        <v>0.66</v>
+        <v>-2.09</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
     </row>
   </sheetData>
@@ -22641,22 +22641,22 @@
         <v>436.69</v>
       </c>
       <c r="F14" t="n">
-        <v>14924</v>
+        <v>14953</v>
       </c>
       <c r="G14" t="n">
         <v>14511.32</v>
       </c>
       <c r="H14" t="n">
-        <v>412.68</v>
+        <v>441.68</v>
       </c>
       <c r="I14" t="n">
-        <v>14620</v>
+        <v>14470</v>
       </c>
       <c r="J14" t="n">
         <v>14376.37</v>
       </c>
       <c r="K14" t="n">
-        <v>243.63</v>
+        <v>93.63</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -23394,31 +23394,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1891.7</v>
+        <v>1882</v>
       </c>
       <c r="D14" t="n">
         <v>1913.14</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.44</v>
+        <v>-31.14</v>
       </c>
       <c r="F14" t="n">
-        <v>1891.7</v>
+        <v>1888.5</v>
       </c>
       <c r="G14" t="n">
         <v>1913.14</v>
       </c>
       <c r="H14" t="n">
-        <v>-21.44</v>
+        <v>-24.64</v>
       </c>
       <c r="I14" t="n">
-        <v>1851</v>
+        <v>1826.5</v>
       </c>
       <c r="J14" t="n">
         <v>1832.84</v>
       </c>
       <c r="K14" t="n">
-        <v>18.16</v>
+        <v>-6.34</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -24052,31 +24052,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5667.5</v>
+        <v>5674</v>
       </c>
       <c r="D12" t="n">
         <v>5542.6</v>
       </c>
       <c r="E12" t="n">
-        <v>124.9</v>
+        <v>131.4</v>
       </c>
       <c r="F12" t="n">
-        <v>5722</v>
+        <v>5706</v>
       </c>
       <c r="G12" t="n">
         <v>5725.33</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.33</v>
+        <v>-19.33</v>
       </c>
       <c r="I12" t="n">
-        <v>5602</v>
+        <v>5534</v>
       </c>
       <c r="J12" t="n">
         <v>5577.53</v>
       </c>
       <c r="K12" t="n">
-        <v>24.47</v>
+        <v>-43.53</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>
@@ -24814,31 +24814,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>116.55</v>
+        <v>118</v>
       </c>
       <c r="D14" t="n">
         <v>122.14</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.59</v>
+        <v>-4.14</v>
       </c>
       <c r="F14" t="n">
-        <v>117.52</v>
+        <v>119.1</v>
       </c>
       <c r="G14" t="n">
         <v>122.14</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.62</v>
+        <v>-3.04</v>
       </c>
       <c r="I14" t="n">
-        <v>115.41</v>
+        <v>117.44</v>
       </c>
       <c r="J14" t="n">
         <v>113.63</v>
       </c>
       <c r="K14" t="n">
-        <v>1.78</v>
+        <v>3.81</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.58</v>
+        <v>3.39</v>
       </c>
     </row>
   </sheetData>
@@ -25524,31 +25524,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3412.2</v>
+        <v>3424.8</v>
       </c>
       <c r="D13" t="n">
         <v>3231.44</v>
       </c>
       <c r="E13" t="n">
-        <v>180.76</v>
+        <v>193.36</v>
       </c>
       <c r="F13" t="n">
-        <v>3453.9</v>
+        <v>3456.4</v>
       </c>
       <c r="G13" t="n">
         <v>3365.55</v>
       </c>
       <c r="H13" t="n">
-        <v>88.34999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3412.2</v>
+        <v>3401</v>
       </c>
       <c r="J13" t="n">
         <v>3329.82</v>
       </c>
       <c r="K13" t="n">
-        <v>82.38</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
     </row>
   </sheetData>
@@ -26234,31 +26234,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>515.05</v>
+        <v>519</v>
       </c>
       <c r="D13" t="n">
         <v>480.87</v>
       </c>
       <c r="E13" t="n">
-        <v>34.18</v>
+        <v>38.13</v>
       </c>
       <c r="F13" t="n">
-        <v>523</v>
+        <v>524.4</v>
       </c>
       <c r="G13" t="n">
         <v>505.57</v>
       </c>
       <c r="H13" t="n">
-        <v>17.43</v>
+        <v>18.83</v>
       </c>
       <c r="I13" t="n">
-        <v>512.15</v>
+        <v>513.8</v>
       </c>
       <c r="J13" t="n">
         <v>498.74</v>
       </c>
       <c r="K13" t="n">
-        <v>13.41</v>
+        <v>15.06</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.11</v>
+        <v>7.93</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -16480,39 +16480,39 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2016</v>
+        <v>291.4</v>
       </c>
       <c r="D309" t="n">
-        <v>2054.95</v>
+        <v>292.72</v>
       </c>
       <c r="E309" t="n">
-        <v>-38.95</v>
+        <v>-1.32</v>
       </c>
       <c r="F309" t="n">
-        <v>2030.1</v>
+        <v>293.75</v>
       </c>
       <c r="G309" t="n">
-        <v>2054.95</v>
+        <v>292.72</v>
       </c>
       <c r="H309" t="n">
-        <v>-24.85</v>
+        <v>1.03</v>
       </c>
       <c r="I309" t="n">
-        <v>2013</v>
+        <v>286.6</v>
       </c>
       <c r="J309" t="n">
-        <v>1991.09</v>
+        <v>284.32</v>
       </c>
       <c r="K309" t="n">
-        <v>21.91</v>
+        <v>2.28</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -16521,7 +16521,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>1.9</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="310">
@@ -16532,35 +16532,35 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>676.15</v>
+        <v>5740.5</v>
       </c>
       <c r="D310" t="n">
-        <v>685.01</v>
+        <v>5813.66</v>
       </c>
       <c r="E310" t="n">
-        <v>-8.859999999999999</v>
+        <v>-73.16</v>
       </c>
       <c r="F310" t="n">
-        <v>682.45</v>
+        <v>5740.5</v>
       </c>
       <c r="G310" t="n">
-        <v>685.01</v>
+        <v>5813.66</v>
       </c>
       <c r="H310" t="n">
-        <v>-2.56</v>
+        <v>-73.16</v>
       </c>
       <c r="I310" t="n">
-        <v>671.95</v>
+        <v>5670</v>
       </c>
       <c r="J310" t="n">
-        <v>655.47</v>
+        <v>5557.57</v>
       </c>
       <c r="K310" t="n">
-        <v>16.48</v>
+        <v>112.43</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="311">
@@ -16584,35 +16584,35 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1048</v>
+        <v>1779.6</v>
       </c>
       <c r="D311" t="n">
-        <v>1050.46</v>
+        <v>1789.64</v>
       </c>
       <c r="E311" t="n">
-        <v>-2.46</v>
+        <v>-10.04</v>
       </c>
       <c r="F311" t="n">
-        <v>1052.9</v>
+        <v>1803.4</v>
       </c>
       <c r="G311" t="n">
-        <v>1050.46</v>
+        <v>1789.64</v>
       </c>
       <c r="H311" t="n">
-        <v>2.44</v>
+        <v>13.76</v>
       </c>
       <c r="I311" t="n">
-        <v>1045.7</v>
+        <v>1764</v>
       </c>
       <c r="J311" t="n">
-        <v>1019.46</v>
+        <v>1725.02</v>
       </c>
       <c r="K311" t="n">
-        <v>26.24</v>
+        <v>38.98</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="312">
@@ -16636,35 +16636,35 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>291.4</v>
+        <v>973.4</v>
       </c>
       <c r="D312" t="n">
-        <v>292.72</v>
+        <v>1027.79</v>
       </c>
       <c r="E312" t="n">
-        <v>-1.32</v>
+        <v>-54.39</v>
       </c>
       <c r="F312" t="n">
-        <v>293.75</v>
+        <v>989.55</v>
       </c>
       <c r="G312" t="n">
-        <v>292.72</v>
+        <v>1027.79</v>
       </c>
       <c r="H312" t="n">
-        <v>1.03</v>
+        <v>-38.24</v>
       </c>
       <c r="I312" t="n">
-        <v>286.6</v>
+        <v>942.15</v>
       </c>
       <c r="J312" t="n">
-        <v>284.32</v>
+        <v>956.1900000000001</v>
       </c>
       <c r="K312" t="n">
-        <v>2.28</v>
+        <v>-14.04</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>0.45</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="313">
@@ -16688,35 +16688,35 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1941.7</v>
+        <v>1260.5</v>
       </c>
       <c r="D313" t="n">
-        <v>1964.08</v>
+        <v>1292.12</v>
       </c>
       <c r="E313" t="n">
-        <v>-22.38</v>
+        <v>-31.62</v>
       </c>
       <c r="F313" t="n">
-        <v>1952.2</v>
+        <v>1282.6</v>
       </c>
       <c r="G313" t="n">
-        <v>1972.01</v>
+        <v>1292.12</v>
       </c>
       <c r="H313" t="n">
-        <v>-19.81</v>
+        <v>-9.52</v>
       </c>
       <c r="I313" t="n">
-        <v>1933</v>
+        <v>1260.5</v>
       </c>
       <c r="J313" t="n">
-        <v>1921.32</v>
+        <v>1223.39</v>
       </c>
       <c r="K313" t="n">
-        <v>11.68</v>
+        <v>37.11</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="314">
@@ -16740,35 +16740,35 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>480.9</v>
+        <v>1029.85</v>
       </c>
       <c r="D314" t="n">
-        <v>478.23</v>
+        <v>1105.03</v>
       </c>
       <c r="E314" t="n">
-        <v>2.67</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="F314" t="n">
-        <v>481.5</v>
+        <v>1048</v>
       </c>
       <c r="G314" t="n">
-        <v>478.23</v>
+        <v>1105.03</v>
       </c>
       <c r="H314" t="n">
-        <v>3.27</v>
+        <v>-57.03</v>
       </c>
       <c r="I314" t="n">
-        <v>465</v>
+        <v>1013</v>
       </c>
       <c r="J314" t="n">
-        <v>462.93</v>
+        <v>1022.2</v>
       </c>
       <c r="K314" t="n">
-        <v>2.07</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="315">
@@ -16792,39 +16792,39 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1882</v>
+        <v>11368</v>
       </c>
       <c r="D315" t="n">
-        <v>1913.14</v>
+        <v>11551.48</v>
       </c>
       <c r="E315" t="n">
-        <v>-31.14</v>
+        <v>-183.48</v>
       </c>
       <c r="F315" t="n">
-        <v>1888.5</v>
+        <v>11423</v>
       </c>
       <c r="G315" t="n">
-        <v>1913.14</v>
+        <v>11551.48</v>
       </c>
       <c r="H315" t="n">
-        <v>-24.64</v>
+        <v>-128.48</v>
       </c>
       <c r="I315" t="n">
-        <v>1826.5</v>
+        <v>11303</v>
       </c>
       <c r="J315" t="n">
-        <v>1832.84</v>
+        <v>11031.46</v>
       </c>
       <c r="K315" t="n">
-        <v>-6.34</v>
+        <v>271.54</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="316">
@@ -16844,39 +16844,39 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>5740.5</v>
+        <v>1203</v>
       </c>
       <c r="D316" t="n">
-        <v>5813.66</v>
+        <v>1205.51</v>
       </c>
       <c r="E316" t="n">
-        <v>-73.16</v>
+        <v>-2.51</v>
       </c>
       <c r="F316" t="n">
-        <v>5740.5</v>
+        <v>1222.9</v>
       </c>
       <c r="G316" t="n">
-        <v>5813.66</v>
+        <v>1205.51</v>
       </c>
       <c r="H316" t="n">
-        <v>-73.16</v>
+        <v>17.39</v>
       </c>
       <c r="I316" t="n">
-        <v>5670</v>
+        <v>1186</v>
       </c>
       <c r="J316" t="n">
-        <v>5557.57</v>
+        <v>1171.8</v>
       </c>
       <c r="K316" t="n">
-        <v>112.43</v>
+        <v>14.2</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>1.26</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="317">
@@ -16896,39 +16896,39 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3126</v>
+        <v>871</v>
       </c>
       <c r="D317" t="n">
-        <v>3190.49</v>
+        <v>884.3099999999999</v>
       </c>
       <c r="E317" t="n">
-        <v>-64.48999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="F317" t="n">
-        <v>3133.2</v>
+        <v>883.8</v>
       </c>
       <c r="G317" t="n">
-        <v>3249.54</v>
+        <v>884.3099999999999</v>
       </c>
       <c r="H317" t="n">
-        <v>-116.34</v>
+        <v>-0.51</v>
       </c>
       <c r="I317" t="n">
-        <v>3006</v>
+        <v>871</v>
       </c>
       <c r="J317" t="n">
-        <v>3166.76</v>
+        <v>850.8099999999999</v>
       </c>
       <c r="K317" t="n">
-        <v>-160.76</v>
+        <v>20.19</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="318">
@@ -16948,39 +16948,39 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1779.6</v>
+        <v>1360.9</v>
       </c>
       <c r="D318" t="n">
-        <v>1789.64</v>
+        <v>1389.34</v>
       </c>
       <c r="E318" t="n">
-        <v>-10.04</v>
+        <v>-28.44</v>
       </c>
       <c r="F318" t="n">
-        <v>1803.4</v>
+        <v>1390.1</v>
       </c>
       <c r="G318" t="n">
-        <v>1789.64</v>
+        <v>1389.34</v>
       </c>
       <c r="H318" t="n">
-        <v>13.76</v>
+        <v>0.76</v>
       </c>
       <c r="I318" t="n">
-        <v>1764</v>
+        <v>1355.3</v>
       </c>
       <c r="J318" t="n">
-        <v>1725.02</v>
+        <v>1296.01</v>
       </c>
       <c r="K318" t="n">
-        <v>38.98</v>
+        <v>59.29</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="319">
@@ -17000,39 +17000,39 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>5674</v>
+        <v>2227</v>
       </c>
       <c r="D319" t="n">
-        <v>5542.6</v>
+        <v>2150.93</v>
       </c>
       <c r="E319" t="n">
-        <v>131.4</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F319" t="n">
-        <v>5706</v>
+        <v>2233.7</v>
       </c>
       <c r="G319" t="n">
-        <v>5725.33</v>
+        <v>2217.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-19.33</v>
+        <v>16.4</v>
       </c>
       <c r="I319" t="n">
-        <v>5534</v>
+        <v>2180.4</v>
       </c>
       <c r="J319" t="n">
-        <v>5577.53</v>
+        <v>2159.24</v>
       </c>
       <c r="K319" t="n">
-        <v>-43.53</v>
+        <v>21.16</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>2.37</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="320">
@@ -17052,39 +17052,39 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>973.4</v>
+        <v>2032.5</v>
       </c>
       <c r="D320" t="n">
-        <v>1027.79</v>
+        <v>2009.94</v>
       </c>
       <c r="E320" t="n">
-        <v>-54.39</v>
+        <v>22.56</v>
       </c>
       <c r="F320" t="n">
-        <v>989.55</v>
+        <v>2032.5</v>
       </c>
       <c r="G320" t="n">
-        <v>1027.79</v>
+        <v>2054.87</v>
       </c>
       <c r="H320" t="n">
-        <v>-38.24</v>
+        <v>-22.37</v>
       </c>
       <c r="I320" t="n">
-        <v>942.15</v>
+        <v>2005</v>
       </c>
       <c r="J320" t="n">
-        <v>956.1900000000001</v>
+        <v>2019</v>
       </c>
       <c r="K320" t="n">
-        <v>-14.04</v>
+        <v>-14</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>5.29</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="321">
@@ -17104,35 +17104,35 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11826</v>
+        <v>1048.7</v>
       </c>
       <c r="D321" t="n">
-        <v>11687.68</v>
+        <v>1054.62</v>
       </c>
       <c r="E321" t="n">
-        <v>138.32</v>
+        <v>-5.92</v>
       </c>
       <c r="F321" t="n">
-        <v>11917</v>
+        <v>1054.7</v>
       </c>
       <c r="G321" t="n">
-        <v>11830.43</v>
+        <v>1054.62</v>
       </c>
       <c r="H321" t="n">
-        <v>86.56999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="I321" t="n">
-        <v>11680</v>
+        <v>1040.1</v>
       </c>
       <c r="J321" t="n">
-        <v>11524.58</v>
+        <v>1033.75</v>
       </c>
       <c r="K321" t="n">
-        <v>155.42</v>
+        <v>6.35</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>1.18</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -17156,35 +17156,35 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>327.95</v>
+        <v>475</v>
       </c>
       <c r="D322" t="n">
-        <v>306.55</v>
+        <v>481.47</v>
       </c>
       <c r="E322" t="n">
-        <v>21.4</v>
+        <v>-6.47</v>
       </c>
       <c r="F322" t="n">
-        <v>328.5</v>
+        <v>482</v>
       </c>
       <c r="G322" t="n">
-        <v>331.99</v>
+        <v>481.47</v>
       </c>
       <c r="H322" t="n">
-        <v>-3.49</v>
+        <v>0.53</v>
       </c>
       <c r="I322" t="n">
-        <v>321.35</v>
+        <v>475</v>
       </c>
       <c r="J322" t="n">
-        <v>323.44</v>
+        <v>469.41</v>
       </c>
       <c r="K322" t="n">
-        <v>-2.09</v>
+        <v>5.59</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>6.98</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="323">
@@ -17208,35 +17208,35 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1260.5</v>
+        <v>678.1</v>
       </c>
       <c r="D323" t="n">
-        <v>1292.12</v>
+        <v>674.6799999999999</v>
       </c>
       <c r="E323" t="n">
-        <v>-31.62</v>
+        <v>3.42</v>
       </c>
       <c r="F323" t="n">
-        <v>1282.6</v>
+        <v>684.45</v>
       </c>
       <c r="G323" t="n">
-        <v>1292.12</v>
+        <v>674.6799999999999</v>
       </c>
       <c r="H323" t="n">
-        <v>-9.52</v>
+        <v>9.77</v>
       </c>
       <c r="I323" t="n">
-        <v>1260.5</v>
+        <v>675.25</v>
       </c>
       <c r="J323" t="n">
-        <v>1223.39</v>
+        <v>664.66</v>
       </c>
       <c r="K323" t="n">
-        <v>37.11</v>
+        <v>10.59</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>2.45</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="324">
@@ -17260,35 +17260,35 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>118</v>
+        <v>3185</v>
       </c>
       <c r="D324" t="n">
-        <v>122.14</v>
+        <v>3160.81</v>
       </c>
       <c r="E324" t="n">
-        <v>-4.14</v>
+        <v>24.19</v>
       </c>
       <c r="F324" t="n">
-        <v>119.1</v>
+        <v>3211.4</v>
       </c>
       <c r="G324" t="n">
-        <v>122.14</v>
+        <v>3266.55</v>
       </c>
       <c r="H324" t="n">
-        <v>-3.04</v>
+        <v>-55.15</v>
       </c>
       <c r="I324" t="n">
-        <v>117.44</v>
+        <v>3132</v>
       </c>
       <c r="J324" t="n">
-        <v>113.63</v>
+        <v>3185</v>
       </c>
       <c r="K324" t="n">
-        <v>3.81</v>
+        <v>-53</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>3.39</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="325">
@@ -17312,35 +17312,35 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1029.85</v>
+        <v>5667.5</v>
       </c>
       <c r="D325" t="n">
-        <v>1105.03</v>
+        <v>5848.29</v>
       </c>
       <c r="E325" t="n">
-        <v>-75.18000000000001</v>
+        <v>-180.79</v>
       </c>
       <c r="F325" t="n">
-        <v>1048</v>
+        <v>5722</v>
       </c>
       <c r="G325" t="n">
-        <v>1105.03</v>
+        <v>5848.29</v>
       </c>
       <c r="H325" t="n">
-        <v>-57.03</v>
+        <v>-126.29</v>
       </c>
       <c r="I325" t="n">
-        <v>1013</v>
+        <v>5602</v>
       </c>
       <c r="J325" t="n">
-        <v>1022.2</v>
+        <v>5655.6</v>
       </c>
       <c r="K325" t="n">
-        <v>-9.199999999999999</v>
+        <v>-53.6</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6.8</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="326">
@@ -17364,35 +17364,35 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>385.6</v>
+        <v>116.55</v>
       </c>
       <c r="D326" t="n">
-        <v>433.84</v>
+        <v>113.5</v>
       </c>
       <c r="E326" t="n">
-        <v>-48.24</v>
+        <v>3.05</v>
       </c>
       <c r="F326" t="n">
-        <v>395.75</v>
+        <v>117.52</v>
       </c>
       <c r="G326" t="n">
-        <v>433.84</v>
+        <v>116.85</v>
       </c>
       <c r="H326" t="n">
-        <v>-38.09</v>
+        <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>385.1</v>
+        <v>115.41</v>
       </c>
       <c r="J326" t="n">
-        <v>390.67</v>
+        <v>115.22</v>
       </c>
       <c r="K326" t="n">
-        <v>-5.57</v>
+        <v>0.19</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>11.12</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="327">
@@ -17416,35 +17416,35 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2140</v>
+        <v>1946</v>
       </c>
       <c r="D327" t="n">
-        <v>2076.31</v>
+        <v>1939.23</v>
       </c>
       <c r="E327" t="n">
-        <v>63.69</v>
+        <v>6.77</v>
       </c>
       <c r="F327" t="n">
-        <v>2153.7</v>
+        <v>1954.9</v>
       </c>
       <c r="G327" t="n">
-        <v>2118.48</v>
+        <v>1982.38</v>
       </c>
       <c r="H327" t="n">
-        <v>35.22</v>
+        <v>-27.48</v>
       </c>
       <c r="I327" t="n">
-        <v>2125</v>
+        <v>1940.5</v>
       </c>
       <c r="J327" t="n">
-        <v>2066.74</v>
+        <v>1946</v>
       </c>
       <c r="K327" t="n">
-        <v>58.26</v>
+        <v>-5.5</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>3.07</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="328">
@@ -17468,35 +17468,35 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3424.8</v>
+        <v>328</v>
       </c>
       <c r="D328" t="n">
-        <v>3231.44</v>
+        <v>353.7</v>
       </c>
       <c r="E328" t="n">
-        <v>193.36</v>
+        <v>-25.7</v>
       </c>
       <c r="F328" t="n">
-        <v>3456.4</v>
+        <v>331.7</v>
       </c>
       <c r="G328" t="n">
-        <v>3365.55</v>
+        <v>353.7</v>
       </c>
       <c r="H328" t="n">
-        <v>90.84999999999999</v>
+        <v>-22</v>
       </c>
       <c r="I328" t="n">
-        <v>3401</v>
+        <v>324.1</v>
       </c>
       <c r="J328" t="n">
-        <v>3329.82</v>
+        <v>327.97</v>
       </c>
       <c r="K328" t="n">
-        <v>71.18000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -17505,11 +17505,11 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N328" t="n">
-        <v>5.98</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="329">
@@ -17520,39 +17520,39 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>173.8</v>
+        <v>11724</v>
       </c>
       <c r="D329" t="n">
-        <v>172.71</v>
+        <v>11957.59</v>
       </c>
       <c r="E329" t="n">
-        <v>1.09</v>
+        <v>-233.59</v>
       </c>
       <c r="F329" t="n">
-        <v>175.57</v>
+        <v>11870</v>
       </c>
       <c r="G329" t="n">
-        <v>172.71</v>
+        <v>11957.59</v>
       </c>
       <c r="H329" t="n">
-        <v>2.86</v>
+        <v>-87.59</v>
       </c>
       <c r="I329" t="n">
-        <v>172.61</v>
+        <v>11650</v>
       </c>
       <c r="J329" t="n">
-        <v>167.6</v>
+        <v>11685.84</v>
       </c>
       <c r="K329" t="n">
-        <v>5.01</v>
+        <v>-35.84</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="330">
@@ -17572,39 +17572,39 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4081</v>
+        <v>1891.7</v>
       </c>
       <c r="D330" t="n">
-        <v>4062.2</v>
+        <v>1875.79</v>
       </c>
       <c r="E330" t="n">
-        <v>18.8</v>
+        <v>15.91</v>
       </c>
       <c r="F330" t="n">
-        <v>4084.9</v>
+        <v>1891.7</v>
       </c>
       <c r="G330" t="n">
-        <v>4101.72</v>
+        <v>1875.79</v>
       </c>
       <c r="H330" t="n">
-        <v>-16.82</v>
+        <v>15.91</v>
       </c>
       <c r="I330" t="n">
-        <v>4048.3</v>
+        <v>1851</v>
       </c>
       <c r="J330" t="n">
-        <v>4014.48</v>
+        <v>1858.54</v>
       </c>
       <c r="K330" t="n">
-        <v>33.82</v>
+        <v>-7.54</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -17613,7 +17613,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="331">
@@ -17624,39 +17624,39 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1585.5</v>
+        <v>2139</v>
       </c>
       <c r="D331" t="n">
-        <v>1625.95</v>
+        <v>2222.24</v>
       </c>
       <c r="E331" t="n">
-        <v>-40.45</v>
+        <v>-83.23999999999999</v>
       </c>
       <c r="F331" t="n">
-        <v>1610</v>
+        <v>2162.2</v>
       </c>
       <c r="G331" t="n">
-        <v>1625.95</v>
+        <v>2222.24</v>
       </c>
       <c r="H331" t="n">
-        <v>-15.95</v>
+        <v>-60.04</v>
       </c>
       <c r="I331" t="n">
-        <v>1581</v>
+        <v>2126.3</v>
       </c>
       <c r="J331" t="n">
-        <v>1568.44</v>
+        <v>2095.72</v>
       </c>
       <c r="K331" t="n">
-        <v>12.56</v>
+        <v>30.58</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>2.49</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="332">
@@ -17676,48 +17676,48 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>11368</v>
+        <v>394.45</v>
       </c>
       <c r="D332" t="n">
-        <v>11551.48</v>
+        <v>353.75</v>
       </c>
       <c r="E332" t="n">
-        <v>-183.48</v>
+        <v>40.7</v>
       </c>
       <c r="F332" t="n">
-        <v>11423</v>
+        <v>397.5</v>
       </c>
       <c r="G332" t="n">
-        <v>11551.48</v>
+        <v>403.03</v>
       </c>
       <c r="H332" t="n">
-        <v>-128.48</v>
+        <v>-5.53</v>
       </c>
       <c r="I332" t="n">
-        <v>11303</v>
+        <v>384.6</v>
       </c>
       <c r="J332" t="n">
-        <v>11031.46</v>
+        <v>394.45</v>
       </c>
       <c r="K332" t="n">
-        <v>271.54</v>
+        <v>-9.85</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N332" t="n">
-        <v>1.59</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="333">
@@ -17728,35 +17728,35 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2570</v>
+        <v>4093</v>
       </c>
       <c r="D333" t="n">
-        <v>2591.15</v>
+        <v>4144.84</v>
       </c>
       <c r="E333" t="n">
-        <v>-21.15</v>
+        <v>-51.84</v>
       </c>
       <c r="F333" t="n">
-        <v>2583.2</v>
+        <v>4100</v>
       </c>
       <c r="G333" t="n">
-        <v>2591.15</v>
+        <v>4144.84</v>
       </c>
       <c r="H333" t="n">
-        <v>-7.95</v>
+        <v>-44.84</v>
       </c>
       <c r="I333" t="n">
-        <v>2552</v>
+        <v>4061.4</v>
       </c>
       <c r="J333" t="n">
-        <v>2463.59</v>
+        <v>4070.76</v>
       </c>
       <c r="K333" t="n">
-        <v>88.41</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>0.82</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="334">
@@ -17780,35 +17780,35 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1203</v>
+        <v>173</v>
       </c>
       <c r="D334" t="n">
-        <v>1205.51</v>
+        <v>175.48</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.51</v>
+        <v>-2.48</v>
       </c>
       <c r="F334" t="n">
-        <v>1222.9</v>
+        <v>173.69</v>
       </c>
       <c r="G334" t="n">
-        <v>1205.51</v>
+        <v>175.48</v>
       </c>
       <c r="H334" t="n">
-        <v>17.39</v>
+        <v>-1.79</v>
       </c>
       <c r="I334" t="n">
-        <v>1186</v>
+        <v>172.3</v>
       </c>
       <c r="J334" t="n">
-        <v>1171.8</v>
+        <v>169.95</v>
       </c>
       <c r="K334" t="n">
-        <v>14.2</v>
+        <v>2.35</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>0.21</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="335">
@@ -17832,35 +17832,35 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>871</v>
+        <v>1631</v>
       </c>
       <c r="D335" t="n">
-        <v>884.3099999999999</v>
+        <v>1603.15</v>
       </c>
       <c r="E335" t="n">
-        <v>-13.31</v>
+        <v>27.85</v>
       </c>
       <c r="F335" t="n">
-        <v>883.8</v>
+        <v>1651.3</v>
       </c>
       <c r="G335" t="n">
-        <v>884.3099999999999</v>
+        <v>1608.2</v>
       </c>
       <c r="H335" t="n">
-        <v>-0.51</v>
+        <v>43.1</v>
       </c>
       <c r="I335" t="n">
-        <v>871</v>
+        <v>1590</v>
       </c>
       <c r="J335" t="n">
-        <v>850.8099999999999</v>
+        <v>1590.43</v>
       </c>
       <c r="K335" t="n">
-        <v>20.19</v>
+        <v>-0.43</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="336">
@@ -17884,35 +17884,35 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1360.9</v>
+        <v>3412.2</v>
       </c>
       <c r="D336" t="n">
-        <v>1389.34</v>
+        <v>3645.32</v>
       </c>
       <c r="E336" t="n">
-        <v>-28.44</v>
+        <v>-233.12</v>
       </c>
       <c r="F336" t="n">
-        <v>1390.1</v>
+        <v>3453.9</v>
       </c>
       <c r="G336" t="n">
-        <v>1389.34</v>
+        <v>3645.32</v>
       </c>
       <c r="H336" t="n">
-        <v>0.76</v>
+        <v>-191.42</v>
       </c>
       <c r="I336" t="n">
-        <v>1355.3</v>
+        <v>3412.2</v>
       </c>
       <c r="J336" t="n">
-        <v>1296.01</v>
+        <v>3376.5</v>
       </c>
       <c r="K336" t="n">
-        <v>59.29</v>
+        <v>35.7</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2.05</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="337">
@@ -17936,35 +17936,35 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>184.68</v>
+        <v>2552</v>
       </c>
       <c r="D337" t="n">
-        <v>195.08</v>
+        <v>2551.43</v>
       </c>
       <c r="E337" t="n">
-        <v>-10.4</v>
+        <v>0.57</v>
       </c>
       <c r="F337" t="n">
-        <v>189.46</v>
+        <v>2596</v>
       </c>
       <c r="G337" t="n">
-        <v>195.08</v>
+        <v>2551.43</v>
       </c>
       <c r="H337" t="n">
-        <v>-5.62</v>
+        <v>44.57</v>
       </c>
       <c r="I337" t="n">
-        <v>184.39</v>
+        <v>2542</v>
       </c>
       <c r="J337" t="n">
-        <v>178.56</v>
+        <v>2498.14</v>
       </c>
       <c r="K337" t="n">
-        <v>5.83</v>
+        <v>43.86</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>5.33</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="338">
@@ -17988,35 +17988,35 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2227</v>
+        <v>14850</v>
       </c>
       <c r="D338" t="n">
-        <v>2150.93</v>
+        <v>15422.35</v>
       </c>
       <c r="E338" t="n">
-        <v>76.06999999999999</v>
+        <v>-572.35</v>
       </c>
       <c r="F338" t="n">
-        <v>2233.7</v>
+        <v>14924</v>
       </c>
       <c r="G338" t="n">
-        <v>2217.3</v>
+        <v>15422.35</v>
       </c>
       <c r="H338" t="n">
-        <v>16.4</v>
+        <v>-498.35</v>
       </c>
       <c r="I338" t="n">
-        <v>2180.4</v>
+        <v>14620</v>
       </c>
       <c r="J338" t="n">
-        <v>2159.24</v>
+        <v>14577.94</v>
       </c>
       <c r="K338" t="n">
-        <v>21.16</v>
+        <v>42.06</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="339">
@@ -18040,35 +18040,35 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>519</v>
+        <v>183.45</v>
       </c>
       <c r="D339" t="n">
-        <v>480.87</v>
+        <v>175.06</v>
       </c>
       <c r="E339" t="n">
-        <v>38.13</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F339" t="n">
-        <v>524.4</v>
+        <v>185.3</v>
       </c>
       <c r="G339" t="n">
-        <v>505.57</v>
+        <v>184.32</v>
       </c>
       <c r="H339" t="n">
-        <v>18.83</v>
+        <v>0.98</v>
       </c>
       <c r="I339" t="n">
-        <v>513.8</v>
+        <v>182.5</v>
       </c>
       <c r="J339" t="n">
-        <v>498.74</v>
+        <v>181.07</v>
       </c>
       <c r="K339" t="n">
-        <v>15.06</v>
+        <v>1.43</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -18077,11 +18077,11 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>7.93</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="340">
@@ -18092,35 +18092,35 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>14850</v>
+        <v>515.05</v>
       </c>
       <c r="D340" t="n">
-        <v>14413.31</v>
+        <v>560.33</v>
       </c>
       <c r="E340" t="n">
-        <v>436.69</v>
+        <v>-45.28</v>
       </c>
       <c r="F340" t="n">
-        <v>14953</v>
+        <v>523</v>
       </c>
       <c r="G340" t="n">
-        <v>14511.32</v>
+        <v>560.33</v>
       </c>
       <c r="H340" t="n">
-        <v>441.68</v>
+        <v>-37.33</v>
       </c>
       <c r="I340" t="n">
-        <v>14470</v>
+        <v>512.15</v>
       </c>
       <c r="J340" t="n">
-        <v>14376.37</v>
+        <v>505.74</v>
       </c>
       <c r="K340" t="n">
-        <v>93.63</v>
+        <v>6.41</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -18129,11 +18129,11 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N340" t="n">
-        <v>3.03</v>
+        <v>8.08</v>
       </c>
     </row>
   </sheetData>
@@ -21870,31 +21870,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>327.95</v>
+        <v>328</v>
       </c>
       <c r="D14" t="n">
-        <v>306.55</v>
+        <v>353.7</v>
       </c>
       <c r="E14" t="n">
-        <v>21.4</v>
+        <v>-25.7</v>
       </c>
       <c r="F14" t="n">
-        <v>328.5</v>
+        <v>331.7</v>
       </c>
       <c r="G14" t="n">
-        <v>331.99</v>
+        <v>353.7</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.49</v>
+        <v>-22</v>
       </c>
       <c r="I14" t="n">
-        <v>321.35</v>
+        <v>324.1</v>
       </c>
       <c r="J14" t="n">
-        <v>323.44</v>
+        <v>327.97</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.09</v>
+        <v>-3.87</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6.98</v>
+        <v>7.27</v>
       </c>
     </row>
   </sheetData>
@@ -22635,28 +22635,28 @@
         <v>14850</v>
       </c>
       <c r="D14" t="n">
-        <v>14413.31</v>
+        <v>15422.35</v>
       </c>
       <c r="E14" t="n">
-        <v>436.69</v>
+        <v>-572.35</v>
       </c>
       <c r="F14" t="n">
-        <v>14953</v>
+        <v>14924</v>
       </c>
       <c r="G14" t="n">
-        <v>14511.32</v>
+        <v>15422.35</v>
       </c>
       <c r="H14" t="n">
-        <v>441.68</v>
+        <v>-498.35</v>
       </c>
       <c r="I14" t="n">
-        <v>14470</v>
+        <v>14620</v>
       </c>
       <c r="J14" t="n">
-        <v>14376.37</v>
+        <v>14577.94</v>
       </c>
       <c r="K14" t="n">
-        <v>93.63</v>
+        <v>42.06</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -22665,11 +22665,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>3.71</v>
       </c>
     </row>
   </sheetData>
@@ -23394,31 +23394,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1882</v>
+        <v>1891.7</v>
       </c>
       <c r="D14" t="n">
-        <v>1913.14</v>
+        <v>1875.79</v>
       </c>
       <c r="E14" t="n">
-        <v>-31.14</v>
+        <v>15.91</v>
       </c>
       <c r="F14" t="n">
-        <v>1888.5</v>
+        <v>1891.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1913.14</v>
+        <v>1875.79</v>
       </c>
       <c r="H14" t="n">
-        <v>-24.64</v>
+        <v>15.91</v>
       </c>
       <c r="I14" t="n">
-        <v>1826.5</v>
+        <v>1851</v>
       </c>
       <c r="J14" t="n">
-        <v>1832.84</v>
+        <v>1858.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.34</v>
+        <v>-7.54</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -24052,31 +24052,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5674</v>
+        <v>5667.5</v>
       </c>
       <c r="D12" t="n">
-        <v>5542.6</v>
+        <v>5848.29</v>
       </c>
       <c r="E12" t="n">
-        <v>131.4</v>
+        <v>-180.79</v>
       </c>
       <c r="F12" t="n">
-        <v>5706</v>
+        <v>5722</v>
       </c>
       <c r="G12" t="n">
-        <v>5725.33</v>
+        <v>5848.29</v>
       </c>
       <c r="H12" t="n">
-        <v>-19.33</v>
+        <v>-126.29</v>
       </c>
       <c r="I12" t="n">
-        <v>5534</v>
+        <v>5602</v>
       </c>
       <c r="J12" t="n">
-        <v>5577.53</v>
+        <v>5655.6</v>
       </c>
       <c r="K12" t="n">
-        <v>-43.53</v>
+        <v>-53.6</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.37</v>
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>
@@ -24814,31 +24814,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>118</v>
+        <v>116.55</v>
       </c>
       <c r="D14" t="n">
-        <v>122.14</v>
+        <v>113.5</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.14</v>
+        <v>3.05</v>
       </c>
       <c r="F14" t="n">
-        <v>119.1</v>
+        <v>117.52</v>
       </c>
       <c r="G14" t="n">
-        <v>122.14</v>
+        <v>116.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.04</v>
+        <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>117.44</v>
+        <v>115.41</v>
       </c>
       <c r="J14" t="n">
-        <v>113.63</v>
+        <v>115.22</v>
       </c>
       <c r="K14" t="n">
-        <v>3.81</v>
+        <v>0.19</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>2.69</v>
       </c>
     </row>
   </sheetData>
@@ -25524,44 +25524,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3424.8</v>
+        <v>3412.2</v>
       </c>
       <c r="D13" t="n">
-        <v>3231.44</v>
+        <v>3645.32</v>
       </c>
       <c r="E13" t="n">
-        <v>193.36</v>
+        <v>-233.12</v>
       </c>
       <c r="F13" t="n">
-        <v>3456.4</v>
+        <v>3453.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3365.55</v>
+        <v>3645.32</v>
       </c>
       <c r="H13" t="n">
-        <v>90.84999999999999</v>
+        <v>-191.42</v>
       </c>
       <c r="I13" t="n">
-        <v>3401</v>
+        <v>3412.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3329.82</v>
+        <v>3376.5</v>
       </c>
       <c r="K13" t="n">
-        <v>71.18000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.98</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -26234,31 +26234,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>519</v>
+        <v>515.05</v>
       </c>
       <c r="D13" t="n">
-        <v>480.87</v>
+        <v>560.33</v>
       </c>
       <c r="E13" t="n">
-        <v>38.13</v>
+        <v>-45.28</v>
       </c>
       <c r="F13" t="n">
-        <v>524.4</v>
+        <v>523</v>
       </c>
       <c r="G13" t="n">
-        <v>505.57</v>
+        <v>560.33</v>
       </c>
       <c r="H13" t="n">
-        <v>18.83</v>
+        <v>-37.33</v>
       </c>
       <c r="I13" t="n">
-        <v>513.8</v>
+        <v>512.15</v>
       </c>
       <c r="J13" t="n">
-        <v>498.74</v>
+        <v>505.74</v>
       </c>
       <c r="K13" t="n">
-        <v>15.06</v>
+        <v>6.41</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -26267,11 +26267,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.93</v>
+        <v>8.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N340"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18134,6 +18134,1462 @@
       </c>
       <c r="N340" t="n">
         <v>8.08</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>689</v>
+      </c>
+      <c r="D341" t="n">
+        <v>698.03</v>
+      </c>
+      <c r="E341" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="F341" t="n">
+        <v>689</v>
+      </c>
+      <c r="G341" t="n">
+        <v>698.03</v>
+      </c>
+      <c r="H341" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="I341" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="J341" t="n">
+        <v>668.46</v>
+      </c>
+      <c r="K341" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="D342" t="n">
+        <v>293.6</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F342" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="G342" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="H342" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="I342" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="J342" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2081.17</v>
+      </c>
+      <c r="E343" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="F343" t="n">
+        <v>2172.8</v>
+      </c>
+      <c r="G343" t="n">
+        <v>2123.58</v>
+      </c>
+      <c r="H343" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="I343" t="n">
+        <v>2131.8</v>
+      </c>
+      <c r="J343" t="n">
+        <v>2087.5</v>
+      </c>
+      <c r="K343" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>3414.1</v>
+      </c>
+      <c r="D344" t="n">
+        <v>3221.33</v>
+      </c>
+      <c r="E344" t="n">
+        <v>192.77</v>
+      </c>
+      <c r="F344" t="n">
+        <v>3444.7</v>
+      </c>
+      <c r="G344" t="n">
+        <v>3418.31</v>
+      </c>
+      <c r="H344" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="I344" t="n">
+        <v>3400</v>
+      </c>
+      <c r="J344" t="n">
+        <v>3344.52</v>
+      </c>
+      <c r="K344" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="D345" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="E345" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F345" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="G345" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="H345" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I345" t="n">
+        <v>115</v>
+      </c>
+      <c r="J345" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="K345" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>5694</v>
+      </c>
+      <c r="D346" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="E346" t="n">
+        <v>131.86</v>
+      </c>
+      <c r="F346" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G346" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="H346" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="I346" t="n">
+        <v>5646</v>
+      </c>
+      <c r="J346" t="n">
+        <v>5533.49</v>
+      </c>
+      <c r="K346" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>2001.7</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2040.35</v>
+      </c>
+      <c r="E347" t="n">
+        <v>-38.65</v>
+      </c>
+      <c r="F347" t="n">
+        <v>2028.6</v>
+      </c>
+      <c r="G347" t="n">
+        <v>2040.35</v>
+      </c>
+      <c r="H347" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="I347" t="n">
+        <v>1995.3</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1960.26</v>
+      </c>
+      <c r="K347" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>11120</v>
+      </c>
+      <c r="D348" t="n">
+        <v>11031.75</v>
+      </c>
+      <c r="E348" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="F348" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G348" t="n">
+        <v>11152.7</v>
+      </c>
+      <c r="H348" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="I348" t="n">
+        <v>11050</v>
+      </c>
+      <c r="J348" t="n">
+        <v>10895.68</v>
+      </c>
+      <c r="K348" t="n">
+        <v>154.32</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="D349" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="E349" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="F349" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G349" t="n">
+        <v>330.12</v>
+      </c>
+      <c r="H349" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I349" t="n">
+        <v>323</v>
+      </c>
+      <c r="J349" t="n">
+        <v>322.58</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D350" t="n">
+        <v>3334.11</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-66.11</v>
+      </c>
+      <c r="F350" t="n">
+        <v>3289.7</v>
+      </c>
+      <c r="G350" t="n">
+        <v>3334.11</v>
+      </c>
+      <c r="H350" t="n">
+        <v>-44.41</v>
+      </c>
+      <c r="I350" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J350" t="n">
+        <v>3257.4</v>
+      </c>
+      <c r="K350" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>477</v>
+      </c>
+      <c r="D351" t="n">
+        <v>474.36</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F351" t="n">
+        <v>479.25</v>
+      </c>
+      <c r="G351" t="n">
+        <v>483.15</v>
+      </c>
+      <c r="H351" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I351" t="n">
+        <v>472</v>
+      </c>
+      <c r="J351" t="n">
+        <v>472.18</v>
+      </c>
+      <c r="K351" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>173.29</v>
+      </c>
+      <c r="D352" t="n">
+        <v>172.21</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F352" t="n">
+        <v>173.66</v>
+      </c>
+      <c r="G352" t="n">
+        <v>174.16</v>
+      </c>
+      <c r="H352" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I352" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="J352" t="n">
+        <v>170.16</v>
+      </c>
+      <c r="K352" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1050.1</v>
+      </c>
+      <c r="E353" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="G353" t="n">
+        <v>1067.24</v>
+      </c>
+      <c r="H353" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="I353" t="n">
+        <v>1043.3</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1042.84</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="D354" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="E354" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F354" t="n">
+        <v>405</v>
+      </c>
+      <c r="G354" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="H354" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I354" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="J354" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1251.3</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1241.37</v>
+      </c>
+      <c r="E355" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1261.6</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1249.06</v>
+      </c>
+      <c r="H355" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="I355" t="n">
+        <v>1245.1</v>
+      </c>
+      <c r="J355" t="n">
+        <v>1220.08</v>
+      </c>
+      <c r="K355" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N355" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>5685</v>
+      </c>
+      <c r="D356" t="n">
+        <v>5639.88</v>
+      </c>
+      <c r="E356" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F356" t="n">
+        <v>5728</v>
+      </c>
+      <c r="G356" t="n">
+        <v>5639.88</v>
+      </c>
+      <c r="H356" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="I356" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J356" t="n">
+        <v>5521.63</v>
+      </c>
+      <c r="K356" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D357" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="F357" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="G357" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="H357" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="I357" t="n">
+        <v>182.02</v>
+      </c>
+      <c r="J357" t="n">
+        <v>179.91</v>
+      </c>
+      <c r="K357" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1635.8</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1677.53</v>
+      </c>
+      <c r="E358" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1641.6</v>
+      </c>
+      <c r="G358" t="n">
+        <v>1677.53</v>
+      </c>
+      <c r="H358" t="n">
+        <v>-35.93</v>
+      </c>
+      <c r="I358" t="n">
+        <v>1618.1</v>
+      </c>
+      <c r="J358" t="n">
+        <v>1577.23</v>
+      </c>
+      <c r="K358" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1785</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1770.83</v>
+      </c>
+      <c r="E359" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F359" t="n">
+        <v>1811.8</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1770.83</v>
+      </c>
+      <c r="H359" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1773.5</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1728.56</v>
+      </c>
+      <c r="K359" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="E360" t="n">
+        <v>-30.99</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="G360" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="H360" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I360" t="n">
+        <v>1869.6</v>
+      </c>
+      <c r="J360" t="n">
+        <v>1820.59</v>
+      </c>
+      <c r="K360" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D361" t="n">
+        <v>4071.14</v>
+      </c>
+      <c r="E361" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4107.1</v>
+      </c>
+      <c r="G361" t="n">
+        <v>4113.19</v>
+      </c>
+      <c r="H361" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="I361" t="n">
+        <v>4077.7</v>
+      </c>
+      <c r="J361" t="n">
+        <v>4035.27</v>
+      </c>
+      <c r="K361" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>990</v>
+      </c>
+      <c r="D362" t="n">
+        <v>982.14</v>
+      </c>
+      <c r="E362" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="F362" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G362" t="n">
+        <v>1002.82</v>
+      </c>
+      <c r="H362" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I362" t="n">
+        <v>988.3</v>
+      </c>
+      <c r="J362" t="n">
+        <v>980.05</v>
+      </c>
+      <c r="K362" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>2207</v>
+      </c>
+      <c r="D363" t="n">
+        <v>2189.74</v>
+      </c>
+      <c r="E363" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2235.4</v>
+      </c>
+      <c r="G363" t="n">
+        <v>2240.9</v>
+      </c>
+      <c r="H363" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="I363" t="n">
+        <v>2206.1</v>
+      </c>
+      <c r="J363" t="n">
+        <v>2190.22</v>
+      </c>
+      <c r="K363" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="D364" t="n">
+        <v>478.47</v>
+      </c>
+      <c r="E364" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="F364" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="G364" t="n">
+        <v>486.67</v>
+      </c>
+      <c r="H364" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="I364" t="n">
+        <v>513.05</v>
+      </c>
+      <c r="J364" t="n">
+        <v>501.38</v>
+      </c>
+      <c r="K364" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>7.93</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>2540</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2560.88</v>
+      </c>
+      <c r="E365" t="n">
+        <v>-20.88</v>
+      </c>
+      <c r="F365" t="n">
+        <v>2572.6</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2560.88</v>
+      </c>
+      <c r="H365" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="I365" t="n">
+        <v>2523.4</v>
+      </c>
+      <c r="J365" t="n">
+        <v>2457.21</v>
+      </c>
+      <c r="K365" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1338.29</v>
+      </c>
+      <c r="E366" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F366" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G366" t="n">
+        <v>1338.29</v>
+      </c>
+      <c r="H366" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="I366" t="n">
+        <v>1336.7</v>
+      </c>
+      <c r="J366" t="n">
+        <v>1301.3</v>
+      </c>
+      <c r="K366" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>14570</v>
+      </c>
+      <c r="D367" t="n">
+        <v>14173.87</v>
+      </c>
+      <c r="E367" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="F367" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G367" t="n">
+        <v>14825.24</v>
+      </c>
+      <c r="H367" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="I367" t="n">
+        <v>14484</v>
+      </c>
+      <c r="J367" t="n">
+        <v>14490.99</v>
+      </c>
+      <c r="K367" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>870.45</v>
+      </c>
+      <c r="D368" t="n">
+        <v>863.54</v>
+      </c>
+      <c r="E368" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="F368" t="n">
+        <v>883.85</v>
+      </c>
+      <c r="G368" t="n">
+        <v>863.9</v>
+      </c>
+      <c r="H368" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I368" t="n">
+        <v>862</v>
+      </c>
+      <c r="J368" t="n">
+        <v>847.41</v>
+      </c>
+      <c r="K368" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -21159,7 +22615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21908,6 +23364,58 @@
       </c>
       <c r="N14" t="n">
         <v>7.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="F15" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>330.12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I15" t="n">
+        <v>323</v>
+      </c>
+      <c r="J15" t="n">
+        <v>322.58</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>6.98</v>
       </c>
     </row>
   </sheetData>
@@ -21921,7 +23429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22670,6 +24178,58 @@
       </c>
       <c r="N14" t="n">
         <v>3.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14570</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14173.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14825.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="I15" t="n">
+        <v>14484</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14490.99</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -22683,7 +24243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23432,6 +24992,58 @@
       </c>
       <c r="N14" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-30.99</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1869.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1820.59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -23445,7 +25057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24090,6 +25702,58 @@
       </c>
       <c r="N12" t="n">
         <v>3.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5694</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>131.86</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5646</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5533.49</v>
+      </c>
+      <c r="K13" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>
@@ -24103,7 +25767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24852,6 +26516,58 @@
       </c>
       <c r="N14" t="n">
         <v>2.69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="D15" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F15" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="G15" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>115</v>
+      </c>
+      <c r="J15" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3.39</v>
       </c>
     </row>
   </sheetData>
@@ -24865,7 +26581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25562,6 +27278,58 @@
       </c>
       <c r="N13" t="n">
         <v>6.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3414.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3221.33</v>
+      </c>
+      <c r="E14" t="n">
+        <v>192.77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3444.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3418.31</v>
+      </c>
+      <c r="H14" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3344.52</v>
+      </c>
+      <c r="K14" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5.98</v>
       </c>
     </row>
   </sheetData>
@@ -25575,7 +27343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26272,6 +28040,58 @@
       </c>
       <c r="N13" t="n">
         <v>8.08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>478.47</v>
+      </c>
+      <c r="E14" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="F14" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>486.67</v>
+      </c>
+      <c r="H14" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="I14" t="n">
+        <v>513.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>501.38</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>7.93</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -18148,31 +18148,31 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>689</v>
+        <v>678.1</v>
       </c>
       <c r="D341" t="n">
         <v>698.03</v>
       </c>
       <c r="E341" t="n">
-        <v>-9.029999999999999</v>
+        <v>-19.93</v>
       </c>
       <c r="F341" t="n">
-        <v>689</v>
+        <v>684.45</v>
       </c>
       <c r="G341" t="n">
         <v>698.03</v>
       </c>
       <c r="H341" t="n">
-        <v>-9.029999999999999</v>
+        <v>-13.58</v>
       </c>
       <c r="I341" t="n">
-        <v>678.1</v>
+        <v>675.25</v>
       </c>
       <c r="J341" t="n">
         <v>668.46</v>
       </c>
       <c r="K341" t="n">
-        <v>9.640000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="342">
@@ -18200,31 +18200,31 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>295.95</v>
+        <v>293</v>
       </c>
       <c r="D342" t="n">
         <v>293.6</v>
       </c>
       <c r="E342" t="n">
-        <v>2.35</v>
+        <v>-0.6</v>
       </c>
       <c r="F342" t="n">
-        <v>296.8</v>
+        <v>293.5</v>
       </c>
       <c r="G342" t="n">
         <v>298.16</v>
       </c>
       <c r="H342" t="n">
-        <v>-1.36</v>
+        <v>-4.66</v>
       </c>
       <c r="I342" t="n">
-        <v>291.4</v>
+        <v>289.75</v>
       </c>
       <c r="J342" t="n">
         <v>291.34</v>
       </c>
       <c r="K342" t="n">
-        <v>0.06</v>
+        <v>-1.59</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="343">
@@ -18252,31 +18252,31 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>2145</v>
+        <v>2139</v>
       </c>
       <c r="D343" t="n">
         <v>2081.17</v>
       </c>
       <c r="E343" t="n">
-        <v>63.83</v>
+        <v>57.83</v>
       </c>
       <c r="F343" t="n">
-        <v>2172.8</v>
+        <v>2162.2</v>
       </c>
       <c r="G343" t="n">
         <v>2123.58</v>
       </c>
       <c r="H343" t="n">
-        <v>49.22</v>
+        <v>38.62</v>
       </c>
       <c r="I343" t="n">
-        <v>2131.8</v>
+        <v>2126.3</v>
       </c>
       <c r="J343" t="n">
         <v>2087.5</v>
       </c>
       <c r="K343" t="n">
-        <v>44.3</v>
+        <v>38.8</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="344">
@@ -18304,31 +18304,31 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3414.1</v>
+        <v>3412.2</v>
       </c>
       <c r="D344" t="n">
         <v>3221.33</v>
       </c>
       <c r="E344" t="n">
-        <v>192.77</v>
+        <v>190.87</v>
       </c>
       <c r="F344" t="n">
-        <v>3444.7</v>
+        <v>3453.9</v>
       </c>
       <c r="G344" t="n">
         <v>3418.31</v>
       </c>
       <c r="H344" t="n">
-        <v>26.39</v>
+        <v>35.59</v>
       </c>
       <c r="I344" t="n">
-        <v>3400</v>
+        <v>3412.2</v>
       </c>
       <c r="J344" t="n">
         <v>3344.52</v>
       </c>
       <c r="K344" t="n">
-        <v>55.48</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="345">
@@ -18356,31 +18356,31 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>115.86</v>
+        <v>116.55</v>
       </c>
       <c r="D345" t="n">
         <v>119.93</v>
       </c>
       <c r="E345" t="n">
-        <v>-4.07</v>
+        <v>-3.38</v>
       </c>
       <c r="F345" t="n">
-        <v>117.03</v>
+        <v>117.52</v>
       </c>
       <c r="G345" t="n">
         <v>119.93</v>
       </c>
       <c r="H345" t="n">
-        <v>-2.9</v>
+        <v>-2.41</v>
       </c>
       <c r="I345" t="n">
-        <v>115</v>
+        <v>115.41</v>
       </c>
       <c r="J345" t="n">
         <v>113.72</v>
       </c>
       <c r="K345" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="346">
@@ -18408,31 +18408,31 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>5694</v>
+        <v>5667.5</v>
       </c>
       <c r="D346" t="n">
         <v>5562.14</v>
       </c>
       <c r="E346" t="n">
-        <v>131.86</v>
+        <v>105.36</v>
       </c>
       <c r="F346" t="n">
-        <v>5725</v>
+        <v>5722</v>
       </c>
       <c r="G346" t="n">
         <v>5562.14</v>
       </c>
       <c r="H346" t="n">
-        <v>162.86</v>
+        <v>159.86</v>
       </c>
       <c r="I346" t="n">
-        <v>5646</v>
+        <v>5602</v>
       </c>
       <c r="J346" t="n">
         <v>5533.49</v>
       </c>
       <c r="K346" t="n">
-        <v>112.51</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="347">
@@ -18460,31 +18460,31 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2001.7</v>
+        <v>2032.5</v>
       </c>
       <c r="D347" t="n">
         <v>2040.35</v>
       </c>
       <c r="E347" t="n">
-        <v>-38.65</v>
+        <v>-7.85</v>
       </c>
       <c r="F347" t="n">
-        <v>2028.6</v>
+        <v>2032.5</v>
       </c>
       <c r="G347" t="n">
         <v>2040.35</v>
       </c>
       <c r="H347" t="n">
-        <v>-11.75</v>
+        <v>-7.85</v>
       </c>
       <c r="I347" t="n">
-        <v>1995.3</v>
+        <v>2005</v>
       </c>
       <c r="J347" t="n">
         <v>1960.26</v>
       </c>
       <c r="K347" t="n">
-        <v>35.04</v>
+        <v>44.74</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>1.89</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="348">
@@ -18512,31 +18512,31 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>11120</v>
+        <v>11320</v>
       </c>
       <c r="D348" t="n">
         <v>11031.75</v>
       </c>
       <c r="E348" t="n">
-        <v>88.25</v>
+        <v>288.25</v>
       </c>
       <c r="F348" t="n">
-        <v>11360</v>
+        <v>11410</v>
       </c>
       <c r="G348" t="n">
         <v>11152.7</v>
       </c>
       <c r="H348" t="n">
-        <v>207.3</v>
+        <v>257.3</v>
       </c>
       <c r="I348" t="n">
-        <v>11050</v>
+        <v>11280</v>
       </c>
       <c r="J348" t="n">
         <v>10895.68</v>
       </c>
       <c r="K348" t="n">
-        <v>154.32</v>
+        <v>384.32</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>0.8</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="349">
@@ -18564,31 +18564,31 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>327.15</v>
+        <v>328</v>
       </c>
       <c r="D349" t="n">
         <v>305.81</v>
       </c>
       <c r="E349" t="n">
-        <v>21.34</v>
+        <v>22.19</v>
       </c>
       <c r="F349" t="n">
-        <v>329.5</v>
+        <v>331.7</v>
       </c>
       <c r="G349" t="n">
         <v>330.12</v>
       </c>
       <c r="H349" t="n">
-        <v>-0.62</v>
+        <v>1.58</v>
       </c>
       <c r="I349" t="n">
-        <v>323</v>
+        <v>324.1</v>
       </c>
       <c r="J349" t="n">
         <v>322.58</v>
       </c>
       <c r="K349" t="n">
-        <v>0.42</v>
+        <v>1.52</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>6.98</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="350">
@@ -18616,31 +18616,31 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3268</v>
+        <v>3185</v>
       </c>
       <c r="D350" t="n">
         <v>3334.11</v>
       </c>
       <c r="E350" t="n">
-        <v>-66.11</v>
+        <v>-149.11</v>
       </c>
       <c r="F350" t="n">
-        <v>3289.7</v>
+        <v>3211.4</v>
       </c>
       <c r="G350" t="n">
         <v>3334.11</v>
       </c>
       <c r="H350" t="n">
-        <v>-44.41</v>
+        <v>-122.71</v>
       </c>
       <c r="I350" t="n">
-        <v>3180.1</v>
+        <v>3132</v>
       </c>
       <c r="J350" t="n">
         <v>3257.4</v>
       </c>
       <c r="K350" t="n">
-        <v>-77.3</v>
+        <v>-125.4</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -18649,11 +18649,11 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N350" t="n">
-        <v>1.98</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="351">
@@ -18668,31 +18668,31 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D351" t="n">
         <v>474.36</v>
       </c>
       <c r="E351" t="n">
-        <v>2.64</v>
+        <v>0.64</v>
       </c>
       <c r="F351" t="n">
-        <v>479.25</v>
+        <v>482</v>
       </c>
       <c r="G351" t="n">
         <v>483.15</v>
       </c>
       <c r="H351" t="n">
-        <v>-3.9</v>
+        <v>-1.15</v>
       </c>
       <c r="I351" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J351" t="n">
         <v>472.18</v>
       </c>
       <c r="K351" t="n">
-        <v>-0.18</v>
+        <v>2.82</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="352">
@@ -18720,31 +18720,31 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>173.29</v>
+        <v>173</v>
       </c>
       <c r="D352" t="n">
         <v>172.21</v>
       </c>
       <c r="E352" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="F352" t="n">
-        <v>173.66</v>
+        <v>173.69</v>
       </c>
       <c r="G352" t="n">
         <v>174.16</v>
       </c>
       <c r="H352" t="n">
-        <v>-0.5</v>
+        <v>-0.47</v>
       </c>
       <c r="I352" t="n">
-        <v>171.65</v>
+        <v>172.3</v>
       </c>
       <c r="J352" t="n">
         <v>170.16</v>
       </c>
       <c r="K352" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="353">
@@ -18772,31 +18772,31 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1058.5</v>
+        <v>1034</v>
       </c>
       <c r="D353" t="n">
         <v>1050.1</v>
       </c>
       <c r="E353" t="n">
-        <v>8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="F353" t="n">
-        <v>1058.5</v>
+        <v>1040.45</v>
       </c>
       <c r="G353" t="n">
         <v>1067.24</v>
       </c>
       <c r="H353" t="n">
-        <v>-8.74</v>
+        <v>-26.79</v>
       </c>
       <c r="I353" t="n">
-        <v>1043.3</v>
+        <v>1024.6</v>
       </c>
       <c r="J353" t="n">
         <v>1042.84</v>
       </c>
       <c r="K353" t="n">
-        <v>0.46</v>
+        <v>-18.24</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>0.8</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="354">
@@ -18824,31 +18824,31 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>403.3</v>
+        <v>393.45</v>
       </c>
       <c r="D354" t="n">
         <v>453.3</v>
       </c>
       <c r="E354" t="n">
-        <v>-50</v>
+        <v>-59.85</v>
       </c>
       <c r="F354" t="n">
-        <v>405</v>
+        <v>396.49</v>
       </c>
       <c r="G354" t="n">
         <v>453.3</v>
       </c>
       <c r="H354" t="n">
-        <v>-48.3</v>
+        <v>-56.81</v>
       </c>
       <c r="I354" t="n">
-        <v>397.5</v>
+        <v>383.62</v>
       </c>
       <c r="J354" t="n">
         <v>396.64</v>
       </c>
       <c r="K354" t="n">
-        <v>0.86</v>
+        <v>-13.02</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -18857,11 +18857,11 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N354" t="n">
-        <v>11.03</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="355">
@@ -18876,31 +18876,31 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1251.3</v>
+        <v>1265</v>
       </c>
       <c r="D355" t="n">
         <v>1241.37</v>
       </c>
       <c r="E355" t="n">
-        <v>9.93</v>
+        <v>23.63</v>
       </c>
       <c r="F355" t="n">
-        <v>1261.6</v>
+        <v>1267</v>
       </c>
       <c r="G355" t="n">
         <v>1249.06</v>
       </c>
       <c r="H355" t="n">
-        <v>12.54</v>
+        <v>17.94</v>
       </c>
       <c r="I355" t="n">
-        <v>1245.1</v>
+        <v>1252</v>
       </c>
       <c r="J355" t="n">
         <v>1220.08</v>
       </c>
       <c r="K355" t="n">
-        <v>25.02</v>
+        <v>31.92</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="356">
@@ -18928,31 +18928,31 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>5685</v>
+        <v>5735</v>
       </c>
       <c r="D356" t="n">
         <v>5639.88</v>
       </c>
       <c r="E356" t="n">
-        <v>45.12</v>
+        <v>95.12</v>
       </c>
       <c r="F356" t="n">
-        <v>5728</v>
+        <v>5735</v>
       </c>
       <c r="G356" t="n">
         <v>5639.88</v>
       </c>
       <c r="H356" t="n">
-        <v>88.12</v>
+        <v>95.12</v>
       </c>
       <c r="I356" t="n">
-        <v>5650</v>
+        <v>5642</v>
       </c>
       <c r="J356" t="n">
         <v>5521.63</v>
       </c>
       <c r="K356" t="n">
-        <v>128.37</v>
+        <v>120.37</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>0.8</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="357">
@@ -18980,31 +18980,31 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>183.6</v>
+        <v>183.45</v>
       </c>
       <c r="D357" t="n">
         <v>193.94</v>
       </c>
       <c r="E357" t="n">
-        <v>-10.34</v>
+        <v>-10.49</v>
       </c>
       <c r="F357" t="n">
-        <v>184.7</v>
+        <v>185.3</v>
       </c>
       <c r="G357" t="n">
         <v>193.94</v>
       </c>
       <c r="H357" t="n">
-        <v>-9.24</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I357" t="n">
-        <v>182.02</v>
+        <v>182.5</v>
       </c>
       <c r="J357" t="n">
         <v>179.91</v>
       </c>
       <c r="K357" t="n">
-        <v>2.11</v>
+        <v>2.59</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>5.33</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="358">
@@ -19032,31 +19032,31 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1635.8</v>
+        <v>1631</v>
       </c>
       <c r="D358" t="n">
         <v>1677.53</v>
       </c>
       <c r="E358" t="n">
-        <v>-41.73</v>
+        <v>-46.53</v>
       </c>
       <c r="F358" t="n">
-        <v>1641.6</v>
+        <v>1651.3</v>
       </c>
       <c r="G358" t="n">
         <v>1677.53</v>
       </c>
       <c r="H358" t="n">
-        <v>-35.93</v>
+        <v>-26.23</v>
       </c>
       <c r="I358" t="n">
-        <v>1618.1</v>
+        <v>1590</v>
       </c>
       <c r="J358" t="n">
         <v>1577.23</v>
       </c>
       <c r="K358" t="n">
-        <v>40.87</v>
+        <v>12.77</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="359">
@@ -19084,31 +19084,31 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1785</v>
+        <v>1795.2</v>
       </c>
       <c r="D359" t="n">
         <v>1770.83</v>
       </c>
       <c r="E359" t="n">
-        <v>14.17</v>
+        <v>24.37</v>
       </c>
       <c r="F359" t="n">
-        <v>1811.8</v>
+        <v>1799</v>
       </c>
       <c r="G359" t="n">
         <v>1770.83</v>
       </c>
       <c r="H359" t="n">
-        <v>40.97</v>
+        <v>28.17</v>
       </c>
       <c r="I359" t="n">
-        <v>1773.5</v>
+        <v>1757</v>
       </c>
       <c r="J359" t="n">
         <v>1728.56</v>
       </c>
       <c r="K359" t="n">
-        <v>44.94</v>
+        <v>28.44</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>0.8</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="360">
@@ -19136,31 +19136,31 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>1873</v>
+        <v>1891.7</v>
       </c>
       <c r="D360" t="n">
         <v>1903.99</v>
       </c>
       <c r="E360" t="n">
-        <v>-30.99</v>
+        <v>-12.29</v>
       </c>
       <c r="F360" t="n">
-        <v>1900.8</v>
+        <v>1891.7</v>
       </c>
       <c r="G360" t="n">
         <v>1903.99</v>
       </c>
       <c r="H360" t="n">
-        <v>-3.19</v>
+        <v>-12.29</v>
       </c>
       <c r="I360" t="n">
-        <v>1869.6</v>
+        <v>1851</v>
       </c>
       <c r="J360" t="n">
         <v>1820.59</v>
       </c>
       <c r="K360" t="n">
-        <v>49.01</v>
+        <v>30.41</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>1.63</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="361">
@@ -19188,31 +19188,31 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>4090</v>
+        <v>4093</v>
       </c>
       <c r="D361" t="n">
         <v>4071.14</v>
       </c>
       <c r="E361" t="n">
-        <v>18.86</v>
+        <v>21.86</v>
       </c>
       <c r="F361" t="n">
-        <v>4107.1</v>
+        <v>4100</v>
       </c>
       <c r="G361" t="n">
         <v>4113.19</v>
       </c>
       <c r="H361" t="n">
-        <v>-6.09</v>
+        <v>-13.19</v>
       </c>
       <c r="I361" t="n">
-        <v>4077.7</v>
+        <v>4061.4</v>
       </c>
       <c r="J361" t="n">
         <v>4035.27</v>
       </c>
       <c r="K361" t="n">
-        <v>42.43</v>
+        <v>26.13</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="362">
@@ -19249,22 +19249,22 @@
         <v>7.86</v>
       </c>
       <c r="F362" t="n">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="G362" t="n">
         <v>1002.82</v>
       </c>
       <c r="H362" t="n">
-        <v>12.18</v>
+        <v>1.18</v>
       </c>
       <c r="I362" t="n">
-        <v>988.3</v>
+        <v>968.55</v>
       </c>
       <c r="J362" t="n">
         <v>980.05</v>
       </c>
       <c r="K362" t="n">
-        <v>8.25</v>
+        <v>-11.5</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -19292,31 +19292,31 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>2207</v>
+        <v>2218.8</v>
       </c>
       <c r="D363" t="n">
         <v>2189.74</v>
       </c>
       <c r="E363" t="n">
-        <v>17.26</v>
+        <v>29.06</v>
       </c>
       <c r="F363" t="n">
-        <v>2235.4</v>
+        <v>2251.7</v>
       </c>
       <c r="G363" t="n">
         <v>2240.9</v>
       </c>
       <c r="H363" t="n">
-        <v>-5.5</v>
+        <v>10.8</v>
       </c>
       <c r="I363" t="n">
-        <v>2206.1</v>
+        <v>2211.1</v>
       </c>
       <c r="J363" t="n">
         <v>2190.22</v>
       </c>
       <c r="K363" t="n">
-        <v>15.88</v>
+        <v>20.88</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>0.79</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="364">
@@ -19344,31 +19344,31 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>516.4</v>
+        <v>515.05</v>
       </c>
       <c r="D364" t="n">
         <v>478.47</v>
       </c>
       <c r="E364" t="n">
-        <v>37.93</v>
+        <v>36.58</v>
       </c>
       <c r="F364" t="n">
-        <v>524.2</v>
+        <v>523</v>
       </c>
       <c r="G364" t="n">
         <v>486.67</v>
       </c>
       <c r="H364" t="n">
-        <v>37.53</v>
+        <v>36.33</v>
       </c>
       <c r="I364" t="n">
-        <v>513.05</v>
+        <v>512.15</v>
       </c>
       <c r="J364" t="n">
         <v>501.38</v>
       </c>
       <c r="K364" t="n">
-        <v>11.67</v>
+        <v>10.77</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>7.93</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="365">
@@ -19396,31 +19396,31 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2540</v>
+        <v>2552</v>
       </c>
       <c r="D365" t="n">
         <v>2560.88</v>
       </c>
       <c r="E365" t="n">
-        <v>-20.88</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="F365" t="n">
-        <v>2572.6</v>
+        <v>2596</v>
       </c>
       <c r="G365" t="n">
         <v>2560.88</v>
       </c>
       <c r="H365" t="n">
-        <v>11.72</v>
+        <v>35.12</v>
       </c>
       <c r="I365" t="n">
-        <v>2523.4</v>
+        <v>2542</v>
       </c>
       <c r="J365" t="n">
         <v>2457.21</v>
       </c>
       <c r="K365" t="n">
-        <v>66.19</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>0.82</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="366">
@@ -19448,31 +19448,31 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1349</v>
+        <v>1350.1</v>
       </c>
       <c r="D366" t="n">
         <v>1338.29</v>
       </c>
       <c r="E366" t="n">
-        <v>10.71</v>
+        <v>11.81</v>
       </c>
       <c r="F366" t="n">
-        <v>1360</v>
+        <v>1367.8</v>
       </c>
       <c r="G366" t="n">
         <v>1338.29</v>
       </c>
       <c r="H366" t="n">
-        <v>21.71</v>
+        <v>29.51</v>
       </c>
       <c r="I366" t="n">
-        <v>1336.7</v>
+        <v>1345.2</v>
       </c>
       <c r="J366" t="n">
         <v>1301.3</v>
       </c>
       <c r="K366" t="n">
-        <v>35.4</v>
+        <v>43.9</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="367">
@@ -19500,31 +19500,31 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14570</v>
+        <v>14850</v>
       </c>
       <c r="D367" t="n">
         <v>14173.87</v>
       </c>
       <c r="E367" t="n">
-        <v>396.13</v>
+        <v>676.13</v>
       </c>
       <c r="F367" t="n">
-        <v>15000</v>
+        <v>14924</v>
       </c>
       <c r="G367" t="n">
         <v>14825.24</v>
       </c>
       <c r="H367" t="n">
-        <v>174.76</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="I367" t="n">
-        <v>14484</v>
+        <v>14620</v>
       </c>
       <c r="J367" t="n">
         <v>14490.99</v>
       </c>
       <c r="K367" t="n">
-        <v>-6.99</v>
+        <v>129.01</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>2.79</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="368">
@@ -19552,31 +19552,31 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>870.45</v>
+        <v>876.9</v>
       </c>
       <c r="D368" t="n">
         <v>863.54</v>
       </c>
       <c r="E368" t="n">
-        <v>6.91</v>
+        <v>13.36</v>
       </c>
       <c r="F368" t="n">
-        <v>883.85</v>
+        <v>880.9</v>
       </c>
       <c r="G368" t="n">
         <v>863.9</v>
       </c>
       <c r="H368" t="n">
-        <v>19.95</v>
+        <v>17</v>
       </c>
       <c r="I368" t="n">
-        <v>862</v>
+        <v>870.5</v>
       </c>
       <c r="J368" t="n">
         <v>847.41</v>
       </c>
       <c r="K368" t="n">
-        <v>14.59</v>
+        <v>23.09</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -23378,31 +23378,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>327.15</v>
+        <v>328</v>
       </c>
       <c r="D15" t="n">
         <v>305.81</v>
       </c>
       <c r="E15" t="n">
-        <v>21.34</v>
+        <v>22.19</v>
       </c>
       <c r="F15" t="n">
-        <v>329.5</v>
+        <v>331.7</v>
       </c>
       <c r="G15" t="n">
         <v>330.12</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.62</v>
+        <v>1.58</v>
       </c>
       <c r="I15" t="n">
-        <v>323</v>
+        <v>324.1</v>
       </c>
       <c r="J15" t="n">
         <v>322.58</v>
       </c>
       <c r="K15" t="n">
-        <v>0.42</v>
+        <v>1.52</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.98</v>
+        <v>7.26</v>
       </c>
     </row>
   </sheetData>
@@ -24192,31 +24192,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14570</v>
+        <v>14850</v>
       </c>
       <c r="D15" t="n">
         <v>14173.87</v>
       </c>
       <c r="E15" t="n">
-        <v>396.13</v>
+        <v>676.13</v>
       </c>
       <c r="F15" t="n">
-        <v>15000</v>
+        <v>14924</v>
       </c>
       <c r="G15" t="n">
         <v>14825.24</v>
       </c>
       <c r="H15" t="n">
-        <v>174.76</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>14484</v>
+        <v>14620</v>
       </c>
       <c r="J15" t="n">
         <v>14490.99</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.99</v>
+        <v>129.01</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.79</v>
+        <v>4.77</v>
       </c>
     </row>
   </sheetData>
@@ -25006,31 +25006,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1873</v>
+        <v>1891.7</v>
       </c>
       <c r="D15" t="n">
         <v>1903.99</v>
       </c>
       <c r="E15" t="n">
-        <v>-30.99</v>
+        <v>-12.29</v>
       </c>
       <c r="F15" t="n">
-        <v>1900.8</v>
+        <v>1891.7</v>
       </c>
       <c r="G15" t="n">
         <v>1903.99</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.19</v>
+        <v>-12.29</v>
       </c>
       <c r="I15" t="n">
-        <v>1869.6</v>
+        <v>1851</v>
       </c>
       <c r="J15" t="n">
         <v>1820.59</v>
       </c>
       <c r="K15" t="n">
-        <v>49.01</v>
+        <v>30.41</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -25716,31 +25716,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5694</v>
+        <v>5667.5</v>
       </c>
       <c r="D13" t="n">
         <v>5562.14</v>
       </c>
       <c r="E13" t="n">
-        <v>131.86</v>
+        <v>105.36</v>
       </c>
       <c r="F13" t="n">
-        <v>5725</v>
+        <v>5722</v>
       </c>
       <c r="G13" t="n">
         <v>5562.14</v>
       </c>
       <c r="H13" t="n">
-        <v>162.86</v>
+        <v>159.86</v>
       </c>
       <c r="I13" t="n">
-        <v>5646</v>
+        <v>5602</v>
       </c>
       <c r="J13" t="n">
         <v>5533.49</v>
       </c>
       <c r="K13" t="n">
-        <v>112.51</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>
@@ -26530,31 +26530,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>115.86</v>
+        <v>116.55</v>
       </c>
       <c r="D15" t="n">
         <v>119.93</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.07</v>
+        <v>-3.38</v>
       </c>
       <c r="F15" t="n">
-        <v>117.03</v>
+        <v>117.52</v>
       </c>
       <c r="G15" t="n">
         <v>119.93</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.9</v>
+        <v>-2.41</v>
       </c>
       <c r="I15" t="n">
-        <v>115</v>
+        <v>115.41</v>
       </c>
       <c r="J15" t="n">
         <v>113.72</v>
       </c>
       <c r="K15" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -27292,31 +27292,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3414.1</v>
+        <v>3412.2</v>
       </c>
       <c r="D14" t="n">
         <v>3221.33</v>
       </c>
       <c r="E14" t="n">
-        <v>192.77</v>
+        <v>190.87</v>
       </c>
       <c r="F14" t="n">
-        <v>3444.7</v>
+        <v>3453.9</v>
       </c>
       <c r="G14" t="n">
         <v>3418.31</v>
       </c>
       <c r="H14" t="n">
-        <v>26.39</v>
+        <v>35.59</v>
       </c>
       <c r="I14" t="n">
-        <v>3400</v>
+        <v>3412.2</v>
       </c>
       <c r="J14" t="n">
         <v>3344.52</v>
       </c>
       <c r="K14" t="n">
-        <v>55.48</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
     </row>
   </sheetData>
@@ -28054,31 +28054,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>516.4</v>
+        <v>515.05</v>
       </c>
       <c r="D14" t="n">
         <v>478.47</v>
       </c>
       <c r="E14" t="n">
-        <v>37.93</v>
+        <v>36.58</v>
       </c>
       <c r="F14" t="n">
-        <v>524.2</v>
+        <v>523</v>
       </c>
       <c r="G14" t="n">
         <v>486.67</v>
       </c>
       <c r="H14" t="n">
-        <v>37.53</v>
+        <v>36.33</v>
       </c>
       <c r="I14" t="n">
-        <v>513.05</v>
+        <v>512.15</v>
       </c>
       <c r="J14" t="n">
         <v>501.38</v>
       </c>
       <c r="K14" t="n">
-        <v>11.67</v>
+        <v>10.77</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.93</v>
+        <v>7.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N368"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19590,6 +19590,1618 @@
       </c>
       <c r="N368" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2012.25</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="F369" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="G369" t="n">
+        <v>2012.25</v>
+      </c>
+      <c r="H369" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="I369" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J369" t="n">
+        <v>1979.81</v>
+      </c>
+      <c r="K369" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1048.91</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F370" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1056.46</v>
+      </c>
+      <c r="H370" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1031.3</v>
+      </c>
+      <c r="J370" t="n">
+        <v>1033.1</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N370" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>115.93</v>
+      </c>
+      <c r="D371" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="E371" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F371" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="G371" t="n">
+        <v>117.64</v>
+      </c>
+      <c r="H371" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I371" t="n">
+        <v>115.01</v>
+      </c>
+      <c r="J371" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N371" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>3443</v>
+      </c>
+      <c r="D372" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="E372" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="F372" t="n">
+        <v>3443</v>
+      </c>
+      <c r="G372" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="H372" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="I372" t="n">
+        <v>3396.8</v>
+      </c>
+      <c r="J372" t="n">
+        <v>3423.64</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-26.84</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N372" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="D373" t="n">
+        <v>11739.24</v>
+      </c>
+      <c r="E373" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="F373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="G373" t="n">
+        <v>11951.36</v>
+      </c>
+      <c r="H373" t="n">
+        <v>-222.36</v>
+      </c>
+      <c r="I373" t="n">
+        <v>11355</v>
+      </c>
+      <c r="J373" t="n">
+        <v>11691.57</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-336.57</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N373" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>2139.3</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2216.34</v>
+      </c>
+      <c r="E374" t="n">
+        <v>-77.04000000000001</v>
+      </c>
+      <c r="F374" t="n">
+        <v>2151.8</v>
+      </c>
+      <c r="G374" t="n">
+        <v>2216.34</v>
+      </c>
+      <c r="H374" t="n">
+        <v>-64.54000000000001</v>
+      </c>
+      <c r="I374" t="n">
+        <v>2124</v>
+      </c>
+      <c r="J374" t="n">
+        <v>2102.97</v>
+      </c>
+      <c r="K374" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N374" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="D375" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="E375" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F375" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="G375" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="H375" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="I375" t="n">
+        <v>171.58</v>
+      </c>
+      <c r="J375" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N375" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1948.7</v>
+      </c>
+      <c r="E376" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G376" t="n">
+        <v>1974.82</v>
+      </c>
+      <c r="H376" t="n">
+        <v>-27.82</v>
+      </c>
+      <c r="I376" t="n">
+        <v>1923.4</v>
+      </c>
+      <c r="J376" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N376" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>1011.5</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-16.25</v>
+      </c>
+      <c r="F377" t="n">
+        <v>1019.9</v>
+      </c>
+      <c r="G377" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="H377" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="I377" t="n">
+        <v>992</v>
+      </c>
+      <c r="J377" t="n">
+        <v>1003.04</v>
+      </c>
+      <c r="K377" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1837.63</v>
+      </c>
+      <c r="E378" t="n">
+        <v>-39.33</v>
+      </c>
+      <c r="F378" t="n">
+        <v>1815</v>
+      </c>
+      <c r="G378" t="n">
+        <v>1837.63</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-22.63</v>
+      </c>
+      <c r="I378" t="n">
+        <v>1775</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1760.02</v>
+      </c>
+      <c r="K378" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>3280</v>
+      </c>
+      <c r="D379" t="n">
+        <v>3158.38</v>
+      </c>
+      <c r="E379" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="F379" t="n">
+        <v>3308.7</v>
+      </c>
+      <c r="G379" t="n">
+        <v>3343.9</v>
+      </c>
+      <c r="H379" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="I379" t="n">
+        <v>3254.3</v>
+      </c>
+      <c r="J379" t="n">
+        <v>3271.27</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-16.97</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N379" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D380" t="n">
+        <v>4174.25</v>
+      </c>
+      <c r="E380" t="n">
+        <v>-55.25</v>
+      </c>
+      <c r="F380" t="n">
+        <v>4125.3</v>
+      </c>
+      <c r="G380" t="n">
+        <v>4179.37</v>
+      </c>
+      <c r="H380" t="n">
+        <v>-54.07</v>
+      </c>
+      <c r="I380" t="n">
+        <v>4066.6</v>
+      </c>
+      <c r="J380" t="n">
+        <v>4106.99</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-40.39</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="D381" t="n">
+        <v>11708.14</v>
+      </c>
+      <c r="E381" t="n">
+        <v>-418.14</v>
+      </c>
+      <c r="F381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="G381" t="n">
+        <v>11708.14</v>
+      </c>
+      <c r="H381" t="n">
+        <v>-418.14</v>
+      </c>
+      <c r="I381" t="n">
+        <v>10811</v>
+      </c>
+      <c r="J381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-479</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="D382" t="n">
+        <v>471.88</v>
+      </c>
+      <c r="E382" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="F382" t="n">
+        <v>479</v>
+      </c>
+      <c r="G382" t="n">
+        <v>471.88</v>
+      </c>
+      <c r="H382" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I382" t="n">
+        <v>466.05</v>
+      </c>
+      <c r="J382" t="n">
+        <v>455.69</v>
+      </c>
+      <c r="K382" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>2232.5</v>
+      </c>
+      <c r="D383" t="n">
+        <v>2288.38</v>
+      </c>
+      <c r="E383" t="n">
+        <v>-55.88</v>
+      </c>
+      <c r="F383" t="n">
+        <v>2243.8</v>
+      </c>
+      <c r="G383" t="n">
+        <v>2292.81</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-49.01</v>
+      </c>
+      <c r="I383" t="n">
+        <v>2190</v>
+      </c>
+      <c r="J383" t="n">
+        <v>2232.5</v>
+      </c>
+      <c r="K383" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="D384" t="n">
+        <v>178.29</v>
+      </c>
+      <c r="E384" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F384" t="n">
+        <v>187.33</v>
+      </c>
+      <c r="G384" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="H384" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="I384" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="J384" t="n">
+        <v>183.96</v>
+      </c>
+      <c r="K384" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>331</v>
+      </c>
+      <c r="D385" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="E385" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="F385" t="n">
+        <v>331</v>
+      </c>
+      <c r="G385" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="H385" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="I385" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J385" t="n">
+        <v>331</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D386" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="E386" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="F386" t="n">
+        <v>402</v>
+      </c>
+      <c r="G386" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="H386" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="I386" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="J386" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1892.8</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1895.63</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="F387" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="G387" t="n">
+        <v>1903.48</v>
+      </c>
+      <c r="H387" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I387" t="n">
+        <v>1870</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1861.23</v>
+      </c>
+      <c r="K387" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="D388" t="n">
+        <v>294.24</v>
+      </c>
+      <c r="E388" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="F388" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="G388" t="n">
+        <v>294.24</v>
+      </c>
+      <c r="H388" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I388" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="J388" t="n">
+        <v>287.9</v>
+      </c>
+      <c r="K388" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>1253.4</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1287.49</v>
+      </c>
+      <c r="E389" t="n">
+        <v>-34.09</v>
+      </c>
+      <c r="F389" t="n">
+        <v>1256.5</v>
+      </c>
+      <c r="G389" t="n">
+        <v>1287.49</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-30.99</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1240.5</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1234.86</v>
+      </c>
+      <c r="K389" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>5624.5</v>
+      </c>
+      <c r="D390" t="n">
+        <v>5765.14</v>
+      </c>
+      <c r="E390" t="n">
+        <v>-140.64</v>
+      </c>
+      <c r="F390" t="n">
+        <v>5682</v>
+      </c>
+      <c r="G390" t="n">
+        <v>5765.14</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-83.14</v>
+      </c>
+      <c r="I390" t="n">
+        <v>5590</v>
+      </c>
+      <c r="J390" t="n">
+        <v>5516.7</v>
+      </c>
+      <c r="K390" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>5655</v>
+      </c>
+      <c r="D391" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="E391" t="n">
+        <v>-153.2</v>
+      </c>
+      <c r="F391" t="n">
+        <v>5687</v>
+      </c>
+      <c r="G391" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="H391" t="n">
+        <v>-121.2</v>
+      </c>
+      <c r="I391" t="n">
+        <v>5570.5</v>
+      </c>
+      <c r="J391" t="n">
+        <v>5555.36</v>
+      </c>
+      <c r="K391" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>2610</v>
+      </c>
+      <c r="D392" t="n">
+        <v>2621.75</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="F392" t="n">
+        <v>2621.7</v>
+      </c>
+      <c r="G392" t="n">
+        <v>2621.75</v>
+      </c>
+      <c r="H392" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2552.86</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-32.86</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1211.06</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F393" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G393" t="n">
+        <v>1223.84</v>
+      </c>
+      <c r="H393" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1196.92</v>
+      </c>
+      <c r="K393" t="n">
+        <v>-10.52</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>1051.05</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1043.22</v>
+      </c>
+      <c r="E394" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F394" t="n">
+        <v>1057</v>
+      </c>
+      <c r="G394" t="n">
+        <v>1069.88</v>
+      </c>
+      <c r="H394" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1046.59</v>
+      </c>
+      <c r="K394" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>682.95</v>
+      </c>
+      <c r="D395" t="n">
+        <v>668.76</v>
+      </c>
+      <c r="E395" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="F395" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="G395" t="n">
+        <v>694.11</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="I395" t="n">
+        <v>678.3</v>
+      </c>
+      <c r="J395" t="n">
+        <v>678.96</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="D396" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="E396" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="F396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="G396" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="I396" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-590</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1372.8</v>
+      </c>
+      <c r="E397" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="F397" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G397" t="n">
+        <v>1372.8</v>
+      </c>
+      <c r="H397" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1328.1</v>
+      </c>
+      <c r="J397" t="n">
+        <v>1315.92</v>
+      </c>
+      <c r="K397" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>878</v>
+      </c>
+      <c r="D398" t="n">
+        <v>898.71</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-20.71</v>
+      </c>
+      <c r="F398" t="n">
+        <v>881.75</v>
+      </c>
+      <c r="G398" t="n">
+        <v>898.71</v>
+      </c>
+      <c r="H398" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="I398" t="n">
+        <v>869</v>
+      </c>
+      <c r="J398" t="n">
+        <v>863.09</v>
+      </c>
+      <c r="K398" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>516</v>
+      </c>
+      <c r="D399" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="F399" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="G399" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="H399" t="n">
+        <v>-41.49</v>
+      </c>
+      <c r="I399" t="n">
+        <v>511.3</v>
+      </c>
+      <c r="J399" t="n">
+        <v>506.16</v>
+      </c>
+      <c r="K399" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>7.84</v>
       </c>
     </row>
   </sheetData>
@@ -19845,7 +21457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20594,6 +22206,58 @@
       </c>
       <c r="N14" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1211.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1223.84</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1196.92</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-10.52</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -22615,7 +24279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23416,6 +25080,58 @@
       </c>
       <c r="N15" t="n">
         <v>7.26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>331</v>
+      </c>
+      <c r="D16" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="F16" t="n">
+        <v>331</v>
+      </c>
+      <c r="G16" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="I16" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>331</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>7.63</v>
       </c>
     </row>
   </sheetData>
@@ -23429,7 +25145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24230,6 +25946,58 @@
       </c>
       <c r="N15" t="n">
         <v>4.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14990</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14990</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14990</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-590</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>6.05</v>
       </c>
     </row>
   </sheetData>
@@ -24243,7 +26011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25044,6 +26812,58 @@
       </c>
       <c r="N15" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1892.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1895.63</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1903.48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1870</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1861.23</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -25057,7 +26877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25754,6 +27574,58 @@
       </c>
       <c r="N13" t="n">
         <v>1.89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5655</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-153.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5687</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-121.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5570.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5555.36</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2.64</v>
       </c>
     </row>
   </sheetData>
@@ -25767,7 +27639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26568,6 +28440,58 @@
       </c>
       <c r="N15" t="n">
         <v>2.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>115.93</v>
+      </c>
+      <c r="D16" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F16" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>117.64</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I16" t="n">
+        <v>115.01</v>
+      </c>
+      <c r="J16" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>
@@ -26581,7 +28505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27330,6 +29254,58 @@
       </c>
       <c r="N14" t="n">
         <v>5.93</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3443</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3443</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3396.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3423.64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-26.84</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>6.34</v>
       </c>
     </row>
   </sheetData>
@@ -27343,7 +29319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28092,6 +30068,58 @@
       </c>
       <c r="N14" t="n">
         <v>7.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>516</v>
+      </c>
+      <c r="D15" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-41.49</v>
+      </c>
+      <c r="I15" t="n">
+        <v>511.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>506.16</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>7.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -19604,31 +19604,31 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>2004</v>
+        <v>2001.7</v>
       </c>
       <c r="D369" t="n">
         <v>2012.25</v>
       </c>
       <c r="E369" t="n">
-        <v>-8.25</v>
+        <v>-10.55</v>
       </c>
       <c r="F369" t="n">
-        <v>2011.7</v>
+        <v>2028.6</v>
       </c>
       <c r="G369" t="n">
         <v>2012.25</v>
       </c>
       <c r="H369" t="n">
-        <v>-0.55</v>
+        <v>16.35</v>
       </c>
       <c r="I369" t="n">
-        <v>1985</v>
+        <v>1995.3</v>
       </c>
       <c r="J369" t="n">
         <v>1979.81</v>
       </c>
       <c r="K369" t="n">
-        <v>5.19</v>
+        <v>15.49</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="370">
@@ -19656,31 +19656,31 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1048</v>
+        <v>1039.5</v>
       </c>
       <c r="D370" t="n">
         <v>1048.91</v>
       </c>
       <c r="E370" t="n">
-        <v>-0.91</v>
+        <v>-9.41</v>
       </c>
       <c r="F370" t="n">
-        <v>1048</v>
+        <v>1047.9</v>
       </c>
       <c r="G370" t="n">
         <v>1056.46</v>
       </c>
       <c r="H370" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="I370" t="n">
-        <v>1031.3</v>
+        <v>1032.1</v>
       </c>
       <c r="J370" t="n">
         <v>1033.1</v>
       </c>
       <c r="K370" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="371">
@@ -19708,31 +19708,31 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>115.93</v>
+        <v>115.86</v>
       </c>
       <c r="D371" t="n">
         <v>113.57</v>
       </c>
       <c r="E371" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="F371" t="n">
-        <v>116.9</v>
+        <v>117.03</v>
       </c>
       <c r="G371" t="n">
         <v>117.64</v>
       </c>
       <c r="H371" t="n">
-        <v>-0.74</v>
+        <v>-0.61</v>
       </c>
       <c r="I371" t="n">
-        <v>115.01</v>
+        <v>115</v>
       </c>
       <c r="J371" t="n">
         <v>115.06</v>
       </c>
       <c r="K371" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="372">
@@ -19760,31 +19760,31 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3443</v>
+        <v>3414.1</v>
       </c>
       <c r="D372" t="n">
         <v>3676.17</v>
       </c>
       <c r="E372" t="n">
-        <v>-233.17</v>
+        <v>-262.07</v>
       </c>
       <c r="F372" t="n">
-        <v>3443</v>
+        <v>3444.7</v>
       </c>
       <c r="G372" t="n">
         <v>3676.17</v>
       </c>
       <c r="H372" t="n">
-        <v>-233.17</v>
+        <v>-231.47</v>
       </c>
       <c r="I372" t="n">
-        <v>3396.8</v>
+        <v>3400</v>
       </c>
       <c r="J372" t="n">
         <v>3423.64</v>
       </c>
       <c r="K372" t="n">
-        <v>-26.84</v>
+        <v>-23.64</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>6.34</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="373">
@@ -19812,31 +19812,31 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>11729</v>
+        <v>11518</v>
       </c>
       <c r="D373" t="n">
         <v>11739.24</v>
       </c>
       <c r="E373" t="n">
-        <v>-10.24</v>
+        <v>-221.24</v>
       </c>
       <c r="F373" t="n">
-        <v>11729</v>
+        <v>11898</v>
       </c>
       <c r="G373" t="n">
         <v>11951.36</v>
       </c>
       <c r="H373" t="n">
-        <v>-222.36</v>
+        <v>-53.36</v>
       </c>
       <c r="I373" t="n">
-        <v>11355</v>
+        <v>11457</v>
       </c>
       <c r="J373" t="n">
         <v>11691.57</v>
       </c>
       <c r="K373" t="n">
-        <v>-336.57</v>
+        <v>-234.57</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>0.09</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="374">
@@ -19864,31 +19864,31 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2139.3</v>
+        <v>2145</v>
       </c>
       <c r="D374" t="n">
         <v>2216.34</v>
       </c>
       <c r="E374" t="n">
-        <v>-77.04000000000001</v>
+        <v>-71.34</v>
       </c>
       <c r="F374" t="n">
-        <v>2151.8</v>
+        <v>2172.8</v>
       </c>
       <c r="G374" t="n">
         <v>2216.34</v>
       </c>
       <c r="H374" t="n">
-        <v>-64.54000000000001</v>
+        <v>-43.54</v>
       </c>
       <c r="I374" t="n">
-        <v>2124</v>
+        <v>2131.8</v>
       </c>
       <c r="J374" t="n">
         <v>2102.97</v>
       </c>
       <c r="K374" t="n">
-        <v>21.03</v>
+        <v>28.83</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="375">
@@ -19916,31 +19916,31 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>174.69</v>
+        <v>173.29</v>
       </c>
       <c r="D375" t="n">
         <v>176.9</v>
       </c>
       <c r="E375" t="n">
-        <v>-2.21</v>
+        <v>-3.61</v>
       </c>
       <c r="F375" t="n">
-        <v>174.69</v>
+        <v>173.66</v>
       </c>
       <c r="G375" t="n">
         <v>176.9</v>
       </c>
       <c r="H375" t="n">
-        <v>-2.21</v>
+        <v>-3.24</v>
       </c>
       <c r="I375" t="n">
-        <v>171.58</v>
+        <v>171.65</v>
       </c>
       <c r="J375" t="n">
         <v>172.04</v>
       </c>
       <c r="K375" t="n">
-        <v>-0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="376">
@@ -19968,31 +19968,31 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1947</v>
+        <v>1935</v>
       </c>
       <c r="D376" t="n">
         <v>1948.7</v>
       </c>
       <c r="E376" t="n">
-        <v>-1.7</v>
+        <v>-13.7</v>
       </c>
       <c r="F376" t="n">
-        <v>1947</v>
+        <v>1952.5</v>
       </c>
       <c r="G376" t="n">
         <v>1974.82</v>
       </c>
       <c r="H376" t="n">
-        <v>-27.82</v>
+        <v>-22.32</v>
       </c>
       <c r="I376" t="n">
-        <v>1923.4</v>
+        <v>1932.5</v>
       </c>
       <c r="J376" t="n">
         <v>1931.58</v>
       </c>
       <c r="K376" t="n">
-        <v>-8.18</v>
+        <v>0.92</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="377">
@@ -20020,31 +20020,31 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1011.5</v>
+        <v>990</v>
       </c>
       <c r="D377" t="n">
         <v>1027.75</v>
       </c>
       <c r="E377" t="n">
-        <v>-16.25</v>
+        <v>-37.75</v>
       </c>
       <c r="F377" t="n">
-        <v>1019.9</v>
+        <v>1015</v>
       </c>
       <c r="G377" t="n">
         <v>1027.75</v>
       </c>
       <c r="H377" t="n">
-        <v>-7.85</v>
+        <v>-12.75</v>
       </c>
       <c r="I377" t="n">
-        <v>992</v>
+        <v>988.3</v>
       </c>
       <c r="J377" t="n">
         <v>1003.04</v>
       </c>
       <c r="K377" t="n">
-        <v>-11.04</v>
+        <v>-14.74</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>1.58</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="378">
@@ -20072,31 +20072,31 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1798.3</v>
+        <v>1785</v>
       </c>
       <c r="D378" t="n">
         <v>1837.63</v>
       </c>
       <c r="E378" t="n">
-        <v>-39.33</v>
+        <v>-52.63</v>
       </c>
       <c r="F378" t="n">
-        <v>1815</v>
+        <v>1811.8</v>
       </c>
       <c r="G378" t="n">
         <v>1837.63</v>
       </c>
       <c r="H378" t="n">
-        <v>-22.63</v>
+        <v>-25.83</v>
       </c>
       <c r="I378" t="n">
-        <v>1775</v>
+        <v>1773.5</v>
       </c>
       <c r="J378" t="n">
         <v>1760.02</v>
       </c>
       <c r="K378" t="n">
-        <v>14.98</v>
+        <v>13.48</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="379">
@@ -20124,31 +20124,31 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3280</v>
+        <v>3268</v>
       </c>
       <c r="D379" t="n">
         <v>3158.38</v>
       </c>
       <c r="E379" t="n">
-        <v>121.62</v>
+        <v>109.62</v>
       </c>
       <c r="F379" t="n">
-        <v>3308.7</v>
+        <v>3289.7</v>
       </c>
       <c r="G379" t="n">
         <v>3343.9</v>
       </c>
       <c r="H379" t="n">
-        <v>-35.2</v>
+        <v>-54.2</v>
       </c>
       <c r="I379" t="n">
-        <v>3254.3</v>
+        <v>3180.1</v>
       </c>
       <c r="J379" t="n">
         <v>3271.27</v>
       </c>
       <c r="K379" t="n">
-        <v>-16.97</v>
+        <v>-91.17</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -20157,11 +20157,11 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N379" t="n">
-        <v>3.85</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="380">
@@ -20176,31 +20176,31 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>4119</v>
+        <v>4090</v>
       </c>
       <c r="D380" t="n">
         <v>4174.25</v>
       </c>
       <c r="E380" t="n">
-        <v>-55.25</v>
+        <v>-84.25</v>
       </c>
       <c r="F380" t="n">
-        <v>4125.3</v>
+        <v>4107.1</v>
       </c>
       <c r="G380" t="n">
         <v>4179.37</v>
       </c>
       <c r="H380" t="n">
-        <v>-54.07</v>
+        <v>-72.27</v>
       </c>
       <c r="I380" t="n">
-        <v>4066.6</v>
+        <v>4077.7</v>
       </c>
       <c r="J380" t="n">
         <v>4106.99</v>
       </c>
       <c r="K380" t="n">
-        <v>-40.39</v>
+        <v>-29.29</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="381">
@@ -20228,31 +20228,31 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>11290</v>
+        <v>11120</v>
       </c>
       <c r="D381" t="n">
         <v>11708.14</v>
       </c>
       <c r="E381" t="n">
-        <v>-418.14</v>
+        <v>-588.14</v>
       </c>
       <c r="F381" t="n">
-        <v>11290</v>
+        <v>11360</v>
       </c>
       <c r="G381" t="n">
         <v>11708.14</v>
       </c>
       <c r="H381" t="n">
-        <v>-418.14</v>
+        <v>-348.14</v>
       </c>
       <c r="I381" t="n">
-        <v>10811</v>
+        <v>11050</v>
       </c>
       <c r="J381" t="n">
         <v>11290</v>
       </c>
       <c r="K381" t="n">
-        <v>-479</v>
+        <v>-240</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>3.57</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="382">
@@ -20280,31 +20280,31 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>467.5</v>
+        <v>477</v>
       </c>
       <c r="D382" t="n">
         <v>471.88</v>
       </c>
       <c r="E382" t="n">
-        <v>-4.38</v>
+        <v>5.12</v>
       </c>
       <c r="F382" t="n">
-        <v>479</v>
+        <v>479.25</v>
       </c>
       <c r="G382" t="n">
         <v>471.88</v>
       </c>
       <c r="H382" t="n">
-        <v>7.12</v>
+        <v>7.37</v>
       </c>
       <c r="I382" t="n">
-        <v>466.05</v>
+        <v>472</v>
       </c>
       <c r="J382" t="n">
         <v>455.69</v>
       </c>
       <c r="K382" t="n">
-        <v>10.36</v>
+        <v>16.31</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="383">
@@ -20332,31 +20332,31 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2232.5</v>
+        <v>2207</v>
       </c>
       <c r="D383" t="n">
         <v>2288.38</v>
       </c>
       <c r="E383" t="n">
-        <v>-55.88</v>
+        <v>-81.38</v>
       </c>
       <c r="F383" t="n">
-        <v>2243.8</v>
+        <v>2235.4</v>
       </c>
       <c r="G383" t="n">
         <v>2292.81</v>
       </c>
       <c r="H383" t="n">
-        <v>-49.01</v>
+        <v>-57.41</v>
       </c>
       <c r="I383" t="n">
-        <v>2190</v>
+        <v>2206.1</v>
       </c>
       <c r="J383" t="n">
         <v>2232.5</v>
       </c>
       <c r="K383" t="n">
-        <v>-42.5</v>
+        <v>-26.4</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>2.44</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="384">
@@ -20384,31 +20384,31 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>186.98</v>
+        <v>183.6</v>
       </c>
       <c r="D384" t="n">
         <v>178.29</v>
       </c>
       <c r="E384" t="n">
-        <v>8.69</v>
+        <v>5.31</v>
       </c>
       <c r="F384" t="n">
-        <v>187.33</v>
+        <v>184.7</v>
       </c>
       <c r="G384" t="n">
         <v>188.14</v>
       </c>
       <c r="H384" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.44</v>
       </c>
       <c r="I384" t="n">
-        <v>181.4</v>
+        <v>182.02</v>
       </c>
       <c r="J384" t="n">
         <v>183.96</v>
       </c>
       <c r="K384" t="n">
-        <v>-2.56</v>
+        <v>-1.94</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>4.87</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="385">
@@ -20436,31 +20436,31 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>331</v>
+        <v>327.15</v>
       </c>
       <c r="D385" t="n">
         <v>358.33</v>
       </c>
       <c r="E385" t="n">
-        <v>-27.33</v>
+        <v>-31.18</v>
       </c>
       <c r="F385" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="G385" t="n">
         <v>358.33</v>
       </c>
       <c r="H385" t="n">
-        <v>-27.33</v>
+        <v>-28.83</v>
       </c>
       <c r="I385" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="J385" t="n">
         <v>331</v>
       </c>
       <c r="K385" t="n">
-        <v>-5.5</v>
+        <v>-8</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>7.63</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -20488,31 +20488,31 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>397.8</v>
+        <v>403.3</v>
       </c>
       <c r="D386" t="n">
         <v>348.04</v>
       </c>
       <c r="E386" t="n">
-        <v>49.76</v>
+        <v>55.26</v>
       </c>
       <c r="F386" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G386" t="n">
         <v>404.41</v>
       </c>
       <c r="H386" t="n">
-        <v>-2.41</v>
+        <v>0.59</v>
       </c>
       <c r="I386" t="n">
-        <v>392.05</v>
+        <v>397.5</v>
       </c>
       <c r="J386" t="n">
         <v>395.59</v>
       </c>
       <c r="K386" t="n">
-        <v>-3.54</v>
+        <v>1.91</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>14.3</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="387">
@@ -20540,31 +20540,31 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1892.8</v>
+        <v>1873</v>
       </c>
       <c r="D387" t="n">
         <v>1895.63</v>
       </c>
       <c r="E387" t="n">
-        <v>-2.83</v>
+        <v>-22.63</v>
       </c>
       <c r="F387" t="n">
-        <v>1899.9</v>
+        <v>1900.8</v>
       </c>
       <c r="G387" t="n">
         <v>1903.48</v>
       </c>
       <c r="H387" t="n">
-        <v>-3.58</v>
+        <v>-2.68</v>
       </c>
       <c r="I387" t="n">
-        <v>1870</v>
+        <v>1869.6</v>
       </c>
       <c r="J387" t="n">
         <v>1861.23</v>
       </c>
       <c r="K387" t="n">
-        <v>8.77</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>0.15</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="388">
@@ -20592,31 +20592,31 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>292.5</v>
+        <v>295.95</v>
       </c>
       <c r="D388" t="n">
         <v>294.24</v>
       </c>
       <c r="E388" t="n">
-        <v>-1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F388" t="n">
-        <v>295.7</v>
+        <v>296.8</v>
       </c>
       <c r="G388" t="n">
         <v>294.24</v>
       </c>
       <c r="H388" t="n">
-        <v>1.46</v>
+        <v>2.56</v>
       </c>
       <c r="I388" t="n">
-        <v>291.6</v>
+        <v>291.4</v>
       </c>
       <c r="J388" t="n">
         <v>287.9</v>
       </c>
       <c r="K388" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="389">
@@ -20644,31 +20644,31 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1253.4</v>
+        <v>1251.3</v>
       </c>
       <c r="D389" t="n">
         <v>1287.49</v>
       </c>
       <c r="E389" t="n">
-        <v>-34.09</v>
+        <v>-36.19</v>
       </c>
       <c r="F389" t="n">
-        <v>1256.5</v>
+        <v>1261.6</v>
       </c>
       <c r="G389" t="n">
         <v>1287.49</v>
       </c>
       <c r="H389" t="n">
-        <v>-30.99</v>
+        <v>-25.89</v>
       </c>
       <c r="I389" t="n">
-        <v>1240.5</v>
+        <v>1245.1</v>
       </c>
       <c r="J389" t="n">
         <v>1234.86</v>
       </c>
       <c r="K389" t="n">
-        <v>5.64</v>
+        <v>10.24</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="390">
@@ -20696,31 +20696,31 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>5624.5</v>
+        <v>5685</v>
       </c>
       <c r="D390" t="n">
         <v>5765.14</v>
       </c>
       <c r="E390" t="n">
-        <v>-140.64</v>
+        <v>-80.14</v>
       </c>
       <c r="F390" t="n">
-        <v>5682</v>
+        <v>5728</v>
       </c>
       <c r="G390" t="n">
         <v>5765.14</v>
       </c>
       <c r="H390" t="n">
-        <v>-83.14</v>
+        <v>-37.14</v>
       </c>
       <c r="I390" t="n">
-        <v>5590</v>
+        <v>5650</v>
       </c>
       <c r="J390" t="n">
         <v>5516.7</v>
       </c>
       <c r="K390" t="n">
-        <v>73.3</v>
+        <v>133.3</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>2.44</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="391">
@@ -20748,31 +20748,31 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>5655</v>
+        <v>5694</v>
       </c>
       <c r="D391" t="n">
         <v>5808.2</v>
       </c>
       <c r="E391" t="n">
-        <v>-153.2</v>
+        <v>-114.2</v>
       </c>
       <c r="F391" t="n">
-        <v>5687</v>
+        <v>5725</v>
       </c>
       <c r="G391" t="n">
         <v>5808.2</v>
       </c>
       <c r="H391" t="n">
-        <v>-121.2</v>
+        <v>-83.2</v>
       </c>
       <c r="I391" t="n">
-        <v>5570.5</v>
+        <v>5646</v>
       </c>
       <c r="J391" t="n">
         <v>5555.36</v>
       </c>
       <c r="K391" t="n">
-        <v>15.14</v>
+        <v>90.64</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="392">
@@ -20800,31 +20800,31 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>2610</v>
+        <v>2540</v>
       </c>
       <c r="D392" t="n">
         <v>2621.75</v>
       </c>
       <c r="E392" t="n">
-        <v>-11.75</v>
+        <v>-81.75</v>
       </c>
       <c r="F392" t="n">
-        <v>2621.7</v>
+        <v>2572.6</v>
       </c>
       <c r="G392" t="n">
         <v>2621.75</v>
       </c>
       <c r="H392" t="n">
-        <v>-0.05</v>
+        <v>-49.15</v>
       </c>
       <c r="I392" t="n">
-        <v>2520</v>
+        <v>2523.4</v>
       </c>
       <c r="J392" t="n">
         <v>2552.86</v>
       </c>
       <c r="K392" t="n">
-        <v>-32.86</v>
+        <v>-29.46</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>0.45</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="393">
@@ -20852,31 +20852,31 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1210</v>
+        <v>1189.8</v>
       </c>
       <c r="D393" t="n">
         <v>1211.06</v>
       </c>
       <c r="E393" t="n">
-        <v>-1.06</v>
+        <v>-21.26</v>
       </c>
       <c r="F393" t="n">
-        <v>1210</v>
+        <v>1215.2</v>
       </c>
       <c r="G393" t="n">
         <v>1223.84</v>
       </c>
       <c r="H393" t="n">
-        <v>-13.84</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I393" t="n">
-        <v>1186.4</v>
+        <v>1189.8</v>
       </c>
       <c r="J393" t="n">
         <v>1196.92</v>
       </c>
       <c r="K393" t="n">
-        <v>-10.52</v>
+        <v>-7.12</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>0.09</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="394">
@@ -20904,31 +20904,31 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1051.05</v>
+        <v>1058.5</v>
       </c>
       <c r="D394" t="n">
         <v>1043.22</v>
       </c>
       <c r="E394" t="n">
-        <v>7.83</v>
+        <v>15.28</v>
       </c>
       <c r="F394" t="n">
-        <v>1057</v>
+        <v>1058.5</v>
       </c>
       <c r="G394" t="n">
         <v>1069.88</v>
       </c>
       <c r="H394" t="n">
-        <v>-12.88</v>
+        <v>-11.38</v>
       </c>
       <c r="I394" t="n">
-        <v>1040.45</v>
+        <v>1043.3</v>
       </c>
       <c r="J394" t="n">
         <v>1046.59</v>
       </c>
       <c r="K394" t="n">
-        <v>-6.14</v>
+        <v>-3.29</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>0.75</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="395">
@@ -20956,31 +20956,31 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>682.95</v>
+        <v>689</v>
       </c>
       <c r="D395" t="n">
         <v>668.76</v>
       </c>
       <c r="E395" t="n">
-        <v>14.19</v>
+        <v>20.24</v>
       </c>
       <c r="F395" t="n">
-        <v>688.2</v>
+        <v>689</v>
       </c>
       <c r="G395" t="n">
         <v>694.11</v>
       </c>
       <c r="H395" t="n">
-        <v>-5.91</v>
+        <v>-5.11</v>
       </c>
       <c r="I395" t="n">
-        <v>678.3</v>
+        <v>678.1</v>
       </c>
       <c r="J395" t="n">
         <v>678.96</v>
       </c>
       <c r="K395" t="n">
-        <v>-0.66</v>
+        <v>-0.86</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="396">
@@ -21008,31 +21008,31 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>14990</v>
+        <v>14570</v>
       </c>
       <c r="D396" t="n">
         <v>15955.71</v>
       </c>
       <c r="E396" t="n">
-        <v>-965.71</v>
+        <v>-1385.71</v>
       </c>
       <c r="F396" t="n">
-        <v>14990</v>
+        <v>15000</v>
       </c>
       <c r="G396" t="n">
         <v>15955.71</v>
       </c>
       <c r="H396" t="n">
-        <v>-965.71</v>
+        <v>-955.71</v>
       </c>
       <c r="I396" t="n">
-        <v>14400</v>
+        <v>14484</v>
       </c>
       <c r="J396" t="n">
         <v>14990</v>
       </c>
       <c r="K396" t="n">
-        <v>-590</v>
+        <v>-506</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>6.05</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="397">
@@ -21060,31 +21060,31 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D397" t="n">
         <v>1372.8</v>
       </c>
       <c r="E397" t="n">
-        <v>-22.8</v>
+        <v>-23.8</v>
       </c>
       <c r="F397" t="n">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="G397" t="n">
         <v>1372.8</v>
       </c>
       <c r="H397" t="n">
-        <v>-22.8</v>
+        <v>-12.8</v>
       </c>
       <c r="I397" t="n">
-        <v>1328.1</v>
+        <v>1336.7</v>
       </c>
       <c r="J397" t="n">
         <v>1315.92</v>
       </c>
       <c r="K397" t="n">
-        <v>12.18</v>
+        <v>20.78</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="398">
@@ -21112,31 +21112,31 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>878</v>
+        <v>870.45</v>
       </c>
       <c r="D398" t="n">
         <v>898.71</v>
       </c>
       <c r="E398" t="n">
-        <v>-20.71</v>
+        <v>-28.26</v>
       </c>
       <c r="F398" t="n">
-        <v>881.75</v>
+        <v>883.85</v>
       </c>
       <c r="G398" t="n">
         <v>898.71</v>
       </c>
       <c r="H398" t="n">
-        <v>-16.96</v>
+        <v>-14.86</v>
       </c>
       <c r="I398" t="n">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="J398" t="n">
         <v>863.09</v>
       </c>
       <c r="K398" t="n">
-        <v>5.91</v>
+        <v>-1.09</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="399">
@@ -21164,31 +21164,31 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>516</v>
+        <v>516.4</v>
       </c>
       <c r="D399" t="n">
         <v>559.89</v>
       </c>
       <c r="E399" t="n">
-        <v>-43.89</v>
+        <v>-43.49</v>
       </c>
       <c r="F399" t="n">
-        <v>518.4</v>
+        <v>524.2</v>
       </c>
       <c r="G399" t="n">
         <v>559.89</v>
       </c>
       <c r="H399" t="n">
-        <v>-41.49</v>
+        <v>-35.69</v>
       </c>
       <c r="I399" t="n">
-        <v>511.3</v>
+        <v>513.05</v>
       </c>
       <c r="J399" t="n">
         <v>506.16</v>
       </c>
       <c r="K399" t="n">
-        <v>5.14</v>
+        <v>6.89</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
     </row>
   </sheetData>
@@ -22220,31 +22220,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1210</v>
+        <v>1189.8</v>
       </c>
       <c r="D15" t="n">
         <v>1211.06</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.06</v>
+        <v>-21.26</v>
       </c>
       <c r="F15" t="n">
-        <v>1210</v>
+        <v>1215.2</v>
       </c>
       <c r="G15" t="n">
         <v>1223.84</v>
       </c>
       <c r="H15" t="n">
-        <v>-13.84</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1186.4</v>
+        <v>1189.8</v>
       </c>
       <c r="J15" t="n">
         <v>1196.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.52</v>
+        <v>-7.12</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.09</v>
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>
@@ -25094,31 +25094,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>331</v>
+        <v>327.15</v>
       </c>
       <c r="D16" t="n">
         <v>358.33</v>
       </c>
       <c r="E16" t="n">
-        <v>-27.33</v>
+        <v>-31.18</v>
       </c>
       <c r="F16" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="G16" t="n">
         <v>358.33</v>
       </c>
       <c r="H16" t="n">
-        <v>-27.33</v>
+        <v>-28.83</v>
       </c>
       <c r="I16" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="J16" t="n">
         <v>331</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.5</v>
+        <v>-8</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>7.63</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -25960,31 +25960,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14990</v>
+        <v>14570</v>
       </c>
       <c r="D16" t="n">
         <v>15955.71</v>
       </c>
       <c r="E16" t="n">
-        <v>-965.71</v>
+        <v>-1385.71</v>
       </c>
       <c r="F16" t="n">
-        <v>14990</v>
+        <v>15000</v>
       </c>
       <c r="G16" t="n">
         <v>15955.71</v>
       </c>
       <c r="H16" t="n">
-        <v>-965.71</v>
+        <v>-955.71</v>
       </c>
       <c r="I16" t="n">
-        <v>14400</v>
+        <v>14484</v>
       </c>
       <c r="J16" t="n">
         <v>14990</v>
       </c>
       <c r="K16" t="n">
-        <v>-590</v>
+        <v>-506</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.05</v>
+        <v>8.68</v>
       </c>
     </row>
   </sheetData>
@@ -26826,31 +26826,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1892.8</v>
+        <v>1873</v>
       </c>
       <c r="D16" t="n">
         <v>1895.63</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.83</v>
+        <v>-22.63</v>
       </c>
       <c r="F16" t="n">
-        <v>1899.9</v>
+        <v>1900.8</v>
       </c>
       <c r="G16" t="n">
         <v>1903.48</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.58</v>
+        <v>-2.68</v>
       </c>
       <c r="I16" t="n">
-        <v>1870</v>
+        <v>1869.6</v>
       </c>
       <c r="J16" t="n">
         <v>1861.23</v>
       </c>
       <c r="K16" t="n">
-        <v>8.77</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.15</v>
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>
@@ -27588,31 +27588,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5655</v>
+        <v>5694</v>
       </c>
       <c r="D14" t="n">
         <v>5808.2</v>
       </c>
       <c r="E14" t="n">
-        <v>-153.2</v>
+        <v>-114.2</v>
       </c>
       <c r="F14" t="n">
-        <v>5687</v>
+        <v>5725</v>
       </c>
       <c r="G14" t="n">
         <v>5808.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-121.2</v>
+        <v>-83.2</v>
       </c>
       <c r="I14" t="n">
-        <v>5570.5</v>
+        <v>5646</v>
       </c>
       <c r="J14" t="n">
         <v>5555.36</v>
       </c>
       <c r="K14" t="n">
-        <v>15.14</v>
+        <v>90.64</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
     </row>
   </sheetData>
@@ -28454,31 +28454,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>115.93</v>
+        <v>115.86</v>
       </c>
       <c r="D16" t="n">
         <v>113.57</v>
       </c>
       <c r="E16" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="F16" t="n">
-        <v>116.9</v>
+        <v>117.03</v>
       </c>
       <c r="G16" t="n">
         <v>117.64</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.74</v>
+        <v>-0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>115.01</v>
+        <v>115</v>
       </c>
       <c r="J16" t="n">
         <v>115.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
     </row>
   </sheetData>
@@ -29268,31 +29268,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3443</v>
+        <v>3414.1</v>
       </c>
       <c r="D15" t="n">
         <v>3676.17</v>
       </c>
       <c r="E15" t="n">
-        <v>-233.17</v>
+        <v>-262.07</v>
       </c>
       <c r="F15" t="n">
-        <v>3443</v>
+        <v>3444.7</v>
       </c>
       <c r="G15" t="n">
         <v>3676.17</v>
       </c>
       <c r="H15" t="n">
-        <v>-233.17</v>
+        <v>-231.47</v>
       </c>
       <c r="I15" t="n">
-        <v>3396.8</v>
+        <v>3400</v>
       </c>
       <c r="J15" t="n">
         <v>3423.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.84</v>
+        <v>-23.64</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.34</v>
+        <v>7.13</v>
       </c>
     </row>
   </sheetData>
@@ -30082,31 +30082,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>516</v>
+        <v>516.4</v>
       </c>
       <c r="D15" t="n">
         <v>559.89</v>
       </c>
       <c r="E15" t="n">
-        <v>-43.89</v>
+        <v>-43.49</v>
       </c>
       <c r="F15" t="n">
-        <v>518.4</v>
+        <v>524.2</v>
       </c>
       <c r="G15" t="n">
         <v>559.89</v>
       </c>
       <c r="H15" t="n">
-        <v>-41.49</v>
+        <v>-35.69</v>
       </c>
       <c r="I15" t="n">
-        <v>511.3</v>
+        <v>513.05</v>
       </c>
       <c r="J15" t="n">
         <v>506.16</v>
       </c>
       <c r="K15" t="n">
-        <v>5.14</v>
+        <v>6.89</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21202,6 +21202,1618 @@
       </c>
       <c r="N399" t="n">
         <v>7.77</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D400" t="n">
+        <v>2015.46</v>
+      </c>
+      <c r="E400" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="F400" t="n">
+        <v>2024.9</v>
+      </c>
+      <c r="G400" t="n">
+        <v>2015.46</v>
+      </c>
+      <c r="H400" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I400" t="n">
+        <v>2005.5</v>
+      </c>
+      <c r="J400" t="n">
+        <v>1964.76</v>
+      </c>
+      <c r="K400" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1050.91</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F401" t="n">
+        <v>1062.3</v>
+      </c>
+      <c r="G401" t="n">
+        <v>1058.98</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1035.78</v>
+      </c>
+      <c r="K401" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1234.38</v>
+      </c>
+      <c r="E402" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F402" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="G402" t="n">
+        <v>1261.24</v>
+      </c>
+      <c r="H402" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1250.7</v>
+      </c>
+      <c r="J402" t="n">
+        <v>1233.35</v>
+      </c>
+      <c r="K402" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D403" t="n">
+        <v>2106.22</v>
+      </c>
+      <c r="E403" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="F403" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G403" t="n">
+        <v>2177.62</v>
+      </c>
+      <c r="H403" t="n">
+        <v>-18.62</v>
+      </c>
+      <c r="I403" t="n">
+        <v>2119.7</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2130.04</v>
+      </c>
+      <c r="K403" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D404" t="n">
+        <v>120</v>
+      </c>
+      <c r="E404" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F404" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G404" t="n">
+        <v>120</v>
+      </c>
+      <c r="H404" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I404" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J404" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D405" t="n">
+        <v>3494.24</v>
+      </c>
+      <c r="E405" t="n">
+        <v>-144.24</v>
+      </c>
+      <c r="F405" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G405" t="n">
+        <v>3494.24</v>
+      </c>
+      <c r="H405" t="n">
+        <v>-139.24</v>
+      </c>
+      <c r="I405" t="n">
+        <v>3243.3</v>
+      </c>
+      <c r="J405" t="n">
+        <v>3320.18</v>
+      </c>
+      <c r="K405" t="n">
+        <v>-76.88</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1801.6</v>
+      </c>
+      <c r="E406" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F406" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G406" t="n">
+        <v>1855.29</v>
+      </c>
+      <c r="H406" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1806.3</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1814.74</v>
+      </c>
+      <c r="K406" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="D407" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="E407" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F407" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G407" t="n">
+        <v>180.12</v>
+      </c>
+      <c r="H407" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I407" t="n">
+        <v>175.41</v>
+      </c>
+      <c r="J407" t="n">
+        <v>176.17</v>
+      </c>
+      <c r="K407" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>187.52</v>
+      </c>
+      <c r="D408" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="F408" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="G408" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="H408" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I408" t="n">
+        <v>187.12</v>
+      </c>
+      <c r="J408" t="n">
+        <v>182.61</v>
+      </c>
+      <c r="K408" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>469.15</v>
+      </c>
+      <c r="D409" t="n">
+        <v>478.03</v>
+      </c>
+      <c r="E409" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="F409" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="G409" t="n">
+        <v>478.03</v>
+      </c>
+      <c r="H409" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="I409" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J409" t="n">
+        <v>452.42</v>
+      </c>
+      <c r="K409" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D410" t="n">
+        <v>11093.82</v>
+      </c>
+      <c r="E410" t="n">
+        <v>446.18</v>
+      </c>
+      <c r="F410" t="n">
+        <v>11540</v>
+      </c>
+      <c r="G410" t="n">
+        <v>11689.23</v>
+      </c>
+      <c r="H410" t="n">
+        <v>-149.23</v>
+      </c>
+      <c r="I410" t="n">
+        <v>11223</v>
+      </c>
+      <c r="J410" t="n">
+        <v>11484.65</v>
+      </c>
+      <c r="K410" t="n">
+        <v>-261.65</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1076.97</v>
+      </c>
+      <c r="E411" t="n">
+        <v>-23.97</v>
+      </c>
+      <c r="F411" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="G411" t="n">
+        <v>1076.97</v>
+      </c>
+      <c r="H411" t="n">
+        <v>-17.47</v>
+      </c>
+      <c r="I411" t="n">
+        <v>1039.15</v>
+      </c>
+      <c r="J411" t="n">
+        <v>1039.21</v>
+      </c>
+      <c r="K411" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1526.1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>1504.36</v>
+      </c>
+      <c r="E412" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1544.6</v>
+      </c>
+      <c r="G412" t="n">
+        <v>1528.5</v>
+      </c>
+      <c r="H412" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I412" t="n">
+        <v>1525.9</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1494.74</v>
+      </c>
+      <c r="K412" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="D413" t="n">
+        <v>3181.19</v>
+      </c>
+      <c r="E413" t="n">
+        <v>217.01</v>
+      </c>
+      <c r="F413" t="n">
+        <v>3447.9</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3414.55</v>
+      </c>
+      <c r="H413" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="I413" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>3339.5</v>
+      </c>
+      <c r="K413" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D414" t="n">
+        <v>2188.49</v>
+      </c>
+      <c r="E414" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>2279</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2280.44</v>
+      </c>
+      <c r="H414" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2232.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>2231</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D415" t="n">
+        <v>466.39</v>
+      </c>
+      <c r="E415" t="n">
+        <v>-67.09</v>
+      </c>
+      <c r="F415" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="G415" t="n">
+        <v>466.39</v>
+      </c>
+      <c r="H415" t="n">
+        <v>-65.94</v>
+      </c>
+      <c r="I415" t="n">
+        <v>393</v>
+      </c>
+      <c r="J415" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="K415" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>14.38</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1012.2</v>
+      </c>
+      <c r="E416" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1048.8</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1055.98</v>
+      </c>
+      <c r="H416" t="n">
+        <v>-7.18</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1010.65</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1033.15</v>
+      </c>
+      <c r="K416" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>289</v>
+      </c>
+      <c r="D417" t="n">
+        <v>293</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F417" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="G417" t="n">
+        <v>293</v>
+      </c>
+      <c r="H417" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I417" t="n">
+        <v>289</v>
+      </c>
+      <c r="J417" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="K417" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D418" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="E418" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="F418" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G418" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="H418" t="n">
+        <v>180.57</v>
+      </c>
+      <c r="I418" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J418" t="n">
+        <v>5424.98</v>
+      </c>
+      <c r="K418" t="n">
+        <v>165.52</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>5250.5</v>
+      </c>
+      <c r="D419" t="n">
+        <v>5175.69</v>
+      </c>
+      <c r="E419" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="F419" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G419" t="n">
+        <v>5279.51</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I419" t="n">
+        <v>5221.5</v>
+      </c>
+      <c r="J419" t="n">
+        <v>5163.61</v>
+      </c>
+      <c r="K419" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>5595</v>
+      </c>
+      <c r="D420" t="n">
+        <v>5561.37</v>
+      </c>
+      <c r="E420" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="F420" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G420" t="n">
+        <v>5561.37</v>
+      </c>
+      <c r="H420" t="n">
+        <v>158.63</v>
+      </c>
+      <c r="I420" t="n">
+        <v>5595</v>
+      </c>
+      <c r="J420" t="n">
+        <v>5438.41</v>
+      </c>
+      <c r="K420" t="n">
+        <v>156.59</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="D421" t="n">
+        <v>698.39</v>
+      </c>
+      <c r="E421" t="n">
+        <v>-25.89</v>
+      </c>
+      <c r="F421" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="G421" t="n">
+        <v>698.39</v>
+      </c>
+      <c r="H421" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="I421" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="J421" t="n">
+        <v>664.92</v>
+      </c>
+      <c r="K421" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>3988.26</v>
+      </c>
+      <c r="E422" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="F422" t="n">
+        <v>4124.9</v>
+      </c>
+      <c r="G422" t="n">
+        <v>4047.72</v>
+      </c>
+      <c r="H422" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="I422" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="J422" t="n">
+        <v>3989.84</v>
+      </c>
+      <c r="K422" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>889</v>
+      </c>
+      <c r="D423" t="n">
+        <v>867.9299999999999</v>
+      </c>
+      <c r="E423" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="F423" t="n">
+        <v>905</v>
+      </c>
+      <c r="G423" t="n">
+        <v>898.46</v>
+      </c>
+      <c r="H423" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I423" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="J423" t="n">
+        <v>878.9</v>
+      </c>
+      <c r="K423" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>1323.5</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1310.96</v>
+      </c>
+      <c r="E424" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F424" t="n">
+        <v>1350.9</v>
+      </c>
+      <c r="G424" t="n">
+        <v>1313.69</v>
+      </c>
+      <c r="H424" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="I424" t="n">
+        <v>1322</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1284.25</v>
+      </c>
+      <c r="K424" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>517</v>
+      </c>
+      <c r="D425" t="n">
+        <v>480.66</v>
+      </c>
+      <c r="E425" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="F425" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="G425" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="I425" t="n">
+        <v>514.75</v>
+      </c>
+      <c r="J425" t="n">
+        <v>501.99</v>
+      </c>
+      <c r="K425" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>327</v>
+      </c>
+      <c r="D426" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="E426" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="F426" t="n">
+        <v>332</v>
+      </c>
+      <c r="G426" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I426" t="n">
+        <v>325</v>
+      </c>
+      <c r="J426" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="K426" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1185.6</v>
+      </c>
+      <c r="E427" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1189.57</v>
+      </c>
+      <c r="H427" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="I427" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1162.96</v>
+      </c>
+      <c r="K427" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D428" t="n">
+        <v>2563.5</v>
+      </c>
+      <c r="E428" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F428" t="n">
+        <v>2656.8</v>
+      </c>
+      <c r="G428" t="n">
+        <v>2584.48</v>
+      </c>
+      <c r="H428" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="I428" t="n">
+        <v>2579.4</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2533.54</v>
+      </c>
+      <c r="K428" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1878.53</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F429" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G429" t="n">
+        <v>1910.56</v>
+      </c>
+      <c r="H429" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I429" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1869.32</v>
+      </c>
+      <c r="K429" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D430" t="n">
+        <v>13562.91</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1172.09</v>
+      </c>
+      <c r="F430" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G430" t="n">
+        <v>14809.22</v>
+      </c>
+      <c r="H430" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="I430" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J430" t="n">
+        <v>14483.88</v>
+      </c>
+      <c r="K430" t="n">
+        <v>236.12</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>8.640000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21457,7 +23069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22258,6 +23870,58 @@
       </c>
       <c r="N15" t="n">
         <v>1.76</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1185.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1189.57</v>
+      </c>
+      <c r="H16" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1162.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -24279,7 +25943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25132,6 +26796,58 @@
       </c>
       <c r="N16" t="n">
         <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>327</v>
+      </c>
+      <c r="D17" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="E17" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="F17" t="n">
+        <v>332</v>
+      </c>
+      <c r="G17" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>325</v>
+      </c>
+      <c r="J17" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>8.66</v>
       </c>
     </row>
   </sheetData>
@@ -25145,7 +26861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25998,6 +27714,58 @@
       </c>
       <c r="N16" t="n">
         <v>8.68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13562.91</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1172.09</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14809.22</v>
+      </c>
+      <c r="H17" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14483.88</v>
+      </c>
+      <c r="K17" t="n">
+        <v>236.12</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>8.640000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26011,7 +27779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26864,6 +28632,58 @@
       </c>
       <c r="N16" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1878.53</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1910.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1869.32</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -26877,7 +28697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27626,6 +29446,58 @@
       </c>
       <c r="N14" t="n">
         <v>1.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="E15" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="H15" t="n">
+        <v>180.57</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5424.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>165.52</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -27639,7 +29511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28492,6 +30364,58 @@
       </c>
       <c r="N16" t="n">
         <v>2.02</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>120</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J17" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -28505,7 +30429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29306,6 +31230,58 @@
       </c>
       <c r="N15" t="n">
         <v>7.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3181.19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>217.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3447.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3414.55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3339.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>6.82</v>
       </c>
     </row>
   </sheetData>
@@ -29319,7 +31295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30120,6 +32096,58 @@
       </c>
       <c r="N15" t="n">
         <v>7.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>517</v>
+      </c>
+      <c r="D16" t="n">
+        <v>480.66</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>514.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>501.99</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>7.56</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -21216,31 +21216,31 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="D400" t="n">
         <v>2015.46</v>
       </c>
       <c r="E400" t="n">
-        <v>-5.46</v>
+        <v>-11.46</v>
       </c>
       <c r="F400" t="n">
-        <v>2024.9</v>
+        <v>2011.7</v>
       </c>
       <c r="G400" t="n">
         <v>2015.46</v>
       </c>
       <c r="H400" t="n">
-        <v>9.44</v>
+        <v>-3.76</v>
       </c>
       <c r="I400" t="n">
-        <v>2005.5</v>
+        <v>1985</v>
       </c>
       <c r="J400" t="n">
         <v>1964.76</v>
       </c>
       <c r="K400" t="n">
-        <v>40.74</v>
+        <v>20.24</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>0.27</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="401">
@@ -21268,31 +21268,31 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="D401" t="n">
         <v>1050.91</v>
       </c>
       <c r="E401" t="n">
-        <v>1.09</v>
+        <v>-2.91</v>
       </c>
       <c r="F401" t="n">
-        <v>1062.3</v>
+        <v>1048</v>
       </c>
       <c r="G401" t="n">
         <v>1058.98</v>
       </c>
       <c r="H401" t="n">
-        <v>3.32</v>
+        <v>-10.98</v>
       </c>
       <c r="I401" t="n">
-        <v>1051.2</v>
+        <v>1031.3</v>
       </c>
       <c r="J401" t="n">
         <v>1035.78</v>
       </c>
       <c r="K401" t="n">
-        <v>15.42</v>
+        <v>-4.48</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="402">
@@ -21320,31 +21320,31 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1260</v>
+        <v>1253.4</v>
       </c>
       <c r="D402" t="n">
         <v>1234.38</v>
       </c>
       <c r="E402" t="n">
-        <v>25.62</v>
+        <v>19.02</v>
       </c>
       <c r="F402" t="n">
-        <v>1272.1</v>
+        <v>1256.5</v>
       </c>
       <c r="G402" t="n">
         <v>1261.24</v>
       </c>
       <c r="H402" t="n">
-        <v>10.86</v>
+        <v>-4.74</v>
       </c>
       <c r="I402" t="n">
-        <v>1250.7</v>
+        <v>1240.5</v>
       </c>
       <c r="J402" t="n">
         <v>1233.35</v>
       </c>
       <c r="K402" t="n">
-        <v>17.35</v>
+        <v>7.15</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="403">
@@ -21372,31 +21372,31 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2159</v>
+        <v>2139.3</v>
       </c>
       <c r="D403" t="n">
         <v>2106.22</v>
       </c>
       <c r="E403" t="n">
-        <v>52.78</v>
+        <v>33.08</v>
       </c>
       <c r="F403" t="n">
-        <v>2159</v>
+        <v>2151.8</v>
       </c>
       <c r="G403" t="n">
         <v>2177.62</v>
       </c>
       <c r="H403" t="n">
-        <v>-18.62</v>
+        <v>-25.82</v>
       </c>
       <c r="I403" t="n">
-        <v>2119.7</v>
+        <v>2124</v>
       </c>
       <c r="J403" t="n">
         <v>2130.04</v>
       </c>
       <c r="K403" t="n">
-        <v>-10.34</v>
+        <v>-6.04</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>2.51</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="404">
@@ -21424,31 +21424,31 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>116.7</v>
+        <v>115.93</v>
       </c>
       <c r="D404" t="n">
         <v>120</v>
       </c>
       <c r="E404" t="n">
-        <v>-3.3</v>
+        <v>-4.07</v>
       </c>
       <c r="F404" t="n">
-        <v>118.2</v>
+        <v>116.9</v>
       </c>
       <c r="G404" t="n">
         <v>120</v>
       </c>
       <c r="H404" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="I404" t="n">
-        <v>116.39</v>
+        <v>115.01</v>
       </c>
       <c r="J404" t="n">
         <v>115.09</v>
       </c>
       <c r="K404" t="n">
-        <v>1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>2.75</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="405">
@@ -21476,31 +21476,31 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3350</v>
+        <v>3280</v>
       </c>
       <c r="D405" t="n">
         <v>3494.24</v>
       </c>
       <c r="E405" t="n">
-        <v>-144.24</v>
+        <v>-214.24</v>
       </c>
       <c r="F405" t="n">
-        <v>3355</v>
+        <v>3308.7</v>
       </c>
       <c r="G405" t="n">
         <v>3494.24</v>
       </c>
       <c r="H405" t="n">
-        <v>-139.24</v>
+        <v>-185.54</v>
       </c>
       <c r="I405" t="n">
-        <v>3243.3</v>
+        <v>3254.3</v>
       </c>
       <c r="J405" t="n">
         <v>3320.18</v>
       </c>
       <c r="K405" t="n">
-        <v>-76.88</v>
+        <v>-65.88</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>4.13</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="406">
@@ -21528,31 +21528,31 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1840</v>
+        <v>1798.3</v>
       </c>
       <c r="D406" t="n">
         <v>1801.6</v>
       </c>
       <c r="E406" t="n">
-        <v>38.4</v>
+        <v>-3.3</v>
       </c>
       <c r="F406" t="n">
-        <v>1875</v>
+        <v>1815</v>
       </c>
       <c r="G406" t="n">
         <v>1855.29</v>
       </c>
       <c r="H406" t="n">
-        <v>19.71</v>
+        <v>-40.29</v>
       </c>
       <c r="I406" t="n">
-        <v>1806.3</v>
+        <v>1775</v>
       </c>
       <c r="J406" t="n">
         <v>1814.74</v>
       </c>
       <c r="K406" t="n">
-        <v>-8.44</v>
+        <v>-39.74</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>2.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="407">
@@ -21580,31 +21580,31 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>179.05</v>
+        <v>174.69</v>
       </c>
       <c r="D407" t="n">
         <v>176.8</v>
       </c>
       <c r="E407" t="n">
-        <v>2.25</v>
+        <v>-2.11</v>
       </c>
       <c r="F407" t="n">
-        <v>179.5</v>
+        <v>174.69</v>
       </c>
       <c r="G407" t="n">
         <v>180.12</v>
       </c>
       <c r="H407" t="n">
-        <v>-0.62</v>
+        <v>-5.43</v>
       </c>
       <c r="I407" t="n">
-        <v>175.41</v>
+        <v>171.58</v>
       </c>
       <c r="J407" t="n">
         <v>176.17</v>
       </c>
       <c r="K407" t="n">
-        <v>-0.76</v>
+        <v>-4.59</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="408">
@@ -21632,31 +21632,31 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>187.52</v>
+        <v>186.98</v>
       </c>
       <c r="D408" t="n">
         <v>194.65</v>
       </c>
       <c r="E408" t="n">
-        <v>-7.13</v>
+        <v>-7.67</v>
       </c>
       <c r="F408" t="n">
-        <v>192.33</v>
+        <v>187.33</v>
       </c>
       <c r="G408" t="n">
         <v>194.65</v>
       </c>
       <c r="H408" t="n">
-        <v>-2.32</v>
+        <v>-7.32</v>
       </c>
       <c r="I408" t="n">
-        <v>187.12</v>
+        <v>181.4</v>
       </c>
       <c r="J408" t="n">
         <v>182.61</v>
       </c>
       <c r="K408" t="n">
-        <v>4.51</v>
+        <v>-1.21</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="409">
@@ -21684,31 +21684,31 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>469.15</v>
+        <v>467.5</v>
       </c>
       <c r="D409" t="n">
         <v>478.03</v>
       </c>
       <c r="E409" t="n">
-        <v>-8.880000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="F409" t="n">
-        <v>471.6</v>
+        <v>479</v>
       </c>
       <c r="G409" t="n">
         <v>478.03</v>
       </c>
       <c r="H409" t="n">
-        <v>-6.43</v>
+        <v>0.97</v>
       </c>
       <c r="I409" t="n">
-        <v>458.7</v>
+        <v>466.05</v>
       </c>
       <c r="J409" t="n">
         <v>452.42</v>
       </c>
       <c r="K409" t="n">
-        <v>6.28</v>
+        <v>13.63</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="410">
@@ -21736,31 +21736,31 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="D410" t="n">
         <v>11093.82</v>
       </c>
       <c r="E410" t="n">
-        <v>446.18</v>
+        <v>196.18</v>
       </c>
       <c r="F410" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="G410" t="n">
         <v>11689.23</v>
       </c>
       <c r="H410" t="n">
-        <v>-149.23</v>
+        <v>-399.23</v>
       </c>
       <c r="I410" t="n">
-        <v>11223</v>
+        <v>10811</v>
       </c>
       <c r="J410" t="n">
         <v>11484.65</v>
       </c>
       <c r="K410" t="n">
-        <v>-261.65</v>
+        <v>-673.65</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -21769,11 +21769,11 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N410" t="n">
-        <v>4.02</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="411">
@@ -21788,31 +21788,31 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1053</v>
+        <v>1051.05</v>
       </c>
       <c r="D411" t="n">
         <v>1076.97</v>
       </c>
       <c r="E411" t="n">
-        <v>-23.97</v>
+        <v>-25.92</v>
       </c>
       <c r="F411" t="n">
-        <v>1059.5</v>
+        <v>1057</v>
       </c>
       <c r="G411" t="n">
         <v>1076.97</v>
       </c>
       <c r="H411" t="n">
-        <v>-17.47</v>
+        <v>-19.97</v>
       </c>
       <c r="I411" t="n">
-        <v>1039.15</v>
+        <v>1040.45</v>
       </c>
       <c r="J411" t="n">
         <v>1039.21</v>
       </c>
       <c r="K411" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="412">
@@ -21840,31 +21840,31 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1526.1</v>
+        <v>1540</v>
       </c>
       <c r="D412" t="n">
         <v>1504.36</v>
       </c>
       <c r="E412" t="n">
-        <v>21.74</v>
+        <v>35.64</v>
       </c>
       <c r="F412" t="n">
-        <v>1544.6</v>
+        <v>1544.7</v>
       </c>
       <c r="G412" t="n">
         <v>1528.5</v>
       </c>
       <c r="H412" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="I412" t="n">
-        <v>1525.9</v>
+        <v>1519</v>
       </c>
       <c r="J412" t="n">
         <v>1494.74</v>
       </c>
       <c r="K412" t="n">
-        <v>31.16</v>
+        <v>24.26</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="413">
@@ -21892,31 +21892,31 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3398.2</v>
+        <v>3443</v>
       </c>
       <c r="D413" t="n">
         <v>3181.19</v>
       </c>
       <c r="E413" t="n">
-        <v>217.01</v>
+        <v>261.81</v>
       </c>
       <c r="F413" t="n">
-        <v>3447.9</v>
+        <v>3443</v>
       </c>
       <c r="G413" t="n">
         <v>3414.55</v>
       </c>
       <c r="H413" t="n">
-        <v>33.35</v>
+        <v>28.45</v>
       </c>
       <c r="I413" t="n">
-        <v>3398.2</v>
+        <v>3396.8</v>
       </c>
       <c r="J413" t="n">
         <v>3339.5</v>
       </c>
       <c r="K413" t="n">
-        <v>58.7</v>
+        <v>57.3</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>6.82</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="414">
@@ -21944,31 +21944,31 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2250</v>
+        <v>2232.5</v>
       </c>
       <c r="D414" t="n">
         <v>2188.49</v>
       </c>
       <c r="E414" t="n">
-        <v>61.51</v>
+        <v>44.01</v>
       </c>
       <c r="F414" t="n">
-        <v>2279</v>
+        <v>2243.8</v>
       </c>
       <c r="G414" t="n">
         <v>2280.44</v>
       </c>
       <c r="H414" t="n">
-        <v>-1.44</v>
+        <v>-36.64</v>
       </c>
       <c r="I414" t="n">
-        <v>2232.3</v>
+        <v>2190</v>
       </c>
       <c r="J414" t="n">
         <v>2231</v>
       </c>
       <c r="K414" t="n">
-        <v>1.3</v>
+        <v>-41</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="415">
@@ -21996,31 +21996,31 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>399.3</v>
+        <v>397.8</v>
       </c>
       <c r="D415" t="n">
         <v>466.39</v>
       </c>
       <c r="E415" t="n">
-        <v>-67.09</v>
+        <v>-68.59</v>
       </c>
       <c r="F415" t="n">
-        <v>400.45</v>
+        <v>402</v>
       </c>
       <c r="G415" t="n">
         <v>466.39</v>
       </c>
       <c r="H415" t="n">
-        <v>-65.94</v>
+        <v>-64.39</v>
       </c>
       <c r="I415" t="n">
-        <v>393</v>
+        <v>392.05</v>
       </c>
       <c r="J415" t="n">
         <v>388.7</v>
       </c>
       <c r="K415" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>14.38</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="416">
@@ -22048,31 +22048,31 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>1040</v>
+        <v>1011.5</v>
       </c>
       <c r="D416" t="n">
         <v>1012.2</v>
       </c>
       <c r="E416" t="n">
-        <v>27.8</v>
+        <v>-0.7</v>
       </c>
       <c r="F416" t="n">
-        <v>1048.8</v>
+        <v>1019.9</v>
       </c>
       <c r="G416" t="n">
         <v>1055.98</v>
       </c>
       <c r="H416" t="n">
-        <v>-7.18</v>
+        <v>-36.08</v>
       </c>
       <c r="I416" t="n">
-        <v>1010.65</v>
+        <v>992</v>
       </c>
       <c r="J416" t="n">
         <v>1033.15</v>
       </c>
       <c r="K416" t="n">
-        <v>-22.5</v>
+        <v>-41.15</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -22081,11 +22081,11 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N416" t="n">
-        <v>2.75</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="417">
@@ -22100,31 +22100,31 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>289</v>
+        <v>292.5</v>
       </c>
       <c r="D417" t="n">
         <v>293</v>
       </c>
       <c r="E417" t="n">
-        <v>-4</v>
+        <v>-0.5</v>
       </c>
       <c r="F417" t="n">
-        <v>295.95</v>
+        <v>295.7</v>
       </c>
       <c r="G417" t="n">
         <v>293</v>
       </c>
       <c r="H417" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="I417" t="n">
-        <v>289</v>
+        <v>291.6</v>
       </c>
       <c r="J417" t="n">
         <v>281.8</v>
       </c>
       <c r="K417" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>1.37</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="418">
@@ -22152,31 +22152,31 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>5590.5</v>
+        <v>5655</v>
       </c>
       <c r="D418" t="n">
         <v>5524.43</v>
       </c>
       <c r="E418" t="n">
-        <v>66.06999999999999</v>
+        <v>130.57</v>
       </c>
       <c r="F418" t="n">
-        <v>5705</v>
+        <v>5687</v>
       </c>
       <c r="G418" t="n">
         <v>5524.43</v>
       </c>
       <c r="H418" t="n">
-        <v>180.57</v>
+        <v>162.57</v>
       </c>
       <c r="I418" t="n">
-        <v>5590.5</v>
+        <v>5570.5</v>
       </c>
       <c r="J418" t="n">
         <v>5424.98</v>
       </c>
       <c r="K418" t="n">
-        <v>165.52</v>
+        <v>145.52</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>1.2</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="419">
@@ -22204,31 +22204,31 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>5250.5</v>
+        <v>5218</v>
       </c>
       <c r="D419" t="n">
         <v>5175.69</v>
       </c>
       <c r="E419" t="n">
-        <v>74.81</v>
+        <v>42.31</v>
       </c>
       <c r="F419" t="n">
-        <v>5280</v>
+        <v>5227.5</v>
       </c>
       <c r="G419" t="n">
         <v>5279.51</v>
       </c>
       <c r="H419" t="n">
-        <v>0.49</v>
+        <v>-52.01</v>
       </c>
       <c r="I419" t="n">
-        <v>5221.5</v>
+        <v>5080.5</v>
       </c>
       <c r="J419" t="n">
         <v>5163.61</v>
       </c>
       <c r="K419" t="n">
-        <v>57.89</v>
+        <v>-83.11</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>1.45</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="420">
@@ -22256,31 +22256,31 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>5595</v>
+        <v>5624.5</v>
       </c>
       <c r="D420" t="n">
         <v>5561.37</v>
       </c>
       <c r="E420" t="n">
-        <v>33.63</v>
+        <v>63.13</v>
       </c>
       <c r="F420" t="n">
-        <v>5720</v>
+        <v>5682</v>
       </c>
       <c r="G420" t="n">
         <v>5561.37</v>
       </c>
       <c r="H420" t="n">
-        <v>158.63</v>
+        <v>120.63</v>
       </c>
       <c r="I420" t="n">
-        <v>5595</v>
+        <v>5590</v>
       </c>
       <c r="J420" t="n">
         <v>5438.41</v>
       </c>
       <c r="K420" t="n">
-        <v>156.59</v>
+        <v>151.59</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="421">
@@ -22308,31 +22308,31 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>672.5</v>
+        <v>682.95</v>
       </c>
       <c r="D421" t="n">
         <v>698.39</v>
       </c>
       <c r="E421" t="n">
-        <v>-25.89</v>
+        <v>-15.44</v>
       </c>
       <c r="F421" t="n">
-        <v>690.4</v>
+        <v>688.2</v>
       </c>
       <c r="G421" t="n">
         <v>698.39</v>
       </c>
       <c r="H421" t="n">
-        <v>-7.99</v>
+        <v>-10.19</v>
       </c>
       <c r="I421" t="n">
-        <v>672.5</v>
+        <v>678.3</v>
       </c>
       <c r="J421" t="n">
         <v>664.92</v>
       </c>
       <c r="K421" t="n">
-        <v>7.58</v>
+        <v>13.38</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>3.71</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="422">
@@ -22360,31 +22360,31 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>4038.1</v>
+        <v>4119</v>
       </c>
       <c r="D422" t="n">
         <v>3988.26</v>
       </c>
       <c r="E422" t="n">
-        <v>49.84</v>
+        <v>130.74</v>
       </c>
       <c r="F422" t="n">
-        <v>4124.9</v>
+        <v>4125.3</v>
       </c>
       <c r="G422" t="n">
         <v>4047.72</v>
       </c>
       <c r="H422" t="n">
-        <v>77.18000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="I422" t="n">
-        <v>4038.1</v>
+        <v>4066.6</v>
       </c>
       <c r="J422" t="n">
         <v>3989.84</v>
       </c>
       <c r="K422" t="n">
-        <v>48.26</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>1.25</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="423">
@@ -22412,31 +22412,31 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="D423" t="n">
         <v>867.9299999999999</v>
       </c>
       <c r="E423" t="n">
-        <v>21.07</v>
+        <v>10.07</v>
       </c>
       <c r="F423" t="n">
-        <v>905</v>
+        <v>881.75</v>
       </c>
       <c r="G423" t="n">
         <v>898.46</v>
       </c>
       <c r="H423" t="n">
-        <v>6.54</v>
+        <v>-16.71</v>
       </c>
       <c r="I423" t="n">
-        <v>882.5</v>
+        <v>869</v>
       </c>
       <c r="J423" t="n">
         <v>878.9</v>
       </c>
       <c r="K423" t="n">
-        <v>3.6</v>
+        <v>-9.9</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="424">
@@ -22464,31 +22464,31 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>1323.5</v>
+        <v>1350</v>
       </c>
       <c r="D424" t="n">
         <v>1310.96</v>
       </c>
       <c r="E424" t="n">
-        <v>12.54</v>
+        <v>39.04</v>
       </c>
       <c r="F424" t="n">
-        <v>1350.9</v>
+        <v>1350</v>
       </c>
       <c r="G424" t="n">
         <v>1313.69</v>
       </c>
       <c r="H424" t="n">
-        <v>37.21</v>
+        <v>36.31</v>
       </c>
       <c r="I424" t="n">
-        <v>1322</v>
+        <v>1328.1</v>
       </c>
       <c r="J424" t="n">
         <v>1284.25</v>
       </c>
       <c r="K424" t="n">
-        <v>37.75</v>
+        <v>43.85</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -22497,11 +22497,11 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N424" t="n">
-        <v>0.96</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="425">
@@ -22516,31 +22516,31 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D425" t="n">
         <v>480.66</v>
       </c>
       <c r="E425" t="n">
-        <v>36.34</v>
+        <v>35.34</v>
       </c>
       <c r="F425" t="n">
-        <v>524.25</v>
+        <v>518.4</v>
       </c>
       <c r="G425" t="n">
         <v>492.1</v>
       </c>
       <c r="H425" t="n">
-        <v>32.15</v>
+        <v>26.3</v>
       </c>
       <c r="I425" t="n">
-        <v>514.75</v>
+        <v>511.3</v>
       </c>
       <c r="J425" t="n">
         <v>501.99</v>
       </c>
       <c r="K425" t="n">
-        <v>12.76</v>
+        <v>9.31</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>7.56</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="426">
@@ -22568,31 +22568,31 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D426" t="n">
         <v>300.94</v>
       </c>
       <c r="E426" t="n">
-        <v>26.06</v>
+        <v>30.06</v>
       </c>
       <c r="F426" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G426" t="n">
         <v>331.1</v>
       </c>
       <c r="H426" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="I426" t="n">
-        <v>325</v>
+        <v>325.5</v>
       </c>
       <c r="J426" t="n">
         <v>323.91</v>
       </c>
       <c r="K426" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>8.66</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="427">
@@ -22620,31 +22620,31 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1197.2</v>
+        <v>1210</v>
       </c>
       <c r="D427" t="n">
         <v>1185.6</v>
       </c>
       <c r="E427" t="n">
-        <v>11.6</v>
+        <v>24.4</v>
       </c>
       <c r="F427" t="n">
-        <v>1219.8</v>
+        <v>1210</v>
       </c>
       <c r="G427" t="n">
         <v>1189.57</v>
       </c>
       <c r="H427" t="n">
-        <v>30.23</v>
+        <v>20.43</v>
       </c>
       <c r="I427" t="n">
-        <v>1195</v>
+        <v>1186.4</v>
       </c>
       <c r="J427" t="n">
         <v>1162.96</v>
       </c>
       <c r="K427" t="n">
-        <v>32.04</v>
+        <v>23.44</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="428">
@@ -22672,31 +22672,31 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="D428" t="n">
         <v>2563.5</v>
       </c>
       <c r="E428" t="n">
-        <v>61.5</v>
+        <v>46.5</v>
       </c>
       <c r="F428" t="n">
-        <v>2656.8</v>
+        <v>2621.7</v>
       </c>
       <c r="G428" t="n">
         <v>2584.48</v>
       </c>
       <c r="H428" t="n">
-        <v>72.31999999999999</v>
+        <v>37.22</v>
       </c>
       <c r="I428" t="n">
-        <v>2579.4</v>
+        <v>2520</v>
       </c>
       <c r="J428" t="n">
         <v>2533.54</v>
       </c>
       <c r="K428" t="n">
-        <v>45.86</v>
+        <v>-13.54</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="429">
@@ -22724,31 +22724,31 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>1880</v>
+        <v>1892.8</v>
       </c>
       <c r="D429" t="n">
         <v>1878.53</v>
       </c>
       <c r="E429" t="n">
-        <v>1.47</v>
+        <v>14.27</v>
       </c>
       <c r="F429" t="n">
-        <v>1937.1</v>
+        <v>1899.9</v>
       </c>
       <c r="G429" t="n">
         <v>1910.56</v>
       </c>
       <c r="H429" t="n">
-        <v>26.54</v>
+        <v>-10.66</v>
       </c>
       <c r="I429" t="n">
-        <v>1878.6</v>
+        <v>1870</v>
       </c>
       <c r="J429" t="n">
         <v>1869.32</v>
       </c>
       <c r="K429" t="n">
-        <v>9.279999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>0.08</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="430">
@@ -22776,31 +22776,31 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>14735</v>
+        <v>14990</v>
       </c>
       <c r="D430" t="n">
         <v>13562.91</v>
       </c>
       <c r="E430" t="n">
-        <v>1172.09</v>
+        <v>1427.09</v>
       </c>
       <c r="F430" t="n">
-        <v>14983</v>
+        <v>14990</v>
       </c>
       <c r="G430" t="n">
         <v>14809.22</v>
       </c>
       <c r="H430" t="n">
-        <v>173.78</v>
+        <v>180.78</v>
       </c>
       <c r="I430" t="n">
-        <v>14720</v>
+        <v>14400</v>
       </c>
       <c r="J430" t="n">
         <v>14483.88</v>
       </c>
       <c r="K430" t="n">
-        <v>236.12</v>
+        <v>-83.88</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>8.640000000000001</v>
+        <v>10.52</v>
       </c>
     </row>
   </sheetData>
@@ -23884,31 +23884,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1197.2</v>
+        <v>1210</v>
       </c>
       <c r="D16" t="n">
         <v>1185.6</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6</v>
+        <v>24.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1219.8</v>
+        <v>1210</v>
       </c>
       <c r="G16" t="n">
         <v>1189.57</v>
       </c>
       <c r="H16" t="n">
-        <v>30.23</v>
+        <v>20.43</v>
       </c>
       <c r="I16" t="n">
-        <v>1195</v>
+        <v>1186.4</v>
       </c>
       <c r="J16" t="n">
         <v>1162.96</v>
       </c>
       <c r="K16" t="n">
-        <v>32.04</v>
+        <v>23.44</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>
@@ -26810,31 +26810,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D17" t="n">
         <v>300.94</v>
       </c>
       <c r="E17" t="n">
-        <v>26.06</v>
+        <v>30.06</v>
       </c>
       <c r="F17" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G17" t="n">
         <v>331.1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>325</v>
+        <v>325.5</v>
       </c>
       <c r="J17" t="n">
         <v>323.91</v>
       </c>
       <c r="K17" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.66</v>
+        <v>9.99</v>
       </c>
     </row>
   </sheetData>
@@ -27728,31 +27728,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14735</v>
+        <v>14990</v>
       </c>
       <c r="D17" t="n">
         <v>13562.91</v>
       </c>
       <c r="E17" t="n">
-        <v>1172.09</v>
+        <v>1427.09</v>
       </c>
       <c r="F17" t="n">
-        <v>14983</v>
+        <v>14990</v>
       </c>
       <c r="G17" t="n">
         <v>14809.22</v>
       </c>
       <c r="H17" t="n">
-        <v>173.78</v>
+        <v>180.78</v>
       </c>
       <c r="I17" t="n">
-        <v>14720</v>
+        <v>14400</v>
       </c>
       <c r="J17" t="n">
         <v>14483.88</v>
       </c>
       <c r="K17" t="n">
-        <v>236.12</v>
+        <v>-83.88</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.640000000000001</v>
+        <v>10.52</v>
       </c>
     </row>
   </sheetData>
@@ -28646,31 +28646,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1880</v>
+        <v>1892.8</v>
       </c>
       <c r="D17" t="n">
         <v>1878.53</v>
       </c>
       <c r="E17" t="n">
-        <v>1.47</v>
+        <v>14.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1937.1</v>
+        <v>1899.9</v>
       </c>
       <c r="G17" t="n">
         <v>1910.56</v>
       </c>
       <c r="H17" t="n">
-        <v>26.54</v>
+        <v>-10.66</v>
       </c>
       <c r="I17" t="n">
-        <v>1878.6</v>
+        <v>1870</v>
       </c>
       <c r="J17" t="n">
         <v>1869.32</v>
       </c>
       <c r="K17" t="n">
-        <v>9.279999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.08</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -29460,31 +29460,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5590.5</v>
+        <v>5655</v>
       </c>
       <c r="D15" t="n">
         <v>5524.43</v>
       </c>
       <c r="E15" t="n">
-        <v>66.06999999999999</v>
+        <v>130.57</v>
       </c>
       <c r="F15" t="n">
-        <v>5705</v>
+        <v>5687</v>
       </c>
       <c r="G15" t="n">
         <v>5524.43</v>
       </c>
       <c r="H15" t="n">
-        <v>180.57</v>
+        <v>162.57</v>
       </c>
       <c r="I15" t="n">
-        <v>5590.5</v>
+        <v>5570.5</v>
       </c>
       <c r="J15" t="n">
         <v>5424.98</v>
       </c>
       <c r="K15" t="n">
-        <v>165.52</v>
+        <v>145.52</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>
@@ -30378,31 +30378,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>116.7</v>
+        <v>115.93</v>
       </c>
       <c r="D17" t="n">
         <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3</v>
+        <v>-4.07</v>
       </c>
       <c r="F17" t="n">
-        <v>118.2</v>
+        <v>116.9</v>
       </c>
       <c r="G17" t="n">
         <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>116.39</v>
+        <v>115.01</v>
       </c>
       <c r="J17" t="n">
         <v>115.09</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.39</v>
       </c>
     </row>
   </sheetData>
@@ -31244,31 +31244,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3398.2</v>
+        <v>3443</v>
       </c>
       <c r="D16" t="n">
         <v>3181.19</v>
       </c>
       <c r="E16" t="n">
-        <v>217.01</v>
+        <v>261.81</v>
       </c>
       <c r="F16" t="n">
-        <v>3447.9</v>
+        <v>3443</v>
       </c>
       <c r="G16" t="n">
         <v>3414.55</v>
       </c>
       <c r="H16" t="n">
-        <v>33.35</v>
+        <v>28.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3398.2</v>
+        <v>3396.8</v>
       </c>
       <c r="J16" t="n">
         <v>3339.5</v>
       </c>
       <c r="K16" t="n">
-        <v>58.7</v>
+        <v>57.3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.82</v>
+        <v>8.23</v>
       </c>
     </row>
   </sheetData>
@@ -32110,31 +32110,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D16" t="n">
         <v>480.66</v>
       </c>
       <c r="E16" t="n">
-        <v>36.34</v>
+        <v>35.34</v>
       </c>
       <c r="F16" t="n">
-        <v>524.25</v>
+        <v>518.4</v>
       </c>
       <c r="G16" t="n">
         <v>492.1</v>
       </c>
       <c r="H16" t="n">
-        <v>32.15</v>
+        <v>26.3</v>
       </c>
       <c r="I16" t="n">
-        <v>514.75</v>
+        <v>511.3</v>
       </c>
       <c r="J16" t="n">
         <v>501.99</v>
       </c>
       <c r="K16" t="n">
-        <v>12.76</v>
+        <v>9.31</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>7.56</v>
+        <v>7.35</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22814,6 +22814,1618 @@
       </c>
       <c r="N430" t="n">
         <v>10.52</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D431" t="n">
+        <v>2015.56</v>
+      </c>
+      <c r="E431" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F431" t="n">
+        <v>2024.9</v>
+      </c>
+      <c r="G431" t="n">
+        <v>2015.56</v>
+      </c>
+      <c r="H431" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="I431" t="n">
+        <v>2005.5</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1981.11</v>
+      </c>
+      <c r="K431" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1312.04</v>
+      </c>
+      <c r="E432" t="n">
+        <v>-52.04</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="G432" t="n">
+        <v>1312.04</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-39.94</v>
+      </c>
+      <c r="I432" t="n">
+        <v>1250.7</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1279.57</v>
+      </c>
+      <c r="K432" t="n">
+        <v>-28.87</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D433" t="n">
+        <v>2240.15</v>
+      </c>
+      <c r="E433" t="n">
+        <v>-81.15000000000001</v>
+      </c>
+      <c r="F433" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G433" t="n">
+        <v>2240.15</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-81.15000000000001</v>
+      </c>
+      <c r="I433" t="n">
+        <v>2119.7</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2149.29</v>
+      </c>
+      <c r="K433" t="n">
+        <v>-29.59</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>469.15</v>
+      </c>
+      <c r="D434" t="n">
+        <v>463.18</v>
+      </c>
+      <c r="E434" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="F434" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="G434" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I434" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="K434" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="D435" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="E435" t="n">
+        <v>-48.32</v>
+      </c>
+      <c r="F435" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="G435" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="H435" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I435" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2020.16</v>
+      </c>
+      <c r="K435" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1885.58</v>
+      </c>
+      <c r="E436" t="n">
+        <v>-15.58</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1905.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1885.58</v>
+      </c>
+      <c r="H436" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="I436" t="n">
+        <v>1867.8</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1829.23</v>
+      </c>
+      <c r="K436" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="D437" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F437" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G437" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="I437" t="n">
+        <v>175.41</v>
+      </c>
+      <c r="J437" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="K437" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>289</v>
+      </c>
+      <c r="D438" t="n">
+        <v>292.78</v>
+      </c>
+      <c r="E438" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="F438" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="G438" t="n">
+        <v>295.83</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I438" t="n">
+        <v>289</v>
+      </c>
+      <c r="J438" t="n">
+        <v>289.37</v>
+      </c>
+      <c r="K438" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="D439" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>5</v>
+      </c>
+      <c r="F439" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="G439" t="n">
+        <v>690.92</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I439" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="J439" t="n">
+        <v>675.96</v>
+      </c>
+      <c r="K439" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D440" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="E440" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F440" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G440" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="H440" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I440" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J440" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="K440" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="E441" t="n">
+        <v>-51.58</v>
+      </c>
+      <c r="F441" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="H441" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="I441" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J441" t="n">
+        <v>1864.49</v>
+      </c>
+      <c r="K441" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1850.81</v>
+      </c>
+      <c r="E442" t="n">
+        <v>-10.81</v>
+      </c>
+      <c r="F442" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G442" t="n">
+        <v>1876.85</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1806.3</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1836.17</v>
+      </c>
+      <c r="K442" t="n">
+        <v>-29.87</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>322.2</v>
+      </c>
+      <c r="D443" t="n">
+        <v>324.08</v>
+      </c>
+      <c r="E443" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F443" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="G443" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="H443" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I443" t="n">
+        <v>320.7</v>
+      </c>
+      <c r="J443" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="K443" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D444" t="n">
+        <v>5833.96</v>
+      </c>
+      <c r="E444" t="n">
+        <v>-243.46</v>
+      </c>
+      <c r="F444" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G444" t="n">
+        <v>5833.96</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-128.96</v>
+      </c>
+      <c r="I444" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J444" t="n">
+        <v>5527.78</v>
+      </c>
+      <c r="K444" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D445" t="n">
+        <v>2323.3</v>
+      </c>
+      <c r="E445" t="n">
+        <v>-73.3</v>
+      </c>
+      <c r="F445" t="n">
+        <v>2279</v>
+      </c>
+      <c r="G445" t="n">
+        <v>2323.3</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-44.3</v>
+      </c>
+      <c r="I445" t="n">
+        <v>2232.3</v>
+      </c>
+      <c r="J445" t="n">
+        <v>2253</v>
+      </c>
+      <c r="K445" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>1526.1</v>
+      </c>
+      <c r="D446" t="n">
+        <v>1577.95</v>
+      </c>
+      <c r="E446" t="n">
+        <v>-51.85</v>
+      </c>
+      <c r="F446" t="n">
+        <v>1544.6</v>
+      </c>
+      <c r="G446" t="n">
+        <v>1577.95</v>
+      </c>
+      <c r="H446" t="n">
+        <v>-33.35</v>
+      </c>
+      <c r="I446" t="n">
+        <v>1525.9</v>
+      </c>
+      <c r="J446" t="n">
+        <v>1501.4</v>
+      </c>
+      <c r="K446" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D447" t="n">
+        <v>1007.35</v>
+      </c>
+      <c r="E447" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="F447" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="G447" t="n">
+        <v>1039.37</v>
+      </c>
+      <c r="H447" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1039.15</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1016.62</v>
+      </c>
+      <c r="K447" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>1323.5</v>
+      </c>
+      <c r="D448" t="n">
+        <v>1380.56</v>
+      </c>
+      <c r="E448" t="n">
+        <v>-57.06</v>
+      </c>
+      <c r="F448" t="n">
+        <v>1350.9</v>
+      </c>
+      <c r="G448" t="n">
+        <v>1380.56</v>
+      </c>
+      <c r="H448" t="n">
+        <v>-29.66</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1322</v>
+      </c>
+      <c r="J448" t="n">
+        <v>1308.48</v>
+      </c>
+      <c r="K448" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>327</v>
+      </c>
+      <c r="D449" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="E449" t="n">
+        <v>-37.75</v>
+      </c>
+      <c r="F449" t="n">
+        <v>332</v>
+      </c>
+      <c r="G449" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="H449" t="n">
+        <v>-32.75</v>
+      </c>
+      <c r="I449" t="n">
+        <v>325</v>
+      </c>
+      <c r="J449" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="K449" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>10.35</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D450" t="n">
+        <v>3096.91</v>
+      </c>
+      <c r="E450" t="n">
+        <v>253.09</v>
+      </c>
+      <c r="F450" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G450" t="n">
+        <v>3259.72</v>
+      </c>
+      <c r="H450" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="I450" t="n">
+        <v>3243.3</v>
+      </c>
+      <c r="J450" t="n">
+        <v>3186.22</v>
+      </c>
+      <c r="K450" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D451" t="n">
+        <v>1045.68</v>
+      </c>
+      <c r="E451" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="F451" t="n">
+        <v>1048.8</v>
+      </c>
+      <c r="G451" t="n">
+        <v>1057.31</v>
+      </c>
+      <c r="H451" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="I451" t="n">
+        <v>1010.65</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1034.29</v>
+      </c>
+      <c r="K451" t="n">
+        <v>-23.64</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>1615.1</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1633.98</v>
+      </c>
+      <c r="E452" t="n">
+        <v>-18.88</v>
+      </c>
+      <c r="F452" t="n">
+        <v>1647.3</v>
+      </c>
+      <c r="G452" t="n">
+        <v>1633.98</v>
+      </c>
+      <c r="H452" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="I452" t="n">
+        <v>1614</v>
+      </c>
+      <c r="J452" t="n">
+        <v>1582.45</v>
+      </c>
+      <c r="K452" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D453" t="n">
+        <v>11693.34</v>
+      </c>
+      <c r="E453" t="n">
+        <v>-153.34</v>
+      </c>
+      <c r="F453" t="n">
+        <v>11540</v>
+      </c>
+      <c r="G453" t="n">
+        <v>11693.34</v>
+      </c>
+      <c r="H453" t="n">
+        <v>-153.34</v>
+      </c>
+      <c r="I453" t="n">
+        <v>11223</v>
+      </c>
+      <c r="J453" t="n">
+        <v>11188.99</v>
+      </c>
+      <c r="K453" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D454" t="n">
+        <v>1238.61</v>
+      </c>
+      <c r="E454" t="n">
+        <v>-41.41</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G454" t="n">
+        <v>1238.61</v>
+      </c>
+      <c r="H454" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="I454" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J454" t="n">
+        <v>1192.73</v>
+      </c>
+      <c r="K454" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>187.52</v>
+      </c>
+      <c r="D455" t="n">
+        <v>178.65</v>
+      </c>
+      <c r="E455" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="F455" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="G455" t="n">
+        <v>188</v>
+      </c>
+      <c r="H455" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I455" t="n">
+        <v>187.12</v>
+      </c>
+      <c r="J455" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="K455" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>5595</v>
+      </c>
+      <c r="D456" t="n">
+        <v>5657.9</v>
+      </c>
+      <c r="E456" t="n">
+        <v>-62.9</v>
+      </c>
+      <c r="F456" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G456" t="n">
+        <v>5657.9</v>
+      </c>
+      <c r="H456" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="I456" t="n">
+        <v>5595</v>
+      </c>
+      <c r="J456" t="n">
+        <v>5439.26</v>
+      </c>
+      <c r="K456" t="n">
+        <v>155.74</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D457" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="E457" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F457" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="G457" t="n">
+        <v>389.96</v>
+      </c>
+      <c r="H457" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I457" t="n">
+        <v>393</v>
+      </c>
+      <c r="J457" t="n">
+        <v>381.25</v>
+      </c>
+      <c r="K457" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="D458" t="n">
+        <v>4192.28</v>
+      </c>
+      <c r="E458" t="n">
+        <v>-154.18</v>
+      </c>
+      <c r="F458" t="n">
+        <v>4124.9</v>
+      </c>
+      <c r="G458" t="n">
+        <v>4192.28</v>
+      </c>
+      <c r="H458" t="n">
+        <v>-67.38</v>
+      </c>
+      <c r="I458" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="J458" t="n">
+        <v>3986.79</v>
+      </c>
+      <c r="K458" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D459" t="n">
+        <v>2656.02</v>
+      </c>
+      <c r="E459" t="n">
+        <v>-31.02</v>
+      </c>
+      <c r="F459" t="n">
+        <v>2656.8</v>
+      </c>
+      <c r="G459" t="n">
+        <v>2656.02</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I459" t="n">
+        <v>2579.4</v>
+      </c>
+      <c r="J459" t="n">
+        <v>2525.21</v>
+      </c>
+      <c r="K459" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>889</v>
+      </c>
+      <c r="D460" t="n">
+        <v>901.8200000000001</v>
+      </c>
+      <c r="E460" t="n">
+        <v>-12.82</v>
+      </c>
+      <c r="F460" t="n">
+        <v>905</v>
+      </c>
+      <c r="G460" t="n">
+        <v>901.8200000000001</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I460" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="J460" t="n">
+        <v>876.62</v>
+      </c>
+      <c r="K460" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D461" t="n">
+        <v>16388.96</v>
+      </c>
+      <c r="E461" t="n">
+        <v>-1653.96</v>
+      </c>
+      <c r="F461" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G461" t="n">
+        <v>16388.96</v>
+      </c>
+      <c r="H461" t="n">
+        <v>-1405.96</v>
+      </c>
+      <c r="I461" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J461" t="n">
+        <v>14637.6</v>
+      </c>
+      <c r="K461" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>10.09</v>
       </c>
     </row>
   </sheetData>
@@ -23069,7 +24681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23922,6 +25534,58 @@
       </c>
       <c r="N16" t="n">
         <v>2.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1238.61</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-41.41</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1238.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1192.73</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
@@ -24991,7 +26655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25272,6 +26936,58 @@
       </c>
       <c r="N5" t="n">
         <v>4.78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-48.32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2020.16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.32</v>
       </c>
     </row>
   </sheetData>
@@ -25943,7 +27659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26848,6 +28564,58 @@
       </c>
       <c r="N17" t="n">
         <v>9.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>327</v>
+      </c>
+      <c r="D18" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-37.75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>332</v>
+      </c>
+      <c r="G18" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-32.75</v>
+      </c>
+      <c r="I18" t="n">
+        <v>325</v>
+      </c>
+      <c r="J18" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>10.35</v>
       </c>
     </row>
   </sheetData>
@@ -26861,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27766,6 +29534,58 @@
       </c>
       <c r="N17" t="n">
         <v>10.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16388.96</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1653.96</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16388.96</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1405.96</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14637.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>10.09</v>
       </c>
     </row>
   </sheetData>
@@ -27779,7 +29599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28684,6 +30504,58 @@
       </c>
       <c r="N17" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-51.58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1864.49</v>
+      </c>
+      <c r="K18" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>
@@ -28697,7 +30569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29498,6 +31370,58 @@
       </c>
       <c r="N15" t="n">
         <v>2.36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5833.96</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-243.46</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5833.96</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-128.96</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5527.78</v>
+      </c>
+      <c r="K16" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4.17</v>
       </c>
     </row>
   </sheetData>
@@ -29511,7 +31435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30416,6 +32340,58 @@
       </c>
       <c r="N17" t="n">
         <v>3.39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F18" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J18" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>3.85</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -22828,31 +22828,31 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D431" t="n">
         <v>2015.56</v>
       </c>
       <c r="E431" t="n">
-        <v>-5.56</v>
+        <v>-4.56</v>
       </c>
       <c r="F431" t="n">
-        <v>2024.9</v>
+        <v>2011</v>
       </c>
       <c r="G431" t="n">
         <v>2015.56</v>
       </c>
       <c r="H431" t="n">
-        <v>9.34</v>
+        <v>-4.56</v>
       </c>
       <c r="I431" t="n">
-        <v>2005.5</v>
+        <v>2011</v>
       </c>
       <c r="J431" t="n">
         <v>1981.11</v>
       </c>
       <c r="K431" t="n">
-        <v>24.39</v>
+        <v>29.89</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="432">
@@ -22880,31 +22880,31 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>1260</v>
+        <v>1280</v>
       </c>
       <c r="D432" t="n">
         <v>1312.04</v>
       </c>
       <c r="E432" t="n">
-        <v>-52.04</v>
+        <v>-32.04</v>
       </c>
       <c r="F432" t="n">
-        <v>1272.1</v>
+        <v>1282</v>
       </c>
       <c r="G432" t="n">
         <v>1312.04</v>
       </c>
       <c r="H432" t="n">
-        <v>-39.94</v>
+        <v>-30.04</v>
       </c>
       <c r="I432" t="n">
-        <v>1250.7</v>
+        <v>1282</v>
       </c>
       <c r="J432" t="n">
         <v>1279.57</v>
       </c>
       <c r="K432" t="n">
-        <v>-28.87</v>
+        <v>2.43</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -22913,11 +22913,11 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N432" t="n">
-        <v>3.97</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="433">
@@ -22932,31 +22932,31 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>2159</v>
+        <v>2188</v>
       </c>
       <c r="D433" t="n">
         <v>2240.15</v>
       </c>
       <c r="E433" t="n">
-        <v>-81.15000000000001</v>
+        <v>-52.15</v>
       </c>
       <c r="F433" t="n">
-        <v>2159</v>
+        <v>2187</v>
       </c>
       <c r="G433" t="n">
         <v>2240.15</v>
       </c>
       <c r="H433" t="n">
-        <v>-81.15000000000001</v>
+        <v>-53.15</v>
       </c>
       <c r="I433" t="n">
-        <v>2119.7</v>
+        <v>2187</v>
       </c>
       <c r="J433" t="n">
         <v>2149.29</v>
       </c>
       <c r="K433" t="n">
-        <v>-29.59</v>
+        <v>37.71</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>3.62</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="434">
@@ -22984,31 +22984,31 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>469.15</v>
+        <v>469.85</v>
       </c>
       <c r="D434" t="n">
         <v>463.18</v>
       </c>
       <c r="E434" t="n">
-        <v>5.97</v>
+        <v>6.67</v>
       </c>
       <c r="F434" t="n">
-        <v>471.6</v>
+        <v>473.5</v>
       </c>
       <c r="G434" t="n">
         <v>470.72</v>
       </c>
       <c r="H434" t="n">
-        <v>0.88</v>
+        <v>2.78</v>
       </c>
       <c r="I434" t="n">
-        <v>458.7</v>
+        <v>473.5</v>
       </c>
       <c r="J434" t="n">
         <v>460.2</v>
       </c>
       <c r="K434" t="n">
-        <v>-1.5</v>
+        <v>13.3</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="435">
@@ -23036,31 +23036,31 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>2035.1</v>
+        <v>2069.4</v>
       </c>
       <c r="D435" t="n">
         <v>2083.42</v>
       </c>
       <c r="E435" t="n">
-        <v>-48.32</v>
+        <v>-14.02</v>
       </c>
       <c r="F435" t="n">
-        <v>2088.5</v>
+        <v>2075.4</v>
       </c>
       <c r="G435" t="n">
         <v>2083.42</v>
       </c>
       <c r="H435" t="n">
-        <v>5.08</v>
+        <v>-8.02</v>
       </c>
       <c r="I435" t="n">
-        <v>2035.1</v>
+        <v>2075.4</v>
       </c>
       <c r="J435" t="n">
         <v>2020.16</v>
       </c>
       <c r="K435" t="n">
-        <v>14.94</v>
+        <v>55.24</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>2.32</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="436">
@@ -23088,31 +23088,31 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>1870</v>
+        <v>1872.9</v>
       </c>
       <c r="D436" t="n">
         <v>1885.58</v>
       </c>
       <c r="E436" t="n">
-        <v>-15.58</v>
+        <v>-12.68</v>
       </c>
       <c r="F436" t="n">
-        <v>1905.5</v>
+        <v>1873.1</v>
       </c>
       <c r="G436" t="n">
         <v>1885.58</v>
       </c>
       <c r="H436" t="n">
-        <v>19.92</v>
+        <v>-12.48</v>
       </c>
       <c r="I436" t="n">
-        <v>1867.8</v>
+        <v>1873.1</v>
       </c>
       <c r="J436" t="n">
         <v>1829.23</v>
       </c>
       <c r="K436" t="n">
-        <v>38.57</v>
+        <v>43.87</v>
       </c>
       <c r="L436" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="437">
@@ -23140,31 +23140,31 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>179.05</v>
+        <v>177.4</v>
       </c>
       <c r="D437" t="n">
         <v>177.1</v>
       </c>
       <c r="E437" t="n">
-        <v>1.95</v>
+        <v>0.3</v>
       </c>
       <c r="F437" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="G437" t="n">
         <v>181.43</v>
       </c>
       <c r="H437" t="n">
-        <v>-1.93</v>
+        <v>-3.43</v>
       </c>
       <c r="I437" t="n">
-        <v>175.41</v>
+        <v>178</v>
       </c>
       <c r="J437" t="n">
         <v>177.4</v>
       </c>
       <c r="K437" t="n">
-        <v>-1.99</v>
+        <v>0.6</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1.1</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="438">
@@ -23192,31 +23192,31 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>289</v>
+        <v>290.95</v>
       </c>
       <c r="D438" t="n">
         <v>292.78</v>
       </c>
       <c r="E438" t="n">
-        <v>-3.78</v>
+        <v>-1.83</v>
       </c>
       <c r="F438" t="n">
-        <v>295.95</v>
+        <v>291</v>
       </c>
       <c r="G438" t="n">
         <v>295.83</v>
       </c>
       <c r="H438" t="n">
-        <v>0.12</v>
+        <v>-4.83</v>
       </c>
       <c r="I438" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J438" t="n">
         <v>289.37</v>
       </c>
       <c r="K438" t="n">
-        <v>-0.37</v>
+        <v>1.63</v>
       </c>
       <c r="L438" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>1.29</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="439">
@@ -23244,31 +23244,31 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>672.5</v>
+        <v>676.15</v>
       </c>
       <c r="D439" t="n">
         <v>667.5</v>
       </c>
       <c r="E439" t="n">
-        <v>5</v>
+        <v>8.65</v>
       </c>
       <c r="F439" t="n">
-        <v>690.4</v>
+        <v>680</v>
       </c>
       <c r="G439" t="n">
         <v>690.92</v>
       </c>
       <c r="H439" t="n">
-        <v>-0.52</v>
+        <v>-10.92</v>
       </c>
       <c r="I439" t="n">
-        <v>672.5</v>
+        <v>680</v>
       </c>
       <c r="J439" t="n">
         <v>675.96</v>
       </c>
       <c r="K439" t="n">
-        <v>-3.46</v>
+        <v>4.04</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="440">
@@ -23296,31 +23296,31 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>116.7</v>
+        <v>115.4</v>
       </c>
       <c r="D440" t="n">
         <v>112.37</v>
       </c>
       <c r="E440" t="n">
-        <v>4.33</v>
+        <v>3.03</v>
       </c>
       <c r="F440" t="n">
-        <v>118.2</v>
+        <v>114.81</v>
       </c>
       <c r="G440" t="n">
         <v>115.61</v>
       </c>
       <c r="H440" t="n">
-        <v>2.59</v>
+        <v>-0.8</v>
       </c>
       <c r="I440" t="n">
-        <v>116.39</v>
+        <v>114.81</v>
       </c>
       <c r="J440" t="n">
         <v>113.31</v>
       </c>
       <c r="K440" t="n">
-        <v>3.08</v>
+        <v>1.5</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="441">
@@ -23348,31 +23348,31 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>1880</v>
+        <v>1901.8</v>
       </c>
       <c r="D441" t="n">
         <v>1931.58</v>
       </c>
       <c r="E441" t="n">
-        <v>-51.58</v>
+        <v>-29.78</v>
       </c>
       <c r="F441" t="n">
-        <v>1937.1</v>
+        <v>1915</v>
       </c>
       <c r="G441" t="n">
         <v>1931.58</v>
       </c>
       <c r="H441" t="n">
-        <v>5.52</v>
+        <v>-16.58</v>
       </c>
       <c r="I441" t="n">
-        <v>1878.6</v>
+        <v>1915</v>
       </c>
       <c r="J441" t="n">
         <v>1864.49</v>
       </c>
       <c r="K441" t="n">
-        <v>14.11</v>
+        <v>50.51</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>2.67</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="442">
@@ -23400,31 +23400,31 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>1840</v>
+        <v>1837.9</v>
       </c>
       <c r="D442" t="n">
         <v>1850.81</v>
       </c>
       <c r="E442" t="n">
-        <v>-10.81</v>
+        <v>-12.91</v>
       </c>
       <c r="F442" t="n">
-        <v>1875</v>
+        <v>1842.7</v>
       </c>
       <c r="G442" t="n">
         <v>1876.85</v>
       </c>
       <c r="H442" t="n">
-        <v>-1.85</v>
+        <v>-34.15</v>
       </c>
       <c r="I442" t="n">
-        <v>1806.3</v>
+        <v>1842.7</v>
       </c>
       <c r="J442" t="n">
         <v>1836.17</v>
       </c>
       <c r="K442" t="n">
-        <v>-29.87</v>
+        <v>6.53</v>
       </c>
       <c r="L442" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="443">
@@ -23452,31 +23452,31 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>322.2</v>
+        <v>321.9</v>
       </c>
       <c r="D443" t="n">
         <v>324.08</v>
       </c>
       <c r="E443" t="n">
-        <v>-1.88</v>
+        <v>-2.18</v>
       </c>
       <c r="F443" t="n">
-        <v>327.3</v>
+        <v>322</v>
       </c>
       <c r="G443" t="n">
         <v>326.19</v>
       </c>
       <c r="H443" t="n">
-        <v>1.11</v>
+        <v>-4.19</v>
       </c>
       <c r="I443" t="n">
-        <v>320.7</v>
+        <v>322</v>
       </c>
       <c r="J443" t="n">
         <v>319.03</v>
       </c>
       <c r="K443" t="n">
-        <v>1.67</v>
+        <v>2.97</v>
       </c>
       <c r="L443" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="444">
@@ -23504,31 +23504,31 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>5590.5</v>
+        <v>5654</v>
       </c>
       <c r="D444" t="n">
         <v>5833.96</v>
       </c>
       <c r="E444" t="n">
-        <v>-243.46</v>
+        <v>-179.96</v>
       </c>
       <c r="F444" t="n">
-        <v>5705</v>
+        <v>5677</v>
       </c>
       <c r="G444" t="n">
         <v>5833.96</v>
       </c>
       <c r="H444" t="n">
-        <v>-128.96</v>
+        <v>-156.96</v>
       </c>
       <c r="I444" t="n">
-        <v>5590.5</v>
+        <v>5677</v>
       </c>
       <c r="J444" t="n">
         <v>5527.78</v>
       </c>
       <c r="K444" t="n">
-        <v>62.72</v>
+        <v>149.22</v>
       </c>
       <c r="L444" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>4.17</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="445">
@@ -23556,31 +23556,31 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="D445" t="n">
         <v>2323.3</v>
       </c>
       <c r="E445" t="n">
-        <v>-73.3</v>
+        <v>-70.3</v>
       </c>
       <c r="F445" t="n">
-        <v>2279</v>
+        <v>2248.7</v>
       </c>
       <c r="G445" t="n">
         <v>2323.3</v>
       </c>
       <c r="H445" t="n">
-        <v>-44.3</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="I445" t="n">
-        <v>2232.3</v>
+        <v>2248.7</v>
       </c>
       <c r="J445" t="n">
         <v>2253</v>
       </c>
       <c r="K445" t="n">
-        <v>-20.7</v>
+        <v>-4.3</v>
       </c>
       <c r="L445" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="446">
@@ -23608,31 +23608,31 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>1526.1</v>
+        <v>1529.2</v>
       </c>
       <c r="D446" t="n">
         <v>1577.95</v>
       </c>
       <c r="E446" t="n">
-        <v>-51.85</v>
+        <v>-48.75</v>
       </c>
       <c r="F446" t="n">
-        <v>1544.6</v>
+        <v>1535.6</v>
       </c>
       <c r="G446" t="n">
         <v>1577.95</v>
       </c>
       <c r="H446" t="n">
-        <v>-33.35</v>
+        <v>-42.35</v>
       </c>
       <c r="I446" t="n">
-        <v>1525.9</v>
+        <v>1535.6</v>
       </c>
       <c r="J446" t="n">
         <v>1501.4</v>
       </c>
       <c r="K446" t="n">
-        <v>24.5</v>
+        <v>34.2</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="447">
@@ -23660,31 +23660,31 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>1053</v>
+        <v>1024</v>
       </c>
       <c r="D447" t="n">
         <v>1007.35</v>
       </c>
       <c r="E447" t="n">
-        <v>45.65</v>
+        <v>16.65</v>
       </c>
       <c r="F447" t="n">
-        <v>1059.5</v>
+        <v>1030</v>
       </c>
       <c r="G447" t="n">
         <v>1039.37</v>
       </c>
       <c r="H447" t="n">
-        <v>20.13</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="I447" t="n">
-        <v>1039.15</v>
+        <v>1030</v>
       </c>
       <c r="J447" t="n">
         <v>1016.62</v>
       </c>
       <c r="K447" t="n">
-        <v>22.53</v>
+        <v>13.38</v>
       </c>
       <c r="L447" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>4.53</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="448">
@@ -23712,31 +23712,31 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>1323.5</v>
+        <v>1330</v>
       </c>
       <c r="D448" t="n">
         <v>1380.56</v>
       </c>
       <c r="E448" t="n">
-        <v>-57.06</v>
+        <v>-50.56</v>
       </c>
       <c r="F448" t="n">
-        <v>1350.9</v>
+        <v>1339</v>
       </c>
       <c r="G448" t="n">
         <v>1380.56</v>
       </c>
       <c r="H448" t="n">
-        <v>-29.66</v>
+        <v>-41.56</v>
       </c>
       <c r="I448" t="n">
-        <v>1322</v>
+        <v>1339</v>
       </c>
       <c r="J448" t="n">
         <v>1308.48</v>
       </c>
       <c r="K448" t="n">
-        <v>13.52</v>
+        <v>30.52</v>
       </c>
       <c r="L448" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>4.13</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="449">
@@ -23764,31 +23764,31 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>327</v>
+        <v>328.5</v>
       </c>
       <c r="D449" t="n">
         <v>364.75</v>
       </c>
       <c r="E449" t="n">
-        <v>-37.75</v>
+        <v>-36.25</v>
       </c>
       <c r="F449" t="n">
-        <v>332</v>
+        <v>329.1</v>
       </c>
       <c r="G449" t="n">
         <v>364.75</v>
       </c>
       <c r="H449" t="n">
-        <v>-32.75</v>
+        <v>-35.65</v>
       </c>
       <c r="I449" t="n">
-        <v>325</v>
+        <v>329.1</v>
       </c>
       <c r="J449" t="n">
         <v>328.4</v>
       </c>
       <c r="K449" t="n">
-        <v>-3.4</v>
+        <v>0.7</v>
       </c>
       <c r="L449" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>10.35</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="450">
@@ -23816,31 +23816,31 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>3350</v>
+        <v>3273</v>
       </c>
       <c r="D450" t="n">
         <v>3096.91</v>
       </c>
       <c r="E450" t="n">
-        <v>253.09</v>
+        <v>176.09</v>
       </c>
       <c r="F450" t="n">
-        <v>3355</v>
+        <v>3273.1</v>
       </c>
       <c r="G450" t="n">
         <v>3259.72</v>
       </c>
       <c r="H450" t="n">
-        <v>95.28</v>
+        <v>13.38</v>
       </c>
       <c r="I450" t="n">
-        <v>3243.3</v>
+        <v>3273.1</v>
       </c>
       <c r="J450" t="n">
         <v>3186.22</v>
       </c>
       <c r="K450" t="n">
-        <v>57.08</v>
+        <v>86.88</v>
       </c>
       <c r="L450" t="inlineStr">
         <is>
@@ -23849,11 +23849,11 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N450" t="n">
-        <v>8.17</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="451">
@@ -23868,31 +23868,31 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>1040</v>
+        <v>1038.1</v>
       </c>
       <c r="D451" t="n">
         <v>1045.68</v>
       </c>
       <c r="E451" t="n">
-        <v>-5.68</v>
+        <v>-7.58</v>
       </c>
       <c r="F451" t="n">
-        <v>1048.8</v>
+        <v>1034</v>
       </c>
       <c r="G451" t="n">
         <v>1057.31</v>
       </c>
       <c r="H451" t="n">
-        <v>-8.51</v>
+        <v>-23.31</v>
       </c>
       <c r="I451" t="n">
-        <v>1010.65</v>
+        <v>1034</v>
       </c>
       <c r="J451" t="n">
         <v>1034.29</v>
       </c>
       <c r="K451" t="n">
-        <v>-23.64</v>
+        <v>-0.29</v>
       </c>
       <c r="L451" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         </is>
       </c>
       <c r="N451" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="452">
@@ -23920,31 +23920,31 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>1615.1</v>
+        <v>1623</v>
       </c>
       <c r="D452" t="n">
         <v>1633.98</v>
       </c>
       <c r="E452" t="n">
-        <v>-18.88</v>
+        <v>-10.98</v>
       </c>
       <c r="F452" t="n">
-        <v>1647.3</v>
+        <v>1624</v>
       </c>
       <c r="G452" t="n">
         <v>1633.98</v>
       </c>
       <c r="H452" t="n">
-        <v>13.32</v>
+        <v>-9.98</v>
       </c>
       <c r="I452" t="n">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="J452" t="n">
         <v>1582.45</v>
       </c>
       <c r="K452" t="n">
-        <v>31.55</v>
+        <v>41.55</v>
       </c>
       <c r="L452" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         </is>
       </c>
       <c r="N452" t="n">
-        <v>1.16</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="453">
@@ -23972,31 +23972,31 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>11540</v>
+        <v>11399</v>
       </c>
       <c r="D453" t="n">
         <v>11693.34</v>
       </c>
       <c r="E453" t="n">
-        <v>-153.34</v>
+        <v>-294.34</v>
       </c>
       <c r="F453" t="n">
-        <v>11540</v>
+        <v>11406</v>
       </c>
       <c r="G453" t="n">
         <v>11693.34</v>
       </c>
       <c r="H453" t="n">
-        <v>-153.34</v>
+        <v>-287.34</v>
       </c>
       <c r="I453" t="n">
-        <v>11223</v>
+        <v>11406</v>
       </c>
       <c r="J453" t="n">
         <v>11188.99</v>
       </c>
       <c r="K453" t="n">
-        <v>34.01</v>
+        <v>217.01</v>
       </c>
       <c r="L453" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="454">
@@ -24024,31 +24024,31 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>1197.2</v>
+        <v>1204</v>
       </c>
       <c r="D454" t="n">
         <v>1238.61</v>
       </c>
       <c r="E454" t="n">
-        <v>-41.41</v>
+        <v>-34.61</v>
       </c>
       <c r="F454" t="n">
-        <v>1219.8</v>
+        <v>1204</v>
       </c>
       <c r="G454" t="n">
         <v>1238.61</v>
       </c>
       <c r="H454" t="n">
-        <v>-18.81</v>
+        <v>-34.61</v>
       </c>
       <c r="I454" t="n">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="J454" t="n">
         <v>1192.73</v>
       </c>
       <c r="K454" t="n">
-        <v>2.27</v>
+        <v>11.27</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         </is>
       </c>
       <c r="N454" t="n">
-        <v>3.34</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="455">
@@ -24076,31 +24076,31 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>187.52</v>
+        <v>184.5</v>
       </c>
       <c r="D455" t="n">
         <v>178.65</v>
       </c>
       <c r="E455" t="n">
-        <v>8.869999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="F455" t="n">
-        <v>192.33</v>
+        <v>184.7</v>
       </c>
       <c r="G455" t="n">
         <v>188</v>
       </c>
       <c r="H455" t="n">
-        <v>4.33</v>
+        <v>-3.3</v>
       </c>
       <c r="I455" t="n">
-        <v>187.12</v>
+        <v>184.7</v>
       </c>
       <c r="J455" t="n">
         <v>183.9</v>
       </c>
       <c r="K455" t="n">
-        <v>3.22</v>
+        <v>0.8</v>
       </c>
       <c r="L455" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>4.97</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="456">
@@ -24128,31 +24128,31 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>5595</v>
+        <v>5550</v>
       </c>
       <c r="D456" t="n">
         <v>5657.9</v>
       </c>
       <c r="E456" t="n">
-        <v>-62.9</v>
+        <v>-107.9</v>
       </c>
       <c r="F456" t="n">
-        <v>5720</v>
+        <v>5549</v>
       </c>
       <c r="G456" t="n">
         <v>5657.9</v>
       </c>
       <c r="H456" t="n">
-        <v>62.1</v>
+        <v>-108.9</v>
       </c>
       <c r="I456" t="n">
-        <v>5595</v>
+        <v>5549</v>
       </c>
       <c r="J456" t="n">
         <v>5439.26</v>
       </c>
       <c r="K456" t="n">
-        <v>155.74</v>
+        <v>109.74</v>
       </c>
       <c r="L456" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="N456" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="457">
@@ -24180,31 +24180,31 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>399.3</v>
+        <v>389.3</v>
       </c>
       <c r="D457" t="n">
         <v>334.7</v>
       </c>
       <c r="E457" t="n">
-        <v>64.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="F457" t="n">
-        <v>400.45</v>
+        <v>392.65</v>
       </c>
       <c r="G457" t="n">
         <v>389.96</v>
       </c>
       <c r="H457" t="n">
-        <v>10.49</v>
+        <v>2.69</v>
       </c>
       <c r="I457" t="n">
-        <v>393</v>
+        <v>392.65</v>
       </c>
       <c r="J457" t="n">
         <v>381.25</v>
       </c>
       <c r="K457" t="n">
-        <v>11.75</v>
+        <v>11.4</v>
       </c>
       <c r="L457" t="inlineStr">
         <is>
@@ -24213,11 +24213,11 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N457" t="n">
-        <v>19.3</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="458">
@@ -24232,31 +24232,31 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>4038.1</v>
+        <v>4027</v>
       </c>
       <c r="D458" t="n">
         <v>4192.28</v>
       </c>
       <c r="E458" t="n">
-        <v>-154.18</v>
+        <v>-165.28</v>
       </c>
       <c r="F458" t="n">
-        <v>4124.9</v>
+        <v>4045</v>
       </c>
       <c r="G458" t="n">
         <v>4192.28</v>
       </c>
       <c r="H458" t="n">
-        <v>-67.38</v>
+        <v>-147.28</v>
       </c>
       <c r="I458" t="n">
-        <v>4038.1</v>
+        <v>4045</v>
       </c>
       <c r="J458" t="n">
         <v>3986.79</v>
       </c>
       <c r="K458" t="n">
-        <v>51.31</v>
+        <v>58.21</v>
       </c>
       <c r="L458" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="459">
@@ -24284,31 +24284,31 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>2625</v>
+        <v>2588</v>
       </c>
       <c r="D459" t="n">
         <v>2656.02</v>
       </c>
       <c r="E459" t="n">
-        <v>-31.02</v>
+        <v>-68.02</v>
       </c>
       <c r="F459" t="n">
-        <v>2656.8</v>
+        <v>2583</v>
       </c>
       <c r="G459" t="n">
         <v>2656.02</v>
       </c>
       <c r="H459" t="n">
-        <v>0.78</v>
+        <v>-73.02</v>
       </c>
       <c r="I459" t="n">
-        <v>2579.4</v>
+        <v>2583</v>
       </c>
       <c r="J459" t="n">
         <v>2525.21</v>
       </c>
       <c r="K459" t="n">
-        <v>54.19</v>
+        <v>57.79</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>1.17</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="460">
@@ -24336,31 +24336,31 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>889</v>
+        <v>884.4</v>
       </c>
       <c r="D460" t="n">
         <v>901.8200000000001</v>
       </c>
       <c r="E460" t="n">
-        <v>-12.82</v>
+        <v>-17.42</v>
       </c>
       <c r="F460" t="n">
-        <v>905</v>
+        <v>882.2</v>
       </c>
       <c r="G460" t="n">
         <v>901.8200000000001</v>
       </c>
       <c r="H460" t="n">
-        <v>3.18</v>
+        <v>-19.62</v>
       </c>
       <c r="I460" t="n">
-        <v>882.5</v>
+        <v>882.2</v>
       </c>
       <c r="J460" t="n">
         <v>876.62</v>
       </c>
       <c r="K460" t="n">
-        <v>5.88</v>
+        <v>5.58</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         </is>
       </c>
       <c r="N460" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="461">
@@ -24388,31 +24388,31 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>14735</v>
+        <v>14711</v>
       </c>
       <c r="D461" t="n">
         <v>16388.96</v>
       </c>
       <c r="E461" t="n">
-        <v>-1653.96</v>
+        <v>-1677.96</v>
       </c>
       <c r="F461" t="n">
-        <v>14983</v>
+        <v>14811</v>
       </c>
       <c r="G461" t="n">
         <v>16388.96</v>
       </c>
       <c r="H461" t="n">
-        <v>-1405.96</v>
+        <v>-1577.96</v>
       </c>
       <c r="I461" t="n">
-        <v>14720</v>
+        <v>14811</v>
       </c>
       <c r="J461" t="n">
         <v>14637.6</v>
       </c>
       <c r="K461" t="n">
-        <v>82.40000000000001</v>
+        <v>173.4</v>
       </c>
       <c r="L461" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>10.09</v>
+        <v>10.24</v>
       </c>
     </row>
   </sheetData>
@@ -25548,31 +25548,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1197.2</v>
+        <v>1204</v>
       </c>
       <c r="D17" t="n">
         <v>1238.61</v>
       </c>
       <c r="E17" t="n">
-        <v>-41.41</v>
+        <v>-34.61</v>
       </c>
       <c r="F17" t="n">
-        <v>1219.8</v>
+        <v>1204</v>
       </c>
       <c r="G17" t="n">
         <v>1238.61</v>
       </c>
       <c r="H17" t="n">
-        <v>-18.81</v>
+        <v>-34.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="J17" t="n">
         <v>1192.73</v>
       </c>
       <c r="K17" t="n">
-        <v>2.27</v>
+        <v>11.27</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.34</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -26950,31 +26950,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2035.1</v>
+        <v>2069.4</v>
       </c>
       <c r="D6" t="n">
         <v>2083.42</v>
       </c>
       <c r="E6" t="n">
-        <v>-48.32</v>
+        <v>-14.02</v>
       </c>
       <c r="F6" t="n">
-        <v>2088.5</v>
+        <v>2075.4</v>
       </c>
       <c r="G6" t="n">
         <v>2083.42</v>
       </c>
       <c r="H6" t="n">
-        <v>5.08</v>
+        <v>-8.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2035.1</v>
+        <v>2075.4</v>
       </c>
       <c r="J6" t="n">
         <v>2020.16</v>
       </c>
       <c r="K6" t="n">
-        <v>14.94</v>
+        <v>55.24</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -28578,31 +28578,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>327</v>
+        <v>328.5</v>
       </c>
       <c r="D18" t="n">
         <v>364.75</v>
       </c>
       <c r="E18" t="n">
-        <v>-37.75</v>
+        <v>-36.25</v>
       </c>
       <c r="F18" t="n">
-        <v>332</v>
+        <v>329.1</v>
       </c>
       <c r="G18" t="n">
         <v>364.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-32.75</v>
+        <v>-35.65</v>
       </c>
       <c r="I18" t="n">
-        <v>325</v>
+        <v>329.1</v>
       </c>
       <c r="J18" t="n">
         <v>328.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.4</v>
+        <v>0.7</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10.35</v>
+        <v>9.94</v>
       </c>
     </row>
   </sheetData>
@@ -29548,31 +29548,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14735</v>
+        <v>14711</v>
       </c>
       <c r="D18" t="n">
         <v>16388.96</v>
       </c>
       <c r="E18" t="n">
-        <v>-1653.96</v>
+        <v>-1677.96</v>
       </c>
       <c r="F18" t="n">
-        <v>14983</v>
+        <v>14811</v>
       </c>
       <c r="G18" t="n">
         <v>16388.96</v>
       </c>
       <c r="H18" t="n">
-        <v>-1405.96</v>
+        <v>-1577.96</v>
       </c>
       <c r="I18" t="n">
-        <v>14720</v>
+        <v>14811</v>
       </c>
       <c r="J18" t="n">
         <v>14637.6</v>
       </c>
       <c r="K18" t="n">
-        <v>82.40000000000001</v>
+        <v>173.4</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10.09</v>
+        <v>10.24</v>
       </c>
     </row>
   </sheetData>
@@ -30518,31 +30518,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1880</v>
+        <v>1901.8</v>
       </c>
       <c r="D18" t="n">
         <v>1931.58</v>
       </c>
       <c r="E18" t="n">
-        <v>-51.58</v>
+        <v>-29.78</v>
       </c>
       <c r="F18" t="n">
-        <v>1937.1</v>
+        <v>1915</v>
       </c>
       <c r="G18" t="n">
         <v>1931.58</v>
       </c>
       <c r="H18" t="n">
-        <v>5.52</v>
+        <v>-16.58</v>
       </c>
       <c r="I18" t="n">
-        <v>1878.6</v>
+        <v>1915</v>
       </c>
       <c r="J18" t="n">
         <v>1864.49</v>
       </c>
       <c r="K18" t="n">
-        <v>14.11</v>
+        <v>50.51</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.67</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -31384,31 +31384,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5590.5</v>
+        <v>5654</v>
       </c>
       <c r="D16" t="n">
         <v>5833.96</v>
       </c>
       <c r="E16" t="n">
-        <v>-243.46</v>
+        <v>-179.96</v>
       </c>
       <c r="F16" t="n">
-        <v>5705</v>
+        <v>5677</v>
       </c>
       <c r="G16" t="n">
         <v>5833.96</v>
       </c>
       <c r="H16" t="n">
-        <v>-128.96</v>
+        <v>-156.96</v>
       </c>
       <c r="I16" t="n">
-        <v>5590.5</v>
+        <v>5677</v>
       </c>
       <c r="J16" t="n">
         <v>5527.78</v>
       </c>
       <c r="K16" t="n">
-        <v>62.72</v>
+        <v>149.22</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.17</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>
@@ -32354,31 +32354,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>116.7</v>
+        <v>115.4</v>
       </c>
       <c r="D18" t="n">
         <v>112.37</v>
       </c>
       <c r="E18" t="n">
-        <v>4.33</v>
+        <v>3.03</v>
       </c>
       <c r="F18" t="n">
-        <v>118.2</v>
+        <v>114.81</v>
       </c>
       <c r="G18" t="n">
         <v>115.61</v>
       </c>
       <c r="H18" t="n">
-        <v>2.59</v>
+        <v>-0.8</v>
       </c>
       <c r="I18" t="n">
-        <v>116.39</v>
+        <v>114.81</v>
       </c>
       <c r="J18" t="n">
         <v>113.31</v>
       </c>
       <c r="K18" t="n">
-        <v>3.08</v>
+        <v>1.5</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N461"/>
+  <dimension ref="A1:N489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24426,6 +24426,1462 @@
       </c>
       <c r="N461" t="n">
         <v>10.24</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>2188</v>
+      </c>
+      <c r="D462" t="n">
+        <v>2230.87</v>
+      </c>
+      <c r="E462" t="n">
+        <v>-42.87</v>
+      </c>
+      <c r="F462" t="n">
+        <v>2235.2</v>
+      </c>
+      <c r="G462" t="n">
+        <v>2288.59</v>
+      </c>
+      <c r="H462" t="n">
+        <v>-53.39</v>
+      </c>
+      <c r="I462" t="n">
+        <v>2154.9</v>
+      </c>
+      <c r="J462" t="n">
+        <v>2265.6</v>
+      </c>
+      <c r="K462" t="n">
+        <v>-110.7</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>469.85</v>
+      </c>
+      <c r="D463" t="n">
+        <v>493.72</v>
+      </c>
+      <c r="E463" t="n">
+        <v>-23.87</v>
+      </c>
+      <c r="F463" t="n">
+        <v>472.95</v>
+      </c>
+      <c r="G463" t="n">
+        <v>493.72</v>
+      </c>
+      <c r="H463" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="I463" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="J463" t="n">
+        <v>478.18</v>
+      </c>
+      <c r="K463" t="n">
+        <v>-13.08</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1038.1</v>
+      </c>
+      <c r="D464" t="n">
+        <v>1039.02</v>
+      </c>
+      <c r="E464" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1044.35</v>
+      </c>
+      <c r="G464" t="n">
+        <v>1045.68</v>
+      </c>
+      <c r="H464" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="I464" t="n">
+        <v>1021.9</v>
+      </c>
+      <c r="J464" t="n">
+        <v>1038.3</v>
+      </c>
+      <c r="K464" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N464" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="D465" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="E465" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F465" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="G465" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I465" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="J465" t="n">
+        <v>292</v>
+      </c>
+      <c r="K465" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N465" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="D466" t="n">
+        <v>177.48</v>
+      </c>
+      <c r="E466" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F466" t="n">
+        <v>181.84</v>
+      </c>
+      <c r="G466" t="n">
+        <v>177.48</v>
+      </c>
+      <c r="H466" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I466" t="n">
+        <v>176.79</v>
+      </c>
+      <c r="J466" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="K466" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N466" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D467" t="n">
+        <v>1062.99</v>
+      </c>
+      <c r="E467" t="n">
+        <v>-38.99</v>
+      </c>
+      <c r="F467" t="n">
+        <v>1061.8</v>
+      </c>
+      <c r="G467" t="n">
+        <v>1062.99</v>
+      </c>
+      <c r="H467" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I467" t="n">
+        <v>1020.05</v>
+      </c>
+      <c r="J467" t="n">
+        <v>1037.11</v>
+      </c>
+      <c r="K467" t="n">
+        <v>-17.06</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N467" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="D468" t="n">
+        <v>193.63</v>
+      </c>
+      <c r="E468" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="F468" t="n">
+        <v>189.64</v>
+      </c>
+      <c r="G468" t="n">
+        <v>193.63</v>
+      </c>
+      <c r="H468" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="I468" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="J468" t="n">
+        <v>184.94</v>
+      </c>
+      <c r="K468" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D469" t="n">
+        <v>1255.78</v>
+      </c>
+      <c r="E469" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="F469" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G469" t="n">
+        <v>1289.76</v>
+      </c>
+      <c r="H469" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="I469" t="n">
+        <v>1252.1</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1276</v>
+      </c>
+      <c r="K469" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N469" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1529.2</v>
+      </c>
+      <c r="D470" t="n">
+        <v>1496.85</v>
+      </c>
+      <c r="E470" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F470" t="n">
+        <v>1547.5</v>
+      </c>
+      <c r="G470" t="n">
+        <v>1522.11</v>
+      </c>
+      <c r="H470" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="I470" t="n">
+        <v>1521.3</v>
+      </c>
+      <c r="J470" t="n">
+        <v>1518.29</v>
+      </c>
+      <c r="K470" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>5654</v>
+      </c>
+      <c r="D471" t="n">
+        <v>5739.31</v>
+      </c>
+      <c r="E471" t="n">
+        <v>-85.31</v>
+      </c>
+      <c r="F471" t="n">
+        <v>5679.5</v>
+      </c>
+      <c r="G471" t="n">
+        <v>5788.59</v>
+      </c>
+      <c r="H471" t="n">
+        <v>-109.09</v>
+      </c>
+      <c r="I471" t="n">
+        <v>5597</v>
+      </c>
+      <c r="J471" t="n">
+        <v>5811.81</v>
+      </c>
+      <c r="K471" t="n">
+        <v>-214.81</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>676.15</v>
+      </c>
+      <c r="D472" t="n">
+        <v>694.12</v>
+      </c>
+      <c r="E472" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="F472" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="G472" t="n">
+        <v>694.12</v>
+      </c>
+      <c r="H472" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="I472" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="J472" t="n">
+        <v>679.8</v>
+      </c>
+      <c r="K472" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>2253</v>
+      </c>
+      <c r="D473" t="n">
+        <v>2215.99</v>
+      </c>
+      <c r="E473" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="F473" t="n">
+        <v>2281</v>
+      </c>
+      <c r="G473" t="n">
+        <v>2225.77</v>
+      </c>
+      <c r="H473" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="I473" t="n">
+        <v>2247</v>
+      </c>
+      <c r="J473" t="n">
+        <v>2243.34</v>
+      </c>
+      <c r="K473" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D474" t="n">
+        <v>2013.46</v>
+      </c>
+      <c r="E474" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F474" t="n">
+        <v>2026.6</v>
+      </c>
+      <c r="G474" t="n">
+        <v>2013.46</v>
+      </c>
+      <c r="H474" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1997.5</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1997.59</v>
+      </c>
+      <c r="K474" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>3265</v>
+      </c>
+      <c r="D475" t="n">
+        <v>3549.63</v>
+      </c>
+      <c r="E475" t="n">
+        <v>-284.63</v>
+      </c>
+      <c r="F475" t="n">
+        <v>3353.78</v>
+      </c>
+      <c r="G475" t="n">
+        <v>3549.63</v>
+      </c>
+      <c r="H475" t="n">
+        <v>-195.85</v>
+      </c>
+      <c r="I475" t="n">
+        <v>3262.81</v>
+      </c>
+      <c r="J475" t="n">
+        <v>3332</v>
+      </c>
+      <c r="K475" t="n">
+        <v>-69.19</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="D476" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="E476" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="F476" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="G476" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="H476" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="I476" t="n">
+        <v>115.07</v>
+      </c>
+      <c r="J476" t="n">
+        <v>114.53</v>
+      </c>
+      <c r="K476" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>5550</v>
+      </c>
+      <c r="D477" t="n">
+        <v>5537.15</v>
+      </c>
+      <c r="E477" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F477" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G477" t="n">
+        <v>5593.05</v>
+      </c>
+      <c r="H477" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="I477" t="n">
+        <v>5511.5</v>
+      </c>
+      <c r="J477" t="n">
+        <v>5580.11</v>
+      </c>
+      <c r="K477" t="n">
+        <v>-68.61</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="D478" t="n">
+        <v>463.05</v>
+      </c>
+      <c r="E478" t="n">
+        <v>-73.75</v>
+      </c>
+      <c r="F478" t="n">
+        <v>403.35</v>
+      </c>
+      <c r="G478" t="n">
+        <v>463.05</v>
+      </c>
+      <c r="H478" t="n">
+        <v>-59.7</v>
+      </c>
+      <c r="I478" t="n">
+        <v>388</v>
+      </c>
+      <c r="J478" t="n">
+        <v>392.75</v>
+      </c>
+      <c r="K478" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N478" t="n">
+        <v>15.93</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D479" t="n">
+        <v>1314.85</v>
+      </c>
+      <c r="E479" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1345.6</v>
+      </c>
+      <c r="G479" t="n">
+        <v>1347.42</v>
+      </c>
+      <c r="H479" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="I479" t="n">
+        <v>1318</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1344.13</v>
+      </c>
+      <c r="K479" t="n">
+        <v>-26.13</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N479" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="D480" t="n">
+        <v>298.11</v>
+      </c>
+      <c r="E480" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="F480" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="G480" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="H480" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I480" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="J480" t="n">
+        <v>328</v>
+      </c>
+      <c r="K480" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>1872.9</v>
+      </c>
+      <c r="D481" t="n">
+        <v>1872.29</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F481" t="n">
+        <v>1875.3</v>
+      </c>
+      <c r="G481" t="n">
+        <v>1872.29</v>
+      </c>
+      <c r="H481" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I481" t="n">
+        <v>1844.9</v>
+      </c>
+      <c r="J481" t="n">
+        <v>1852.28</v>
+      </c>
+      <c r="K481" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N481" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>1837.9</v>
+      </c>
+      <c r="D482" t="n">
+        <v>1813.24</v>
+      </c>
+      <c r="E482" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="F482" t="n">
+        <v>1852</v>
+      </c>
+      <c r="G482" t="n">
+        <v>1827.66</v>
+      </c>
+      <c r="H482" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="I482" t="n">
+        <v>1821.1</v>
+      </c>
+      <c r="J482" t="n">
+        <v>1811.5</v>
+      </c>
+      <c r="K482" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N482" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>1585</v>
+      </c>
+      <c r="D483" t="n">
+        <v>1638.56</v>
+      </c>
+      <c r="E483" t="n">
+        <v>-53.56</v>
+      </c>
+      <c r="F483" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G483" t="n">
+        <v>1658.83</v>
+      </c>
+      <c r="H483" t="n">
+        <v>-58.83</v>
+      </c>
+      <c r="I483" t="n">
+        <v>1571.6</v>
+      </c>
+      <c r="J483" t="n">
+        <v>1640.9</v>
+      </c>
+      <c r="K483" t="n">
+        <v>-69.3</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N483" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>11399</v>
+      </c>
+      <c r="D484" t="n">
+        <v>11143.01</v>
+      </c>
+      <c r="E484" t="n">
+        <v>255.99</v>
+      </c>
+      <c r="F484" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G484" t="n">
+        <v>11236.46</v>
+      </c>
+      <c r="H484" t="n">
+        <v>283.54</v>
+      </c>
+      <c r="I484" t="n">
+        <v>11331</v>
+      </c>
+      <c r="J484" t="n">
+        <v>11236.12</v>
+      </c>
+      <c r="K484" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N484" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>4027</v>
+      </c>
+      <c r="D485" t="n">
+        <v>3917.41</v>
+      </c>
+      <c r="E485" t="n">
+        <v>109.59</v>
+      </c>
+      <c r="F485" t="n">
+        <v>4067.3</v>
+      </c>
+      <c r="G485" t="n">
+        <v>4051.09</v>
+      </c>
+      <c r="H485" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="I485" t="n">
+        <v>4023</v>
+      </c>
+      <c r="J485" t="n">
+        <v>4045.8</v>
+      </c>
+      <c r="K485" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N485" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>1204</v>
+      </c>
+      <c r="D486" t="n">
+        <v>1175.8</v>
+      </c>
+      <c r="E486" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F486" t="n">
+        <v>1207</v>
+      </c>
+      <c r="G486" t="n">
+        <v>1176.03</v>
+      </c>
+      <c r="H486" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="I486" t="n">
+        <v>1191.7</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1184.35</v>
+      </c>
+      <c r="K486" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N486" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>2588</v>
+      </c>
+      <c r="D487" t="n">
+        <v>2509.48</v>
+      </c>
+      <c r="E487" t="n">
+        <v>78.52</v>
+      </c>
+      <c r="F487" t="n">
+        <v>2634</v>
+      </c>
+      <c r="G487" t="n">
+        <v>2518.49</v>
+      </c>
+      <c r="H487" t="n">
+        <v>115.51</v>
+      </c>
+      <c r="I487" t="n">
+        <v>2583.1</v>
+      </c>
+      <c r="J487" t="n">
+        <v>2517.62</v>
+      </c>
+      <c r="K487" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N487" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>884.4</v>
+      </c>
+      <c r="D488" t="n">
+        <v>872.28</v>
+      </c>
+      <c r="E488" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="F488" t="n">
+        <v>896.15</v>
+      </c>
+      <c r="G488" t="n">
+        <v>878.21</v>
+      </c>
+      <c r="H488" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="I488" t="n">
+        <v>875.35</v>
+      </c>
+      <c r="J488" t="n">
+        <v>876.0599999999999</v>
+      </c>
+      <c r="K488" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N488" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>14711</v>
+      </c>
+      <c r="D489" t="n">
+        <v>13255.33</v>
+      </c>
+      <c r="E489" t="n">
+        <v>1455.67</v>
+      </c>
+      <c r="F489" t="n">
+        <v>14849</v>
+      </c>
+      <c r="G489" t="n">
+        <v>14683.34</v>
+      </c>
+      <c r="H489" t="n">
+        <v>165.66</v>
+      </c>
+      <c r="I489" t="n">
+        <v>14684</v>
+      </c>
+      <c r="J489" t="n">
+        <v>14650</v>
+      </c>
+      <c r="K489" t="n">
+        <v>34</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N489" t="n">
+        <v>10.98</v>
       </c>
     </row>
   </sheetData>
@@ -24681,7 +26137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25586,6 +27042,58 @@
       </c>
       <c r="N17" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1204</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1175.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1207</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1176.03</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1191.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1184.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -27001,7 +28509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27646,6 +29154,58 @@
       </c>
       <c r="N12" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1585</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1638.56</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-53.56</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1658.83</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-58.83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1571.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1640.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-69.3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>3.27</v>
       </c>
     </row>
   </sheetData>
@@ -27659,7 +29219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28616,6 +30176,58 @@
       </c>
       <c r="N18" t="n">
         <v>9.94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>298.11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="F19" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I19" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>328</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10.19</v>
       </c>
     </row>
   </sheetData>
@@ -28629,7 +30241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29586,6 +31198,58 @@
       </c>
       <c r="N18" t="n">
         <v>10.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14711</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13255.33</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1455.67</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14849</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14683.34</v>
+      </c>
+      <c r="H19" t="n">
+        <v>165.66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14684</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14650</v>
+      </c>
+      <c r="K19" t="n">
+        <v>34</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10.98</v>
       </c>
     </row>
   </sheetData>
@@ -30569,7 +32233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31422,6 +33086,58 @@
       </c>
       <c r="N16" t="n">
         <v>3.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5654</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5739.31</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5679.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5788.59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-109.09</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5597</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5811.81</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-214.81</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
@@ -31435,7 +33151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32392,6 +34108,58 @@
       </c>
       <c r="N18" t="n">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="F19" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>115.07</v>
+      </c>
+      <c r="J19" t="n">
+        <v>114.53</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -24436,48 +24436,48 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2188</v>
+        <v>469.85</v>
       </c>
       <c r="D462" t="n">
-        <v>2230.87</v>
+        <v>493.72</v>
       </c>
       <c r="E462" t="n">
-        <v>-42.87</v>
+        <v>-23.87</v>
       </c>
       <c r="F462" t="n">
-        <v>2235.2</v>
+        <v>472.95</v>
       </c>
       <c r="G462" t="n">
-        <v>2288.59</v>
+        <v>493.72</v>
       </c>
       <c r="H462" t="n">
-        <v>-53.39</v>
+        <v>-20.77</v>
       </c>
       <c r="I462" t="n">
-        <v>2154.9</v>
+        <v>465.1</v>
       </c>
       <c r="J462" t="n">
-        <v>2265.6</v>
+        <v>478.18</v>
       </c>
       <c r="K462" t="n">
-        <v>-110.7</v>
+        <v>-13.08</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N462" t="n">
-        <v>1.92</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="463">
@@ -24488,35 +24488,35 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>469.85</v>
+        <v>290.95</v>
       </c>
       <c r="D463" t="n">
-        <v>493.72</v>
+        <v>292.5</v>
       </c>
       <c r="E463" t="n">
-        <v>-23.87</v>
+        <v>-1.55</v>
       </c>
       <c r="F463" t="n">
-        <v>472.95</v>
+        <v>293.35</v>
       </c>
       <c r="G463" t="n">
-        <v>493.72</v>
+        <v>292.74</v>
       </c>
       <c r="H463" t="n">
-        <v>-20.77</v>
+        <v>0.61</v>
       </c>
       <c r="I463" t="n">
-        <v>465.1</v>
+        <v>289.6</v>
       </c>
       <c r="J463" t="n">
-        <v>478.18</v>
+        <v>292</v>
       </c>
       <c r="K463" t="n">
-        <v>-13.08</v>
+        <v>-2.4</v>
       </c>
       <c r="L463" t="inlineStr">
         <is>
@@ -24525,11 +24525,11 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N463" t="n">
-        <v>4.83</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="464">
@@ -24540,35 +24540,35 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>1038.1</v>
+        <v>1280</v>
       </c>
       <c r="D464" t="n">
-        <v>1039.02</v>
+        <v>1255.78</v>
       </c>
       <c r="E464" t="n">
-        <v>-0.92</v>
+        <v>24.22</v>
       </c>
       <c r="F464" t="n">
-        <v>1044.35</v>
+        <v>1285</v>
       </c>
       <c r="G464" t="n">
-        <v>1045.68</v>
+        <v>1289.76</v>
       </c>
       <c r="H464" t="n">
-        <v>-1.33</v>
+        <v>-4.76</v>
       </c>
       <c r="I464" t="n">
-        <v>1021.9</v>
+        <v>1252.1</v>
       </c>
       <c r="J464" t="n">
-        <v>1038.3</v>
+        <v>1276</v>
       </c>
       <c r="K464" t="n">
-        <v>-16.4</v>
+        <v>-23.9</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         </is>
       </c>
       <c r="N464" t="n">
-        <v>0.09</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="465">
@@ -24592,35 +24592,35 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>290.95</v>
+        <v>389.3</v>
       </c>
       <c r="D465" t="n">
-        <v>292.5</v>
+        <v>463.05</v>
       </c>
       <c r="E465" t="n">
-        <v>-1.55</v>
+        <v>-73.75</v>
       </c>
       <c r="F465" t="n">
-        <v>293.35</v>
+        <v>403.35</v>
       </c>
       <c r="G465" t="n">
-        <v>292.74</v>
+        <v>463.05</v>
       </c>
       <c r="H465" t="n">
-        <v>0.61</v>
+        <v>-59.7</v>
       </c>
       <c r="I465" t="n">
-        <v>289.6</v>
+        <v>388</v>
       </c>
       <c r="J465" t="n">
-        <v>292</v>
+        <v>392.75</v>
       </c>
       <c r="K465" t="n">
-        <v>-2.4</v>
+        <v>-4.75</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N465" t="n">
-        <v>0.53</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="466">
@@ -24644,39 +24644,39 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>177.4</v>
+        <v>1872.9</v>
       </c>
       <c r="D466" t="n">
-        <v>177.48</v>
+        <v>1872.29</v>
       </c>
       <c r="E466" t="n">
-        <v>-0.08</v>
+        <v>0.61</v>
       </c>
       <c r="F466" t="n">
-        <v>181.84</v>
+        <v>1875.3</v>
       </c>
       <c r="G466" t="n">
-        <v>177.48</v>
+        <v>1872.29</v>
       </c>
       <c r="H466" t="n">
-        <v>4.36</v>
+        <v>3.01</v>
       </c>
       <c r="I466" t="n">
-        <v>176.79</v>
+        <v>1844.9</v>
       </c>
       <c r="J466" t="n">
-        <v>175.77</v>
+        <v>1852.28</v>
       </c>
       <c r="K466" t="n">
-        <v>1.02</v>
+        <v>-7.38</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -24685,7 +24685,7 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="467">
@@ -24696,48 +24696,48 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>1024</v>
+        <v>11399</v>
       </c>
       <c r="D467" t="n">
-        <v>1062.99</v>
+        <v>11143.01</v>
       </c>
       <c r="E467" t="n">
-        <v>-38.99</v>
+        <v>255.99</v>
       </c>
       <c r="F467" t="n">
-        <v>1061.8</v>
+        <v>11520</v>
       </c>
       <c r="G467" t="n">
-        <v>1062.99</v>
+        <v>11236.46</v>
       </c>
       <c r="H467" t="n">
-        <v>-1.19</v>
+        <v>283.54</v>
       </c>
       <c r="I467" t="n">
-        <v>1020.05</v>
+        <v>11331</v>
       </c>
       <c r="J467" t="n">
-        <v>1037.11</v>
+        <v>11236.12</v>
       </c>
       <c r="K467" t="n">
-        <v>-17.06</v>
+        <v>94.88</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N467" t="n">
-        <v>3.67</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="468">
@@ -24748,39 +24748,39 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>184.5</v>
+        <v>1204</v>
       </c>
       <c r="D468" t="n">
-        <v>193.63</v>
+        <v>1175.8</v>
       </c>
       <c r="E468" t="n">
-        <v>-9.130000000000001</v>
+        <v>28.2</v>
       </c>
       <c r="F468" t="n">
-        <v>189.64</v>
+        <v>1207</v>
       </c>
       <c r="G468" t="n">
-        <v>193.63</v>
+        <v>1176.03</v>
       </c>
       <c r="H468" t="n">
-        <v>-3.99</v>
+        <v>30.97</v>
       </c>
       <c r="I468" t="n">
-        <v>184.08</v>
+        <v>1191.7</v>
       </c>
       <c r="J468" t="n">
-        <v>184.94</v>
+        <v>1184.35</v>
       </c>
       <c r="K468" t="n">
-        <v>-0.86</v>
+        <v>7.35</v>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -24789,7 +24789,7 @@
         </is>
       </c>
       <c r="N468" t="n">
-        <v>4.72</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="469">
@@ -24800,39 +24800,39 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>1280</v>
+        <v>2265.6</v>
       </c>
       <c r="D469" t="n">
-        <v>1255.78</v>
+        <v>2240.12</v>
       </c>
       <c r="E469" t="n">
-        <v>24.22</v>
+        <v>25.48</v>
       </c>
       <c r="F469" t="n">
-        <v>1285</v>
+        <v>2278.4</v>
       </c>
       <c r="G469" t="n">
-        <v>1289.76</v>
+        <v>2321.72</v>
       </c>
       <c r="H469" t="n">
-        <v>-4.76</v>
+        <v>-43.32</v>
       </c>
       <c r="I469" t="n">
-        <v>1252.1</v>
+        <v>2182.5</v>
       </c>
       <c r="J469" t="n">
-        <v>1276</v>
+        <v>2222.39</v>
       </c>
       <c r="K469" t="n">
-        <v>-23.9</v>
+        <v>-39.89</v>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>1.93</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="470">
@@ -24852,35 +24852,35 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>1529.2</v>
+        <v>1038.3</v>
       </c>
       <c r="D470" t="n">
-        <v>1496.85</v>
+        <v>1045.68</v>
       </c>
       <c r="E470" t="n">
-        <v>32.35</v>
+        <v>-7.38</v>
       </c>
       <c r="F470" t="n">
-        <v>1547.5</v>
+        <v>1053</v>
       </c>
       <c r="G470" t="n">
-        <v>1522.11</v>
+        <v>1060.83</v>
       </c>
       <c r="H470" t="n">
-        <v>25.39</v>
+        <v>-7.83</v>
       </c>
       <c r="I470" t="n">
-        <v>1521.3</v>
+        <v>1027.15</v>
       </c>
       <c r="J470" t="n">
-        <v>1518.29</v>
+        <v>1015.34</v>
       </c>
       <c r="K470" t="n">
-        <v>3.01</v>
+        <v>11.81</v>
       </c>
       <c r="L470" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         </is>
       </c>
       <c r="N470" t="n">
-        <v>2.16</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="471">
@@ -24908,31 +24908,31 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>5654</v>
+        <v>5875</v>
       </c>
       <c r="D471" t="n">
-        <v>5739.31</v>
+        <v>5834</v>
       </c>
       <c r="E471" t="n">
-        <v>-85.31</v>
+        <v>41</v>
       </c>
       <c r="F471" t="n">
-        <v>5679.5</v>
+        <v>5910</v>
       </c>
       <c r="G471" t="n">
-        <v>5788.59</v>
+        <v>5872.58</v>
       </c>
       <c r="H471" t="n">
-        <v>-109.09</v>
+        <v>37.42</v>
       </c>
       <c r="I471" t="n">
-        <v>5597</v>
+        <v>5677</v>
       </c>
       <c r="J471" t="n">
-        <v>5811.81</v>
+        <v>5654.55</v>
       </c>
       <c r="K471" t="n">
-        <v>-214.81</v>
+        <v>22.45</v>
       </c>
       <c r="L471" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>1.49</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="472">
@@ -24956,35 +24956,35 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>676.15</v>
+        <v>175.77</v>
       </c>
       <c r="D472" t="n">
-        <v>694.12</v>
+        <v>177.1</v>
       </c>
       <c r="E472" t="n">
-        <v>-17.97</v>
+        <v>-1.33</v>
       </c>
       <c r="F472" t="n">
-        <v>687.5</v>
+        <v>178.18</v>
       </c>
       <c r="G472" t="n">
-        <v>694.12</v>
+        <v>179.6</v>
       </c>
       <c r="H472" t="n">
-        <v>-6.62</v>
+        <v>-1.42</v>
       </c>
       <c r="I472" t="n">
-        <v>673.55</v>
+        <v>174.81</v>
       </c>
       <c r="J472" t="n">
-        <v>679.8</v>
+        <v>171.89</v>
       </c>
       <c r="K472" t="n">
-        <v>-6.25</v>
+        <v>2.92</v>
       </c>
       <c r="L472" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         </is>
       </c>
       <c r="N472" t="n">
-        <v>2.59</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="473">
@@ -25008,35 +25008,35 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2253</v>
+        <v>5600</v>
       </c>
       <c r="D473" t="n">
-        <v>2215.99</v>
+        <v>5657.9</v>
       </c>
       <c r="E473" t="n">
-        <v>37.01</v>
+        <v>-57.9</v>
       </c>
       <c r="F473" t="n">
-        <v>2281</v>
+        <v>5654</v>
       </c>
       <c r="G473" t="n">
-        <v>2225.77</v>
+        <v>5674.07</v>
       </c>
       <c r="H473" t="n">
-        <v>55.23</v>
+        <v>-20.07</v>
       </c>
       <c r="I473" t="n">
-        <v>2247</v>
+        <v>5529</v>
       </c>
       <c r="J473" t="n">
-        <v>2243.34</v>
+        <v>5429.14</v>
       </c>
       <c r="K473" t="n">
-        <v>3.66</v>
+        <v>99.86</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         </is>
       </c>
       <c r="N473" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="474">
@@ -25060,35 +25060,35 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>2011</v>
+        <v>679.8</v>
       </c>
       <c r="D474" t="n">
-        <v>2013.46</v>
+        <v>667.5</v>
       </c>
       <c r="E474" t="n">
-        <v>-2.46</v>
+        <v>12.3</v>
       </c>
       <c r="F474" t="n">
-        <v>2026.6</v>
+        <v>682.95</v>
       </c>
       <c r="G474" t="n">
-        <v>2013.46</v>
+        <v>696.45</v>
       </c>
       <c r="H474" t="n">
-        <v>13.14</v>
+        <v>-13.5</v>
       </c>
       <c r="I474" t="n">
-        <v>1997.5</v>
+        <v>672.5</v>
       </c>
       <c r="J474" t="n">
-        <v>1997.59</v>
+        <v>666.64</v>
       </c>
       <c r="K474" t="n">
-        <v>-0.09</v>
+        <v>5.86</v>
       </c>
       <c r="L474" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         </is>
       </c>
       <c r="N474" t="n">
-        <v>0.12</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="475">
@@ -25112,35 +25112,35 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3265</v>
+        <v>1532.3</v>
       </c>
       <c r="D475" t="n">
-        <v>3549.63</v>
+        <v>1577.94</v>
       </c>
       <c r="E475" t="n">
-        <v>-284.63</v>
+        <v>-45.64</v>
       </c>
       <c r="F475" t="n">
-        <v>3353.78</v>
+        <v>1556.4</v>
       </c>
       <c r="G475" t="n">
-        <v>3549.63</v>
+        <v>1577.94</v>
       </c>
       <c r="H475" t="n">
-        <v>-195.85</v>
+        <v>-21.54</v>
       </c>
       <c r="I475" t="n">
-        <v>3262.81</v>
+        <v>1529.5</v>
       </c>
       <c r="J475" t="n">
-        <v>3332</v>
+        <v>1477.21</v>
       </c>
       <c r="K475" t="n">
-        <v>-69.19</v>
+        <v>52.29</v>
       </c>
       <c r="L475" t="inlineStr">
         <is>
@@ -25149,11 +25149,11 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N475" t="n">
-        <v>8.02</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="476">
@@ -25164,35 +25164,35 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>115.4</v>
+        <v>2002</v>
       </c>
       <c r="D476" t="n">
-        <v>119.46</v>
+        <v>2015.56</v>
       </c>
       <c r="E476" t="n">
-        <v>-4.06</v>
+        <v>-13.56</v>
       </c>
       <c r="F476" t="n">
-        <v>117.2</v>
+        <v>2014.7</v>
       </c>
       <c r="G476" t="n">
-        <v>119.46</v>
+        <v>2015.56</v>
       </c>
       <c r="H476" t="n">
-        <v>-2.26</v>
+        <v>-0.86</v>
       </c>
       <c r="I476" t="n">
-        <v>115.07</v>
+        <v>1982.3</v>
       </c>
       <c r="J476" t="n">
-        <v>114.53</v>
+        <v>1943.54</v>
       </c>
       <c r="K476" t="n">
-        <v>0.54</v>
+        <v>38.76</v>
       </c>
       <c r="L476" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="N476" t="n">
-        <v>3.4</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="477">
@@ -25216,35 +25216,35 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>5550</v>
+        <v>2267</v>
       </c>
       <c r="D477" t="n">
-        <v>5537.15</v>
+        <v>2323.3</v>
       </c>
       <c r="E477" t="n">
-        <v>12.85</v>
+        <v>-56.3</v>
       </c>
       <c r="F477" t="n">
-        <v>5610</v>
+        <v>2279</v>
       </c>
       <c r="G477" t="n">
-        <v>5593.05</v>
+        <v>2323.3</v>
       </c>
       <c r="H477" t="n">
-        <v>16.95</v>
+        <v>-44.3</v>
       </c>
       <c r="I477" t="n">
-        <v>5511.5</v>
+        <v>2240.3</v>
       </c>
       <c r="J477" t="n">
-        <v>5580.11</v>
+        <v>2182.64</v>
       </c>
       <c r="K477" t="n">
-        <v>-68.61</v>
+        <v>57.66</v>
       </c>
       <c r="L477" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="N477" t="n">
-        <v>0.23</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="478">
@@ -25268,35 +25268,35 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>389.3</v>
+        <v>3332</v>
       </c>
       <c r="D478" t="n">
-        <v>463.05</v>
+        <v>3089.33</v>
       </c>
       <c r="E478" t="n">
-        <v>-73.75</v>
+        <v>242.67</v>
       </c>
       <c r="F478" t="n">
-        <v>403.35</v>
+        <v>3339</v>
       </c>
       <c r="G478" t="n">
-        <v>463.05</v>
+        <v>3410.7</v>
       </c>
       <c r="H478" t="n">
-        <v>-59.7</v>
+        <v>-71.7</v>
       </c>
       <c r="I478" t="n">
-        <v>388</v>
+        <v>3245</v>
       </c>
       <c r="J478" t="n">
-        <v>392.75</v>
+        <v>3264.65</v>
       </c>
       <c r="K478" t="n">
-        <v>-4.75</v>
+        <v>-19.65</v>
       </c>
       <c r="L478" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         </is>
       </c>
       <c r="N478" t="n">
-        <v>15.93</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="479">
@@ -25324,31 +25324,31 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>1330</v>
+        <v>1354</v>
       </c>
       <c r="D479" t="n">
-        <v>1314.85</v>
+        <v>1380.55</v>
       </c>
       <c r="E479" t="n">
-        <v>15.15</v>
+        <v>-26.55</v>
       </c>
       <c r="F479" t="n">
-        <v>1345.6</v>
+        <v>1369.4</v>
       </c>
       <c r="G479" t="n">
-        <v>1347.42</v>
+        <v>1380.55</v>
       </c>
       <c r="H479" t="n">
-        <v>-1.82</v>
+        <v>-11.15</v>
       </c>
       <c r="I479" t="n">
-        <v>1318</v>
+        <v>1339</v>
       </c>
       <c r="J479" t="n">
-        <v>1344.13</v>
+        <v>1307.79</v>
       </c>
       <c r="K479" t="n">
-        <v>-26.13</v>
+        <v>31.21</v>
       </c>
       <c r="L479" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1.15</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="480">
@@ -25372,35 +25372,35 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>328.5</v>
+        <v>186</v>
       </c>
       <c r="D480" t="n">
-        <v>298.11</v>
+        <v>178.65</v>
       </c>
       <c r="E480" t="n">
-        <v>30.39</v>
+        <v>7.35</v>
       </c>
       <c r="F480" t="n">
-        <v>330.9</v>
+        <v>186.31</v>
       </c>
       <c r="G480" t="n">
-        <v>331.66</v>
+        <v>188.06</v>
       </c>
       <c r="H480" t="n">
-        <v>-0.76</v>
+        <v>-1.75</v>
       </c>
       <c r="I480" t="n">
-        <v>325.3</v>
+        <v>184.09</v>
       </c>
       <c r="J480" t="n">
-        <v>328</v>
+        <v>179.93</v>
       </c>
       <c r="K480" t="n">
-        <v>-2.7</v>
+        <v>4.16</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         </is>
       </c>
       <c r="N480" t="n">
-        <v>10.19</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="481">
@@ -25424,39 +25424,39 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>1872.9</v>
+        <v>115.4</v>
       </c>
       <c r="D481" t="n">
-        <v>1872.29</v>
+        <v>112.37</v>
       </c>
       <c r="E481" t="n">
-        <v>0.61</v>
+        <v>3.03</v>
       </c>
       <c r="F481" t="n">
-        <v>1875.3</v>
+        <v>115.75</v>
       </c>
       <c r="G481" t="n">
-        <v>1872.29</v>
+        <v>116.48</v>
       </c>
       <c r="H481" t="n">
-        <v>3.01</v>
+        <v>-0.73</v>
       </c>
       <c r="I481" t="n">
-        <v>1844.9</v>
+        <v>114.42</v>
       </c>
       <c r="J481" t="n">
-        <v>1852.28</v>
+        <v>111.43</v>
       </c>
       <c r="K481" t="n">
-        <v>-7.38</v>
+        <v>2.99</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="N481" t="n">
-        <v>0.03</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="482">
@@ -25476,39 +25476,39 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>1837.9</v>
+        <v>1037.4</v>
       </c>
       <c r="D482" t="n">
-        <v>1813.24</v>
+        <v>1007.34</v>
       </c>
       <c r="E482" t="n">
-        <v>24.66</v>
+        <v>30.06</v>
       </c>
       <c r="F482" t="n">
-        <v>1852</v>
+        <v>1037.4</v>
       </c>
       <c r="G482" t="n">
-        <v>1827.66</v>
+        <v>1054.45</v>
       </c>
       <c r="H482" t="n">
-        <v>24.34</v>
+        <v>-17.05</v>
       </c>
       <c r="I482" t="n">
-        <v>1821.1</v>
+        <v>1025.95</v>
       </c>
       <c r="J482" t="n">
-        <v>1811.5</v>
+        <v>1009.04</v>
       </c>
       <c r="K482" t="n">
-        <v>9.6</v>
+        <v>16.91</v>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -25517,7 +25517,7 @@
         </is>
       </c>
       <c r="N482" t="n">
-        <v>1.36</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="483">
@@ -25528,48 +25528,48 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>1585</v>
+        <v>4045.8</v>
       </c>
       <c r="D483" t="n">
-        <v>1638.56</v>
+        <v>4192.28</v>
       </c>
       <c r="E483" t="n">
-        <v>-53.56</v>
+        <v>-146.48</v>
       </c>
       <c r="F483" t="n">
-        <v>1600</v>
+        <v>4060</v>
       </c>
       <c r="G483" t="n">
-        <v>1658.83</v>
+        <v>4192.28</v>
       </c>
       <c r="H483" t="n">
-        <v>-58.83</v>
+        <v>-132.28</v>
       </c>
       <c r="I483" t="n">
-        <v>1571.6</v>
+        <v>4021.3</v>
       </c>
       <c r="J483" t="n">
-        <v>1640.9</v>
+        <v>3937.28</v>
       </c>
       <c r="K483" t="n">
-        <v>-69.3</v>
+        <v>84.02</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N483" t="n">
-        <v>3.27</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="484">
@@ -25580,39 +25580,39 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>11399</v>
+        <v>328</v>
       </c>
       <c r="D484" t="n">
-        <v>11143.01</v>
+        <v>364.75</v>
       </c>
       <c r="E484" t="n">
-        <v>255.99</v>
+        <v>-36.75</v>
       </c>
       <c r="F484" t="n">
-        <v>11520</v>
+        <v>330</v>
       </c>
       <c r="G484" t="n">
-        <v>11236.46</v>
+        <v>364.75</v>
       </c>
       <c r="H484" t="n">
-        <v>283.54</v>
+        <v>-34.75</v>
       </c>
       <c r="I484" t="n">
-        <v>11331</v>
+        <v>324.3</v>
       </c>
       <c r="J484" t="n">
-        <v>11236.12</v>
+        <v>322.08</v>
       </c>
       <c r="K484" t="n">
-        <v>94.88</v>
+        <v>2.22</v>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -25621,7 +25621,7 @@
         </is>
       </c>
       <c r="N484" t="n">
-        <v>2.3</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="485">
@@ -25632,35 +25632,35 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>4027</v>
+        <v>1640.9</v>
       </c>
       <c r="D485" t="n">
-        <v>3917.41</v>
+        <v>1614.25</v>
       </c>
       <c r="E485" t="n">
-        <v>109.59</v>
+        <v>26.65</v>
       </c>
       <c r="F485" t="n">
-        <v>4067.3</v>
+        <v>1642</v>
       </c>
       <c r="G485" t="n">
-        <v>4051.09</v>
+        <v>1682.86</v>
       </c>
       <c r="H485" t="n">
-        <v>16.21</v>
+        <v>-40.86</v>
       </c>
       <c r="I485" t="n">
-        <v>4023</v>
+        <v>1598</v>
       </c>
       <c r="J485" t="n">
-        <v>4045.8</v>
+        <v>1623.97</v>
       </c>
       <c r="K485" t="n">
-        <v>-22.8</v>
+        <v>-25.97</v>
       </c>
       <c r="L485" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="486">
@@ -25684,35 +25684,35 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>1204</v>
+        <v>1811.5</v>
       </c>
       <c r="D486" t="n">
-        <v>1175.8</v>
+        <v>1850.82</v>
       </c>
       <c r="E486" t="n">
-        <v>28.2</v>
+        <v>-39.32</v>
       </c>
       <c r="F486" t="n">
-        <v>1207</v>
+        <v>1844.8</v>
       </c>
       <c r="G486" t="n">
-        <v>1176.03</v>
+        <v>1854.13</v>
       </c>
       <c r="H486" t="n">
-        <v>30.97</v>
+        <v>-9.33</v>
       </c>
       <c r="I486" t="n">
-        <v>1191.7</v>
+        <v>1804.8</v>
       </c>
       <c r="J486" t="n">
-        <v>1184.35</v>
+        <v>1774.73</v>
       </c>
       <c r="K486" t="n">
-        <v>7.35</v>
+        <v>30.07</v>
       </c>
       <c r="L486" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         </is>
       </c>
       <c r="N486" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="487">
@@ -25736,35 +25736,35 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>2588</v>
+        <v>882.4</v>
       </c>
       <c r="D487" t="n">
-        <v>2509.48</v>
+        <v>901.8099999999999</v>
       </c>
       <c r="E487" t="n">
-        <v>78.52</v>
+        <v>-19.41</v>
       </c>
       <c r="F487" t="n">
-        <v>2634</v>
+        <v>883.95</v>
       </c>
       <c r="G487" t="n">
-        <v>2518.49</v>
+        <v>901.8099999999999</v>
       </c>
       <c r="H487" t="n">
-        <v>115.51</v>
+        <v>-17.86</v>
       </c>
       <c r="I487" t="n">
-        <v>2583.1</v>
+        <v>872.45</v>
       </c>
       <c r="J487" t="n">
-        <v>2517.62</v>
+        <v>852.34</v>
       </c>
       <c r="K487" t="n">
-        <v>65.48</v>
+        <v>20.11</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -25773,11 +25773,11 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N487" t="n">
-        <v>3.13</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="488">
@@ -25788,35 +25788,35 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>884.4</v>
+        <v>2555</v>
       </c>
       <c r="D488" t="n">
-        <v>872.28</v>
+        <v>2656.03</v>
       </c>
       <c r="E488" t="n">
-        <v>12.12</v>
+        <v>-101.03</v>
       </c>
       <c r="F488" t="n">
-        <v>896.15</v>
+        <v>2596</v>
       </c>
       <c r="G488" t="n">
-        <v>878.21</v>
+        <v>2656.03</v>
       </c>
       <c r="H488" t="n">
-        <v>17.94</v>
+        <v>-60.03</v>
       </c>
       <c r="I488" t="n">
-        <v>875.35</v>
+        <v>2543</v>
       </c>
       <c r="J488" t="n">
-        <v>876.0599999999999</v>
+        <v>2449.49</v>
       </c>
       <c r="K488" t="n">
-        <v>-0.71</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>1.39</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="489">
@@ -25844,31 +25844,31 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>14711</v>
+        <v>14650</v>
       </c>
       <c r="D489" t="n">
-        <v>13255.33</v>
+        <v>16388.93</v>
       </c>
       <c r="E489" t="n">
-        <v>1455.67</v>
+        <v>-1738.93</v>
       </c>
       <c r="F489" t="n">
-        <v>14849</v>
+        <v>14920</v>
       </c>
       <c r="G489" t="n">
-        <v>14683.34</v>
+        <v>16388.93</v>
       </c>
       <c r="H489" t="n">
-        <v>165.66</v>
+        <v>-1468.93</v>
       </c>
       <c r="I489" t="n">
-        <v>14684</v>
+        <v>14650</v>
       </c>
       <c r="J489" t="n">
-        <v>14650</v>
+        <v>14254.76</v>
       </c>
       <c r="K489" t="n">
-        <v>34</v>
+        <v>395.24</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>10.98</v>
+        <v>10.61</v>
       </c>
     </row>
   </sheetData>
@@ -29168,31 +29168,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1585</v>
+        <v>1640.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1638.56</v>
+        <v>1614.25</v>
       </c>
       <c r="E13" t="n">
-        <v>-53.56</v>
+        <v>26.65</v>
       </c>
       <c r="F13" t="n">
-        <v>1600</v>
+        <v>1642</v>
       </c>
       <c r="G13" t="n">
-        <v>1658.83</v>
+        <v>1682.86</v>
       </c>
       <c r="H13" t="n">
-        <v>-58.83</v>
+        <v>-40.86</v>
       </c>
       <c r="I13" t="n">
-        <v>1571.6</v>
+        <v>1598</v>
       </c>
       <c r="J13" t="n">
-        <v>1640.9</v>
+        <v>1623.97</v>
       </c>
       <c r="K13" t="n">
-        <v>-69.3</v>
+        <v>-25.97</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -29201,11 +29201,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.27</v>
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -30190,31 +30190,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>328.5</v>
+        <v>328</v>
       </c>
       <c r="D19" t="n">
-        <v>298.11</v>
+        <v>364.75</v>
       </c>
       <c r="E19" t="n">
-        <v>30.39</v>
+        <v>-36.75</v>
       </c>
       <c r="F19" t="n">
-        <v>330.9</v>
+        <v>330</v>
       </c>
       <c r="G19" t="n">
-        <v>331.66</v>
+        <v>364.75</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.76</v>
+        <v>-34.75</v>
       </c>
       <c r="I19" t="n">
-        <v>325.3</v>
+        <v>324.3</v>
       </c>
       <c r="J19" t="n">
-        <v>328</v>
+        <v>322.08</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.7</v>
+        <v>2.22</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10.19</v>
+        <v>10.08</v>
       </c>
     </row>
   </sheetData>
@@ -31212,31 +31212,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14711</v>
+        <v>14650</v>
       </c>
       <c r="D19" t="n">
-        <v>13255.33</v>
+        <v>16388.93</v>
       </c>
       <c r="E19" t="n">
-        <v>1455.67</v>
+        <v>-1738.93</v>
       </c>
       <c r="F19" t="n">
-        <v>14849</v>
+        <v>14920</v>
       </c>
       <c r="G19" t="n">
-        <v>14683.34</v>
+        <v>16388.93</v>
       </c>
       <c r="H19" t="n">
-        <v>165.66</v>
+        <v>-1468.93</v>
       </c>
       <c r="I19" t="n">
-        <v>14684</v>
+        <v>14650</v>
       </c>
       <c r="J19" t="n">
-        <v>14650</v>
+        <v>14254.76</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>395.24</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10.98</v>
+        <v>10.61</v>
       </c>
     </row>
   </sheetData>
@@ -33100,31 +33100,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5654</v>
+        <v>5875</v>
       </c>
       <c r="D17" t="n">
-        <v>5739.31</v>
+        <v>5834</v>
       </c>
       <c r="E17" t="n">
-        <v>-85.31</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>5679.5</v>
+        <v>5910</v>
       </c>
       <c r="G17" t="n">
-        <v>5788.59</v>
+        <v>5872.58</v>
       </c>
       <c r="H17" t="n">
-        <v>-109.09</v>
+        <v>37.42</v>
       </c>
       <c r="I17" t="n">
-        <v>5597</v>
+        <v>5677</v>
       </c>
       <c r="J17" t="n">
-        <v>5811.81</v>
+        <v>5654.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-214.81</v>
+        <v>22.45</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -34125,28 +34125,28 @@
         <v>115.4</v>
       </c>
       <c r="D19" t="n">
-        <v>119.46</v>
+        <v>112.37</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.06</v>
+        <v>3.03</v>
       </c>
       <c r="F19" t="n">
-        <v>117.2</v>
+        <v>115.75</v>
       </c>
       <c r="G19" t="n">
-        <v>119.46</v>
+        <v>116.48</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.26</v>
+        <v>-0.73</v>
       </c>
       <c r="I19" t="n">
-        <v>115.07</v>
+        <v>114.42</v>
       </c>
       <c r="J19" t="n">
-        <v>114.53</v>
+        <v>111.43</v>
       </c>
       <c r="K19" t="n">
-        <v>0.54</v>
+        <v>2.99</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N489"/>
+  <dimension ref="A1:N517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25882,6 +25882,1462 @@
       </c>
       <c r="N489" t="n">
         <v>10.61</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D490" t="n">
+        <v>2023.46</v>
+      </c>
+      <c r="E490" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F490" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G490" t="n">
+        <v>2023.46</v>
+      </c>
+      <c r="H490" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="I490" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J490" t="n">
+        <v>2011.83</v>
+      </c>
+      <c r="K490" t="n">
+        <v>-43.83</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N490" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D491" t="n">
+        <v>1046.49</v>
+      </c>
+      <c r="E491" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="F491" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G491" t="n">
+        <v>1053.64</v>
+      </c>
+      <c r="H491" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1034.5</v>
+      </c>
+      <c r="J491" t="n">
+        <v>1055.67</v>
+      </c>
+      <c r="K491" t="n">
+        <v>-21.17</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N491" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>691.05</v>
+      </c>
+      <c r="D492" t="n">
+        <v>709.42</v>
+      </c>
+      <c r="E492" t="n">
+        <v>-18.37</v>
+      </c>
+      <c r="F492" t="n">
+        <v>691.05</v>
+      </c>
+      <c r="G492" t="n">
+        <v>709.42</v>
+      </c>
+      <c r="H492" t="n">
+        <v>-18.37</v>
+      </c>
+      <c r="I492" t="n">
+        <v>664</v>
+      </c>
+      <c r="J492" t="n">
+        <v>691.05</v>
+      </c>
+      <c r="K492" t="n">
+        <v>-27.05</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N492" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>1042.9</v>
+      </c>
+      <c r="D493" t="n">
+        <v>1043.82</v>
+      </c>
+      <c r="E493" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1045.35</v>
+      </c>
+      <c r="G493" t="n">
+        <v>1043.82</v>
+      </c>
+      <c r="H493" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I493" t="n">
+        <v>1022</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1036.9</v>
+      </c>
+      <c r="K493" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N493" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>483.15</v>
+      </c>
+      <c r="D494" t="n">
+        <v>477</v>
+      </c>
+      <c r="E494" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="F494" t="n">
+        <v>500</v>
+      </c>
+      <c r="G494" t="n">
+        <v>479.48</v>
+      </c>
+      <c r="H494" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="I494" t="n">
+        <v>479.25</v>
+      </c>
+      <c r="J494" t="n">
+        <v>476.89</v>
+      </c>
+      <c r="K494" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N494" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>1875</v>
+      </c>
+      <c r="D495" t="n">
+        <v>1849.86</v>
+      </c>
+      <c r="E495" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="F495" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G495" t="n">
+        <v>1889.29</v>
+      </c>
+      <c r="H495" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1796.4</v>
+      </c>
+      <c r="J495" t="n">
+        <v>1875</v>
+      </c>
+      <c r="K495" t="n">
+        <v>-78.59999999999999</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N495" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>1276</v>
+      </c>
+      <c r="D496" t="n">
+        <v>1260.91</v>
+      </c>
+      <c r="E496" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1292.5</v>
+      </c>
+      <c r="G496" t="n">
+        <v>1289.75</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I496" t="n">
+        <v>1261.1</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1276</v>
+      </c>
+      <c r="K496" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N496" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>188.63</v>
+      </c>
+      <c r="D497" t="n">
+        <v>197.96</v>
+      </c>
+      <c r="E497" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="F497" t="n">
+        <v>188.63</v>
+      </c>
+      <c r="G497" t="n">
+        <v>197.96</v>
+      </c>
+      <c r="H497" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="I497" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="J497" t="n">
+        <v>188.63</v>
+      </c>
+      <c r="K497" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N497" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D498" t="n">
+        <v>3696.41</v>
+      </c>
+      <c r="E498" t="n">
+        <v>-296.41</v>
+      </c>
+      <c r="F498" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G498" t="n">
+        <v>3696.41</v>
+      </c>
+      <c r="H498" t="n">
+        <v>-296.41</v>
+      </c>
+      <c r="I498" t="n">
+        <v>3300</v>
+      </c>
+      <c r="J498" t="n">
+        <v>3356.51</v>
+      </c>
+      <c r="K498" t="n">
+        <v>-56.51</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N498" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>5594.5</v>
+      </c>
+      <c r="D499" t="n">
+        <v>5678.9</v>
+      </c>
+      <c r="E499" t="n">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="F499" t="n">
+        <v>5855.5</v>
+      </c>
+      <c r="G499" t="n">
+        <v>5678.9</v>
+      </c>
+      <c r="H499" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="I499" t="n">
+        <v>5593</v>
+      </c>
+      <c r="J499" t="n">
+        <v>5539.54</v>
+      </c>
+      <c r="K499" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N499" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>175.64</v>
+      </c>
+      <c r="D500" t="n">
+        <v>175.72</v>
+      </c>
+      <c r="E500" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F500" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="G500" t="n">
+        <v>175.72</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I500" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="J500" t="n">
+        <v>174.71</v>
+      </c>
+      <c r="K500" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N500" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>11644</v>
+      </c>
+      <c r="D501" t="n">
+        <v>11495.6</v>
+      </c>
+      <c r="E501" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="F501" t="n">
+        <v>11644</v>
+      </c>
+      <c r="G501" t="n">
+        <v>11555.48</v>
+      </c>
+      <c r="H501" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="I501" t="n">
+        <v>11230</v>
+      </c>
+      <c r="J501" t="n">
+        <v>11509.83</v>
+      </c>
+      <c r="K501" t="n">
+        <v>-279.83</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N501" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="D502" t="n">
+        <v>296.76</v>
+      </c>
+      <c r="E502" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F502" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="G502" t="n">
+        <v>302.21</v>
+      </c>
+      <c r="H502" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="I502" t="n">
+        <v>289</v>
+      </c>
+      <c r="J502" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="K502" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N502" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>1522.2</v>
+      </c>
+      <c r="D503" t="n">
+        <v>1490.01</v>
+      </c>
+      <c r="E503" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1581</v>
+      </c>
+      <c r="G503" t="n">
+        <v>1515.33</v>
+      </c>
+      <c r="H503" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="I503" t="n">
+        <v>1515.5</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1507.32</v>
+      </c>
+      <c r="K503" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N503" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>2223.4</v>
+      </c>
+      <c r="D504" t="n">
+        <v>2266.67</v>
+      </c>
+      <c r="E504" t="n">
+        <v>-43.27</v>
+      </c>
+      <c r="F504" t="n">
+        <v>2264.9</v>
+      </c>
+      <c r="G504" t="n">
+        <v>2266.67</v>
+      </c>
+      <c r="H504" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="I504" t="n">
+        <v>2207.1</v>
+      </c>
+      <c r="J504" t="n">
+        <v>2192.15</v>
+      </c>
+      <c r="K504" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N504" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="D505" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="E505" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F505" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="G505" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="H505" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I505" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="J505" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="K505" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N505" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>1015.45</v>
+      </c>
+      <c r="D506" t="n">
+        <v>1054.11</v>
+      </c>
+      <c r="E506" t="n">
+        <v>-38.66</v>
+      </c>
+      <c r="F506" t="n">
+        <v>1029.9</v>
+      </c>
+      <c r="G506" t="n">
+        <v>1054.11</v>
+      </c>
+      <c r="H506" t="n">
+        <v>-24.21</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1005.4</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1004.53</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N506" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="D507" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="E507" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F507" t="n">
+        <v>392</v>
+      </c>
+      <c r="G507" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="H507" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="I507" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="J507" t="n">
+        <v>376.12</v>
+      </c>
+      <c r="K507" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N507" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>1868</v>
+      </c>
+      <c r="D508" t="n">
+        <v>1844.19</v>
+      </c>
+      <c r="E508" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="F508" t="n">
+        <v>1875.3</v>
+      </c>
+      <c r="G508" t="n">
+        <v>1854.01</v>
+      </c>
+      <c r="H508" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="I508" t="n">
+        <v>1842.1</v>
+      </c>
+      <c r="J508" t="n">
+        <v>1844</v>
+      </c>
+      <c r="K508" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N508" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="D509" t="n">
+        <v>734.0700000000001</v>
+      </c>
+      <c r="E509" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F509" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="G509" t="n">
+        <v>741.47</v>
+      </c>
+      <c r="H509" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="I509" t="n">
+        <v>701.55</v>
+      </c>
+      <c r="J509" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="K509" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N509" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>1633</v>
+      </c>
+      <c r="D510" t="n">
+        <v>1612.18</v>
+      </c>
+      <c r="E510" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="F510" t="n">
+        <v>1633</v>
+      </c>
+      <c r="G510" t="n">
+        <v>1619.13</v>
+      </c>
+      <c r="H510" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1542</v>
+      </c>
+      <c r="J510" t="n">
+        <v>1610.33</v>
+      </c>
+      <c r="K510" t="n">
+        <v>-68.33</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N510" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>2205</v>
+      </c>
+      <c r="D511" t="n">
+        <v>2168.79</v>
+      </c>
+      <c r="E511" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="F511" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G511" t="n">
+        <v>2209.78</v>
+      </c>
+      <c r="H511" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="I511" t="n">
+        <v>2205</v>
+      </c>
+      <c r="J511" t="n">
+        <v>2198.61</v>
+      </c>
+      <c r="K511" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N511" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="D512" t="n">
+        <v>886.4400000000001</v>
+      </c>
+      <c r="E512" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="F512" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="G512" t="n">
+        <v>893.78</v>
+      </c>
+      <c r="H512" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I512" t="n">
+        <v>864.8</v>
+      </c>
+      <c r="J512" t="n">
+        <v>889.02</v>
+      </c>
+      <c r="K512" t="n">
+        <v>-24.22</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N512" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>1313</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1298.05</v>
+      </c>
+      <c r="E513" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F513" t="n">
+        <v>1358</v>
+      </c>
+      <c r="G513" t="n">
+        <v>1308.28</v>
+      </c>
+      <c r="H513" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="I513" t="n">
+        <v>1313</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1301.41</v>
+      </c>
+      <c r="K513" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N513" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D514" t="n">
+        <v>13380.61</v>
+      </c>
+      <c r="E514" t="n">
+        <v>1469.39</v>
+      </c>
+      <c r="F514" t="n">
+        <v>14850</v>
+      </c>
+      <c r="G514" t="n">
+        <v>14987.08</v>
+      </c>
+      <c r="H514" t="n">
+        <v>-137.08</v>
+      </c>
+      <c r="I514" t="n">
+        <v>14601</v>
+      </c>
+      <c r="J514" t="n">
+        <v>14850</v>
+      </c>
+      <c r="K514" t="n">
+        <v>-249</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N514" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D515" t="n">
+        <v>1160.03</v>
+      </c>
+      <c r="E515" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="F515" t="n">
+        <v>1199.6</v>
+      </c>
+      <c r="G515" t="n">
+        <v>1160.03</v>
+      </c>
+      <c r="H515" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1149.3</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1155.47</v>
+      </c>
+      <c r="K515" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N515" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>4044.9</v>
+      </c>
+      <c r="D516" t="n">
+        <v>3934.8</v>
+      </c>
+      <c r="E516" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="F516" t="n">
+        <v>4044.9</v>
+      </c>
+      <c r="G516" t="n">
+        <v>4047.96</v>
+      </c>
+      <c r="H516" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I516" t="n">
+        <v>3976</v>
+      </c>
+      <c r="J516" t="n">
+        <v>4044.9</v>
+      </c>
+      <c r="K516" t="n">
+        <v>-68.90000000000001</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N516" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>1628</v>
+      </c>
+      <c r="D517" t="n">
+        <v>1668.11</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-40.11</v>
+      </c>
+      <c r="F517" t="n">
+        <v>1640.9</v>
+      </c>
+      <c r="G517" t="n">
+        <v>1668.11</v>
+      </c>
+      <c r="H517" t="n">
+        <v>-27.21</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1609.1</v>
+      </c>
+      <c r="J517" t="n">
+        <v>1607.37</v>
+      </c>
+      <c r="K517" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N517" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -25895,7 +27351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26124,6 +27580,58 @@
       </c>
       <c r="N4" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>734.0700000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F5" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>741.47</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="I5" t="n">
+        <v>701.55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -26137,7 +27645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27094,6 +28602,58 @@
       </c>
       <c r="N18" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1160.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1199.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1160.03</v>
+      </c>
+      <c r="H19" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1149.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1155.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -28509,7 +30069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29206,6 +30766,58 @@
       </c>
       <c r="N13" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1628</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1668.11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-40.11</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1640.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1668.11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-27.21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1609.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1607.37</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -29219,7 +30831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30228,6 +31840,58 @@
       </c>
       <c r="N19" t="n">
         <v>10.08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>10.32</v>
       </c>
     </row>
   </sheetData>
@@ -30241,7 +31905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31250,6 +32914,58 @@
       </c>
       <c r="N19" t="n">
         <v>10.61</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13380.61</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1469.39</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14850</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14987.08</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-137.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>14601</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14850</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-249</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>10.98</v>
       </c>
     </row>
   </sheetData>
@@ -32233,7 +33949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33138,6 +34854,58 @@
       </c>
       <c r="N17" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5594.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5678.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5855.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5678.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5593</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5539.54</v>
+      </c>
+      <c r="K18" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -25896,31 +25896,31 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="D490" t="n">
         <v>2023.46</v>
       </c>
       <c r="E490" t="n">
-        <v>-2.46</v>
+        <v>-21.46</v>
       </c>
       <c r="F490" t="n">
-        <v>2021</v>
+        <v>2014.7</v>
       </c>
       <c r="G490" t="n">
         <v>2023.46</v>
       </c>
       <c r="H490" t="n">
-        <v>-2.46</v>
+        <v>-8.76</v>
       </c>
       <c r="I490" t="n">
-        <v>1968</v>
+        <v>1982.3</v>
       </c>
       <c r="J490" t="n">
         <v>2011.83</v>
       </c>
       <c r="K490" t="n">
-        <v>-43.83</v>
+        <v>-29.53</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>0.12</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="491">
@@ -25948,31 +25948,31 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1060</v>
+        <v>1047.5</v>
       </c>
       <c r="D491" t="n">
         <v>1046.49</v>
       </c>
       <c r="E491" t="n">
-        <v>13.51</v>
+        <v>1.01</v>
       </c>
       <c r="F491" t="n">
-        <v>1060</v>
+        <v>1051.2</v>
       </c>
       <c r="G491" t="n">
         <v>1053.64</v>
       </c>
       <c r="H491" t="n">
-        <v>6.36</v>
+        <v>-2.44</v>
       </c>
       <c r="I491" t="n">
-        <v>1034.5</v>
+        <v>1040.5</v>
       </c>
       <c r="J491" t="n">
         <v>1055.67</v>
       </c>
       <c r="K491" t="n">
-        <v>-21.17</v>
+        <v>-15.17</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>1.29</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="492">
@@ -26000,31 +26000,31 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>691.05</v>
+        <v>679.8</v>
       </c>
       <c r="D492" t="n">
         <v>709.42</v>
       </c>
       <c r="E492" t="n">
-        <v>-18.37</v>
+        <v>-29.62</v>
       </c>
       <c r="F492" t="n">
-        <v>691.05</v>
+        <v>682.95</v>
       </c>
       <c r="G492" t="n">
         <v>709.42</v>
       </c>
       <c r="H492" t="n">
-        <v>-18.37</v>
+        <v>-26.47</v>
       </c>
       <c r="I492" t="n">
-        <v>664</v>
+        <v>672.5</v>
       </c>
       <c r="J492" t="n">
         <v>691.05</v>
       </c>
       <c r="K492" t="n">
-        <v>-27.05</v>
+        <v>-18.55</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         </is>
       </c>
       <c r="N492" t="n">
-        <v>2.59</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="493">
@@ -26052,31 +26052,31 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>1042.9</v>
+        <v>1038.3</v>
       </c>
       <c r="D493" t="n">
         <v>1043.82</v>
       </c>
       <c r="E493" t="n">
-        <v>-0.92</v>
+        <v>-5.52</v>
       </c>
       <c r="F493" t="n">
-        <v>1045.35</v>
+        <v>1053</v>
       </c>
       <c r="G493" t="n">
         <v>1043.82</v>
       </c>
       <c r="H493" t="n">
-        <v>1.53</v>
+        <v>9.18</v>
       </c>
       <c r="I493" t="n">
-        <v>1022</v>
+        <v>1027.15</v>
       </c>
       <c r="J493" t="n">
         <v>1036.9</v>
       </c>
       <c r="K493" t="n">
-        <v>-14.9</v>
+        <v>-9.75</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         </is>
       </c>
       <c r="N493" t="n">
-        <v>0.09</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="494">
@@ -26104,31 +26104,31 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>483.15</v>
+        <v>482.85</v>
       </c>
       <c r="D494" t="n">
         <v>477</v>
       </c>
       <c r="E494" t="n">
-        <v>6.15</v>
+        <v>5.85</v>
       </c>
       <c r="F494" t="n">
-        <v>500</v>
+        <v>484.7</v>
       </c>
       <c r="G494" t="n">
         <v>479.48</v>
       </c>
       <c r="H494" t="n">
-        <v>20.52</v>
+        <v>5.22</v>
       </c>
       <c r="I494" t="n">
-        <v>479.25</v>
+        <v>471.75</v>
       </c>
       <c r="J494" t="n">
         <v>476.89</v>
       </c>
       <c r="K494" t="n">
-        <v>2.36</v>
+        <v>-5.14</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         </is>
       </c>
       <c r="N494" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="495">
@@ -26156,31 +26156,31 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>1875</v>
+        <v>1811.5</v>
       </c>
       <c r="D495" t="n">
         <v>1849.86</v>
       </c>
       <c r="E495" t="n">
-        <v>25.14</v>
+        <v>-38.36</v>
       </c>
       <c r="F495" t="n">
-        <v>1875</v>
+        <v>1844.8</v>
       </c>
       <c r="G495" t="n">
         <v>1889.29</v>
       </c>
       <c r="H495" t="n">
-        <v>-14.29</v>
+        <v>-44.49</v>
       </c>
       <c r="I495" t="n">
-        <v>1796.4</v>
+        <v>1804.8</v>
       </c>
       <c r="J495" t="n">
         <v>1875</v>
       </c>
       <c r="K495" t="n">
-        <v>-78.59999999999999</v>
+        <v>-70.2</v>
       </c>
       <c r="L495" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="496">
@@ -26217,22 +26217,22 @@
         <v>15.09</v>
       </c>
       <c r="F496" t="n">
-        <v>1292.5</v>
+        <v>1283.1</v>
       </c>
       <c r="G496" t="n">
         <v>1289.75</v>
       </c>
       <c r="H496" t="n">
-        <v>2.75</v>
+        <v>-6.65</v>
       </c>
       <c r="I496" t="n">
-        <v>1261.1</v>
+        <v>1263.4</v>
       </c>
       <c r="J496" t="n">
         <v>1276</v>
       </c>
       <c r="K496" t="n">
-        <v>-14.9</v>
+        <v>-12.6</v>
       </c>
       <c r="L496" t="inlineStr">
         <is>
@@ -26260,31 +26260,31 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>188.63</v>
+        <v>186</v>
       </c>
       <c r="D497" t="n">
         <v>197.96</v>
       </c>
       <c r="E497" t="n">
-        <v>-9.33</v>
+        <v>-11.96</v>
       </c>
       <c r="F497" t="n">
-        <v>188.63</v>
+        <v>186.31</v>
       </c>
       <c r="G497" t="n">
         <v>197.96</v>
       </c>
       <c r="H497" t="n">
-        <v>-9.33</v>
+        <v>-11.65</v>
       </c>
       <c r="I497" t="n">
-        <v>181.8</v>
+        <v>184.09</v>
       </c>
       <c r="J497" t="n">
         <v>188.63</v>
       </c>
       <c r="K497" t="n">
-        <v>-6.83</v>
+        <v>-4.54</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>4.71</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="498">
@@ -26312,31 +26312,31 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3400</v>
+        <v>3332</v>
       </c>
       <c r="D498" t="n">
         <v>3696.41</v>
       </c>
       <c r="E498" t="n">
-        <v>-296.41</v>
+        <v>-364.41</v>
       </c>
       <c r="F498" t="n">
-        <v>3400</v>
+        <v>3339</v>
       </c>
       <c r="G498" t="n">
         <v>3696.41</v>
       </c>
       <c r="H498" t="n">
-        <v>-296.41</v>
+        <v>-357.41</v>
       </c>
       <c r="I498" t="n">
-        <v>3300</v>
+        <v>3245</v>
       </c>
       <c r="J498" t="n">
         <v>3356.51</v>
       </c>
       <c r="K498" t="n">
-        <v>-56.51</v>
+        <v>-111.51</v>
       </c>
       <c r="L498" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>8.02</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="499">
@@ -26364,31 +26364,31 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>5594.5</v>
+        <v>5875</v>
       </c>
       <c r="D499" t="n">
         <v>5678.9</v>
       </c>
       <c r="E499" t="n">
-        <v>-84.40000000000001</v>
+        <v>196.1</v>
       </c>
       <c r="F499" t="n">
-        <v>5855.5</v>
+        <v>5910</v>
       </c>
       <c r="G499" t="n">
         <v>5678.9</v>
       </c>
       <c r="H499" t="n">
-        <v>176.6</v>
+        <v>231.1</v>
       </c>
       <c r="I499" t="n">
-        <v>5593</v>
+        <v>5677</v>
       </c>
       <c r="J499" t="n">
         <v>5539.54</v>
       </c>
       <c r="K499" t="n">
-        <v>53.46</v>
+        <v>137.46</v>
       </c>
       <c r="L499" t="inlineStr">
         <is>
@@ -26397,11 +26397,11 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N499" t="n">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="500">
@@ -26416,31 +26416,31 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>175.64</v>
+        <v>175.77</v>
       </c>
       <c r="D500" t="n">
         <v>175.72</v>
       </c>
       <c r="E500" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F500" t="n">
-        <v>176.6</v>
+        <v>178.18</v>
       </c>
       <c r="G500" t="n">
         <v>175.72</v>
       </c>
       <c r="H500" t="n">
-        <v>0.88</v>
+        <v>2.46</v>
       </c>
       <c r="I500" t="n">
-        <v>173.82</v>
+        <v>174.81</v>
       </c>
       <c r="J500" t="n">
         <v>174.71</v>
       </c>
       <c r="K500" t="n">
-        <v>-0.89</v>
+        <v>0.1</v>
       </c>
       <c r="L500" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="501">
@@ -26468,31 +26468,31 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>11644</v>
+        <v>11340</v>
       </c>
       <c r="D501" t="n">
         <v>11495.6</v>
       </c>
       <c r="E501" t="n">
-        <v>148.4</v>
+        <v>-155.6</v>
       </c>
       <c r="F501" t="n">
-        <v>11644</v>
+        <v>11429</v>
       </c>
       <c r="G501" t="n">
         <v>11555.48</v>
       </c>
       <c r="H501" t="n">
-        <v>88.52</v>
+        <v>-126.48</v>
       </c>
       <c r="I501" t="n">
-        <v>11230</v>
+        <v>11250</v>
       </c>
       <c r="J501" t="n">
         <v>11509.83</v>
       </c>
       <c r="K501" t="n">
-        <v>-279.83</v>
+        <v>-259.83</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         </is>
       </c>
       <c r="N501" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="502">
@@ -26520,31 +26520,31 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>300.6</v>
+        <v>292</v>
       </c>
       <c r="D502" t="n">
         <v>296.76</v>
       </c>
       <c r="E502" t="n">
-        <v>3.84</v>
+        <v>-4.76</v>
       </c>
       <c r="F502" t="n">
-        <v>300.6</v>
+        <v>292.85</v>
       </c>
       <c r="G502" t="n">
         <v>302.21</v>
       </c>
       <c r="H502" t="n">
-        <v>-1.61</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I502" t="n">
-        <v>289</v>
+        <v>290.05</v>
       </c>
       <c r="J502" t="n">
         <v>300.6</v>
       </c>
       <c r="K502" t="n">
-        <v>-11.6</v>
+        <v>-10.55</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="503">
@@ -26572,31 +26572,31 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>1522.2</v>
+        <v>1532.3</v>
       </c>
       <c r="D503" t="n">
         <v>1490.01</v>
       </c>
       <c r="E503" t="n">
-        <v>32.19</v>
+        <v>42.29</v>
       </c>
       <c r="F503" t="n">
-        <v>1581</v>
+        <v>1556.4</v>
       </c>
       <c r="G503" t="n">
         <v>1515.33</v>
       </c>
       <c r="H503" t="n">
-        <v>65.67</v>
+        <v>41.07</v>
       </c>
       <c r="I503" t="n">
-        <v>1515.5</v>
+        <v>1529.5</v>
       </c>
       <c r="J503" t="n">
         <v>1507.32</v>
       </c>
       <c r="K503" t="n">
-        <v>8.18</v>
+        <v>22.18</v>
       </c>
       <c r="L503" t="inlineStr">
         <is>
@@ -26605,11 +26605,11 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N503" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="504">
@@ -26624,31 +26624,31 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>2223.4</v>
+        <v>2265.6</v>
       </c>
       <c r="D504" t="n">
         <v>2266.67</v>
       </c>
       <c r="E504" t="n">
-        <v>-43.27</v>
+        <v>-1.07</v>
       </c>
       <c r="F504" t="n">
-        <v>2264.9</v>
+        <v>2278.4</v>
       </c>
       <c r="G504" t="n">
         <v>2266.67</v>
       </c>
       <c r="H504" t="n">
-        <v>-1.77</v>
+        <v>11.73</v>
       </c>
       <c r="I504" t="n">
-        <v>2207.1</v>
+        <v>2182.5</v>
       </c>
       <c r="J504" t="n">
         <v>2192.15</v>
       </c>
       <c r="K504" t="n">
-        <v>14.95</v>
+        <v>-9.65</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>1.91</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="505">
@@ -26676,31 +26676,31 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>328.1</v>
+        <v>328</v>
       </c>
       <c r="D505" t="n">
         <v>297.4</v>
       </c>
       <c r="E505" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="F505" t="n">
-        <v>332.95</v>
+        <v>330</v>
       </c>
       <c r="G505" t="n">
         <v>327.11</v>
       </c>
       <c r="H505" t="n">
-        <v>5.84</v>
+        <v>2.89</v>
       </c>
       <c r="I505" t="n">
-        <v>315.8</v>
+        <v>324.3</v>
       </c>
       <c r="J505" t="n">
         <v>325.4</v>
       </c>
       <c r="K505" t="n">
-        <v>-9.6</v>
+        <v>-1.1</v>
       </c>
       <c r="L505" t="inlineStr">
         <is>
@@ -26709,11 +26709,11 @@
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N505" t="n">
-        <v>10.32</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="506">
@@ -26728,31 +26728,31 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>1015.45</v>
+        <v>1037.4</v>
       </c>
       <c r="D506" t="n">
         <v>1054.11</v>
       </c>
       <c r="E506" t="n">
-        <v>-38.66</v>
+        <v>-16.71</v>
       </c>
       <c r="F506" t="n">
-        <v>1029.9</v>
+        <v>1037.4</v>
       </c>
       <c r="G506" t="n">
         <v>1054.11</v>
       </c>
       <c r="H506" t="n">
-        <v>-24.21</v>
+        <v>-16.71</v>
       </c>
       <c r="I506" t="n">
-        <v>1005.4</v>
+        <v>1025.95</v>
       </c>
       <c r="J506" t="n">
         <v>1004.53</v>
       </c>
       <c r="K506" t="n">
-        <v>0.87</v>
+        <v>21.42</v>
       </c>
       <c r="L506" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>3.67</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="507">
@@ -26780,31 +26780,31 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>381.5</v>
+        <v>394.95</v>
       </c>
       <c r="D507" t="n">
         <v>376.64</v>
       </c>
       <c r="E507" t="n">
-        <v>4.86</v>
+        <v>18.31</v>
       </c>
       <c r="F507" t="n">
-        <v>392</v>
+        <v>394.95</v>
       </c>
       <c r="G507" t="n">
         <v>378.19</v>
       </c>
       <c r="H507" t="n">
-        <v>13.81</v>
+        <v>16.76</v>
       </c>
       <c r="I507" t="n">
-        <v>377.15</v>
+        <v>389.3</v>
       </c>
       <c r="J507" t="n">
         <v>376.12</v>
       </c>
       <c r="K507" t="n">
-        <v>1.03</v>
+        <v>13.18</v>
       </c>
       <c r="L507" t="inlineStr">
         <is>
@@ -26813,11 +26813,11 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N507" t="n">
-        <v>1.29</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="508">
@@ -26832,31 +26832,31 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D508" t="n">
         <v>1844.19</v>
       </c>
       <c r="E508" t="n">
-        <v>23.81</v>
+        <v>25.81</v>
       </c>
       <c r="F508" t="n">
-        <v>1875.3</v>
+        <v>1880.8</v>
       </c>
       <c r="G508" t="n">
         <v>1854.01</v>
       </c>
       <c r="H508" t="n">
-        <v>21.29</v>
+        <v>26.79</v>
       </c>
       <c r="I508" t="n">
-        <v>1842.1</v>
+        <v>1855.7</v>
       </c>
       <c r="J508" t="n">
         <v>1844</v>
       </c>
       <c r="K508" t="n">
-        <v>-1.9</v>
+        <v>11.7</v>
       </c>
       <c r="L508" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="509">
@@ -26884,31 +26884,31 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>737.9</v>
+        <v>706.4</v>
       </c>
       <c r="D509" t="n">
         <v>734.0700000000001</v>
       </c>
       <c r="E509" t="n">
-        <v>3.83</v>
+        <v>-27.67</v>
       </c>
       <c r="F509" t="n">
-        <v>737.9</v>
+        <v>716.9</v>
       </c>
       <c r="G509" t="n">
         <v>741.47</v>
       </c>
       <c r="H509" t="n">
-        <v>-3.57</v>
+        <v>-24.57</v>
       </c>
       <c r="I509" t="n">
-        <v>701.55</v>
+        <v>703.55</v>
       </c>
       <c r="J509" t="n">
         <v>737.9</v>
       </c>
       <c r="K509" t="n">
-        <v>-36.35</v>
+        <v>-34.35</v>
       </c>
       <c r="L509" t="inlineStr">
         <is>
@@ -26917,11 +26917,11 @@
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N509" t="n">
-        <v>0.52</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="510">
@@ -26936,31 +26936,31 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="D510" t="n">
         <v>1612.18</v>
       </c>
       <c r="E510" t="n">
-        <v>20.82</v>
+        <v>-24.18</v>
       </c>
       <c r="F510" t="n">
-        <v>1633</v>
+        <v>1628.5</v>
       </c>
       <c r="G510" t="n">
         <v>1619.13</v>
       </c>
       <c r="H510" t="n">
-        <v>13.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="I510" t="n">
-        <v>1542</v>
+        <v>1584.5</v>
       </c>
       <c r="J510" t="n">
         <v>1610.33</v>
       </c>
       <c r="K510" t="n">
-        <v>-68.33</v>
+        <v>-25.83</v>
       </c>
       <c r="L510" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="511">
@@ -26988,31 +26988,31 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>2205</v>
+        <v>2267</v>
       </c>
       <c r="D511" t="n">
         <v>2168.79</v>
       </c>
       <c r="E511" t="n">
-        <v>36.21</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="F511" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G511" t="n">
         <v>2209.78</v>
       </c>
       <c r="H511" t="n">
-        <v>70.22</v>
+        <v>69.22</v>
       </c>
       <c r="I511" t="n">
-        <v>2205</v>
+        <v>2240.3</v>
       </c>
       <c r="J511" t="n">
         <v>2198.61</v>
       </c>
       <c r="K511" t="n">
-        <v>6.39</v>
+        <v>41.69</v>
       </c>
       <c r="L511" t="inlineStr">
         <is>
@@ -27021,11 +27021,11 @@
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N511" t="n">
-        <v>1.67</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="512">
@@ -27040,31 +27040,31 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>898.75</v>
+        <v>882.4</v>
       </c>
       <c r="D512" t="n">
         <v>886.4400000000001</v>
       </c>
       <c r="E512" t="n">
-        <v>12.31</v>
+        <v>-4.04</v>
       </c>
       <c r="F512" t="n">
-        <v>898.75</v>
+        <v>883.95</v>
       </c>
       <c r="G512" t="n">
         <v>893.78</v>
       </c>
       <c r="H512" t="n">
-        <v>4.97</v>
+        <v>-9.83</v>
       </c>
       <c r="I512" t="n">
-        <v>864.8</v>
+        <v>872.45</v>
       </c>
       <c r="J512" t="n">
         <v>889.02</v>
       </c>
       <c r="K512" t="n">
-        <v>-24.22</v>
+        <v>-16.57</v>
       </c>
       <c r="L512" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>1.39</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="513">
@@ -27092,31 +27092,31 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>1313</v>
+        <v>1354</v>
       </c>
       <c r="D513" t="n">
         <v>1298.05</v>
       </c>
       <c r="E513" t="n">
-        <v>14.95</v>
+        <v>55.95</v>
       </c>
       <c r="F513" t="n">
-        <v>1358</v>
+        <v>1369.4</v>
       </c>
       <c r="G513" t="n">
         <v>1308.28</v>
       </c>
       <c r="H513" t="n">
-        <v>49.72</v>
+        <v>61.12</v>
       </c>
       <c r="I513" t="n">
-        <v>1313</v>
+        <v>1339</v>
       </c>
       <c r="J513" t="n">
         <v>1301.41</v>
       </c>
       <c r="K513" t="n">
-        <v>11.59</v>
+        <v>37.59</v>
       </c>
       <c r="L513" t="inlineStr">
         <is>
@@ -27125,11 +27125,11 @@
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N513" t="n">
-        <v>1.15</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="514">
@@ -27144,31 +27144,31 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>14850</v>
+        <v>14650</v>
       </c>
       <c r="D514" t="n">
         <v>13380.61</v>
       </c>
       <c r="E514" t="n">
-        <v>1469.39</v>
+        <v>1269.39</v>
       </c>
       <c r="F514" t="n">
-        <v>14850</v>
+        <v>14920</v>
       </c>
       <c r="G514" t="n">
         <v>14987.08</v>
       </c>
       <c r="H514" t="n">
-        <v>-137.08</v>
+        <v>-67.08</v>
       </c>
       <c r="I514" t="n">
-        <v>14601</v>
+        <v>14650</v>
       </c>
       <c r="J514" t="n">
         <v>14850</v>
       </c>
       <c r="K514" t="n">
-        <v>-249</v>
+        <v>-200</v>
       </c>
       <c r="L514" t="inlineStr">
         <is>
@@ -27177,11 +27177,11 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N514" t="n">
-        <v>10.98</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="515">
@@ -27196,31 +27196,31 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="D515" t="n">
         <v>1160.03</v>
       </c>
       <c r="E515" t="n">
-        <v>14.97</v>
+        <v>39.97</v>
       </c>
       <c r="F515" t="n">
-        <v>1199.6</v>
+        <v>1208</v>
       </c>
       <c r="G515" t="n">
         <v>1160.03</v>
       </c>
       <c r="H515" t="n">
-        <v>39.57</v>
+        <v>47.97</v>
       </c>
       <c r="I515" t="n">
-        <v>1149.3</v>
+        <v>1193.9</v>
       </c>
       <c r="J515" t="n">
         <v>1155.47</v>
       </c>
       <c r="K515" t="n">
-        <v>-6.17</v>
+        <v>38.43</v>
       </c>
       <c r="L515" t="inlineStr">
         <is>
@@ -27229,11 +27229,11 @@
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N515" t="n">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="516">
@@ -27248,31 +27248,31 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>4044.9</v>
+        <v>4045.8</v>
       </c>
       <c r="D516" t="n">
         <v>3934.8</v>
       </c>
       <c r="E516" t="n">
-        <v>110.1</v>
+        <v>111</v>
       </c>
       <c r="F516" t="n">
-        <v>4044.9</v>
+        <v>4060</v>
       </c>
       <c r="G516" t="n">
         <v>4047.96</v>
       </c>
       <c r="H516" t="n">
-        <v>-3.06</v>
+        <v>12.04</v>
       </c>
       <c r="I516" t="n">
-        <v>3976</v>
+        <v>4021.3</v>
       </c>
       <c r="J516" t="n">
         <v>4044.9</v>
       </c>
       <c r="K516" t="n">
-        <v>-68.90000000000001</v>
+        <v>-23.6</v>
       </c>
       <c r="L516" t="inlineStr">
         <is>
@@ -27281,11 +27281,11 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N516" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="517">
@@ -27300,31 +27300,31 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>1628</v>
+        <v>1640.9</v>
       </c>
       <c r="D517" t="n">
         <v>1668.11</v>
       </c>
       <c r="E517" t="n">
-        <v>-40.11</v>
+        <v>-27.21</v>
       </c>
       <c r="F517" t="n">
-        <v>1640.9</v>
+        <v>1642</v>
       </c>
       <c r="G517" t="n">
         <v>1668.11</v>
       </c>
       <c r="H517" t="n">
-        <v>-27.21</v>
+        <v>-26.11</v>
       </c>
       <c r="I517" t="n">
-        <v>1609.1</v>
+        <v>1598</v>
       </c>
       <c r="J517" t="n">
         <v>1607.37</v>
       </c>
       <c r="K517" t="n">
-        <v>1.73</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L517" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -27594,31 +27594,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>737.9</v>
+        <v>706.4</v>
       </c>
       <c r="D5" t="n">
         <v>734.0700000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.83</v>
+        <v>-27.67</v>
       </c>
       <c r="F5" t="n">
-        <v>737.9</v>
+        <v>716.9</v>
       </c>
       <c r="G5" t="n">
         <v>741.47</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.57</v>
+        <v>-24.57</v>
       </c>
       <c r="I5" t="n">
-        <v>701.55</v>
+        <v>703.55</v>
       </c>
       <c r="J5" t="n">
         <v>737.9</v>
       </c>
       <c r="K5" t="n">
-        <v>-36.35</v>
+        <v>-34.35</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -27627,11 +27627,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.52</v>
+        <v>3.77</v>
       </c>
     </row>
   </sheetData>
@@ -28616,31 +28616,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="D19" t="n">
         <v>1160.03</v>
       </c>
       <c r="E19" t="n">
-        <v>14.97</v>
+        <v>39.97</v>
       </c>
       <c r="F19" t="n">
-        <v>1199.6</v>
+        <v>1208</v>
       </c>
       <c r="G19" t="n">
         <v>1160.03</v>
       </c>
       <c r="H19" t="n">
-        <v>39.57</v>
+        <v>47.97</v>
       </c>
       <c r="I19" t="n">
-        <v>1149.3</v>
+        <v>1193.9</v>
       </c>
       <c r="J19" t="n">
         <v>1155.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.17</v>
+        <v>38.43</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -28649,11 +28649,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
@@ -30780,31 +30780,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1628</v>
+        <v>1640.9</v>
       </c>
       <c r="D14" t="n">
         <v>1668.11</v>
       </c>
       <c r="E14" t="n">
-        <v>-40.11</v>
+        <v>-27.21</v>
       </c>
       <c r="F14" t="n">
-        <v>1640.9</v>
+        <v>1642</v>
       </c>
       <c r="G14" t="n">
         <v>1668.11</v>
       </c>
       <c r="H14" t="n">
-        <v>-27.21</v>
+        <v>-26.11</v>
       </c>
       <c r="I14" t="n">
-        <v>1609.1</v>
+        <v>1598</v>
       </c>
       <c r="J14" t="n">
         <v>1607.37</v>
       </c>
       <c r="K14" t="n">
-        <v>1.73</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -31854,31 +31854,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>328.1</v>
+        <v>328</v>
       </c>
       <c r="D20" t="n">
         <v>297.4</v>
       </c>
       <c r="E20" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="F20" t="n">
-        <v>332.95</v>
+        <v>330</v>
       </c>
       <c r="G20" t="n">
         <v>327.11</v>
       </c>
       <c r="H20" t="n">
-        <v>5.84</v>
+        <v>2.89</v>
       </c>
       <c r="I20" t="n">
-        <v>315.8</v>
+        <v>324.3</v>
       </c>
       <c r="J20" t="n">
         <v>325.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.6</v>
+        <v>-1.1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -31887,11 +31887,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>10.32</v>
+        <v>10.29</v>
       </c>
     </row>
   </sheetData>
@@ -32928,31 +32928,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14850</v>
+        <v>14650</v>
       </c>
       <c r="D20" t="n">
         <v>13380.61</v>
       </c>
       <c r="E20" t="n">
-        <v>1469.39</v>
+        <v>1269.39</v>
       </c>
       <c r="F20" t="n">
-        <v>14850</v>
+        <v>14920</v>
       </c>
       <c r="G20" t="n">
         <v>14987.08</v>
       </c>
       <c r="H20" t="n">
-        <v>-137.08</v>
+        <v>-67.08</v>
       </c>
       <c r="I20" t="n">
-        <v>14601</v>
+        <v>14650</v>
       </c>
       <c r="J20" t="n">
         <v>14850</v>
       </c>
       <c r="K20" t="n">
-        <v>-249</v>
+        <v>-200</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -32961,11 +32961,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>10.98</v>
+        <v>9.49</v>
       </c>
     </row>
   </sheetData>
@@ -34868,31 +34868,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5594.5</v>
+        <v>5875</v>
       </c>
       <c r="D18" t="n">
         <v>5678.9</v>
       </c>
       <c r="E18" t="n">
-        <v>-84.40000000000001</v>
+        <v>196.1</v>
       </c>
       <c r="F18" t="n">
-        <v>5855.5</v>
+        <v>5910</v>
       </c>
       <c r="G18" t="n">
         <v>5678.9</v>
       </c>
       <c r="H18" t="n">
-        <v>176.6</v>
+        <v>231.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5593</v>
+        <v>5677</v>
       </c>
       <c r="J18" t="n">
         <v>5539.54</v>
       </c>
       <c r="K18" t="n">
-        <v>53.46</v>
+        <v>137.46</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -34901,11 +34901,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N517"/>
+  <dimension ref="A1:N540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27338,6 +27338,1202 @@
       </c>
       <c r="N517" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>2234</v>
+      </c>
+      <c r="D518" t="n">
+        <v>2250.81</v>
+      </c>
+      <c r="E518" t="n">
+        <v>-16.81</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2258.8</v>
+      </c>
+      <c r="G518" t="n">
+        <v>2263.59</v>
+      </c>
+      <c r="H518" t="n">
+        <v>-4.79</v>
+      </c>
+      <c r="I518" t="n">
+        <v>2214</v>
+      </c>
+      <c r="J518" t="n">
+        <v>2180.01</v>
+      </c>
+      <c r="K518" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N518" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>490</v>
+      </c>
+      <c r="D519" t="n">
+        <v>500.52</v>
+      </c>
+      <c r="E519" t="n">
+        <v>-10.52</v>
+      </c>
+      <c r="F519" t="n">
+        <v>493</v>
+      </c>
+      <c r="G519" t="n">
+        <v>502.56</v>
+      </c>
+      <c r="H519" t="n">
+        <v>-9.56</v>
+      </c>
+      <c r="I519" t="n">
+        <v>484.2</v>
+      </c>
+      <c r="J519" t="n">
+        <v>484.21</v>
+      </c>
+      <c r="K519" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N519" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D520" t="n">
+        <v>5570.27</v>
+      </c>
+      <c r="E520" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="F520" t="n">
+        <v>5659</v>
+      </c>
+      <c r="G520" t="n">
+        <v>5674.7</v>
+      </c>
+      <c r="H520" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="I520" t="n">
+        <v>5495.5</v>
+      </c>
+      <c r="J520" t="n">
+        <v>5466.75</v>
+      </c>
+      <c r="K520" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N520" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="D521" t="n">
+        <v>115.53</v>
+      </c>
+      <c r="E521" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F521" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G521" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="H521" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I521" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="J521" t="n">
+        <v>113.12</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N521" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D522" t="n">
+        <v>6048.28</v>
+      </c>
+      <c r="E522" t="n">
+        <v>-248.28</v>
+      </c>
+      <c r="F522" t="n">
+        <v>5852.5</v>
+      </c>
+      <c r="G522" t="n">
+        <v>6048.28</v>
+      </c>
+      <c r="H522" t="n">
+        <v>-195.78</v>
+      </c>
+      <c r="I522" t="n">
+        <v>5603</v>
+      </c>
+      <c r="J522" t="n">
+        <v>5660.68</v>
+      </c>
+      <c r="K522" t="n">
+        <v>-57.68</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N522" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D523" t="n">
+        <v>1018.71</v>
+      </c>
+      <c r="E523" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="F523" t="n">
+        <v>1047.9</v>
+      </c>
+      <c r="G523" t="n">
+        <v>1022.73</v>
+      </c>
+      <c r="H523" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="I523" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J523" t="n">
+        <v>984.74</v>
+      </c>
+      <c r="K523" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N523" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>1356</v>
+      </c>
+      <c r="D524" t="n">
+        <v>1441.03</v>
+      </c>
+      <c r="E524" t="n">
+        <v>-85.03</v>
+      </c>
+      <c r="F524" t="n">
+        <v>1371.7</v>
+      </c>
+      <c r="G524" t="n">
+        <v>1441.03</v>
+      </c>
+      <c r="H524" t="n">
+        <v>-69.33</v>
+      </c>
+      <c r="I524" t="n">
+        <v>1327.2</v>
+      </c>
+      <c r="J524" t="n">
+        <v>1353.04</v>
+      </c>
+      <c r="K524" t="n">
+        <v>-25.84</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N524" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>1880.7</v>
+      </c>
+      <c r="D525" t="n">
+        <v>1922.29</v>
+      </c>
+      <c r="E525" t="n">
+        <v>-41.59</v>
+      </c>
+      <c r="F525" t="n">
+        <v>1887.2</v>
+      </c>
+      <c r="G525" t="n">
+        <v>1922.29</v>
+      </c>
+      <c r="H525" t="n">
+        <v>-35.09</v>
+      </c>
+      <c r="I525" t="n">
+        <v>1846.6</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1810.61</v>
+      </c>
+      <c r="K525" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N525" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>1274.4</v>
+      </c>
+      <c r="D526" t="n">
+        <v>1299.98</v>
+      </c>
+      <c r="E526" t="n">
+        <v>-25.58</v>
+      </c>
+      <c r="F526" t="n">
+        <v>1307.5</v>
+      </c>
+      <c r="G526" t="n">
+        <v>1299.98</v>
+      </c>
+      <c r="H526" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1261.5</v>
+      </c>
+      <c r="J526" t="n">
+        <v>1246.75</v>
+      </c>
+      <c r="K526" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N526" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="D527" t="n">
+        <v>289.91</v>
+      </c>
+      <c r="E527" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F527" t="n">
+        <v>296.65</v>
+      </c>
+      <c r="G527" t="n">
+        <v>290.28</v>
+      </c>
+      <c r="H527" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="I527" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="J527" t="n">
+        <v>283.08</v>
+      </c>
+      <c r="K527" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N527" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="D528" t="n">
+        <v>175.25</v>
+      </c>
+      <c r="E528" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F528" t="n">
+        <v>186.32</v>
+      </c>
+      <c r="G528" t="n">
+        <v>189.58</v>
+      </c>
+      <c r="H528" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="I528" t="n">
+        <v>183.26</v>
+      </c>
+      <c r="J528" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N528" t="n">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>1391</v>
+      </c>
+      <c r="D529" t="n">
+        <v>1394.82</v>
+      </c>
+      <c r="E529" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="F529" t="n">
+        <v>1407.4</v>
+      </c>
+      <c r="G529" t="n">
+        <v>1415.1</v>
+      </c>
+      <c r="H529" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1376</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1363.05</v>
+      </c>
+      <c r="K529" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N529" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>170.53</v>
+      </c>
+      <c r="D530" t="n">
+        <v>171.94</v>
+      </c>
+      <c r="E530" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="F530" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="G530" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="H530" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I530" t="n">
+        <v>168.53</v>
+      </c>
+      <c r="J530" t="n">
+        <v>166.37</v>
+      </c>
+      <c r="K530" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N530" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>11310</v>
+      </c>
+      <c r="D531" t="n">
+        <v>11246.12</v>
+      </c>
+      <c r="E531" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="F531" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G531" t="n">
+        <v>11246.12</v>
+      </c>
+      <c r="H531" t="n">
+        <v>253.88</v>
+      </c>
+      <c r="I531" t="n">
+        <v>11282</v>
+      </c>
+      <c r="J531" t="n">
+        <v>10961.51</v>
+      </c>
+      <c r="K531" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N531" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D532" t="n">
+        <v>1624.17</v>
+      </c>
+      <c r="E532" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1649</v>
+      </c>
+      <c r="G532" t="n">
+        <v>1645.23</v>
+      </c>
+      <c r="H532" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I532" t="n">
+        <v>1613.7</v>
+      </c>
+      <c r="J532" t="n">
+        <v>1587.64</v>
+      </c>
+      <c r="K532" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N532" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>1829.2</v>
+      </c>
+      <c r="D533" t="n">
+        <v>1805.59</v>
+      </c>
+      <c r="E533" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="F533" t="n">
+        <v>1847.8</v>
+      </c>
+      <c r="G533" t="n">
+        <v>1864.08</v>
+      </c>
+      <c r="H533" t="n">
+        <v>-16.28</v>
+      </c>
+      <c r="I533" t="n">
+        <v>1812.1</v>
+      </c>
+      <c r="J533" t="n">
+        <v>1795.61</v>
+      </c>
+      <c r="K533" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N533" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="D534" t="n">
+        <v>652.14</v>
+      </c>
+      <c r="E534" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="F534" t="n">
+        <v>676</v>
+      </c>
+      <c r="G534" t="n">
+        <v>688</v>
+      </c>
+      <c r="H534" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I534" t="n">
+        <v>665.95</v>
+      </c>
+      <c r="J534" t="n">
+        <v>662.73</v>
+      </c>
+      <c r="K534" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N534" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>3303</v>
+      </c>
+      <c r="D535" t="n">
+        <v>3001.21</v>
+      </c>
+      <c r="E535" t="n">
+        <v>301.79</v>
+      </c>
+      <c r="F535" t="n">
+        <v>3369</v>
+      </c>
+      <c r="G535" t="n">
+        <v>3314.16</v>
+      </c>
+      <c r="H535" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="I535" t="n">
+        <v>3255.2</v>
+      </c>
+      <c r="J535" t="n">
+        <v>3190.66</v>
+      </c>
+      <c r="K535" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N535" t="n">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>2179.8</v>
+      </c>
+      <c r="D536" t="n">
+        <v>2296.73</v>
+      </c>
+      <c r="E536" t="n">
+        <v>-116.93</v>
+      </c>
+      <c r="F536" t="n">
+        <v>2260</v>
+      </c>
+      <c r="G536" t="n">
+        <v>2296.73</v>
+      </c>
+      <c r="H536" t="n">
+        <v>-36.73</v>
+      </c>
+      <c r="I536" t="n">
+        <v>2156.2</v>
+      </c>
+      <c r="J536" t="n">
+        <v>2127.36</v>
+      </c>
+      <c r="K536" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N536" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>881.75</v>
+      </c>
+      <c r="D537" t="n">
+        <v>884.75</v>
+      </c>
+      <c r="E537" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F537" t="n">
+        <v>890.5</v>
+      </c>
+      <c r="G537" t="n">
+        <v>901.89</v>
+      </c>
+      <c r="H537" t="n">
+        <v>-11.39</v>
+      </c>
+      <c r="I537" t="n">
+        <v>874.05</v>
+      </c>
+      <c r="J537" t="n">
+        <v>868.88</v>
+      </c>
+      <c r="K537" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N537" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D538" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="E538" t="n">
+        <v>-36.61</v>
+      </c>
+      <c r="F538" t="n">
+        <v>329.4</v>
+      </c>
+      <c r="G538" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="H538" t="n">
+        <v>-34.96</v>
+      </c>
+      <c r="I538" t="n">
+        <v>323</v>
+      </c>
+      <c r="J538" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="K538" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N538" t="n">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>1165.6</v>
+      </c>
+      <c r="D539" t="n">
+        <v>1215.41</v>
+      </c>
+      <c r="E539" t="n">
+        <v>-49.81</v>
+      </c>
+      <c r="F539" t="n">
+        <v>1184.3</v>
+      </c>
+      <c r="G539" t="n">
+        <v>1215.41</v>
+      </c>
+      <c r="H539" t="n">
+        <v>-31.11</v>
+      </c>
+      <c r="I539" t="n">
+        <v>1147.5</v>
+      </c>
+      <c r="J539" t="n">
+        <v>1135.96</v>
+      </c>
+      <c r="K539" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N539" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>14461</v>
+      </c>
+      <c r="D540" t="n">
+        <v>15959.58</v>
+      </c>
+      <c r="E540" t="n">
+        <v>-1498.58</v>
+      </c>
+      <c r="F540" t="n">
+        <v>14820</v>
+      </c>
+      <c r="G540" t="n">
+        <v>15959.58</v>
+      </c>
+      <c r="H540" t="n">
+        <v>-1139.58</v>
+      </c>
+      <c r="I540" t="n">
+        <v>14450</v>
+      </c>
+      <c r="J540" t="n">
+        <v>14205.39</v>
+      </c>
+      <c r="K540" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N540" t="n">
+        <v>9.390000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -27645,7 +28841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28654,6 +29850,58 @@
       </c>
       <c r="N19" t="n">
         <v>3.45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1165.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1215.41</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-49.81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1184.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1215.41</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-31.11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1147.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1135.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
@@ -30069,7 +31317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30818,6 +32066,58 @@
       </c>
       <c r="N14" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1624.17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1649</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1645.23</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1613.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1587.64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -30831,7 +32131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31892,6 +33192,58 @@
       </c>
       <c r="N20" t="n">
         <v>10.29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-36.61</v>
+      </c>
+      <c r="F21" t="n">
+        <v>329.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-34.96</v>
+      </c>
+      <c r="I21" t="n">
+        <v>323</v>
+      </c>
+      <c r="J21" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>10.05</v>
       </c>
     </row>
   </sheetData>
@@ -31905,7 +33257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32966,6 +34318,58 @@
       </c>
       <c r="N20" t="n">
         <v>9.49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14461</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15959.58</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1498.58</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14820</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15959.58</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1139.58</v>
+      </c>
+      <c r="I21" t="n">
+        <v>14450</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14205.39</v>
+      </c>
+      <c r="K21" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>9.390000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -33949,7 +35353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34906,6 +36310,58 @@
       </c>
       <c r="N18" t="n">
         <v>3.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6048.28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-248.28</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5852.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6048.28</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-195.78</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5603</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5660.68</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-57.68</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
@@ -34919,7 +36375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35928,6 +37384,58 @@
       </c>
       <c r="N19" t="n">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="D20" t="n">
+        <v>115.53</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F20" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="J20" t="n">
+        <v>113.12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -27352,31 +27352,31 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>2234</v>
+        <v>2223.4</v>
       </c>
       <c r="D518" t="n">
         <v>2250.81</v>
       </c>
       <c r="E518" t="n">
-        <v>-16.81</v>
+        <v>-27.41</v>
       </c>
       <c r="F518" t="n">
-        <v>2258.8</v>
+        <v>2264.9</v>
       </c>
       <c r="G518" t="n">
         <v>2263.59</v>
       </c>
       <c r="H518" t="n">
-        <v>-4.79</v>
+        <v>1.31</v>
       </c>
       <c r="I518" t="n">
-        <v>2214</v>
+        <v>2207.1</v>
       </c>
       <c r="J518" t="n">
         <v>2180.01</v>
       </c>
       <c r="K518" t="n">
-        <v>33.99</v>
+        <v>27.09</v>
       </c>
       <c r="L518" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="519">
@@ -27404,31 +27404,31 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>490</v>
+        <v>483.15</v>
       </c>
       <c r="D519" t="n">
         <v>500.52</v>
       </c>
       <c r="E519" t="n">
-        <v>-10.52</v>
+        <v>-17.37</v>
       </c>
       <c r="F519" t="n">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="G519" t="n">
         <v>502.56</v>
       </c>
       <c r="H519" t="n">
-        <v>-9.56</v>
+        <v>-2.56</v>
       </c>
       <c r="I519" t="n">
-        <v>484.2</v>
+        <v>479.25</v>
       </c>
       <c r="J519" t="n">
         <v>484.21</v>
       </c>
       <c r="K519" t="n">
-        <v>-0.01</v>
+        <v>-4.96</v>
       </c>
       <c r="L519" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>2.1</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="520">
@@ -27456,31 +27456,31 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>5555</v>
+        <v>5450</v>
       </c>
       <c r="D520" t="n">
         <v>5570.27</v>
       </c>
       <c r="E520" t="n">
-        <v>-15.27</v>
+        <v>-120.27</v>
       </c>
       <c r="F520" t="n">
-        <v>5659</v>
+        <v>5614</v>
       </c>
       <c r="G520" t="n">
         <v>5674.7</v>
       </c>
       <c r="H520" t="n">
-        <v>-15.7</v>
+        <v>-60.7</v>
       </c>
       <c r="I520" t="n">
-        <v>5495.5</v>
+        <v>5450</v>
       </c>
       <c r="J520" t="n">
         <v>5466.75</v>
       </c>
       <c r="K520" t="n">
-        <v>28.75</v>
+        <v>-16.75</v>
       </c>
       <c r="L520" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>0.27</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="521">
@@ -27508,31 +27508,31 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>115.22</v>
+        <v>114.23</v>
       </c>
       <c r="D521" t="n">
         <v>115.53</v>
       </c>
       <c r="E521" t="n">
-        <v>-0.31</v>
+        <v>-1.3</v>
       </c>
       <c r="F521" t="n">
-        <v>116.5</v>
+        <v>115.35</v>
       </c>
       <c r="G521" t="n">
         <v>117.44</v>
       </c>
       <c r="H521" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.09</v>
       </c>
       <c r="I521" t="n">
-        <v>114.07</v>
+        <v>113.16</v>
       </c>
       <c r="J521" t="n">
         <v>113.12</v>
       </c>
       <c r="K521" t="n">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="L521" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>0.27</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="522">
@@ -27560,31 +27560,31 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>5800</v>
+        <v>5594.5</v>
       </c>
       <c r="D522" t="n">
         <v>6048.28</v>
       </c>
       <c r="E522" t="n">
-        <v>-248.28</v>
+        <v>-453.78</v>
       </c>
       <c r="F522" t="n">
-        <v>5852.5</v>
+        <v>5855.5</v>
       </c>
       <c r="G522" t="n">
         <v>6048.28</v>
       </c>
       <c r="H522" t="n">
-        <v>-195.78</v>
+        <v>-192.78</v>
       </c>
       <c r="I522" t="n">
-        <v>5603</v>
+        <v>5593</v>
       </c>
       <c r="J522" t="n">
         <v>5660.68</v>
       </c>
       <c r="K522" t="n">
-        <v>-57.68</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="L522" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="523">
@@ -27612,31 +27612,31 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>1016</v>
+        <v>1042.9</v>
       </c>
       <c r="D523" t="n">
         <v>1018.71</v>
       </c>
       <c r="E523" t="n">
-        <v>-2.71</v>
+        <v>24.19</v>
       </c>
       <c r="F523" t="n">
-        <v>1047.9</v>
+        <v>1045.35</v>
       </c>
       <c r="G523" t="n">
         <v>1022.73</v>
       </c>
       <c r="H523" t="n">
-        <v>25.17</v>
+        <v>22.62</v>
       </c>
       <c r="I523" t="n">
-        <v>1008</v>
+        <v>1022</v>
       </c>
       <c r="J523" t="n">
         <v>984.74</v>
       </c>
       <c r="K523" t="n">
-        <v>23.26</v>
+        <v>37.26</v>
       </c>
       <c r="L523" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>0.27</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="524">
@@ -27664,31 +27664,31 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>1356</v>
+        <v>1313</v>
       </c>
       <c r="D524" t="n">
         <v>1441.03</v>
       </c>
       <c r="E524" t="n">
-        <v>-85.03</v>
+        <v>-128.03</v>
       </c>
       <c r="F524" t="n">
-        <v>1371.7</v>
+        <v>1358</v>
       </c>
       <c r="G524" t="n">
         <v>1441.03</v>
       </c>
       <c r="H524" t="n">
-        <v>-69.33</v>
+        <v>-83.03</v>
       </c>
       <c r="I524" t="n">
-        <v>1327.2</v>
+        <v>1313</v>
       </c>
       <c r="J524" t="n">
         <v>1353.04</v>
       </c>
       <c r="K524" t="n">
-        <v>-25.84</v>
+        <v>-40.04</v>
       </c>
       <c r="L524" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>5.9</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="525">
@@ -27716,31 +27716,31 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>1880.7</v>
+        <v>1868</v>
       </c>
       <c r="D525" t="n">
         <v>1922.29</v>
       </c>
       <c r="E525" t="n">
-        <v>-41.59</v>
+        <v>-54.29</v>
       </c>
       <c r="F525" t="n">
-        <v>1887.2</v>
+        <v>1875.3</v>
       </c>
       <c r="G525" t="n">
         <v>1922.29</v>
       </c>
       <c r="H525" t="n">
-        <v>-35.09</v>
+        <v>-46.99</v>
       </c>
       <c r="I525" t="n">
-        <v>1846.6</v>
+        <v>1842.1</v>
       </c>
       <c r="J525" t="n">
         <v>1810.61</v>
       </c>
       <c r="K525" t="n">
-        <v>35.99</v>
+        <v>31.49</v>
       </c>
       <c r="L525" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="526">
@@ -27768,31 +27768,31 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>1274.4</v>
+        <v>1276</v>
       </c>
       <c r="D526" t="n">
         <v>1299.98</v>
       </c>
       <c r="E526" t="n">
-        <v>-25.58</v>
+        <v>-23.98</v>
       </c>
       <c r="F526" t="n">
-        <v>1307.5</v>
+        <v>1292.5</v>
       </c>
       <c r="G526" t="n">
         <v>1299.98</v>
       </c>
       <c r="H526" t="n">
-        <v>7.52</v>
+        <v>-7.48</v>
       </c>
       <c r="I526" t="n">
-        <v>1261.5</v>
+        <v>1261.1</v>
       </c>
       <c r="J526" t="n">
         <v>1246.75</v>
       </c>
       <c r="K526" t="n">
-        <v>14.75</v>
+        <v>14.35</v>
       </c>
       <c r="L526" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="527">
@@ -27820,31 +27820,31 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>292.3</v>
+        <v>300.6</v>
       </c>
       <c r="D527" t="n">
         <v>289.91</v>
       </c>
       <c r="E527" t="n">
-        <v>2.39</v>
+        <v>10.69</v>
       </c>
       <c r="F527" t="n">
-        <v>296.65</v>
+        <v>300.6</v>
       </c>
       <c r="G527" t="n">
         <v>290.28</v>
       </c>
       <c r="H527" t="n">
-        <v>6.37</v>
+        <v>10.32</v>
       </c>
       <c r="I527" t="n">
-        <v>290.4</v>
+        <v>289</v>
       </c>
       <c r="J527" t="n">
         <v>283.08</v>
       </c>
       <c r="K527" t="n">
-        <v>7.32</v>
+        <v>5.92</v>
       </c>
       <c r="L527" t="inlineStr">
         <is>
@@ -27853,11 +27853,11 @@
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N527" t="n">
-        <v>0.82</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="528">
@@ -27872,31 +27872,31 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>184.9</v>
+        <v>188.63</v>
       </c>
       <c r="D528" t="n">
         <v>175.25</v>
       </c>
       <c r="E528" t="n">
-        <v>9.65</v>
+        <v>13.38</v>
       </c>
       <c r="F528" t="n">
-        <v>186.32</v>
+        <v>188.63</v>
       </c>
       <c r="G528" t="n">
         <v>189.58</v>
       </c>
       <c r="H528" t="n">
-        <v>-3.26</v>
+        <v>-0.95</v>
       </c>
       <c r="I528" t="n">
-        <v>183.26</v>
+        <v>181.8</v>
       </c>
       <c r="J528" t="n">
         <v>182.65</v>
       </c>
       <c r="K528" t="n">
-        <v>0.61</v>
+        <v>-0.85</v>
       </c>
       <c r="L528" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>5.51</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="529">
@@ -27924,31 +27924,31 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>1391</v>
+        <v>1402.5</v>
       </c>
       <c r="D529" t="n">
         <v>1394.82</v>
       </c>
       <c r="E529" t="n">
-        <v>-3.82</v>
+        <v>7.68</v>
       </c>
       <c r="F529" t="n">
-        <v>1407.4</v>
+        <v>1413.9</v>
       </c>
       <c r="G529" t="n">
         <v>1415.1</v>
       </c>
       <c r="H529" t="n">
-        <v>-7.7</v>
+        <v>-1.2</v>
       </c>
       <c r="I529" t="n">
-        <v>1376</v>
+        <v>1382.7</v>
       </c>
       <c r="J529" t="n">
         <v>1363.05</v>
       </c>
       <c r="K529" t="n">
-        <v>12.95</v>
+        <v>19.65</v>
       </c>
       <c r="L529" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>0.27</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="530">
@@ -27976,31 +27976,31 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>170.53</v>
+        <v>175.64</v>
       </c>
       <c r="D530" t="n">
         <v>171.94</v>
       </c>
       <c r="E530" t="n">
-        <v>-1.41</v>
+        <v>3.7</v>
       </c>
       <c r="F530" t="n">
-        <v>176.5</v>
+        <v>176.6</v>
       </c>
       <c r="G530" t="n">
         <v>172.75</v>
       </c>
       <c r="H530" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I530" t="n">
-        <v>168.53</v>
+        <v>173.82</v>
       </c>
       <c r="J530" t="n">
         <v>166.37</v>
       </c>
       <c r="K530" t="n">
-        <v>2.16</v>
+        <v>7.45</v>
       </c>
       <c r="L530" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>0.82</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="531">
@@ -28028,31 +28028,31 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>11310</v>
+        <v>11644</v>
       </c>
       <c r="D531" t="n">
         <v>11246.12</v>
       </c>
       <c r="E531" t="n">
-        <v>63.88</v>
+        <v>397.88</v>
       </c>
       <c r="F531" t="n">
-        <v>11500</v>
+        <v>11644</v>
       </c>
       <c r="G531" t="n">
         <v>11246.12</v>
       </c>
       <c r="H531" t="n">
-        <v>253.88</v>
+        <v>397.88</v>
       </c>
       <c r="I531" t="n">
-        <v>11282</v>
+        <v>11230</v>
       </c>
       <c r="J531" t="n">
         <v>10961.51</v>
       </c>
       <c r="K531" t="n">
-        <v>320.49</v>
+        <v>268.49</v>
       </c>
       <c r="L531" t="inlineStr">
         <is>
@@ -28061,11 +28061,11 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N531" t="n">
-        <v>0.57</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="532">
@@ -28080,31 +28080,31 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="D532" t="n">
         <v>1624.17</v>
       </c>
       <c r="E532" t="n">
-        <v>13.83</v>
+        <v>3.83</v>
       </c>
       <c r="F532" t="n">
-        <v>1649</v>
+        <v>1640.9</v>
       </c>
       <c r="G532" t="n">
         <v>1645.23</v>
       </c>
       <c r="H532" t="n">
-        <v>3.77</v>
+        <v>-4.33</v>
       </c>
       <c r="I532" t="n">
-        <v>1613.7</v>
+        <v>1609.1</v>
       </c>
       <c r="J532" t="n">
         <v>1587.64</v>
       </c>
       <c r="K532" t="n">
-        <v>26.06</v>
+        <v>21.46</v>
       </c>
       <c r="L532" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>0.85</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="533">
@@ -28132,31 +28132,31 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>1829.2</v>
+        <v>1875</v>
       </c>
       <c r="D533" t="n">
         <v>1805.59</v>
       </c>
       <c r="E533" t="n">
-        <v>23.61</v>
+        <v>69.41</v>
       </c>
       <c r="F533" t="n">
-        <v>1847.8</v>
+        <v>1875</v>
       </c>
       <c r="G533" t="n">
         <v>1864.08</v>
       </c>
       <c r="H533" t="n">
-        <v>-16.28</v>
+        <v>10.92</v>
       </c>
       <c r="I533" t="n">
-        <v>1812.1</v>
+        <v>1796.4</v>
       </c>
       <c r="J533" t="n">
         <v>1795.61</v>
       </c>
       <c r="K533" t="n">
-        <v>16.49</v>
+        <v>0.79</v>
       </c>
       <c r="L533" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>1.31</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="534">
@@ -28184,31 +28184,31 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>675.15</v>
+        <v>691.05</v>
       </c>
       <c r="D534" t="n">
         <v>652.14</v>
       </c>
       <c r="E534" t="n">
-        <v>23.01</v>
+        <v>38.91</v>
       </c>
       <c r="F534" t="n">
-        <v>676</v>
+        <v>691.05</v>
       </c>
       <c r="G534" t="n">
         <v>688</v>
       </c>
       <c r="H534" t="n">
-        <v>-12</v>
+        <v>3.05</v>
       </c>
       <c r="I534" t="n">
-        <v>665.95</v>
+        <v>664</v>
       </c>
       <c r="J534" t="n">
         <v>662.73</v>
       </c>
       <c r="K534" t="n">
-        <v>3.22</v>
+        <v>1.27</v>
       </c>
       <c r="L534" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>3.53</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="535">
@@ -28236,31 +28236,31 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>3303</v>
+        <v>3400</v>
       </c>
       <c r="D535" t="n">
         <v>3001.21</v>
       </c>
       <c r="E535" t="n">
-        <v>301.79</v>
+        <v>398.79</v>
       </c>
       <c r="F535" t="n">
-        <v>3369</v>
+        <v>3400</v>
       </c>
       <c r="G535" t="n">
         <v>3314.16</v>
       </c>
       <c r="H535" t="n">
-        <v>54.84</v>
+        <v>85.84</v>
       </c>
       <c r="I535" t="n">
-        <v>3255.2</v>
+        <v>3300</v>
       </c>
       <c r="J535" t="n">
         <v>3190.66</v>
       </c>
       <c r="K535" t="n">
-        <v>64.54000000000001</v>
+        <v>109.34</v>
       </c>
       <c r="L535" t="inlineStr">
         <is>
@@ -28269,11 +28269,11 @@
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N535" t="n">
-        <v>10.06</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="536">
@@ -28288,31 +28288,31 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>2179.8</v>
+        <v>2205</v>
       </c>
       <c r="D536" t="n">
         <v>2296.73</v>
       </c>
       <c r="E536" t="n">
-        <v>-116.93</v>
+        <v>-91.73</v>
       </c>
       <c r="F536" t="n">
-        <v>2260</v>
+        <v>2280</v>
       </c>
       <c r="G536" t="n">
         <v>2296.73</v>
       </c>
       <c r="H536" t="n">
-        <v>-36.73</v>
+        <v>-16.73</v>
       </c>
       <c r="I536" t="n">
-        <v>2156.2</v>
+        <v>2205</v>
       </c>
       <c r="J536" t="n">
         <v>2127.36</v>
       </c>
       <c r="K536" t="n">
-        <v>28.84</v>
+        <v>77.64</v>
       </c>
       <c r="L536" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>5.09</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="537">
@@ -28340,31 +28340,31 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>881.75</v>
+        <v>898.75</v>
       </c>
       <c r="D537" t="n">
         <v>884.75</v>
       </c>
       <c r="E537" t="n">
-        <v>-3</v>
+        <v>14</v>
       </c>
       <c r="F537" t="n">
-        <v>890.5</v>
+        <v>898.75</v>
       </c>
       <c r="G537" t="n">
         <v>901.89</v>
       </c>
       <c r="H537" t="n">
-        <v>-11.39</v>
+        <v>-3.14</v>
       </c>
       <c r="I537" t="n">
-        <v>874.05</v>
+        <v>864.8</v>
       </c>
       <c r="J537" t="n">
         <v>868.88</v>
       </c>
       <c r="K537" t="n">
-        <v>5.17</v>
+        <v>-4.08</v>
       </c>
       <c r="L537" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>0.34</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="538">
@@ -28392,31 +28392,31 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>327.75</v>
+        <v>328.1</v>
       </c>
       <c r="D538" t="n">
         <v>364.36</v>
       </c>
       <c r="E538" t="n">
-        <v>-36.61</v>
+        <v>-36.26</v>
       </c>
       <c r="F538" t="n">
-        <v>329.4</v>
+        <v>332.95</v>
       </c>
       <c r="G538" t="n">
         <v>364.36</v>
       </c>
       <c r="H538" t="n">
-        <v>-34.96</v>
+        <v>-31.41</v>
       </c>
       <c r="I538" t="n">
-        <v>323</v>
+        <v>315.8</v>
       </c>
       <c r="J538" t="n">
         <v>321.06</v>
       </c>
       <c r="K538" t="n">
-        <v>1.94</v>
+        <v>-5.26</v>
       </c>
       <c r="L538" t="inlineStr">
         <is>
@@ -28425,11 +28425,11 @@
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N538" t="n">
-        <v>10.05</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="539">
@@ -28444,31 +28444,31 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>1165.6</v>
+        <v>1175</v>
       </c>
       <c r="D539" t="n">
         <v>1215.41</v>
       </c>
       <c r="E539" t="n">
-        <v>-49.81</v>
+        <v>-40.41</v>
       </c>
       <c r="F539" t="n">
-        <v>1184.3</v>
+        <v>1199.6</v>
       </c>
       <c r="G539" t="n">
         <v>1215.41</v>
       </c>
       <c r="H539" t="n">
-        <v>-31.11</v>
+        <v>-15.81</v>
       </c>
       <c r="I539" t="n">
-        <v>1147.5</v>
+        <v>1149.3</v>
       </c>
       <c r="J539" t="n">
         <v>1135.96</v>
       </c>
       <c r="K539" t="n">
-        <v>11.54</v>
+        <v>13.34</v>
       </c>
       <c r="L539" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         </is>
       </c>
       <c r="N539" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="540">
@@ -28496,31 +28496,31 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>14461</v>
+        <v>14850</v>
       </c>
       <c r="D540" t="n">
         <v>15959.58</v>
       </c>
       <c r="E540" t="n">
-        <v>-1498.58</v>
+        <v>-1109.58</v>
       </c>
       <c r="F540" t="n">
-        <v>14820</v>
+        <v>14850</v>
       </c>
       <c r="G540" t="n">
         <v>15959.58</v>
       </c>
       <c r="H540" t="n">
-        <v>-1139.58</v>
+        <v>-1109.58</v>
       </c>
       <c r="I540" t="n">
-        <v>14450</v>
+        <v>14601</v>
       </c>
       <c r="J540" t="n">
         <v>14205.39</v>
       </c>
       <c r="K540" t="n">
-        <v>244.61</v>
+        <v>395.61</v>
       </c>
       <c r="L540" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         </is>
       </c>
       <c r="N540" t="n">
-        <v>9.390000000000001</v>
+        <v>6.95</v>
       </c>
     </row>
   </sheetData>
@@ -29864,31 +29864,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1165.6</v>
+        <v>1175</v>
       </c>
       <c r="D20" t="n">
         <v>1215.41</v>
       </c>
       <c r="E20" t="n">
-        <v>-49.81</v>
+        <v>-40.41</v>
       </c>
       <c r="F20" t="n">
-        <v>1184.3</v>
+        <v>1199.6</v>
       </c>
       <c r="G20" t="n">
         <v>1215.41</v>
       </c>
       <c r="H20" t="n">
-        <v>-31.11</v>
+        <v>-15.81</v>
       </c>
       <c r="I20" t="n">
-        <v>1147.5</v>
+        <v>1149.3</v>
       </c>
       <c r="J20" t="n">
         <v>1135.96</v>
       </c>
       <c r="K20" t="n">
-        <v>11.54</v>
+        <v>13.34</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
     </row>
   </sheetData>
@@ -32080,31 +32080,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="D15" t="n">
         <v>1624.17</v>
       </c>
       <c r="E15" t="n">
-        <v>13.83</v>
+        <v>3.83</v>
       </c>
       <c r="F15" t="n">
-        <v>1649</v>
+        <v>1640.9</v>
       </c>
       <c r="G15" t="n">
         <v>1645.23</v>
       </c>
       <c r="H15" t="n">
-        <v>3.77</v>
+        <v>-4.33</v>
       </c>
       <c r="I15" t="n">
-        <v>1613.7</v>
+        <v>1609.1</v>
       </c>
       <c r="J15" t="n">
         <v>1587.64</v>
       </c>
       <c r="K15" t="n">
-        <v>26.06</v>
+        <v>21.46</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.85</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -33206,31 +33206,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>327.75</v>
+        <v>328.1</v>
       </c>
       <c r="D21" t="n">
         <v>364.36</v>
       </c>
       <c r="E21" t="n">
-        <v>-36.61</v>
+        <v>-36.26</v>
       </c>
       <c r="F21" t="n">
-        <v>329.4</v>
+        <v>332.95</v>
       </c>
       <c r="G21" t="n">
         <v>364.36</v>
       </c>
       <c r="H21" t="n">
-        <v>-34.96</v>
+        <v>-31.41</v>
       </c>
       <c r="I21" t="n">
-        <v>323</v>
+        <v>315.8</v>
       </c>
       <c r="J21" t="n">
         <v>321.06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.94</v>
+        <v>-5.26</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -33239,11 +33239,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10.05</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -34332,31 +34332,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14461</v>
+        <v>14850</v>
       </c>
       <c r="D21" t="n">
         <v>15959.58</v>
       </c>
       <c r="E21" t="n">
-        <v>-1498.58</v>
+        <v>-1109.58</v>
       </c>
       <c r="F21" t="n">
-        <v>14820</v>
+        <v>14850</v>
       </c>
       <c r="G21" t="n">
         <v>15959.58</v>
       </c>
       <c r="H21" t="n">
-        <v>-1139.58</v>
+        <v>-1109.58</v>
       </c>
       <c r="I21" t="n">
-        <v>14450</v>
+        <v>14601</v>
       </c>
       <c r="J21" t="n">
         <v>14205.39</v>
       </c>
       <c r="K21" t="n">
-        <v>244.61</v>
+        <v>395.61</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>9.390000000000001</v>
+        <v>6.95</v>
       </c>
     </row>
   </sheetData>
@@ -36324,31 +36324,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5800</v>
+        <v>5594.5</v>
       </c>
       <c r="D19" t="n">
         <v>6048.28</v>
       </c>
       <c r="E19" t="n">
-        <v>-248.28</v>
+        <v>-453.78</v>
       </c>
       <c r="F19" t="n">
-        <v>5852.5</v>
+        <v>5855.5</v>
       </c>
       <c r="G19" t="n">
         <v>6048.28</v>
       </c>
       <c r="H19" t="n">
-        <v>-195.78</v>
+        <v>-192.78</v>
       </c>
       <c r="I19" t="n">
-        <v>5603</v>
+        <v>5593</v>
       </c>
       <c r="J19" t="n">
         <v>5660.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-57.68</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -37398,31 +37398,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>115.22</v>
+        <v>114.23</v>
       </c>
       <c r="D20" t="n">
         <v>115.53</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.31</v>
+        <v>-1.3</v>
       </c>
       <c r="F20" t="n">
-        <v>116.5</v>
+        <v>115.35</v>
       </c>
       <c r="G20" t="n">
         <v>117.44</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.09</v>
       </c>
       <c r="I20" t="n">
-        <v>114.07</v>
+        <v>113.16</v>
       </c>
       <c r="J20" t="n">
         <v>113.12</v>
       </c>
       <c r="K20" t="n">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.27</v>
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N540"/>
+  <dimension ref="A1:N560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28534,6 +28534,1046 @@
       </c>
       <c r="N540" t="n">
         <v>6.95</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>498.15</v>
+      </c>
+      <c r="D541" t="n">
+        <v>484.72</v>
+      </c>
+      <c r="E541" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F541" t="n">
+        <v>499.5</v>
+      </c>
+      <c r="G541" t="n">
+        <v>507.41</v>
+      </c>
+      <c r="H541" t="n">
+        <v>-7.91</v>
+      </c>
+      <c r="I541" t="n">
+        <v>484.15</v>
+      </c>
+      <c r="J541" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="K541" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N541" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>1851.9</v>
+      </c>
+      <c r="D542" t="n">
+        <v>1938.48</v>
+      </c>
+      <c r="E542" t="n">
+        <v>-86.58</v>
+      </c>
+      <c r="F542" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G542" t="n">
+        <v>1938.48</v>
+      </c>
+      <c r="H542" t="n">
+        <v>-78.48</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1810</v>
+      </c>
+      <c r="J542" t="n">
+        <v>1850.43</v>
+      </c>
+      <c r="K542" t="n">
+        <v>-40.43</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N542" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>1017.6</v>
+      </c>
+      <c r="D543" t="n">
+        <v>1050.1</v>
+      </c>
+      <c r="E543" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="F543" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G543" t="n">
+        <v>1050.1</v>
+      </c>
+      <c r="H543" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="I543" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="J543" t="n">
+        <v>999.5599999999999</v>
+      </c>
+      <c r="K543" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N543" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>186.86</v>
+      </c>
+      <c r="D544" t="n">
+        <v>202.76</v>
+      </c>
+      <c r="E544" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="F544" t="n">
+        <v>186.86</v>
+      </c>
+      <c r="G544" t="n">
+        <v>202.76</v>
+      </c>
+      <c r="H544" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="I544" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J544" t="n">
+        <v>186.86</v>
+      </c>
+      <c r="K544" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N544" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D545" t="n">
+        <v>2206.49</v>
+      </c>
+      <c r="E545" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F545" t="n">
+        <v>2228.5</v>
+      </c>
+      <c r="G545" t="n">
+        <v>2266.33</v>
+      </c>
+      <c r="H545" t="n">
+        <v>-37.83</v>
+      </c>
+      <c r="I545" t="n">
+        <v>2186.7</v>
+      </c>
+      <c r="J545" t="n">
+        <v>2210</v>
+      </c>
+      <c r="K545" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N545" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>117</v>
+      </c>
+      <c r="D546" t="n">
+        <v>116.69</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F546" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="G546" t="n">
+        <v>119.38</v>
+      </c>
+      <c r="H546" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I546" t="n">
+        <v>113.92</v>
+      </c>
+      <c r="J546" t="n">
+        <v>117</v>
+      </c>
+      <c r="K546" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N546" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="D547" t="n">
+        <v>719.45</v>
+      </c>
+      <c r="E547" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="F547" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="G547" t="n">
+        <v>719.45</v>
+      </c>
+      <c r="H547" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="I547" t="n">
+        <v>651.3</v>
+      </c>
+      <c r="J547" t="n">
+        <v>668.0599999999999</v>
+      </c>
+      <c r="K547" t="n">
+        <v>-16.76</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N547" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="D548" t="n">
+        <v>297.09</v>
+      </c>
+      <c r="E548" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="F548" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="G548" t="n">
+        <v>327.62</v>
+      </c>
+      <c r="H548" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I548" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="J548" t="n">
+        <v>321.54</v>
+      </c>
+      <c r="K548" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N548" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D549" t="n">
+        <v>5305.18</v>
+      </c>
+      <c r="E549" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="F549" t="n">
+        <v>5738</v>
+      </c>
+      <c r="G549" t="n">
+        <v>5594.23</v>
+      </c>
+      <c r="H549" t="n">
+        <v>143.77</v>
+      </c>
+      <c r="I549" t="n">
+        <v>5640.5</v>
+      </c>
+      <c r="J549" t="n">
+        <v>5556.38</v>
+      </c>
+      <c r="K549" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N549" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>1181.3</v>
+      </c>
+      <c r="D550" t="n">
+        <v>1151.16</v>
+      </c>
+      <c r="E550" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="F550" t="n">
+        <v>1181.3</v>
+      </c>
+      <c r="G550" t="n">
+        <v>1196.76</v>
+      </c>
+      <c r="H550" t="n">
+        <v>-15.46</v>
+      </c>
+      <c r="I550" t="n">
+        <v>1128.6</v>
+      </c>
+      <c r="J550" t="n">
+        <v>1172.55</v>
+      </c>
+      <c r="K550" t="n">
+        <v>-43.95</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N550" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>1236</v>
+      </c>
+      <c r="D551" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="E551" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F551" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G551" t="n">
+        <v>1258.19</v>
+      </c>
+      <c r="H551" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="I551" t="n">
+        <v>1228.3</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1232.95</v>
+      </c>
+      <c r="K551" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N551" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D552" t="n">
+        <v>1827.81</v>
+      </c>
+      <c r="E552" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="F552" t="n">
+        <v>1869</v>
+      </c>
+      <c r="G552" t="n">
+        <v>1891.04</v>
+      </c>
+      <c r="H552" t="n">
+        <v>-22.04</v>
+      </c>
+      <c r="I552" t="n">
+        <v>1828.9</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1852.83</v>
+      </c>
+      <c r="K552" t="n">
+        <v>-23.93</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N552" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1365.2</v>
+      </c>
+      <c r="D553" t="n">
+        <v>1383.7</v>
+      </c>
+      <c r="E553" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="F553" t="n">
+        <v>1379.7</v>
+      </c>
+      <c r="G553" t="n">
+        <v>1383.7</v>
+      </c>
+      <c r="H553" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I553" t="n">
+        <v>1355.9</v>
+      </c>
+      <c r="J553" t="n">
+        <v>1352.81</v>
+      </c>
+      <c r="K553" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N553" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="D554" t="n">
+        <v>302.26</v>
+      </c>
+      <c r="E554" t="n">
+        <v>-13.06</v>
+      </c>
+      <c r="F554" t="n">
+        <v>294</v>
+      </c>
+      <c r="G554" t="n">
+        <v>302.26</v>
+      </c>
+      <c r="H554" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="I554" t="n">
+        <v>288.35</v>
+      </c>
+      <c r="J554" t="n">
+        <v>286.68</v>
+      </c>
+      <c r="K554" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N554" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>14590</v>
+      </c>
+      <c r="D555" t="n">
+        <v>13684.31</v>
+      </c>
+      <c r="E555" t="n">
+        <v>905.6900000000001</v>
+      </c>
+      <c r="F555" t="n">
+        <v>14620</v>
+      </c>
+      <c r="G555" t="n">
+        <v>14833.46</v>
+      </c>
+      <c r="H555" t="n">
+        <v>-213.46</v>
+      </c>
+      <c r="I555" t="n">
+        <v>14315</v>
+      </c>
+      <c r="J555" t="n">
+        <v>14535.34</v>
+      </c>
+      <c r="K555" t="n">
+        <v>-220.34</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N555" t="n">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>3286</v>
+      </c>
+      <c r="D556" t="n">
+        <v>3766.38</v>
+      </c>
+      <c r="E556" t="n">
+        <v>-480.38</v>
+      </c>
+      <c r="F556" t="n">
+        <v>3333</v>
+      </c>
+      <c r="G556" t="n">
+        <v>3766.38</v>
+      </c>
+      <c r="H556" t="n">
+        <v>-433.38</v>
+      </c>
+      <c r="I556" t="n">
+        <v>3258</v>
+      </c>
+      <c r="J556" t="n">
+        <v>3286</v>
+      </c>
+      <c r="K556" t="n">
+        <v>-28</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N556" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="D557" t="n">
+        <v>585.1900000000001</v>
+      </c>
+      <c r="E557" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F557" t="n">
+        <v>592.9</v>
+      </c>
+      <c r="G557" t="n">
+        <v>592</v>
+      </c>
+      <c r="H557" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I557" t="n">
+        <v>581.3</v>
+      </c>
+      <c r="J557" t="n">
+        <v>579.89</v>
+      </c>
+      <c r="K557" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N557" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>1623</v>
+      </c>
+      <c r="D558" t="n">
+        <v>1639.84</v>
+      </c>
+      <c r="E558" t="n">
+        <v>-16.84</v>
+      </c>
+      <c r="F558" t="n">
+        <v>1637.2</v>
+      </c>
+      <c r="G558" t="n">
+        <v>1639.84</v>
+      </c>
+      <c r="H558" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="I558" t="n">
+        <v>1604.5</v>
+      </c>
+      <c r="J558" t="n">
+        <v>1597.15</v>
+      </c>
+      <c r="K558" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N558" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>1343.7</v>
+      </c>
+      <c r="D559" t="n">
+        <v>1234.11</v>
+      </c>
+      <c r="E559" t="n">
+        <v>109.59</v>
+      </c>
+      <c r="F559" t="n">
+        <v>1352.4</v>
+      </c>
+      <c r="G559" t="n">
+        <v>1359.57</v>
+      </c>
+      <c r="H559" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="I559" t="n">
+        <v>1314.8</v>
+      </c>
+      <c r="J559" t="n">
+        <v>1332.02</v>
+      </c>
+      <c r="K559" t="n">
+        <v>-17.22</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N559" t="n">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>878.8</v>
+      </c>
+      <c r="D560" t="n">
+        <v>901.28</v>
+      </c>
+      <c r="E560" t="n">
+        <v>-22.48</v>
+      </c>
+      <c r="F560" t="n">
+        <v>884.4</v>
+      </c>
+      <c r="G560" t="n">
+        <v>901.28</v>
+      </c>
+      <c r="H560" t="n">
+        <v>-16.88</v>
+      </c>
+      <c r="I560" t="n">
+        <v>866</v>
+      </c>
+      <c r="J560" t="n">
+        <v>878.8</v>
+      </c>
+      <c r="K560" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N560" t="n">
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>
@@ -28841,7 +29881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29902,6 +30942,58 @@
       </c>
       <c r="N20" t="n">
         <v>3.32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1181.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1151.16</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1181.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1196.76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-15.46</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1128.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1172.55</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-43.95</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>
@@ -31317,7 +32409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32118,6 +33210,58 @@
       </c>
       <c r="N15" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1623</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1639.84</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-16.84</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1637.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1639.84</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1604.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1597.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -32131,7 +33275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33244,6 +34388,58 @@
       </c>
       <c r="N21" t="n">
         <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>297.09</v>
+      </c>
+      <c r="E22" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="F22" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>327.62</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>321.54</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>10.17</v>
       </c>
     </row>
   </sheetData>
@@ -33257,7 +34453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34370,6 +35566,58 @@
       </c>
       <c r="N21" t="n">
         <v>6.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>14590</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13684.31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>905.6900000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14620</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14833.46</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-213.46</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14315</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14535.34</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-220.34</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>6.62</v>
       </c>
     </row>
   </sheetData>
@@ -35353,7 +36601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36362,6 +37610,58 @@
       </c>
       <c r="N19" t="n">
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5305.18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5738</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5594.23</v>
+      </c>
+      <c r="H20" t="n">
+        <v>143.77</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5640.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5556.38</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -36375,7 +37675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37436,6 +38736,58 @@
       </c>
       <c r="N20" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>117</v>
+      </c>
+      <c r="D21" t="n">
+        <v>116.69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F21" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>119.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I21" t="n">
+        <v>113.92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>117</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -28548,31 +28548,31 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>498.15</v>
+        <v>490</v>
       </c>
       <c r="D541" t="n">
         <v>484.72</v>
       </c>
       <c r="E541" t="n">
-        <v>13.43</v>
+        <v>5.28</v>
       </c>
       <c r="F541" t="n">
-        <v>499.5</v>
+        <v>493</v>
       </c>
       <c r="G541" t="n">
         <v>507.41</v>
       </c>
       <c r="H541" t="n">
-        <v>-7.91</v>
+        <v>-14.41</v>
       </c>
       <c r="I541" t="n">
-        <v>484.15</v>
+        <v>484.2</v>
       </c>
       <c r="J541" t="n">
         <v>497.25</v>
       </c>
       <c r="K541" t="n">
-        <v>-13.1</v>
+        <v>-13.05</v>
       </c>
       <c r="L541" t="inlineStr">
         <is>
@@ -28581,11 +28581,11 @@
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N541" t="n">
-        <v>2.77</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="542">
@@ -28600,31 +28600,31 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>1851.9</v>
+        <v>1829.2</v>
       </c>
       <c r="D542" t="n">
         <v>1938.48</v>
       </c>
       <c r="E542" t="n">
-        <v>-86.58</v>
+        <v>-109.28</v>
       </c>
       <c r="F542" t="n">
-        <v>1860</v>
+        <v>1847.8</v>
       </c>
       <c r="G542" t="n">
         <v>1938.48</v>
       </c>
       <c r="H542" t="n">
-        <v>-78.48</v>
+        <v>-90.68000000000001</v>
       </c>
       <c r="I542" t="n">
-        <v>1810</v>
+        <v>1812.1</v>
       </c>
       <c r="J542" t="n">
         <v>1850.43</v>
       </c>
       <c r="K542" t="n">
-        <v>-40.43</v>
+        <v>-38.33</v>
       </c>
       <c r="L542" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>4.47</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="543">
@@ -28652,31 +28652,31 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>1017.6</v>
+        <v>1016</v>
       </c>
       <c r="D543" t="n">
         <v>1050.1</v>
       </c>
       <c r="E543" t="n">
-        <v>-32.5</v>
+        <v>-34.1</v>
       </c>
       <c r="F543" t="n">
-        <v>1025</v>
+        <v>1047.9</v>
       </c>
       <c r="G543" t="n">
         <v>1050.1</v>
       </c>
       <c r="H543" t="n">
-        <v>-25.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I543" t="n">
-        <v>993.2</v>
+        <v>1008</v>
       </c>
       <c r="J543" t="n">
         <v>999.5599999999999</v>
       </c>
       <c r="K543" t="n">
-        <v>-6.36</v>
+        <v>8.44</v>
       </c>
       <c r="L543" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         </is>
       </c>
       <c r="N543" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="544">
@@ -28704,31 +28704,31 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>186.86</v>
+        <v>184.9</v>
       </c>
       <c r="D544" t="n">
         <v>202.76</v>
       </c>
       <c r="E544" t="n">
-        <v>-15.9</v>
+        <v>-17.86</v>
       </c>
       <c r="F544" t="n">
-        <v>186.86</v>
+        <v>186.32</v>
       </c>
       <c r="G544" t="n">
         <v>202.76</v>
       </c>
       <c r="H544" t="n">
-        <v>-15.9</v>
+        <v>-16.44</v>
       </c>
       <c r="I544" t="n">
-        <v>182.5</v>
+        <v>183.26</v>
       </c>
       <c r="J544" t="n">
         <v>186.86</v>
       </c>
       <c r="K544" t="n">
-        <v>-4.36</v>
+        <v>-3.6</v>
       </c>
       <c r="L544" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="N544" t="n">
-        <v>7.84</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="545">
@@ -28756,31 +28756,31 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>2210</v>
+        <v>2234</v>
       </c>
       <c r="D545" t="n">
         <v>2206.49</v>
       </c>
       <c r="E545" t="n">
-        <v>3.51</v>
+        <v>27.51</v>
       </c>
       <c r="F545" t="n">
-        <v>2228.5</v>
+        <v>2258.8</v>
       </c>
       <c r="G545" t="n">
         <v>2266.33</v>
       </c>
       <c r="H545" t="n">
-        <v>-37.83</v>
+        <v>-7.53</v>
       </c>
       <c r="I545" t="n">
-        <v>2186.7</v>
+        <v>2214</v>
       </c>
       <c r="J545" t="n">
         <v>2210</v>
       </c>
       <c r="K545" t="n">
-        <v>-23.3</v>
+        <v>4</v>
       </c>
       <c r="L545" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>0.16</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="546">
@@ -28808,31 +28808,31 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>117</v>
+        <v>115.22</v>
       </c>
       <c r="D546" t="n">
         <v>116.69</v>
       </c>
       <c r="E546" t="n">
-        <v>0.31</v>
+        <v>-1.47</v>
       </c>
       <c r="F546" t="n">
-        <v>117.25</v>
+        <v>116.5</v>
       </c>
       <c r="G546" t="n">
         <v>119.38</v>
       </c>
       <c r="H546" t="n">
-        <v>-2.13</v>
+        <v>-2.88</v>
       </c>
       <c r="I546" t="n">
-        <v>113.92</v>
+        <v>114.07</v>
       </c>
       <c r="J546" t="n">
         <v>117</v>
       </c>
       <c r="K546" t="n">
-        <v>-3.08</v>
+        <v>-2.93</v>
       </c>
       <c r="L546" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>0.27</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="547">
@@ -28860,31 +28860,31 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>673.55</v>
+        <v>675.15</v>
       </c>
       <c r="D547" t="n">
         <v>719.45</v>
       </c>
       <c r="E547" t="n">
-        <v>-45.9</v>
+        <v>-44.3</v>
       </c>
       <c r="F547" t="n">
-        <v>673.55</v>
+        <v>676</v>
       </c>
       <c r="G547" t="n">
         <v>719.45</v>
       </c>
       <c r="H547" t="n">
-        <v>-45.9</v>
+        <v>-43.45</v>
       </c>
       <c r="I547" t="n">
-        <v>651.3</v>
+        <v>665.95</v>
       </c>
       <c r="J547" t="n">
         <v>668.0599999999999</v>
       </c>
       <c r="K547" t="n">
-        <v>-16.76</v>
+        <v>-2.11</v>
       </c>
       <c r="L547" t="inlineStr">
         <is>
@@ -28893,11 +28893,11 @@
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N547" t="n">
-        <v>6.38</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="548">
@@ -28912,31 +28912,31 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>327.3</v>
+        <v>327.75</v>
       </c>
       <c r="D548" t="n">
         <v>297.09</v>
       </c>
       <c r="E548" t="n">
-        <v>30.21</v>
+        <v>30.66</v>
       </c>
       <c r="F548" t="n">
-        <v>327.5</v>
+        <v>329.4</v>
       </c>
       <c r="G548" t="n">
         <v>327.62</v>
       </c>
       <c r="H548" t="n">
-        <v>-0.12</v>
+        <v>1.78</v>
       </c>
       <c r="I548" t="n">
-        <v>320.3</v>
+        <v>323</v>
       </c>
       <c r="J548" t="n">
         <v>321.54</v>
       </c>
       <c r="K548" t="n">
-        <v>-1.24</v>
+        <v>1.46</v>
       </c>
       <c r="L548" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         </is>
       </c>
       <c r="N548" t="n">
-        <v>10.17</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="549">
@@ -28964,31 +28964,31 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>5690</v>
+        <v>5800</v>
       </c>
       <c r="D549" t="n">
         <v>5305.18</v>
       </c>
       <c r="E549" t="n">
-        <v>384.82</v>
+        <v>494.82</v>
       </c>
       <c r="F549" t="n">
-        <v>5738</v>
+        <v>5852.5</v>
       </c>
       <c r="G549" t="n">
         <v>5594.23</v>
       </c>
       <c r="H549" t="n">
-        <v>143.77</v>
+        <v>258.27</v>
       </c>
       <c r="I549" t="n">
-        <v>5640.5</v>
+        <v>5603</v>
       </c>
       <c r="J549" t="n">
         <v>5556.38</v>
       </c>
       <c r="K549" t="n">
-        <v>84.12</v>
+        <v>46.62</v>
       </c>
       <c r="L549" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         </is>
       </c>
       <c r="N549" t="n">
-        <v>7.25</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="550">
@@ -29016,31 +29016,31 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>1181.3</v>
+        <v>1165.6</v>
       </c>
       <c r="D550" t="n">
         <v>1151.16</v>
       </c>
       <c r="E550" t="n">
-        <v>30.14</v>
+        <v>14.44</v>
       </c>
       <c r="F550" t="n">
-        <v>1181.3</v>
+        <v>1184.3</v>
       </c>
       <c r="G550" t="n">
         <v>1196.76</v>
       </c>
       <c r="H550" t="n">
-        <v>-15.46</v>
+        <v>-12.46</v>
       </c>
       <c r="I550" t="n">
-        <v>1128.6</v>
+        <v>1147.5</v>
       </c>
       <c r="J550" t="n">
         <v>1172.55</v>
       </c>
       <c r="K550" t="n">
-        <v>-43.95</v>
+        <v>-25.05</v>
       </c>
       <c r="L550" t="inlineStr">
         <is>
@@ -29049,11 +29049,11 @@
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="551">
@@ -29068,31 +29068,31 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>1236</v>
+        <v>1274.4</v>
       </c>
       <c r="D551" t="n">
         <v>1222.9</v>
       </c>
       <c r="E551" t="n">
-        <v>13.1</v>
+        <v>51.5</v>
       </c>
       <c r="F551" t="n">
-        <v>1272</v>
+        <v>1307.5</v>
       </c>
       <c r="G551" t="n">
         <v>1258.19</v>
       </c>
       <c r="H551" t="n">
-        <v>13.81</v>
+        <v>49.31</v>
       </c>
       <c r="I551" t="n">
-        <v>1228.3</v>
+        <v>1261.5</v>
       </c>
       <c r="J551" t="n">
         <v>1232.95</v>
       </c>
       <c r="K551" t="n">
-        <v>-4.65</v>
+        <v>28.55</v>
       </c>
       <c r="L551" t="inlineStr">
         <is>
@@ -29101,11 +29101,11 @@
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N551" t="n">
-        <v>1.07</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="552">
@@ -29120,31 +29120,31 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>1866</v>
+        <v>1880.7</v>
       </c>
       <c r="D552" t="n">
         <v>1827.81</v>
       </c>
       <c r="E552" t="n">
-        <v>38.19</v>
+        <v>52.89</v>
       </c>
       <c r="F552" t="n">
-        <v>1869</v>
+        <v>1887.2</v>
       </c>
       <c r="G552" t="n">
         <v>1891.04</v>
       </c>
       <c r="H552" t="n">
-        <v>-22.04</v>
+        <v>-3.84</v>
       </c>
       <c r="I552" t="n">
-        <v>1828.9</v>
+        <v>1846.6</v>
       </c>
       <c r="J552" t="n">
         <v>1852.83</v>
       </c>
       <c r="K552" t="n">
-        <v>-23.93</v>
+        <v>-6.23</v>
       </c>
       <c r="L552" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         </is>
       </c>
       <c r="N552" t="n">
-        <v>2.09</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="553">
@@ -29172,31 +29172,31 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>1365.2</v>
+        <v>1391</v>
       </c>
       <c r="D553" t="n">
         <v>1383.7</v>
       </c>
       <c r="E553" t="n">
-        <v>-18.5</v>
+        <v>7.3</v>
       </c>
       <c r="F553" t="n">
-        <v>1379.7</v>
+        <v>1407.4</v>
       </c>
       <c r="G553" t="n">
         <v>1383.7</v>
       </c>
       <c r="H553" t="n">
-        <v>-4</v>
+        <v>23.7</v>
       </c>
       <c r="I553" t="n">
-        <v>1355.9</v>
+        <v>1376</v>
       </c>
       <c r="J553" t="n">
         <v>1352.81</v>
       </c>
       <c r="K553" t="n">
-        <v>3.09</v>
+        <v>23.19</v>
       </c>
       <c r="L553" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="N553" t="n">
-        <v>1.34</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="554">
@@ -29224,31 +29224,31 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>289.2</v>
+        <v>292.3</v>
       </c>
       <c r="D554" t="n">
         <v>302.26</v>
       </c>
       <c r="E554" t="n">
-        <v>-13.06</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="F554" t="n">
-        <v>294</v>
+        <v>296.65</v>
       </c>
       <c r="G554" t="n">
         <v>302.26</v>
       </c>
       <c r="H554" t="n">
-        <v>-8.26</v>
+        <v>-5.61</v>
       </c>
       <c r="I554" t="n">
-        <v>288.35</v>
+        <v>290.4</v>
       </c>
       <c r="J554" t="n">
         <v>286.68</v>
       </c>
       <c r="K554" t="n">
-        <v>1.67</v>
+        <v>3.72</v>
       </c>
       <c r="L554" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         </is>
       </c>
       <c r="N554" t="n">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="555">
@@ -29276,31 +29276,31 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>14590</v>
+        <v>14461</v>
       </c>
       <c r="D555" t="n">
         <v>13684.31</v>
       </c>
       <c r="E555" t="n">
-        <v>905.6900000000001</v>
+        <v>776.6900000000001</v>
       </c>
       <c r="F555" t="n">
-        <v>14620</v>
+        <v>14820</v>
       </c>
       <c r="G555" t="n">
         <v>14833.46</v>
       </c>
       <c r="H555" t="n">
-        <v>-213.46</v>
+        <v>-13.46</v>
       </c>
       <c r="I555" t="n">
-        <v>14315</v>
+        <v>14450</v>
       </c>
       <c r="J555" t="n">
         <v>14535.34</v>
       </c>
       <c r="K555" t="n">
-        <v>-220.34</v>
+        <v>-85.34</v>
       </c>
       <c r="L555" t="inlineStr">
         <is>
@@ -29309,11 +29309,11 @@
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N555" t="n">
-        <v>6.62</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="556">
@@ -29328,31 +29328,31 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>3286</v>
+        <v>3303</v>
       </c>
       <c r="D556" t="n">
         <v>3766.38</v>
       </c>
       <c r="E556" t="n">
-        <v>-480.38</v>
+        <v>-463.38</v>
       </c>
       <c r="F556" t="n">
-        <v>3333</v>
+        <v>3369</v>
       </c>
       <c r="G556" t="n">
         <v>3766.38</v>
       </c>
       <c r="H556" t="n">
-        <v>-433.38</v>
+        <v>-397.38</v>
       </c>
       <c r="I556" t="n">
-        <v>3258</v>
+        <v>3255.2</v>
       </c>
       <c r="J556" t="n">
         <v>3286</v>
       </c>
       <c r="K556" t="n">
-        <v>-28</v>
+        <v>-30.8</v>
       </c>
       <c r="L556" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="N556" t="n">
-        <v>12.75</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="557">
@@ -29380,31 +29380,31 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>588.4</v>
+        <v>597</v>
       </c>
       <c r="D557" t="n">
         <v>585.1900000000001</v>
       </c>
       <c r="E557" t="n">
-        <v>3.21</v>
+        <v>11.81</v>
       </c>
       <c r="F557" t="n">
-        <v>592.9</v>
+        <v>608.95</v>
       </c>
       <c r="G557" t="n">
         <v>592</v>
       </c>
       <c r="H557" t="n">
-        <v>0.9</v>
+        <v>16.95</v>
       </c>
       <c r="I557" t="n">
-        <v>581.3</v>
+        <v>593.05</v>
       </c>
       <c r="J557" t="n">
         <v>579.89</v>
       </c>
       <c r="K557" t="n">
-        <v>1.41</v>
+        <v>13.16</v>
       </c>
       <c r="L557" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         </is>
       </c>
       <c r="N557" t="n">
-        <v>0.55</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="558">
@@ -29432,31 +29432,31 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>1623</v>
+        <v>1638</v>
       </c>
       <c r="D558" t="n">
         <v>1639.84</v>
       </c>
       <c r="E558" t="n">
-        <v>-16.84</v>
+        <v>-1.84</v>
       </c>
       <c r="F558" t="n">
-        <v>1637.2</v>
+        <v>1649</v>
       </c>
       <c r="G558" t="n">
         <v>1639.84</v>
       </c>
       <c r="H558" t="n">
-        <v>-2.64</v>
+        <v>9.16</v>
       </c>
       <c r="I558" t="n">
-        <v>1604.5</v>
+        <v>1613.7</v>
       </c>
       <c r="J558" t="n">
         <v>1597.15</v>
       </c>
       <c r="K558" t="n">
-        <v>7.35</v>
+        <v>16.55</v>
       </c>
       <c r="L558" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         </is>
       </c>
       <c r="N558" t="n">
-        <v>1.03</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="559">
@@ -29484,31 +29484,31 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>1343.7</v>
+        <v>1356</v>
       </c>
       <c r="D559" t="n">
         <v>1234.11</v>
       </c>
       <c r="E559" t="n">
-        <v>109.59</v>
+        <v>121.89</v>
       </c>
       <c r="F559" t="n">
-        <v>1352.4</v>
+        <v>1371.7</v>
       </c>
       <c r="G559" t="n">
         <v>1359.57</v>
       </c>
       <c r="H559" t="n">
-        <v>-7.17</v>
+        <v>12.13</v>
       </c>
       <c r="I559" t="n">
-        <v>1314.8</v>
+        <v>1327.2</v>
       </c>
       <c r="J559" t="n">
         <v>1332.02</v>
       </c>
       <c r="K559" t="n">
-        <v>-17.22</v>
+        <v>-4.82</v>
       </c>
       <c r="L559" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         </is>
       </c>
       <c r="N559" t="n">
-        <v>8.880000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="560">
@@ -29536,31 +29536,31 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>878.8</v>
+        <v>881.75</v>
       </c>
       <c r="D560" t="n">
         <v>901.28</v>
       </c>
       <c r="E560" t="n">
-        <v>-22.48</v>
+        <v>-19.53</v>
       </c>
       <c r="F560" t="n">
-        <v>884.4</v>
+        <v>890.5</v>
       </c>
       <c r="G560" t="n">
         <v>901.28</v>
       </c>
       <c r="H560" t="n">
-        <v>-16.88</v>
+        <v>-10.78</v>
       </c>
       <c r="I560" t="n">
-        <v>866</v>
+        <v>874.05</v>
       </c>
       <c r="J560" t="n">
         <v>878.8</v>
       </c>
       <c r="K560" t="n">
-        <v>-12.8</v>
+        <v>-4.75</v>
       </c>
       <c r="L560" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         </is>
       </c>
       <c r="N560" t="n">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>
@@ -30956,31 +30956,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1181.3</v>
+        <v>1165.6</v>
       </c>
       <c r="D21" t="n">
         <v>1151.16</v>
       </c>
       <c r="E21" t="n">
-        <v>30.14</v>
+        <v>14.44</v>
       </c>
       <c r="F21" t="n">
-        <v>1181.3</v>
+        <v>1184.3</v>
       </c>
       <c r="G21" t="n">
         <v>1196.76</v>
       </c>
       <c r="H21" t="n">
-        <v>-15.46</v>
+        <v>-12.46</v>
       </c>
       <c r="I21" t="n">
-        <v>1128.6</v>
+        <v>1147.5</v>
       </c>
       <c r="J21" t="n">
         <v>1172.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-43.95</v>
+        <v>-25.05</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -30989,11 +30989,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -33224,31 +33224,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1623</v>
+        <v>1638</v>
       </c>
       <c r="D16" t="n">
         <v>1639.84</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.84</v>
+        <v>-1.84</v>
       </c>
       <c r="F16" t="n">
-        <v>1637.2</v>
+        <v>1649</v>
       </c>
       <c r="G16" t="n">
         <v>1639.84</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.64</v>
+        <v>9.16</v>
       </c>
       <c r="I16" t="n">
-        <v>1604.5</v>
+        <v>1613.7</v>
       </c>
       <c r="J16" t="n">
         <v>1597.15</v>
       </c>
       <c r="K16" t="n">
-        <v>7.35</v>
+        <v>16.55</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.03</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -34402,31 +34402,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>327.3</v>
+        <v>327.75</v>
       </c>
       <c r="D22" t="n">
         <v>297.09</v>
       </c>
       <c r="E22" t="n">
-        <v>30.21</v>
+        <v>30.66</v>
       </c>
       <c r="F22" t="n">
-        <v>327.5</v>
+        <v>329.4</v>
       </c>
       <c r="G22" t="n">
         <v>327.62</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.12</v>
+        <v>1.78</v>
       </c>
       <c r="I22" t="n">
-        <v>320.3</v>
+        <v>323</v>
       </c>
       <c r="J22" t="n">
         <v>321.54</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.24</v>
+        <v>1.46</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>10.17</v>
+        <v>10.32</v>
       </c>
     </row>
   </sheetData>
@@ -35580,31 +35580,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14590</v>
+        <v>14461</v>
       </c>
       <c r="D22" t="n">
         <v>13684.31</v>
       </c>
       <c r="E22" t="n">
-        <v>905.6900000000001</v>
+        <v>776.6900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>14620</v>
+        <v>14820</v>
       </c>
       <c r="G22" t="n">
         <v>14833.46</v>
       </c>
       <c r="H22" t="n">
-        <v>-213.46</v>
+        <v>-13.46</v>
       </c>
       <c r="I22" t="n">
-        <v>14315</v>
+        <v>14450</v>
       </c>
       <c r="J22" t="n">
         <v>14535.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-220.34</v>
+        <v>-85.34</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -35613,11 +35613,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>6.62</v>
+        <v>5.68</v>
       </c>
     </row>
   </sheetData>
@@ -37624,31 +37624,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5690</v>
+        <v>5800</v>
       </c>
       <c r="D20" t="n">
         <v>5305.18</v>
       </c>
       <c r="E20" t="n">
-        <v>384.82</v>
+        <v>494.82</v>
       </c>
       <c r="F20" t="n">
-        <v>5738</v>
+        <v>5852.5</v>
       </c>
       <c r="G20" t="n">
         <v>5594.23</v>
       </c>
       <c r="H20" t="n">
-        <v>143.77</v>
+        <v>258.27</v>
       </c>
       <c r="I20" t="n">
-        <v>5640.5</v>
+        <v>5603</v>
       </c>
       <c r="J20" t="n">
         <v>5556.38</v>
       </c>
       <c r="K20" t="n">
-        <v>84.12</v>
+        <v>46.62</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>7.25</v>
+        <v>9.33</v>
       </c>
     </row>
   </sheetData>
@@ -38750,31 +38750,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>117</v>
+        <v>115.22</v>
       </c>
       <c r="D21" t="n">
         <v>116.69</v>
       </c>
       <c r="E21" t="n">
-        <v>0.31</v>
+        <v>-1.47</v>
       </c>
       <c r="F21" t="n">
-        <v>117.25</v>
+        <v>116.5</v>
       </c>
       <c r="G21" t="n">
         <v>119.38</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.13</v>
+        <v>-2.88</v>
       </c>
       <c r="I21" t="n">
-        <v>113.92</v>
+        <v>114.07</v>
       </c>
       <c r="J21" t="n">
         <v>117</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.08</v>
+        <v>-2.93</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.27</v>
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N560"/>
+  <dimension ref="A1:N582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29574,6 +29574,1150 @@
       </c>
       <c r="N560" t="n">
         <v>2.17</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>189</v>
+      </c>
+      <c r="D561" t="n">
+        <v>174.79</v>
+      </c>
+      <c r="E561" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F561" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G561" t="n">
+        <v>193.63</v>
+      </c>
+      <c r="H561" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="I561" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="J561" t="n">
+        <v>188.32</v>
+      </c>
+      <c r="K561" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N561" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D562" t="n">
+        <v>1778.7</v>
+      </c>
+      <c r="E562" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="F562" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G562" t="n">
+        <v>1860.37</v>
+      </c>
+      <c r="H562" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="I562" t="n">
+        <v>1834.4</v>
+      </c>
+      <c r="J562" t="n">
+        <v>1807.92</v>
+      </c>
+      <c r="K562" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N562" t="n">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>197</v>
+      </c>
+      <c r="D563" t="n">
+        <v>197.07</v>
+      </c>
+      <c r="E563" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F563" t="n">
+        <v>200.04</v>
+      </c>
+      <c r="G563" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="H563" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I563" t="n">
+        <v>194.26</v>
+      </c>
+      <c r="J563" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N563" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="D564" t="n">
+        <v>282.2</v>
+      </c>
+      <c r="E564" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F564" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="G564" t="n">
+        <v>293.19</v>
+      </c>
+      <c r="H564" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I564" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="J564" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="K564" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N564" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2159.4</v>
+      </c>
+      <c r="D565" t="n">
+        <v>2203.82</v>
+      </c>
+      <c r="E565" t="n">
+        <v>-44.42</v>
+      </c>
+      <c r="F565" t="n">
+        <v>2232</v>
+      </c>
+      <c r="G565" t="n">
+        <v>2203.82</v>
+      </c>
+      <c r="H565" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="I565" t="n">
+        <v>2136.5</v>
+      </c>
+      <c r="J565" t="n">
+        <v>2136.86</v>
+      </c>
+      <c r="K565" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N565" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>681.65</v>
+      </c>
+      <c r="D566" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E566" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="F566" t="n">
+        <v>689.35</v>
+      </c>
+      <c r="G566" t="n">
+        <v>683.76</v>
+      </c>
+      <c r="H566" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I566" t="n">
+        <v>671</v>
+      </c>
+      <c r="J566" t="n">
+        <v>664.5</v>
+      </c>
+      <c r="K566" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N566" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="D567" t="n">
+        <v>115.77</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F567" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="G567" t="n">
+        <v>115.77</v>
+      </c>
+      <c r="H567" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I567" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="J567" t="n">
+        <v>113.51</v>
+      </c>
+      <c r="K567" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N567" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>490</v>
+      </c>
+      <c r="D568" t="n">
+        <v>499.3</v>
+      </c>
+      <c r="E568" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="F568" t="n">
+        <v>499.65</v>
+      </c>
+      <c r="G568" t="n">
+        <v>499.3</v>
+      </c>
+      <c r="H568" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I568" t="n">
+        <v>487.35</v>
+      </c>
+      <c r="J568" t="n">
+        <v>481.72</v>
+      </c>
+      <c r="K568" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N568" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>1012.8</v>
+      </c>
+      <c r="D569" t="n">
+        <v>987.75</v>
+      </c>
+      <c r="E569" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F569" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="G569" t="n">
+        <v>1006.74</v>
+      </c>
+      <c r="H569" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="I569" t="n">
+        <v>1006.8</v>
+      </c>
+      <c r="J569" t="n">
+        <v>978.0700000000001</v>
+      </c>
+      <c r="K569" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N569" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D570" t="n">
+        <v>1972.7</v>
+      </c>
+      <c r="E570" t="n">
+        <v>-70.7</v>
+      </c>
+      <c r="F570" t="n">
+        <v>1912.7</v>
+      </c>
+      <c r="G570" t="n">
+        <v>1972.7</v>
+      </c>
+      <c r="H570" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I570" t="n">
+        <v>1866.1</v>
+      </c>
+      <c r="J570" t="n">
+        <v>1871.43</v>
+      </c>
+      <c r="K570" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N570" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D571" t="n">
+        <v>1335.81</v>
+      </c>
+      <c r="E571" t="n">
+        <v>-66.81</v>
+      </c>
+      <c r="F571" t="n">
+        <v>1269</v>
+      </c>
+      <c r="G571" t="n">
+        <v>1335.81</v>
+      </c>
+      <c r="H571" t="n">
+        <v>-66.81</v>
+      </c>
+      <c r="I571" t="n">
+        <v>1235.8</v>
+      </c>
+      <c r="J571" t="n">
+        <v>1259.37</v>
+      </c>
+      <c r="K571" t="n">
+        <v>-23.57</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N571" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="D572" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="E572" t="n">
+        <v>-36.39</v>
+      </c>
+      <c r="F572" t="n">
+        <v>331</v>
+      </c>
+      <c r="G572" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="H572" t="n">
+        <v>-30.19</v>
+      </c>
+      <c r="I572" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="J572" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="K572" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N572" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>5657</v>
+      </c>
+      <c r="D573" t="n">
+        <v>6234.11</v>
+      </c>
+      <c r="E573" t="n">
+        <v>-577.11</v>
+      </c>
+      <c r="F573" t="n">
+        <v>5668</v>
+      </c>
+      <c r="G573" t="n">
+        <v>6234.11</v>
+      </c>
+      <c r="H573" t="n">
+        <v>-566.11</v>
+      </c>
+      <c r="I573" t="n">
+        <v>5501</v>
+      </c>
+      <c r="J573" t="n">
+        <v>5483.5</v>
+      </c>
+      <c r="K573" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N573" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>1839.2</v>
+      </c>
+      <c r="D574" t="n">
+        <v>1843.86</v>
+      </c>
+      <c r="E574" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="F574" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G574" t="n">
+        <v>1877.19</v>
+      </c>
+      <c r="H574" t="n">
+        <v>-7.19</v>
+      </c>
+      <c r="I574" t="n">
+        <v>1800.2</v>
+      </c>
+      <c r="J574" t="n">
+        <v>1825.44</v>
+      </c>
+      <c r="K574" t="n">
+        <v>-25.24</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N574" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>1145</v>
+      </c>
+      <c r="D575" t="n">
+        <v>1145.38</v>
+      </c>
+      <c r="E575" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F575" t="n">
+        <v>1169</v>
+      </c>
+      <c r="G575" t="n">
+        <v>1162.03</v>
+      </c>
+      <c r="H575" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="I575" t="n">
+        <v>1134.7</v>
+      </c>
+      <c r="J575" t="n">
+        <v>1129.77</v>
+      </c>
+      <c r="K575" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N575" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>732</v>
+      </c>
+      <c r="D576" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="E576" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F576" t="n">
+        <v>733.85</v>
+      </c>
+      <c r="G576" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="H576" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I576" t="n">
+        <v>720</v>
+      </c>
+      <c r="J576" t="n">
+        <v>711.86</v>
+      </c>
+      <c r="K576" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N576" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>1394</v>
+      </c>
+      <c r="D577" t="n">
+        <v>1412.57</v>
+      </c>
+      <c r="E577" t="n">
+        <v>-18.57</v>
+      </c>
+      <c r="F577" t="n">
+        <v>1397.3</v>
+      </c>
+      <c r="G577" t="n">
+        <v>1412.57</v>
+      </c>
+      <c r="H577" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="I577" t="n">
+        <v>1367</v>
+      </c>
+      <c r="J577" t="n">
+        <v>1368.7</v>
+      </c>
+      <c r="K577" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N577" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>888.75</v>
+      </c>
+      <c r="D578" t="n">
+        <v>880.48</v>
+      </c>
+      <c r="E578" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F578" t="n">
+        <v>906.7</v>
+      </c>
+      <c r="G578" t="n">
+        <v>908.7</v>
+      </c>
+      <c r="H578" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I578" t="n">
+        <v>882.45</v>
+      </c>
+      <c r="J578" t="n">
+        <v>884.24</v>
+      </c>
+      <c r="K578" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N578" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>587.95</v>
+      </c>
+      <c r="D579" t="n">
+        <v>604.61</v>
+      </c>
+      <c r="E579" t="n">
+        <v>-16.66</v>
+      </c>
+      <c r="F579" t="n">
+        <v>599</v>
+      </c>
+      <c r="G579" t="n">
+        <v>604.61</v>
+      </c>
+      <c r="H579" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="I579" t="n">
+        <v>584.5</v>
+      </c>
+      <c r="J579" t="n">
+        <v>574.6900000000001</v>
+      </c>
+      <c r="K579" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N579" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>3170.2</v>
+      </c>
+      <c r="D580" t="n">
+        <v>2802.41</v>
+      </c>
+      <c r="E580" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="F580" t="n">
+        <v>3333</v>
+      </c>
+      <c r="G580" t="n">
+        <v>3182.75</v>
+      </c>
+      <c r="H580" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="I580" t="n">
+        <v>3170.2</v>
+      </c>
+      <c r="J580" t="n">
+        <v>3093.2</v>
+      </c>
+      <c r="K580" t="n">
+        <v>77</v>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N580" t="n">
+        <v>13.12</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D581" t="n">
+        <v>1473.06</v>
+      </c>
+      <c r="E581" t="n">
+        <v>-143.06</v>
+      </c>
+      <c r="F581" t="n">
+        <v>1348.9</v>
+      </c>
+      <c r="G581" t="n">
+        <v>1473.06</v>
+      </c>
+      <c r="H581" t="n">
+        <v>-124.16</v>
+      </c>
+      <c r="I581" t="n">
+        <v>1320.2</v>
+      </c>
+      <c r="J581" t="n">
+        <v>1286.08</v>
+      </c>
+      <c r="K581" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N581" t="n">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>14445</v>
+      </c>
+      <c r="D582" t="n">
+        <v>15387.02</v>
+      </c>
+      <c r="E582" t="n">
+        <v>-942.02</v>
+      </c>
+      <c r="F582" t="n">
+        <v>14670</v>
+      </c>
+      <c r="G582" t="n">
+        <v>15387.02</v>
+      </c>
+      <c r="H582" t="n">
+        <v>-717.02</v>
+      </c>
+      <c r="I582" t="n">
+        <v>14380</v>
+      </c>
+      <c r="J582" t="n">
+        <v>14142.26</v>
+      </c>
+      <c r="K582" t="n">
+        <v>237.74</v>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N582" t="n">
+        <v>6.12</v>
       </c>
     </row>
   </sheetData>
@@ -29587,7 +30731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29868,6 +31012,58 @@
       </c>
       <c r="N5" t="n">
         <v>3.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>732</v>
+      </c>
+      <c r="D6" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>733.85</v>
+      </c>
+      <c r="G6" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I6" t="n">
+        <v>720</v>
+      </c>
+      <c r="J6" t="n">
+        <v>711.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -33275,7 +34471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34440,6 +35636,58 @@
       </c>
       <c r="N22" t="n">
         <v>10.32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-36.39</v>
+      </c>
+      <c r="F23" t="n">
+        <v>331</v>
+      </c>
+      <c r="G23" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-30.19</v>
+      </c>
+      <c r="I23" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="J23" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>10.08</v>
       </c>
     </row>
   </sheetData>
@@ -34453,7 +35701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35618,6 +36866,58 @@
       </c>
       <c r="N22" t="n">
         <v>5.68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14445</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15387.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-942.02</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14670</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15387.02</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-717.02</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14380</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14142.26</v>
+      </c>
+      <c r="K23" t="n">
+        <v>237.74</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>6.12</v>
       </c>
     </row>
   </sheetData>
@@ -36601,7 +37901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37662,6 +38962,58 @@
       </c>
       <c r="N20" t="n">
         <v>9.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5657</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6234.11</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-577.11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5668</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6234.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-566.11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5501</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5483.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>9.26</v>
       </c>
     </row>
   </sheetData>
@@ -37675,7 +39027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38788,6 +40140,58 @@
       </c>
       <c r="N21" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="D22" t="n">
+        <v>115.77</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="G22" t="n">
+        <v>115.77</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I22" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="J22" t="n">
+        <v>113.51</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -29588,31 +29588,31 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>189</v>
+        <v>186.86</v>
       </c>
       <c r="D561" t="n">
         <v>174.79</v>
       </c>
       <c r="E561" t="n">
-        <v>14.21</v>
+        <v>12.07</v>
       </c>
       <c r="F561" t="n">
-        <v>190.75</v>
+        <v>186.86</v>
       </c>
       <c r="G561" t="n">
         <v>193.63</v>
       </c>
       <c r="H561" t="n">
-        <v>-2.88</v>
+        <v>-6.77</v>
       </c>
       <c r="I561" t="n">
-        <v>186.75</v>
+        <v>182.5</v>
       </c>
       <c r="J561" t="n">
         <v>188.32</v>
       </c>
       <c r="K561" t="n">
-        <v>-1.57</v>
+        <v>-5.82</v>
       </c>
       <c r="L561" t="inlineStr">
         <is>
@@ -29621,11 +29621,11 @@
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N561" t="n">
-        <v>8.130000000000001</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="562">
@@ -29640,31 +29640,31 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>1870</v>
+        <v>1851.9</v>
       </c>
       <c r="D562" t="n">
         <v>1778.7</v>
       </c>
       <c r="E562" t="n">
-        <v>91.3</v>
+        <v>73.2</v>
       </c>
       <c r="F562" t="n">
-        <v>1870</v>
+        <v>1860</v>
       </c>
       <c r="G562" t="n">
         <v>1860.37</v>
       </c>
       <c r="H562" t="n">
-        <v>9.630000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="I562" t="n">
-        <v>1834.4</v>
+        <v>1810</v>
       </c>
       <c r="J562" t="n">
         <v>1807.92</v>
       </c>
       <c r="K562" t="n">
-        <v>26.48</v>
+        <v>2.08</v>
       </c>
       <c r="L562" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         </is>
       </c>
       <c r="N562" t="n">
-        <v>5.13</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="563">
@@ -29692,31 +29692,31 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>197</v>
+        <v>196.5</v>
       </c>
       <c r="D563" t="n">
         <v>197.07</v>
       </c>
       <c r="E563" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="F563" t="n">
-        <v>200.04</v>
+        <v>198.39</v>
       </c>
       <c r="G563" t="n">
         <v>199.49</v>
       </c>
       <c r="H563" t="n">
-        <v>0.55</v>
+        <v>-1.1</v>
       </c>
       <c r="I563" t="n">
-        <v>194.26</v>
+        <v>190.27</v>
       </c>
       <c r="J563" t="n">
         <v>193.94</v>
       </c>
       <c r="K563" t="n">
-        <v>0.32</v>
+        <v>-3.67</v>
       </c>
       <c r="L563" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         </is>
       </c>
       <c r="N563" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="564">
@@ -29744,31 +29744,31 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>289.5</v>
+        <v>289.2</v>
       </c>
       <c r="D564" t="n">
         <v>282.2</v>
       </c>
       <c r="E564" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="F564" t="n">
-        <v>293.2</v>
+        <v>294</v>
       </c>
       <c r="G564" t="n">
         <v>293.19</v>
       </c>
       <c r="H564" t="n">
-        <v>0.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I564" t="n">
-        <v>289.2</v>
+        <v>288.35</v>
       </c>
       <c r="J564" t="n">
         <v>285.03</v>
       </c>
       <c r="K564" t="n">
-        <v>4.17</v>
+        <v>3.32</v>
       </c>
       <c r="L564" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         </is>
       </c>
       <c r="N564" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="565">
@@ -29796,31 +29796,31 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>2159.4</v>
+        <v>2210</v>
       </c>
       <c r="D565" t="n">
         <v>2203.82</v>
       </c>
       <c r="E565" t="n">
-        <v>-44.42</v>
+        <v>6.18</v>
       </c>
       <c r="F565" t="n">
-        <v>2232</v>
+        <v>2228.5</v>
       </c>
       <c r="G565" t="n">
         <v>2203.82</v>
       </c>
       <c r="H565" t="n">
-        <v>28.18</v>
+        <v>24.68</v>
       </c>
       <c r="I565" t="n">
-        <v>2136.5</v>
+        <v>2186.7</v>
       </c>
       <c r="J565" t="n">
         <v>2136.86</v>
       </c>
       <c r="K565" t="n">
-        <v>-0.36</v>
+        <v>49.84</v>
       </c>
       <c r="L565" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         </is>
       </c>
       <c r="N565" t="n">
-        <v>2.02</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="566">
@@ -29848,31 +29848,31 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>681.65</v>
+        <v>673.55</v>
       </c>
       <c r="D566" t="n">
         <v>644.8</v>
       </c>
       <c r="E566" t="n">
-        <v>36.85</v>
+        <v>28.75</v>
       </c>
       <c r="F566" t="n">
-        <v>689.35</v>
+        <v>673.55</v>
       </c>
       <c r="G566" t="n">
         <v>683.76</v>
       </c>
       <c r="H566" t="n">
-        <v>5.59</v>
+        <v>-10.21</v>
       </c>
       <c r="I566" t="n">
-        <v>671</v>
+        <v>651.3</v>
       </c>
       <c r="J566" t="n">
         <v>664.5</v>
       </c>
       <c r="K566" t="n">
-        <v>6.5</v>
+        <v>-13.2</v>
       </c>
       <c r="L566" t="inlineStr">
         <is>
@@ -29881,11 +29881,11 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N566" t="n">
-        <v>5.71</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="567">
@@ -29900,31 +29900,31 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="D567" t="n">
         <v>115.77</v>
       </c>
       <c r="E567" t="n">
-        <v>0.55</v>
+        <v>1.23</v>
       </c>
       <c r="F567" t="n">
-        <v>118.25</v>
+        <v>117.25</v>
       </c>
       <c r="G567" t="n">
         <v>115.77</v>
       </c>
       <c r="H567" t="n">
-        <v>2.48</v>
+        <v>1.48</v>
       </c>
       <c r="I567" t="n">
-        <v>116.32</v>
+        <v>113.92</v>
       </c>
       <c r="J567" t="n">
         <v>113.51</v>
       </c>
       <c r="K567" t="n">
-        <v>2.81</v>
+        <v>0.41</v>
       </c>
       <c r="L567" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="568">
@@ -29952,31 +29952,31 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>490</v>
+        <v>498.15</v>
       </c>
       <c r="D568" t="n">
         <v>499.3</v>
       </c>
       <c r="E568" t="n">
-        <v>-9.300000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="F568" t="n">
-        <v>499.65</v>
+        <v>499.5</v>
       </c>
       <c r="G568" t="n">
         <v>499.3</v>
       </c>
       <c r="H568" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="I568" t="n">
-        <v>487.35</v>
+        <v>484.15</v>
       </c>
       <c r="J568" t="n">
         <v>481.72</v>
       </c>
       <c r="K568" t="n">
-        <v>5.63</v>
+        <v>2.43</v>
       </c>
       <c r="L568" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         </is>
       </c>
       <c r="N568" t="n">
-        <v>1.86</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="569">
@@ -30004,31 +30004,31 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>1012.8</v>
+        <v>1017.6</v>
       </c>
       <c r="D569" t="n">
         <v>987.75</v>
       </c>
       <c r="E569" t="n">
-        <v>25.05</v>
+        <v>29.85</v>
       </c>
       <c r="F569" t="n">
-        <v>1033.2</v>
+        <v>1025</v>
       </c>
       <c r="G569" t="n">
         <v>1006.74</v>
       </c>
       <c r="H569" t="n">
-        <v>26.46</v>
+        <v>18.26</v>
       </c>
       <c r="I569" t="n">
-        <v>1006.8</v>
+        <v>993.2</v>
       </c>
       <c r="J569" t="n">
         <v>978.0700000000001</v>
       </c>
       <c r="K569" t="n">
-        <v>28.73</v>
+        <v>15.13</v>
       </c>
       <c r="L569" t="inlineStr">
         <is>
@@ -30037,11 +30037,11 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N569" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="570">
@@ -30056,31 +30056,31 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>1902</v>
+        <v>1866</v>
       </c>
       <c r="D570" t="n">
         <v>1972.7</v>
       </c>
       <c r="E570" t="n">
-        <v>-70.7</v>
+        <v>-106.7</v>
       </c>
       <c r="F570" t="n">
-        <v>1912.7</v>
+        <v>1869</v>
       </c>
       <c r="G570" t="n">
         <v>1972.7</v>
       </c>
       <c r="H570" t="n">
-        <v>-60</v>
+        <v>-103.7</v>
       </c>
       <c r="I570" t="n">
-        <v>1866.1</v>
+        <v>1828.9</v>
       </c>
       <c r="J570" t="n">
         <v>1871.43</v>
       </c>
       <c r="K570" t="n">
-        <v>-5.33</v>
+        <v>-42.53</v>
       </c>
       <c r="L570" t="inlineStr">
         <is>
@@ -30089,11 +30089,11 @@
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N570" t="n">
-        <v>3.58</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="571">
@@ -30108,31 +30108,31 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>1269</v>
+        <v>1236</v>
       </c>
       <c r="D571" t="n">
         <v>1335.81</v>
       </c>
       <c r="E571" t="n">
-        <v>-66.81</v>
+        <v>-99.81</v>
       </c>
       <c r="F571" t="n">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G571" t="n">
         <v>1335.81</v>
       </c>
       <c r="H571" t="n">
-        <v>-66.81</v>
+        <v>-63.81</v>
       </c>
       <c r="I571" t="n">
-        <v>1235.8</v>
+        <v>1228.3</v>
       </c>
       <c r="J571" t="n">
         <v>1259.37</v>
       </c>
       <c r="K571" t="n">
-        <v>-23.57</v>
+        <v>-31.07</v>
       </c>
       <c r="L571" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="N571" t="n">
-        <v>5</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="572">
@@ -30160,31 +30160,31 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>324.8</v>
+        <v>327.3</v>
       </c>
       <c r="D572" t="n">
         <v>361.19</v>
       </c>
       <c r="E572" t="n">
-        <v>-36.39</v>
+        <v>-33.89</v>
       </c>
       <c r="F572" t="n">
-        <v>331</v>
+        <v>327.5</v>
       </c>
       <c r="G572" t="n">
         <v>361.19</v>
       </c>
       <c r="H572" t="n">
-        <v>-30.19</v>
+        <v>-33.69</v>
       </c>
       <c r="I572" t="n">
-        <v>324.15</v>
+        <v>320.3</v>
       </c>
       <c r="J572" t="n">
         <v>316.38</v>
       </c>
       <c r="K572" t="n">
-        <v>7.77</v>
+        <v>3.92</v>
       </c>
       <c r="L572" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         </is>
       </c>
       <c r="N572" t="n">
-        <v>10.08</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="573">
@@ -30212,31 +30212,31 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>5657</v>
+        <v>5690</v>
       </c>
       <c r="D573" t="n">
         <v>6234.11</v>
       </c>
       <c r="E573" t="n">
-        <v>-577.11</v>
+        <v>-544.11</v>
       </c>
       <c r="F573" t="n">
-        <v>5668</v>
+        <v>5738</v>
       </c>
       <c r="G573" t="n">
         <v>6234.11</v>
       </c>
       <c r="H573" t="n">
-        <v>-566.11</v>
+        <v>-496.11</v>
       </c>
       <c r="I573" t="n">
-        <v>5501</v>
+        <v>5640.5</v>
       </c>
       <c r="J573" t="n">
         <v>5483.5</v>
       </c>
       <c r="K573" t="n">
-        <v>17.5</v>
+        <v>157</v>
       </c>
       <c r="L573" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         </is>
       </c>
       <c r="N573" t="n">
-        <v>9.26</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="574">
@@ -30264,31 +30264,31 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>1839.2</v>
+        <v>1841</v>
       </c>
       <c r="D574" t="n">
         <v>1843.86</v>
       </c>
       <c r="E574" t="n">
-        <v>-4.66</v>
+        <v>-2.86</v>
       </c>
       <c r="F574" t="n">
-        <v>1870</v>
+        <v>1903.9</v>
       </c>
       <c r="G574" t="n">
         <v>1877.19</v>
       </c>
       <c r="H574" t="n">
-        <v>-7.19</v>
+        <v>26.71</v>
       </c>
       <c r="I574" t="n">
-        <v>1800.2</v>
+        <v>1751.7</v>
       </c>
       <c r="J574" t="n">
         <v>1825.44</v>
       </c>
       <c r="K574" t="n">
-        <v>-25.24</v>
+        <v>-73.73999999999999</v>
       </c>
       <c r="L574" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         </is>
       </c>
       <c r="N574" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="575">
@@ -30316,31 +30316,31 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>1145</v>
+        <v>1159.4</v>
       </c>
       <c r="D575" t="n">
         <v>1145.38</v>
       </c>
       <c r="E575" t="n">
-        <v>-0.38</v>
+        <v>14.02</v>
       </c>
       <c r="F575" t="n">
-        <v>1169</v>
+        <v>1165.3</v>
       </c>
       <c r="G575" t="n">
         <v>1162.03</v>
       </c>
       <c r="H575" t="n">
-        <v>6.97</v>
+        <v>3.27</v>
       </c>
       <c r="I575" t="n">
-        <v>1134.7</v>
+        <v>1141</v>
       </c>
       <c r="J575" t="n">
         <v>1129.77</v>
       </c>
       <c r="K575" t="n">
-        <v>4.93</v>
+        <v>11.23</v>
       </c>
       <c r="L575" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         </is>
       </c>
       <c r="N575" t="n">
-        <v>0.03</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="576">
@@ -30368,31 +30368,31 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>732</v>
+        <v>727.7</v>
       </c>
       <c r="D576" t="n">
         <v>732.24</v>
       </c>
       <c r="E576" t="n">
-        <v>-0.24</v>
+        <v>-4.54</v>
       </c>
       <c r="F576" t="n">
-        <v>733.85</v>
+        <v>727.7</v>
       </c>
       <c r="G576" t="n">
         <v>732.24</v>
       </c>
       <c r="H576" t="n">
-        <v>1.61</v>
+        <v>-4.54</v>
       </c>
       <c r="I576" t="n">
-        <v>720</v>
+        <v>706.05</v>
       </c>
       <c r="J576" t="n">
         <v>711.86</v>
       </c>
       <c r="K576" t="n">
-        <v>8.140000000000001</v>
+        <v>-5.81</v>
       </c>
       <c r="L576" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         </is>
       </c>
       <c r="N576" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="577">
@@ -30420,31 +30420,31 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>1394</v>
+        <v>1365.2</v>
       </c>
       <c r="D577" t="n">
         <v>1412.57</v>
       </c>
       <c r="E577" t="n">
-        <v>-18.57</v>
+        <v>-47.37</v>
       </c>
       <c r="F577" t="n">
-        <v>1397.3</v>
+        <v>1379.7</v>
       </c>
       <c r="G577" t="n">
         <v>1412.57</v>
       </c>
       <c r="H577" t="n">
-        <v>-15.27</v>
+        <v>-32.87</v>
       </c>
       <c r="I577" t="n">
-        <v>1367</v>
+        <v>1355.9</v>
       </c>
       <c r="J577" t="n">
         <v>1368.7</v>
       </c>
       <c r="K577" t="n">
-        <v>-1.7</v>
+        <v>-12.8</v>
       </c>
       <c r="L577" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         </is>
       </c>
       <c r="N577" t="n">
-        <v>1.31</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="578">
@@ -30472,31 +30472,31 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>888.75</v>
+        <v>878.8</v>
       </c>
       <c r="D578" t="n">
         <v>880.48</v>
       </c>
       <c r="E578" t="n">
-        <v>8.27</v>
+        <v>-1.68</v>
       </c>
       <c r="F578" t="n">
-        <v>906.7</v>
+        <v>884.4</v>
       </c>
       <c r="G578" t="n">
         <v>908.7</v>
       </c>
       <c r="H578" t="n">
-        <v>-2</v>
+        <v>-24.3</v>
       </c>
       <c r="I578" t="n">
-        <v>882.45</v>
+        <v>866</v>
       </c>
       <c r="J578" t="n">
         <v>884.24</v>
       </c>
       <c r="K578" t="n">
-        <v>-1.79</v>
+        <v>-18.24</v>
       </c>
       <c r="L578" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         </is>
       </c>
       <c r="N578" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="579">
@@ -30524,31 +30524,31 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>587.95</v>
+        <v>588.4</v>
       </c>
       <c r="D579" t="n">
         <v>604.61</v>
       </c>
       <c r="E579" t="n">
-        <v>-16.66</v>
+        <v>-16.21</v>
       </c>
       <c r="F579" t="n">
-        <v>599</v>
+        <v>592.9</v>
       </c>
       <c r="G579" t="n">
         <v>604.61</v>
       </c>
       <c r="H579" t="n">
-        <v>-5.61</v>
+        <v>-11.71</v>
       </c>
       <c r="I579" t="n">
-        <v>584.5</v>
+        <v>581.3</v>
       </c>
       <c r="J579" t="n">
         <v>574.6900000000001</v>
       </c>
       <c r="K579" t="n">
-        <v>9.81</v>
+        <v>6.61</v>
       </c>
       <c r="L579" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         </is>
       </c>
       <c r="N579" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="580">
@@ -30576,13 +30576,13 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>3170.2</v>
+        <v>3286</v>
       </c>
       <c r="D580" t="n">
         <v>2802.41</v>
       </c>
       <c r="E580" t="n">
-        <v>367.79</v>
+        <v>483.59</v>
       </c>
       <c r="F580" t="n">
         <v>3333</v>
@@ -30594,13 +30594,13 @@
         <v>150.25</v>
       </c>
       <c r="I580" t="n">
-        <v>3170.2</v>
+        <v>3258</v>
       </c>
       <c r="J580" t="n">
         <v>3093.2</v>
       </c>
       <c r="K580" t="n">
-        <v>77</v>
+        <v>164.8</v>
       </c>
       <c r="L580" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         </is>
       </c>
       <c r="N580" t="n">
-        <v>13.12</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="581">
@@ -30628,31 +30628,31 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>1330</v>
+        <v>1343.7</v>
       </c>
       <c r="D581" t="n">
         <v>1473.06</v>
       </c>
       <c r="E581" t="n">
-        <v>-143.06</v>
+        <v>-129.36</v>
       </c>
       <c r="F581" t="n">
-        <v>1348.9</v>
+        <v>1352.4</v>
       </c>
       <c r="G581" t="n">
         <v>1473.06</v>
       </c>
       <c r="H581" t="n">
-        <v>-124.16</v>
+        <v>-120.66</v>
       </c>
       <c r="I581" t="n">
-        <v>1320.2</v>
+        <v>1314.8</v>
       </c>
       <c r="J581" t="n">
         <v>1286.08</v>
       </c>
       <c r="K581" t="n">
-        <v>34.12</v>
+        <v>28.72</v>
       </c>
       <c r="L581" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         </is>
       </c>
       <c r="N581" t="n">
-        <v>9.710000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="582">
@@ -30680,31 +30680,31 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>14445</v>
+        <v>14590</v>
       </c>
       <c r="D582" t="n">
         <v>15387.02</v>
       </c>
       <c r="E582" t="n">
-        <v>-942.02</v>
+        <v>-797.02</v>
       </c>
       <c r="F582" t="n">
-        <v>14670</v>
+        <v>14620</v>
       </c>
       <c r="G582" t="n">
         <v>15387.02</v>
       </c>
       <c r="H582" t="n">
-        <v>-717.02</v>
+        <v>-767.02</v>
       </c>
       <c r="I582" t="n">
-        <v>14380</v>
+        <v>14315</v>
       </c>
       <c r="J582" t="n">
         <v>14142.26</v>
       </c>
       <c r="K582" t="n">
-        <v>237.74</v>
+        <v>172.74</v>
       </c>
       <c r="L582" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         </is>
       </c>
       <c r="N582" t="n">
-        <v>6.12</v>
+        <v>5.18</v>
       </c>
     </row>
   </sheetData>
@@ -31026,31 +31026,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>732</v>
+        <v>727.7</v>
       </c>
       <c r="D6" t="n">
         <v>732.24</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.24</v>
+        <v>-4.54</v>
       </c>
       <c r="F6" t="n">
-        <v>733.85</v>
+        <v>727.7</v>
       </c>
       <c r="G6" t="n">
         <v>732.24</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>-4.54</v>
       </c>
       <c r="I6" t="n">
-        <v>720</v>
+        <v>706.05</v>
       </c>
       <c r="J6" t="n">
         <v>711.86</v>
       </c>
       <c r="K6" t="n">
-        <v>8.140000000000001</v>
+        <v>-5.81</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -35650,31 +35650,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>324.8</v>
+        <v>327.3</v>
       </c>
       <c r="D23" t="n">
         <v>361.19</v>
       </c>
       <c r="E23" t="n">
-        <v>-36.39</v>
+        <v>-33.89</v>
       </c>
       <c r="F23" t="n">
-        <v>331</v>
+        <v>327.5</v>
       </c>
       <c r="G23" t="n">
         <v>361.19</v>
       </c>
       <c r="H23" t="n">
-        <v>-30.19</v>
+        <v>-33.69</v>
       </c>
       <c r="I23" t="n">
-        <v>324.15</v>
+        <v>320.3</v>
       </c>
       <c r="J23" t="n">
         <v>316.38</v>
       </c>
       <c r="K23" t="n">
-        <v>7.77</v>
+        <v>3.92</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10.08</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -36880,31 +36880,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14445</v>
+        <v>14590</v>
       </c>
       <c r="D23" t="n">
         <v>15387.02</v>
       </c>
       <c r="E23" t="n">
-        <v>-942.02</v>
+        <v>-797.02</v>
       </c>
       <c r="F23" t="n">
-        <v>14670</v>
+        <v>14620</v>
       </c>
       <c r="G23" t="n">
         <v>15387.02</v>
       </c>
       <c r="H23" t="n">
-        <v>-717.02</v>
+        <v>-767.02</v>
       </c>
       <c r="I23" t="n">
-        <v>14380</v>
+        <v>14315</v>
       </c>
       <c r="J23" t="n">
         <v>14142.26</v>
       </c>
       <c r="K23" t="n">
-        <v>237.74</v>
+        <v>172.74</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.12</v>
+        <v>5.18</v>
       </c>
     </row>
   </sheetData>
@@ -38976,31 +38976,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5657</v>
+        <v>5690</v>
       </c>
       <c r="D21" t="n">
         <v>6234.11</v>
       </c>
       <c r="E21" t="n">
-        <v>-577.11</v>
+        <v>-544.11</v>
       </c>
       <c r="F21" t="n">
-        <v>5668</v>
+        <v>5738</v>
       </c>
       <c r="G21" t="n">
         <v>6234.11</v>
       </c>
       <c r="H21" t="n">
-        <v>-566.11</v>
+        <v>-496.11</v>
       </c>
       <c r="I21" t="n">
-        <v>5501</v>
+        <v>5640.5</v>
       </c>
       <c r="J21" t="n">
         <v>5483.5</v>
       </c>
       <c r="K21" t="n">
-        <v>17.5</v>
+        <v>157</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>9.26</v>
+        <v>8.73</v>
       </c>
     </row>
   </sheetData>
@@ -40154,31 +40154,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="D22" t="n">
         <v>115.77</v>
       </c>
       <c r="E22" t="n">
-        <v>0.55</v>
+        <v>1.23</v>
       </c>
       <c r="F22" t="n">
-        <v>118.25</v>
+        <v>117.25</v>
       </c>
       <c r="G22" t="n">
         <v>115.77</v>
       </c>
       <c r="H22" t="n">
-        <v>2.48</v>
+        <v>1.48</v>
       </c>
       <c r="I22" t="n">
-        <v>116.32</v>
+        <v>113.92</v>
       </c>
       <c r="J22" t="n">
         <v>113.51</v>
       </c>
       <c r="K22" t="n">
-        <v>2.81</v>
+        <v>0.41</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N582"/>
+  <dimension ref="A1:N605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30718,6 +30718,1202 @@
       </c>
       <c r="N582" t="n">
         <v>5.18</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D583" t="n">
+        <v>2295.45</v>
+      </c>
+      <c r="E583" t="n">
+        <v>-45.45</v>
+      </c>
+      <c r="F583" t="n">
+        <v>2281</v>
+      </c>
+      <c r="G583" t="n">
+        <v>2295.45</v>
+      </c>
+      <c r="H583" t="n">
+        <v>-14.45</v>
+      </c>
+      <c r="I583" t="n">
+        <v>2150.4</v>
+      </c>
+      <c r="J583" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K583" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N583" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>117</v>
+      </c>
+      <c r="D584" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="E584" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="F584" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="G584" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="H584" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I584" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="J584" t="n">
+        <v>115.73</v>
+      </c>
+      <c r="K584" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N584" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>681.9</v>
+      </c>
+      <c r="D585" t="n">
+        <v>718.01</v>
+      </c>
+      <c r="E585" t="n">
+        <v>-36.11</v>
+      </c>
+      <c r="F585" t="n">
+        <v>689.75</v>
+      </c>
+      <c r="G585" t="n">
+        <v>718.01</v>
+      </c>
+      <c r="H585" t="n">
+        <v>-28.26</v>
+      </c>
+      <c r="I585" t="n">
+        <v>680.8</v>
+      </c>
+      <c r="J585" t="n">
+        <v>661.8200000000001</v>
+      </c>
+      <c r="K585" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N585" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>488.3</v>
+      </c>
+      <c r="D586" t="n">
+        <v>491.08</v>
+      </c>
+      <c r="E586" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="F586" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="G586" t="n">
+        <v>491.73</v>
+      </c>
+      <c r="H586" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I586" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="J586" t="n">
+        <v>481.73</v>
+      </c>
+      <c r="K586" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N586" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D587" t="n">
+        <v>1188.69</v>
+      </c>
+      <c r="E587" t="n">
+        <v>-23.69</v>
+      </c>
+      <c r="F587" t="n">
+        <v>1170.9</v>
+      </c>
+      <c r="G587" t="n">
+        <v>1188.69</v>
+      </c>
+      <c r="H587" t="n">
+        <v>-17.79</v>
+      </c>
+      <c r="I587" t="n">
+        <v>1138.7</v>
+      </c>
+      <c r="J587" t="n">
+        <v>1157.24</v>
+      </c>
+      <c r="K587" t="n">
+        <v>-18.54</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N587" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D588" t="n">
+        <v>1076.89</v>
+      </c>
+      <c r="E588" t="n">
+        <v>-39.89</v>
+      </c>
+      <c r="F588" t="n">
+        <v>1040.8</v>
+      </c>
+      <c r="G588" t="n">
+        <v>1076.89</v>
+      </c>
+      <c r="H588" t="n">
+        <v>-36.09</v>
+      </c>
+      <c r="I588" t="n">
+        <v>1022.8</v>
+      </c>
+      <c r="J588" t="n">
+        <v>997.86</v>
+      </c>
+      <c r="K588" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N588" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>1394.6</v>
+      </c>
+      <c r="D589" t="n">
+        <v>1358.62</v>
+      </c>
+      <c r="E589" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="F589" t="n">
+        <v>1417.9</v>
+      </c>
+      <c r="G589" t="n">
+        <v>1395.75</v>
+      </c>
+      <c r="H589" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="I589" t="n">
+        <v>1391.6</v>
+      </c>
+      <c r="J589" t="n">
+        <v>1367.05</v>
+      </c>
+      <c r="K589" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N589" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="D590" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="E590" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="F590" t="n">
+        <v>292.15</v>
+      </c>
+      <c r="G590" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="H590" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="I590" t="n">
+        <v>287.8</v>
+      </c>
+      <c r="J590" t="n">
+        <v>287.02</v>
+      </c>
+      <c r="K590" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N590" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>3275.4</v>
+      </c>
+      <c r="D591" t="n">
+        <v>3871.32</v>
+      </c>
+      <c r="E591" t="n">
+        <v>-595.92</v>
+      </c>
+      <c r="F591" t="n">
+        <v>3287.4</v>
+      </c>
+      <c r="G591" t="n">
+        <v>3871.32</v>
+      </c>
+      <c r="H591" t="n">
+        <v>-583.92</v>
+      </c>
+      <c r="I591" t="n">
+        <v>3165.6</v>
+      </c>
+      <c r="J591" t="n">
+        <v>3240.93</v>
+      </c>
+      <c r="K591" t="n">
+        <v>-75.33</v>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N591" t="n">
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>187.22</v>
+      </c>
+      <c r="D592" t="n">
+        <v>201.82</v>
+      </c>
+      <c r="E592" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="F592" t="n">
+        <v>189.95</v>
+      </c>
+      <c r="G592" t="n">
+        <v>201.82</v>
+      </c>
+      <c r="H592" t="n">
+        <v>-11.87</v>
+      </c>
+      <c r="I592" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="J592" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="K592" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N592" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>1249.7</v>
+      </c>
+      <c r="D593" t="n">
+        <v>1165.58</v>
+      </c>
+      <c r="E593" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1260.3</v>
+      </c>
+      <c r="G593" t="n">
+        <v>1265.81</v>
+      </c>
+      <c r="H593" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="I593" t="n">
+        <v>1237.5</v>
+      </c>
+      <c r="J593" t="n">
+        <v>1240.31</v>
+      </c>
+      <c r="K593" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N593" t="n">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="D594" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="E594" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F594" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="G594" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="H594" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I594" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="J594" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="K594" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N594" t="n">
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>1815.6</v>
+      </c>
+      <c r="D595" t="n">
+        <v>1827.28</v>
+      </c>
+      <c r="E595" t="n">
+        <v>-11.68</v>
+      </c>
+      <c r="F595" t="n">
+        <v>1862.8</v>
+      </c>
+      <c r="G595" t="n">
+        <v>1827.28</v>
+      </c>
+      <c r="H595" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="I595" t="n">
+        <v>1796.4</v>
+      </c>
+      <c r="J595" t="n">
+        <v>1768.25</v>
+      </c>
+      <c r="K595" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N595" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2205</v>
+      </c>
+      <c r="D596" t="n">
+        <v>2184.32</v>
+      </c>
+      <c r="E596" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="F596" t="n">
+        <v>2214.5</v>
+      </c>
+      <c r="G596" t="n">
+        <v>2222.1</v>
+      </c>
+      <c r="H596" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I596" t="n">
+        <v>2150.7</v>
+      </c>
+      <c r="J596" t="n">
+        <v>2176.95</v>
+      </c>
+      <c r="K596" t="n">
+        <v>-26.25</v>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N596" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="D597" t="n">
+        <v>420.52</v>
+      </c>
+      <c r="E597" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F597" t="n">
+        <v>425.95</v>
+      </c>
+      <c r="G597" t="n">
+        <v>424.98</v>
+      </c>
+      <c r="H597" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I597" t="n">
+        <v>421.65</v>
+      </c>
+      <c r="J597" t="n">
+        <v>416.24</v>
+      </c>
+      <c r="K597" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N597" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="D598" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="E598" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F598" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="G598" t="n">
+        <v>198.98</v>
+      </c>
+      <c r="H598" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I598" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="J598" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="K598" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N598" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>601</v>
+      </c>
+      <c r="D599" t="n">
+        <v>589.5700000000001</v>
+      </c>
+      <c r="E599" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="F599" t="n">
+        <v>603</v>
+      </c>
+      <c r="G599" t="n">
+        <v>602.8099999999999</v>
+      </c>
+      <c r="H599" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I599" t="n">
+        <v>592</v>
+      </c>
+      <c r="J599" t="n">
+        <v>590.47</v>
+      </c>
+      <c r="K599" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N599" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D600" t="n">
+        <v>1926.85</v>
+      </c>
+      <c r="E600" t="n">
+        <v>-90.84999999999999</v>
+      </c>
+      <c r="F600" t="n">
+        <v>1866.6</v>
+      </c>
+      <c r="G600" t="n">
+        <v>1926.85</v>
+      </c>
+      <c r="H600" t="n">
+        <v>-60.25</v>
+      </c>
+      <c r="I600" t="n">
+        <v>1828.7</v>
+      </c>
+      <c r="J600" t="n">
+        <v>1778.39</v>
+      </c>
+      <c r="K600" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N600" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="D601" t="n">
+        <v>427.06</v>
+      </c>
+      <c r="E601" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F601" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="G601" t="n">
+        <v>435.37</v>
+      </c>
+      <c r="H601" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I601" t="n">
+        <v>429.2</v>
+      </c>
+      <c r="J601" t="n">
+        <v>426.55</v>
+      </c>
+      <c r="K601" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N601" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>5643</v>
+      </c>
+      <c r="D602" t="n">
+        <v>5191.68</v>
+      </c>
+      <c r="E602" t="n">
+        <v>451.32</v>
+      </c>
+      <c r="F602" t="n">
+        <v>5724.5</v>
+      </c>
+      <c r="G602" t="n">
+        <v>5576.42</v>
+      </c>
+      <c r="H602" t="n">
+        <v>148.08</v>
+      </c>
+      <c r="I602" t="n">
+        <v>5634</v>
+      </c>
+      <c r="J602" t="n">
+        <v>5459.25</v>
+      </c>
+      <c r="K602" t="n">
+        <v>174.75</v>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N602" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>1875.6</v>
+      </c>
+      <c r="D603" t="n">
+        <v>1788.34</v>
+      </c>
+      <c r="E603" t="n">
+        <v>87.26000000000001</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1932.8</v>
+      </c>
+      <c r="G603" t="n">
+        <v>1848.68</v>
+      </c>
+      <c r="H603" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="I603" t="n">
+        <v>1874</v>
+      </c>
+      <c r="J603" t="n">
+        <v>1817.04</v>
+      </c>
+      <c r="K603" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N603" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="D604" t="n">
+        <v>1213.53</v>
+      </c>
+      <c r="E604" t="n">
+        <v>106.27</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1349.5</v>
+      </c>
+      <c r="G604" t="n">
+        <v>1320.6</v>
+      </c>
+      <c r="H604" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I604" t="n">
+        <v>1313.1</v>
+      </c>
+      <c r="J604" t="n">
+        <v>1293.43</v>
+      </c>
+      <c r="K604" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N604" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>879.7</v>
+      </c>
+      <c r="D605" t="n">
+        <v>885.05</v>
+      </c>
+      <c r="E605" t="n">
+        <v>-5.35</v>
+      </c>
+      <c r="F605" t="n">
+        <v>892.4</v>
+      </c>
+      <c r="G605" t="n">
+        <v>891.26</v>
+      </c>
+      <c r="H605" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I605" t="n">
+        <v>879.1</v>
+      </c>
+      <c r="J605" t="n">
+        <v>873.3099999999999</v>
+      </c>
+      <c r="K605" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N605" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -34471,7 +35667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35688,6 +36884,58 @@
       </c>
       <c r="N23" t="n">
         <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F24" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>9.48</v>
       </c>
     </row>
   </sheetData>
@@ -37901,7 +39149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39014,6 +40262,58 @@
       </c>
       <c r="N21" t="n">
         <v>8.73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5643</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5191.68</v>
+      </c>
+      <c r="E22" t="n">
+        <v>451.32</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5724.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5576.42</v>
+      </c>
+      <c r="H22" t="n">
+        <v>148.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5634</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5459.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>174.75</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>8.69</v>
       </c>
     </row>
   </sheetData>
@@ -39027,7 +40327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40192,6 +41492,58 @@
       </c>
       <c r="N22" t="n">
         <v>1.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>117</v>
+      </c>
+      <c r="D23" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="G23" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="J23" t="n">
+        <v>115.73</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -30732,31 +30732,31 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>2250</v>
+        <v>2159.4</v>
       </c>
       <c r="D583" t="n">
         <v>2295.45</v>
       </c>
       <c r="E583" t="n">
-        <v>-45.45</v>
+        <v>-136.05</v>
       </c>
       <c r="F583" t="n">
-        <v>2281</v>
+        <v>2232</v>
       </c>
       <c r="G583" t="n">
         <v>2295.45</v>
       </c>
       <c r="H583" t="n">
-        <v>-14.45</v>
+        <v>-63.45</v>
       </c>
       <c r="I583" t="n">
-        <v>2150.4</v>
+        <v>2136.5</v>
       </c>
       <c r="J583" t="n">
         <v>2250</v>
       </c>
       <c r="K583" t="n">
-        <v>-99.59999999999999</v>
+        <v>-113.5</v>
       </c>
       <c r="L583" t="inlineStr">
         <is>
@@ -30765,11 +30765,11 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N583" t="n">
-        <v>1.98</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="584">
@@ -30784,31 +30784,31 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>117</v>
+        <v>116.32</v>
       </c>
       <c r="D584" t="n">
         <v>119.19</v>
       </c>
       <c r="E584" t="n">
-        <v>-2.19</v>
+        <v>-2.87</v>
       </c>
       <c r="F584" t="n">
-        <v>118.05</v>
+        <v>118.25</v>
       </c>
       <c r="G584" t="n">
         <v>119.19</v>
       </c>
       <c r="H584" t="n">
-        <v>-1.14</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I584" t="n">
-        <v>116.45</v>
+        <v>116.32</v>
       </c>
       <c r="J584" t="n">
         <v>115.73</v>
       </c>
       <c r="K584" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="L584" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="N584" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="585">
@@ -30836,31 +30836,31 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>681.9</v>
+        <v>681.65</v>
       </c>
       <c r="D585" t="n">
         <v>718.01</v>
       </c>
       <c r="E585" t="n">
-        <v>-36.11</v>
+        <v>-36.36</v>
       </c>
       <c r="F585" t="n">
-        <v>689.75</v>
+        <v>689.35</v>
       </c>
       <c r="G585" t="n">
         <v>718.01</v>
       </c>
       <c r="H585" t="n">
-        <v>-28.26</v>
+        <v>-28.66</v>
       </c>
       <c r="I585" t="n">
-        <v>680.8</v>
+        <v>671</v>
       </c>
       <c r="J585" t="n">
         <v>661.8200000000001</v>
       </c>
       <c r="K585" t="n">
-        <v>18.98</v>
+        <v>9.18</v>
       </c>
       <c r="L585" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="586">
@@ -30888,31 +30888,31 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>488.3</v>
+        <v>489</v>
       </c>
       <c r="D586" t="n">
         <v>491.08</v>
       </c>
       <c r="E586" t="n">
-        <v>-2.78</v>
+        <v>-2.08</v>
       </c>
       <c r="F586" t="n">
-        <v>492.55</v>
+        <v>498.63</v>
       </c>
       <c r="G586" t="n">
         <v>491.73</v>
       </c>
       <c r="H586" t="n">
-        <v>0.82</v>
+        <v>6.9</v>
       </c>
       <c r="I586" t="n">
-        <v>486.5</v>
+        <v>486.36</v>
       </c>
       <c r="J586" t="n">
         <v>481.73</v>
       </c>
       <c r="K586" t="n">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="L586" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         </is>
       </c>
       <c r="N586" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="587">
@@ -30940,31 +30940,31 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>1165</v>
+        <v>1145</v>
       </c>
       <c r="D587" t="n">
         <v>1188.69</v>
       </c>
       <c r="E587" t="n">
-        <v>-23.69</v>
+        <v>-43.69</v>
       </c>
       <c r="F587" t="n">
-        <v>1170.9</v>
+        <v>1169</v>
       </c>
       <c r="G587" t="n">
         <v>1188.69</v>
       </c>
       <c r="H587" t="n">
-        <v>-17.79</v>
+        <v>-19.69</v>
       </c>
       <c r="I587" t="n">
-        <v>1138.7</v>
+        <v>1134.7</v>
       </c>
       <c r="J587" t="n">
         <v>1157.24</v>
       </c>
       <c r="K587" t="n">
-        <v>-18.54</v>
+        <v>-22.54</v>
       </c>
       <c r="L587" t="inlineStr">
         <is>
@@ -30973,11 +30973,11 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N587" t="n">
-        <v>1.99</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="588">
@@ -30992,31 +30992,31 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1037</v>
+        <v>1012.8</v>
       </c>
       <c r="D588" t="n">
         <v>1076.89</v>
       </c>
       <c r="E588" t="n">
-        <v>-39.89</v>
+        <v>-64.09</v>
       </c>
       <c r="F588" t="n">
-        <v>1040.8</v>
+        <v>1033.2</v>
       </c>
       <c r="G588" t="n">
         <v>1076.89</v>
       </c>
       <c r="H588" t="n">
-        <v>-36.09</v>
+        <v>-43.69</v>
       </c>
       <c r="I588" t="n">
-        <v>1022.8</v>
+        <v>1006.8</v>
       </c>
       <c r="J588" t="n">
         <v>997.86</v>
       </c>
       <c r="K588" t="n">
-        <v>24.94</v>
+        <v>8.94</v>
       </c>
       <c r="L588" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         </is>
       </c>
       <c r="N588" t="n">
-        <v>3.7</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="589">
@@ -31044,31 +31044,31 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>1394.6</v>
+        <v>1394</v>
       </c>
       <c r="D589" t="n">
         <v>1358.62</v>
       </c>
       <c r="E589" t="n">
-        <v>35.98</v>
+        <v>35.38</v>
       </c>
       <c r="F589" t="n">
-        <v>1417.9</v>
+        <v>1397.3</v>
       </c>
       <c r="G589" t="n">
         <v>1395.75</v>
       </c>
       <c r="H589" t="n">
-        <v>22.15</v>
+        <v>1.55</v>
       </c>
       <c r="I589" t="n">
-        <v>1391.6</v>
+        <v>1367</v>
       </c>
       <c r="J589" t="n">
         <v>1367.05</v>
       </c>
       <c r="K589" t="n">
-        <v>24.55</v>
+        <v>-0.05</v>
       </c>
       <c r="L589" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         </is>
       </c>
       <c r="N589" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="590">
@@ -31096,31 +31096,31 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>288.1</v>
+        <v>289.5</v>
       </c>
       <c r="D590" t="n">
         <v>298.46</v>
       </c>
       <c r="E590" t="n">
-        <v>-10.36</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="F590" t="n">
-        <v>292.15</v>
+        <v>293.2</v>
       </c>
       <c r="G590" t="n">
         <v>298.46</v>
       </c>
       <c r="H590" t="n">
-        <v>-6.31</v>
+        <v>-5.26</v>
       </c>
       <c r="I590" t="n">
-        <v>287.8</v>
+        <v>289.2</v>
       </c>
       <c r="J590" t="n">
         <v>287.02</v>
       </c>
       <c r="K590" t="n">
-        <v>0.78</v>
+        <v>2.18</v>
       </c>
       <c r="L590" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="N590" t="n">
-        <v>3.47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="591">
@@ -31148,31 +31148,31 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>3275.4</v>
+        <v>3170.2</v>
       </c>
       <c r="D591" t="n">
         <v>3871.32</v>
       </c>
       <c r="E591" t="n">
-        <v>-595.92</v>
+        <v>-701.12</v>
       </c>
       <c r="F591" t="n">
-        <v>3287.4</v>
+        <v>3333</v>
       </c>
       <c r="G591" t="n">
         <v>3871.32</v>
       </c>
       <c r="H591" t="n">
-        <v>-583.92</v>
+        <v>-538.3200000000001</v>
       </c>
       <c r="I591" t="n">
-        <v>3165.6</v>
+        <v>3170.2</v>
       </c>
       <c r="J591" t="n">
         <v>3240.93</v>
       </c>
       <c r="K591" t="n">
-        <v>-75.33</v>
+        <v>-70.73</v>
       </c>
       <c r="L591" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="N591" t="n">
-        <v>15.39</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="592">
@@ -31200,31 +31200,31 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>187.22</v>
+        <v>189</v>
       </c>
       <c r="D592" t="n">
         <v>201.82</v>
       </c>
       <c r="E592" t="n">
-        <v>-14.6</v>
+        <v>-12.82</v>
       </c>
       <c r="F592" t="n">
-        <v>189.95</v>
+        <v>190.75</v>
       </c>
       <c r="G592" t="n">
         <v>201.82</v>
       </c>
       <c r="H592" t="n">
-        <v>-11.87</v>
+        <v>-11.07</v>
       </c>
       <c r="I592" t="n">
-        <v>187.05</v>
+        <v>186.75</v>
       </c>
       <c r="J592" t="n">
         <v>186.04</v>
       </c>
       <c r="K592" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>7.23</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="593">
@@ -31252,31 +31252,31 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1249.7</v>
+        <v>1269</v>
       </c>
       <c r="D593" t="n">
         <v>1165.58</v>
       </c>
       <c r="E593" t="n">
-        <v>84.12</v>
+        <v>103.42</v>
       </c>
       <c r="F593" t="n">
-        <v>1260.3</v>
+        <v>1269</v>
       </c>
       <c r="G593" t="n">
         <v>1265.81</v>
       </c>
       <c r="H593" t="n">
-        <v>-5.51</v>
+        <v>3.19</v>
       </c>
       <c r="I593" t="n">
-        <v>1237.5</v>
+        <v>1235.8</v>
       </c>
       <c r="J593" t="n">
         <v>1240.31</v>
       </c>
       <c r="K593" t="n">
-        <v>-2.81</v>
+        <v>-4.51</v>
       </c>
       <c r="L593" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         </is>
       </c>
       <c r="N593" t="n">
-        <v>7.22</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="594">
@@ -31304,31 +31304,31 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>322.75</v>
+        <v>324.8</v>
       </c>
       <c r="D594" t="n">
         <v>294.8</v>
       </c>
       <c r="E594" t="n">
-        <v>27.95</v>
+        <v>30</v>
       </c>
       <c r="F594" t="n">
-        <v>327.75</v>
+        <v>331</v>
       </c>
       <c r="G594" t="n">
         <v>320.95</v>
       </c>
       <c r="H594" t="n">
-        <v>6.8</v>
+        <v>10.05</v>
       </c>
       <c r="I594" t="n">
-        <v>320.8</v>
+        <v>324.15</v>
       </c>
       <c r="J594" t="n">
         <v>314.28</v>
       </c>
       <c r="K594" t="n">
-        <v>6.52</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L594" t="inlineStr">
         <is>
@@ -31337,11 +31337,11 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N594" t="n">
-        <v>9.48</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="595">
@@ -31356,31 +31356,31 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>1815.6</v>
+        <v>1839.2</v>
       </c>
       <c r="D595" t="n">
         <v>1827.28</v>
       </c>
       <c r="E595" t="n">
-        <v>-11.68</v>
+        <v>11.92</v>
       </c>
       <c r="F595" t="n">
-        <v>1862.8</v>
+        <v>1870</v>
       </c>
       <c r="G595" t="n">
         <v>1827.28</v>
       </c>
       <c r="H595" t="n">
-        <v>35.52</v>
+        <v>42.72</v>
       </c>
       <c r="I595" t="n">
-        <v>1796.4</v>
+        <v>1800.2</v>
       </c>
       <c r="J595" t="n">
         <v>1768.25</v>
       </c>
       <c r="K595" t="n">
-        <v>28.15</v>
+        <v>31.95</v>
       </c>
       <c r="L595" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="N595" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="596">
@@ -31408,31 +31408,31 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>2205</v>
+        <v>2152</v>
       </c>
       <c r="D596" t="n">
         <v>2184.32</v>
       </c>
       <c r="E596" t="n">
-        <v>20.68</v>
+        <v>-32.32</v>
       </c>
       <c r="F596" t="n">
-        <v>2214.5</v>
+        <v>2184.8</v>
       </c>
       <c r="G596" t="n">
         <v>2222.1</v>
       </c>
       <c r="H596" t="n">
-        <v>-7.6</v>
+        <v>-37.3</v>
       </c>
       <c r="I596" t="n">
-        <v>2150.7</v>
+        <v>2147.6</v>
       </c>
       <c r="J596" t="n">
         <v>2176.95</v>
       </c>
       <c r="K596" t="n">
-        <v>-26.25</v>
+        <v>-29.35</v>
       </c>
       <c r="L596" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         </is>
       </c>
       <c r="N596" t="n">
-        <v>0.95</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="597">
@@ -31460,31 +31460,31 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>424.5</v>
+        <v>421.15</v>
       </c>
       <c r="D597" t="n">
         <v>420.52</v>
       </c>
       <c r="E597" t="n">
-        <v>3.98</v>
+        <v>0.63</v>
       </c>
       <c r="F597" t="n">
-        <v>425.95</v>
+        <v>426.9</v>
       </c>
       <c r="G597" t="n">
         <v>424.98</v>
       </c>
       <c r="H597" t="n">
-        <v>0.97</v>
+        <v>1.92</v>
       </c>
       <c r="I597" t="n">
-        <v>421.65</v>
+        <v>421.15</v>
       </c>
       <c r="J597" t="n">
         <v>416.24</v>
       </c>
       <c r="K597" t="n">
-        <v>5.41</v>
+        <v>4.91</v>
       </c>
       <c r="L597" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         </is>
       </c>
       <c r="N597" t="n">
-        <v>0.95</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="598">
@@ -31512,31 +31512,31 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>196.8</v>
+        <v>197</v>
       </c>
       <c r="D598" t="n">
         <v>197.8</v>
       </c>
       <c r="E598" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="F598" t="n">
-        <v>200.1</v>
+        <v>200.04</v>
       </c>
       <c r="G598" t="n">
         <v>198.98</v>
       </c>
       <c r="H598" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="I598" t="n">
-        <v>194.3</v>
+        <v>194.26</v>
       </c>
       <c r="J598" t="n">
         <v>194.95</v>
       </c>
       <c r="K598" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L598" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         </is>
       </c>
       <c r="N598" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="599">
@@ -31564,31 +31564,31 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>601</v>
+        <v>587.95</v>
       </c>
       <c r="D599" t="n">
         <v>589.5700000000001</v>
       </c>
       <c r="E599" t="n">
-        <v>11.43</v>
+        <v>-1.62</v>
       </c>
       <c r="F599" t="n">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="G599" t="n">
         <v>602.8099999999999</v>
       </c>
       <c r="H599" t="n">
-        <v>0.19</v>
+        <v>-3.81</v>
       </c>
       <c r="I599" t="n">
-        <v>592</v>
+        <v>584.5</v>
       </c>
       <c r="J599" t="n">
         <v>590.47</v>
       </c>
       <c r="K599" t="n">
-        <v>1.53</v>
+        <v>-5.97</v>
       </c>
       <c r="L599" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         </is>
       </c>
       <c r="N599" t="n">
-        <v>1.94</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="600">
@@ -31616,31 +31616,31 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>1836</v>
+        <v>1870</v>
       </c>
       <c r="D600" t="n">
         <v>1926.85</v>
       </c>
       <c r="E600" t="n">
-        <v>-90.84999999999999</v>
+        <v>-56.85</v>
       </c>
       <c r="F600" t="n">
-        <v>1866.6</v>
+        <v>1870</v>
       </c>
       <c r="G600" t="n">
         <v>1926.85</v>
       </c>
       <c r="H600" t="n">
-        <v>-60.25</v>
+        <v>-56.85</v>
       </c>
       <c r="I600" t="n">
-        <v>1828.7</v>
+        <v>1834.4</v>
       </c>
       <c r="J600" t="n">
         <v>1778.39</v>
       </c>
       <c r="K600" t="n">
-        <v>50.31</v>
+        <v>56.01</v>
       </c>
       <c r="L600" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         </is>
       </c>
       <c r="N600" t="n">
-        <v>4.71</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="601">
@@ -31668,31 +31668,31 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>431.1</v>
+        <v>431.8</v>
       </c>
       <c r="D601" t="n">
         <v>427.06</v>
       </c>
       <c r="E601" t="n">
-        <v>4.04</v>
+        <v>4.74</v>
       </c>
       <c r="F601" t="n">
-        <v>439.2</v>
+        <v>432.7</v>
       </c>
       <c r="G601" t="n">
         <v>435.37</v>
       </c>
       <c r="H601" t="n">
-        <v>3.83</v>
+        <v>-2.67</v>
       </c>
       <c r="I601" t="n">
-        <v>429.2</v>
+        <v>424.05</v>
       </c>
       <c r="J601" t="n">
         <v>426.55</v>
       </c>
       <c r="K601" t="n">
-        <v>2.65</v>
+        <v>-2.5</v>
       </c>
       <c r="L601" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         </is>
       </c>
       <c r="N601" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="602">
@@ -31720,31 +31720,31 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>5643</v>
+        <v>5657</v>
       </c>
       <c r="D602" t="n">
         <v>5191.68</v>
       </c>
       <c r="E602" t="n">
-        <v>451.32</v>
+        <v>465.32</v>
       </c>
       <c r="F602" t="n">
-        <v>5724.5</v>
+        <v>5668</v>
       </c>
       <c r="G602" t="n">
         <v>5576.42</v>
       </c>
       <c r="H602" t="n">
-        <v>148.08</v>
+        <v>91.58</v>
       </c>
       <c r="I602" t="n">
-        <v>5634</v>
+        <v>5501</v>
       </c>
       <c r="J602" t="n">
         <v>5459.25</v>
       </c>
       <c r="K602" t="n">
-        <v>174.75</v>
+        <v>41.75</v>
       </c>
       <c r="L602" t="inlineStr">
         <is>
@@ -31753,11 +31753,11 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N602" t="n">
-        <v>8.69</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="603">
@@ -31772,31 +31772,31 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>1875.6</v>
+        <v>1902</v>
       </c>
       <c r="D603" t="n">
         <v>1788.34</v>
       </c>
       <c r="E603" t="n">
-        <v>87.26000000000001</v>
+        <v>113.66</v>
       </c>
       <c r="F603" t="n">
-        <v>1932.8</v>
+        <v>1912.7</v>
       </c>
       <c r="G603" t="n">
         <v>1848.68</v>
       </c>
       <c r="H603" t="n">
-        <v>84.12</v>
+        <v>64.02</v>
       </c>
       <c r="I603" t="n">
-        <v>1874</v>
+        <v>1866.1</v>
       </c>
       <c r="J603" t="n">
         <v>1817.04</v>
       </c>
       <c r="K603" t="n">
-        <v>56.96</v>
+        <v>49.06</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="N603" t="n">
-        <v>4.88</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="604">
@@ -31824,31 +31824,31 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>1319.8</v>
+        <v>1330</v>
       </c>
       <c r="D604" t="n">
         <v>1213.53</v>
       </c>
       <c r="E604" t="n">
-        <v>106.27</v>
+        <v>116.47</v>
       </c>
       <c r="F604" t="n">
-        <v>1349.5</v>
+        <v>1348.9</v>
       </c>
       <c r="G604" t="n">
         <v>1320.6</v>
       </c>
       <c r="H604" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="I604" t="n">
-        <v>1313.1</v>
+        <v>1320.2</v>
       </c>
       <c r="J604" t="n">
         <v>1293.43</v>
       </c>
       <c r="K604" t="n">
-        <v>19.67</v>
+        <v>26.77</v>
       </c>
       <c r="L604" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>8.76</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="605">
@@ -31876,31 +31876,31 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>879.7</v>
+        <v>888.75</v>
       </c>
       <c r="D605" t="n">
         <v>885.05</v>
       </c>
       <c r="E605" t="n">
-        <v>-5.35</v>
+        <v>3.7</v>
       </c>
       <c r="F605" t="n">
-        <v>892.4</v>
+        <v>906.7</v>
       </c>
       <c r="G605" t="n">
         <v>891.26</v>
       </c>
       <c r="H605" t="n">
-        <v>1.14</v>
+        <v>15.44</v>
       </c>
       <c r="I605" t="n">
-        <v>879.1</v>
+        <v>882.45</v>
       </c>
       <c r="J605" t="n">
         <v>873.3099999999999</v>
       </c>
       <c r="K605" t="n">
-        <v>5.79</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L605" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         </is>
       </c>
       <c r="N605" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -36898,31 +36898,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>322.75</v>
+        <v>324.8</v>
       </c>
       <c r="D24" t="n">
         <v>294.8</v>
       </c>
       <c r="E24" t="n">
-        <v>27.95</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>327.75</v>
+        <v>331</v>
       </c>
       <c r="G24" t="n">
         <v>320.95</v>
       </c>
       <c r="H24" t="n">
-        <v>6.8</v>
+        <v>10.05</v>
       </c>
       <c r="I24" t="n">
-        <v>320.8</v>
+        <v>324.15</v>
       </c>
       <c r="J24" t="n">
         <v>314.28</v>
       </c>
       <c r="K24" t="n">
-        <v>6.52</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -36931,11 +36931,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>9.48</v>
+        <v>10.18</v>
       </c>
     </row>
   </sheetData>
@@ -40276,31 +40276,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5643</v>
+        <v>5657</v>
       </c>
       <c r="D22" t="n">
         <v>5191.68</v>
       </c>
       <c r="E22" t="n">
-        <v>451.32</v>
+        <v>465.32</v>
       </c>
       <c r="F22" t="n">
-        <v>5724.5</v>
+        <v>5668</v>
       </c>
       <c r="G22" t="n">
         <v>5576.42</v>
       </c>
       <c r="H22" t="n">
-        <v>148.08</v>
+        <v>91.58</v>
       </c>
       <c r="I22" t="n">
-        <v>5634</v>
+        <v>5501</v>
       </c>
       <c r="J22" t="n">
         <v>5459.25</v>
       </c>
       <c r="K22" t="n">
-        <v>174.75</v>
+        <v>41.75</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -40309,11 +40309,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>8.69</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -41506,31 +41506,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>117</v>
+        <v>116.32</v>
       </c>
       <c r="D23" t="n">
         <v>119.19</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.19</v>
+        <v>-2.87</v>
       </c>
       <c r="F23" t="n">
-        <v>118.05</v>
+        <v>118.25</v>
       </c>
       <c r="G23" t="n">
         <v>119.19</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.14</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>116.45</v>
+        <v>116.32</v>
       </c>
       <c r="J23" t="n">
         <v>115.73</v>
       </c>
       <c r="K23" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -30728,35 +30728,35 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>2159.4</v>
+        <v>117</v>
       </c>
       <c r="D583" t="n">
-        <v>2295.45</v>
+        <v>115.1</v>
       </c>
       <c r="E583" t="n">
-        <v>-136.05</v>
+        <v>1.9</v>
       </c>
       <c r="F583" t="n">
-        <v>2232</v>
+        <v>118.05</v>
       </c>
       <c r="G583" t="n">
-        <v>2295.45</v>
+        <v>119.15</v>
       </c>
       <c r="H583" t="n">
-        <v>-63.45</v>
+        <v>-1.1</v>
       </c>
       <c r="I583" t="n">
-        <v>2136.5</v>
+        <v>116.45</v>
       </c>
       <c r="J583" t="n">
-        <v>2250</v>
+        <v>116.15</v>
       </c>
       <c r="K583" t="n">
-        <v>-113.5</v>
+        <v>0.3</v>
       </c>
       <c r="L583" t="inlineStr">
         <is>
@@ -30765,11 +30765,11 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N583" t="n">
-        <v>5.93</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="584">
@@ -30780,35 +30780,35 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>116.32</v>
+        <v>2250</v>
       </c>
       <c r="D584" t="n">
-        <v>119.19</v>
+        <v>2153.37</v>
       </c>
       <c r="E584" t="n">
-        <v>-2.87</v>
+        <v>96.63</v>
       </c>
       <c r="F584" t="n">
-        <v>118.25</v>
+        <v>2281</v>
       </c>
       <c r="G584" t="n">
-        <v>119.19</v>
+        <v>2313.72</v>
       </c>
       <c r="H584" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-32.72</v>
       </c>
       <c r="I584" t="n">
-        <v>116.32</v>
+        <v>2150.4</v>
       </c>
       <c r="J584" t="n">
-        <v>115.73</v>
+        <v>2250</v>
       </c>
       <c r="K584" t="n">
-        <v>0.59</v>
+        <v>-99.59999999999999</v>
       </c>
       <c r="L584" t="inlineStr">
         <is>
@@ -30817,11 +30817,11 @@
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N584" t="n">
-        <v>2.41</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="585">
@@ -30836,31 +30836,31 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>681.65</v>
+        <v>681.9</v>
       </c>
       <c r="D585" t="n">
-        <v>718.01</v>
+        <v>652.55</v>
       </c>
       <c r="E585" t="n">
-        <v>-36.36</v>
+        <v>29.35</v>
       </c>
       <c r="F585" t="n">
-        <v>689.35</v>
+        <v>689.75</v>
       </c>
       <c r="G585" t="n">
-        <v>718.01</v>
+        <v>658.47</v>
       </c>
       <c r="H585" t="n">
-        <v>-28.66</v>
+        <v>31.28</v>
       </c>
       <c r="I585" t="n">
-        <v>671</v>
+        <v>680.8</v>
       </c>
       <c r="J585" t="n">
-        <v>661.8200000000001</v>
+        <v>664.1900000000001</v>
       </c>
       <c r="K585" t="n">
-        <v>9.18</v>
+        <v>16.61</v>
       </c>
       <c r="L585" t="inlineStr">
         <is>
@@ -30869,11 +30869,11 @@
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5.06</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="586">
@@ -30888,31 +30888,31 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>489</v>
+        <v>488.3</v>
       </c>
       <c r="D586" t="n">
-        <v>491.08</v>
+        <v>490.12</v>
       </c>
       <c r="E586" t="n">
-        <v>-2.08</v>
+        <v>-1.82</v>
       </c>
       <c r="F586" t="n">
-        <v>498.63</v>
+        <v>492.55</v>
       </c>
       <c r="G586" t="n">
-        <v>491.73</v>
+        <v>496.02</v>
       </c>
       <c r="H586" t="n">
-        <v>6.9</v>
+        <v>-3.47</v>
       </c>
       <c r="I586" t="n">
-        <v>486.36</v>
+        <v>486.5</v>
       </c>
       <c r="J586" t="n">
-        <v>481.73</v>
+        <v>483.44</v>
       </c>
       <c r="K586" t="n">
-        <v>4.63</v>
+        <v>3.06</v>
       </c>
       <c r="L586" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         </is>
       </c>
       <c r="N586" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="587">
@@ -30940,31 +30940,31 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>1145</v>
+        <v>1165</v>
       </c>
       <c r="D587" t="n">
-        <v>1188.69</v>
+        <v>1131.16</v>
       </c>
       <c r="E587" t="n">
-        <v>-43.69</v>
+        <v>33.84</v>
       </c>
       <c r="F587" t="n">
-        <v>1169</v>
+        <v>1170.9</v>
       </c>
       <c r="G587" t="n">
-        <v>1188.69</v>
+        <v>1191.33</v>
       </c>
       <c r="H587" t="n">
-        <v>-19.69</v>
+        <v>-20.43</v>
       </c>
       <c r="I587" t="n">
-        <v>1134.7</v>
+        <v>1138.7</v>
       </c>
       <c r="J587" t="n">
-        <v>1157.24</v>
+        <v>1161.37</v>
       </c>
       <c r="K587" t="n">
-        <v>-22.54</v>
+        <v>-22.67</v>
       </c>
       <c r="L587" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         </is>
       </c>
       <c r="N587" t="n">
-        <v>3.68</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="588">
@@ -30988,35 +30988,35 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1012.8</v>
+        <v>288.1</v>
       </c>
       <c r="D588" t="n">
-        <v>1076.89</v>
+        <v>282.48</v>
       </c>
       <c r="E588" t="n">
-        <v>-64.09</v>
+        <v>5.62</v>
       </c>
       <c r="F588" t="n">
-        <v>1033.2</v>
+        <v>292.15</v>
       </c>
       <c r="G588" t="n">
-        <v>1076.89</v>
+        <v>295.33</v>
       </c>
       <c r="H588" t="n">
-        <v>-43.69</v>
+        <v>-3.18</v>
       </c>
       <c r="I588" t="n">
-        <v>1006.8</v>
+        <v>287.8</v>
       </c>
       <c r="J588" t="n">
-        <v>997.86</v>
+        <v>288.03</v>
       </c>
       <c r="K588" t="n">
-        <v>8.94</v>
+        <v>-0.23</v>
       </c>
       <c r="L588" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         </is>
       </c>
       <c r="N588" t="n">
-        <v>5.95</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="589">
@@ -31044,31 +31044,31 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>1394</v>
+        <v>1394.6</v>
       </c>
       <c r="D589" t="n">
-        <v>1358.62</v>
+        <v>1442.37</v>
       </c>
       <c r="E589" t="n">
-        <v>35.38</v>
+        <v>-47.77</v>
       </c>
       <c r="F589" t="n">
-        <v>1397.3</v>
+        <v>1417.9</v>
       </c>
       <c r="G589" t="n">
-        <v>1395.75</v>
+        <v>1442.37</v>
       </c>
       <c r="H589" t="n">
-        <v>1.55</v>
+        <v>-24.47</v>
       </c>
       <c r="I589" t="n">
-        <v>1367</v>
+        <v>1391.6</v>
       </c>
       <c r="J589" t="n">
-        <v>1367.05</v>
+        <v>1371.92</v>
       </c>
       <c r="K589" t="n">
-        <v>-0.05</v>
+        <v>19.68</v>
       </c>
       <c r="L589" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         </is>
       </c>
       <c r="N589" t="n">
-        <v>2.6</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="590">
@@ -31092,35 +31092,35 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>289.5</v>
+        <v>1037</v>
       </c>
       <c r="D590" t="n">
-        <v>298.46</v>
+        <v>983.09</v>
       </c>
       <c r="E590" t="n">
-        <v>-8.960000000000001</v>
+        <v>53.91</v>
       </c>
       <c r="F590" t="n">
-        <v>293.2</v>
+        <v>1040.8</v>
       </c>
       <c r="G590" t="n">
-        <v>298.46</v>
+        <v>1022.72</v>
       </c>
       <c r="H590" t="n">
-        <v>-5.26</v>
+        <v>18.08</v>
       </c>
       <c r="I590" t="n">
-        <v>289.2</v>
+        <v>1022.8</v>
       </c>
       <c r="J590" t="n">
-        <v>287.02</v>
+        <v>1001.42</v>
       </c>
       <c r="K590" t="n">
-        <v>2.18</v>
+        <v>21.38</v>
       </c>
       <c r="L590" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="N590" t="n">
-        <v>3</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="591">
@@ -31148,31 +31148,31 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>3170.2</v>
+        <v>3275.4</v>
       </c>
       <c r="D591" t="n">
-        <v>3871.32</v>
+        <v>2703.65</v>
       </c>
       <c r="E591" t="n">
-        <v>-701.12</v>
+        <v>571.75</v>
       </c>
       <c r="F591" t="n">
-        <v>3333</v>
+        <v>3287.4</v>
       </c>
       <c r="G591" t="n">
-        <v>3871.32</v>
+        <v>3336.8</v>
       </c>
       <c r="H591" t="n">
-        <v>-538.3200000000001</v>
+        <v>-49.4</v>
       </c>
       <c r="I591" t="n">
-        <v>3170.2</v>
+        <v>3165.6</v>
       </c>
       <c r="J591" t="n">
-        <v>3240.93</v>
+        <v>3252.46</v>
       </c>
       <c r="K591" t="n">
-        <v>-70.73</v>
+        <v>-86.86</v>
       </c>
       <c r="L591" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="N591" t="n">
-        <v>18.11</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="592">
@@ -31200,31 +31200,31 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>189</v>
+        <v>187.22</v>
       </c>
       <c r="D592" t="n">
-        <v>201.82</v>
+        <v>176.79</v>
       </c>
       <c r="E592" t="n">
-        <v>-12.82</v>
+        <v>10.43</v>
       </c>
       <c r="F592" t="n">
-        <v>190.75</v>
+        <v>189.95</v>
       </c>
       <c r="G592" t="n">
-        <v>201.82</v>
+        <v>191.52</v>
       </c>
       <c r="H592" t="n">
-        <v>-11.07</v>
+        <v>-1.57</v>
       </c>
       <c r="I592" t="n">
-        <v>186.75</v>
+        <v>187.05</v>
       </c>
       <c r="J592" t="n">
-        <v>186.04</v>
+        <v>186.7</v>
       </c>
       <c r="K592" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>6.35</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="593">
@@ -31252,31 +31252,31 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1269</v>
+        <v>1249.7</v>
       </c>
       <c r="D593" t="n">
-        <v>1165.58</v>
+        <v>1371.47</v>
       </c>
       <c r="E593" t="n">
-        <v>103.42</v>
+        <v>-121.77</v>
       </c>
       <c r="F593" t="n">
-        <v>1269</v>
+        <v>1260.3</v>
       </c>
       <c r="G593" t="n">
-        <v>1265.81</v>
+        <v>1371.47</v>
       </c>
       <c r="H593" t="n">
-        <v>3.19</v>
+        <v>-111.17</v>
       </c>
       <c r="I593" t="n">
-        <v>1235.8</v>
+        <v>1237.5</v>
       </c>
       <c r="J593" t="n">
-        <v>1240.31</v>
+        <v>1244.74</v>
       </c>
       <c r="K593" t="n">
-        <v>-4.51</v>
+        <v>-7.24</v>
       </c>
       <c r="L593" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         </is>
       </c>
       <c r="N593" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="594">
@@ -31304,31 +31304,31 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>324.8</v>
+        <v>322.75</v>
       </c>
       <c r="D594" t="n">
-        <v>294.8</v>
+        <v>358.44</v>
       </c>
       <c r="E594" t="n">
-        <v>30</v>
+        <v>-35.69</v>
       </c>
       <c r="F594" t="n">
-        <v>331</v>
+        <v>327.75</v>
       </c>
       <c r="G594" t="n">
-        <v>320.95</v>
+        <v>358.44</v>
       </c>
       <c r="H594" t="n">
-        <v>10.05</v>
+        <v>-30.69</v>
       </c>
       <c r="I594" t="n">
-        <v>324.15</v>
+        <v>320.8</v>
       </c>
       <c r="J594" t="n">
-        <v>314.28</v>
+        <v>315.4</v>
       </c>
       <c r="K594" t="n">
-        <v>9.869999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="L594" t="inlineStr">
         <is>
@@ -31337,11 +31337,11 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N594" t="n">
-        <v>10.18</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="595">
@@ -31352,35 +31352,35 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>1839.2</v>
+        <v>424.5</v>
       </c>
       <c r="D595" t="n">
-        <v>1827.28</v>
+        <v>428.54</v>
       </c>
       <c r="E595" t="n">
-        <v>11.92</v>
+        <v>-4.04</v>
       </c>
       <c r="F595" t="n">
-        <v>1870</v>
+        <v>425.95</v>
       </c>
       <c r="G595" t="n">
-        <v>1827.28</v>
+        <v>428.7</v>
       </c>
       <c r="H595" t="n">
-        <v>42.72</v>
+        <v>-2.75</v>
       </c>
       <c r="I595" t="n">
-        <v>1800.2</v>
+        <v>421.65</v>
       </c>
       <c r="J595" t="n">
-        <v>1768.25</v>
+        <v>417.73</v>
       </c>
       <c r="K595" t="n">
-        <v>31.95</v>
+        <v>3.92</v>
       </c>
       <c r="L595" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="N595" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="596">
@@ -31404,35 +31404,35 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>2152</v>
+        <v>1815.6</v>
       </c>
       <c r="D596" t="n">
-        <v>2184.32</v>
+        <v>1842.05</v>
       </c>
       <c r="E596" t="n">
-        <v>-32.32</v>
+        <v>-26.45</v>
       </c>
       <c r="F596" t="n">
-        <v>2184.8</v>
+        <v>1862.8</v>
       </c>
       <c r="G596" t="n">
-        <v>2222.1</v>
+        <v>1842.05</v>
       </c>
       <c r="H596" t="n">
-        <v>-37.3</v>
+        <v>20.75</v>
       </c>
       <c r="I596" t="n">
-        <v>2147.6</v>
+        <v>1796.4</v>
       </c>
       <c r="J596" t="n">
-        <v>2176.95</v>
+        <v>1774.56</v>
       </c>
       <c r="K596" t="n">
-        <v>-29.35</v>
+        <v>21.84</v>
       </c>
       <c r="L596" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         </is>
       </c>
       <c r="N596" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="597">
@@ -31456,35 +31456,35 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>421.15</v>
+        <v>2205</v>
       </c>
       <c r="D597" t="n">
-        <v>420.52</v>
+        <v>2189.74</v>
       </c>
       <c r="E597" t="n">
-        <v>0.63</v>
+        <v>15.26</v>
       </c>
       <c r="F597" t="n">
-        <v>426.9</v>
+        <v>2214.5</v>
       </c>
       <c r="G597" t="n">
-        <v>424.98</v>
+        <v>2241.53</v>
       </c>
       <c r="H597" t="n">
-        <v>1.92</v>
+        <v>-27.03</v>
       </c>
       <c r="I597" t="n">
-        <v>421.15</v>
+        <v>2150.7</v>
       </c>
       <c r="J597" t="n">
-        <v>416.24</v>
+        <v>2184.71</v>
       </c>
       <c r="K597" t="n">
-        <v>4.91</v>
+        <v>-34.01</v>
       </c>
       <c r="L597" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         </is>
       </c>
       <c r="N597" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="598">
@@ -31508,35 +31508,35 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>197</v>
+        <v>1836</v>
       </c>
       <c r="D598" t="n">
-        <v>197.8</v>
+        <v>1796.09</v>
       </c>
       <c r="E598" t="n">
-        <v>-0.8</v>
+        <v>39.91</v>
       </c>
       <c r="F598" t="n">
-        <v>200.04</v>
+        <v>1866.6</v>
       </c>
       <c r="G598" t="n">
-        <v>198.98</v>
+        <v>1806.48</v>
       </c>
       <c r="H598" t="n">
-        <v>1.06</v>
+        <v>60.12</v>
       </c>
       <c r="I598" t="n">
-        <v>194.26</v>
+        <v>1828.7</v>
       </c>
       <c r="J598" t="n">
-        <v>194.95</v>
+        <v>1784.73</v>
       </c>
       <c r="K598" t="n">
-        <v>-0.6899999999999999</v>
+        <v>43.97</v>
       </c>
       <c r="L598" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         </is>
       </c>
       <c r="N598" t="n">
-        <v>0.4</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="599">
@@ -31564,31 +31564,31 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>587.95</v>
+        <v>601</v>
       </c>
       <c r="D599" t="n">
-        <v>589.5700000000001</v>
+        <v>604.14</v>
       </c>
       <c r="E599" t="n">
-        <v>-1.62</v>
+        <v>-3.14</v>
       </c>
       <c r="F599" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G599" t="n">
-        <v>602.8099999999999</v>
+        <v>608.08</v>
       </c>
       <c r="H599" t="n">
-        <v>-3.81</v>
+        <v>-5.08</v>
       </c>
       <c r="I599" t="n">
-        <v>584.5</v>
+        <v>592</v>
       </c>
       <c r="J599" t="n">
-        <v>590.47</v>
+        <v>592.58</v>
       </c>
       <c r="K599" t="n">
-        <v>-5.97</v>
+        <v>-0.58</v>
       </c>
       <c r="L599" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         </is>
       </c>
       <c r="N599" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="600">
@@ -31612,35 +31612,35 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>1870</v>
+        <v>196.8</v>
       </c>
       <c r="D600" t="n">
-        <v>1926.85</v>
+        <v>197.57</v>
       </c>
       <c r="E600" t="n">
-        <v>-56.85</v>
+        <v>-0.77</v>
       </c>
       <c r="F600" t="n">
-        <v>1870</v>
+        <v>200.1</v>
       </c>
       <c r="G600" t="n">
-        <v>1926.85</v>
+        <v>200.71</v>
       </c>
       <c r="H600" t="n">
-        <v>-56.85</v>
+        <v>-0.61</v>
       </c>
       <c r="I600" t="n">
-        <v>1834.4</v>
+        <v>194.3</v>
       </c>
       <c r="J600" t="n">
-        <v>1778.39</v>
+        <v>195.65</v>
       </c>
       <c r="K600" t="n">
-        <v>56.01</v>
+        <v>-1.35</v>
       </c>
       <c r="L600" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         </is>
       </c>
       <c r="N600" t="n">
-        <v>2.95</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="601">
@@ -31664,35 +31664,35 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>431.8</v>
+        <v>5643</v>
       </c>
       <c r="D601" t="n">
-        <v>427.06</v>
+        <v>6197.97</v>
       </c>
       <c r="E601" t="n">
-        <v>4.74</v>
+        <v>-554.97</v>
       </c>
       <c r="F601" t="n">
-        <v>432.7</v>
+        <v>5724.5</v>
       </c>
       <c r="G601" t="n">
-        <v>435.37</v>
+        <v>6197.97</v>
       </c>
       <c r="H601" t="n">
-        <v>-2.67</v>
+        <v>-473.47</v>
       </c>
       <c r="I601" t="n">
-        <v>424.05</v>
+        <v>5634</v>
       </c>
       <c r="J601" t="n">
-        <v>426.55</v>
+        <v>5478.73</v>
       </c>
       <c r="K601" t="n">
-        <v>-2.5</v>
+        <v>155.27</v>
       </c>
       <c r="L601" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         </is>
       </c>
       <c r="N601" t="n">
-        <v>1.11</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="602">
@@ -31716,35 +31716,35 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>5657</v>
+        <v>431.1</v>
       </c>
       <c r="D602" t="n">
-        <v>5191.68</v>
+        <v>439.37</v>
       </c>
       <c r="E602" t="n">
-        <v>465.32</v>
+        <v>-8.27</v>
       </c>
       <c r="F602" t="n">
-        <v>5668</v>
+        <v>439.2</v>
       </c>
       <c r="G602" t="n">
-        <v>5576.42</v>
+        <v>439.37</v>
       </c>
       <c r="H602" t="n">
-        <v>91.58</v>
+        <v>-0.17</v>
       </c>
       <c r="I602" t="n">
-        <v>5501</v>
+        <v>429.2</v>
       </c>
       <c r="J602" t="n">
-        <v>5459.25</v>
+        <v>428.07</v>
       </c>
       <c r="K602" t="n">
-        <v>41.75</v>
+        <v>1.13</v>
       </c>
       <c r="L602" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         </is>
       </c>
       <c r="N602" t="n">
-        <v>8.960000000000001</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="603">
@@ -31772,31 +31772,31 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>1902</v>
+        <v>1875.6</v>
       </c>
       <c r="D603" t="n">
-        <v>1788.34</v>
+        <v>2010.77</v>
       </c>
       <c r="E603" t="n">
-        <v>113.66</v>
+        <v>-135.17</v>
       </c>
       <c r="F603" t="n">
-        <v>1912.7</v>
+        <v>1932.8</v>
       </c>
       <c r="G603" t="n">
-        <v>1848.68</v>
+        <v>2010.77</v>
       </c>
       <c r="H603" t="n">
-        <v>64.02</v>
+        <v>-77.97</v>
       </c>
       <c r="I603" t="n">
-        <v>1866.1</v>
+        <v>1874</v>
       </c>
       <c r="J603" t="n">
-        <v>1817.04</v>
+        <v>1823.53</v>
       </c>
       <c r="K603" t="n">
-        <v>49.06</v>
+        <v>50.47</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -31805,11 +31805,11 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N603" t="n">
-        <v>6.36</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="604">
@@ -31824,31 +31824,31 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>1330</v>
+        <v>1319.8</v>
       </c>
       <c r="D604" t="n">
-        <v>1213.53</v>
+        <v>1458.05</v>
       </c>
       <c r="E604" t="n">
-        <v>116.47</v>
+        <v>-138.25</v>
       </c>
       <c r="F604" t="n">
-        <v>1348.9</v>
+        <v>1349.5</v>
       </c>
       <c r="G604" t="n">
-        <v>1320.6</v>
+        <v>1458.05</v>
       </c>
       <c r="H604" t="n">
-        <v>28.3</v>
+        <v>-108.55</v>
       </c>
       <c r="I604" t="n">
-        <v>1320.2</v>
+        <v>1313.1</v>
       </c>
       <c r="J604" t="n">
-        <v>1293.43</v>
+        <v>1298.04</v>
       </c>
       <c r="K604" t="n">
-        <v>26.77</v>
+        <v>15.06</v>
       </c>
       <c r="L604" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="605">
@@ -31876,31 +31876,31 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>888.75</v>
+        <v>879.7</v>
       </c>
       <c r="D605" t="n">
-        <v>885.05</v>
+        <v>890.45</v>
       </c>
       <c r="E605" t="n">
-        <v>3.7</v>
+        <v>-10.75</v>
       </c>
       <c r="F605" t="n">
-        <v>906.7</v>
+        <v>892.4</v>
       </c>
       <c r="G605" t="n">
-        <v>891.26</v>
+        <v>899.05</v>
       </c>
       <c r="H605" t="n">
-        <v>15.44</v>
+        <v>-6.65</v>
       </c>
       <c r="I605" t="n">
-        <v>882.45</v>
+        <v>879.1</v>
       </c>
       <c r="J605" t="n">
-        <v>873.3099999999999</v>
+        <v>876.4299999999999</v>
       </c>
       <c r="K605" t="n">
-        <v>9.140000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="L605" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         </is>
       </c>
       <c r="N605" t="n">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>
@@ -36898,31 +36898,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>324.8</v>
+        <v>322.75</v>
       </c>
       <c r="D24" t="n">
-        <v>294.8</v>
+        <v>358.44</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>-35.69</v>
       </c>
       <c r="F24" t="n">
-        <v>331</v>
+        <v>327.75</v>
       </c>
       <c r="G24" t="n">
-        <v>320.95</v>
+        <v>358.44</v>
       </c>
       <c r="H24" t="n">
-        <v>10.05</v>
+        <v>-30.69</v>
       </c>
       <c r="I24" t="n">
-        <v>324.15</v>
+        <v>320.8</v>
       </c>
       <c r="J24" t="n">
-        <v>314.28</v>
+        <v>315.4</v>
       </c>
       <c r="K24" t="n">
-        <v>9.869999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -36931,11 +36931,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>10.18</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -40276,31 +40276,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="D22" t="n">
-        <v>5191.68</v>
+        <v>6197.97</v>
       </c>
       <c r="E22" t="n">
-        <v>465.32</v>
+        <v>-554.97</v>
       </c>
       <c r="F22" t="n">
-        <v>5668</v>
+        <v>5724.5</v>
       </c>
       <c r="G22" t="n">
-        <v>5576.42</v>
+        <v>6197.97</v>
       </c>
       <c r="H22" t="n">
-        <v>91.58</v>
+        <v>-473.47</v>
       </c>
       <c r="I22" t="n">
-        <v>5501</v>
+        <v>5634</v>
       </c>
       <c r="J22" t="n">
-        <v>5459.25</v>
+        <v>5478.73</v>
       </c>
       <c r="K22" t="n">
-        <v>41.75</v>
+        <v>155.27</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41506,31 +41506,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="D23" t="n">
-        <v>119.19</v>
+        <v>115.1</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.87</v>
+        <v>1.9</v>
       </c>
       <c r="F23" t="n">
-        <v>118.25</v>
+        <v>118.05</v>
       </c>
       <c r="G23" t="n">
-        <v>119.19</v>
+        <v>119.15</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>116.32</v>
+        <v>116.45</v>
       </c>
       <c r="J23" t="n">
-        <v>115.73</v>
+        <v>116.15</v>
       </c>
       <c r="K23" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N605"/>
+  <dimension ref="A1:N623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31914,6 +31914,942 @@
       </c>
       <c r="N605" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D606" t="n">
+        <v>2243.21</v>
+      </c>
+      <c r="E606" t="n">
+        <v>-33.21</v>
+      </c>
+      <c r="F606" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="G606" t="n">
+        <v>2243.21</v>
+      </c>
+      <c r="H606" t="n">
+        <v>-18.71</v>
+      </c>
+      <c r="I606" t="n">
+        <v>2190.2</v>
+      </c>
+      <c r="J606" t="n">
+        <v>2178.44</v>
+      </c>
+      <c r="K606" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N606" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>1832.4</v>
+      </c>
+      <c r="D607" t="n">
+        <v>1820.54</v>
+      </c>
+      <c r="E607" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1859</v>
+      </c>
+      <c r="G607" t="n">
+        <v>1821.66</v>
+      </c>
+      <c r="H607" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I607" t="n">
+        <v>1815</v>
+      </c>
+      <c r="J607" t="n">
+        <v>1790.07</v>
+      </c>
+      <c r="K607" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N607" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>487</v>
+      </c>
+      <c r="D608" t="n">
+        <v>489.08</v>
+      </c>
+      <c r="E608" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F608" t="n">
+        <v>492.75</v>
+      </c>
+      <c r="G608" t="n">
+        <v>492.53</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I608" t="n">
+        <v>481.45</v>
+      </c>
+      <c r="J608" t="n">
+        <v>484.28</v>
+      </c>
+      <c r="K608" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N608" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="D609" t="n">
+        <v>299.5</v>
+      </c>
+      <c r="E609" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="F609" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="G609" t="n">
+        <v>299.5</v>
+      </c>
+      <c r="H609" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="I609" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="J609" t="n">
+        <v>290.24</v>
+      </c>
+      <c r="K609" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N609" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>1792</v>
+      </c>
+      <c r="D610" t="n">
+        <v>1846.48</v>
+      </c>
+      <c r="E610" t="n">
+        <v>-54.48</v>
+      </c>
+      <c r="F610" t="n">
+        <v>1843.2</v>
+      </c>
+      <c r="G610" t="n">
+        <v>1846.48</v>
+      </c>
+      <c r="H610" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="I610" t="n">
+        <v>1752.3</v>
+      </c>
+      <c r="J610" t="n">
+        <v>1750.76</v>
+      </c>
+      <c r="K610" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N610" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D611" t="n">
+        <v>1121.76</v>
+      </c>
+      <c r="E611" t="n">
+        <v>-66.76000000000001</v>
+      </c>
+      <c r="F611" t="n">
+        <v>1058.9</v>
+      </c>
+      <c r="G611" t="n">
+        <v>1121.76</v>
+      </c>
+      <c r="H611" t="n">
+        <v>-62.86</v>
+      </c>
+      <c r="I611" t="n">
+        <v>1031.4</v>
+      </c>
+      <c r="J611" t="n">
+        <v>1022.17</v>
+      </c>
+      <c r="K611" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N611" t="n">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>672.7</v>
+      </c>
+      <c r="D612" t="n">
+        <v>708.58</v>
+      </c>
+      <c r="E612" t="n">
+        <v>-35.88</v>
+      </c>
+      <c r="F612" t="n">
+        <v>685</v>
+      </c>
+      <c r="G612" t="n">
+        <v>708.58</v>
+      </c>
+      <c r="H612" t="n">
+        <v>-23.58</v>
+      </c>
+      <c r="I612" t="n">
+        <v>672.7</v>
+      </c>
+      <c r="J612" t="n">
+        <v>655.08</v>
+      </c>
+      <c r="K612" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N612" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>1414.9</v>
+      </c>
+      <c r="D613" t="n">
+        <v>1380.11</v>
+      </c>
+      <c r="E613" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="F613" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G613" t="n">
+        <v>1434.67</v>
+      </c>
+      <c r="H613" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I613" t="n">
+        <v>1383.8</v>
+      </c>
+      <c r="J613" t="n">
+        <v>1410.79</v>
+      </c>
+      <c r="K613" t="n">
+        <v>-26.99</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N613" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="D614" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="E614" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="F614" t="n">
+        <v>117.17</v>
+      </c>
+      <c r="G614" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="H614" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="I614" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="J614" t="n">
+        <v>115.04</v>
+      </c>
+      <c r="K614" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N614" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>3330.2</v>
+      </c>
+      <c r="D615" t="n">
+        <v>4066.71</v>
+      </c>
+      <c r="E615" t="n">
+        <v>-736.51</v>
+      </c>
+      <c r="F615" t="n">
+        <v>3374.4</v>
+      </c>
+      <c r="G615" t="n">
+        <v>4066.71</v>
+      </c>
+      <c r="H615" t="n">
+        <v>-692.3099999999999</v>
+      </c>
+      <c r="I615" t="n">
+        <v>3276.9</v>
+      </c>
+      <c r="J615" t="n">
+        <v>3287.13</v>
+      </c>
+      <c r="K615" t="n">
+        <v>-10.23</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N615" t="n">
+        <v>18.11</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2215</v>
+      </c>
+      <c r="D616" t="n">
+        <v>2332.9</v>
+      </c>
+      <c r="E616" t="n">
+        <v>-117.9</v>
+      </c>
+      <c r="F616" t="n">
+        <v>2255</v>
+      </c>
+      <c r="G616" t="n">
+        <v>2332.9</v>
+      </c>
+      <c r="H616" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+      <c r="I616" t="n">
+        <v>2198.8</v>
+      </c>
+      <c r="J616" t="n">
+        <v>2185.43</v>
+      </c>
+      <c r="K616" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N616" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>1147.9</v>
+      </c>
+      <c r="D617" t="n">
+        <v>1191.7</v>
+      </c>
+      <c r="E617" t="n">
+        <v>-43.8</v>
+      </c>
+      <c r="F617" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G617" t="n">
+        <v>1191.7</v>
+      </c>
+      <c r="H617" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="I617" t="n">
+        <v>1130</v>
+      </c>
+      <c r="J617" t="n">
+        <v>1141.51</v>
+      </c>
+      <c r="K617" t="n">
+        <v>-11.51</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N617" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>589.15</v>
+      </c>
+      <c r="D618" t="n">
+        <v>590.77</v>
+      </c>
+      <c r="E618" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F618" t="n">
+        <v>598</v>
+      </c>
+      <c r="G618" t="n">
+        <v>590.77</v>
+      </c>
+      <c r="H618" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="I618" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="J618" t="n">
+        <v>577.21</v>
+      </c>
+      <c r="K618" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N618" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="D619" t="n">
+        <v>421.47</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F619" t="n">
+        <v>425.7</v>
+      </c>
+      <c r="G619" t="n">
+        <v>421.47</v>
+      </c>
+      <c r="H619" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I619" t="n">
+        <v>421</v>
+      </c>
+      <c r="J619" t="n">
+        <v>414.21</v>
+      </c>
+      <c r="K619" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N619" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="D620" t="n">
+        <v>188.66</v>
+      </c>
+      <c r="E620" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F620" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="G620" t="n">
+        <v>189.17</v>
+      </c>
+      <c r="H620" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I620" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="J620" t="n">
+        <v>185.97</v>
+      </c>
+      <c r="K620" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N620" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>421.45</v>
+      </c>
+      <c r="D621" t="n">
+        <v>416.82</v>
+      </c>
+      <c r="E621" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F621" t="n">
+        <v>434.95</v>
+      </c>
+      <c r="G621" t="n">
+        <v>424.15</v>
+      </c>
+      <c r="H621" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I621" t="n">
+        <v>418.55</v>
+      </c>
+      <c r="J621" t="n">
+        <v>416.98</v>
+      </c>
+      <c r="K621" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N621" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="D622" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="E622" t="n">
+        <v>-12.55</v>
+      </c>
+      <c r="F622" t="n">
+        <v>188.45</v>
+      </c>
+      <c r="G622" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="H622" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="I622" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="J622" t="n">
+        <v>184.32</v>
+      </c>
+      <c r="K622" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N622" t="n">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="D623" t="n">
+        <v>291.17</v>
+      </c>
+      <c r="E623" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="F623" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="G623" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="H623" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="I623" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="J623" t="n">
+        <v>314.23</v>
+      </c>
+      <c r="K623" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N623" t="n">
+        <v>10.18</v>
       </c>
     </row>
   </sheetData>
@@ -35667,7 +36603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36936,6 +37872,58 @@
       </c>
       <c r="N24" t="n">
         <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>291.17</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="F25" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="G25" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="I25" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>314.23</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>10.18</v>
       </c>
     </row>
   </sheetData>
@@ -40327,7 +41315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41544,6 +42532,58 @@
       </c>
       <c r="N23" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="F24" t="n">
+        <v>117.17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="I24" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="J24" t="n">
+        <v>115.04</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -31928,31 +31928,31 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="D606" t="n">
         <v>2243.21</v>
       </c>
       <c r="E606" t="n">
-        <v>-33.21</v>
+        <v>-38.21</v>
       </c>
       <c r="F606" t="n">
-        <v>2224.5</v>
+        <v>2214.5</v>
       </c>
       <c r="G606" t="n">
         <v>2243.21</v>
       </c>
       <c r="H606" t="n">
-        <v>-18.71</v>
+        <v>-28.71</v>
       </c>
       <c r="I606" t="n">
-        <v>2190.2</v>
+        <v>2150.7</v>
       </c>
       <c r="J606" t="n">
         <v>2178.44</v>
       </c>
       <c r="K606" t="n">
-        <v>11.76</v>
+        <v>-27.74</v>
       </c>
       <c r="L606" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         </is>
       </c>
       <c r="N606" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="607">
@@ -31980,31 +31980,31 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1832.4</v>
+        <v>1815.6</v>
       </c>
       <c r="D607" t="n">
         <v>1820.54</v>
       </c>
       <c r="E607" t="n">
-        <v>11.86</v>
+        <v>-4.94</v>
       </c>
       <c r="F607" t="n">
-        <v>1859</v>
+        <v>1862.8</v>
       </c>
       <c r="G607" t="n">
         <v>1821.66</v>
       </c>
       <c r="H607" t="n">
-        <v>37.34</v>
+        <v>41.14</v>
       </c>
       <c r="I607" t="n">
-        <v>1815</v>
+        <v>1796.4</v>
       </c>
       <c r="J607" t="n">
         <v>1790.07</v>
       </c>
       <c r="K607" t="n">
-        <v>24.93</v>
+        <v>6.33</v>
       </c>
       <c r="L607" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         </is>
       </c>
       <c r="N607" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="608">
@@ -32032,31 +32032,31 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>487</v>
+        <v>488.3</v>
       </c>
       <c r="D608" t="n">
         <v>489.08</v>
       </c>
       <c r="E608" t="n">
-        <v>-2.08</v>
+        <v>-0.78</v>
       </c>
       <c r="F608" t="n">
-        <v>492.75</v>
+        <v>492.55</v>
       </c>
       <c r="G608" t="n">
         <v>492.53</v>
       </c>
       <c r="H608" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="I608" t="n">
-        <v>481.45</v>
+        <v>486.5</v>
       </c>
       <c r="J608" t="n">
         <v>484.28</v>
       </c>
       <c r="K608" t="n">
-        <v>-2.83</v>
+        <v>2.22</v>
       </c>
       <c r="L608" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         </is>
       </c>
       <c r="N608" t="n">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="609">
@@ -32084,31 +32084,31 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>290.95</v>
+        <v>288.1</v>
       </c>
       <c r="D609" t="n">
         <v>299.5</v>
       </c>
       <c r="E609" t="n">
-        <v>-8.550000000000001</v>
+        <v>-11.4</v>
       </c>
       <c r="F609" t="n">
-        <v>293.8</v>
+        <v>292.15</v>
       </c>
       <c r="G609" t="n">
         <v>299.5</v>
       </c>
       <c r="H609" t="n">
-        <v>-5.7</v>
+        <v>-7.35</v>
       </c>
       <c r="I609" t="n">
-        <v>288.1</v>
+        <v>287.8</v>
       </c>
       <c r="J609" t="n">
         <v>290.24</v>
       </c>
       <c r="K609" t="n">
-        <v>-2.14</v>
+        <v>-2.44</v>
       </c>
       <c r="L609" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         </is>
       </c>
       <c r="N609" t="n">
-        <v>2.85</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="610">
@@ -32136,31 +32136,31 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1792</v>
+        <v>1836</v>
       </c>
       <c r="D610" t="n">
         <v>1846.48</v>
       </c>
       <c r="E610" t="n">
-        <v>-54.48</v>
+        <v>-10.48</v>
       </c>
       <c r="F610" t="n">
-        <v>1843.2</v>
+        <v>1866.6</v>
       </c>
       <c r="G610" t="n">
         <v>1846.48</v>
       </c>
       <c r="H610" t="n">
-        <v>-3.28</v>
+        <v>20.12</v>
       </c>
       <c r="I610" t="n">
-        <v>1752.3</v>
+        <v>1828.7</v>
       </c>
       <c r="J610" t="n">
         <v>1750.76</v>
       </c>
       <c r="K610" t="n">
-        <v>1.54</v>
+        <v>77.94</v>
       </c>
       <c r="L610" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         </is>
       </c>
       <c r="N610" t="n">
-        <v>2.95</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="611">
@@ -32188,31 +32188,31 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1055</v>
+        <v>1037</v>
       </c>
       <c r="D611" t="n">
         <v>1121.76</v>
       </c>
       <c r="E611" t="n">
-        <v>-66.76000000000001</v>
+        <v>-84.76000000000001</v>
       </c>
       <c r="F611" t="n">
-        <v>1058.9</v>
+        <v>1040.8</v>
       </c>
       <c r="G611" t="n">
         <v>1121.76</v>
       </c>
       <c r="H611" t="n">
-        <v>-62.86</v>
+        <v>-80.95999999999999</v>
       </c>
       <c r="I611" t="n">
-        <v>1031.4</v>
+        <v>1022.8</v>
       </c>
       <c r="J611" t="n">
         <v>1022.17</v>
       </c>
       <c r="K611" t="n">
-        <v>9.23</v>
+        <v>0.63</v>
       </c>
       <c r="L611" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>5.95</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="612">
@@ -32240,31 +32240,31 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>672.7</v>
+        <v>681.9</v>
       </c>
       <c r="D612" t="n">
         <v>708.58</v>
       </c>
       <c r="E612" t="n">
-        <v>-35.88</v>
+        <v>-26.68</v>
       </c>
       <c r="F612" t="n">
-        <v>685</v>
+        <v>689.75</v>
       </c>
       <c r="G612" t="n">
         <v>708.58</v>
       </c>
       <c r="H612" t="n">
-        <v>-23.58</v>
+        <v>-18.83</v>
       </c>
       <c r="I612" t="n">
-        <v>672.7</v>
+        <v>680.8</v>
       </c>
       <c r="J612" t="n">
         <v>655.08</v>
       </c>
       <c r="K612" t="n">
-        <v>17.62</v>
+        <v>25.72</v>
       </c>
       <c r="L612" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         </is>
       </c>
       <c r="N612" t="n">
-        <v>5.06</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="613">
@@ -32292,31 +32292,31 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>1414.9</v>
+        <v>1394.6</v>
       </c>
       <c r="D613" t="n">
         <v>1380.11</v>
       </c>
       <c r="E613" t="n">
-        <v>34.79</v>
+        <v>14.49</v>
       </c>
       <c r="F613" t="n">
-        <v>1438</v>
+        <v>1417.9</v>
       </c>
       <c r="G613" t="n">
         <v>1434.67</v>
       </c>
       <c r="H613" t="n">
-        <v>3.33</v>
+        <v>-16.77</v>
       </c>
       <c r="I613" t="n">
-        <v>1383.8</v>
+        <v>1391.6</v>
       </c>
       <c r="J613" t="n">
         <v>1410.79</v>
       </c>
       <c r="K613" t="n">
-        <v>-26.99</v>
+        <v>-19.19</v>
       </c>
       <c r="L613" t="inlineStr">
         <is>
@@ -32325,11 +32325,11 @@
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N613" t="n">
-        <v>2.52</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="614">
@@ -32344,31 +32344,31 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>115.6</v>
+        <v>117</v>
       </c>
       <c r="D614" t="n">
         <v>118.44</v>
       </c>
       <c r="E614" t="n">
-        <v>-2.84</v>
+        <v>-1.44</v>
       </c>
       <c r="F614" t="n">
-        <v>117.17</v>
+        <v>118.05</v>
       </c>
       <c r="G614" t="n">
         <v>118.44</v>
       </c>
       <c r="H614" t="n">
-        <v>-1.27</v>
+        <v>-0.39</v>
       </c>
       <c r="I614" t="n">
-        <v>115.55</v>
+        <v>116.45</v>
       </c>
       <c r="J614" t="n">
         <v>115.04</v>
       </c>
       <c r="K614" t="n">
-        <v>0.51</v>
+        <v>1.41</v>
       </c>
       <c r="L614" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         </is>
       </c>
       <c r="N614" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="615">
@@ -32396,31 +32396,31 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>3330.2</v>
+        <v>3275.4</v>
       </c>
       <c r="D615" t="n">
         <v>4066.71</v>
       </c>
       <c r="E615" t="n">
-        <v>-736.51</v>
+        <v>-791.3099999999999</v>
       </c>
       <c r="F615" t="n">
-        <v>3374.4</v>
+        <v>3287.4</v>
       </c>
       <c r="G615" t="n">
         <v>4066.71</v>
       </c>
       <c r="H615" t="n">
-        <v>-692.3099999999999</v>
+        <v>-779.3099999999999</v>
       </c>
       <c r="I615" t="n">
-        <v>3276.9</v>
+        <v>3165.6</v>
       </c>
       <c r="J615" t="n">
         <v>3287.13</v>
       </c>
       <c r="K615" t="n">
-        <v>-10.23</v>
+        <v>-121.53</v>
       </c>
       <c r="L615" t="inlineStr">
         <is>
@@ -32429,11 +32429,11 @@
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N615" t="n">
-        <v>18.11</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="616">
@@ -32448,31 +32448,31 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>2215</v>
+        <v>2250</v>
       </c>
       <c r="D616" t="n">
         <v>2332.9</v>
       </c>
       <c r="E616" t="n">
-        <v>-117.9</v>
+        <v>-82.90000000000001</v>
       </c>
       <c r="F616" t="n">
-        <v>2255</v>
+        <v>2281</v>
       </c>
       <c r="G616" t="n">
         <v>2332.9</v>
       </c>
       <c r="H616" t="n">
-        <v>-77.90000000000001</v>
+        <v>-51.9</v>
       </c>
       <c r="I616" t="n">
-        <v>2198.8</v>
+        <v>2150.4</v>
       </c>
       <c r="J616" t="n">
         <v>2185.43</v>
       </c>
       <c r="K616" t="n">
-        <v>13.37</v>
+        <v>-35.03</v>
       </c>
       <c r="L616" t="inlineStr">
         <is>
@@ -32481,11 +32481,11 @@
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N616" t="n">
-        <v>5.05</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="617">
@@ -32500,31 +32500,31 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>1147.9</v>
+        <v>1165</v>
       </c>
       <c r="D617" t="n">
         <v>1191.7</v>
       </c>
       <c r="E617" t="n">
-        <v>-43.8</v>
+        <v>-26.7</v>
       </c>
       <c r="F617" t="n">
-        <v>1168</v>
+        <v>1170.9</v>
       </c>
       <c r="G617" t="n">
         <v>1191.7</v>
       </c>
       <c r="H617" t="n">
-        <v>-23.7</v>
+        <v>-20.8</v>
       </c>
       <c r="I617" t="n">
-        <v>1130</v>
+        <v>1138.7</v>
       </c>
       <c r="J617" t="n">
         <v>1141.51</v>
       </c>
       <c r="K617" t="n">
-        <v>-11.51</v>
+        <v>-2.81</v>
       </c>
       <c r="L617" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="N617" t="n">
-        <v>3.68</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="618">
@@ -32552,31 +32552,31 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>589.15</v>
+        <v>601</v>
       </c>
       <c r="D618" t="n">
         <v>590.77</v>
       </c>
       <c r="E618" t="n">
-        <v>-1.62</v>
+        <v>10.23</v>
       </c>
       <c r="F618" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="G618" t="n">
         <v>590.77</v>
       </c>
       <c r="H618" t="n">
-        <v>7.23</v>
+        <v>12.23</v>
       </c>
       <c r="I618" t="n">
-        <v>587.5</v>
+        <v>592</v>
       </c>
       <c r="J618" t="n">
         <v>577.21</v>
       </c>
       <c r="K618" t="n">
-        <v>10.29</v>
+        <v>14.79</v>
       </c>
       <c r="L618" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="N618" t="n">
-        <v>0.27</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="619">
@@ -32604,31 +32604,31 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>422.1</v>
+        <v>424.5</v>
       </c>
       <c r="D619" t="n">
         <v>421.47</v>
       </c>
       <c r="E619" t="n">
-        <v>0.63</v>
+        <v>3.03</v>
       </c>
       <c r="F619" t="n">
-        <v>425.7</v>
+        <v>425.95</v>
       </c>
       <c r="G619" t="n">
         <v>421.47</v>
       </c>
       <c r="H619" t="n">
-        <v>4.23</v>
+        <v>4.48</v>
       </c>
       <c r="I619" t="n">
-        <v>421</v>
+        <v>421.65</v>
       </c>
       <c r="J619" t="n">
         <v>414.21</v>
       </c>
       <c r="K619" t="n">
-        <v>6.79</v>
+        <v>7.44</v>
       </c>
       <c r="L619" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         </is>
       </c>
       <c r="N619" t="n">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="620">
@@ -32656,31 +32656,31 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>187.9</v>
+        <v>196.8</v>
       </c>
       <c r="D620" t="n">
         <v>188.66</v>
       </c>
       <c r="E620" t="n">
-        <v>-0.76</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F620" t="n">
-        <v>196.99</v>
+        <v>200.1</v>
       </c>
       <c r="G620" t="n">
         <v>189.17</v>
       </c>
       <c r="H620" t="n">
-        <v>7.82</v>
+        <v>10.93</v>
       </c>
       <c r="I620" t="n">
-        <v>187.3</v>
+        <v>194.3</v>
       </c>
       <c r="J620" t="n">
         <v>185.97</v>
       </c>
       <c r="K620" t="n">
-        <v>1.33</v>
+        <v>8.33</v>
       </c>
       <c r="L620" t="inlineStr">
         <is>
@@ -32689,11 +32689,11 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N620" t="n">
-        <v>0.4</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="621">
@@ -32708,31 +32708,31 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>421.45</v>
+        <v>431.1</v>
       </c>
       <c r="D621" t="n">
         <v>416.82</v>
       </c>
       <c r="E621" t="n">
-        <v>4.63</v>
+        <v>14.28</v>
       </c>
       <c r="F621" t="n">
-        <v>434.95</v>
+        <v>439.2</v>
       </c>
       <c r="G621" t="n">
         <v>424.15</v>
       </c>
       <c r="H621" t="n">
-        <v>10.8</v>
+        <v>15.05</v>
       </c>
       <c r="I621" t="n">
-        <v>418.55</v>
+        <v>429.2</v>
       </c>
       <c r="J621" t="n">
         <v>416.98</v>
       </c>
       <c r="K621" t="n">
-        <v>1.57</v>
+        <v>12.22</v>
       </c>
       <c r="L621" t="inlineStr">
         <is>
@@ -32741,11 +32741,11 @@
       </c>
       <c r="M621" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N621" t="n">
-        <v>1.11</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="622">
@@ -32760,31 +32760,31 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>186.04</v>
+        <v>187.22</v>
       </c>
       <c r="D622" t="n">
         <v>198.59</v>
       </c>
       <c r="E622" t="n">
-        <v>-12.55</v>
+        <v>-11.37</v>
       </c>
       <c r="F622" t="n">
-        <v>188.45</v>
+        <v>189.95</v>
       </c>
       <c r="G622" t="n">
         <v>198.59</v>
       </c>
       <c r="H622" t="n">
-        <v>-10.14</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I622" t="n">
-        <v>183.2</v>
+        <v>187.05</v>
       </c>
       <c r="J622" t="n">
         <v>184.32</v>
       </c>
       <c r="K622" t="n">
-        <v>-1.12</v>
+        <v>2.73</v>
       </c>
       <c r="L622" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         </is>
       </c>
       <c r="N622" t="n">
-        <v>6.32</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="623">
@@ -32812,31 +32812,31 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>320.8</v>
+        <v>322.75</v>
       </c>
       <c r="D623" t="n">
         <v>291.17</v>
       </c>
       <c r="E623" t="n">
-        <v>29.63</v>
+        <v>31.58</v>
       </c>
       <c r="F623" t="n">
-        <v>325.75</v>
+        <v>327.75</v>
       </c>
       <c r="G623" t="n">
         <v>319.74</v>
       </c>
       <c r="H623" t="n">
-        <v>6.01</v>
+        <v>8.01</v>
       </c>
       <c r="I623" t="n">
-        <v>319.7</v>
+        <v>320.8</v>
       </c>
       <c r="J623" t="n">
         <v>314.23</v>
       </c>
       <c r="K623" t="n">
-        <v>5.47</v>
+        <v>6.57</v>
       </c>
       <c r="L623" t="inlineStr">
         <is>
@@ -32845,11 +32845,11 @@
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N623" t="n">
-        <v>10.18</v>
+        <v>10.85</v>
       </c>
     </row>
   </sheetData>
@@ -37886,31 +37886,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>320.8</v>
+        <v>322.75</v>
       </c>
       <c r="D25" t="n">
         <v>291.17</v>
       </c>
       <c r="E25" t="n">
-        <v>29.63</v>
+        <v>31.58</v>
       </c>
       <c r="F25" t="n">
-        <v>325.75</v>
+        <v>327.75</v>
       </c>
       <c r="G25" t="n">
         <v>319.74</v>
       </c>
       <c r="H25" t="n">
-        <v>6.01</v>
+        <v>8.01</v>
       </c>
       <c r="I25" t="n">
-        <v>319.7</v>
+        <v>320.8</v>
       </c>
       <c r="J25" t="n">
         <v>314.23</v>
       </c>
       <c r="K25" t="n">
-        <v>5.47</v>
+        <v>6.57</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -37919,11 +37919,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10.18</v>
+        <v>10.85</v>
       </c>
     </row>
   </sheetData>
@@ -42546,31 +42546,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>115.6</v>
+        <v>117</v>
       </c>
       <c r="D24" t="n">
         <v>118.44</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.84</v>
+        <v>-1.44</v>
       </c>
       <c r="F24" t="n">
-        <v>117.17</v>
+        <v>118.05</v>
       </c>
       <c r="G24" t="n">
         <v>118.44</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.27</v>
+        <v>-0.39</v>
       </c>
       <c r="I24" t="n">
-        <v>115.55</v>
+        <v>116.45</v>
       </c>
       <c r="J24" t="n">
         <v>115.04</v>
       </c>
       <c r="K24" t="n">
-        <v>0.51</v>
+        <v>1.41</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N623"/>
+  <dimension ref="A1:N640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32850,6 +32850,890 @@
       </c>
       <c r="N623" t="n">
         <v>10.85</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="D624" t="n">
+        <v>501.3</v>
+      </c>
+      <c r="E624" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="F624" t="n">
+        <v>501.3</v>
+      </c>
+      <c r="G624" t="n">
+        <v>509.59</v>
+      </c>
+      <c r="H624" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="I624" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="J624" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="K624" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N624" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="D625" t="n">
+        <v>1846.07</v>
+      </c>
+      <c r="E625" t="n">
+        <v>-9.67</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1849.9</v>
+      </c>
+      <c r="G625" t="n">
+        <v>1846.07</v>
+      </c>
+      <c r="H625" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I625" t="n">
+        <v>1786.7</v>
+      </c>
+      <c r="J625" t="n">
+        <v>1802.73</v>
+      </c>
+      <c r="K625" t="n">
+        <v>-16.03</v>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N625" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>116</v>
+      </c>
+      <c r="D626" t="n">
+        <v>115.51</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F626" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="G626" t="n">
+        <v>118.11</v>
+      </c>
+      <c r="H626" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="I626" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="J626" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="K626" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N626" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D627" t="n">
+        <v>2199.65</v>
+      </c>
+      <c r="E627" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="F627" t="n">
+        <v>2222</v>
+      </c>
+      <c r="G627" t="n">
+        <v>2255.96</v>
+      </c>
+      <c r="H627" t="n">
+        <v>-33.96</v>
+      </c>
+      <c r="I627" t="n">
+        <v>2198.9</v>
+      </c>
+      <c r="J627" t="n">
+        <v>2206.89</v>
+      </c>
+      <c r="K627" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N627" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D628" t="n">
+        <v>1830.16</v>
+      </c>
+      <c r="E628" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="F628" t="n">
+        <v>1827.9</v>
+      </c>
+      <c r="G628" t="n">
+        <v>1841.34</v>
+      </c>
+      <c r="H628" t="n">
+        <v>-13.44</v>
+      </c>
+      <c r="I628" t="n">
+        <v>1775.9</v>
+      </c>
+      <c r="J628" t="n">
+        <v>1800.79</v>
+      </c>
+      <c r="K628" t="n">
+        <v>-24.89</v>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N628" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>3342</v>
+      </c>
+      <c r="D629" t="n">
+        <v>2713.25</v>
+      </c>
+      <c r="E629" t="n">
+        <v>628.75</v>
+      </c>
+      <c r="F629" t="n">
+        <v>3366.4</v>
+      </c>
+      <c r="G629" t="n">
+        <v>3362.63</v>
+      </c>
+      <c r="H629" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I629" t="n">
+        <v>3279.9</v>
+      </c>
+      <c r="J629" t="n">
+        <v>3288.32</v>
+      </c>
+      <c r="K629" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N629" t="n">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D630" t="n">
+        <v>1426.12</v>
+      </c>
+      <c r="E630" t="n">
+        <v>-26.12</v>
+      </c>
+      <c r="F630" t="n">
+        <v>1417</v>
+      </c>
+      <c r="G630" t="n">
+        <v>1432.51</v>
+      </c>
+      <c r="H630" t="n">
+        <v>-15.51</v>
+      </c>
+      <c r="I630" t="n">
+        <v>1395</v>
+      </c>
+      <c r="J630" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K630" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N630" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>675.1</v>
+      </c>
+      <c r="D631" t="n">
+        <v>654.88</v>
+      </c>
+      <c r="E631" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="F631" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="G631" t="n">
+        <v>654.88</v>
+      </c>
+      <c r="H631" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="I631" t="n">
+        <v>665</v>
+      </c>
+      <c r="J631" t="n">
+        <v>660.7</v>
+      </c>
+      <c r="K631" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N631" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>422.15</v>
+      </c>
+      <c r="D632" t="n">
+        <v>440.51</v>
+      </c>
+      <c r="E632" t="n">
+        <v>-18.36</v>
+      </c>
+      <c r="F632" t="n">
+        <v>426.7</v>
+      </c>
+      <c r="G632" t="n">
+        <v>440.51</v>
+      </c>
+      <c r="H632" t="n">
+        <v>-13.81</v>
+      </c>
+      <c r="I632" t="n">
+        <v>419.85</v>
+      </c>
+      <c r="J632" t="n">
+        <v>422.15</v>
+      </c>
+      <c r="K632" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N632" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>595.5</v>
+      </c>
+      <c r="D633" t="n">
+        <v>610.66</v>
+      </c>
+      <c r="E633" t="n">
+        <v>-15.16</v>
+      </c>
+      <c r="F633" t="n">
+        <v>606.7</v>
+      </c>
+      <c r="G633" t="n">
+        <v>610.66</v>
+      </c>
+      <c r="H633" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="I633" t="n">
+        <v>593</v>
+      </c>
+      <c r="J633" t="n">
+        <v>591.9</v>
+      </c>
+      <c r="K633" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N633" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="D634" t="n">
+        <v>425.64</v>
+      </c>
+      <c r="E634" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="F634" t="n">
+        <v>423.85</v>
+      </c>
+      <c r="G634" t="n">
+        <v>425.64</v>
+      </c>
+      <c r="H634" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="I634" t="n">
+        <v>419</v>
+      </c>
+      <c r="J634" t="n">
+        <v>415.29</v>
+      </c>
+      <c r="K634" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N634" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>1051.5</v>
+      </c>
+      <c r="D635" t="n">
+        <v>979.8200000000001</v>
+      </c>
+      <c r="E635" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="F635" t="n">
+        <v>1060.2</v>
+      </c>
+      <c r="G635" t="n">
+        <v>1052.47</v>
+      </c>
+      <c r="H635" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="I635" t="n">
+        <v>1035.2</v>
+      </c>
+      <c r="J635" t="n">
+        <v>1029.02</v>
+      </c>
+      <c r="K635" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N635" t="n">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D636" t="n">
+        <v>2129.58</v>
+      </c>
+      <c r="E636" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="F636" t="n">
+        <v>2204.8</v>
+      </c>
+      <c r="G636" t="n">
+        <v>2241.12</v>
+      </c>
+      <c r="H636" t="n">
+        <v>-36.32</v>
+      </c>
+      <c r="I636" t="n">
+        <v>2165</v>
+      </c>
+      <c r="J636" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K636" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N636" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="D637" t="n">
+        <v>277.18</v>
+      </c>
+      <c r="E637" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="F637" t="n">
+        <v>291</v>
+      </c>
+      <c r="G637" t="n">
+        <v>292.48</v>
+      </c>
+      <c r="H637" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="I637" t="n">
+        <v>285</v>
+      </c>
+      <c r="J637" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="K637" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N637" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="D638" t="n">
+        <v>174.27</v>
+      </c>
+      <c r="E638" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="F638" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="G638" t="n">
+        <v>187.63</v>
+      </c>
+      <c r="H638" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="I638" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="J638" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="K638" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N638" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="D639" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="E639" t="n">
+        <v>-37.73</v>
+      </c>
+      <c r="F639" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="G639" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="H639" t="n">
+        <v>-35.03</v>
+      </c>
+      <c r="I639" t="n">
+        <v>320.5</v>
+      </c>
+      <c r="J639" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="K639" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N639" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="D640" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="E640" t="n">
+        <v>-9.58</v>
+      </c>
+      <c r="F640" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="G640" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="H640" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="I640" t="n">
+        <v>186.05</v>
+      </c>
+      <c r="J640" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="K640" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N640" t="n">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
@@ -36603,7 +37487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37924,6 +38808,58 @@
       </c>
       <c r="N25" t="n">
         <v>10.85</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-37.73</v>
+      </c>
+      <c r="F26" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-35.03</v>
+      </c>
+      <c r="I26" t="n">
+        <v>320.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>
@@ -41315,7 +42251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42584,6 +43520,58 @@
       </c>
       <c r="N24" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>116</v>
+      </c>
+      <c r="D25" t="n">
+        <v>115.51</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F25" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="G25" t="n">
+        <v>118.11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="I25" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="J25" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -32864,31 +32864,31 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>495.4</v>
+        <v>487</v>
       </c>
       <c r="D624" t="n">
         <v>501.3</v>
       </c>
       <c r="E624" t="n">
-        <v>-5.9</v>
+        <v>-14.3</v>
       </c>
       <c r="F624" t="n">
-        <v>501.3</v>
+        <v>492.75</v>
       </c>
       <c r="G624" t="n">
         <v>509.59</v>
       </c>
       <c r="H624" t="n">
-        <v>-8.289999999999999</v>
+        <v>-16.84</v>
       </c>
       <c r="I624" t="n">
-        <v>482.8</v>
+        <v>481.45</v>
       </c>
       <c r="J624" t="n">
         <v>495.4</v>
       </c>
       <c r="K624" t="n">
-        <v>-12.6</v>
+        <v>-13.95</v>
       </c>
       <c r="L624" t="inlineStr">
         <is>
@@ -32897,11 +32897,11 @@
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N624" t="n">
-        <v>1.18</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="625">
@@ -32916,31 +32916,31 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>1836.4</v>
+        <v>1815.6</v>
       </c>
       <c r="D625" t="n">
         <v>1846.07</v>
       </c>
       <c r="E625" t="n">
-        <v>-9.67</v>
+        <v>-30.47</v>
       </c>
       <c r="F625" t="n">
-        <v>1849.9</v>
+        <v>1862.8</v>
       </c>
       <c r="G625" t="n">
         <v>1846.07</v>
       </c>
       <c r="H625" t="n">
-        <v>3.83</v>
+        <v>16.73</v>
       </c>
       <c r="I625" t="n">
-        <v>1786.7</v>
+        <v>1796.4</v>
       </c>
       <c r="J625" t="n">
         <v>1802.73</v>
       </c>
       <c r="K625" t="n">
-        <v>-16.03</v>
+        <v>-6.33</v>
       </c>
       <c r="L625" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         </is>
       </c>
       <c r="N625" t="n">
-        <v>0.52</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="626">
@@ -32968,31 +32968,31 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>116</v>
+        <v>115.6</v>
       </c>
       <c r="D626" t="n">
         <v>115.51</v>
       </c>
       <c r="E626" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="F626" t="n">
-        <v>116.68</v>
+        <v>117.17</v>
       </c>
       <c r="G626" t="n">
         <v>118.11</v>
       </c>
       <c r="H626" t="n">
-        <v>-1.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I626" t="n">
-        <v>114.95</v>
+        <v>115.55</v>
       </c>
       <c r="J626" t="n">
         <v>115.55</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="L626" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         </is>
       </c>
       <c r="N626" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="627">
@@ -33020,31 +33020,31 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="D627" t="n">
         <v>2199.65</v>
       </c>
       <c r="E627" t="n">
-        <v>20.35</v>
+        <v>10.35</v>
       </c>
       <c r="F627" t="n">
-        <v>2222</v>
+        <v>2224.5</v>
       </c>
       <c r="G627" t="n">
         <v>2255.96</v>
       </c>
       <c r="H627" t="n">
-        <v>-33.96</v>
+        <v>-31.46</v>
       </c>
       <c r="I627" t="n">
-        <v>2198.9</v>
+        <v>2190.2</v>
       </c>
       <c r="J627" t="n">
         <v>2206.89</v>
       </c>
       <c r="K627" t="n">
-        <v>-7.99</v>
+        <v>-16.69</v>
       </c>
       <c r="L627" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="N627" t="n">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="628">
@@ -33072,31 +33072,31 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="D628" t="n">
         <v>1830.16</v>
       </c>
       <c r="E628" t="n">
-        <v>-4.16</v>
+        <v>5.84</v>
       </c>
       <c r="F628" t="n">
-        <v>1827.9</v>
+        <v>1866.6</v>
       </c>
       <c r="G628" t="n">
         <v>1841.34</v>
       </c>
       <c r="H628" t="n">
-        <v>-13.44</v>
+        <v>25.26</v>
       </c>
       <c r="I628" t="n">
-        <v>1775.9</v>
+        <v>1828.7</v>
       </c>
       <c r="J628" t="n">
         <v>1800.79</v>
       </c>
       <c r="K628" t="n">
-        <v>-24.89</v>
+        <v>27.91</v>
       </c>
       <c r="L628" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         </is>
       </c>
       <c r="N628" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="629">
@@ -33124,31 +33124,31 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>3342</v>
+        <v>3330.2</v>
       </c>
       <c r="D629" t="n">
         <v>2713.25</v>
       </c>
       <c r="E629" t="n">
-        <v>628.75</v>
+        <v>616.95</v>
       </c>
       <c r="F629" t="n">
-        <v>3366.4</v>
+        <v>3374.4</v>
       </c>
       <c r="G629" t="n">
         <v>3362.63</v>
       </c>
       <c r="H629" t="n">
-        <v>3.77</v>
+        <v>11.77</v>
       </c>
       <c r="I629" t="n">
-        <v>3279.9</v>
+        <v>3276.9</v>
       </c>
       <c r="J629" t="n">
         <v>3288.32</v>
       </c>
       <c r="K629" t="n">
-        <v>-8.42</v>
+        <v>-11.42</v>
       </c>
       <c r="L629" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         </is>
       </c>
       <c r="N629" t="n">
-        <v>23.17</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="630">
@@ -33176,31 +33176,31 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>1400</v>
+        <v>1394.6</v>
       </c>
       <c r="D630" t="n">
         <v>1426.12</v>
       </c>
       <c r="E630" t="n">
-        <v>-26.12</v>
+        <v>-31.52</v>
       </c>
       <c r="F630" t="n">
-        <v>1417</v>
+        <v>1417.9</v>
       </c>
       <c r="G630" t="n">
         <v>1432.51</v>
       </c>
       <c r="H630" t="n">
-        <v>-15.51</v>
+        <v>-14.61</v>
       </c>
       <c r="I630" t="n">
-        <v>1395</v>
+        <v>1391.6</v>
       </c>
       <c r="J630" t="n">
         <v>1400</v>
       </c>
       <c r="K630" t="n">
-        <v>-5</v>
+        <v>-8.4</v>
       </c>
       <c r="L630" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         </is>
       </c>
       <c r="N630" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="631">
@@ -33228,31 +33228,31 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>675.1</v>
+        <v>681.9</v>
       </c>
       <c r="D631" t="n">
         <v>654.88</v>
       </c>
       <c r="E631" t="n">
-        <v>20.22</v>
+        <v>27.02</v>
       </c>
       <c r="F631" t="n">
-        <v>676.4</v>
+        <v>689.75</v>
       </c>
       <c r="G631" t="n">
         <v>654.88</v>
       </c>
       <c r="H631" t="n">
-        <v>21.52</v>
+        <v>34.87</v>
       </c>
       <c r="I631" t="n">
-        <v>665</v>
+        <v>680.8</v>
       </c>
       <c r="J631" t="n">
         <v>660.7</v>
       </c>
       <c r="K631" t="n">
-        <v>4.3</v>
+        <v>20.1</v>
       </c>
       <c r="L631" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="N631" t="n">
-        <v>3.09</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="632">
@@ -33280,31 +33280,31 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>422.15</v>
+        <v>421.45</v>
       </c>
       <c r="D632" t="n">
         <v>440.51</v>
       </c>
       <c r="E632" t="n">
-        <v>-18.36</v>
+        <v>-19.06</v>
       </c>
       <c r="F632" t="n">
-        <v>426.7</v>
+        <v>434.95</v>
       </c>
       <c r="G632" t="n">
         <v>440.51</v>
       </c>
       <c r="H632" t="n">
-        <v>-13.81</v>
+        <v>-5.56</v>
       </c>
       <c r="I632" t="n">
-        <v>419.85</v>
+        <v>418.55</v>
       </c>
       <c r="J632" t="n">
         <v>422.15</v>
       </c>
       <c r="K632" t="n">
-        <v>-2.3</v>
+        <v>-3.6</v>
       </c>
       <c r="L632" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         </is>
       </c>
       <c r="N632" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="633">
@@ -33332,31 +33332,31 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>595.5</v>
+        <v>589.15</v>
       </c>
       <c r="D633" t="n">
         <v>610.66</v>
       </c>
       <c r="E633" t="n">
-        <v>-15.16</v>
+        <v>-21.51</v>
       </c>
       <c r="F633" t="n">
-        <v>606.7</v>
+        <v>598</v>
       </c>
       <c r="G633" t="n">
         <v>610.66</v>
       </c>
       <c r="H633" t="n">
-        <v>-3.96</v>
+        <v>-12.66</v>
       </c>
       <c r="I633" t="n">
-        <v>593</v>
+        <v>587.5</v>
       </c>
       <c r="J633" t="n">
         <v>591.9</v>
       </c>
       <c r="K633" t="n">
-        <v>1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="L633" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         </is>
       </c>
       <c r="N633" t="n">
-        <v>2.48</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="634">
@@ -33384,31 +33384,31 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>419.25</v>
+        <v>422.1</v>
       </c>
       <c r="D634" t="n">
         <v>425.64</v>
       </c>
       <c r="E634" t="n">
-        <v>-6.39</v>
+        <v>-3.54</v>
       </c>
       <c r="F634" t="n">
-        <v>423.85</v>
+        <v>425.7</v>
       </c>
       <c r="G634" t="n">
         <v>425.64</v>
       </c>
       <c r="H634" t="n">
-        <v>-1.79</v>
+        <v>0.06</v>
       </c>
       <c r="I634" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J634" t="n">
         <v>415.29</v>
       </c>
       <c r="K634" t="n">
-        <v>3.71</v>
+        <v>5.71</v>
       </c>
       <c r="L634" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         </is>
       </c>
       <c r="N634" t="n">
-        <v>1.5</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="635">
@@ -33436,31 +33436,31 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>1051.5</v>
+        <v>1055</v>
       </c>
       <c r="D635" t="n">
         <v>979.8200000000001</v>
       </c>
       <c r="E635" t="n">
-        <v>71.68000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="F635" t="n">
-        <v>1060.2</v>
+        <v>1058.9</v>
       </c>
       <c r="G635" t="n">
         <v>1052.47</v>
       </c>
       <c r="H635" t="n">
-        <v>7.73</v>
+        <v>6.43</v>
       </c>
       <c r="I635" t="n">
-        <v>1035.2</v>
+        <v>1031.4</v>
       </c>
       <c r="J635" t="n">
         <v>1029.02</v>
       </c>
       <c r="K635" t="n">
-        <v>6.18</v>
+        <v>2.38</v>
       </c>
       <c r="L635" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         </is>
       </c>
       <c r="N635" t="n">
-        <v>7.32</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="636">
@@ -33488,31 +33488,31 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>2185</v>
+        <v>2206.5</v>
       </c>
       <c r="D636" t="n">
         <v>2129.58</v>
       </c>
       <c r="E636" t="n">
-        <v>55.42</v>
+        <v>76.92</v>
       </c>
       <c r="F636" t="n">
-        <v>2204.8</v>
+        <v>2246.35</v>
       </c>
       <c r="G636" t="n">
         <v>2241.12</v>
       </c>
       <c r="H636" t="n">
-        <v>-36.32</v>
+        <v>5.23</v>
       </c>
       <c r="I636" t="n">
-        <v>2165</v>
+        <v>2190.36</v>
       </c>
       <c r="J636" t="n">
         <v>2185</v>
       </c>
       <c r="K636" t="n">
-        <v>-20</v>
+        <v>5.36</v>
       </c>
       <c r="L636" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         </is>
       </c>
       <c r="N636" t="n">
-        <v>2.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="637">
@@ -33540,31 +33540,31 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>285.8</v>
+        <v>288.1</v>
       </c>
       <c r="D637" t="n">
         <v>277.18</v>
       </c>
       <c r="E637" t="n">
-        <v>8.619999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="F637" t="n">
-        <v>291</v>
+        <v>292.15</v>
       </c>
       <c r="G637" t="n">
         <v>292.48</v>
       </c>
       <c r="H637" t="n">
-        <v>-1.48</v>
+        <v>-0.33</v>
       </c>
       <c r="I637" t="n">
-        <v>285</v>
+        <v>287.8</v>
       </c>
       <c r="J637" t="n">
         <v>285.8</v>
       </c>
       <c r="K637" t="n">
-        <v>-0.8</v>
+        <v>2</v>
       </c>
       <c r="L637" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         </is>
       </c>
       <c r="N637" t="n">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="638">
@@ -33592,31 +33592,31 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>183.22</v>
+        <v>186.04</v>
       </c>
       <c r="D638" t="n">
         <v>174.27</v>
       </c>
       <c r="E638" t="n">
-        <v>8.949999999999999</v>
+        <v>11.77</v>
       </c>
       <c r="F638" t="n">
-        <v>185.15</v>
+        <v>188.45</v>
       </c>
       <c r="G638" t="n">
         <v>187.63</v>
       </c>
       <c r="H638" t="n">
-        <v>-2.48</v>
+        <v>0.82</v>
       </c>
       <c r="I638" t="n">
-        <v>181.4</v>
+        <v>183.2</v>
       </c>
       <c r="J638" t="n">
         <v>183.22</v>
       </c>
       <c r="K638" t="n">
-        <v>-1.82</v>
+        <v>-0.02</v>
       </c>
       <c r="L638" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         </is>
       </c>
       <c r="N638" t="n">
-        <v>5.14</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="639">
@@ -33644,31 +33644,31 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>321.6</v>
+        <v>322.75</v>
       </c>
       <c r="D639" t="n">
         <v>359.33</v>
       </c>
       <c r="E639" t="n">
-        <v>-37.73</v>
+        <v>-36.58</v>
       </c>
       <c r="F639" t="n">
-        <v>324.3</v>
+        <v>327.75</v>
       </c>
       <c r="G639" t="n">
         <v>359.33</v>
       </c>
       <c r="H639" t="n">
-        <v>-35.03</v>
+        <v>-31.58</v>
       </c>
       <c r="I639" t="n">
-        <v>320.5</v>
+        <v>320.8</v>
       </c>
       <c r="J639" t="n">
         <v>316.58</v>
       </c>
       <c r="K639" t="n">
-        <v>3.92</v>
+        <v>4.22</v>
       </c>
       <c r="L639" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         </is>
       </c>
       <c r="N639" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="640">
@@ -33696,31 +33696,31 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>186.1</v>
+        <v>187.9</v>
       </c>
       <c r="D640" t="n">
         <v>195.68</v>
       </c>
       <c r="E640" t="n">
-        <v>-9.58</v>
+        <v>-7.78</v>
       </c>
       <c r="F640" t="n">
-        <v>190.8</v>
+        <v>196.99</v>
       </c>
       <c r="G640" t="n">
         <v>195.68</v>
       </c>
       <c r="H640" t="n">
-        <v>-4.88</v>
+        <v>1.31</v>
       </c>
       <c r="I640" t="n">
-        <v>186.05</v>
+        <v>187.3</v>
       </c>
       <c r="J640" t="n">
         <v>186.1</v>
       </c>
       <c r="K640" t="n">
-        <v>-0.05</v>
+        <v>1.2</v>
       </c>
       <c r="L640" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         </is>
       </c>
       <c r="N640" t="n">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
     </row>
   </sheetData>
@@ -38822,31 +38822,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>321.6</v>
+        <v>322.75</v>
       </c>
       <c r="D26" t="n">
         <v>359.33</v>
       </c>
       <c r="E26" t="n">
-        <v>-37.73</v>
+        <v>-36.58</v>
       </c>
       <c r="F26" t="n">
-        <v>324.3</v>
+        <v>327.75</v>
       </c>
       <c r="G26" t="n">
         <v>359.33</v>
       </c>
       <c r="H26" t="n">
-        <v>-35.03</v>
+        <v>-31.58</v>
       </c>
       <c r="I26" t="n">
-        <v>320.5</v>
+        <v>320.8</v>
       </c>
       <c r="J26" t="n">
         <v>316.58</v>
       </c>
       <c r="K26" t="n">
-        <v>3.92</v>
+        <v>4.22</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
     </row>
   </sheetData>
@@ -43534,31 +43534,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>116</v>
+        <v>115.6</v>
       </c>
       <c r="D25" t="n">
         <v>115.51</v>
       </c>
       <c r="E25" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="F25" t="n">
-        <v>116.68</v>
+        <v>117.17</v>
       </c>
       <c r="G25" t="n">
         <v>118.11</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>114.95</v>
+        <v>115.55</v>
       </c>
       <c r="J25" t="n">
         <v>115.55</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N640"/>
+  <dimension ref="A1:N655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33734,6 +33734,786 @@
       </c>
       <c r="N640" t="n">
         <v>3.98</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>498.95</v>
+      </c>
+      <c r="D641" t="n">
+        <v>488.59</v>
+      </c>
+      <c r="E641" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="F641" t="n">
+        <v>504.9</v>
+      </c>
+      <c r="G641" t="n">
+        <v>500.46</v>
+      </c>
+      <c r="H641" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="I641" t="n">
+        <v>496</v>
+      </c>
+      <c r="J641" t="n">
+        <v>486.3</v>
+      </c>
+      <c r="K641" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N641" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="D642" t="n">
+        <v>116.62</v>
+      </c>
+      <c r="E642" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F642" t="n">
+        <v>117</v>
+      </c>
+      <c r="G642" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="H642" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I642" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="J642" t="n">
+        <v>114.21</v>
+      </c>
+      <c r="K642" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N642" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D643" t="n">
+        <v>4144.62</v>
+      </c>
+      <c r="E643" t="n">
+        <v>-794.62</v>
+      </c>
+      <c r="F643" t="n">
+        <v>3398</v>
+      </c>
+      <c r="G643" t="n">
+        <v>4144.62</v>
+      </c>
+      <c r="H643" t="n">
+        <v>-746.62</v>
+      </c>
+      <c r="I643" t="n">
+        <v>3323.5</v>
+      </c>
+      <c r="J643" t="n">
+        <v>3320.78</v>
+      </c>
+      <c r="K643" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N643" t="n">
+        <v>19.17</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>183.89</v>
+      </c>
+      <c r="D644" t="n">
+        <v>197.88</v>
+      </c>
+      <c r="E644" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="F644" t="n">
+        <v>183.89</v>
+      </c>
+      <c r="G644" t="n">
+        <v>197.88</v>
+      </c>
+      <c r="H644" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="I644" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="J644" t="n">
+        <v>182.04</v>
+      </c>
+      <c r="K644" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N644" t="n">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="D645" t="n">
+        <v>418.73</v>
+      </c>
+      <c r="E645" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="F645" t="n">
+        <v>436</v>
+      </c>
+      <c r="G645" t="n">
+        <v>443.68</v>
+      </c>
+      <c r="H645" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="I645" t="n">
+        <v>421.65</v>
+      </c>
+      <c r="J645" t="n">
+        <v>431.43</v>
+      </c>
+      <c r="K645" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N645" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="D646" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="E646" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="F646" t="n">
+        <v>189.4</v>
+      </c>
+      <c r="G646" t="n">
+        <v>189.59</v>
+      </c>
+      <c r="H646" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I646" t="n">
+        <v>185.36</v>
+      </c>
+      <c r="J646" t="n">
+        <v>184.31</v>
+      </c>
+      <c r="K646" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N646" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>605.4</v>
+      </c>
+      <c r="D647" t="n">
+        <v>588.75</v>
+      </c>
+      <c r="E647" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="F647" t="n">
+        <v>608.75</v>
+      </c>
+      <c r="G647" t="n">
+        <v>610.71</v>
+      </c>
+      <c r="H647" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="I647" t="n">
+        <v>593.1</v>
+      </c>
+      <c r="J647" t="n">
+        <v>593.55</v>
+      </c>
+      <c r="K647" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N647" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="D648" t="n">
+        <v>299.54</v>
+      </c>
+      <c r="E648" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="F648" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="G648" t="n">
+        <v>299.54</v>
+      </c>
+      <c r="H648" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="I648" t="n">
+        <v>284.15</v>
+      </c>
+      <c r="J648" t="n">
+        <v>283.91</v>
+      </c>
+      <c r="K648" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N648" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D649" t="n">
+        <v>1820.19</v>
+      </c>
+      <c r="E649" t="n">
+        <v>-20.19</v>
+      </c>
+      <c r="F649" t="n">
+        <v>1814.7</v>
+      </c>
+      <c r="G649" t="n">
+        <v>1820.19</v>
+      </c>
+      <c r="H649" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="I649" t="n">
+        <v>1787.5</v>
+      </c>
+      <c r="J649" t="n">
+        <v>1741.68</v>
+      </c>
+      <c r="K649" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N649" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>1368.6</v>
+      </c>
+      <c r="D650" t="n">
+        <v>1349.06</v>
+      </c>
+      <c r="E650" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="F650" t="n">
+        <v>1393</v>
+      </c>
+      <c r="G650" t="n">
+        <v>1387.43</v>
+      </c>
+      <c r="H650" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="I650" t="n">
+        <v>1360</v>
+      </c>
+      <c r="J650" t="n">
+        <v>1348.67</v>
+      </c>
+      <c r="K650" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N650" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>414</v>
+      </c>
+      <c r="D651" t="n">
+        <v>413.84</v>
+      </c>
+      <c r="E651" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F651" t="n">
+        <v>420.65</v>
+      </c>
+      <c r="G651" t="n">
+        <v>416.75</v>
+      </c>
+      <c r="H651" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I651" t="n">
+        <v>413.95</v>
+      </c>
+      <c r="J651" t="n">
+        <v>405.18</v>
+      </c>
+      <c r="K651" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N651" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>2168</v>
+      </c>
+      <c r="D652" t="n">
+        <v>2266.37</v>
+      </c>
+      <c r="E652" t="n">
+        <v>-98.37</v>
+      </c>
+      <c r="F652" t="n">
+        <v>2194.9</v>
+      </c>
+      <c r="G652" t="n">
+        <v>2266.37</v>
+      </c>
+      <c r="H652" t="n">
+        <v>-71.47</v>
+      </c>
+      <c r="I652" t="n">
+        <v>2165</v>
+      </c>
+      <c r="J652" t="n">
+        <v>2156.18</v>
+      </c>
+      <c r="K652" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N652" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>555</v>
+      </c>
+      <c r="D653" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="E653" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F653" t="n">
+        <v>564.75</v>
+      </c>
+      <c r="G653" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="H653" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="I653" t="n">
+        <v>550.45</v>
+      </c>
+      <c r="J653" t="n">
+        <v>536.85</v>
+      </c>
+      <c r="K653" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N653" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D654" t="n">
+        <v>1112.48</v>
+      </c>
+      <c r="E654" t="n">
+        <v>-87.48</v>
+      </c>
+      <c r="F654" t="n">
+        <v>1049.6</v>
+      </c>
+      <c r="G654" t="n">
+        <v>1112.48</v>
+      </c>
+      <c r="H654" t="n">
+        <v>-62.88</v>
+      </c>
+      <c r="I654" t="n">
+        <v>1019</v>
+      </c>
+      <c r="J654" t="n">
+        <v>991.4400000000001</v>
+      </c>
+      <c r="K654" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N654" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="D655" t="n">
+        <v>290.26</v>
+      </c>
+      <c r="E655" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="F655" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="G655" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="H655" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I655" t="n">
+        <v>318</v>
+      </c>
+      <c r="J655" t="n">
+        <v>312.05</v>
+      </c>
+      <c r="K655" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N655" t="n">
+        <v>10.45</v>
       </c>
     </row>
   </sheetData>
@@ -37487,7 +38267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38860,6 +39640,58 @@
       </c>
       <c r="N26" t="n">
         <v>10.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>290.26</v>
+      </c>
+      <c r="E27" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="F27" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I27" t="n">
+        <v>318</v>
+      </c>
+      <c r="J27" t="n">
+        <v>312.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>10.45</v>
       </c>
     </row>
   </sheetData>
@@ -42251,7 +43083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43572,6 +44404,58 @@
       </c>
       <c r="N25" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="D26" t="n">
+        <v>116.62</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F26" t="n">
+        <v>117</v>
+      </c>
+      <c r="G26" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>114.21</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -33748,31 +33748,31 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>498.95</v>
+        <v>495.4</v>
       </c>
       <c r="D641" t="n">
         <v>488.59</v>
       </c>
       <c r="E641" t="n">
-        <v>10.36</v>
+        <v>6.81</v>
       </c>
       <c r="F641" t="n">
-        <v>504.9</v>
+        <v>501.3</v>
       </c>
       <c r="G641" t="n">
         <v>500.46</v>
       </c>
       <c r="H641" t="n">
-        <v>4.44</v>
+        <v>0.84</v>
       </c>
       <c r="I641" t="n">
-        <v>496</v>
+        <v>482.8</v>
       </c>
       <c r="J641" t="n">
         <v>486.3</v>
       </c>
       <c r="K641" t="n">
-        <v>9.699999999999999</v>
+        <v>-3.5</v>
       </c>
       <c r="L641" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         </is>
       </c>
       <c r="N641" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="642">
@@ -33800,31 +33800,31 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>115.61</v>
+        <v>116</v>
       </c>
       <c r="D642" t="n">
         <v>116.62</v>
       </c>
       <c r="E642" t="n">
-        <v>-1.01</v>
+        <v>-0.62</v>
       </c>
       <c r="F642" t="n">
-        <v>117</v>
+        <v>116.68</v>
       </c>
       <c r="G642" t="n">
         <v>117.48</v>
       </c>
       <c r="H642" t="n">
-        <v>-0.48</v>
+        <v>-0.8</v>
       </c>
       <c r="I642" t="n">
-        <v>115.25</v>
+        <v>114.95</v>
       </c>
       <c r="J642" t="n">
         <v>114.21</v>
       </c>
       <c r="K642" t="n">
-        <v>1.04</v>
+        <v>0.74</v>
       </c>
       <c r="L642" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         </is>
       </c>
       <c r="N642" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="643">
@@ -33852,31 +33852,31 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>3350</v>
+        <v>3342</v>
       </c>
       <c r="D643" t="n">
         <v>4144.62</v>
       </c>
       <c r="E643" t="n">
-        <v>-794.62</v>
+        <v>-802.62</v>
       </c>
       <c r="F643" t="n">
-        <v>3398</v>
+        <v>3366.4</v>
       </c>
       <c r="G643" t="n">
         <v>4144.62</v>
       </c>
       <c r="H643" t="n">
-        <v>-746.62</v>
+        <v>-778.22</v>
       </c>
       <c r="I643" t="n">
-        <v>3323.5</v>
+        <v>3279.9</v>
       </c>
       <c r="J643" t="n">
         <v>3320.78</v>
       </c>
       <c r="K643" t="n">
-        <v>2.72</v>
+        <v>-40.88</v>
       </c>
       <c r="L643" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         </is>
       </c>
       <c r="N643" t="n">
-        <v>19.17</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="644">
@@ -33904,31 +33904,31 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>183.89</v>
+        <v>183.22</v>
       </c>
       <c r="D644" t="n">
         <v>197.88</v>
       </c>
       <c r="E644" t="n">
-        <v>-13.99</v>
+        <v>-14.66</v>
       </c>
       <c r="F644" t="n">
-        <v>183.89</v>
+        <v>185.15</v>
       </c>
       <c r="G644" t="n">
         <v>197.88</v>
       </c>
       <c r="H644" t="n">
-        <v>-13.99</v>
+        <v>-12.73</v>
       </c>
       <c r="I644" t="n">
-        <v>180.82</v>
+        <v>181.4</v>
       </c>
       <c r="J644" t="n">
         <v>182.04</v>
       </c>
       <c r="K644" t="n">
-        <v>-1.22</v>
+        <v>-0.64</v>
       </c>
       <c r="L644" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         </is>
       </c>
       <c r="N644" t="n">
-        <v>7.07</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="645">
@@ -33956,31 +33956,31 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>433.7</v>
+        <v>422.15</v>
       </c>
       <c r="D645" t="n">
         <v>418.73</v>
       </c>
       <c r="E645" t="n">
-        <v>14.97</v>
+        <v>3.42</v>
       </c>
       <c r="F645" t="n">
-        <v>436</v>
+        <v>426.7</v>
       </c>
       <c r="G645" t="n">
         <v>443.68</v>
       </c>
       <c r="H645" t="n">
-        <v>-7.68</v>
+        <v>-16.98</v>
       </c>
       <c r="I645" t="n">
-        <v>421.65</v>
+        <v>419.85</v>
       </c>
       <c r="J645" t="n">
         <v>431.43</v>
       </c>
       <c r="K645" t="n">
-        <v>-9.779999999999999</v>
+        <v>-11.58</v>
       </c>
       <c r="L645" t="inlineStr">
         <is>
@@ -33989,11 +33989,11 @@
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N645" t="n">
-        <v>3.58</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="646">
@@ -34008,31 +34008,31 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>186.4</v>
+        <v>186.1</v>
       </c>
       <c r="D646" t="n">
         <v>180.42</v>
       </c>
       <c r="E646" t="n">
-        <v>5.98</v>
+        <v>5.68</v>
       </c>
       <c r="F646" t="n">
-        <v>189.4</v>
+        <v>190.8</v>
       </c>
       <c r="G646" t="n">
         <v>189.59</v>
       </c>
       <c r="H646" t="n">
-        <v>-0.19</v>
+        <v>1.21</v>
       </c>
       <c r="I646" t="n">
-        <v>185.36</v>
+        <v>186.05</v>
       </c>
       <c r="J646" t="n">
         <v>184.31</v>
       </c>
       <c r="K646" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="L646" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="N646" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="647">
@@ -34060,31 +34060,31 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>605.4</v>
+        <v>595.5</v>
       </c>
       <c r="D647" t="n">
         <v>588.75</v>
       </c>
       <c r="E647" t="n">
-        <v>16.65</v>
+        <v>6.75</v>
       </c>
       <c r="F647" t="n">
-        <v>608.75</v>
+        <v>606.7</v>
       </c>
       <c r="G647" t="n">
         <v>610.71</v>
       </c>
       <c r="H647" t="n">
-        <v>-1.96</v>
+        <v>-4.01</v>
       </c>
       <c r="I647" t="n">
-        <v>593.1</v>
+        <v>593</v>
       </c>
       <c r="J647" t="n">
         <v>593.55</v>
       </c>
       <c r="K647" t="n">
-        <v>-0.45</v>
+        <v>-0.55</v>
       </c>
       <c r="L647" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         </is>
       </c>
       <c r="N647" t="n">
-        <v>2.83</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="648">
@@ -34112,31 +34112,31 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>285.9</v>
+        <v>285.8</v>
       </c>
       <c r="D648" t="n">
         <v>299.54</v>
       </c>
       <c r="E648" t="n">
-        <v>-13.64</v>
+        <v>-13.74</v>
       </c>
       <c r="F648" t="n">
-        <v>288.5</v>
+        <v>291</v>
       </c>
       <c r="G648" t="n">
         <v>299.54</v>
       </c>
       <c r="H648" t="n">
-        <v>-11.04</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="I648" t="n">
-        <v>284.15</v>
+        <v>285</v>
       </c>
       <c r="J648" t="n">
         <v>283.91</v>
       </c>
       <c r="K648" t="n">
-        <v>0.24</v>
+        <v>1.09</v>
       </c>
       <c r="L648" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         </is>
       </c>
       <c r="N648" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="649">
@@ -34164,31 +34164,31 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>1800</v>
+        <v>1826</v>
       </c>
       <c r="D649" t="n">
         <v>1820.19</v>
       </c>
       <c r="E649" t="n">
-        <v>-20.19</v>
+        <v>5.81</v>
       </c>
       <c r="F649" t="n">
-        <v>1814.7</v>
+        <v>1827.9</v>
       </c>
       <c r="G649" t="n">
         <v>1820.19</v>
       </c>
       <c r="H649" t="n">
-        <v>-5.49</v>
+        <v>7.71</v>
       </c>
       <c r="I649" t="n">
-        <v>1787.5</v>
+        <v>1775.9</v>
       </c>
       <c r="J649" t="n">
         <v>1741.68</v>
       </c>
       <c r="K649" t="n">
-        <v>45.82</v>
+        <v>34.22</v>
       </c>
       <c r="L649" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         </is>
       </c>
       <c r="N649" t="n">
-        <v>1.11</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="650">
@@ -34216,31 +34216,31 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1368.6</v>
+        <v>1400</v>
       </c>
       <c r="D650" t="n">
         <v>1349.06</v>
       </c>
       <c r="E650" t="n">
-        <v>19.54</v>
+        <v>50.94</v>
       </c>
       <c r="F650" t="n">
-        <v>1393</v>
+        <v>1417</v>
       </c>
       <c r="G650" t="n">
         <v>1387.43</v>
       </c>
       <c r="H650" t="n">
-        <v>5.57</v>
+        <v>29.57</v>
       </c>
       <c r="I650" t="n">
-        <v>1360</v>
+        <v>1395</v>
       </c>
       <c r="J650" t="n">
         <v>1348.67</v>
       </c>
       <c r="K650" t="n">
-        <v>11.33</v>
+        <v>46.33</v>
       </c>
       <c r="L650" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         </is>
       </c>
       <c r="N650" t="n">
-        <v>1.45</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="651">
@@ -34268,31 +34268,31 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>414</v>
+        <v>419.25</v>
       </c>
       <c r="D651" t="n">
         <v>413.84</v>
       </c>
       <c r="E651" t="n">
-        <v>0.16</v>
+        <v>5.41</v>
       </c>
       <c r="F651" t="n">
-        <v>420.65</v>
+        <v>423.85</v>
       </c>
       <c r="G651" t="n">
         <v>416.75</v>
       </c>
       <c r="H651" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="I651" t="n">
-        <v>413.95</v>
+        <v>419</v>
       </c>
       <c r="J651" t="n">
         <v>405.18</v>
       </c>
       <c r="K651" t="n">
-        <v>8.77</v>
+        <v>13.82</v>
       </c>
       <c r="L651" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         </is>
       </c>
       <c r="N651" t="n">
-        <v>0.04</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="652">
@@ -34320,22 +34320,22 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>2168</v>
+        <v>2185</v>
       </c>
       <c r="D652" t="n">
         <v>2266.37</v>
       </c>
       <c r="E652" t="n">
-        <v>-98.37</v>
+        <v>-81.37</v>
       </c>
       <c r="F652" t="n">
-        <v>2194.9</v>
+        <v>2204.8</v>
       </c>
       <c r="G652" t="n">
         <v>2266.37</v>
       </c>
       <c r="H652" t="n">
-        <v>-71.47</v>
+        <v>-61.57</v>
       </c>
       <c r="I652" t="n">
         <v>2165</v>
@@ -34357,7 +34357,7 @@
         </is>
       </c>
       <c r="N652" t="n">
-        <v>4.34</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="653">
@@ -34372,31 +34372,31 @@
         </is>
       </c>
       <c r="C653" t="n">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D653" t="n">
         <v>558.8</v>
       </c>
       <c r="E653" t="n">
-        <v>-3.8</v>
+        <v>4.2</v>
       </c>
       <c r="F653" t="n">
-        <v>564.75</v>
+        <v>563</v>
       </c>
       <c r="G653" t="n">
         <v>558.8</v>
       </c>
       <c r="H653" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="I653" t="n">
-        <v>550.45</v>
+        <v>545.4</v>
       </c>
       <c r="J653" t="n">
         <v>536.85</v>
       </c>
       <c r="K653" t="n">
-        <v>13.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L653" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         </is>
       </c>
       <c r="N653" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="654">
@@ -34424,31 +34424,31 @@
         </is>
       </c>
       <c r="C654" t="n">
-        <v>1025</v>
+        <v>1051.5</v>
       </c>
       <c r="D654" t="n">
         <v>1112.48</v>
       </c>
       <c r="E654" t="n">
-        <v>-87.48</v>
+        <v>-60.98</v>
       </c>
       <c r="F654" t="n">
-        <v>1049.6</v>
+        <v>1060.2</v>
       </c>
       <c r="G654" t="n">
         <v>1112.48</v>
       </c>
       <c r="H654" t="n">
-        <v>-62.88</v>
+        <v>-52.28</v>
       </c>
       <c r="I654" t="n">
-        <v>1019</v>
+        <v>1035.2</v>
       </c>
       <c r="J654" t="n">
         <v>991.4400000000001</v>
       </c>
       <c r="K654" t="n">
-        <v>27.56</v>
+        <v>43.76</v>
       </c>
       <c r="L654" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="N654" t="n">
-        <v>7.86</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="655">
@@ -34476,31 +34476,31 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>320.6</v>
+        <v>321.6</v>
       </c>
       <c r="D655" t="n">
         <v>290.26</v>
       </c>
       <c r="E655" t="n">
-        <v>30.34</v>
+        <v>31.34</v>
       </c>
       <c r="F655" t="n">
-        <v>322.55</v>
+        <v>324.3</v>
       </c>
       <c r="G655" t="n">
         <v>318.31</v>
       </c>
       <c r="H655" t="n">
-        <v>4.24</v>
+        <v>5.99</v>
       </c>
       <c r="I655" t="n">
-        <v>318</v>
+        <v>320.5</v>
       </c>
       <c r="J655" t="n">
         <v>312.05</v>
       </c>
       <c r="K655" t="n">
-        <v>5.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L655" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         </is>
       </c>
       <c r="N655" t="n">
-        <v>10.45</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
@@ -39654,31 +39654,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>320.6</v>
+        <v>321.6</v>
       </c>
       <c r="D27" t="n">
         <v>290.26</v>
       </c>
       <c r="E27" t="n">
-        <v>30.34</v>
+        <v>31.34</v>
       </c>
       <c r="F27" t="n">
-        <v>322.55</v>
+        <v>324.3</v>
       </c>
       <c r="G27" t="n">
         <v>318.31</v>
       </c>
       <c r="H27" t="n">
-        <v>4.24</v>
+        <v>5.99</v>
       </c>
       <c r="I27" t="n">
-        <v>318</v>
+        <v>320.5</v>
       </c>
       <c r="J27" t="n">
         <v>312.05</v>
       </c>
       <c r="K27" t="n">
-        <v>5.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>10.45</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
@@ -44418,31 +44418,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>115.61</v>
+        <v>116</v>
       </c>
       <c r="D26" t="n">
         <v>116.62</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.01</v>
+        <v>-0.62</v>
       </c>
       <c r="F26" t="n">
-        <v>117</v>
+        <v>116.68</v>
       </c>
       <c r="G26" t="n">
         <v>117.48</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.48</v>
+        <v>-0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>115.25</v>
+        <v>114.95</v>
       </c>
       <c r="J26" t="n">
         <v>114.21</v>
       </c>
       <c r="K26" t="n">
-        <v>1.04</v>
+        <v>0.74</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N655"/>
+  <dimension ref="A1:N668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34514,6 +34514,682 @@
       </c>
       <c r="N655" t="n">
         <v>10.8</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="D656" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="E656" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="F656" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G656" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="H656" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I656" t="n">
+        <v>115.47</v>
+      </c>
+      <c r="J656" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="K656" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N656" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>500.3</v>
+      </c>
+      <c r="D657" t="n">
+        <v>511.33</v>
+      </c>
+      <c r="E657" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="F657" t="n">
+        <v>514.45</v>
+      </c>
+      <c r="G657" t="n">
+        <v>511.33</v>
+      </c>
+      <c r="H657" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I657" t="n">
+        <v>497.75</v>
+      </c>
+      <c r="J657" t="n">
+        <v>494.72</v>
+      </c>
+      <c r="K657" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N657" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="D658" t="n">
+        <v>2132.94</v>
+      </c>
+      <c r="E658" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="F658" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="G658" t="n">
+        <v>2204.11</v>
+      </c>
+      <c r="H658" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="I658" t="n">
+        <v>2158.4</v>
+      </c>
+      <c r="J658" t="n">
+        <v>2172.86</v>
+      </c>
+      <c r="K658" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N658" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D659" t="n">
+        <v>2690.92</v>
+      </c>
+      <c r="E659" t="n">
+        <v>609.08</v>
+      </c>
+      <c r="F659" t="n">
+        <v>3335.5</v>
+      </c>
+      <c r="G659" t="n">
+        <v>3357.59</v>
+      </c>
+      <c r="H659" t="n">
+        <v>-22.09</v>
+      </c>
+      <c r="I659" t="n">
+        <v>3285</v>
+      </c>
+      <c r="J659" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K659" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N659" t="n">
+        <v>22.63</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="D660" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="E660" t="n">
+        <v>-37.64</v>
+      </c>
+      <c r="F660" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="G660" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="H660" t="n">
+        <v>-36.84</v>
+      </c>
+      <c r="I660" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="J660" t="n">
+        <v>319.64</v>
+      </c>
+      <c r="K660" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N660" t="n">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>288.7</v>
+      </c>
+      <c r="D661" t="n">
+        <v>277.66</v>
+      </c>
+      <c r="E661" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="F661" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="G661" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="H661" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I661" t="n">
+        <v>283.05</v>
+      </c>
+      <c r="J661" t="n">
+        <v>287.51</v>
+      </c>
+      <c r="K661" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N661" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="D662" t="n">
+        <v>425.37</v>
+      </c>
+      <c r="E662" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="F662" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="G662" t="n">
+        <v>425.37</v>
+      </c>
+      <c r="H662" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="I662" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="J662" t="n">
+        <v>411.99</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N662" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D663" t="n">
+        <v>1820.19</v>
+      </c>
+      <c r="E663" t="n">
+        <v>-20.19</v>
+      </c>
+      <c r="F663" t="n">
+        <v>1808.1</v>
+      </c>
+      <c r="G663" t="n">
+        <v>1821.6</v>
+      </c>
+      <c r="H663" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="I663" t="n">
+        <v>1780.5</v>
+      </c>
+      <c r="J663" t="n">
+        <v>1796.27</v>
+      </c>
+      <c r="K663" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N663" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="D664" t="n">
+        <v>436.48</v>
+      </c>
+      <c r="E664" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="F664" t="n">
+        <v>435.45</v>
+      </c>
+      <c r="G664" t="n">
+        <v>436.48</v>
+      </c>
+      <c r="H664" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="I664" t="n">
+        <v>427.05</v>
+      </c>
+      <c r="J664" t="n">
+        <v>427.75</v>
+      </c>
+      <c r="K664" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N664" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>593.6</v>
+      </c>
+      <c r="D665" t="n">
+        <v>605.21</v>
+      </c>
+      <c r="E665" t="n">
+        <v>-11.61</v>
+      </c>
+      <c r="F665" t="n">
+        <v>610.9</v>
+      </c>
+      <c r="G665" t="n">
+        <v>605.21</v>
+      </c>
+      <c r="H665" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="I665" t="n">
+        <v>592.25</v>
+      </c>
+      <c r="J665" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="K665" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N665" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D666" t="n">
+        <v>967.04</v>
+      </c>
+      <c r="E666" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="F666" t="n">
+        <v>1024.9</v>
+      </c>
+      <c r="G666" t="n">
+        <v>1011.29</v>
+      </c>
+      <c r="H666" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="I666" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J666" t="n">
+        <v>996.67</v>
+      </c>
+      <c r="K666" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N666" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="D667" t="n">
+        <v>191.05</v>
+      </c>
+      <c r="E667" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="F667" t="n">
+        <v>187.03</v>
+      </c>
+      <c r="G667" t="n">
+        <v>191.05</v>
+      </c>
+      <c r="H667" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="I667" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="J667" t="n">
+        <v>178.38</v>
+      </c>
+      <c r="K667" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N667" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="D668" t="n">
+        <v>560.91</v>
+      </c>
+      <c r="E668" t="n">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="F668" t="n">
+        <v>558</v>
+      </c>
+      <c r="G668" t="n">
+        <v>560.91</v>
+      </c>
+      <c r="H668" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="I668" t="n">
+        <v>543.8</v>
+      </c>
+      <c r="J668" t="n">
+        <v>536.84</v>
+      </c>
+      <c r="K668" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N668" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -38267,7 +38943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39692,6 +40368,58 @@
       </c>
       <c r="N27" t="n">
         <v>10.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-37.64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-36.84</v>
+      </c>
+      <c r="I28" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="J28" t="n">
+        <v>319.64</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>10.46</v>
       </c>
     </row>
   </sheetData>
@@ -43083,7 +43811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44456,6 +45184,58 @@
       </c>
       <c r="N26" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="D27" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="F27" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I27" t="n">
+        <v>115.47</v>
+      </c>
+      <c r="J27" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -34528,31 +34528,31 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>116.85</v>
+        <v>115.61</v>
       </c>
       <c r="D656" t="n">
         <v>117.38</v>
       </c>
       <c r="E656" t="n">
-        <v>-0.53</v>
+        <v>-1.77</v>
       </c>
       <c r="F656" t="n">
-        <v>118.2</v>
+        <v>117</v>
       </c>
       <c r="G656" t="n">
         <v>118.35</v>
       </c>
       <c r="H656" t="n">
-        <v>-0.15</v>
+        <v>-1.35</v>
       </c>
       <c r="I656" t="n">
-        <v>115.47</v>
+        <v>115.25</v>
       </c>
       <c r="J656" t="n">
         <v>116.85</v>
       </c>
       <c r="K656" t="n">
-        <v>-1.38</v>
+        <v>-1.6</v>
       </c>
       <c r="L656" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         </is>
       </c>
       <c r="N656" t="n">
-        <v>0.45</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="657">
@@ -34580,31 +34580,31 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>500.3</v>
+        <v>498.95</v>
       </c>
       <c r="D657" t="n">
         <v>511.33</v>
       </c>
       <c r="E657" t="n">
-        <v>-11.03</v>
+        <v>-12.38</v>
       </c>
       <c r="F657" t="n">
-        <v>514.45</v>
+        <v>504.9</v>
       </c>
       <c r="G657" t="n">
         <v>511.33</v>
       </c>
       <c r="H657" t="n">
-        <v>3.12</v>
+        <v>-6.43</v>
       </c>
       <c r="I657" t="n">
-        <v>497.75</v>
+        <v>496</v>
       </c>
       <c r="J657" t="n">
         <v>494.72</v>
       </c>
       <c r="K657" t="n">
-        <v>3.03</v>
+        <v>1.28</v>
       </c>
       <c r="L657" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         </is>
       </c>
       <c r="N657" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="658">
@@ -34632,31 +34632,31 @@
         </is>
       </c>
       <c r="C658" t="n">
-        <v>2194.8</v>
+        <v>2168</v>
       </c>
       <c r="D658" t="n">
         <v>2132.94</v>
       </c>
       <c r="E658" t="n">
-        <v>61.86</v>
+        <v>35.06</v>
       </c>
       <c r="F658" t="n">
-        <v>2194.8</v>
+        <v>2194.9</v>
       </c>
       <c r="G658" t="n">
         <v>2204.11</v>
       </c>
       <c r="H658" t="n">
-        <v>-9.31</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="I658" t="n">
-        <v>2158.4</v>
+        <v>2165</v>
       </c>
       <c r="J658" t="n">
         <v>2172.86</v>
       </c>
       <c r="K658" t="n">
-        <v>-14.46</v>
+        <v>-7.86</v>
       </c>
       <c r="L658" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         </is>
       </c>
       <c r="N658" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="659">
@@ -34684,31 +34684,31 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="D659" t="n">
         <v>2690.92</v>
       </c>
       <c r="E659" t="n">
-        <v>609.08</v>
+        <v>659.08</v>
       </c>
       <c r="F659" t="n">
-        <v>3335.5</v>
+        <v>3398</v>
       </c>
       <c r="G659" t="n">
         <v>3357.59</v>
       </c>
       <c r="H659" t="n">
-        <v>-22.09</v>
+        <v>40.41</v>
       </c>
       <c r="I659" t="n">
-        <v>3285</v>
+        <v>3323.5</v>
       </c>
       <c r="J659" t="n">
         <v>3300</v>
       </c>
       <c r="K659" t="n">
-        <v>-15</v>
+        <v>23.5</v>
       </c>
       <c r="L659" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="N659" t="n">
-        <v>22.63</v>
+        <v>24.49</v>
       </c>
     </row>
     <row r="660">
@@ -34736,31 +34736,31 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>322.1</v>
+        <v>320.6</v>
       </c>
       <c r="D660" t="n">
         <v>359.74</v>
       </c>
       <c r="E660" t="n">
-        <v>-37.64</v>
+        <v>-39.14</v>
       </c>
       <c r="F660" t="n">
-        <v>322.9</v>
+        <v>322.55</v>
       </c>
       <c r="G660" t="n">
         <v>359.74</v>
       </c>
       <c r="H660" t="n">
-        <v>-36.84</v>
+        <v>-37.19</v>
       </c>
       <c r="I660" t="n">
-        <v>317.55</v>
+        <v>318</v>
       </c>
       <c r="J660" t="n">
         <v>319.64</v>
       </c>
       <c r="K660" t="n">
-        <v>-2.09</v>
+        <v>-1.64</v>
       </c>
       <c r="L660" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         </is>
       </c>
       <c r="N660" t="n">
-        <v>10.46</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="661">
@@ -34788,31 +34788,31 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>288.7</v>
+        <v>285.9</v>
       </c>
       <c r="D661" t="n">
         <v>277.66</v>
       </c>
       <c r="E661" t="n">
-        <v>11.04</v>
+        <v>8.24</v>
       </c>
       <c r="F661" t="n">
-        <v>290.7</v>
+        <v>288.5</v>
       </c>
       <c r="G661" t="n">
         <v>291.58</v>
       </c>
       <c r="H661" t="n">
-        <v>-0.88</v>
+        <v>-3.08</v>
       </c>
       <c r="I661" t="n">
-        <v>283.05</v>
+        <v>284.15</v>
       </c>
       <c r="J661" t="n">
         <v>287.51</v>
       </c>
       <c r="K661" t="n">
-        <v>-4.46</v>
+        <v>-3.36</v>
       </c>
       <c r="L661" t="inlineStr">
         <is>
@@ -34821,11 +34821,11 @@
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N661" t="n">
-        <v>3.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="662">
@@ -34840,31 +34840,31 @@
         </is>
       </c>
       <c r="C662" t="n">
-        <v>416.55</v>
+        <v>414</v>
       </c>
       <c r="D662" t="n">
         <v>425.37</v>
       </c>
       <c r="E662" t="n">
-        <v>-8.82</v>
+        <v>-11.37</v>
       </c>
       <c r="F662" t="n">
-        <v>416.55</v>
+        <v>420.65</v>
       </c>
       <c r="G662" t="n">
         <v>425.37</v>
       </c>
       <c r="H662" t="n">
-        <v>-8.82</v>
+        <v>-4.72</v>
       </c>
       <c r="I662" t="n">
-        <v>412.8</v>
+        <v>413.95</v>
       </c>
       <c r="J662" t="n">
         <v>411.99</v>
       </c>
       <c r="K662" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="L662" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="N662" t="n">
-        <v>2.07</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="663">
@@ -34901,22 +34901,22 @@
         <v>-20.19</v>
       </c>
       <c r="F663" t="n">
-        <v>1808.1</v>
+        <v>1814.7</v>
       </c>
       <c r="G663" t="n">
         <v>1821.6</v>
       </c>
       <c r="H663" t="n">
-        <v>-13.5</v>
+        <v>-6.9</v>
       </c>
       <c r="I663" t="n">
-        <v>1780.5</v>
+        <v>1787.5</v>
       </c>
       <c r="J663" t="n">
         <v>1796.27</v>
       </c>
       <c r="K663" t="n">
-        <v>-15.77</v>
+        <v>-8.77</v>
       </c>
       <c r="L663" t="inlineStr">
         <is>
@@ -34944,31 +34944,31 @@
         </is>
       </c>
       <c r="C664" t="n">
-        <v>429.5</v>
+        <v>433.7</v>
       </c>
       <c r="D664" t="n">
         <v>436.48</v>
       </c>
       <c r="E664" t="n">
-        <v>-6.98</v>
+        <v>-2.78</v>
       </c>
       <c r="F664" t="n">
-        <v>435.45</v>
+        <v>436</v>
       </c>
       <c r="G664" t="n">
         <v>436.48</v>
       </c>
       <c r="H664" t="n">
-        <v>-1.03</v>
+        <v>-0.48</v>
       </c>
       <c r="I664" t="n">
-        <v>427.05</v>
+        <v>421.65</v>
       </c>
       <c r="J664" t="n">
         <v>427.75</v>
       </c>
       <c r="K664" t="n">
-        <v>-0.7</v>
+        <v>-6.1</v>
       </c>
       <c r="L664" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="N664" t="n">
-        <v>1.6</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="665">
@@ -34996,31 +34996,31 @@
         </is>
       </c>
       <c r="C665" t="n">
-        <v>593.6</v>
+        <v>605.4</v>
       </c>
       <c r="D665" t="n">
         <v>605.21</v>
       </c>
       <c r="E665" t="n">
-        <v>-11.61</v>
+        <v>0.19</v>
       </c>
       <c r="F665" t="n">
-        <v>610.9</v>
+        <v>608.75</v>
       </c>
       <c r="G665" t="n">
         <v>605.21</v>
       </c>
       <c r="H665" t="n">
-        <v>5.69</v>
+        <v>3.54</v>
       </c>
       <c r="I665" t="n">
-        <v>592.25</v>
+        <v>593.1</v>
       </c>
       <c r="J665" t="n">
         <v>585.5</v>
       </c>
       <c r="K665" t="n">
-        <v>6.75</v>
+        <v>7.6</v>
       </c>
       <c r="L665" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="N665" t="n">
-        <v>1.92</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="666">
@@ -35048,31 +35048,31 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="D666" t="n">
         <v>967.04</v>
       </c>
       <c r="E666" t="n">
-        <v>47.96</v>
+        <v>57.96</v>
       </c>
       <c r="F666" t="n">
-        <v>1024.9</v>
+        <v>1049.6</v>
       </c>
       <c r="G666" t="n">
         <v>1011.29</v>
       </c>
       <c r="H666" t="n">
-        <v>13.61</v>
+        <v>38.31</v>
       </c>
       <c r="I666" t="n">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="J666" t="n">
         <v>996.67</v>
       </c>
       <c r="K666" t="n">
-        <v>11.33</v>
+        <v>22.33</v>
       </c>
       <c r="L666" t="inlineStr">
         <is>
@@ -35081,11 +35081,11 @@
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N666" t="n">
-        <v>4.96</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="667">
@@ -35100,31 +35100,31 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>183.75</v>
+        <v>186.4</v>
       </c>
       <c r="D667" t="n">
         <v>191.05</v>
       </c>
       <c r="E667" t="n">
-        <v>-7.3</v>
+        <v>-4.65</v>
       </c>
       <c r="F667" t="n">
-        <v>187.03</v>
+        <v>189.4</v>
       </c>
       <c r="G667" t="n">
         <v>191.05</v>
       </c>
       <c r="H667" t="n">
-        <v>-4.02</v>
+        <v>-1.65</v>
       </c>
       <c r="I667" t="n">
-        <v>183.1</v>
+        <v>185.36</v>
       </c>
       <c r="J667" t="n">
         <v>178.38</v>
       </c>
       <c r="K667" t="n">
-        <v>4.72</v>
+        <v>6.98</v>
       </c>
       <c r="L667" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         </is>
       </c>
       <c r="N667" t="n">
-        <v>3.82</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="668">
@@ -35152,31 +35152,31 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>552.3</v>
+        <v>555</v>
       </c>
       <c r="D668" t="n">
         <v>560.91</v>
       </c>
       <c r="E668" t="n">
-        <v>-8.609999999999999</v>
+        <v>-5.91</v>
       </c>
       <c r="F668" t="n">
-        <v>558</v>
+        <v>564.75</v>
       </c>
       <c r="G668" t="n">
         <v>560.91</v>
       </c>
       <c r="H668" t="n">
-        <v>-2.91</v>
+        <v>3.84</v>
       </c>
       <c r="I668" t="n">
-        <v>543.8</v>
+        <v>550.45</v>
       </c>
       <c r="J668" t="n">
         <v>536.84</v>
       </c>
       <c r="K668" t="n">
-        <v>6.96</v>
+        <v>13.61</v>
       </c>
       <c r="L668" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         </is>
       </c>
       <c r="N668" t="n">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
     </row>
   </sheetData>
@@ -40382,31 +40382,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>322.1</v>
+        <v>320.6</v>
       </c>
       <c r="D28" t="n">
         <v>359.74</v>
       </c>
       <c r="E28" t="n">
-        <v>-37.64</v>
+        <v>-39.14</v>
       </c>
       <c r="F28" t="n">
-        <v>322.9</v>
+        <v>322.55</v>
       </c>
       <c r="G28" t="n">
         <v>359.74</v>
       </c>
       <c r="H28" t="n">
-        <v>-36.84</v>
+        <v>-37.19</v>
       </c>
       <c r="I28" t="n">
-        <v>317.55</v>
+        <v>318</v>
       </c>
       <c r="J28" t="n">
         <v>319.64</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.09</v>
+        <v>-1.64</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>10.46</v>
+        <v>10.88</v>
       </c>
     </row>
   </sheetData>
@@ -45198,31 +45198,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>116.85</v>
+        <v>115.61</v>
       </c>
       <c r="D27" t="n">
         <v>117.38</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.53</v>
+        <v>-1.77</v>
       </c>
       <c r="F27" t="n">
-        <v>118.2</v>
+        <v>117</v>
       </c>
       <c r="G27" t="n">
         <v>118.35</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.15</v>
+        <v>-1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>115.47</v>
+        <v>115.25</v>
       </c>
       <c r="J27" t="n">
         <v>116.85</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.38</v>
+        <v>-1.6</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.45</v>
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N668"/>
+  <dimension ref="A1:N679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35190,6 +35190,578 @@
       </c>
       <c r="N668" t="n">
         <v>1.05</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="D669" t="n">
+        <v>481.77</v>
+      </c>
+      <c r="E669" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="F669" t="n">
+        <v>511.95</v>
+      </c>
+      <c r="G669" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="H669" t="n">
+        <v>12</v>
+      </c>
+      <c r="I669" t="n">
+        <v>485.4</v>
+      </c>
+      <c r="J669" t="n">
+        <v>483.03</v>
+      </c>
+      <c r="K669" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N669" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="D670" t="n">
+        <v>290.61</v>
+      </c>
+      <c r="E670" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="F670" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="G670" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="H670" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="I670" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="J670" t="n">
+        <v>318.54</v>
+      </c>
+      <c r="K670" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N670" t="n">
+        <v>11.32</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>3276</v>
+      </c>
+      <c r="D671" t="n">
+        <v>4111.02</v>
+      </c>
+      <c r="E671" t="n">
+        <v>-835.02</v>
+      </c>
+      <c r="F671" t="n">
+        <v>3389</v>
+      </c>
+      <c r="G671" t="n">
+        <v>4111.02</v>
+      </c>
+      <c r="H671" t="n">
+        <v>-722.02</v>
+      </c>
+      <c r="I671" t="n">
+        <v>3247.2</v>
+      </c>
+      <c r="J671" t="n">
+        <v>3250.46</v>
+      </c>
+      <c r="K671" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N671" t="n">
+        <v>20.31</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>1026.5</v>
+      </c>
+      <c r="D672" t="n">
+        <v>1096.73</v>
+      </c>
+      <c r="E672" t="n">
+        <v>-70.23</v>
+      </c>
+      <c r="F672" t="n">
+        <v>1030.7</v>
+      </c>
+      <c r="G672" t="n">
+        <v>1096.73</v>
+      </c>
+      <c r="H672" t="n">
+        <v>-66.03</v>
+      </c>
+      <c r="I672" t="n">
+        <v>988</v>
+      </c>
+      <c r="J672" t="n">
+        <v>1008.14</v>
+      </c>
+      <c r="K672" t="n">
+        <v>-20.14</v>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N672" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>431</v>
+      </c>
+      <c r="D673" t="n">
+        <v>431.93</v>
+      </c>
+      <c r="E673" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="F673" t="n">
+        <v>433</v>
+      </c>
+      <c r="G673" t="n">
+        <v>443.61</v>
+      </c>
+      <c r="H673" t="n">
+        <v>-10.61</v>
+      </c>
+      <c r="I673" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="J673" t="n">
+        <v>428.71</v>
+      </c>
+      <c r="K673" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N673" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2153.5</v>
+      </c>
+      <c r="D674" t="n">
+        <v>2206.42</v>
+      </c>
+      <c r="E674" t="n">
+        <v>-52.92</v>
+      </c>
+      <c r="F674" t="n">
+        <v>2176.2</v>
+      </c>
+      <c r="G674" t="n">
+        <v>2208.74</v>
+      </c>
+      <c r="H674" t="n">
+        <v>-32.54</v>
+      </c>
+      <c r="I674" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="J674" t="n">
+        <v>2134.32</v>
+      </c>
+      <c r="K674" t="n">
+        <v>-24.52</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N674" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>419</v>
+      </c>
+      <c r="D675" t="n">
+        <v>411.06</v>
+      </c>
+      <c r="E675" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F675" t="n">
+        <v>420</v>
+      </c>
+      <c r="G675" t="n">
+        <v>427.73</v>
+      </c>
+      <c r="H675" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="I675" t="n">
+        <v>409.25</v>
+      </c>
+      <c r="J675" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="K675" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N675" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="D676" t="n">
+        <v>298.09</v>
+      </c>
+      <c r="E676" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="F676" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="G676" t="n">
+        <v>298.09</v>
+      </c>
+      <c r="H676" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="I676" t="n">
+        <v>283.85</v>
+      </c>
+      <c r="J676" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="K676" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N676" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="D677" t="n">
+        <v>115.91</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F677" t="n">
+        <v>117.79</v>
+      </c>
+      <c r="G677" t="n">
+        <v>119.84</v>
+      </c>
+      <c r="H677" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I677" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="J677" t="n">
+        <v>115.81</v>
+      </c>
+      <c r="K677" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N677" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="D678" t="n">
+        <v>561.42</v>
+      </c>
+      <c r="E678" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F678" t="n">
+        <v>572.35</v>
+      </c>
+      <c r="G678" t="n">
+        <v>566.25</v>
+      </c>
+      <c r="H678" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I678" t="n">
+        <v>546</v>
+      </c>
+      <c r="J678" t="n">
+        <v>546.8</v>
+      </c>
+      <c r="K678" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N678" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>1797.3</v>
+      </c>
+      <c r="D679" t="n">
+        <v>1791.59</v>
+      </c>
+      <c r="E679" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F679" t="n">
+        <v>1813.3</v>
+      </c>
+      <c r="G679" t="n">
+        <v>1843.08</v>
+      </c>
+      <c r="H679" t="n">
+        <v>-29.78</v>
+      </c>
+      <c r="I679" t="n">
+        <v>1757.3</v>
+      </c>
+      <c r="J679" t="n">
+        <v>1780.96</v>
+      </c>
+      <c r="K679" t="n">
+        <v>-23.66</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N679" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -38943,7 +39515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40420,6 +40992,58 @@
       </c>
       <c r="N28" t="n">
         <v>10.88</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>290.61</v>
+      </c>
+      <c r="E29" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="F29" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="J29" t="n">
+        <v>318.54</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>11.32</v>
       </c>
     </row>
   </sheetData>
@@ -43811,7 +44435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45236,6 +45860,58 @@
       </c>
       <c r="N27" t="n">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="D28" t="n">
+        <v>115.91</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F28" t="n">
+        <v>117.79</v>
+      </c>
+      <c r="G28" t="n">
+        <v>119.84</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I28" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="J28" t="n">
+        <v>115.81</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -35204,31 +35204,31 @@
         </is>
       </c>
       <c r="C669" t="n">
-        <v>489.8</v>
+        <v>500.3</v>
       </c>
       <c r="D669" t="n">
         <v>481.77</v>
       </c>
       <c r="E669" t="n">
-        <v>8.029999999999999</v>
+        <v>18.53</v>
       </c>
       <c r="F669" t="n">
-        <v>511.95</v>
+        <v>514.45</v>
       </c>
       <c r="G669" t="n">
         <v>499.95</v>
       </c>
       <c r="H669" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="I669" t="n">
-        <v>485.4</v>
+        <v>497.75</v>
       </c>
       <c r="J669" t="n">
         <v>483.03</v>
       </c>
       <c r="K669" t="n">
-        <v>2.37</v>
+        <v>14.72</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -35237,11 +35237,11 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N669" t="n">
-        <v>1.67</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="670">
@@ -35256,31 +35256,31 @@
         </is>
       </c>
       <c r="C670" t="n">
-        <v>323.5</v>
+        <v>322.1</v>
       </c>
       <c r="D670" t="n">
         <v>290.61</v>
       </c>
       <c r="E670" t="n">
-        <v>32.89</v>
+        <v>31.49</v>
       </c>
       <c r="F670" t="n">
-        <v>324.8</v>
+        <v>322.9</v>
       </c>
       <c r="G670" t="n">
         <v>329.72</v>
       </c>
       <c r="H670" t="n">
-        <v>-4.92</v>
+        <v>-6.82</v>
       </c>
       <c r="I670" t="n">
-        <v>316.05</v>
+        <v>317.55</v>
       </c>
       <c r="J670" t="n">
         <v>318.54</v>
       </c>
       <c r="K670" t="n">
-        <v>-2.49</v>
+        <v>-0.99</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         </is>
       </c>
       <c r="N670" t="n">
-        <v>11.32</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="671">
@@ -35308,31 +35308,31 @@
         </is>
       </c>
       <c r="C671" t="n">
-        <v>3276</v>
+        <v>3300</v>
       </c>
       <c r="D671" t="n">
         <v>4111.02</v>
       </c>
       <c r="E671" t="n">
-        <v>-835.02</v>
+        <v>-811.02</v>
       </c>
       <c r="F671" t="n">
-        <v>3389</v>
+        <v>3335.5</v>
       </c>
       <c r="G671" t="n">
         <v>4111.02</v>
       </c>
       <c r="H671" t="n">
-        <v>-722.02</v>
+        <v>-775.52</v>
       </c>
       <c r="I671" t="n">
-        <v>3247.2</v>
+        <v>3285</v>
       </c>
       <c r="J671" t="n">
         <v>3250.46</v>
       </c>
       <c r="K671" t="n">
-        <v>-3.26</v>
+        <v>34.54</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         </is>
       </c>
       <c r="N671" t="n">
-        <v>20.31</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="672">
@@ -35360,31 +35360,31 @@
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1026.5</v>
+        <v>1015</v>
       </c>
       <c r="D672" t="n">
         <v>1096.73</v>
       </c>
       <c r="E672" t="n">
-        <v>-70.23</v>
+        <v>-81.73</v>
       </c>
       <c r="F672" t="n">
-        <v>1030.7</v>
+        <v>1024.9</v>
       </c>
       <c r="G672" t="n">
         <v>1096.73</v>
       </c>
       <c r="H672" t="n">
-        <v>-66.03</v>
+        <v>-71.83</v>
       </c>
       <c r="I672" t="n">
-        <v>988</v>
+        <v>1008</v>
       </c>
       <c r="J672" t="n">
         <v>1008.14</v>
       </c>
       <c r="K672" t="n">
-        <v>-20.14</v>
+        <v>-0.14</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -35393,11 +35393,11 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.4</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="673">
@@ -35412,31 +35412,31 @@
         </is>
       </c>
       <c r="C673" t="n">
-        <v>431</v>
+        <v>429.5</v>
       </c>
       <c r="D673" t="n">
         <v>431.93</v>
       </c>
       <c r="E673" t="n">
-        <v>-0.93</v>
+        <v>-2.43</v>
       </c>
       <c r="F673" t="n">
-        <v>433</v>
+        <v>435.45</v>
       </c>
       <c r="G673" t="n">
         <v>443.61</v>
       </c>
       <c r="H673" t="n">
-        <v>-10.61</v>
+        <v>-8.16</v>
       </c>
       <c r="I673" t="n">
-        <v>418.2</v>
+        <v>427.05</v>
       </c>
       <c r="J673" t="n">
         <v>428.71</v>
       </c>
       <c r="K673" t="n">
-        <v>-10.51</v>
+        <v>-1.66</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         </is>
       </c>
       <c r="N673" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="674">
@@ -35464,31 +35464,31 @@
         </is>
       </c>
       <c r="C674" t="n">
-        <v>2153.5</v>
+        <v>2194.8</v>
       </c>
       <c r="D674" t="n">
         <v>2206.42</v>
       </c>
       <c r="E674" t="n">
-        <v>-52.92</v>
+        <v>-11.62</v>
       </c>
       <c r="F674" t="n">
-        <v>2176.2</v>
+        <v>2194.8</v>
       </c>
       <c r="G674" t="n">
         <v>2208.74</v>
       </c>
       <c r="H674" t="n">
-        <v>-32.54</v>
+        <v>-13.94</v>
       </c>
       <c r="I674" t="n">
-        <v>2109.8</v>
+        <v>2158.4</v>
       </c>
       <c r="J674" t="n">
         <v>2134.32</v>
       </c>
       <c r="K674" t="n">
-        <v>-24.52</v>
+        <v>24.08</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>2.4</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="675">
@@ -35516,31 +35516,31 @@
         </is>
       </c>
       <c r="C675" t="n">
-        <v>419</v>
+        <v>416.55</v>
       </c>
       <c r="D675" t="n">
         <v>411.06</v>
       </c>
       <c r="E675" t="n">
-        <v>7.94</v>
+        <v>5.49</v>
       </c>
       <c r="F675" t="n">
-        <v>420</v>
+        <v>416.55</v>
       </c>
       <c r="G675" t="n">
         <v>427.73</v>
       </c>
       <c r="H675" t="n">
-        <v>-7.73</v>
+        <v>-11.18</v>
       </c>
       <c r="I675" t="n">
-        <v>409.25</v>
+        <v>412.8</v>
       </c>
       <c r="J675" t="n">
         <v>413.26</v>
       </c>
       <c r="K675" t="n">
-        <v>-4.01</v>
+        <v>-0.46</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="676">
@@ -35568,31 +35568,31 @@
         </is>
       </c>
       <c r="C676" t="n">
-        <v>287.2</v>
+        <v>288.7</v>
       </c>
       <c r="D676" t="n">
         <v>298.09</v>
       </c>
       <c r="E676" t="n">
-        <v>-10.89</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="F676" t="n">
-        <v>287.2</v>
+        <v>290.7</v>
       </c>
       <c r="G676" t="n">
         <v>298.09</v>
       </c>
       <c r="H676" t="n">
-        <v>-10.89</v>
+        <v>-7.39</v>
       </c>
       <c r="I676" t="n">
-        <v>283.85</v>
+        <v>283.05</v>
       </c>
       <c r="J676" t="n">
         <v>282.6</v>
       </c>
       <c r="K676" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         </is>
       </c>
       <c r="N676" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="677">
@@ -35620,31 +35620,31 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>116.75</v>
+        <v>116.85</v>
       </c>
       <c r="D677" t="n">
         <v>115.91</v>
       </c>
       <c r="E677" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F677" t="n">
-        <v>117.79</v>
+        <v>118.2</v>
       </c>
       <c r="G677" t="n">
         <v>119.84</v>
       </c>
       <c r="H677" t="n">
-        <v>-2.05</v>
+        <v>-1.64</v>
       </c>
       <c r="I677" t="n">
-        <v>114.52</v>
+        <v>115.47</v>
       </c>
       <c r="J677" t="n">
         <v>115.81</v>
       </c>
       <c r="K677" t="n">
-        <v>-1.29</v>
+        <v>-0.34</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         </is>
       </c>
       <c r="N677" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="678">
@@ -35672,31 +35672,31 @@
         </is>
       </c>
       <c r="C678" t="n">
-        <v>562.9</v>
+        <v>552.3</v>
       </c>
       <c r="D678" t="n">
         <v>561.42</v>
       </c>
       <c r="E678" t="n">
-        <v>1.48</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="F678" t="n">
-        <v>572.35</v>
+        <v>558</v>
       </c>
       <c r="G678" t="n">
         <v>566.25</v>
       </c>
       <c r="H678" t="n">
-        <v>6.1</v>
+        <v>-8.25</v>
       </c>
       <c r="I678" t="n">
-        <v>546</v>
+        <v>543.8</v>
       </c>
       <c r="J678" t="n">
         <v>546.8</v>
       </c>
       <c r="K678" t="n">
-        <v>-0.8</v>
+        <v>-3</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="N678" t="n">
-        <v>0.26</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="679">
@@ -35724,31 +35724,31 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>1797.3</v>
+        <v>1800</v>
       </c>
       <c r="D679" t="n">
         <v>1791.59</v>
       </c>
       <c r="E679" t="n">
-        <v>5.71</v>
+        <v>8.41</v>
       </c>
       <c r="F679" t="n">
-        <v>1813.3</v>
+        <v>1808.1</v>
       </c>
       <c r="G679" t="n">
         <v>1843.08</v>
       </c>
       <c r="H679" t="n">
-        <v>-29.78</v>
+        <v>-34.98</v>
       </c>
       <c r="I679" t="n">
-        <v>1757.3</v>
+        <v>1780.5</v>
       </c>
       <c r="J679" t="n">
         <v>1780.96</v>
       </c>
       <c r="K679" t="n">
-        <v>-23.66</v>
+        <v>-0.46</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         </is>
       </c>
       <c r="N679" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -41006,31 +41006,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>323.5</v>
+        <v>322.1</v>
       </c>
       <c r="D29" t="n">
         <v>290.61</v>
       </c>
       <c r="E29" t="n">
-        <v>32.89</v>
+        <v>31.49</v>
       </c>
       <c r="F29" t="n">
-        <v>324.8</v>
+        <v>322.9</v>
       </c>
       <c r="G29" t="n">
         <v>329.72</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.92</v>
+        <v>-6.82</v>
       </c>
       <c r="I29" t="n">
-        <v>316.05</v>
+        <v>317.55</v>
       </c>
       <c r="J29" t="n">
         <v>318.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.49</v>
+        <v>-0.99</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>11.32</v>
+        <v>10.84</v>
       </c>
     </row>
   </sheetData>
@@ -45874,31 +45874,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>116.75</v>
+        <v>116.85</v>
       </c>
       <c r="D28" t="n">
         <v>115.91</v>
       </c>
       <c r="E28" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>117.79</v>
+        <v>118.2</v>
       </c>
       <c r="G28" t="n">
         <v>119.84</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.05</v>
+        <v>-1.64</v>
       </c>
       <c r="I28" t="n">
-        <v>114.52</v>
+        <v>115.47</v>
       </c>
       <c r="J28" t="n">
         <v>115.81</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.29</v>
+        <v>-0.34</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -35200,35 +35200,35 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>500.3</v>
+        <v>323.5</v>
       </c>
       <c r="D669" t="n">
-        <v>481.77</v>
+        <v>361.43</v>
       </c>
       <c r="E669" t="n">
-        <v>18.53</v>
+        <v>-37.93</v>
       </c>
       <c r="F669" t="n">
-        <v>514.45</v>
+        <v>324.8</v>
       </c>
       <c r="G669" t="n">
-        <v>499.95</v>
+        <v>361.43</v>
       </c>
       <c r="H669" t="n">
-        <v>14.5</v>
+        <v>-36.63</v>
       </c>
       <c r="I669" t="n">
-        <v>497.75</v>
+        <v>316.05</v>
       </c>
       <c r="J669" t="n">
-        <v>483.03</v>
+        <v>318.96</v>
       </c>
       <c r="K669" t="n">
-        <v>14.72</v>
+        <v>-2.91</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -35237,11 +35237,11 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N669" t="n">
-        <v>3.85</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="670">
@@ -35252,35 +35252,35 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>322.1</v>
+        <v>489.8</v>
       </c>
       <c r="D670" t="n">
-        <v>290.61</v>
+        <v>512.71</v>
       </c>
       <c r="E670" t="n">
-        <v>31.49</v>
+        <v>-22.91</v>
       </c>
       <c r="F670" t="n">
-        <v>322.9</v>
+        <v>511.95</v>
       </c>
       <c r="G670" t="n">
-        <v>329.72</v>
+        <v>512.71</v>
       </c>
       <c r="H670" t="n">
-        <v>-6.82</v>
+        <v>-0.76</v>
       </c>
       <c r="I670" t="n">
-        <v>317.55</v>
+        <v>485.4</v>
       </c>
       <c r="J670" t="n">
-        <v>318.54</v>
+        <v>483.68</v>
       </c>
       <c r="K670" t="n">
-        <v>-0.99</v>
+        <v>1.72</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         </is>
       </c>
       <c r="N670" t="n">
-        <v>10.84</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="671">
@@ -35308,31 +35308,31 @@
         </is>
       </c>
       <c r="C671" t="n">
-        <v>3300</v>
+        <v>3276</v>
       </c>
       <c r="D671" t="n">
-        <v>4111.02</v>
+        <v>2650.75</v>
       </c>
       <c r="E671" t="n">
-        <v>-811.02</v>
+        <v>625.25</v>
       </c>
       <c r="F671" t="n">
-        <v>3335.5</v>
+        <v>3389</v>
       </c>
       <c r="G671" t="n">
-        <v>4111.02</v>
+        <v>3293.11</v>
       </c>
       <c r="H671" t="n">
-        <v>-775.52</v>
+        <v>95.89</v>
       </c>
       <c r="I671" t="n">
-        <v>3285</v>
+        <v>3247.2</v>
       </c>
       <c r="J671" t="n">
-        <v>3250.46</v>
+        <v>3254.88</v>
       </c>
       <c r="K671" t="n">
-        <v>34.54</v>
+        <v>-7.68</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -35341,11 +35341,11 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N671" t="n">
-        <v>19.73</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="672">
@@ -35360,31 +35360,31 @@
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1015</v>
+        <v>1026.5</v>
       </c>
       <c r="D672" t="n">
-        <v>1096.73</v>
+        <v>957.6</v>
       </c>
       <c r="E672" t="n">
-        <v>-81.73</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F672" t="n">
-        <v>1024.9</v>
+        <v>1030.7</v>
       </c>
       <c r="G672" t="n">
-        <v>1096.73</v>
+        <v>1021.74</v>
       </c>
       <c r="H672" t="n">
-        <v>-71.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I672" t="n">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="J672" t="n">
-        <v>1008.14</v>
+        <v>1009.53</v>
       </c>
       <c r="K672" t="n">
-        <v>-0.14</v>
+        <v>-21.53</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -35393,11 +35393,11 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.45</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="673">
@@ -35408,35 +35408,35 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>429.5</v>
+        <v>2153.5</v>
       </c>
       <c r="D673" t="n">
-        <v>431.93</v>
+        <v>2159.29</v>
       </c>
       <c r="E673" t="n">
-        <v>-2.43</v>
+        <v>-5.79</v>
       </c>
       <c r="F673" t="n">
-        <v>435.45</v>
+        <v>2176.2</v>
       </c>
       <c r="G673" t="n">
-        <v>443.61</v>
+        <v>2162.34</v>
       </c>
       <c r="H673" t="n">
-        <v>-8.16</v>
+        <v>13.86</v>
       </c>
       <c r="I673" t="n">
-        <v>427.05</v>
+        <v>2109.8</v>
       </c>
       <c r="J673" t="n">
-        <v>428.71</v>
+        <v>2137.15</v>
       </c>
       <c r="K673" t="n">
-        <v>-1.66</v>
+        <v>-27.35</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         </is>
       </c>
       <c r="N673" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="674">
@@ -35460,35 +35460,35 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>2194.8</v>
+        <v>431</v>
       </c>
       <c r="D674" t="n">
-        <v>2206.42</v>
+        <v>432.25</v>
       </c>
       <c r="E674" t="n">
-        <v>-11.62</v>
+        <v>-1.25</v>
       </c>
       <c r="F674" t="n">
-        <v>2194.8</v>
+        <v>433</v>
       </c>
       <c r="G674" t="n">
-        <v>2208.74</v>
+        <v>434.29</v>
       </c>
       <c r="H674" t="n">
-        <v>-13.94</v>
+        <v>-1.29</v>
       </c>
       <c r="I674" t="n">
-        <v>2158.4</v>
+        <v>418.2</v>
       </c>
       <c r="J674" t="n">
-        <v>2134.32</v>
+        <v>429.28</v>
       </c>
       <c r="K674" t="n">
-        <v>24.08</v>
+        <v>-11.08</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>0.53</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="675">
@@ -35512,35 +35512,35 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>416.55</v>
+        <v>116.75</v>
       </c>
       <c r="D675" t="n">
-        <v>411.06</v>
+        <v>118.63</v>
       </c>
       <c r="E675" t="n">
-        <v>5.49</v>
+        <v>-1.88</v>
       </c>
       <c r="F675" t="n">
-        <v>416.55</v>
+        <v>117.79</v>
       </c>
       <c r="G675" t="n">
-        <v>427.73</v>
+        <v>118.63</v>
       </c>
       <c r="H675" t="n">
-        <v>-11.18</v>
+        <v>-0.84</v>
       </c>
       <c r="I675" t="n">
-        <v>412.8</v>
+        <v>114.52</v>
       </c>
       <c r="J675" t="n">
-        <v>413.26</v>
+        <v>115.96</v>
       </c>
       <c r="K675" t="n">
-        <v>-0.46</v>
+        <v>-1.44</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="676">
@@ -35564,35 +35564,35 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>288.7</v>
+        <v>419</v>
       </c>
       <c r="D676" t="n">
-        <v>298.09</v>
+        <v>427.99</v>
       </c>
       <c r="E676" t="n">
-        <v>-9.390000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="F676" t="n">
-        <v>290.7</v>
+        <v>420</v>
       </c>
       <c r="G676" t="n">
-        <v>298.09</v>
+        <v>427.99</v>
       </c>
       <c r="H676" t="n">
-        <v>-7.39</v>
+        <v>-7.99</v>
       </c>
       <c r="I676" t="n">
-        <v>283.05</v>
+        <v>409.25</v>
       </c>
       <c r="J676" t="n">
-        <v>282.6</v>
+        <v>413.81</v>
       </c>
       <c r="K676" t="n">
-        <v>0.45</v>
+        <v>-4.56</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         </is>
       </c>
       <c r="N676" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="677">
@@ -35616,35 +35616,35 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>116.85</v>
+        <v>287.2</v>
       </c>
       <c r="D677" t="n">
-        <v>115.91</v>
+        <v>280.38</v>
       </c>
       <c r="E677" t="n">
-        <v>0.9399999999999999</v>
+        <v>6.82</v>
       </c>
       <c r="F677" t="n">
-        <v>118.2</v>
+        <v>287.2</v>
       </c>
       <c r="G677" t="n">
-        <v>119.84</v>
+        <v>286.38</v>
       </c>
       <c r="H677" t="n">
-        <v>-1.64</v>
+        <v>0.82</v>
       </c>
       <c r="I677" t="n">
-        <v>115.47</v>
+        <v>283.85</v>
       </c>
       <c r="J677" t="n">
-        <v>115.81</v>
+        <v>282.97</v>
       </c>
       <c r="K677" t="n">
-        <v>-0.34</v>
+        <v>0.88</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         </is>
       </c>
       <c r="N677" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="678">
@@ -35668,35 +35668,35 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>552.3</v>
+        <v>1797.3</v>
       </c>
       <c r="D678" t="n">
-        <v>561.42</v>
+        <v>1820.18</v>
       </c>
       <c r="E678" t="n">
-        <v>-9.119999999999999</v>
+        <v>-22.88</v>
       </c>
       <c r="F678" t="n">
-        <v>558</v>
+        <v>1813.3</v>
       </c>
       <c r="G678" t="n">
-        <v>566.25</v>
+        <v>1820.18</v>
       </c>
       <c r="H678" t="n">
-        <v>-8.25</v>
+        <v>-6.88</v>
       </c>
       <c r="I678" t="n">
-        <v>543.8</v>
+        <v>1757.3</v>
       </c>
       <c r="J678" t="n">
-        <v>546.8</v>
+        <v>1783.33</v>
       </c>
       <c r="K678" t="n">
-        <v>-3</v>
+        <v>-26.03</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="N678" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="679">
@@ -35720,35 +35720,35 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>1800</v>
+        <v>562.9</v>
       </c>
       <c r="D679" t="n">
-        <v>1791.59</v>
+        <v>558.1900000000001</v>
       </c>
       <c r="E679" t="n">
-        <v>8.41</v>
+        <v>4.71</v>
       </c>
       <c r="F679" t="n">
-        <v>1808.1</v>
+        <v>572.35</v>
       </c>
       <c r="G679" t="n">
-        <v>1843.08</v>
+        <v>558.1900000000001</v>
       </c>
       <c r="H679" t="n">
-        <v>-34.98</v>
+        <v>14.16</v>
       </c>
       <c r="I679" t="n">
-        <v>1780.5</v>
+        <v>546</v>
       </c>
       <c r="J679" t="n">
-        <v>1780.96</v>
+        <v>547.52</v>
       </c>
       <c r="K679" t="n">
-        <v>-0.46</v>
+        <v>-1.52</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         </is>
       </c>
       <c r="N679" t="n">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -41006,31 +41006,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>322.1</v>
+        <v>323.5</v>
       </c>
       <c r="D29" t="n">
-        <v>290.61</v>
+        <v>361.43</v>
       </c>
       <c r="E29" t="n">
-        <v>31.49</v>
+        <v>-37.93</v>
       </c>
       <c r="F29" t="n">
-        <v>322.9</v>
+        <v>324.8</v>
       </c>
       <c r="G29" t="n">
-        <v>329.72</v>
+        <v>361.43</v>
       </c>
       <c r="H29" t="n">
-        <v>-6.82</v>
+        <v>-36.63</v>
       </c>
       <c r="I29" t="n">
-        <v>317.55</v>
+        <v>316.05</v>
       </c>
       <c r="J29" t="n">
-        <v>318.54</v>
+        <v>318.96</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.99</v>
+        <v>-2.91</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>10.84</v>
+        <v>10.49</v>
       </c>
     </row>
   </sheetData>
@@ -45874,31 +45874,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>116.85</v>
+        <v>116.75</v>
       </c>
       <c r="D28" t="n">
-        <v>115.91</v>
+        <v>118.63</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.88</v>
       </c>
       <c r="F28" t="n">
-        <v>118.2</v>
+        <v>117.79</v>
       </c>
       <c r="G28" t="n">
-        <v>119.84</v>
+        <v>118.63</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.64</v>
+        <v>-0.84</v>
       </c>
       <c r="I28" t="n">
-        <v>115.47</v>
+        <v>114.52</v>
       </c>
       <c r="J28" t="n">
-        <v>115.81</v>
+        <v>115.96</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.34</v>
+        <v>-1.44</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
